--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="49">
+  <fonts count="50">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -353,8 +353,14 @@
       <color rgb="005D4037"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00B71C1C"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="72">
+  <fills count="73">
     <fill>
       <patternFill/>
     </fill>
@@ -772,6 +778,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1073,7 +1084,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1278,6 +1289,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="71" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="72" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1692,7 +1706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W60"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1954,44 +1968,40 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G4" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G4" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H4" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I4" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J4" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K4" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L4" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M4" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M4" s="69" t="inlineStr"/>
+      <c r="N4" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N4" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O4" s="69" t="inlineStr"/>
@@ -2002,254 +2012,250 @@
       <c r="T4" s="69" t="inlineStr"/>
       <c r="U4" s="69" t="inlineStr"/>
       <c r="V4" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W4" s="69" t="inlineStr"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B5" s="63" t="inlineStr"/>
+      <c r="C5" s="64" t="inlineStr"/>
+      <c r="D5" s="64" t="inlineStr"/>
+      <c r="E5" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G5" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H5" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L5" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N5" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O5" s="69" t="inlineStr"/>
+      <c r="P5" s="69" t="inlineStr"/>
+      <c r="Q5" s="69" t="inlineStr"/>
+      <c r="R5" s="69" t="inlineStr"/>
+      <c r="S5" s="69" t="inlineStr"/>
+      <c r="T5" s="69" t="inlineStr"/>
+      <c r="U5" s="69" t="inlineStr"/>
+      <c r="V5" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W4" s="69" t="inlineStr"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="W5" s="69" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C5" s="38" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D5" s="38" t="inlineStr">
+      <c r="D6" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E5" s="39" t="n">
+      <c r="E6" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F5" s="39" t="n">
+      <c r="F6" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G5" s="40" t="n">
+      <c r="G6" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H5" s="41" t="n">
+      <c r="H6" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I5" s="41" t="n">
+      <c r="I6" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="42" t="n">
+      <c r="J6" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K5" s="42" t="n">
+      <c r="K6" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L5" s="42" t="n">
+      <c r="L6" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M5" s="43" t="inlineStr">
+      <c r="M6" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N5" s="43" t="inlineStr"/>
-      <c r="O5" s="43" t="inlineStr">
+      <c r="N6" s="43" t="inlineStr"/>
+      <c r="O6" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P5" s="43" t="inlineStr"/>
-      <c r="Q5" s="43" t="inlineStr"/>
-      <c r="R5" s="43" t="inlineStr"/>
-      <c r="S5" s="43" t="inlineStr"/>
-      <c r="T5" s="43" t="inlineStr"/>
-      <c r="U5" s="43" t="inlineStr"/>
-      <c r="V5" s="43" t="n">
+      <c r="P6" s="43" t="inlineStr"/>
+      <c r="Q6" s="43" t="inlineStr"/>
+      <c r="R6" s="43" t="inlineStr"/>
+      <c r="S6" s="43" t="inlineStr"/>
+      <c r="T6" s="43" t="inlineStr"/>
+      <c r="U6" s="43" t="inlineStr"/>
+      <c r="V6" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W5" s="43" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B6" s="45" t="n"/>
-      <c r="C6" s="46" t="n"/>
-      <c r="D6" s="46" t="n"/>
-      <c r="E6" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F6" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G6" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H6" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K6" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L6" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M6" s="51" t="n"/>
-      <c r="N6" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O6" s="51" t="n"/>
-      <c r="P6" s="51" t="n"/>
-      <c r="Q6" s="51" t="n"/>
-      <c r="R6" s="51" t="n"/>
-      <c r="S6" s="51" t="n"/>
-      <c r="T6" s="51" t="n"/>
-      <c r="U6" s="51" t="n"/>
-      <c r="V6" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W6" s="43" t="inlineStr"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B7" s="45" t="n"/>
-      <c r="C7" s="53" t="n"/>
-      <c r="D7" s="53" t="n"/>
+      <c r="C7" s="46" t="n"/>
+      <c r="D7" s="46" t="n"/>
       <c r="E7" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F7" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G7" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G7" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H7" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I7" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J7" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K7" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L7" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N7" s="55" t="n"/>
-      <c r="O7" s="55" t="n"/>
-      <c r="P7" s="55" t="n"/>
-      <c r="Q7" s="55" t="n"/>
-      <c r="R7" s="55" t="n"/>
-      <c r="S7" s="55" t="n"/>
-      <c r="T7" s="55" t="n"/>
-      <c r="U7" s="55" t="n"/>
-      <c r="V7" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W7" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M7" s="51" t="n"/>
+      <c r="N7" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O7" s="51" t="n"/>
+      <c r="P7" s="51" t="n"/>
+      <c r="Q7" s="51" t="n"/>
+      <c r="R7" s="51" t="n"/>
+      <c r="S7" s="51" t="n"/>
+      <c r="T7" s="51" t="n"/>
+      <c r="U7" s="51" t="n"/>
+      <c r="V7" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B8" s="45" t="n"/>
-      <c r="C8" s="46" t="n"/>
-      <c r="D8" s="46" t="n"/>
+      <c r="C8" s="53" t="n"/>
+      <c r="D8" s="53" t="n"/>
       <c r="E8" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F8" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G8" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G8" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H8" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I8" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J8" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K8" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L8" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M8" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N8" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O8" s="51" t="n"/>
-      <c r="P8" s="51" t="n"/>
-      <c r="Q8" s="51" t="n"/>
-      <c r="R8" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S8" s="51" t="n"/>
-      <c r="T8" s="51" t="n"/>
-      <c r="U8" s="51" t="n"/>
-      <c r="V8" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W8" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M8" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N8" s="55" t="n"/>
+      <c r="O8" s="55" t="n"/>
+      <c r="P8" s="55" t="n"/>
+      <c r="Q8" s="55" t="n"/>
+      <c r="R8" s="55" t="n"/>
+      <c r="S8" s="55" t="n"/>
+      <c r="T8" s="55" t="n"/>
+      <c r="U8" s="55" t="n"/>
+      <c r="V8" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W8" s="57" t="n"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B9" s="45" t="n"/>
-      <c r="C9" s="53" t="n"/>
-      <c r="D9" s="53" t="n"/>
+      <c r="C9" s="46" t="n"/>
+      <c r="D9" s="46" t="n"/>
       <c r="E9" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F9" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G9" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H9" s="49" t="n">
         <v>1</v>
@@ -2258,493 +2264,497 @@
         <v>1</v>
       </c>
       <c r="J9" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K9" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L9" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M9" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N9" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N9" s="55" t="n"/>
-      <c r="O9" s="55" t="n"/>
-      <c r="P9" s="55" t="n"/>
-      <c r="Q9" s="55" t="inlineStr">
+      <c r="O9" s="51" t="n"/>
+      <c r="P9" s="51" t="n"/>
+      <c r="Q9" s="51" t="n"/>
+      <c r="R9" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R9" s="55" t="n"/>
-      <c r="S9" s="55" t="n"/>
-      <c r="T9" s="55" t="n"/>
-      <c r="U9" s="55" t="n"/>
-      <c r="V9" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W9" s="57" t="n"/>
+      <c r="S9" s="51" t="n"/>
+      <c r="T9" s="51" t="n"/>
+      <c r="U9" s="51" t="n"/>
+      <c r="V9" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W9" s="58" t="n"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B10" s="45" t="n"/>
-      <c r="C10" s="46" t="n"/>
-      <c r="D10" s="46" t="n"/>
+      <c r="C10" s="53" t="n"/>
+      <c r="D10" s="53" t="n"/>
       <c r="E10" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F10" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G10" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G10" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H10" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I10" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J10" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K10" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L10" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N10" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O10" s="51" t="n"/>
-      <c r="P10" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M10" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N10" s="55" t="n"/>
+      <c r="O10" s="55" t="n"/>
+      <c r="P10" s="55" t="n"/>
+      <c r="Q10" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q10" s="51" t="n"/>
-      <c r="R10" s="51" t="n"/>
-      <c r="S10" s="51" t="n"/>
-      <c r="T10" s="51" t="n"/>
-      <c r="U10" s="51" t="n"/>
-      <c r="V10" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W10" s="58" t="n"/>
+      <c r="R10" s="55" t="n"/>
+      <c r="S10" s="55" t="n"/>
+      <c r="T10" s="55" t="n"/>
+      <c r="U10" s="55" t="n"/>
+      <c r="V10" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W10" s="57" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B11" s="45" t="n"/>
-      <c r="C11" s="53" t="n"/>
-      <c r="D11" s="53" t="n"/>
+      <c r="C11" s="46" t="n"/>
+      <c r="D11" s="46" t="n"/>
       <c r="E11" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F11" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G11" s="59" t="n">
-        <v>45.1</v>
+      <c r="G11" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H11" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I11" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J11" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K11" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L11" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N11" s="55" t="n"/>
-      <c r="O11" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P11" s="55" t="n"/>
-      <c r="Q11" s="55" t="n"/>
-      <c r="R11" s="55" t="n"/>
-      <c r="S11" s="55" t="n"/>
-      <c r="T11" s="55" t="n"/>
-      <c r="U11" s="55" t="n"/>
-      <c r="V11" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W11" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M11" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N11" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O11" s="51" t="n"/>
+      <c r="P11" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q11" s="51" t="n"/>
+      <c r="R11" s="51" t="n"/>
+      <c r="S11" s="51" t="n"/>
+      <c r="T11" s="51" t="n"/>
+      <c r="U11" s="51" t="n"/>
+      <c r="V11" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W11" s="58" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B12" s="45" t="n"/>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
+      <c r="C12" s="53" t="n"/>
+      <c r="D12" s="53" t="n"/>
       <c r="E12" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F12" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G12" s="54" t="n">
-        <v>26.3</v>
+      <c r="G12" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H12" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I12" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J12" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K12" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L12" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M12" s="51" t="n"/>
-      <c r="N12" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M12" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N12" s="55" t="n"/>
+      <c r="O12" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O12" s="51" t="n"/>
-      <c r="P12" s="51" t="n"/>
-      <c r="Q12" s="51" t="n"/>
-      <c r="R12" s="51" t="n"/>
-      <c r="S12" s="51" t="n"/>
-      <c r="T12" s="51" t="n"/>
-      <c r="U12" s="51" t="n"/>
-      <c r="V12" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W12" s="58" t="n"/>
+      <c r="P12" s="55" t="n"/>
+      <c r="Q12" s="55" t="n"/>
+      <c r="R12" s="55" t="n"/>
+      <c r="S12" s="55" t="n"/>
+      <c r="T12" s="55" t="n"/>
+      <c r="U12" s="55" t="n"/>
+      <c r="V12" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W12" s="57" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B13" s="45" t="n"/>
-      <c r="C13" s="53" t="n"/>
-      <c r="D13" s="53" t="n"/>
+      <c r="C13" s="46" t="n"/>
+      <c r="D13" s="46" t="n"/>
       <c r="E13" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F13" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G13" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H13" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J13" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K13" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L13" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M13" s="51" t="n"/>
+      <c r="N13" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N13" s="55" t="n"/>
-      <c r="O13" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P13" s="55" t="n"/>
-      <c r="Q13" s="55" t="n"/>
-      <c r="R13" s="55" t="n"/>
-      <c r="S13" s="55" t="n"/>
-      <c r="T13" s="55" t="n"/>
-      <c r="U13" s="55" t="n"/>
-      <c r="V13" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W13" s="57" t="n"/>
+      <c r="O13" s="51" t="n"/>
+      <c r="P13" s="51" t="n"/>
+      <c r="Q13" s="51" t="n"/>
+      <c r="R13" s="51" t="n"/>
+      <c r="S13" s="51" t="n"/>
+      <c r="T13" s="51" t="n"/>
+      <c r="U13" s="51" t="n"/>
+      <c r="V13" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W13" s="58" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B14" s="45" t="n"/>
-      <c r="C14" s="46" t="n"/>
-      <c r="D14" s="46" t="n"/>
+      <c r="C14" s="53" t="n"/>
+      <c r="D14" s="53" t="n"/>
       <c r="E14" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F14" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G14" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H14" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I14" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J14" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K14" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L14" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M14" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N14" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O14" s="51" t="n"/>
-      <c r="P14" s="51" t="n"/>
-      <c r="Q14" s="51" t="n"/>
-      <c r="R14" s="51" t="n"/>
-      <c r="S14" s="51" t="n"/>
-      <c r="T14" s="51" t="n"/>
-      <c r="U14" s="51" t="n"/>
-      <c r="V14" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W14" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M14" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N14" s="55" t="n"/>
+      <c r="O14" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P14" s="55" t="n"/>
+      <c r="Q14" s="55" t="n"/>
+      <c r="R14" s="55" t="n"/>
+      <c r="S14" s="55" t="n"/>
+      <c r="T14" s="55" t="n"/>
+      <c r="U14" s="55" t="n"/>
+      <c r="V14" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W14" s="57" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B15" s="45" t="n"/>
-      <c r="C15" s="53" t="n"/>
-      <c r="D15" s="53" t="n"/>
+      <c r="C15" s="46" t="n"/>
+      <c r="D15" s="46" t="n"/>
       <c r="E15" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F15" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G15" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H15" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K15" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L15" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I15" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K15" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L15" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M15" s="55" t="inlineStr">
+      <c r="M15" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N15" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N15" s="55" t="n"/>
-      <c r="O15" s="55" t="n"/>
-      <c r="P15" s="55" t="n"/>
-      <c r="Q15" s="55" t="n"/>
-      <c r="R15" s="55" t="n"/>
-      <c r="S15" s="55" t="n"/>
-      <c r="T15" s="55" t="n"/>
-      <c r="U15" s="55" t="n"/>
-      <c r="V15" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W15" s="57" t="n"/>
+      <c r="O15" s="51" t="n"/>
+      <c r="P15" s="51" t="n"/>
+      <c r="Q15" s="51" t="n"/>
+      <c r="R15" s="51" t="n"/>
+      <c r="S15" s="51" t="n"/>
+      <c r="T15" s="51" t="n"/>
+      <c r="U15" s="51" t="n"/>
+      <c r="V15" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W15" s="58" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B16" s="45" t="n"/>
-      <c r="C16" s="46" t="n"/>
-      <c r="D16" s="46" t="n"/>
+      <c r="C16" s="53" t="n"/>
+      <c r="D16" s="53" t="n"/>
       <c r="E16" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F16" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G16" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G16" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H16" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I16" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J16" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K16" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L16" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M16" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N16" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O16" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P16" s="51" t="n"/>
-      <c r="Q16" s="51" t="n"/>
-      <c r="R16" s="51" t="n"/>
-      <c r="S16" s="51" t="n"/>
-      <c r="T16" s="51" t="n"/>
-      <c r="U16" s="51" t="n"/>
-      <c r="V16" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W16" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M16" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N16" s="55" t="n"/>
+      <c r="O16" s="55" t="n"/>
+      <c r="P16" s="55" t="n"/>
+      <c r="Q16" s="55" t="n"/>
+      <c r="R16" s="55" t="n"/>
+      <c r="S16" s="55" t="n"/>
+      <c r="T16" s="55" t="n"/>
+      <c r="U16" s="55" t="n"/>
+      <c r="V16" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W16" s="57" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B17" s="45" t="n"/>
-      <c r="C17" s="53" t="n"/>
-      <c r="D17" s="53" t="n"/>
+      <c r="C17" s="46" t="n"/>
+      <c r="D17" s="46" t="n"/>
       <c r="E17" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F17" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G17" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G17" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H17" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J17" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K17" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L17" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M17" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N17" s="55" t="inlineStr">
+      <c r="M17" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N17" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O17" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O17" s="55" t="n"/>
-      <c r="P17" s="55" t="n"/>
-      <c r="Q17" s="55" t="n"/>
-      <c r="R17" s="55" t="n"/>
-      <c r="S17" s="55" t="n"/>
-      <c r="T17" s="55" t="n"/>
-      <c r="U17" s="55" t="n"/>
-      <c r="V17" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W17" s="57" t="n"/>
+      <c r="P17" s="51" t="n"/>
+      <c r="Q17" s="51" t="n"/>
+      <c r="R17" s="51" t="n"/>
+      <c r="S17" s="51" t="n"/>
+      <c r="T17" s="51" t="n"/>
+      <c r="U17" s="51" t="n"/>
+      <c r="V17" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W17" s="58" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B18" s="45" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="53" t="n"/>
       <c r="E18" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F18" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G18" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H18" s="49" t="n">
         <v>2</v>
@@ -2753,208 +2763,218 @@
         <v>2</v>
       </c>
       <c r="J18" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K18" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L18" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M18" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M18" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N18" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N18" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O18" s="51" t="n"/>
-      <c r="P18" s="51" t="n"/>
-      <c r="Q18" s="51" t="n"/>
-      <c r="R18" s="51" t="n"/>
-      <c r="S18" s="51" t="n"/>
-      <c r="T18" s="51" t="n"/>
-      <c r="U18" s="51" t="n"/>
-      <c r="V18" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W18" s="58" t="n"/>
+      <c r="O18" s="55" t="n"/>
+      <c r="P18" s="55" t="n"/>
+      <c r="Q18" s="55" t="n"/>
+      <c r="R18" s="55" t="n"/>
+      <c r="S18" s="55" t="n"/>
+      <c r="T18" s="55" t="n"/>
+      <c r="U18" s="55" t="n"/>
+      <c r="V18" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W18" s="57" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B19" s="45" t="n"/>
-      <c r="C19" s="53" t="n"/>
-      <c r="D19" s="53" t="n"/>
+      <c r="C19" s="46" t="n"/>
+      <c r="D19" s="46" t="n"/>
       <c r="E19" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F19" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G19" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H19" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J19" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K19" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L19" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M19" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M19" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N19" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N19" s="55" t="n"/>
-      <c r="O19" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P19" s="55" t="n"/>
-      <c r="Q19" s="55" t="n"/>
-      <c r="R19" s="55" t="n"/>
-      <c r="S19" s="55" t="n"/>
-      <c r="T19" s="55" t="n"/>
-      <c r="U19" s="55" t="n"/>
-      <c r="V19" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W19" s="57" t="n"/>
+      <c r="O19" s="51" t="n"/>
+      <c r="P19" s="51" t="n"/>
+      <c r="Q19" s="51" t="n"/>
+      <c r="R19" s="51" t="n"/>
+      <c r="S19" s="51" t="n"/>
+      <c r="T19" s="51" t="n"/>
+      <c r="U19" s="51" t="n"/>
+      <c r="V19" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W19" s="58" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B20" s="45" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="46" t="n"/>
+      <c r="C20" s="53" t="n"/>
+      <c r="D20" s="53" t="n"/>
       <c r="E20" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F20" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G20" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G20" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H20" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K20" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L20" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M20" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N20" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O20" s="51" t="n"/>
-      <c r="P20" s="51" t="n"/>
-      <c r="Q20" s="51" t="n"/>
-      <c r="R20" s="51" t="n"/>
-      <c r="S20" s="51" t="n"/>
-      <c r="T20" s="51" t="n"/>
-      <c r="U20" s="51" t="n"/>
-      <c r="V20" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W20" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M20" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N20" s="55" t="n"/>
+      <c r="O20" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P20" s="55" t="n"/>
+      <c r="Q20" s="55" t="n"/>
+      <c r="R20" s="55" t="n"/>
+      <c r="S20" s="55" t="n"/>
+      <c r="T20" s="55" t="n"/>
+      <c r="U20" s="55" t="n"/>
+      <c r="V20" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W20" s="57" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="53" t="n"/>
-      <c r="D21" s="53" t="n"/>
+      <c r="C21" s="46" t="n"/>
+      <c r="D21" s="46" t="n"/>
       <c r="E21" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F21" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G21" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G21" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H21" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K21" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L21" s="50" t="n"/>
-      <c r="M21" s="55" t="n"/>
-      <c r="N21" s="55" t="n"/>
-      <c r="O21" s="55" t="n"/>
-      <c r="P21" s="55" t="n"/>
-      <c r="Q21" s="55" t="n"/>
-      <c r="R21" s="55" t="n"/>
-      <c r="S21" s="55" t="n"/>
-      <c r="T21" s="55" t="n"/>
-      <c r="U21" s="55" t="n"/>
-      <c r="V21" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W21" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L21" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M21" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N21" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O21" s="51" t="n"/>
+      <c r="P21" s="51" t="n"/>
+      <c r="Q21" s="51" t="n"/>
+      <c r="R21" s="51" t="n"/>
+      <c r="S21" s="51" t="n"/>
+      <c r="T21" s="51" t="n"/>
+      <c r="U21" s="51" t="n"/>
+      <c r="V21" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W21" s="58" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="46" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
       <c r="E22" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G22" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H22" s="49" t="n">
         <v>0</v>
@@ -2963,43 +2983,43 @@
         <v>0</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K22" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L22" s="50" t="n"/>
-      <c r="M22" s="51" t="n"/>
-      <c r="N22" s="51" t="n"/>
-      <c r="O22" s="51" t="n"/>
-      <c r="P22" s="51" t="n"/>
-      <c r="Q22" s="51" t="n"/>
-      <c r="R22" s="51" t="n"/>
-      <c r="S22" s="51" t="n"/>
-      <c r="T22" s="51" t="n"/>
-      <c r="U22" s="51" t="n"/>
-      <c r="V22" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W22" s="58" t="n"/>
+      <c r="M22" s="55" t="n"/>
+      <c r="N22" s="55" t="n"/>
+      <c r="O22" s="55" t="n"/>
+      <c r="P22" s="55" t="n"/>
+      <c r="Q22" s="55" t="n"/>
+      <c r="R22" s="55" t="n"/>
+      <c r="S22" s="55" t="n"/>
+      <c r="T22" s="55" t="n"/>
+      <c r="U22" s="55" t="n"/>
+      <c r="V22" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W22" s="57" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="53" t="n"/>
-      <c r="D23" s="53" t="n"/>
+      <c r="C23" s="46" t="n"/>
+      <c r="D23" s="46" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G23" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H23" s="49" t="n">
         <v>0</v>
@@ -3008,43 +3028,43 @@
         <v>0</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L23" s="50" t="n"/>
-      <c r="M23" s="55" t="n"/>
-      <c r="N23" s="55" t="n"/>
-      <c r="O23" s="55" t="n"/>
-      <c r="P23" s="55" t="n"/>
-      <c r="Q23" s="55" t="n"/>
-      <c r="R23" s="55" t="n"/>
-      <c r="S23" s="55" t="n"/>
-      <c r="T23" s="55" t="n"/>
-      <c r="U23" s="55" t="n"/>
-      <c r="V23" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W23" s="57" t="n"/>
+      <c r="M23" s="51" t="n"/>
+      <c r="N23" s="51" t="n"/>
+      <c r="O23" s="51" t="n"/>
+      <c r="P23" s="51" t="n"/>
+      <c r="Q23" s="51" t="n"/>
+      <c r="R23" s="51" t="n"/>
+      <c r="S23" s="51" t="n"/>
+      <c r="T23" s="51" t="n"/>
+      <c r="U23" s="51" t="n"/>
+      <c r="V23" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W23" s="58" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G24" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G24" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H24" s="49" t="n">
         <v>0</v>
@@ -3053,43 +3073,43 @@
         <v>0</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L24" s="50" t="n"/>
-      <c r="M24" s="51" t="n"/>
-      <c r="N24" s="51" t="n"/>
-      <c r="O24" s="51" t="n"/>
-      <c r="P24" s="51" t="n"/>
-      <c r="Q24" s="51" t="n"/>
-      <c r="R24" s="51" t="n"/>
-      <c r="S24" s="51" t="n"/>
-      <c r="T24" s="51" t="n"/>
-      <c r="U24" s="51" t="n"/>
-      <c r="V24" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W24" s="58" t="n"/>
+      <c r="M24" s="55" t="n"/>
+      <c r="N24" s="55" t="n"/>
+      <c r="O24" s="55" t="n"/>
+      <c r="P24" s="55" t="n"/>
+      <c r="Q24" s="55" t="n"/>
+      <c r="R24" s="55" t="n"/>
+      <c r="S24" s="55" t="n"/>
+      <c r="T24" s="55" t="n"/>
+      <c r="U24" s="55" t="n"/>
+      <c r="V24" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W24" s="57" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="53" t="n"/>
-      <c r="D25" s="53" t="n"/>
+      <c r="C25" s="46" t="n"/>
+      <c r="D25" s="46" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G25" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H25" s="49" t="n">
         <v>0</v>
@@ -3098,43 +3118,43 @@
         <v>0</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L25" s="50" t="n"/>
-      <c r="M25" s="55" t="n"/>
-      <c r="N25" s="55" t="n"/>
-      <c r="O25" s="55" t="n"/>
-      <c r="P25" s="55" t="n"/>
-      <c r="Q25" s="55" t="n"/>
-      <c r="R25" s="55" t="n"/>
-      <c r="S25" s="55" t="n"/>
-      <c r="T25" s="55" t="n"/>
-      <c r="U25" s="55" t="n"/>
-      <c r="V25" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W25" s="57" t="n"/>
+      <c r="M25" s="51" t="n"/>
+      <c r="N25" s="51" t="n"/>
+      <c r="O25" s="51" t="n"/>
+      <c r="P25" s="51" t="n"/>
+      <c r="Q25" s="51" t="n"/>
+      <c r="R25" s="51" t="n"/>
+      <c r="S25" s="51" t="n"/>
+      <c r="T25" s="51" t="n"/>
+      <c r="U25" s="51" t="n"/>
+      <c r="V25" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W25" s="58" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="46" t="n"/>
-      <c r="D26" s="46" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G26" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H26" s="49" t="n">
         <v>0</v>
@@ -3143,1371 +3163,1375 @@
         <v>0</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L26" s="50" t="n"/>
-      <c r="M26" s="51" t="n"/>
-      <c r="N26" s="51" t="n"/>
-      <c r="O26" s="51" t="n"/>
-      <c r="P26" s="51" t="n"/>
-      <c r="Q26" s="51" t="n"/>
-      <c r="R26" s="51" t="n"/>
-      <c r="S26" s="51" t="n"/>
-      <c r="T26" s="51" t="n"/>
-      <c r="U26" s="51" t="n"/>
-      <c r="V26" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W26" s="58" t="n"/>
+      <c r="M26" s="55" t="n"/>
+      <c r="N26" s="55" t="n"/>
+      <c r="O26" s="55" t="n"/>
+      <c r="P26" s="55" t="n"/>
+      <c r="Q26" s="55" t="n"/>
+      <c r="R26" s="55" t="n"/>
+      <c r="S26" s="55" t="n"/>
+      <c r="T26" s="55" t="n"/>
+      <c r="U26" s="55" t="n"/>
+      <c r="V26" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W26" s="57" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="53" t="n"/>
-      <c r="D27" s="53" t="n"/>
+      <c r="C27" s="46" t="n"/>
+      <c r="D27" s="46" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G27" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H27" s="49" t="n"/>
-      <c r="I27" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G27" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H27" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J27" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L27" s="50" t="n"/>
-      <c r="M27" s="55" t="n"/>
-      <c r="N27" s="55" t="n"/>
-      <c r="O27" s="55" t="n"/>
-      <c r="P27" s="55" t="n"/>
-      <c r="Q27" s="55" t="n"/>
-      <c r="R27" s="55" t="n"/>
-      <c r="S27" s="55" t="n"/>
-      <c r="T27" s="55" t="n"/>
-      <c r="U27" s="55" t="n"/>
-      <c r="V27" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W27" s="57" t="n"/>
+      <c r="M27" s="51" t="n"/>
+      <c r="N27" s="51" t="n"/>
+      <c r="O27" s="51" t="n"/>
+      <c r="P27" s="51" t="n"/>
+      <c r="Q27" s="51" t="n"/>
+      <c r="R27" s="51" t="n"/>
+      <c r="S27" s="51" t="n"/>
+      <c r="T27" s="51" t="n"/>
+      <c r="U27" s="51" t="n"/>
+      <c r="V27" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W27" s="58" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="46" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="53" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G28" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H28" s="49" t="n"/>
       <c r="I28" s="49" t="n"/>
       <c r="J28" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L28" s="50" t="n"/>
-      <c r="M28" s="51" t="n"/>
-      <c r="N28" s="51" t="n"/>
-      <c r="O28" s="51" t="n"/>
-      <c r="P28" s="51" t="n"/>
-      <c r="Q28" s="51" t="n"/>
-      <c r="R28" s="51" t="n"/>
-      <c r="S28" s="51" t="n"/>
-      <c r="T28" s="51" t="n"/>
-      <c r="U28" s="51" t="n"/>
-      <c r="V28" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W28" s="58" t="n"/>
+      <c r="M28" s="55" t="n"/>
+      <c r="N28" s="55" t="n"/>
+      <c r="O28" s="55" t="n"/>
+      <c r="P28" s="55" t="n"/>
+      <c r="Q28" s="55" t="n"/>
+      <c r="R28" s="55" t="n"/>
+      <c r="S28" s="55" t="n"/>
+      <c r="T28" s="55" t="n"/>
+      <c r="U28" s="55" t="n"/>
+      <c r="V28" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W28" s="57" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="53" t="n"/>
-      <c r="D29" s="53" t="n"/>
+      <c r="C29" s="46" t="n"/>
+      <c r="D29" s="46" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G29" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H29" s="49" t="n"/>
       <c r="I29" s="49" t="n"/>
       <c r="J29" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L29" s="50" t="n"/>
-      <c r="M29" s="55" t="n"/>
-      <c r="N29" s="55" t="n"/>
-      <c r="O29" s="55" t="n"/>
-      <c r="P29" s="55" t="n"/>
-      <c r="Q29" s="55" t="n"/>
-      <c r="R29" s="55" t="n"/>
-      <c r="S29" s="55" t="n"/>
-      <c r="T29" s="55" t="n"/>
-      <c r="U29" s="55" t="n"/>
-      <c r="V29" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W29" s="57" t="n"/>
+      <c r="M29" s="51" t="n"/>
+      <c r="N29" s="51" t="n"/>
+      <c r="O29" s="51" t="n"/>
+      <c r="P29" s="51" t="n"/>
+      <c r="Q29" s="51" t="n"/>
+      <c r="R29" s="51" t="n"/>
+      <c r="S29" s="51" t="n"/>
+      <c r="T29" s="51" t="n"/>
+      <c r="U29" s="51" t="n"/>
+      <c r="V29" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W29" s="58" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="46" t="n"/>
-      <c r="D30" s="46" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="53" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G30" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H30" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I30" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H30" s="49" t="n"/>
+      <c r="I30" s="49" t="n"/>
       <c r="J30" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L30" s="50" t="n"/>
-      <c r="M30" s="51" t="n"/>
-      <c r="N30" s="51" t="n"/>
-      <c r="O30" s="51" t="n"/>
-      <c r="P30" s="51" t="n"/>
-      <c r="Q30" s="51" t="n"/>
-      <c r="R30" s="51" t="n"/>
-      <c r="S30" s="51" t="n"/>
-      <c r="T30" s="51" t="n"/>
-      <c r="U30" s="51" t="n"/>
-      <c r="V30" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W30" s="58" t="n"/>
+      <c r="M30" s="55" t="n"/>
+      <c r="N30" s="55" t="n"/>
+      <c r="O30" s="55" t="n"/>
+      <c r="P30" s="55" t="n"/>
+      <c r="Q30" s="55" t="n"/>
+      <c r="R30" s="55" t="n"/>
+      <c r="S30" s="55" t="n"/>
+      <c r="T30" s="55" t="n"/>
+      <c r="U30" s="55" t="n"/>
+      <c r="V30" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W30" s="57" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="53" t="n"/>
-      <c r="D31" s="53" t="n"/>
+      <c r="C31" s="46" t="n"/>
+      <c r="D31" s="46" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G31" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H31" s="49" t="n"/>
-      <c r="I31" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G31" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H31" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I31" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J31" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L31" s="50" t="n"/>
-      <c r="M31" s="55" t="n"/>
-      <c r="N31" s="55" t="n"/>
-      <c r="O31" s="55" t="n"/>
-      <c r="P31" s="55" t="n"/>
-      <c r="Q31" s="55" t="n"/>
-      <c r="R31" s="55" t="n"/>
-      <c r="S31" s="55" t="n"/>
-      <c r="T31" s="55" t="n"/>
-      <c r="U31" s="55" t="n"/>
-      <c r="V31" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W31" s="57" t="n"/>
+      <c r="M31" s="51" t="n"/>
+      <c r="N31" s="51" t="n"/>
+      <c r="O31" s="51" t="n"/>
+      <c r="P31" s="51" t="n"/>
+      <c r="Q31" s="51" t="n"/>
+      <c r="R31" s="51" t="n"/>
+      <c r="S31" s="51" t="n"/>
+      <c r="T31" s="51" t="n"/>
+      <c r="U31" s="51" t="n"/>
+      <c r="V31" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W31" s="58" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="46" t="n"/>
-      <c r="D32" s="46" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G32" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G32" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H32" s="49" t="n"/>
       <c r="I32" s="49" t="n"/>
       <c r="J32" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L32" s="50" t="n"/>
-      <c r="M32" s="51" t="n"/>
-      <c r="N32" s="51" t="n"/>
-      <c r="O32" s="51" t="n"/>
-      <c r="P32" s="51" t="n"/>
-      <c r="Q32" s="51" t="n"/>
-      <c r="R32" s="51" t="n"/>
-      <c r="S32" s="51" t="n"/>
-      <c r="T32" s="51" t="n"/>
-      <c r="U32" s="51" t="n"/>
-      <c r="V32" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W32" s="58" t="n"/>
+      <c r="M32" s="55" t="n"/>
+      <c r="N32" s="55" t="n"/>
+      <c r="O32" s="55" t="n"/>
+      <c r="P32" s="55" t="n"/>
+      <c r="Q32" s="55" t="n"/>
+      <c r="R32" s="55" t="n"/>
+      <c r="S32" s="55" t="n"/>
+      <c r="T32" s="55" t="n"/>
+      <c r="U32" s="55" t="n"/>
+      <c r="V32" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W32" s="57" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="53" t="n"/>
-      <c r="D33" s="53" t="n"/>
+      <c r="C33" s="46" t="n"/>
+      <c r="D33" s="46" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G33" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G33" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H33" s="49" t="n"/>
       <c r="I33" s="49" t="n"/>
       <c r="J33" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K33" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K33" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L33" s="50" t="n"/>
-      <c r="M33" s="55" t="n"/>
-      <c r="N33" s="55" t="n"/>
-      <c r="O33" s="55" t="n"/>
-      <c r="P33" s="55" t="n"/>
-      <c r="Q33" s="55" t="n"/>
-      <c r="R33" s="55" t="n"/>
-      <c r="S33" s="55" t="n"/>
-      <c r="T33" s="55" t="n"/>
-      <c r="U33" s="55" t="n"/>
-      <c r="V33" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W33" s="57" t="n"/>
+      <c r="M33" s="51" t="n"/>
+      <c r="N33" s="51" t="n"/>
+      <c r="O33" s="51" t="n"/>
+      <c r="P33" s="51" t="n"/>
+      <c r="Q33" s="51" t="n"/>
+      <c r="R33" s="51" t="n"/>
+      <c r="S33" s="51" t="n"/>
+      <c r="T33" s="51" t="n"/>
+      <c r="U33" s="51" t="n"/>
+      <c r="V33" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W33" s="58" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="46" t="n"/>
-      <c r="D34" s="46" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G34" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H34" s="49" t="n"/>
       <c r="I34" s="49" t="n"/>
       <c r="J34" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L34" s="50" t="n"/>
-      <c r="M34" s="51" t="n"/>
-      <c r="N34" s="51" t="n"/>
-      <c r="O34" s="51" t="n"/>
-      <c r="P34" s="51" t="n"/>
-      <c r="Q34" s="51" t="n"/>
-      <c r="R34" s="51" t="n"/>
-      <c r="S34" s="51" t="n"/>
-      <c r="T34" s="51" t="n"/>
-      <c r="U34" s="51" t="n"/>
-      <c r="V34" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W34" s="58" t="n"/>
+      <c r="M34" s="55" t="n"/>
+      <c r="N34" s="55" t="n"/>
+      <c r="O34" s="55" t="n"/>
+      <c r="P34" s="55" t="n"/>
+      <c r="Q34" s="55" t="n"/>
+      <c r="R34" s="55" t="n"/>
+      <c r="S34" s="55" t="n"/>
+      <c r="T34" s="55" t="n"/>
+      <c r="U34" s="55" t="n"/>
+      <c r="V34" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W34" s="57" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="53" t="n"/>
-      <c r="D35" s="53" t="n"/>
+      <c r="C35" s="46" t="n"/>
+      <c r="D35" s="46" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G35" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G35" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H35" s="49" t="n"/>
       <c r="I35" s="49" t="n"/>
       <c r="J35" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L35" s="50" t="n"/>
-      <c r="M35" s="55" t="n"/>
-      <c r="N35" s="55" t="n"/>
-      <c r="O35" s="55" t="n"/>
-      <c r="P35" s="55" t="n"/>
-      <c r="Q35" s="55" t="n"/>
-      <c r="R35" s="55" t="n"/>
-      <c r="S35" s="55" t="n"/>
-      <c r="T35" s="55" t="n"/>
-      <c r="U35" s="55" t="n"/>
-      <c r="V35" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W35" s="57" t="n"/>
+      <c r="M35" s="51" t="n"/>
+      <c r="N35" s="51" t="n"/>
+      <c r="O35" s="51" t="n"/>
+      <c r="P35" s="51" t="n"/>
+      <c r="Q35" s="51" t="n"/>
+      <c r="R35" s="51" t="n"/>
+      <c r="S35" s="51" t="n"/>
+      <c r="T35" s="51" t="n"/>
+      <c r="U35" s="51" t="n"/>
+      <c r="V35" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W35" s="58" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
+      <c r="C36" s="53" t="n"/>
+      <c r="D36" s="53" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G36" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H36" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I36" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G36" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H36" s="49" t="n"/>
+      <c r="I36" s="49" t="n"/>
       <c r="J36" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="51" t="n"/>
-      <c r="N36" s="51" t="n"/>
-      <c r="O36" s="51" t="n"/>
-      <c r="P36" s="51" t="n"/>
-      <c r="Q36" s="51" t="n"/>
-      <c r="R36" s="51" t="n"/>
-      <c r="S36" s="51" t="n"/>
-      <c r="T36" s="51" t="n"/>
-      <c r="U36" s="51" t="n"/>
-      <c r="V36" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W36" s="58" t="n"/>
+      <c r="M36" s="55" t="n"/>
+      <c r="N36" s="55" t="n"/>
+      <c r="O36" s="55" t="n"/>
+      <c r="P36" s="55" t="n"/>
+      <c r="Q36" s="55" t="n"/>
+      <c r="R36" s="55" t="n"/>
+      <c r="S36" s="55" t="n"/>
+      <c r="T36" s="55" t="n"/>
+      <c r="U36" s="55" t="n"/>
+      <c r="V36" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W36" s="57" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="53" t="n"/>
-      <c r="D37" s="53" t="n"/>
+      <c r="C37" s="46" t="n"/>
+      <c r="D37" s="46" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G37" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H37" s="49" t="n"/>
-      <c r="I37" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H37" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I37" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J37" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="55" t="n"/>
-      <c r="N37" s="55" t="n"/>
-      <c r="O37" s="55" t="n"/>
-      <c r="P37" s="55" t="n"/>
-      <c r="Q37" s="55" t="n"/>
-      <c r="R37" s="55" t="n"/>
-      <c r="S37" s="55" t="n"/>
-      <c r="T37" s="55" t="n"/>
-      <c r="U37" s="55" t="n"/>
-      <c r="V37" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W37" s="57" t="n"/>
+      <c r="M37" s="51" t="n"/>
+      <c r="N37" s="51" t="n"/>
+      <c r="O37" s="51" t="n"/>
+      <c r="P37" s="51" t="n"/>
+      <c r="Q37" s="51" t="n"/>
+      <c r="R37" s="51" t="n"/>
+      <c r="S37" s="51" t="n"/>
+      <c r="T37" s="51" t="n"/>
+      <c r="U37" s="51" t="n"/>
+      <c r="V37" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W37" s="58" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="46" t="n"/>
-      <c r="D38" s="46" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G38" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H38" s="49" t="n"/>
       <c r="I38" s="49" t="n"/>
       <c r="J38" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="51" t="n"/>
-      <c r="N38" s="51" t="n"/>
-      <c r="O38" s="51" t="n"/>
-      <c r="P38" s="51" t="n"/>
-      <c r="Q38" s="51" t="n"/>
-      <c r="R38" s="51" t="n"/>
-      <c r="S38" s="51" t="n"/>
-      <c r="T38" s="51" t="n"/>
-      <c r="U38" s="51" t="n"/>
-      <c r="V38" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W38" s="58" t="n"/>
+      <c r="M38" s="55" t="n"/>
+      <c r="N38" s="55" t="n"/>
+      <c r="O38" s="55" t="n"/>
+      <c r="P38" s="55" t="n"/>
+      <c r="Q38" s="55" t="n"/>
+      <c r="R38" s="55" t="n"/>
+      <c r="S38" s="55" t="n"/>
+      <c r="T38" s="55" t="n"/>
+      <c r="U38" s="55" t="n"/>
+      <c r="V38" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W38" s="57" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="53" t="n"/>
-      <c r="D39" s="53" t="n"/>
+      <c r="C39" s="46" t="n"/>
+      <c r="D39" s="46" t="n"/>
       <c r="E39" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F39" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G39" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H39" s="49" t="n"/>
+      <c r="I39" s="49" t="n"/>
+      <c r="J39" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F39" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G39" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H39" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I39" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J39" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K39" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="55" t="n"/>
-      <c r="N39" s="55" t="n"/>
-      <c r="O39" s="55" t="n"/>
-      <c r="P39" s="55" t="n"/>
-      <c r="Q39" s="55" t="n"/>
-      <c r="R39" s="55" t="n"/>
-      <c r="S39" s="55" t="n"/>
-      <c r="T39" s="55" t="n"/>
-      <c r="U39" s="55" t="n"/>
-      <c r="V39" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W39" s="57" t="n"/>
+      <c r="M39" s="51" t="n"/>
+      <c r="N39" s="51" t="n"/>
+      <c r="O39" s="51" t="n"/>
+      <c r="P39" s="51" t="n"/>
+      <c r="Q39" s="51" t="n"/>
+      <c r="R39" s="51" t="n"/>
+      <c r="S39" s="51" t="n"/>
+      <c r="T39" s="51" t="n"/>
+      <c r="U39" s="51" t="n"/>
+      <c r="V39" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W39" s="58" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="46" t="n"/>
-      <c r="D40" s="46" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G40" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H40" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I40" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J40" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="51" t="n"/>
-      <c r="N40" s="51" t="n"/>
-      <c r="O40" s="51" t="n"/>
-      <c r="P40" s="51" t="n"/>
-      <c r="Q40" s="51" t="n"/>
-      <c r="R40" s="51" t="n"/>
-      <c r="S40" s="51" t="n"/>
-      <c r="T40" s="51" t="n"/>
-      <c r="U40" s="51" t="n"/>
-      <c r="V40" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W40" s="58" t="n"/>
+      <c r="M40" s="55" t="n"/>
+      <c r="N40" s="55" t="n"/>
+      <c r="O40" s="55" t="n"/>
+      <c r="P40" s="55" t="n"/>
+      <c r="Q40" s="55" t="n"/>
+      <c r="R40" s="55" t="n"/>
+      <c r="S40" s="55" t="n"/>
+      <c r="T40" s="55" t="n"/>
+      <c r="U40" s="55" t="n"/>
+      <c r="V40" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W40" s="57" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="53" t="n"/>
-      <c r="D41" s="53" t="n"/>
+      <c r="C41" s="46" t="n"/>
+      <c r="D41" s="46" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G41" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H41" s="49" t="n"/>
-      <c r="I41" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H41" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I41" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J41" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="55" t="n"/>
-      <c r="N41" s="55" t="n"/>
-      <c r="O41" s="55" t="n"/>
-      <c r="P41" s="55" t="n"/>
-      <c r="Q41" s="55" t="n"/>
-      <c r="R41" s="55" t="n"/>
-      <c r="S41" s="55" t="n"/>
-      <c r="T41" s="55" t="n"/>
-      <c r="U41" s="55" t="n"/>
-      <c r="V41" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W41" s="57" t="n"/>
+      <c r="M41" s="51" t="n"/>
+      <c r="N41" s="51" t="n"/>
+      <c r="O41" s="51" t="n"/>
+      <c r="P41" s="51" t="n"/>
+      <c r="Q41" s="51" t="n"/>
+      <c r="R41" s="51" t="n"/>
+      <c r="S41" s="51" t="n"/>
+      <c r="T41" s="51" t="n"/>
+      <c r="U41" s="51" t="n"/>
+      <c r="V41" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W41" s="58" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="46" t="n"/>
-      <c r="D42" s="46" t="n"/>
+      <c r="C42" s="53" t="n"/>
+      <c r="D42" s="53" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G42" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G42" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H42" s="49" t="n"/>
       <c r="I42" s="49" t="n"/>
       <c r="J42" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K42" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="51" t="n"/>
-      <c r="N42" s="51" t="n"/>
-      <c r="O42" s="51" t="n"/>
-      <c r="P42" s="51" t="n"/>
-      <c r="Q42" s="51" t="n"/>
-      <c r="R42" s="51" t="n"/>
-      <c r="S42" s="51" t="n"/>
-      <c r="T42" s="51" t="n"/>
-      <c r="U42" s="51" t="n"/>
-      <c r="V42" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W42" s="58" t="n"/>
+      <c r="M42" s="55" t="n"/>
+      <c r="N42" s="55" t="n"/>
+      <c r="O42" s="55" t="n"/>
+      <c r="P42" s="55" t="n"/>
+      <c r="Q42" s="55" t="n"/>
+      <c r="R42" s="55" t="n"/>
+      <c r="S42" s="55" t="n"/>
+      <c r="T42" s="55" t="n"/>
+      <c r="U42" s="55" t="n"/>
+      <c r="V42" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W42" s="57" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="53" t="n"/>
-      <c r="D43" s="53" t="n"/>
+      <c r="C43" s="46" t="n"/>
+      <c r="D43" s="46" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G43" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G43" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H43" s="49" t="n"/>
       <c r="I43" s="49" t="n"/>
       <c r="J43" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K43" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="55" t="n"/>
-      <c r="N43" s="55" t="n"/>
-      <c r="O43" s="55" t="n"/>
-      <c r="P43" s="55" t="n"/>
-      <c r="Q43" s="55" t="n"/>
-      <c r="R43" s="55" t="n"/>
-      <c r="S43" s="55" t="n"/>
-      <c r="T43" s="55" t="n"/>
-      <c r="U43" s="55" t="n"/>
-      <c r="V43" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W43" s="57" t="n"/>
+      <c r="M43" s="51" t="n"/>
+      <c r="N43" s="51" t="n"/>
+      <c r="O43" s="51" t="n"/>
+      <c r="P43" s="51" t="n"/>
+      <c r="Q43" s="51" t="n"/>
+      <c r="R43" s="51" t="n"/>
+      <c r="S43" s="51" t="n"/>
+      <c r="T43" s="51" t="n"/>
+      <c r="U43" s="51" t="n"/>
+      <c r="V43" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W43" s="58" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="46" t="n"/>
-      <c r="D44" s="46" t="n"/>
+      <c r="C44" s="53" t="n"/>
+      <c r="D44" s="53" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G44" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H44" s="49" t="n"/>
       <c r="I44" s="49" t="n"/>
       <c r="J44" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K44" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="51" t="n"/>
-      <c r="N44" s="51" t="n"/>
-      <c r="O44" s="51" t="n"/>
-      <c r="P44" s="51" t="n"/>
-      <c r="Q44" s="51" t="n"/>
-      <c r="R44" s="51" t="n"/>
-      <c r="S44" s="51" t="n"/>
-      <c r="T44" s="51" t="n"/>
-      <c r="U44" s="51" t="n"/>
-      <c r="V44" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W44" s="58" t="n"/>
+      <c r="M44" s="55" t="n"/>
+      <c r="N44" s="55" t="n"/>
+      <c r="O44" s="55" t="n"/>
+      <c r="P44" s="55" t="n"/>
+      <c r="Q44" s="55" t="n"/>
+      <c r="R44" s="55" t="n"/>
+      <c r="S44" s="55" t="n"/>
+      <c r="T44" s="55" t="n"/>
+      <c r="U44" s="55" t="n"/>
+      <c r="V44" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W44" s="57" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="53" t="n"/>
-      <c r="D45" s="53" t="n"/>
+      <c r="C45" s="46" t="n"/>
+      <c r="D45" s="46" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G45" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G45" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H45" s="49" t="n"/>
       <c r="I45" s="49" t="n"/>
       <c r="J45" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K45" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="55" t="n"/>
-      <c r="N45" s="55" t="n"/>
-      <c r="O45" s="55" t="n"/>
-      <c r="P45" s="55" t="n"/>
-      <c r="Q45" s="55" t="n"/>
-      <c r="R45" s="55" t="n"/>
-      <c r="S45" s="55" t="n"/>
-      <c r="T45" s="55" t="n"/>
-      <c r="U45" s="55" t="n"/>
-      <c r="V45" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W45" s="57" t="n"/>
+      <c r="M45" s="51" t="n"/>
+      <c r="N45" s="51" t="n"/>
+      <c r="O45" s="51" t="n"/>
+      <c r="P45" s="51" t="n"/>
+      <c r="Q45" s="51" t="n"/>
+      <c r="R45" s="51" t="n"/>
+      <c r="S45" s="51" t="n"/>
+      <c r="T45" s="51" t="n"/>
+      <c r="U45" s="51" t="n"/>
+      <c r="V45" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W45" s="58" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="46" t="n"/>
-      <c r="D46" s="46" t="n"/>
+      <c r="C46" s="53" t="n"/>
+      <c r="D46" s="53" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G46" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G46" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H46" s="49" t="n"/>
       <c r="I46" s="49" t="n"/>
       <c r="J46" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K46" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="51" t="n"/>
-      <c r="N46" s="51" t="n"/>
-      <c r="O46" s="51" t="n"/>
-      <c r="P46" s="51" t="n"/>
-      <c r="Q46" s="51" t="n"/>
-      <c r="R46" s="51" t="n"/>
-      <c r="S46" s="51" t="n"/>
-      <c r="T46" s="51" t="n"/>
-      <c r="U46" s="51" t="n"/>
-      <c r="V46" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W46" s="58" t="n"/>
+      <c r="M46" s="55" t="n"/>
+      <c r="N46" s="55" t="n"/>
+      <c r="O46" s="55" t="n"/>
+      <c r="P46" s="55" t="n"/>
+      <c r="Q46" s="55" t="n"/>
+      <c r="R46" s="55" t="n"/>
+      <c r="S46" s="55" t="n"/>
+      <c r="T46" s="55" t="n"/>
+      <c r="U46" s="55" t="n"/>
+      <c r="V46" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W46" s="57" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="53" t="n"/>
-      <c r="D47" s="53" t="n"/>
+      <c r="C47" s="46" t="n"/>
+      <c r="D47" s="46" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G47" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G47" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H47" s="49" t="n"/>
       <c r="I47" s="49" t="n"/>
       <c r="J47" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K47" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="55" t="n"/>
-      <c r="N47" s="55" t="n"/>
-      <c r="O47" s="55" t="n"/>
-      <c r="P47" s="55" t="n"/>
-      <c r="Q47" s="55" t="n"/>
-      <c r="R47" s="55" t="n"/>
-      <c r="S47" s="55" t="n"/>
-      <c r="T47" s="55" t="n"/>
-      <c r="U47" s="55" t="n"/>
-      <c r="V47" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W47" s="57" t="n"/>
+      <c r="M47" s="51" t="n"/>
+      <c r="N47" s="51" t="n"/>
+      <c r="O47" s="51" t="n"/>
+      <c r="P47" s="51" t="n"/>
+      <c r="Q47" s="51" t="n"/>
+      <c r="R47" s="51" t="n"/>
+      <c r="S47" s="51" t="n"/>
+      <c r="T47" s="51" t="n"/>
+      <c r="U47" s="51" t="n"/>
+      <c r="V47" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W47" s="58" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
+      <c r="C48" s="53" t="n"/>
+      <c r="D48" s="53" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G48" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H48" s="49" t="n"/>
       <c r="I48" s="49" t="n"/>
       <c r="J48" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K48" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="51" t="n"/>
-      <c r="N48" s="51" t="n"/>
-      <c r="O48" s="51" t="n"/>
-      <c r="P48" s="51" t="n"/>
-      <c r="Q48" s="51" t="n"/>
-      <c r="R48" s="51" t="n"/>
-      <c r="S48" s="51" t="n"/>
-      <c r="T48" s="51" t="n"/>
-      <c r="U48" s="51" t="n"/>
-      <c r="V48" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W48" s="58" t="n"/>
+      <c r="M48" s="55" t="n"/>
+      <c r="N48" s="55" t="n"/>
+      <c r="O48" s="55" t="n"/>
+      <c r="P48" s="55" t="n"/>
+      <c r="Q48" s="55" t="n"/>
+      <c r="R48" s="55" t="n"/>
+      <c r="S48" s="55" t="n"/>
+      <c r="T48" s="55" t="n"/>
+      <c r="U48" s="55" t="n"/>
+      <c r="V48" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W48" s="57" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="53" t="n"/>
-      <c r="D49" s="53" t="n"/>
+      <c r="C49" s="46" t="n"/>
+      <c r="D49" s="46" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G49" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H49" s="49" t="n"/>
       <c r="I49" s="49" t="n"/>
       <c r="J49" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K49" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="55" t="n"/>
-      <c r="N49" s="55" t="n"/>
-      <c r="O49" s="55" t="n"/>
-      <c r="P49" s="55" t="n"/>
-      <c r="Q49" s="55" t="n"/>
-      <c r="R49" s="55" t="n"/>
-      <c r="S49" s="55" t="n"/>
-      <c r="T49" s="55" t="n"/>
-      <c r="U49" s="55" t="n"/>
-      <c r="V49" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W49" s="57" t="n"/>
+      <c r="M49" s="51" t="n"/>
+      <c r="N49" s="51" t="n"/>
+      <c r="O49" s="51" t="n"/>
+      <c r="P49" s="51" t="n"/>
+      <c r="Q49" s="51" t="n"/>
+      <c r="R49" s="51" t="n"/>
+      <c r="S49" s="51" t="n"/>
+      <c r="T49" s="51" t="n"/>
+      <c r="U49" s="51" t="n"/>
+      <c r="V49" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W49" s="58" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
+      <c r="C50" s="53" t="n"/>
+      <c r="D50" s="53" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G50" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G50" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="49" t="n"/>
       <c r="J50" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="51" t="n"/>
-      <c r="N50" s="51" t="n"/>
-      <c r="O50" s="51" t="n"/>
-      <c r="P50" s="51" t="n"/>
-      <c r="Q50" s="51" t="n"/>
-      <c r="R50" s="51" t="n"/>
-      <c r="S50" s="51" t="n"/>
-      <c r="T50" s="51" t="n"/>
-      <c r="U50" s="51" t="n"/>
-      <c r="V50" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W50" s="58" t="n"/>
+      <c r="M50" s="55" t="n"/>
+      <c r="N50" s="55" t="n"/>
+      <c r="O50" s="55" t="n"/>
+      <c r="P50" s="55" t="n"/>
+      <c r="Q50" s="55" t="n"/>
+      <c r="R50" s="55" t="n"/>
+      <c r="S50" s="55" t="n"/>
+      <c r="T50" s="55" t="n"/>
+      <c r="U50" s="55" t="n"/>
+      <c r="V50" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W50" s="57" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="53" t="n"/>
-      <c r="D51" s="53" t="n"/>
+      <c r="C51" s="46" t="n"/>
+      <c r="D51" s="46" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G51" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G51" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H51" s="49" t="n"/>
       <c r="I51" s="49" t="n"/>
       <c r="J51" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="55" t="n"/>
-      <c r="N51" s="55" t="n"/>
-      <c r="O51" s="55" t="n"/>
-      <c r="P51" s="55" t="n"/>
-      <c r="Q51" s="55" t="n"/>
-      <c r="R51" s="55" t="n"/>
-      <c r="S51" s="55" t="n"/>
-      <c r="T51" s="55" t="n"/>
-      <c r="U51" s="55" t="n"/>
-      <c r="V51" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W51" s="57" t="n"/>
+      <c r="M51" s="51" t="n"/>
+      <c r="N51" s="51" t="n"/>
+      <c r="O51" s="51" t="n"/>
+      <c r="P51" s="51" t="n"/>
+      <c r="Q51" s="51" t="n"/>
+      <c r="R51" s="51" t="n"/>
+      <c r="S51" s="51" t="n"/>
+      <c r="T51" s="51" t="n"/>
+      <c r="U51" s="51" t="n"/>
+      <c r="V51" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W51" s="58" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="46" t="n"/>
-      <c r="D52" s="46" t="n"/>
+      <c r="C52" s="53" t="n"/>
+      <c r="D52" s="53" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G52" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G52" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H52" s="49" t="n"/>
       <c r="I52" s="49" t="n"/>
       <c r="J52" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="51" t="n"/>
-      <c r="N52" s="51" t="n"/>
-      <c r="O52" s="51" t="n"/>
-      <c r="P52" s="51" t="n"/>
-      <c r="Q52" s="51" t="n"/>
-      <c r="R52" s="51" t="n"/>
-      <c r="S52" s="51" t="n"/>
-      <c r="T52" s="51" t="n"/>
-      <c r="U52" s="51" t="n"/>
-      <c r="V52" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W52" s="58" t="n"/>
+      <c r="M52" s="55" t="n"/>
+      <c r="N52" s="55" t="n"/>
+      <c r="O52" s="55" t="n"/>
+      <c r="P52" s="55" t="n"/>
+      <c r="Q52" s="55" t="n"/>
+      <c r="R52" s="55" t="n"/>
+      <c r="S52" s="55" t="n"/>
+      <c r="T52" s="55" t="n"/>
+      <c r="U52" s="55" t="n"/>
+      <c r="V52" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W52" s="57" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="53" t="n"/>
-      <c r="D53" s="53" t="n"/>
+      <c r="C53" s="46" t="n"/>
+      <c r="D53" s="46" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G53" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G53" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H53" s="49" t="n"/>
       <c r="I53" s="49" t="n"/>
       <c r="J53" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="55" t="n"/>
-      <c r="N53" s="55" t="n"/>
-      <c r="O53" s="55" t="n"/>
-      <c r="P53" s="55" t="n"/>
-      <c r="Q53" s="55" t="n"/>
-      <c r="R53" s="55" t="n"/>
-      <c r="S53" s="55" t="n"/>
-      <c r="T53" s="55" t="n"/>
-      <c r="U53" s="55" t="n"/>
-      <c r="V53" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W53" s="57" t="n"/>
+      <c r="M53" s="51" t="n"/>
+      <c r="N53" s="51" t="n"/>
+      <c r="O53" s="51" t="n"/>
+      <c r="P53" s="51" t="n"/>
+      <c r="Q53" s="51" t="n"/>
+      <c r="R53" s="51" t="n"/>
+      <c r="S53" s="51" t="n"/>
+      <c r="T53" s="51" t="n"/>
+      <c r="U53" s="51" t="n"/>
+      <c r="V53" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W53" s="58" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="46" t="n"/>
-      <c r="D54" s="46" t="n"/>
+      <c r="C54" s="53" t="n"/>
+      <c r="D54" s="53" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G54" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G54" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="51" t="n"/>
-      <c r="N54" s="51" t="n"/>
-      <c r="O54" s="51" t="n"/>
-      <c r="P54" s="51" t="n"/>
-      <c r="Q54" s="51" t="n"/>
-      <c r="R54" s="51" t="n"/>
-      <c r="S54" s="51" t="n"/>
-      <c r="T54" s="51" t="n"/>
-      <c r="U54" s="51" t="n"/>
-      <c r="V54" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W54" s="58" t="n"/>
+      <c r="M54" s="55" t="n"/>
+      <c r="N54" s="55" t="n"/>
+      <c r="O54" s="55" t="n"/>
+      <c r="P54" s="55" t="n"/>
+      <c r="Q54" s="55" t="n"/>
+      <c r="R54" s="55" t="n"/>
+      <c r="S54" s="55" t="n"/>
+      <c r="T54" s="55" t="n"/>
+      <c r="U54" s="55" t="n"/>
+      <c r="V54" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W54" s="57" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="53" t="n"/>
-      <c r="D55" s="53" t="n"/>
+      <c r="C55" s="46" t="n"/>
+      <c r="D55" s="46" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G55" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G55" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="55" t="n"/>
-      <c r="N55" s="55" t="n"/>
-      <c r="O55" s="55" t="n"/>
-      <c r="P55" s="55" t="n"/>
-      <c r="Q55" s="55" t="n"/>
-      <c r="R55" s="55" t="n"/>
-      <c r="S55" s="55" t="n"/>
-      <c r="T55" s="55" t="n"/>
-      <c r="U55" s="55" t="n"/>
-      <c r="V55" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W55" s="57" t="n"/>
+      <c r="M55" s="51" t="n"/>
+      <c r="N55" s="51" t="n"/>
+      <c r="O55" s="51" t="n"/>
+      <c r="P55" s="51" t="n"/>
+      <c r="Q55" s="51" t="n"/>
+      <c r="R55" s="51" t="n"/>
+      <c r="S55" s="51" t="n"/>
+      <c r="T55" s="51" t="n"/>
+      <c r="U55" s="51" t="n"/>
+      <c r="V55" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W55" s="58" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="46" t="n"/>
-      <c r="D56" s="46" t="n"/>
+      <c r="C56" s="53" t="n"/>
+      <c r="D56" s="53" t="n"/>
       <c r="E56" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F56" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G56" s="48" t="n">
-        <v>24</v>
+      <c r="G56" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="51" t="n"/>
-      <c r="N56" s="51" t="n"/>
-      <c r="O56" s="51" t="n"/>
-      <c r="P56" s="51" t="n"/>
-      <c r="Q56" s="51" t="n"/>
-      <c r="R56" s="51" t="n"/>
-      <c r="S56" s="51" t="n"/>
-      <c r="T56" s="51" t="n"/>
-      <c r="U56" s="51" t="n"/>
-      <c r="V56" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W56" s="58" t="n"/>
+      <c r="M56" s="55" t="n"/>
+      <c r="N56" s="55" t="n"/>
+      <c r="O56" s="55" t="n"/>
+      <c r="P56" s="55" t="n"/>
+      <c r="Q56" s="55" t="n"/>
+      <c r="R56" s="55" t="n"/>
+      <c r="S56" s="55" t="n"/>
+      <c r="T56" s="55" t="n"/>
+      <c r="U56" s="55" t="n"/>
+      <c r="V56" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W56" s="57" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="53" t="n"/>
-      <c r="D57" s="53" t="n"/>
+      <c r="C57" s="46" t="n"/>
+      <c r="D57" s="46" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G57" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G57" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="55" t="n"/>
-      <c r="N57" s="55" t="n"/>
-      <c r="O57" s="55" t="n"/>
-      <c r="P57" s="55" t="n"/>
-      <c r="Q57" s="55" t="n"/>
-      <c r="R57" s="55" t="n"/>
-      <c r="S57" s="55" t="n"/>
-      <c r="T57" s="55" t="n"/>
-      <c r="U57" s="55" t="n"/>
-      <c r="V57" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W57" s="57" t="n"/>
+      <c r="M57" s="51" t="n"/>
+      <c r="N57" s="51" t="n"/>
+      <c r="O57" s="51" t="n"/>
+      <c r="P57" s="51" t="n"/>
+      <c r="Q57" s="51" t="n"/>
+      <c r="R57" s="51" t="n"/>
+      <c r="S57" s="51" t="n"/>
+      <c r="T57" s="51" t="n"/>
+      <c r="U57" s="51" t="n"/>
+      <c r="V57" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W57" s="58" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="46" t="n"/>
-      <c r="D58" s="46" t="n"/>
+      <c r="C58" s="53" t="n"/>
+      <c r="D58" s="53" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G58" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G58" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="51" t="n"/>
-      <c r="N58" s="51" t="n"/>
-      <c r="O58" s="51" t="n"/>
-      <c r="P58" s="51" t="n"/>
-      <c r="Q58" s="51" t="n"/>
-      <c r="R58" s="51" t="n"/>
-      <c r="S58" s="51" t="n"/>
-      <c r="T58" s="51" t="n"/>
-      <c r="U58" s="51" t="n"/>
-      <c r="V58" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W58" s="58" t="n"/>
+      <c r="M58" s="55" t="n"/>
+      <c r="N58" s="55" t="n"/>
+      <c r="O58" s="55" t="n"/>
+      <c r="P58" s="55" t="n"/>
+      <c r="Q58" s="55" t="n"/>
+      <c r="R58" s="55" t="n"/>
+      <c r="S58" s="55" t="n"/>
+      <c r="T58" s="55" t="n"/>
+      <c r="U58" s="55" t="n"/>
+      <c r="V58" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W58" s="57" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="53" t="n"/>
-      <c r="D59" s="53" t="n"/>
+      <c r="C59" s="46" t="n"/>
+      <c r="D59" s="46" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G59" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
@@ -4515,51 +4539,92 @@
         <v>59</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="55" t="n"/>
-      <c r="N59" s="55" t="n"/>
-      <c r="O59" s="55" t="n"/>
-      <c r="P59" s="55" t="n"/>
-      <c r="Q59" s="55" t="n"/>
-      <c r="R59" s="55" t="n"/>
-      <c r="S59" s="55" t="n"/>
-      <c r="T59" s="55" t="n"/>
-      <c r="U59" s="55" t="n"/>
-      <c r="V59" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W59" s="57" t="n"/>
+      <c r="M59" s="51" t="n"/>
+      <c r="N59" s="51" t="n"/>
+      <c r="O59" s="51" t="n"/>
+      <c r="P59" s="51" t="n"/>
+      <c r="Q59" s="51" t="n"/>
+      <c r="R59" s="51" t="n"/>
+      <c r="S59" s="51" t="n"/>
+      <c r="T59" s="51" t="n"/>
+      <c r="U59" s="51" t="n"/>
+      <c r="V59" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W59" s="58" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
-      <c r="E60" s="47" t="n"/>
-      <c r="F60" s="47" t="n"/>
-      <c r="G60" s="60" t="n"/>
+      <c r="C60" s="53" t="n"/>
+      <c r="D60" s="53" t="n"/>
+      <c r="E60" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F60" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G60" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
-      <c r="J60" s="50" t="n"/>
-      <c r="K60" s="50" t="n"/>
+      <c r="J60" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K60" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="51" t="n"/>
-      <c r="N60" s="51" t="n"/>
-      <c r="O60" s="51" t="n"/>
-      <c r="P60" s="51" t="n"/>
-      <c r="Q60" s="51" t="n"/>
-      <c r="R60" s="51" t="n"/>
-      <c r="S60" s="51" t="n"/>
-      <c r="T60" s="51" t="n"/>
-      <c r="U60" s="51" t="n"/>
-      <c r="V60" s="61" t="n"/>
-      <c r="W60" s="61" t="n"/>
+      <c r="M60" s="55" t="n"/>
+      <c r="N60" s="55" t="n"/>
+      <c r="O60" s="55" t="n"/>
+      <c r="P60" s="55" t="n"/>
+      <c r="Q60" s="55" t="n"/>
+      <c r="R60" s="55" t="n"/>
+      <c r="S60" s="55" t="n"/>
+      <c r="T60" s="55" t="n"/>
+      <c r="U60" s="55" t="n"/>
+      <c r="V60" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W60" s="57" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B61" s="45" t="n"/>
+      <c r="C61" s="46" t="n"/>
+      <c r="D61" s="46" t="n"/>
+      <c r="E61" s="47" t="n"/>
+      <c r="F61" s="47" t="n"/>
+      <c r="G61" s="60" t="n"/>
+      <c r="H61" s="49" t="n"/>
+      <c r="I61" s="49" t="n"/>
+      <c r="J61" s="50" t="n"/>
+      <c r="K61" s="50" t="n"/>
+      <c r="L61" s="50" t="n"/>
+      <c r="M61" s="51" t="n"/>
+      <c r="N61" s="51" t="n"/>
+      <c r="O61" s="51" t="n"/>
+      <c r="P61" s="51" t="n"/>
+      <c r="Q61" s="51" t="n"/>
+      <c r="R61" s="51" t="n"/>
+      <c r="S61" s="51" t="n"/>
+      <c r="T61" s="51" t="n"/>
+      <c r="U61" s="51" t="n"/>
+      <c r="V61" s="61" t="n"/>
+      <c r="W61" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="50">
+  <fonts count="51">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -359,8 +359,14 @@
       <color rgb="00B71C1C"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00F57F17"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="73">
+  <fills count="74">
     <fill>
       <patternFill/>
     </fill>
@@ -783,6 +789,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFCDD2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -1084,7 +1095,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1292,6 +1303,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="72" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="73" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1706,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W61"/>
+  <dimension ref="A1:W62"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1968,43 +1982,47 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G4" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G4" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H4" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I4" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K4" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L4" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" s="69" t="inlineStr"/>
-      <c r="N4" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M4" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N4" s="69" t="inlineStr"/>
+      <c r="O4" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O4" s="69" t="inlineStr"/>
       <c r="P4" s="69" t="inlineStr"/>
       <c r="Q4" s="69" t="inlineStr"/>
       <c r="R4" s="69" t="inlineStr"/>
@@ -2012,51 +2030,47 @@
       <c r="T4" s="69" t="inlineStr"/>
       <c r="U4" s="69" t="inlineStr"/>
       <c r="V4" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W4" s="69" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
       <c r="C5" s="64" t="inlineStr"/>
       <c r="D5" s="64" t="inlineStr"/>
       <c r="E5" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G5" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G5" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I5" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J5" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K5" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L5" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M5" s="69" t="inlineStr"/>
+      <c r="N5" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N5" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O5" s="69" t="inlineStr"/>
@@ -2067,254 +2081,250 @@
       <c r="T5" s="69" t="inlineStr"/>
       <c r="U5" s="69" t="inlineStr"/>
       <c r="V5" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W5" s="69" t="inlineStr"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B6" s="63" t="inlineStr"/>
+      <c r="C6" s="64" t="inlineStr"/>
+      <c r="D6" s="64" t="inlineStr"/>
+      <c r="E6" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F6" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G6" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H6" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L6" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N6" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O6" s="69" t="inlineStr"/>
+      <c r="P6" s="69" t="inlineStr"/>
+      <c r="Q6" s="69" t="inlineStr"/>
+      <c r="R6" s="69" t="inlineStr"/>
+      <c r="S6" s="69" t="inlineStr"/>
+      <c r="T6" s="69" t="inlineStr"/>
+      <c r="U6" s="69" t="inlineStr"/>
+      <c r="V6" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W5" s="69" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="W6" s="69" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D6" s="38" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E6" s="39" t="n">
+      <c r="E7" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F6" s="39" t="n">
+      <c r="F7" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G6" s="40" t="n">
+      <c r="G7" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H6" s="41" t="n">
+      <c r="H7" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="41" t="n">
+      <c r="I7" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J6" s="42" t="n">
+      <c r="J7" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K6" s="42" t="n">
+      <c r="K7" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L6" s="42" t="n">
+      <c r="L7" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="43" t="inlineStr">
+      <c r="M7" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N6" s="43" t="inlineStr"/>
-      <c r="O6" s="43" t="inlineStr">
+      <c r="N7" s="43" t="inlineStr"/>
+      <c r="O7" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P6" s="43" t="inlineStr"/>
-      <c r="Q6" s="43" t="inlineStr"/>
-      <c r="R6" s="43" t="inlineStr"/>
-      <c r="S6" s="43" t="inlineStr"/>
-      <c r="T6" s="43" t="inlineStr"/>
-      <c r="U6" s="43" t="inlineStr"/>
-      <c r="V6" s="43" t="n">
+      <c r="P7" s="43" t="inlineStr"/>
+      <c r="Q7" s="43" t="inlineStr"/>
+      <c r="R7" s="43" t="inlineStr"/>
+      <c r="S7" s="43" t="inlineStr"/>
+      <c r="T7" s="43" t="inlineStr"/>
+      <c r="U7" s="43" t="inlineStr"/>
+      <c r="V7" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W6" s="43" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B7" s="45" t="n"/>
-      <c r="C7" s="46" t="n"/>
-      <c r="D7" s="46" t="n"/>
-      <c r="E7" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F7" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G7" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H7" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K7" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L7" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M7" s="51" t="n"/>
-      <c r="N7" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O7" s="51" t="n"/>
-      <c r="P7" s="51" t="n"/>
-      <c r="Q7" s="51" t="n"/>
-      <c r="R7" s="51" t="n"/>
-      <c r="S7" s="51" t="n"/>
-      <c r="T7" s="51" t="n"/>
-      <c r="U7" s="51" t="n"/>
-      <c r="V7" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W7" s="43" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B8" s="45" t="n"/>
-      <c r="C8" s="53" t="n"/>
-      <c r="D8" s="53" t="n"/>
+      <c r="C8" s="46" t="n"/>
+      <c r="D8" s="46" t="n"/>
       <c r="E8" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F8" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G8" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G8" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H8" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I8" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J8" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K8" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L8" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M8" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N8" s="55" t="n"/>
-      <c r="O8" s="55" t="n"/>
-      <c r="P8" s="55" t="n"/>
-      <c r="Q8" s="55" t="n"/>
-      <c r="R8" s="55" t="n"/>
-      <c r="S8" s="55" t="n"/>
-      <c r="T8" s="55" t="n"/>
-      <c r="U8" s="55" t="n"/>
-      <c r="V8" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W8" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M8" s="51" t="n"/>
+      <c r="N8" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O8" s="51" t="n"/>
+      <c r="P8" s="51" t="n"/>
+      <c r="Q8" s="51" t="n"/>
+      <c r="R8" s="51" t="n"/>
+      <c r="S8" s="51" t="n"/>
+      <c r="T8" s="51" t="n"/>
+      <c r="U8" s="51" t="n"/>
+      <c r="V8" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B9" s="45" t="n"/>
-      <c r="C9" s="46" t="n"/>
-      <c r="D9" s="46" t="n"/>
+      <c r="C9" s="53" t="n"/>
+      <c r="D9" s="53" t="n"/>
       <c r="E9" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F9" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G9" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G9" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H9" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I9" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J9" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K9" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L9" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M9" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N9" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O9" s="51" t="n"/>
-      <c r="P9" s="51" t="n"/>
-      <c r="Q9" s="51" t="n"/>
-      <c r="R9" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S9" s="51" t="n"/>
-      <c r="T9" s="51" t="n"/>
-      <c r="U9" s="51" t="n"/>
-      <c r="V9" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W9" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M9" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N9" s="55" t="n"/>
+      <c r="O9" s="55" t="n"/>
+      <c r="P9" s="55" t="n"/>
+      <c r="Q9" s="55" t="n"/>
+      <c r="R9" s="55" t="n"/>
+      <c r="S9" s="55" t="n"/>
+      <c r="T9" s="55" t="n"/>
+      <c r="U9" s="55" t="n"/>
+      <c r="V9" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W9" s="57" t="n"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B10" s="45" t="n"/>
-      <c r="C10" s="53" t="n"/>
-      <c r="D10" s="53" t="n"/>
+      <c r="C10" s="46" t="n"/>
+      <c r="D10" s="46" t="n"/>
       <c r="E10" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F10" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G10" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H10" s="49" t="n">
         <v>1</v>
@@ -2323,493 +2333,497 @@
         <v>1</v>
       </c>
       <c r="J10" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K10" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L10" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M10" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M10" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N10" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N10" s="55" t="n"/>
-      <c r="O10" s="55" t="n"/>
-      <c r="P10" s="55" t="n"/>
-      <c r="Q10" s="55" t="inlineStr">
+      <c r="O10" s="51" t="n"/>
+      <c r="P10" s="51" t="n"/>
+      <c r="Q10" s="51" t="n"/>
+      <c r="R10" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R10" s="55" t="n"/>
-      <c r="S10" s="55" t="n"/>
-      <c r="T10" s="55" t="n"/>
-      <c r="U10" s="55" t="n"/>
-      <c r="V10" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W10" s="57" t="n"/>
+      <c r="S10" s="51" t="n"/>
+      <c r="T10" s="51" t="n"/>
+      <c r="U10" s="51" t="n"/>
+      <c r="V10" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W10" s="58" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B11" s="45" t="n"/>
-      <c r="C11" s="46" t="n"/>
-      <c r="D11" s="46" t="n"/>
+      <c r="C11" s="53" t="n"/>
+      <c r="D11" s="53" t="n"/>
       <c r="E11" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F11" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G11" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G11" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H11" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I11" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J11" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K11" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L11" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N11" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O11" s="51" t="n"/>
-      <c r="P11" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M11" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N11" s="55" t="n"/>
+      <c r="O11" s="55" t="n"/>
+      <c r="P11" s="55" t="n"/>
+      <c r="Q11" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q11" s="51" t="n"/>
-      <c r="R11" s="51" t="n"/>
-      <c r="S11" s="51" t="n"/>
-      <c r="T11" s="51" t="n"/>
-      <c r="U11" s="51" t="n"/>
-      <c r="V11" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W11" s="58" t="n"/>
+      <c r="R11" s="55" t="n"/>
+      <c r="S11" s="55" t="n"/>
+      <c r="T11" s="55" t="n"/>
+      <c r="U11" s="55" t="n"/>
+      <c r="V11" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W11" s="57" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B12" s="45" t="n"/>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
+      <c r="C12" s="46" t="n"/>
+      <c r="D12" s="46" t="n"/>
       <c r="E12" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F12" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G12" s="59" t="n">
-        <v>45.1</v>
+      <c r="G12" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H12" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I12" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J12" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K12" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L12" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N12" s="55" t="n"/>
-      <c r="O12" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P12" s="55" t="n"/>
-      <c r="Q12" s="55" t="n"/>
-      <c r="R12" s="55" t="n"/>
-      <c r="S12" s="55" t="n"/>
-      <c r="T12" s="55" t="n"/>
-      <c r="U12" s="55" t="n"/>
-      <c r="V12" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W12" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M12" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N12" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O12" s="51" t="n"/>
+      <c r="P12" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q12" s="51" t="n"/>
+      <c r="R12" s="51" t="n"/>
+      <c r="S12" s="51" t="n"/>
+      <c r="T12" s="51" t="n"/>
+      <c r="U12" s="51" t="n"/>
+      <c r="V12" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W12" s="58" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B13" s="45" t="n"/>
-      <c r="C13" s="46" t="n"/>
-      <c r="D13" s="46" t="n"/>
+      <c r="C13" s="53" t="n"/>
+      <c r="D13" s="53" t="n"/>
       <c r="E13" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F13" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G13" s="54" t="n">
-        <v>26.3</v>
+      <c r="G13" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H13" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I13" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J13" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K13" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L13" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M13" s="51" t="n"/>
-      <c r="N13" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M13" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N13" s="55" t="n"/>
+      <c r="O13" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O13" s="51" t="n"/>
-      <c r="P13" s="51" t="n"/>
-      <c r="Q13" s="51" t="n"/>
-      <c r="R13" s="51" t="n"/>
-      <c r="S13" s="51" t="n"/>
-      <c r="T13" s="51" t="n"/>
-      <c r="U13" s="51" t="n"/>
-      <c r="V13" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W13" s="58" t="n"/>
+      <c r="P13" s="55" t="n"/>
+      <c r="Q13" s="55" t="n"/>
+      <c r="R13" s="55" t="n"/>
+      <c r="S13" s="55" t="n"/>
+      <c r="T13" s="55" t="n"/>
+      <c r="U13" s="55" t="n"/>
+      <c r="V13" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W13" s="57" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B14" s="45" t="n"/>
-      <c r="C14" s="53" t="n"/>
-      <c r="D14" s="53" t="n"/>
+      <c r="C14" s="46" t="n"/>
+      <c r="D14" s="46" t="n"/>
       <c r="E14" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F14" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G14" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H14" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K14" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L14" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M14" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M14" s="51" t="n"/>
+      <c r="N14" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N14" s="55" t="n"/>
-      <c r="O14" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P14" s="55" t="n"/>
-      <c r="Q14" s="55" t="n"/>
-      <c r="R14" s="55" t="n"/>
-      <c r="S14" s="55" t="n"/>
-      <c r="T14" s="55" t="n"/>
-      <c r="U14" s="55" t="n"/>
-      <c r="V14" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W14" s="57" t="n"/>
+      <c r="O14" s="51" t="n"/>
+      <c r="P14" s="51" t="n"/>
+      <c r="Q14" s="51" t="n"/>
+      <c r="R14" s="51" t="n"/>
+      <c r="S14" s="51" t="n"/>
+      <c r="T14" s="51" t="n"/>
+      <c r="U14" s="51" t="n"/>
+      <c r="V14" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W14" s="58" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B15" s="45" t="n"/>
-      <c r="C15" s="46" t="n"/>
-      <c r="D15" s="46" t="n"/>
+      <c r="C15" s="53" t="n"/>
+      <c r="D15" s="53" t="n"/>
       <c r="E15" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F15" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G15" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H15" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I15" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J15" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K15" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L15" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M15" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N15" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O15" s="51" t="n"/>
-      <c r="P15" s="51" t="n"/>
-      <c r="Q15" s="51" t="n"/>
-      <c r="R15" s="51" t="n"/>
-      <c r="S15" s="51" t="n"/>
-      <c r="T15" s="51" t="n"/>
-      <c r="U15" s="51" t="n"/>
-      <c r="V15" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W15" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M15" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N15" s="55" t="n"/>
+      <c r="O15" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P15" s="55" t="n"/>
+      <c r="Q15" s="55" t="n"/>
+      <c r="R15" s="55" t="n"/>
+      <c r="S15" s="55" t="n"/>
+      <c r="T15" s="55" t="n"/>
+      <c r="U15" s="55" t="n"/>
+      <c r="V15" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W15" s="57" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B16" s="45" t="n"/>
-      <c r="C16" s="53" t="n"/>
-      <c r="D16" s="53" t="n"/>
+      <c r="C16" s="46" t="n"/>
+      <c r="D16" s="46" t="n"/>
       <c r="E16" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F16" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G16" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H16" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K16" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L16" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I16" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K16" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L16" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" s="55" t="inlineStr">
+      <c r="M16" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N16" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N16" s="55" t="n"/>
-      <c r="O16" s="55" t="n"/>
-      <c r="P16" s="55" t="n"/>
-      <c r="Q16" s="55" t="n"/>
-      <c r="R16" s="55" t="n"/>
-      <c r="S16" s="55" t="n"/>
-      <c r="T16" s="55" t="n"/>
-      <c r="U16" s="55" t="n"/>
-      <c r="V16" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W16" s="57" t="n"/>
+      <c r="O16" s="51" t="n"/>
+      <c r="P16" s="51" t="n"/>
+      <c r="Q16" s="51" t="n"/>
+      <c r="R16" s="51" t="n"/>
+      <c r="S16" s="51" t="n"/>
+      <c r="T16" s="51" t="n"/>
+      <c r="U16" s="51" t="n"/>
+      <c r="V16" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W16" s="58" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B17" s="45" t="n"/>
-      <c r="C17" s="46" t="n"/>
-      <c r="D17" s="46" t="n"/>
+      <c r="C17" s="53" t="n"/>
+      <c r="D17" s="53" t="n"/>
       <c r="E17" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F17" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G17" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G17" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H17" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J17" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K17" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L17" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M17" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N17" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O17" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P17" s="51" t="n"/>
-      <c r="Q17" s="51" t="n"/>
-      <c r="R17" s="51" t="n"/>
-      <c r="S17" s="51" t="n"/>
-      <c r="T17" s="51" t="n"/>
-      <c r="U17" s="51" t="n"/>
-      <c r="V17" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W17" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M17" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N17" s="55" t="n"/>
+      <c r="O17" s="55" t="n"/>
+      <c r="P17" s="55" t="n"/>
+      <c r="Q17" s="55" t="n"/>
+      <c r="R17" s="55" t="n"/>
+      <c r="S17" s="55" t="n"/>
+      <c r="T17" s="55" t="n"/>
+      <c r="U17" s="55" t="n"/>
+      <c r="V17" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W17" s="57" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B18" s="45" t="n"/>
-      <c r="C18" s="53" t="n"/>
-      <c r="D18" s="53" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="46" t="n"/>
       <c r="E18" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F18" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G18" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G18" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H18" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I18" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J18" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K18" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L18" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M18" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N18" s="55" t="inlineStr">
+      <c r="M18" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N18" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O18" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O18" s="55" t="n"/>
-      <c r="P18" s="55" t="n"/>
-      <c r="Q18" s="55" t="n"/>
-      <c r="R18" s="55" t="n"/>
-      <c r="S18" s="55" t="n"/>
-      <c r="T18" s="55" t="n"/>
-      <c r="U18" s="55" t="n"/>
-      <c r="V18" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W18" s="57" t="n"/>
+      <c r="P18" s="51" t="n"/>
+      <c r="Q18" s="51" t="n"/>
+      <c r="R18" s="51" t="n"/>
+      <c r="S18" s="51" t="n"/>
+      <c r="T18" s="51" t="n"/>
+      <c r="U18" s="51" t="n"/>
+      <c r="V18" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W18" s="58" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B19" s="45" t="n"/>
-      <c r="C19" s="46" t="n"/>
-      <c r="D19" s="46" t="n"/>
+      <c r="C19" s="53" t="n"/>
+      <c r="D19" s="53" t="n"/>
       <c r="E19" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F19" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G19" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H19" s="49" t="n">
         <v>2</v>
@@ -2818,208 +2832,218 @@
         <v>2</v>
       </c>
       <c r="J19" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K19" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L19" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M19" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M19" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N19" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N19" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O19" s="51" t="n"/>
-      <c r="P19" s="51" t="n"/>
-      <c r="Q19" s="51" t="n"/>
-      <c r="R19" s="51" t="n"/>
-      <c r="S19" s="51" t="n"/>
-      <c r="T19" s="51" t="n"/>
-      <c r="U19" s="51" t="n"/>
-      <c r="V19" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W19" s="58" t="n"/>
+      <c r="O19" s="55" t="n"/>
+      <c r="P19" s="55" t="n"/>
+      <c r="Q19" s="55" t="n"/>
+      <c r="R19" s="55" t="n"/>
+      <c r="S19" s="55" t="n"/>
+      <c r="T19" s="55" t="n"/>
+      <c r="U19" s="55" t="n"/>
+      <c r="V19" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W19" s="57" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B20" s="45" t="n"/>
-      <c r="C20" s="53" t="n"/>
-      <c r="D20" s="53" t="n"/>
+      <c r="C20" s="46" t="n"/>
+      <c r="D20" s="46" t="n"/>
       <c r="E20" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F20" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G20" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H20" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J20" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K20" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L20" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M20" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M20" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N20" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N20" s="55" t="n"/>
-      <c r="O20" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P20" s="55" t="n"/>
-      <c r="Q20" s="55" t="n"/>
-      <c r="R20" s="55" t="n"/>
-      <c r="S20" s="55" t="n"/>
-      <c r="T20" s="55" t="n"/>
-      <c r="U20" s="55" t="n"/>
-      <c r="V20" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W20" s="57" t="n"/>
+      <c r="O20" s="51" t="n"/>
+      <c r="P20" s="51" t="n"/>
+      <c r="Q20" s="51" t="n"/>
+      <c r="R20" s="51" t="n"/>
+      <c r="S20" s="51" t="n"/>
+      <c r="T20" s="51" t="n"/>
+      <c r="U20" s="51" t="n"/>
+      <c r="V20" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W20" s="58" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="46" t="n"/>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="53" t="n"/>
       <c r="E21" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F21" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G21" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G21" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H21" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J21" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K21" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L21" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M21" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N21" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O21" s="51" t="n"/>
-      <c r="P21" s="51" t="n"/>
-      <c r="Q21" s="51" t="n"/>
-      <c r="R21" s="51" t="n"/>
-      <c r="S21" s="51" t="n"/>
-      <c r="T21" s="51" t="n"/>
-      <c r="U21" s="51" t="n"/>
-      <c r="V21" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W21" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M21" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N21" s="55" t="n"/>
+      <c r="O21" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P21" s="55" t="n"/>
+      <c r="Q21" s="55" t="n"/>
+      <c r="R21" s="55" t="n"/>
+      <c r="S21" s="55" t="n"/>
+      <c r="T21" s="55" t="n"/>
+      <c r="U21" s="55" t="n"/>
+      <c r="V21" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W21" s="57" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="53" t="n"/>
+      <c r="C22" s="46" t="n"/>
+      <c r="D22" s="46" t="n"/>
       <c r="E22" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G22" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G22" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H22" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K22" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L22" s="50" t="n"/>
-      <c r="M22" s="55" t="n"/>
-      <c r="N22" s="55" t="n"/>
-      <c r="O22" s="55" t="n"/>
-      <c r="P22" s="55" t="n"/>
-      <c r="Q22" s="55" t="n"/>
-      <c r="R22" s="55" t="n"/>
-      <c r="S22" s="55" t="n"/>
-      <c r="T22" s="55" t="n"/>
-      <c r="U22" s="55" t="n"/>
-      <c r="V22" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W22" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L22" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M22" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N22" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O22" s="51" t="n"/>
+      <c r="P22" s="51" t="n"/>
+      <c r="Q22" s="51" t="n"/>
+      <c r="R22" s="51" t="n"/>
+      <c r="S22" s="51" t="n"/>
+      <c r="T22" s="51" t="n"/>
+      <c r="U22" s="51" t="n"/>
+      <c r="V22" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W22" s="58" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="46" t="n"/>
-      <c r="D23" s="46" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G23" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H23" s="49" t="n">
         <v>0</v>
@@ -3028,43 +3052,43 @@
         <v>0</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L23" s="50" t="n"/>
-      <c r="M23" s="51" t="n"/>
-      <c r="N23" s="51" t="n"/>
-      <c r="O23" s="51" t="n"/>
-      <c r="P23" s="51" t="n"/>
-      <c r="Q23" s="51" t="n"/>
-      <c r="R23" s="51" t="n"/>
-      <c r="S23" s="51" t="n"/>
-      <c r="T23" s="51" t="n"/>
-      <c r="U23" s="51" t="n"/>
-      <c r="V23" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W23" s="58" t="n"/>
+      <c r="M23" s="55" t="n"/>
+      <c r="N23" s="55" t="n"/>
+      <c r="O23" s="55" t="n"/>
+      <c r="P23" s="55" t="n"/>
+      <c r="Q23" s="55" t="n"/>
+      <c r="R23" s="55" t="n"/>
+      <c r="S23" s="55" t="n"/>
+      <c r="T23" s="55" t="n"/>
+      <c r="U23" s="55" t="n"/>
+      <c r="V23" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W23" s="57" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
+      <c r="C24" s="46" t="n"/>
+      <c r="D24" s="46" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G24" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H24" s="49" t="n">
         <v>0</v>
@@ -3073,43 +3097,43 @@
         <v>0</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L24" s="50" t="n"/>
-      <c r="M24" s="55" t="n"/>
-      <c r="N24" s="55" t="n"/>
-      <c r="O24" s="55" t="n"/>
-      <c r="P24" s="55" t="n"/>
-      <c r="Q24" s="55" t="n"/>
-      <c r="R24" s="55" t="n"/>
-      <c r="S24" s="55" t="n"/>
-      <c r="T24" s="55" t="n"/>
-      <c r="U24" s="55" t="n"/>
-      <c r="V24" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W24" s="57" t="n"/>
+      <c r="M24" s="51" t="n"/>
+      <c r="N24" s="51" t="n"/>
+      <c r="O24" s="51" t="n"/>
+      <c r="P24" s="51" t="n"/>
+      <c r="Q24" s="51" t="n"/>
+      <c r="R24" s="51" t="n"/>
+      <c r="S24" s="51" t="n"/>
+      <c r="T24" s="51" t="n"/>
+      <c r="U24" s="51" t="n"/>
+      <c r="V24" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W24" s="58" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="46" t="n"/>
-      <c r="D25" s="46" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G25" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G25" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H25" s="49" t="n">
         <v>0</v>
@@ -3118,43 +3142,43 @@
         <v>0</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L25" s="50" t="n"/>
-      <c r="M25" s="51" t="n"/>
-      <c r="N25" s="51" t="n"/>
-      <c r="O25" s="51" t="n"/>
-      <c r="P25" s="51" t="n"/>
-      <c r="Q25" s="51" t="n"/>
-      <c r="R25" s="51" t="n"/>
-      <c r="S25" s="51" t="n"/>
-      <c r="T25" s="51" t="n"/>
-      <c r="U25" s="51" t="n"/>
-      <c r="V25" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W25" s="58" t="n"/>
+      <c r="M25" s="55" t="n"/>
+      <c r="N25" s="55" t="n"/>
+      <c r="O25" s="55" t="n"/>
+      <c r="P25" s="55" t="n"/>
+      <c r="Q25" s="55" t="n"/>
+      <c r="R25" s="55" t="n"/>
+      <c r="S25" s="55" t="n"/>
+      <c r="T25" s="55" t="n"/>
+      <c r="U25" s="55" t="n"/>
+      <c r="V25" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W25" s="57" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="53" t="n"/>
-      <c r="D26" s="53" t="n"/>
+      <c r="C26" s="46" t="n"/>
+      <c r="D26" s="46" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G26" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H26" s="49" t="n">
         <v>0</v>
@@ -3163,43 +3187,43 @@
         <v>0</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L26" s="50" t="n"/>
-      <c r="M26" s="55" t="n"/>
-      <c r="N26" s="55" t="n"/>
-      <c r="O26" s="55" t="n"/>
-      <c r="P26" s="55" t="n"/>
-      <c r="Q26" s="55" t="n"/>
-      <c r="R26" s="55" t="n"/>
-      <c r="S26" s="55" t="n"/>
-      <c r="T26" s="55" t="n"/>
-      <c r="U26" s="55" t="n"/>
-      <c r="V26" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W26" s="57" t="n"/>
+      <c r="M26" s="51" t="n"/>
+      <c r="N26" s="51" t="n"/>
+      <c r="O26" s="51" t="n"/>
+      <c r="P26" s="51" t="n"/>
+      <c r="Q26" s="51" t="n"/>
+      <c r="R26" s="51" t="n"/>
+      <c r="S26" s="51" t="n"/>
+      <c r="T26" s="51" t="n"/>
+      <c r="U26" s="51" t="n"/>
+      <c r="V26" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W26" s="58" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="46" t="n"/>
-      <c r="D27" s="46" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G27" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H27" s="49" t="n">
         <v>0</v>
@@ -3208,1371 +3232,1375 @@
         <v>0</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L27" s="50" t="n"/>
-      <c r="M27" s="51" t="n"/>
-      <c r="N27" s="51" t="n"/>
-      <c r="O27" s="51" t="n"/>
-      <c r="P27" s="51" t="n"/>
-      <c r="Q27" s="51" t="n"/>
-      <c r="R27" s="51" t="n"/>
-      <c r="S27" s="51" t="n"/>
-      <c r="T27" s="51" t="n"/>
-      <c r="U27" s="51" t="n"/>
-      <c r="V27" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W27" s="58" t="n"/>
+      <c r="M27" s="55" t="n"/>
+      <c r="N27" s="55" t="n"/>
+      <c r="O27" s="55" t="n"/>
+      <c r="P27" s="55" t="n"/>
+      <c r="Q27" s="55" t="n"/>
+      <c r="R27" s="55" t="n"/>
+      <c r="S27" s="55" t="n"/>
+      <c r="T27" s="55" t="n"/>
+      <c r="U27" s="55" t="n"/>
+      <c r="V27" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W27" s="57" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="53" t="n"/>
-      <c r="D28" s="53" t="n"/>
+      <c r="C28" s="46" t="n"/>
+      <c r="D28" s="46" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G28" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H28" s="49" t="n"/>
-      <c r="I28" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G28" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H28" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J28" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L28" s="50" t="n"/>
-      <c r="M28" s="55" t="n"/>
-      <c r="N28" s="55" t="n"/>
-      <c r="O28" s="55" t="n"/>
-      <c r="P28" s="55" t="n"/>
-      <c r="Q28" s="55" t="n"/>
-      <c r="R28" s="55" t="n"/>
-      <c r="S28" s="55" t="n"/>
-      <c r="T28" s="55" t="n"/>
-      <c r="U28" s="55" t="n"/>
-      <c r="V28" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W28" s="57" t="n"/>
+      <c r="M28" s="51" t="n"/>
+      <c r="N28" s="51" t="n"/>
+      <c r="O28" s="51" t="n"/>
+      <c r="P28" s="51" t="n"/>
+      <c r="Q28" s="51" t="n"/>
+      <c r="R28" s="51" t="n"/>
+      <c r="S28" s="51" t="n"/>
+      <c r="T28" s="51" t="n"/>
+      <c r="U28" s="51" t="n"/>
+      <c r="V28" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W28" s="58" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="46" t="n"/>
-      <c r="D29" s="46" t="n"/>
+      <c r="C29" s="53" t="n"/>
+      <c r="D29" s="53" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G29" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H29" s="49" t="n"/>
       <c r="I29" s="49" t="n"/>
       <c r="J29" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L29" s="50" t="n"/>
-      <c r="M29" s="51" t="n"/>
-      <c r="N29" s="51" t="n"/>
-      <c r="O29" s="51" t="n"/>
-      <c r="P29" s="51" t="n"/>
-      <c r="Q29" s="51" t="n"/>
-      <c r="R29" s="51" t="n"/>
-      <c r="S29" s="51" t="n"/>
-      <c r="T29" s="51" t="n"/>
-      <c r="U29" s="51" t="n"/>
-      <c r="V29" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W29" s="58" t="n"/>
+      <c r="M29" s="55" t="n"/>
+      <c r="N29" s="55" t="n"/>
+      <c r="O29" s="55" t="n"/>
+      <c r="P29" s="55" t="n"/>
+      <c r="Q29" s="55" t="n"/>
+      <c r="R29" s="55" t="n"/>
+      <c r="S29" s="55" t="n"/>
+      <c r="T29" s="55" t="n"/>
+      <c r="U29" s="55" t="n"/>
+      <c r="V29" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W29" s="57" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="53" t="n"/>
-      <c r="D30" s="53" t="n"/>
+      <c r="C30" s="46" t="n"/>
+      <c r="D30" s="46" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G30" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H30" s="49" t="n"/>
       <c r="I30" s="49" t="n"/>
       <c r="J30" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L30" s="50" t="n"/>
-      <c r="M30" s="55" t="n"/>
-      <c r="N30" s="55" t="n"/>
-      <c r="O30" s="55" t="n"/>
-      <c r="P30" s="55" t="n"/>
-      <c r="Q30" s="55" t="n"/>
-      <c r="R30" s="55" t="n"/>
-      <c r="S30" s="55" t="n"/>
-      <c r="T30" s="55" t="n"/>
-      <c r="U30" s="55" t="n"/>
-      <c r="V30" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W30" s="57" t="n"/>
+      <c r="M30" s="51" t="n"/>
+      <c r="N30" s="51" t="n"/>
+      <c r="O30" s="51" t="n"/>
+      <c r="P30" s="51" t="n"/>
+      <c r="Q30" s="51" t="n"/>
+      <c r="R30" s="51" t="n"/>
+      <c r="S30" s="51" t="n"/>
+      <c r="T30" s="51" t="n"/>
+      <c r="U30" s="51" t="n"/>
+      <c r="V30" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W30" s="58" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="46" t="n"/>
-      <c r="D31" s="46" t="n"/>
+      <c r="C31" s="53" t="n"/>
+      <c r="D31" s="53" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G31" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H31" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I31" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H31" s="49" t="n"/>
+      <c r="I31" s="49" t="n"/>
       <c r="J31" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L31" s="50" t="n"/>
-      <c r="M31" s="51" t="n"/>
-      <c r="N31" s="51" t="n"/>
-      <c r="O31" s="51" t="n"/>
-      <c r="P31" s="51" t="n"/>
-      <c r="Q31" s="51" t="n"/>
-      <c r="R31" s="51" t="n"/>
-      <c r="S31" s="51" t="n"/>
-      <c r="T31" s="51" t="n"/>
-      <c r="U31" s="51" t="n"/>
-      <c r="V31" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W31" s="58" t="n"/>
+      <c r="M31" s="55" t="n"/>
+      <c r="N31" s="55" t="n"/>
+      <c r="O31" s="55" t="n"/>
+      <c r="P31" s="55" t="n"/>
+      <c r="Q31" s="55" t="n"/>
+      <c r="R31" s="55" t="n"/>
+      <c r="S31" s="55" t="n"/>
+      <c r="T31" s="55" t="n"/>
+      <c r="U31" s="55" t="n"/>
+      <c r="V31" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W31" s="57" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="53" t="n"/>
-      <c r="D32" s="53" t="n"/>
+      <c r="C32" s="46" t="n"/>
+      <c r="D32" s="46" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G32" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H32" s="49" t="n"/>
-      <c r="I32" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G32" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H32" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I32" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J32" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L32" s="50" t="n"/>
-      <c r="M32" s="55" t="n"/>
-      <c r="N32" s="55" t="n"/>
-      <c r="O32" s="55" t="n"/>
-      <c r="P32" s="55" t="n"/>
-      <c r="Q32" s="55" t="n"/>
-      <c r="R32" s="55" t="n"/>
-      <c r="S32" s="55" t="n"/>
-      <c r="T32" s="55" t="n"/>
-      <c r="U32" s="55" t="n"/>
-      <c r="V32" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W32" s="57" t="n"/>
+      <c r="M32" s="51" t="n"/>
+      <c r="N32" s="51" t="n"/>
+      <c r="O32" s="51" t="n"/>
+      <c r="P32" s="51" t="n"/>
+      <c r="Q32" s="51" t="n"/>
+      <c r="R32" s="51" t="n"/>
+      <c r="S32" s="51" t="n"/>
+      <c r="T32" s="51" t="n"/>
+      <c r="U32" s="51" t="n"/>
+      <c r="V32" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W32" s="58" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="46" t="n"/>
-      <c r="D33" s="46" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G33" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G33" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H33" s="49" t="n"/>
       <c r="I33" s="49" t="n"/>
       <c r="J33" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L33" s="50" t="n"/>
-      <c r="M33" s="51" t="n"/>
-      <c r="N33" s="51" t="n"/>
-      <c r="O33" s="51" t="n"/>
-      <c r="P33" s="51" t="n"/>
-      <c r="Q33" s="51" t="n"/>
-      <c r="R33" s="51" t="n"/>
-      <c r="S33" s="51" t="n"/>
-      <c r="T33" s="51" t="n"/>
-      <c r="U33" s="51" t="n"/>
-      <c r="V33" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W33" s="58" t="n"/>
+      <c r="M33" s="55" t="n"/>
+      <c r="N33" s="55" t="n"/>
+      <c r="O33" s="55" t="n"/>
+      <c r="P33" s="55" t="n"/>
+      <c r="Q33" s="55" t="n"/>
+      <c r="R33" s="55" t="n"/>
+      <c r="S33" s="55" t="n"/>
+      <c r="T33" s="55" t="n"/>
+      <c r="U33" s="55" t="n"/>
+      <c r="V33" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W33" s="57" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="53" t="n"/>
-      <c r="D34" s="53" t="n"/>
+      <c r="C34" s="46" t="n"/>
+      <c r="D34" s="46" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G34" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G34" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H34" s="49" t="n"/>
       <c r="I34" s="49" t="n"/>
       <c r="J34" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K34" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K34" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L34" s="50" t="n"/>
-      <c r="M34" s="55" t="n"/>
-      <c r="N34" s="55" t="n"/>
-      <c r="O34" s="55" t="n"/>
-      <c r="P34" s="55" t="n"/>
-      <c r="Q34" s="55" t="n"/>
-      <c r="R34" s="55" t="n"/>
-      <c r="S34" s="55" t="n"/>
-      <c r="T34" s="55" t="n"/>
-      <c r="U34" s="55" t="n"/>
-      <c r="V34" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W34" s="57" t="n"/>
+      <c r="M34" s="51" t="n"/>
+      <c r="N34" s="51" t="n"/>
+      <c r="O34" s="51" t="n"/>
+      <c r="P34" s="51" t="n"/>
+      <c r="Q34" s="51" t="n"/>
+      <c r="R34" s="51" t="n"/>
+      <c r="S34" s="51" t="n"/>
+      <c r="T34" s="51" t="n"/>
+      <c r="U34" s="51" t="n"/>
+      <c r="V34" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W34" s="58" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="46" t="n"/>
-      <c r="D35" s="46" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G35" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H35" s="49" t="n"/>
       <c r="I35" s="49" t="n"/>
       <c r="J35" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L35" s="50" t="n"/>
-      <c r="M35" s="51" t="n"/>
-      <c r="N35" s="51" t="n"/>
-      <c r="O35" s="51" t="n"/>
-      <c r="P35" s="51" t="n"/>
-      <c r="Q35" s="51" t="n"/>
-      <c r="R35" s="51" t="n"/>
-      <c r="S35" s="51" t="n"/>
-      <c r="T35" s="51" t="n"/>
-      <c r="U35" s="51" t="n"/>
-      <c r="V35" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W35" s="58" t="n"/>
+      <c r="M35" s="55" t="n"/>
+      <c r="N35" s="55" t="n"/>
+      <c r="O35" s="55" t="n"/>
+      <c r="P35" s="55" t="n"/>
+      <c r="Q35" s="55" t="n"/>
+      <c r="R35" s="55" t="n"/>
+      <c r="S35" s="55" t="n"/>
+      <c r="T35" s="55" t="n"/>
+      <c r="U35" s="55" t="n"/>
+      <c r="V35" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W35" s="57" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
+      <c r="C36" s="46" t="n"/>
+      <c r="D36" s="46" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G36" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G36" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H36" s="49" t="n"/>
       <c r="I36" s="49" t="n"/>
       <c r="J36" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="55" t="n"/>
-      <c r="N36" s="55" t="n"/>
-      <c r="O36" s="55" t="n"/>
-      <c r="P36" s="55" t="n"/>
-      <c r="Q36" s="55" t="n"/>
-      <c r="R36" s="55" t="n"/>
-      <c r="S36" s="55" t="n"/>
-      <c r="T36" s="55" t="n"/>
-      <c r="U36" s="55" t="n"/>
-      <c r="V36" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W36" s="57" t="n"/>
+      <c r="M36" s="51" t="n"/>
+      <c r="N36" s="51" t="n"/>
+      <c r="O36" s="51" t="n"/>
+      <c r="P36" s="51" t="n"/>
+      <c r="Q36" s="51" t="n"/>
+      <c r="R36" s="51" t="n"/>
+      <c r="S36" s="51" t="n"/>
+      <c r="T36" s="51" t="n"/>
+      <c r="U36" s="51" t="n"/>
+      <c r="V36" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W36" s="58" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="46" t="n"/>
-      <c r="D37" s="46" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G37" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H37" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I37" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G37" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H37" s="49" t="n"/>
+      <c r="I37" s="49" t="n"/>
       <c r="J37" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="51" t="n"/>
-      <c r="N37" s="51" t="n"/>
-      <c r="O37" s="51" t="n"/>
-      <c r="P37" s="51" t="n"/>
-      <c r="Q37" s="51" t="n"/>
-      <c r="R37" s="51" t="n"/>
-      <c r="S37" s="51" t="n"/>
-      <c r="T37" s="51" t="n"/>
-      <c r="U37" s="51" t="n"/>
-      <c r="V37" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W37" s="58" t="n"/>
+      <c r="M37" s="55" t="n"/>
+      <c r="N37" s="55" t="n"/>
+      <c r="O37" s="55" t="n"/>
+      <c r="P37" s="55" t="n"/>
+      <c r="Q37" s="55" t="n"/>
+      <c r="R37" s="55" t="n"/>
+      <c r="S37" s="55" t="n"/>
+      <c r="T37" s="55" t="n"/>
+      <c r="U37" s="55" t="n"/>
+      <c r="V37" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W37" s="57" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="53" t="n"/>
-      <c r="D38" s="53" t="n"/>
+      <c r="C38" s="46" t="n"/>
+      <c r="D38" s="46" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G38" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H38" s="49" t="n"/>
-      <c r="I38" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H38" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I38" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J38" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="55" t="n"/>
-      <c r="N38" s="55" t="n"/>
-      <c r="O38" s="55" t="n"/>
-      <c r="P38" s="55" t="n"/>
-      <c r="Q38" s="55" t="n"/>
-      <c r="R38" s="55" t="n"/>
-      <c r="S38" s="55" t="n"/>
-      <c r="T38" s="55" t="n"/>
-      <c r="U38" s="55" t="n"/>
-      <c r="V38" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W38" s="57" t="n"/>
+      <c r="M38" s="51" t="n"/>
+      <c r="N38" s="51" t="n"/>
+      <c r="O38" s="51" t="n"/>
+      <c r="P38" s="51" t="n"/>
+      <c r="Q38" s="51" t="n"/>
+      <c r="R38" s="51" t="n"/>
+      <c r="S38" s="51" t="n"/>
+      <c r="T38" s="51" t="n"/>
+      <c r="U38" s="51" t="n"/>
+      <c r="V38" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W38" s="58" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="46" t="n"/>
-      <c r="D39" s="46" t="n"/>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G39" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H39" s="49" t="n"/>
       <c r="I39" s="49" t="n"/>
       <c r="J39" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="51" t="n"/>
-      <c r="N39" s="51" t="n"/>
-      <c r="O39" s="51" t="n"/>
-      <c r="P39" s="51" t="n"/>
-      <c r="Q39" s="51" t="n"/>
-      <c r="R39" s="51" t="n"/>
-      <c r="S39" s="51" t="n"/>
-      <c r="T39" s="51" t="n"/>
-      <c r="U39" s="51" t="n"/>
-      <c r="V39" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W39" s="58" t="n"/>
+      <c r="M39" s="55" t="n"/>
+      <c r="N39" s="55" t="n"/>
+      <c r="O39" s="55" t="n"/>
+      <c r="P39" s="55" t="n"/>
+      <c r="Q39" s="55" t="n"/>
+      <c r="R39" s="55" t="n"/>
+      <c r="S39" s="55" t="n"/>
+      <c r="T39" s="55" t="n"/>
+      <c r="U39" s="55" t="n"/>
+      <c r="V39" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W39" s="57" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="53" t="n"/>
-      <c r="D40" s="53" t="n"/>
+      <c r="C40" s="46" t="n"/>
+      <c r="D40" s="46" t="n"/>
       <c r="E40" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F40" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G40" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H40" s="49" t="n"/>
+      <c r="I40" s="49" t="n"/>
+      <c r="J40" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F40" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G40" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H40" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I40" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J40" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K40" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="55" t="n"/>
-      <c r="N40" s="55" t="n"/>
-      <c r="O40" s="55" t="n"/>
-      <c r="P40" s="55" t="n"/>
-      <c r="Q40" s="55" t="n"/>
-      <c r="R40" s="55" t="n"/>
-      <c r="S40" s="55" t="n"/>
-      <c r="T40" s="55" t="n"/>
-      <c r="U40" s="55" t="n"/>
-      <c r="V40" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W40" s="57" t="n"/>
+      <c r="M40" s="51" t="n"/>
+      <c r="N40" s="51" t="n"/>
+      <c r="O40" s="51" t="n"/>
+      <c r="P40" s="51" t="n"/>
+      <c r="Q40" s="51" t="n"/>
+      <c r="R40" s="51" t="n"/>
+      <c r="S40" s="51" t="n"/>
+      <c r="T40" s="51" t="n"/>
+      <c r="U40" s="51" t="n"/>
+      <c r="V40" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W40" s="58" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="46" t="n"/>
-      <c r="D41" s="46" t="n"/>
+      <c r="C41" s="53" t="n"/>
+      <c r="D41" s="53" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G41" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H41" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I41" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J41" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="51" t="n"/>
-      <c r="N41" s="51" t="n"/>
-      <c r="O41" s="51" t="n"/>
-      <c r="P41" s="51" t="n"/>
-      <c r="Q41" s="51" t="n"/>
-      <c r="R41" s="51" t="n"/>
-      <c r="S41" s="51" t="n"/>
-      <c r="T41" s="51" t="n"/>
-      <c r="U41" s="51" t="n"/>
-      <c r="V41" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W41" s="58" t="n"/>
+      <c r="M41" s="55" t="n"/>
+      <c r="N41" s="55" t="n"/>
+      <c r="O41" s="55" t="n"/>
+      <c r="P41" s="55" t="n"/>
+      <c r="Q41" s="55" t="n"/>
+      <c r="R41" s="55" t="n"/>
+      <c r="S41" s="55" t="n"/>
+      <c r="T41" s="55" t="n"/>
+      <c r="U41" s="55" t="n"/>
+      <c r="V41" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W41" s="57" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="53" t="n"/>
-      <c r="D42" s="53" t="n"/>
+      <c r="C42" s="46" t="n"/>
+      <c r="D42" s="46" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G42" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H42" s="49" t="n"/>
-      <c r="I42" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H42" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I42" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J42" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K42" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="55" t="n"/>
-      <c r="N42" s="55" t="n"/>
-      <c r="O42" s="55" t="n"/>
-      <c r="P42" s="55" t="n"/>
-      <c r="Q42" s="55" t="n"/>
-      <c r="R42" s="55" t="n"/>
-      <c r="S42" s="55" t="n"/>
-      <c r="T42" s="55" t="n"/>
-      <c r="U42" s="55" t="n"/>
-      <c r="V42" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W42" s="57" t="n"/>
+      <c r="M42" s="51" t="n"/>
+      <c r="N42" s="51" t="n"/>
+      <c r="O42" s="51" t="n"/>
+      <c r="P42" s="51" t="n"/>
+      <c r="Q42" s="51" t="n"/>
+      <c r="R42" s="51" t="n"/>
+      <c r="S42" s="51" t="n"/>
+      <c r="T42" s="51" t="n"/>
+      <c r="U42" s="51" t="n"/>
+      <c r="V42" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W42" s="58" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="46" t="n"/>
-      <c r="D43" s="46" t="n"/>
+      <c r="C43" s="53" t="n"/>
+      <c r="D43" s="53" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G43" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G43" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H43" s="49" t="n"/>
       <c r="I43" s="49" t="n"/>
       <c r="J43" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K43" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="51" t="n"/>
-      <c r="N43" s="51" t="n"/>
-      <c r="O43" s="51" t="n"/>
-      <c r="P43" s="51" t="n"/>
-      <c r="Q43" s="51" t="n"/>
-      <c r="R43" s="51" t="n"/>
-      <c r="S43" s="51" t="n"/>
-      <c r="T43" s="51" t="n"/>
-      <c r="U43" s="51" t="n"/>
-      <c r="V43" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W43" s="58" t="n"/>
+      <c r="M43" s="55" t="n"/>
+      <c r="N43" s="55" t="n"/>
+      <c r="O43" s="55" t="n"/>
+      <c r="P43" s="55" t="n"/>
+      <c r="Q43" s="55" t="n"/>
+      <c r="R43" s="55" t="n"/>
+      <c r="S43" s="55" t="n"/>
+      <c r="T43" s="55" t="n"/>
+      <c r="U43" s="55" t="n"/>
+      <c r="V43" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W43" s="57" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="53" t="n"/>
-      <c r="D44" s="53" t="n"/>
+      <c r="C44" s="46" t="n"/>
+      <c r="D44" s="46" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G44" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G44" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H44" s="49" t="n"/>
       <c r="I44" s="49" t="n"/>
       <c r="J44" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K44" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="55" t="n"/>
-      <c r="N44" s="55" t="n"/>
-      <c r="O44" s="55" t="n"/>
-      <c r="P44" s="55" t="n"/>
-      <c r="Q44" s="55" t="n"/>
-      <c r="R44" s="55" t="n"/>
-      <c r="S44" s="55" t="n"/>
-      <c r="T44" s="55" t="n"/>
-      <c r="U44" s="55" t="n"/>
-      <c r="V44" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W44" s="57" t="n"/>
+      <c r="M44" s="51" t="n"/>
+      <c r="N44" s="51" t="n"/>
+      <c r="O44" s="51" t="n"/>
+      <c r="P44" s="51" t="n"/>
+      <c r="Q44" s="51" t="n"/>
+      <c r="R44" s="51" t="n"/>
+      <c r="S44" s="51" t="n"/>
+      <c r="T44" s="51" t="n"/>
+      <c r="U44" s="51" t="n"/>
+      <c r="V44" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W44" s="58" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="46" t="n"/>
-      <c r="D45" s="46" t="n"/>
+      <c r="C45" s="53" t="n"/>
+      <c r="D45" s="53" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G45" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H45" s="49" t="n"/>
       <c r="I45" s="49" t="n"/>
       <c r="J45" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K45" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="51" t="n"/>
-      <c r="N45" s="51" t="n"/>
-      <c r="O45" s="51" t="n"/>
-      <c r="P45" s="51" t="n"/>
-      <c r="Q45" s="51" t="n"/>
-      <c r="R45" s="51" t="n"/>
-      <c r="S45" s="51" t="n"/>
-      <c r="T45" s="51" t="n"/>
-      <c r="U45" s="51" t="n"/>
-      <c r="V45" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W45" s="58" t="n"/>
+      <c r="M45" s="55" t="n"/>
+      <c r="N45" s="55" t="n"/>
+      <c r="O45" s="55" t="n"/>
+      <c r="P45" s="55" t="n"/>
+      <c r="Q45" s="55" t="n"/>
+      <c r="R45" s="55" t="n"/>
+      <c r="S45" s="55" t="n"/>
+      <c r="T45" s="55" t="n"/>
+      <c r="U45" s="55" t="n"/>
+      <c r="V45" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W45" s="57" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="53" t="n"/>
-      <c r="D46" s="53" t="n"/>
+      <c r="C46" s="46" t="n"/>
+      <c r="D46" s="46" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G46" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G46" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H46" s="49" t="n"/>
       <c r="I46" s="49" t="n"/>
       <c r="J46" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K46" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="55" t="n"/>
-      <c r="N46" s="55" t="n"/>
-      <c r="O46" s="55" t="n"/>
-      <c r="P46" s="55" t="n"/>
-      <c r="Q46" s="55" t="n"/>
-      <c r="R46" s="55" t="n"/>
-      <c r="S46" s="55" t="n"/>
-      <c r="T46" s="55" t="n"/>
-      <c r="U46" s="55" t="n"/>
-      <c r="V46" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W46" s="57" t="n"/>
+      <c r="M46" s="51" t="n"/>
+      <c r="N46" s="51" t="n"/>
+      <c r="O46" s="51" t="n"/>
+      <c r="P46" s="51" t="n"/>
+      <c r="Q46" s="51" t="n"/>
+      <c r="R46" s="51" t="n"/>
+      <c r="S46" s="51" t="n"/>
+      <c r="T46" s="51" t="n"/>
+      <c r="U46" s="51" t="n"/>
+      <c r="V46" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W46" s="58" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="46" t="n"/>
-      <c r="D47" s="46" t="n"/>
+      <c r="C47" s="53" t="n"/>
+      <c r="D47" s="53" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G47" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G47" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H47" s="49" t="n"/>
       <c r="I47" s="49" t="n"/>
       <c r="J47" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K47" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="51" t="n"/>
-      <c r="N47" s="51" t="n"/>
-      <c r="O47" s="51" t="n"/>
-      <c r="P47" s="51" t="n"/>
-      <c r="Q47" s="51" t="n"/>
-      <c r="R47" s="51" t="n"/>
-      <c r="S47" s="51" t="n"/>
-      <c r="T47" s="51" t="n"/>
-      <c r="U47" s="51" t="n"/>
-      <c r="V47" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W47" s="58" t="n"/>
+      <c r="M47" s="55" t="n"/>
+      <c r="N47" s="55" t="n"/>
+      <c r="O47" s="55" t="n"/>
+      <c r="P47" s="55" t="n"/>
+      <c r="Q47" s="55" t="n"/>
+      <c r="R47" s="55" t="n"/>
+      <c r="S47" s="55" t="n"/>
+      <c r="T47" s="55" t="n"/>
+      <c r="U47" s="55" t="n"/>
+      <c r="V47" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W47" s="57" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
+      <c r="C48" s="46" t="n"/>
+      <c r="D48" s="46" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G48" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G48" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H48" s="49" t="n"/>
       <c r="I48" s="49" t="n"/>
       <c r="J48" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K48" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="55" t="n"/>
-      <c r="N48" s="55" t="n"/>
-      <c r="O48" s="55" t="n"/>
-      <c r="P48" s="55" t="n"/>
-      <c r="Q48" s="55" t="n"/>
-      <c r="R48" s="55" t="n"/>
-      <c r="S48" s="55" t="n"/>
-      <c r="T48" s="55" t="n"/>
-      <c r="U48" s="55" t="n"/>
-      <c r="V48" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W48" s="57" t="n"/>
+      <c r="M48" s="51" t="n"/>
+      <c r="N48" s="51" t="n"/>
+      <c r="O48" s="51" t="n"/>
+      <c r="P48" s="51" t="n"/>
+      <c r="Q48" s="51" t="n"/>
+      <c r="R48" s="51" t="n"/>
+      <c r="S48" s="51" t="n"/>
+      <c r="T48" s="51" t="n"/>
+      <c r="U48" s="51" t="n"/>
+      <c r="V48" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W48" s="58" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="46" t="n"/>
-      <c r="D49" s="46" t="n"/>
+      <c r="C49" s="53" t="n"/>
+      <c r="D49" s="53" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G49" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H49" s="49" t="n"/>
       <c r="I49" s="49" t="n"/>
       <c r="J49" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K49" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="51" t="n"/>
-      <c r="N49" s="51" t="n"/>
-      <c r="O49" s="51" t="n"/>
-      <c r="P49" s="51" t="n"/>
-      <c r="Q49" s="51" t="n"/>
-      <c r="R49" s="51" t="n"/>
-      <c r="S49" s="51" t="n"/>
-      <c r="T49" s="51" t="n"/>
-      <c r="U49" s="51" t="n"/>
-      <c r="V49" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W49" s="58" t="n"/>
+      <c r="M49" s="55" t="n"/>
+      <c r="N49" s="55" t="n"/>
+      <c r="O49" s="55" t="n"/>
+      <c r="P49" s="55" t="n"/>
+      <c r="Q49" s="55" t="n"/>
+      <c r="R49" s="55" t="n"/>
+      <c r="S49" s="55" t="n"/>
+      <c r="T49" s="55" t="n"/>
+      <c r="U49" s="55" t="n"/>
+      <c r="V49" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W49" s="57" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="53" t="n"/>
-      <c r="D50" s="53" t="n"/>
+      <c r="C50" s="46" t="n"/>
+      <c r="D50" s="46" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G50" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="49" t="n"/>
       <c r="J50" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="55" t="n"/>
-      <c r="N50" s="55" t="n"/>
-      <c r="O50" s="55" t="n"/>
-      <c r="P50" s="55" t="n"/>
-      <c r="Q50" s="55" t="n"/>
-      <c r="R50" s="55" t="n"/>
-      <c r="S50" s="55" t="n"/>
-      <c r="T50" s="55" t="n"/>
-      <c r="U50" s="55" t="n"/>
-      <c r="V50" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W50" s="57" t="n"/>
+      <c r="M50" s="51" t="n"/>
+      <c r="N50" s="51" t="n"/>
+      <c r="O50" s="51" t="n"/>
+      <c r="P50" s="51" t="n"/>
+      <c r="Q50" s="51" t="n"/>
+      <c r="R50" s="51" t="n"/>
+      <c r="S50" s="51" t="n"/>
+      <c r="T50" s="51" t="n"/>
+      <c r="U50" s="51" t="n"/>
+      <c r="V50" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W50" s="58" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="46" t="n"/>
-      <c r="D51" s="46" t="n"/>
+      <c r="C51" s="53" t="n"/>
+      <c r="D51" s="53" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G51" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G51" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H51" s="49" t="n"/>
       <c r="I51" s="49" t="n"/>
       <c r="J51" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="51" t="n"/>
-      <c r="N51" s="51" t="n"/>
-      <c r="O51" s="51" t="n"/>
-      <c r="P51" s="51" t="n"/>
-      <c r="Q51" s="51" t="n"/>
-      <c r="R51" s="51" t="n"/>
-      <c r="S51" s="51" t="n"/>
-      <c r="T51" s="51" t="n"/>
-      <c r="U51" s="51" t="n"/>
-      <c r="V51" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W51" s="58" t="n"/>
+      <c r="M51" s="55" t="n"/>
+      <c r="N51" s="55" t="n"/>
+      <c r="O51" s="55" t="n"/>
+      <c r="P51" s="55" t="n"/>
+      <c r="Q51" s="55" t="n"/>
+      <c r="R51" s="55" t="n"/>
+      <c r="S51" s="55" t="n"/>
+      <c r="T51" s="55" t="n"/>
+      <c r="U51" s="55" t="n"/>
+      <c r="V51" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W51" s="57" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="53" t="n"/>
-      <c r="D52" s="53" t="n"/>
+      <c r="C52" s="46" t="n"/>
+      <c r="D52" s="46" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G52" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G52" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H52" s="49" t="n"/>
       <c r="I52" s="49" t="n"/>
       <c r="J52" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="55" t="n"/>
-      <c r="N52" s="55" t="n"/>
-      <c r="O52" s="55" t="n"/>
-      <c r="P52" s="55" t="n"/>
-      <c r="Q52" s="55" t="n"/>
-      <c r="R52" s="55" t="n"/>
-      <c r="S52" s="55" t="n"/>
-      <c r="T52" s="55" t="n"/>
-      <c r="U52" s="55" t="n"/>
-      <c r="V52" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W52" s="57" t="n"/>
+      <c r="M52" s="51" t="n"/>
+      <c r="N52" s="51" t="n"/>
+      <c r="O52" s="51" t="n"/>
+      <c r="P52" s="51" t="n"/>
+      <c r="Q52" s="51" t="n"/>
+      <c r="R52" s="51" t="n"/>
+      <c r="S52" s="51" t="n"/>
+      <c r="T52" s="51" t="n"/>
+      <c r="U52" s="51" t="n"/>
+      <c r="V52" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W52" s="58" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="46" t="n"/>
-      <c r="D53" s="46" t="n"/>
+      <c r="C53" s="53" t="n"/>
+      <c r="D53" s="53" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G53" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G53" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H53" s="49" t="n"/>
       <c r="I53" s="49" t="n"/>
       <c r="J53" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="51" t="n"/>
-      <c r="N53" s="51" t="n"/>
-      <c r="O53" s="51" t="n"/>
-      <c r="P53" s="51" t="n"/>
-      <c r="Q53" s="51" t="n"/>
-      <c r="R53" s="51" t="n"/>
-      <c r="S53" s="51" t="n"/>
-      <c r="T53" s="51" t="n"/>
-      <c r="U53" s="51" t="n"/>
-      <c r="V53" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W53" s="58" t="n"/>
+      <c r="M53" s="55" t="n"/>
+      <c r="N53" s="55" t="n"/>
+      <c r="O53" s="55" t="n"/>
+      <c r="P53" s="55" t="n"/>
+      <c r="Q53" s="55" t="n"/>
+      <c r="R53" s="55" t="n"/>
+      <c r="S53" s="55" t="n"/>
+      <c r="T53" s="55" t="n"/>
+      <c r="U53" s="55" t="n"/>
+      <c r="V53" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W53" s="57" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="53" t="n"/>
-      <c r="D54" s="53" t="n"/>
+      <c r="C54" s="46" t="n"/>
+      <c r="D54" s="46" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G54" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G54" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="55" t="n"/>
-      <c r="N54" s="55" t="n"/>
-      <c r="O54" s="55" t="n"/>
-      <c r="P54" s="55" t="n"/>
-      <c r="Q54" s="55" t="n"/>
-      <c r="R54" s="55" t="n"/>
-      <c r="S54" s="55" t="n"/>
-      <c r="T54" s="55" t="n"/>
-      <c r="U54" s="55" t="n"/>
-      <c r="V54" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W54" s="57" t="n"/>
+      <c r="M54" s="51" t="n"/>
+      <c r="N54" s="51" t="n"/>
+      <c r="O54" s="51" t="n"/>
+      <c r="P54" s="51" t="n"/>
+      <c r="Q54" s="51" t="n"/>
+      <c r="R54" s="51" t="n"/>
+      <c r="S54" s="51" t="n"/>
+      <c r="T54" s="51" t="n"/>
+      <c r="U54" s="51" t="n"/>
+      <c r="V54" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W54" s="58" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="46" t="n"/>
-      <c r="D55" s="46" t="n"/>
+      <c r="C55" s="53" t="n"/>
+      <c r="D55" s="53" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G55" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G55" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="51" t="n"/>
-      <c r="N55" s="51" t="n"/>
-      <c r="O55" s="51" t="n"/>
-      <c r="P55" s="51" t="n"/>
-      <c r="Q55" s="51" t="n"/>
-      <c r="R55" s="51" t="n"/>
-      <c r="S55" s="51" t="n"/>
-      <c r="T55" s="51" t="n"/>
-      <c r="U55" s="51" t="n"/>
-      <c r="V55" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W55" s="58" t="n"/>
+      <c r="M55" s="55" t="n"/>
+      <c r="N55" s="55" t="n"/>
+      <c r="O55" s="55" t="n"/>
+      <c r="P55" s="55" t="n"/>
+      <c r="Q55" s="55" t="n"/>
+      <c r="R55" s="55" t="n"/>
+      <c r="S55" s="55" t="n"/>
+      <c r="T55" s="55" t="n"/>
+      <c r="U55" s="55" t="n"/>
+      <c r="V55" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W55" s="57" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="53" t="n"/>
-      <c r="D56" s="53" t="n"/>
+      <c r="C56" s="46" t="n"/>
+      <c r="D56" s="46" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G56" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G56" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="55" t="n"/>
-      <c r="N56" s="55" t="n"/>
-      <c r="O56" s="55" t="n"/>
-      <c r="P56" s="55" t="n"/>
-      <c r="Q56" s="55" t="n"/>
-      <c r="R56" s="55" t="n"/>
-      <c r="S56" s="55" t="n"/>
-      <c r="T56" s="55" t="n"/>
-      <c r="U56" s="55" t="n"/>
-      <c r="V56" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W56" s="57" t="n"/>
+      <c r="M56" s="51" t="n"/>
+      <c r="N56" s="51" t="n"/>
+      <c r="O56" s="51" t="n"/>
+      <c r="P56" s="51" t="n"/>
+      <c r="Q56" s="51" t="n"/>
+      <c r="R56" s="51" t="n"/>
+      <c r="S56" s="51" t="n"/>
+      <c r="T56" s="51" t="n"/>
+      <c r="U56" s="51" t="n"/>
+      <c r="V56" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W56" s="58" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="46" t="n"/>
-      <c r="D57" s="46" t="n"/>
+      <c r="C57" s="53" t="n"/>
+      <c r="D57" s="53" t="n"/>
       <c r="E57" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F57" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G57" s="48" t="n">
-        <v>24</v>
+      <c r="G57" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="51" t="n"/>
-      <c r="N57" s="51" t="n"/>
-      <c r="O57" s="51" t="n"/>
-      <c r="P57" s="51" t="n"/>
-      <c r="Q57" s="51" t="n"/>
-      <c r="R57" s="51" t="n"/>
-      <c r="S57" s="51" t="n"/>
-      <c r="T57" s="51" t="n"/>
-      <c r="U57" s="51" t="n"/>
-      <c r="V57" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W57" s="58" t="n"/>
+      <c r="M57" s="55" t="n"/>
+      <c r="N57" s="55" t="n"/>
+      <c r="O57" s="55" t="n"/>
+      <c r="P57" s="55" t="n"/>
+      <c r="Q57" s="55" t="n"/>
+      <c r="R57" s="55" t="n"/>
+      <c r="S57" s="55" t="n"/>
+      <c r="T57" s="55" t="n"/>
+      <c r="U57" s="55" t="n"/>
+      <c r="V57" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W57" s="57" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="53" t="n"/>
-      <c r="D58" s="53" t="n"/>
+      <c r="C58" s="46" t="n"/>
+      <c r="D58" s="46" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G58" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G58" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="55" t="n"/>
-      <c r="N58" s="55" t="n"/>
-      <c r="O58" s="55" t="n"/>
-      <c r="P58" s="55" t="n"/>
-      <c r="Q58" s="55" t="n"/>
-      <c r="R58" s="55" t="n"/>
-      <c r="S58" s="55" t="n"/>
-      <c r="T58" s="55" t="n"/>
-      <c r="U58" s="55" t="n"/>
-      <c r="V58" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W58" s="57" t="n"/>
+      <c r="M58" s="51" t="n"/>
+      <c r="N58" s="51" t="n"/>
+      <c r="O58" s="51" t="n"/>
+      <c r="P58" s="51" t="n"/>
+      <c r="Q58" s="51" t="n"/>
+      <c r="R58" s="51" t="n"/>
+      <c r="S58" s="51" t="n"/>
+      <c r="T58" s="51" t="n"/>
+      <c r="U58" s="51" t="n"/>
+      <c r="V58" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W58" s="58" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="46" t="n"/>
-      <c r="D59" s="46" t="n"/>
+      <c r="C59" s="53" t="n"/>
+      <c r="D59" s="53" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G59" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G59" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="51" t="n"/>
-      <c r="N59" s="51" t="n"/>
-      <c r="O59" s="51" t="n"/>
-      <c r="P59" s="51" t="n"/>
-      <c r="Q59" s="51" t="n"/>
-      <c r="R59" s="51" t="n"/>
-      <c r="S59" s="51" t="n"/>
-      <c r="T59" s="51" t="n"/>
-      <c r="U59" s="51" t="n"/>
-      <c r="V59" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W59" s="58" t="n"/>
+      <c r="M59" s="55" t="n"/>
+      <c r="N59" s="55" t="n"/>
+      <c r="O59" s="55" t="n"/>
+      <c r="P59" s="55" t="n"/>
+      <c r="Q59" s="55" t="n"/>
+      <c r="R59" s="55" t="n"/>
+      <c r="S59" s="55" t="n"/>
+      <c r="T59" s="55" t="n"/>
+      <c r="U59" s="55" t="n"/>
+      <c r="V59" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W59" s="57" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
+      <c r="C60" s="46" t="n"/>
+      <c r="D60" s="46" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G60" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
@@ -4580,51 +4608,92 @@
         <v>59</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="55" t="n"/>
-      <c r="N60" s="55" t="n"/>
-      <c r="O60" s="55" t="n"/>
-      <c r="P60" s="55" t="n"/>
-      <c r="Q60" s="55" t="n"/>
-      <c r="R60" s="55" t="n"/>
-      <c r="S60" s="55" t="n"/>
-      <c r="T60" s="55" t="n"/>
-      <c r="U60" s="55" t="n"/>
-      <c r="V60" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W60" s="57" t="n"/>
+      <c r="M60" s="51" t="n"/>
+      <c r="N60" s="51" t="n"/>
+      <c r="O60" s="51" t="n"/>
+      <c r="P60" s="51" t="n"/>
+      <c r="Q60" s="51" t="n"/>
+      <c r="R60" s="51" t="n"/>
+      <c r="S60" s="51" t="n"/>
+      <c r="T60" s="51" t="n"/>
+      <c r="U60" s="51" t="n"/>
+      <c r="V60" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W60" s="58" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="46" t="n"/>
-      <c r="D61" s="46" t="n"/>
-      <c r="E61" s="47" t="n"/>
-      <c r="F61" s="47" t="n"/>
-      <c r="G61" s="60" t="n"/>
+      <c r="C61" s="53" t="n"/>
+      <c r="D61" s="53" t="n"/>
+      <c r="E61" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F61" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G61" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
-      <c r="J61" s="50" t="n"/>
-      <c r="K61" s="50" t="n"/>
+      <c r="J61" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K61" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="51" t="n"/>
-      <c r="N61" s="51" t="n"/>
-      <c r="O61" s="51" t="n"/>
-      <c r="P61" s="51" t="n"/>
-      <c r="Q61" s="51" t="n"/>
-      <c r="R61" s="51" t="n"/>
-      <c r="S61" s="51" t="n"/>
-      <c r="T61" s="51" t="n"/>
-      <c r="U61" s="51" t="n"/>
-      <c r="V61" s="61" t="n"/>
-      <c r="W61" s="61" t="n"/>
+      <c r="M61" s="55" t="n"/>
+      <c r="N61" s="55" t="n"/>
+      <c r="O61" s="55" t="n"/>
+      <c r="P61" s="55" t="n"/>
+      <c r="Q61" s="55" t="n"/>
+      <c r="R61" s="55" t="n"/>
+      <c r="S61" s="55" t="n"/>
+      <c r="T61" s="55" t="n"/>
+      <c r="U61" s="55" t="n"/>
+      <c r="V61" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W61" s="57" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B62" s="45" t="n"/>
+      <c r="C62" s="46" t="n"/>
+      <c r="D62" s="46" t="n"/>
+      <c r="E62" s="47" t="n"/>
+      <c r="F62" s="47" t="n"/>
+      <c r="G62" s="60" t="n"/>
+      <c r="H62" s="49" t="n"/>
+      <c r="I62" s="49" t="n"/>
+      <c r="J62" s="50" t="n"/>
+      <c r="K62" s="50" t="n"/>
+      <c r="L62" s="50" t="n"/>
+      <c r="M62" s="51" t="n"/>
+      <c r="N62" s="51" t="n"/>
+      <c r="O62" s="51" t="n"/>
+      <c r="P62" s="51" t="n"/>
+      <c r="Q62" s="51" t="n"/>
+      <c r="R62" s="51" t="n"/>
+      <c r="S62" s="51" t="n"/>
+      <c r="T62" s="51" t="n"/>
+      <c r="U62" s="51" t="n"/>
+      <c r="V62" s="61" t="n"/>
+      <c r="W62" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W62"/>
+  <dimension ref="A1:W63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,98 +1982,98 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G4" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H4" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I4" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J4" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K4" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L4" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M4" s="69" t="inlineStr"/>
       <c r="N4" s="69" t="inlineStr"/>
-      <c r="O4" s="69" t="inlineStr">
+      <c r="O4" s="69" t="inlineStr"/>
+      <c r="P4" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P4" s="69" t="inlineStr"/>
       <c r="Q4" s="69" t="inlineStr"/>
       <c r="R4" s="69" t="inlineStr"/>
       <c r="S4" s="69" t="inlineStr"/>
       <c r="T4" s="69" t="inlineStr"/>
       <c r="U4" s="69" t="inlineStr"/>
       <c r="V4" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W4" s="69" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
       <c r="C5" s="64" t="inlineStr"/>
       <c r="D5" s="64" t="inlineStr"/>
       <c r="E5" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G5" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G5" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H5" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I5" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K5" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L5" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" s="69" t="inlineStr"/>
-      <c r="N5" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M5" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N5" s="69" t="inlineStr"/>
+      <c r="O5" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O5" s="69" t="inlineStr"/>
       <c r="P5" s="69" t="inlineStr"/>
       <c r="Q5" s="69" t="inlineStr"/>
       <c r="R5" s="69" t="inlineStr"/>
@@ -2081,51 +2081,47 @@
       <c r="T5" s="69" t="inlineStr"/>
       <c r="U5" s="69" t="inlineStr"/>
       <c r="V5" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W5" s="69" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
       <c r="C6" s="64" t="inlineStr"/>
       <c r="D6" s="64" t="inlineStr"/>
       <c r="E6" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G6" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G6" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H6" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I6" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J6" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K6" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L6" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M6" s="69" t="inlineStr"/>
+      <c r="N6" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N6" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O6" s="69" t="inlineStr"/>
@@ -2136,254 +2132,250 @@
       <c r="T6" s="69" t="inlineStr"/>
       <c r="U6" s="69" t="inlineStr"/>
       <c r="V6" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W6" s="69" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B7" s="63" t="inlineStr"/>
+      <c r="C7" s="64" t="inlineStr"/>
+      <c r="D7" s="64" t="inlineStr"/>
+      <c r="E7" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F7" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G7" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H7" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L7" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N7" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O7" s="69" t="inlineStr"/>
+      <c r="P7" s="69" t="inlineStr"/>
+      <c r="Q7" s="69" t="inlineStr"/>
+      <c r="R7" s="69" t="inlineStr"/>
+      <c r="S7" s="69" t="inlineStr"/>
+      <c r="T7" s="69" t="inlineStr"/>
+      <c r="U7" s="69" t="inlineStr"/>
+      <c r="V7" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="69" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="W7" s="69" t="inlineStr"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D7" s="38" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E7" s="39" t="n">
+      <c r="E8" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F8" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G7" s="40" t="n">
+      <c r="G8" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H7" s="41" t="n">
+      <c r="H8" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I7" s="41" t="n">
+      <c r="I8" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J7" s="42" t="n">
+      <c r="J8" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K7" s="42" t="n">
+      <c r="K8" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L7" s="42" t="n">
+      <c r="L8" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M7" s="43" t="inlineStr">
+      <c r="M8" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N7" s="43" t="inlineStr"/>
-      <c r="O7" s="43" t="inlineStr">
+      <c r="N8" s="43" t="inlineStr"/>
+      <c r="O8" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P7" s="43" t="inlineStr"/>
-      <c r="Q7" s="43" t="inlineStr"/>
-      <c r="R7" s="43" t="inlineStr"/>
-      <c r="S7" s="43" t="inlineStr"/>
-      <c r="T7" s="43" t="inlineStr"/>
-      <c r="U7" s="43" t="inlineStr"/>
-      <c r="V7" s="43" t="n">
+      <c r="P8" s="43" t="inlineStr"/>
+      <c r="Q8" s="43" t="inlineStr"/>
+      <c r="R8" s="43" t="inlineStr"/>
+      <c r="S8" s="43" t="inlineStr"/>
+      <c r="T8" s="43" t="inlineStr"/>
+      <c r="U8" s="43" t="inlineStr"/>
+      <c r="V8" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W7" s="43" t="inlineStr"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B8" s="45" t="n"/>
-      <c r="C8" s="46" t="n"/>
-      <c r="D8" s="46" t="n"/>
-      <c r="E8" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F8" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G8" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H8" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L8" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M8" s="51" t="n"/>
-      <c r="N8" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O8" s="51" t="n"/>
-      <c r="P8" s="51" t="n"/>
-      <c r="Q8" s="51" t="n"/>
-      <c r="R8" s="51" t="n"/>
-      <c r="S8" s="51" t="n"/>
-      <c r="T8" s="51" t="n"/>
-      <c r="U8" s="51" t="n"/>
-      <c r="V8" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W8" s="43" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B9" s="45" t="n"/>
-      <c r="C9" s="53" t="n"/>
-      <c r="D9" s="53" t="n"/>
+      <c r="C9" s="46" t="n"/>
+      <c r="D9" s="46" t="n"/>
       <c r="E9" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F9" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G9" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H9" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I9" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J9" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K9" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L9" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M9" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N9" s="55" t="n"/>
-      <c r="O9" s="55" t="n"/>
-      <c r="P9" s="55" t="n"/>
-      <c r="Q9" s="55" t="n"/>
-      <c r="R9" s="55" t="n"/>
-      <c r="S9" s="55" t="n"/>
-      <c r="T9" s="55" t="n"/>
-      <c r="U9" s="55" t="n"/>
-      <c r="V9" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W9" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M9" s="51" t="n"/>
+      <c r="N9" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O9" s="51" t="n"/>
+      <c r="P9" s="51" t="n"/>
+      <c r="Q9" s="51" t="n"/>
+      <c r="R9" s="51" t="n"/>
+      <c r="S9" s="51" t="n"/>
+      <c r="T9" s="51" t="n"/>
+      <c r="U9" s="51" t="n"/>
+      <c r="V9" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B10" s="45" t="n"/>
-      <c r="C10" s="46" t="n"/>
-      <c r="D10" s="46" t="n"/>
+      <c r="C10" s="53" t="n"/>
+      <c r="D10" s="53" t="n"/>
       <c r="E10" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F10" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G10" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G10" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H10" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I10" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J10" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K10" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L10" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M10" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N10" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O10" s="51" t="n"/>
-      <c r="P10" s="51" t="n"/>
-      <c r="Q10" s="51" t="n"/>
-      <c r="R10" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S10" s="51" t="n"/>
-      <c r="T10" s="51" t="n"/>
-      <c r="U10" s="51" t="n"/>
-      <c r="V10" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W10" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M10" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N10" s="55" t="n"/>
+      <c r="O10" s="55" t="n"/>
+      <c r="P10" s="55" t="n"/>
+      <c r="Q10" s="55" t="n"/>
+      <c r="R10" s="55" t="n"/>
+      <c r="S10" s="55" t="n"/>
+      <c r="T10" s="55" t="n"/>
+      <c r="U10" s="55" t="n"/>
+      <c r="V10" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W10" s="57" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B11" s="45" t="n"/>
-      <c r="C11" s="53" t="n"/>
-      <c r="D11" s="53" t="n"/>
+      <c r="C11" s="46" t="n"/>
+      <c r="D11" s="46" t="n"/>
       <c r="E11" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F11" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G11" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H11" s="49" t="n">
         <v>1</v>
@@ -2392,493 +2384,497 @@
         <v>1</v>
       </c>
       <c r="J11" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K11" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L11" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M11" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N11" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N11" s="55" t="n"/>
-      <c r="O11" s="55" t="n"/>
-      <c r="P11" s="55" t="n"/>
-      <c r="Q11" s="55" t="inlineStr">
+      <c r="O11" s="51" t="n"/>
+      <c r="P11" s="51" t="n"/>
+      <c r="Q11" s="51" t="n"/>
+      <c r="R11" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R11" s="55" t="n"/>
-      <c r="S11" s="55" t="n"/>
-      <c r="T11" s="55" t="n"/>
-      <c r="U11" s="55" t="n"/>
-      <c r="V11" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W11" s="57" t="n"/>
+      <c r="S11" s="51" t="n"/>
+      <c r="T11" s="51" t="n"/>
+      <c r="U11" s="51" t="n"/>
+      <c r="V11" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W11" s="58" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B12" s="45" t="n"/>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
+      <c r="C12" s="53" t="n"/>
+      <c r="D12" s="53" t="n"/>
       <c r="E12" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F12" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G12" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G12" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H12" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I12" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J12" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K12" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L12" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N12" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O12" s="51" t="n"/>
-      <c r="P12" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M12" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N12" s="55" t="n"/>
+      <c r="O12" s="55" t="n"/>
+      <c r="P12" s="55" t="n"/>
+      <c r="Q12" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q12" s="51" t="n"/>
-      <c r="R12" s="51" t="n"/>
-      <c r="S12" s="51" t="n"/>
-      <c r="T12" s="51" t="n"/>
-      <c r="U12" s="51" t="n"/>
-      <c r="V12" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W12" s="58" t="n"/>
+      <c r="R12" s="55" t="n"/>
+      <c r="S12" s="55" t="n"/>
+      <c r="T12" s="55" t="n"/>
+      <c r="U12" s="55" t="n"/>
+      <c r="V12" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W12" s="57" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B13" s="45" t="n"/>
-      <c r="C13" s="53" t="n"/>
-      <c r="D13" s="53" t="n"/>
+      <c r="C13" s="46" t="n"/>
+      <c r="D13" s="46" t="n"/>
       <c r="E13" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F13" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G13" s="59" t="n">
-        <v>45.1</v>
+      <c r="G13" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H13" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I13" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J13" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K13" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L13" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N13" s="55" t="n"/>
-      <c r="O13" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P13" s="55" t="n"/>
-      <c r="Q13" s="55" t="n"/>
-      <c r="R13" s="55" t="n"/>
-      <c r="S13" s="55" t="n"/>
-      <c r="T13" s="55" t="n"/>
-      <c r="U13" s="55" t="n"/>
-      <c r="V13" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W13" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M13" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N13" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O13" s="51" t="n"/>
+      <c r="P13" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q13" s="51" t="n"/>
+      <c r="R13" s="51" t="n"/>
+      <c r="S13" s="51" t="n"/>
+      <c r="T13" s="51" t="n"/>
+      <c r="U13" s="51" t="n"/>
+      <c r="V13" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W13" s="58" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B14" s="45" t="n"/>
-      <c r="C14" s="46" t="n"/>
-      <c r="D14" s="46" t="n"/>
+      <c r="C14" s="53" t="n"/>
+      <c r="D14" s="53" t="n"/>
       <c r="E14" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F14" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G14" s="54" t="n">
-        <v>26.3</v>
+      <c r="G14" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H14" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I14" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J14" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K14" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L14" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M14" s="51" t="n"/>
-      <c r="N14" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M14" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N14" s="55" t="n"/>
+      <c r="O14" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O14" s="51" t="n"/>
-      <c r="P14" s="51" t="n"/>
-      <c r="Q14" s="51" t="n"/>
-      <c r="R14" s="51" t="n"/>
-      <c r="S14" s="51" t="n"/>
-      <c r="T14" s="51" t="n"/>
-      <c r="U14" s="51" t="n"/>
-      <c r="V14" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W14" s="58" t="n"/>
+      <c r="P14" s="55" t="n"/>
+      <c r="Q14" s="55" t="n"/>
+      <c r="R14" s="55" t="n"/>
+      <c r="S14" s="55" t="n"/>
+      <c r="T14" s="55" t="n"/>
+      <c r="U14" s="55" t="n"/>
+      <c r="V14" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W14" s="57" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B15" s="45" t="n"/>
-      <c r="C15" s="53" t="n"/>
-      <c r="D15" s="53" t="n"/>
+      <c r="C15" s="46" t="n"/>
+      <c r="D15" s="46" t="n"/>
       <c r="E15" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F15" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G15" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H15" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K15" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L15" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M15" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M15" s="51" t="n"/>
+      <c r="N15" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N15" s="55" t="n"/>
-      <c r="O15" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P15" s="55" t="n"/>
-      <c r="Q15" s="55" t="n"/>
-      <c r="R15" s="55" t="n"/>
-      <c r="S15" s="55" t="n"/>
-      <c r="T15" s="55" t="n"/>
-      <c r="U15" s="55" t="n"/>
-      <c r="V15" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W15" s="57" t="n"/>
+      <c r="O15" s="51" t="n"/>
+      <c r="P15" s="51" t="n"/>
+      <c r="Q15" s="51" t="n"/>
+      <c r="R15" s="51" t="n"/>
+      <c r="S15" s="51" t="n"/>
+      <c r="T15" s="51" t="n"/>
+      <c r="U15" s="51" t="n"/>
+      <c r="V15" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W15" s="58" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B16" s="45" t="n"/>
-      <c r="C16" s="46" t="n"/>
-      <c r="D16" s="46" t="n"/>
+      <c r="C16" s="53" t="n"/>
+      <c r="D16" s="53" t="n"/>
       <c r="E16" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F16" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G16" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H16" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I16" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J16" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K16" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L16" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M16" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N16" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O16" s="51" t="n"/>
-      <c r="P16" s="51" t="n"/>
-      <c r="Q16" s="51" t="n"/>
-      <c r="R16" s="51" t="n"/>
-      <c r="S16" s="51" t="n"/>
-      <c r="T16" s="51" t="n"/>
-      <c r="U16" s="51" t="n"/>
-      <c r="V16" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W16" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M16" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N16" s="55" t="n"/>
+      <c r="O16" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P16" s="55" t="n"/>
+      <c r="Q16" s="55" t="n"/>
+      <c r="R16" s="55" t="n"/>
+      <c r="S16" s="55" t="n"/>
+      <c r="T16" s="55" t="n"/>
+      <c r="U16" s="55" t="n"/>
+      <c r="V16" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W16" s="57" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B17" s="45" t="n"/>
-      <c r="C17" s="53" t="n"/>
-      <c r="D17" s="53" t="n"/>
+      <c r="C17" s="46" t="n"/>
+      <c r="D17" s="46" t="n"/>
       <c r="E17" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F17" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G17" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H17" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K17" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L17" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I17" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J17" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K17" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L17" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" s="55" t="inlineStr">
+      <c r="M17" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N17" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N17" s="55" t="n"/>
-      <c r="O17" s="55" t="n"/>
-      <c r="P17" s="55" t="n"/>
-      <c r="Q17" s="55" t="n"/>
-      <c r="R17" s="55" t="n"/>
-      <c r="S17" s="55" t="n"/>
-      <c r="T17" s="55" t="n"/>
-      <c r="U17" s="55" t="n"/>
-      <c r="V17" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W17" s="57" t="n"/>
+      <c r="O17" s="51" t="n"/>
+      <c r="P17" s="51" t="n"/>
+      <c r="Q17" s="51" t="n"/>
+      <c r="R17" s="51" t="n"/>
+      <c r="S17" s="51" t="n"/>
+      <c r="T17" s="51" t="n"/>
+      <c r="U17" s="51" t="n"/>
+      <c r="V17" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W17" s="58" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B18" s="45" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="53" t="n"/>
       <c r="E18" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F18" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G18" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G18" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H18" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I18" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J18" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K18" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L18" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N18" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O18" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P18" s="51" t="n"/>
-      <c r="Q18" s="51" t="n"/>
-      <c r="R18" s="51" t="n"/>
-      <c r="S18" s="51" t="n"/>
-      <c r="T18" s="51" t="n"/>
-      <c r="U18" s="51" t="n"/>
-      <c r="V18" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W18" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M18" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N18" s="55" t="n"/>
+      <c r="O18" s="55" t="n"/>
+      <c r="P18" s="55" t="n"/>
+      <c r="Q18" s="55" t="n"/>
+      <c r="R18" s="55" t="n"/>
+      <c r="S18" s="55" t="n"/>
+      <c r="T18" s="55" t="n"/>
+      <c r="U18" s="55" t="n"/>
+      <c r="V18" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W18" s="57" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B19" s="45" t="n"/>
-      <c r="C19" s="53" t="n"/>
-      <c r="D19" s="53" t="n"/>
+      <c r="C19" s="46" t="n"/>
+      <c r="D19" s="46" t="n"/>
       <c r="E19" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F19" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G19" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G19" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H19" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J19" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K19" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L19" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M19" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N19" s="55" t="inlineStr">
+      <c r="M19" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N19" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O19" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O19" s="55" t="n"/>
-      <c r="P19" s="55" t="n"/>
-      <c r="Q19" s="55" t="n"/>
-      <c r="R19" s="55" t="n"/>
-      <c r="S19" s="55" t="n"/>
-      <c r="T19" s="55" t="n"/>
-      <c r="U19" s="55" t="n"/>
-      <c r="V19" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W19" s="57" t="n"/>
+      <c r="P19" s="51" t="n"/>
+      <c r="Q19" s="51" t="n"/>
+      <c r="R19" s="51" t="n"/>
+      <c r="S19" s="51" t="n"/>
+      <c r="T19" s="51" t="n"/>
+      <c r="U19" s="51" t="n"/>
+      <c r="V19" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W19" s="58" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B20" s="45" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="46" t="n"/>
+      <c r="C20" s="53" t="n"/>
+      <c r="D20" s="53" t="n"/>
       <c r="E20" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F20" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G20" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H20" s="49" t="n">
         <v>2</v>
@@ -2887,208 +2883,218 @@
         <v>2</v>
       </c>
       <c r="J20" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K20" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L20" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M20" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M20" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N20" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N20" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O20" s="51" t="n"/>
-      <c r="P20" s="51" t="n"/>
-      <c r="Q20" s="51" t="n"/>
-      <c r="R20" s="51" t="n"/>
-      <c r="S20" s="51" t="n"/>
-      <c r="T20" s="51" t="n"/>
-      <c r="U20" s="51" t="n"/>
-      <c r="V20" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W20" s="58" t="n"/>
+      <c r="O20" s="55" t="n"/>
+      <c r="P20" s="55" t="n"/>
+      <c r="Q20" s="55" t="n"/>
+      <c r="R20" s="55" t="n"/>
+      <c r="S20" s="55" t="n"/>
+      <c r="T20" s="55" t="n"/>
+      <c r="U20" s="55" t="n"/>
+      <c r="V20" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W20" s="57" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="53" t="n"/>
-      <c r="D21" s="53" t="n"/>
+      <c r="C21" s="46" t="n"/>
+      <c r="D21" s="46" t="n"/>
       <c r="E21" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F21" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G21" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H21" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J21" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K21" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L21" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M21" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N21" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N21" s="55" t="n"/>
-      <c r="O21" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P21" s="55" t="n"/>
-      <c r="Q21" s="55" t="n"/>
-      <c r="R21" s="55" t="n"/>
-      <c r="S21" s="55" t="n"/>
-      <c r="T21" s="55" t="n"/>
-      <c r="U21" s="55" t="n"/>
-      <c r="V21" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W21" s="57" t="n"/>
+      <c r="O21" s="51" t="n"/>
+      <c r="P21" s="51" t="n"/>
+      <c r="Q21" s="51" t="n"/>
+      <c r="R21" s="51" t="n"/>
+      <c r="S21" s="51" t="n"/>
+      <c r="T21" s="51" t="n"/>
+      <c r="U21" s="51" t="n"/>
+      <c r="V21" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W21" s="58" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="46" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
       <c r="E22" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G22" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G22" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H22" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K22" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L22" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M22" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N22" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O22" s="51" t="n"/>
-      <c r="P22" s="51" t="n"/>
-      <c r="Q22" s="51" t="n"/>
-      <c r="R22" s="51" t="n"/>
-      <c r="S22" s="51" t="n"/>
-      <c r="T22" s="51" t="n"/>
-      <c r="U22" s="51" t="n"/>
-      <c r="V22" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W22" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M22" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N22" s="55" t="n"/>
+      <c r="O22" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P22" s="55" t="n"/>
+      <c r="Q22" s="55" t="n"/>
+      <c r="R22" s="55" t="n"/>
+      <c r="S22" s="55" t="n"/>
+      <c r="T22" s="55" t="n"/>
+      <c r="U22" s="55" t="n"/>
+      <c r="V22" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W22" s="57" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="53" t="n"/>
-      <c r="D23" s="53" t="n"/>
+      <c r="C23" s="46" t="n"/>
+      <c r="D23" s="46" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G23" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G23" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H23" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L23" s="50" t="n"/>
-      <c r="M23" s="55" t="n"/>
-      <c r="N23" s="55" t="n"/>
-      <c r="O23" s="55" t="n"/>
-      <c r="P23" s="55" t="n"/>
-      <c r="Q23" s="55" t="n"/>
-      <c r="R23" s="55" t="n"/>
-      <c r="S23" s="55" t="n"/>
-      <c r="T23" s="55" t="n"/>
-      <c r="U23" s="55" t="n"/>
-      <c r="V23" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W23" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L23" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M23" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N23" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O23" s="51" t="n"/>
+      <c r="P23" s="51" t="n"/>
+      <c r="Q23" s="51" t="n"/>
+      <c r="R23" s="51" t="n"/>
+      <c r="S23" s="51" t="n"/>
+      <c r="T23" s="51" t="n"/>
+      <c r="U23" s="51" t="n"/>
+      <c r="V23" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W23" s="58" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G24" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H24" s="49" t="n">
         <v>0</v>
@@ -3097,43 +3103,43 @@
         <v>0</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L24" s="50" t="n"/>
-      <c r="M24" s="51" t="n"/>
-      <c r="N24" s="51" t="n"/>
-      <c r="O24" s="51" t="n"/>
-      <c r="P24" s="51" t="n"/>
-      <c r="Q24" s="51" t="n"/>
-      <c r="R24" s="51" t="n"/>
-      <c r="S24" s="51" t="n"/>
-      <c r="T24" s="51" t="n"/>
-      <c r="U24" s="51" t="n"/>
-      <c r="V24" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W24" s="58" t="n"/>
+      <c r="M24" s="55" t="n"/>
+      <c r="N24" s="55" t="n"/>
+      <c r="O24" s="55" t="n"/>
+      <c r="P24" s="55" t="n"/>
+      <c r="Q24" s="55" t="n"/>
+      <c r="R24" s="55" t="n"/>
+      <c r="S24" s="55" t="n"/>
+      <c r="T24" s="55" t="n"/>
+      <c r="U24" s="55" t="n"/>
+      <c r="V24" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W24" s="57" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="53" t="n"/>
-      <c r="D25" s="53" t="n"/>
+      <c r="C25" s="46" t="n"/>
+      <c r="D25" s="46" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G25" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H25" s="49" t="n">
         <v>0</v>
@@ -3142,43 +3148,43 @@
         <v>0</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L25" s="50" t="n"/>
-      <c r="M25" s="55" t="n"/>
-      <c r="N25" s="55" t="n"/>
-      <c r="O25" s="55" t="n"/>
-      <c r="P25" s="55" t="n"/>
-      <c r="Q25" s="55" t="n"/>
-      <c r="R25" s="55" t="n"/>
-      <c r="S25" s="55" t="n"/>
-      <c r="T25" s="55" t="n"/>
-      <c r="U25" s="55" t="n"/>
-      <c r="V25" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W25" s="57" t="n"/>
+      <c r="M25" s="51" t="n"/>
+      <c r="N25" s="51" t="n"/>
+      <c r="O25" s="51" t="n"/>
+      <c r="P25" s="51" t="n"/>
+      <c r="Q25" s="51" t="n"/>
+      <c r="R25" s="51" t="n"/>
+      <c r="S25" s="51" t="n"/>
+      <c r="T25" s="51" t="n"/>
+      <c r="U25" s="51" t="n"/>
+      <c r="V25" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W25" s="58" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="46" t="n"/>
-      <c r="D26" s="46" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G26" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G26" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H26" s="49" t="n">
         <v>0</v>
@@ -3187,43 +3193,43 @@
         <v>0</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L26" s="50" t="n"/>
-      <c r="M26" s="51" t="n"/>
-      <c r="N26" s="51" t="n"/>
-      <c r="O26" s="51" t="n"/>
-      <c r="P26" s="51" t="n"/>
-      <c r="Q26" s="51" t="n"/>
-      <c r="R26" s="51" t="n"/>
-      <c r="S26" s="51" t="n"/>
-      <c r="T26" s="51" t="n"/>
-      <c r="U26" s="51" t="n"/>
-      <c r="V26" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W26" s="58" t="n"/>
+      <c r="M26" s="55" t="n"/>
+      <c r="N26" s="55" t="n"/>
+      <c r="O26" s="55" t="n"/>
+      <c r="P26" s="55" t="n"/>
+      <c r="Q26" s="55" t="n"/>
+      <c r="R26" s="55" t="n"/>
+      <c r="S26" s="55" t="n"/>
+      <c r="T26" s="55" t="n"/>
+      <c r="U26" s="55" t="n"/>
+      <c r="V26" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W26" s="57" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="53" t="n"/>
-      <c r="D27" s="53" t="n"/>
+      <c r="C27" s="46" t="n"/>
+      <c r="D27" s="46" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G27" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H27" s="49" t="n">
         <v>0</v>
@@ -3232,43 +3238,43 @@
         <v>0</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L27" s="50" t="n"/>
-      <c r="M27" s="55" t="n"/>
-      <c r="N27" s="55" t="n"/>
-      <c r="O27" s="55" t="n"/>
-      <c r="P27" s="55" t="n"/>
-      <c r="Q27" s="55" t="n"/>
-      <c r="R27" s="55" t="n"/>
-      <c r="S27" s="55" t="n"/>
-      <c r="T27" s="55" t="n"/>
-      <c r="U27" s="55" t="n"/>
-      <c r="V27" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W27" s="57" t="n"/>
+      <c r="M27" s="51" t="n"/>
+      <c r="N27" s="51" t="n"/>
+      <c r="O27" s="51" t="n"/>
+      <c r="P27" s="51" t="n"/>
+      <c r="Q27" s="51" t="n"/>
+      <c r="R27" s="51" t="n"/>
+      <c r="S27" s="51" t="n"/>
+      <c r="T27" s="51" t="n"/>
+      <c r="U27" s="51" t="n"/>
+      <c r="V27" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W27" s="58" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="46" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="53" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G28" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H28" s="49" t="n">
         <v>0</v>
@@ -3277,1371 +3283,1375 @@
         <v>0</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L28" s="50" t="n"/>
-      <c r="M28" s="51" t="n"/>
-      <c r="N28" s="51" t="n"/>
-      <c r="O28" s="51" t="n"/>
-      <c r="P28" s="51" t="n"/>
-      <c r="Q28" s="51" t="n"/>
-      <c r="R28" s="51" t="n"/>
-      <c r="S28" s="51" t="n"/>
-      <c r="T28" s="51" t="n"/>
-      <c r="U28" s="51" t="n"/>
-      <c r="V28" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W28" s="58" t="n"/>
+      <c r="M28" s="55" t="n"/>
+      <c r="N28" s="55" t="n"/>
+      <c r="O28" s="55" t="n"/>
+      <c r="P28" s="55" t="n"/>
+      <c r="Q28" s="55" t="n"/>
+      <c r="R28" s="55" t="n"/>
+      <c r="S28" s="55" t="n"/>
+      <c r="T28" s="55" t="n"/>
+      <c r="U28" s="55" t="n"/>
+      <c r="V28" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W28" s="57" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="53" t="n"/>
-      <c r="D29" s="53" t="n"/>
+      <c r="C29" s="46" t="n"/>
+      <c r="D29" s="46" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G29" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H29" s="49" t="n"/>
-      <c r="I29" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G29" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H29" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J29" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L29" s="50" t="n"/>
-      <c r="M29" s="55" t="n"/>
-      <c r="N29" s="55" t="n"/>
-      <c r="O29" s="55" t="n"/>
-      <c r="P29" s="55" t="n"/>
-      <c r="Q29" s="55" t="n"/>
-      <c r="R29" s="55" t="n"/>
-      <c r="S29" s="55" t="n"/>
-      <c r="T29" s="55" t="n"/>
-      <c r="U29" s="55" t="n"/>
-      <c r="V29" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W29" s="57" t="n"/>
+      <c r="M29" s="51" t="n"/>
+      <c r="N29" s="51" t="n"/>
+      <c r="O29" s="51" t="n"/>
+      <c r="P29" s="51" t="n"/>
+      <c r="Q29" s="51" t="n"/>
+      <c r="R29" s="51" t="n"/>
+      <c r="S29" s="51" t="n"/>
+      <c r="T29" s="51" t="n"/>
+      <c r="U29" s="51" t="n"/>
+      <c r="V29" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W29" s="58" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="46" t="n"/>
-      <c r="D30" s="46" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="53" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G30" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H30" s="49" t="n"/>
       <c r="I30" s="49" t="n"/>
       <c r="J30" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L30" s="50" t="n"/>
-      <c r="M30" s="51" t="n"/>
-      <c r="N30" s="51" t="n"/>
-      <c r="O30" s="51" t="n"/>
-      <c r="P30" s="51" t="n"/>
-      <c r="Q30" s="51" t="n"/>
-      <c r="R30" s="51" t="n"/>
-      <c r="S30" s="51" t="n"/>
-      <c r="T30" s="51" t="n"/>
-      <c r="U30" s="51" t="n"/>
-      <c r="V30" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W30" s="58" t="n"/>
+      <c r="M30" s="55" t="n"/>
+      <c r="N30" s="55" t="n"/>
+      <c r="O30" s="55" t="n"/>
+      <c r="P30" s="55" t="n"/>
+      <c r="Q30" s="55" t="n"/>
+      <c r="R30" s="55" t="n"/>
+      <c r="S30" s="55" t="n"/>
+      <c r="T30" s="55" t="n"/>
+      <c r="U30" s="55" t="n"/>
+      <c r="V30" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W30" s="57" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="53" t="n"/>
-      <c r="D31" s="53" t="n"/>
+      <c r="C31" s="46" t="n"/>
+      <c r="D31" s="46" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G31" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H31" s="49" t="n"/>
       <c r="I31" s="49" t="n"/>
       <c r="J31" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L31" s="50" t="n"/>
-      <c r="M31" s="55" t="n"/>
-      <c r="N31" s="55" t="n"/>
-      <c r="O31" s="55" t="n"/>
-      <c r="P31" s="55" t="n"/>
-      <c r="Q31" s="55" t="n"/>
-      <c r="R31" s="55" t="n"/>
-      <c r="S31" s="55" t="n"/>
-      <c r="T31" s="55" t="n"/>
-      <c r="U31" s="55" t="n"/>
-      <c r="V31" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W31" s="57" t="n"/>
+      <c r="M31" s="51" t="n"/>
+      <c r="N31" s="51" t="n"/>
+      <c r="O31" s="51" t="n"/>
+      <c r="P31" s="51" t="n"/>
+      <c r="Q31" s="51" t="n"/>
+      <c r="R31" s="51" t="n"/>
+      <c r="S31" s="51" t="n"/>
+      <c r="T31" s="51" t="n"/>
+      <c r="U31" s="51" t="n"/>
+      <c r="V31" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W31" s="58" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="46" t="n"/>
-      <c r="D32" s="46" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G32" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H32" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I32" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H32" s="49" t="n"/>
+      <c r="I32" s="49" t="n"/>
       <c r="J32" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L32" s="50" t="n"/>
-      <c r="M32" s="51" t="n"/>
-      <c r="N32" s="51" t="n"/>
-      <c r="O32" s="51" t="n"/>
-      <c r="P32" s="51" t="n"/>
-      <c r="Q32" s="51" t="n"/>
-      <c r="R32" s="51" t="n"/>
-      <c r="S32" s="51" t="n"/>
-      <c r="T32" s="51" t="n"/>
-      <c r="U32" s="51" t="n"/>
-      <c r="V32" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W32" s="58" t="n"/>
+      <c r="M32" s="55" t="n"/>
+      <c r="N32" s="55" t="n"/>
+      <c r="O32" s="55" t="n"/>
+      <c r="P32" s="55" t="n"/>
+      <c r="Q32" s="55" t="n"/>
+      <c r="R32" s="55" t="n"/>
+      <c r="S32" s="55" t="n"/>
+      <c r="T32" s="55" t="n"/>
+      <c r="U32" s="55" t="n"/>
+      <c r="V32" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W32" s="57" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="53" t="n"/>
-      <c r="D33" s="53" t="n"/>
+      <c r="C33" s="46" t="n"/>
+      <c r="D33" s="46" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G33" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H33" s="49" t="n"/>
-      <c r="I33" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G33" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H33" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I33" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J33" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L33" s="50" t="n"/>
-      <c r="M33" s="55" t="n"/>
-      <c r="N33" s="55" t="n"/>
-      <c r="O33" s="55" t="n"/>
-      <c r="P33" s="55" t="n"/>
-      <c r="Q33" s="55" t="n"/>
-      <c r="R33" s="55" t="n"/>
-      <c r="S33" s="55" t="n"/>
-      <c r="T33" s="55" t="n"/>
-      <c r="U33" s="55" t="n"/>
-      <c r="V33" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W33" s="57" t="n"/>
+      <c r="M33" s="51" t="n"/>
+      <c r="N33" s="51" t="n"/>
+      <c r="O33" s="51" t="n"/>
+      <c r="P33" s="51" t="n"/>
+      <c r="Q33" s="51" t="n"/>
+      <c r="R33" s="51" t="n"/>
+      <c r="S33" s="51" t="n"/>
+      <c r="T33" s="51" t="n"/>
+      <c r="U33" s="51" t="n"/>
+      <c r="V33" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W33" s="58" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="46" t="n"/>
-      <c r="D34" s="46" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G34" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G34" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H34" s="49" t="n"/>
       <c r="I34" s="49" t="n"/>
       <c r="J34" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L34" s="50" t="n"/>
-      <c r="M34" s="51" t="n"/>
-      <c r="N34" s="51" t="n"/>
-      <c r="O34" s="51" t="n"/>
-      <c r="P34" s="51" t="n"/>
-      <c r="Q34" s="51" t="n"/>
-      <c r="R34" s="51" t="n"/>
-      <c r="S34" s="51" t="n"/>
-      <c r="T34" s="51" t="n"/>
-      <c r="U34" s="51" t="n"/>
-      <c r="V34" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W34" s="58" t="n"/>
+      <c r="M34" s="55" t="n"/>
+      <c r="N34" s="55" t="n"/>
+      <c r="O34" s="55" t="n"/>
+      <c r="P34" s="55" t="n"/>
+      <c r="Q34" s="55" t="n"/>
+      <c r="R34" s="55" t="n"/>
+      <c r="S34" s="55" t="n"/>
+      <c r="T34" s="55" t="n"/>
+      <c r="U34" s="55" t="n"/>
+      <c r="V34" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W34" s="57" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="53" t="n"/>
-      <c r="D35" s="53" t="n"/>
+      <c r="C35" s="46" t="n"/>
+      <c r="D35" s="46" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G35" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G35" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H35" s="49" t="n"/>
       <c r="I35" s="49" t="n"/>
       <c r="J35" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K35" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K35" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L35" s="50" t="n"/>
-      <c r="M35" s="55" t="n"/>
-      <c r="N35" s="55" t="n"/>
-      <c r="O35" s="55" t="n"/>
-      <c r="P35" s="55" t="n"/>
-      <c r="Q35" s="55" t="n"/>
-      <c r="R35" s="55" t="n"/>
-      <c r="S35" s="55" t="n"/>
-      <c r="T35" s="55" t="n"/>
-      <c r="U35" s="55" t="n"/>
-      <c r="V35" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W35" s="57" t="n"/>
+      <c r="M35" s="51" t="n"/>
+      <c r="N35" s="51" t="n"/>
+      <c r="O35" s="51" t="n"/>
+      <c r="P35" s="51" t="n"/>
+      <c r="Q35" s="51" t="n"/>
+      <c r="R35" s="51" t="n"/>
+      <c r="S35" s="51" t="n"/>
+      <c r="T35" s="51" t="n"/>
+      <c r="U35" s="51" t="n"/>
+      <c r="V35" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W35" s="58" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
+      <c r="C36" s="53" t="n"/>
+      <c r="D36" s="53" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G36" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H36" s="49" t="n"/>
       <c r="I36" s="49" t="n"/>
       <c r="J36" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="51" t="n"/>
-      <c r="N36" s="51" t="n"/>
-      <c r="O36" s="51" t="n"/>
-      <c r="P36" s="51" t="n"/>
-      <c r="Q36" s="51" t="n"/>
-      <c r="R36" s="51" t="n"/>
-      <c r="S36" s="51" t="n"/>
-      <c r="T36" s="51" t="n"/>
-      <c r="U36" s="51" t="n"/>
-      <c r="V36" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W36" s="58" t="n"/>
+      <c r="M36" s="55" t="n"/>
+      <c r="N36" s="55" t="n"/>
+      <c r="O36" s="55" t="n"/>
+      <c r="P36" s="55" t="n"/>
+      <c r="Q36" s="55" t="n"/>
+      <c r="R36" s="55" t="n"/>
+      <c r="S36" s="55" t="n"/>
+      <c r="T36" s="55" t="n"/>
+      <c r="U36" s="55" t="n"/>
+      <c r="V36" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W36" s="57" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="53" t="n"/>
-      <c r="D37" s="53" t="n"/>
+      <c r="C37" s="46" t="n"/>
+      <c r="D37" s="46" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G37" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G37" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H37" s="49" t="n"/>
       <c r="I37" s="49" t="n"/>
       <c r="J37" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="55" t="n"/>
-      <c r="N37" s="55" t="n"/>
-      <c r="O37" s="55" t="n"/>
-      <c r="P37" s="55" t="n"/>
-      <c r="Q37" s="55" t="n"/>
-      <c r="R37" s="55" t="n"/>
-      <c r="S37" s="55" t="n"/>
-      <c r="T37" s="55" t="n"/>
-      <c r="U37" s="55" t="n"/>
-      <c r="V37" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W37" s="57" t="n"/>
+      <c r="M37" s="51" t="n"/>
+      <c r="N37" s="51" t="n"/>
+      <c r="O37" s="51" t="n"/>
+      <c r="P37" s="51" t="n"/>
+      <c r="Q37" s="51" t="n"/>
+      <c r="R37" s="51" t="n"/>
+      <c r="S37" s="51" t="n"/>
+      <c r="T37" s="51" t="n"/>
+      <c r="U37" s="51" t="n"/>
+      <c r="V37" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W37" s="58" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="46" t="n"/>
-      <c r="D38" s="46" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G38" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H38" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I38" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G38" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H38" s="49" t="n"/>
+      <c r="I38" s="49" t="n"/>
       <c r="J38" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="51" t="n"/>
-      <c r="N38" s="51" t="n"/>
-      <c r="O38" s="51" t="n"/>
-      <c r="P38" s="51" t="n"/>
-      <c r="Q38" s="51" t="n"/>
-      <c r="R38" s="51" t="n"/>
-      <c r="S38" s="51" t="n"/>
-      <c r="T38" s="51" t="n"/>
-      <c r="U38" s="51" t="n"/>
-      <c r="V38" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W38" s="58" t="n"/>
+      <c r="M38" s="55" t="n"/>
+      <c r="N38" s="55" t="n"/>
+      <c r="O38" s="55" t="n"/>
+      <c r="P38" s="55" t="n"/>
+      <c r="Q38" s="55" t="n"/>
+      <c r="R38" s="55" t="n"/>
+      <c r="S38" s="55" t="n"/>
+      <c r="T38" s="55" t="n"/>
+      <c r="U38" s="55" t="n"/>
+      <c r="V38" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W38" s="57" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="53" t="n"/>
-      <c r="D39" s="53" t="n"/>
+      <c r="C39" s="46" t="n"/>
+      <c r="D39" s="46" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G39" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H39" s="49" t="n"/>
-      <c r="I39" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H39" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I39" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J39" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="55" t="n"/>
-      <c r="N39" s="55" t="n"/>
-      <c r="O39" s="55" t="n"/>
-      <c r="P39" s="55" t="n"/>
-      <c r="Q39" s="55" t="n"/>
-      <c r="R39" s="55" t="n"/>
-      <c r="S39" s="55" t="n"/>
-      <c r="T39" s="55" t="n"/>
-      <c r="U39" s="55" t="n"/>
-      <c r="V39" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W39" s="57" t="n"/>
+      <c r="M39" s="51" t="n"/>
+      <c r="N39" s="51" t="n"/>
+      <c r="O39" s="51" t="n"/>
+      <c r="P39" s="51" t="n"/>
+      <c r="Q39" s="51" t="n"/>
+      <c r="R39" s="51" t="n"/>
+      <c r="S39" s="51" t="n"/>
+      <c r="T39" s="51" t="n"/>
+      <c r="U39" s="51" t="n"/>
+      <c r="V39" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W39" s="58" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="46" t="n"/>
-      <c r="D40" s="46" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G40" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H40" s="49" t="n"/>
       <c r="I40" s="49" t="n"/>
       <c r="J40" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="51" t="n"/>
-      <c r="N40" s="51" t="n"/>
-      <c r="O40" s="51" t="n"/>
-      <c r="P40" s="51" t="n"/>
-      <c r="Q40" s="51" t="n"/>
-      <c r="R40" s="51" t="n"/>
-      <c r="S40" s="51" t="n"/>
-      <c r="T40" s="51" t="n"/>
-      <c r="U40" s="51" t="n"/>
-      <c r="V40" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W40" s="58" t="n"/>
+      <c r="M40" s="55" t="n"/>
+      <c r="N40" s="55" t="n"/>
+      <c r="O40" s="55" t="n"/>
+      <c r="P40" s="55" t="n"/>
+      <c r="Q40" s="55" t="n"/>
+      <c r="R40" s="55" t="n"/>
+      <c r="S40" s="55" t="n"/>
+      <c r="T40" s="55" t="n"/>
+      <c r="U40" s="55" t="n"/>
+      <c r="V40" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W40" s="57" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="53" t="n"/>
-      <c r="D41" s="53" t="n"/>
+      <c r="C41" s="46" t="n"/>
+      <c r="D41" s="46" t="n"/>
       <c r="E41" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F41" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G41" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H41" s="49" t="n"/>
+      <c r="I41" s="49" t="n"/>
+      <c r="J41" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F41" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G41" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H41" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I41" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J41" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K41" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="55" t="n"/>
-      <c r="N41" s="55" t="n"/>
-      <c r="O41" s="55" t="n"/>
-      <c r="P41" s="55" t="n"/>
-      <c r="Q41" s="55" t="n"/>
-      <c r="R41" s="55" t="n"/>
-      <c r="S41" s="55" t="n"/>
-      <c r="T41" s="55" t="n"/>
-      <c r="U41" s="55" t="n"/>
-      <c r="V41" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W41" s="57" t="n"/>
+      <c r="M41" s="51" t="n"/>
+      <c r="N41" s="51" t="n"/>
+      <c r="O41" s="51" t="n"/>
+      <c r="P41" s="51" t="n"/>
+      <c r="Q41" s="51" t="n"/>
+      <c r="R41" s="51" t="n"/>
+      <c r="S41" s="51" t="n"/>
+      <c r="T41" s="51" t="n"/>
+      <c r="U41" s="51" t="n"/>
+      <c r="V41" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W41" s="58" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="46" t="n"/>
-      <c r="D42" s="46" t="n"/>
+      <c r="C42" s="53" t="n"/>
+      <c r="D42" s="53" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G42" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H42" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I42" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J42" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K42" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="51" t="n"/>
-      <c r="N42" s="51" t="n"/>
-      <c r="O42" s="51" t="n"/>
-      <c r="P42" s="51" t="n"/>
-      <c r="Q42" s="51" t="n"/>
-      <c r="R42" s="51" t="n"/>
-      <c r="S42" s="51" t="n"/>
-      <c r="T42" s="51" t="n"/>
-      <c r="U42" s="51" t="n"/>
-      <c r="V42" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W42" s="58" t="n"/>
+      <c r="M42" s="55" t="n"/>
+      <c r="N42" s="55" t="n"/>
+      <c r="O42" s="55" t="n"/>
+      <c r="P42" s="55" t="n"/>
+      <c r="Q42" s="55" t="n"/>
+      <c r="R42" s="55" t="n"/>
+      <c r="S42" s="55" t="n"/>
+      <c r="T42" s="55" t="n"/>
+      <c r="U42" s="55" t="n"/>
+      <c r="V42" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W42" s="57" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="53" t="n"/>
-      <c r="D43" s="53" t="n"/>
+      <c r="C43" s="46" t="n"/>
+      <c r="D43" s="46" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G43" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H43" s="49" t="n"/>
-      <c r="I43" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H43" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I43" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J43" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K43" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="55" t="n"/>
-      <c r="N43" s="55" t="n"/>
-      <c r="O43" s="55" t="n"/>
-      <c r="P43" s="55" t="n"/>
-      <c r="Q43" s="55" t="n"/>
-      <c r="R43" s="55" t="n"/>
-      <c r="S43" s="55" t="n"/>
-      <c r="T43" s="55" t="n"/>
-      <c r="U43" s="55" t="n"/>
-      <c r="V43" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W43" s="57" t="n"/>
+      <c r="M43" s="51" t="n"/>
+      <c r="N43" s="51" t="n"/>
+      <c r="O43" s="51" t="n"/>
+      <c r="P43" s="51" t="n"/>
+      <c r="Q43" s="51" t="n"/>
+      <c r="R43" s="51" t="n"/>
+      <c r="S43" s="51" t="n"/>
+      <c r="T43" s="51" t="n"/>
+      <c r="U43" s="51" t="n"/>
+      <c r="V43" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W43" s="58" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="46" t="n"/>
-      <c r="D44" s="46" t="n"/>
+      <c r="C44" s="53" t="n"/>
+      <c r="D44" s="53" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G44" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G44" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H44" s="49" t="n"/>
       <c r="I44" s="49" t="n"/>
       <c r="J44" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K44" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="51" t="n"/>
-      <c r="N44" s="51" t="n"/>
-      <c r="O44" s="51" t="n"/>
-      <c r="P44" s="51" t="n"/>
-      <c r="Q44" s="51" t="n"/>
-      <c r="R44" s="51" t="n"/>
-      <c r="S44" s="51" t="n"/>
-      <c r="T44" s="51" t="n"/>
-      <c r="U44" s="51" t="n"/>
-      <c r="V44" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W44" s="58" t="n"/>
+      <c r="M44" s="55" t="n"/>
+      <c r="N44" s="55" t="n"/>
+      <c r="O44" s="55" t="n"/>
+      <c r="P44" s="55" t="n"/>
+      <c r="Q44" s="55" t="n"/>
+      <c r="R44" s="55" t="n"/>
+      <c r="S44" s="55" t="n"/>
+      <c r="T44" s="55" t="n"/>
+      <c r="U44" s="55" t="n"/>
+      <c r="V44" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W44" s="57" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="53" t="n"/>
-      <c r="D45" s="53" t="n"/>
+      <c r="C45" s="46" t="n"/>
+      <c r="D45" s="46" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G45" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G45" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H45" s="49" t="n"/>
       <c r="I45" s="49" t="n"/>
       <c r="J45" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K45" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="55" t="n"/>
-      <c r="N45" s="55" t="n"/>
-      <c r="O45" s="55" t="n"/>
-      <c r="P45" s="55" t="n"/>
-      <c r="Q45" s="55" t="n"/>
-      <c r="R45" s="55" t="n"/>
-      <c r="S45" s="55" t="n"/>
-      <c r="T45" s="55" t="n"/>
-      <c r="U45" s="55" t="n"/>
-      <c r="V45" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W45" s="57" t="n"/>
+      <c r="M45" s="51" t="n"/>
+      <c r="N45" s="51" t="n"/>
+      <c r="O45" s="51" t="n"/>
+      <c r="P45" s="51" t="n"/>
+      <c r="Q45" s="51" t="n"/>
+      <c r="R45" s="51" t="n"/>
+      <c r="S45" s="51" t="n"/>
+      <c r="T45" s="51" t="n"/>
+      <c r="U45" s="51" t="n"/>
+      <c r="V45" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W45" s="58" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="46" t="n"/>
-      <c r="D46" s="46" t="n"/>
+      <c r="C46" s="53" t="n"/>
+      <c r="D46" s="53" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G46" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H46" s="49" t="n"/>
       <c r="I46" s="49" t="n"/>
       <c r="J46" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K46" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="51" t="n"/>
-      <c r="N46" s="51" t="n"/>
-      <c r="O46" s="51" t="n"/>
-      <c r="P46" s="51" t="n"/>
-      <c r="Q46" s="51" t="n"/>
-      <c r="R46" s="51" t="n"/>
-      <c r="S46" s="51" t="n"/>
-      <c r="T46" s="51" t="n"/>
-      <c r="U46" s="51" t="n"/>
-      <c r="V46" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W46" s="58" t="n"/>
+      <c r="M46" s="55" t="n"/>
+      <c r="N46" s="55" t="n"/>
+      <c r="O46" s="55" t="n"/>
+      <c r="P46" s="55" t="n"/>
+      <c r="Q46" s="55" t="n"/>
+      <c r="R46" s="55" t="n"/>
+      <c r="S46" s="55" t="n"/>
+      <c r="T46" s="55" t="n"/>
+      <c r="U46" s="55" t="n"/>
+      <c r="V46" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W46" s="57" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="53" t="n"/>
-      <c r="D47" s="53" t="n"/>
+      <c r="C47" s="46" t="n"/>
+      <c r="D47" s="46" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G47" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G47" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H47" s="49" t="n"/>
       <c r="I47" s="49" t="n"/>
       <c r="J47" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K47" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="55" t="n"/>
-      <c r="N47" s="55" t="n"/>
-      <c r="O47" s="55" t="n"/>
-      <c r="P47" s="55" t="n"/>
-      <c r="Q47" s="55" t="n"/>
-      <c r="R47" s="55" t="n"/>
-      <c r="S47" s="55" t="n"/>
-      <c r="T47" s="55" t="n"/>
-      <c r="U47" s="55" t="n"/>
-      <c r="V47" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W47" s="57" t="n"/>
+      <c r="M47" s="51" t="n"/>
+      <c r="N47" s="51" t="n"/>
+      <c r="O47" s="51" t="n"/>
+      <c r="P47" s="51" t="n"/>
+      <c r="Q47" s="51" t="n"/>
+      <c r="R47" s="51" t="n"/>
+      <c r="S47" s="51" t="n"/>
+      <c r="T47" s="51" t="n"/>
+      <c r="U47" s="51" t="n"/>
+      <c r="V47" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W47" s="58" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
+      <c r="C48" s="53" t="n"/>
+      <c r="D48" s="53" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G48" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G48" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H48" s="49" t="n"/>
       <c r="I48" s="49" t="n"/>
       <c r="J48" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K48" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="51" t="n"/>
-      <c r="N48" s="51" t="n"/>
-      <c r="O48" s="51" t="n"/>
-      <c r="P48" s="51" t="n"/>
-      <c r="Q48" s="51" t="n"/>
-      <c r="R48" s="51" t="n"/>
-      <c r="S48" s="51" t="n"/>
-      <c r="T48" s="51" t="n"/>
-      <c r="U48" s="51" t="n"/>
-      <c r="V48" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W48" s="58" t="n"/>
+      <c r="M48" s="55" t="n"/>
+      <c r="N48" s="55" t="n"/>
+      <c r="O48" s="55" t="n"/>
+      <c r="P48" s="55" t="n"/>
+      <c r="Q48" s="55" t="n"/>
+      <c r="R48" s="55" t="n"/>
+      <c r="S48" s="55" t="n"/>
+      <c r="T48" s="55" t="n"/>
+      <c r="U48" s="55" t="n"/>
+      <c r="V48" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W48" s="57" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="53" t="n"/>
-      <c r="D49" s="53" t="n"/>
+      <c r="C49" s="46" t="n"/>
+      <c r="D49" s="46" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G49" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G49" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H49" s="49" t="n"/>
       <c r="I49" s="49" t="n"/>
       <c r="J49" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K49" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="55" t="n"/>
-      <c r="N49" s="55" t="n"/>
-      <c r="O49" s="55" t="n"/>
-      <c r="P49" s="55" t="n"/>
-      <c r="Q49" s="55" t="n"/>
-      <c r="R49" s="55" t="n"/>
-      <c r="S49" s="55" t="n"/>
-      <c r="T49" s="55" t="n"/>
-      <c r="U49" s="55" t="n"/>
-      <c r="V49" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W49" s="57" t="n"/>
+      <c r="M49" s="51" t="n"/>
+      <c r="N49" s="51" t="n"/>
+      <c r="O49" s="51" t="n"/>
+      <c r="P49" s="51" t="n"/>
+      <c r="Q49" s="51" t="n"/>
+      <c r="R49" s="51" t="n"/>
+      <c r="S49" s="51" t="n"/>
+      <c r="T49" s="51" t="n"/>
+      <c r="U49" s="51" t="n"/>
+      <c r="V49" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W49" s="58" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
+      <c r="C50" s="53" t="n"/>
+      <c r="D50" s="53" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G50" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="49" t="n"/>
       <c r="J50" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="51" t="n"/>
-      <c r="N50" s="51" t="n"/>
-      <c r="O50" s="51" t="n"/>
-      <c r="P50" s="51" t="n"/>
-      <c r="Q50" s="51" t="n"/>
-      <c r="R50" s="51" t="n"/>
-      <c r="S50" s="51" t="n"/>
-      <c r="T50" s="51" t="n"/>
-      <c r="U50" s="51" t="n"/>
-      <c r="V50" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W50" s="58" t="n"/>
+      <c r="M50" s="55" t="n"/>
+      <c r="N50" s="55" t="n"/>
+      <c r="O50" s="55" t="n"/>
+      <c r="P50" s="55" t="n"/>
+      <c r="Q50" s="55" t="n"/>
+      <c r="R50" s="55" t="n"/>
+      <c r="S50" s="55" t="n"/>
+      <c r="T50" s="55" t="n"/>
+      <c r="U50" s="55" t="n"/>
+      <c r="V50" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W50" s="57" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="53" t="n"/>
-      <c r="D51" s="53" t="n"/>
+      <c r="C51" s="46" t="n"/>
+      <c r="D51" s="46" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G51" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H51" s="49" t="n"/>
       <c r="I51" s="49" t="n"/>
       <c r="J51" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="55" t="n"/>
-      <c r="N51" s="55" t="n"/>
-      <c r="O51" s="55" t="n"/>
-      <c r="P51" s="55" t="n"/>
-      <c r="Q51" s="55" t="n"/>
-      <c r="R51" s="55" t="n"/>
-      <c r="S51" s="55" t="n"/>
-      <c r="T51" s="55" t="n"/>
-      <c r="U51" s="55" t="n"/>
-      <c r="V51" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W51" s="57" t="n"/>
+      <c r="M51" s="51" t="n"/>
+      <c r="N51" s="51" t="n"/>
+      <c r="O51" s="51" t="n"/>
+      <c r="P51" s="51" t="n"/>
+      <c r="Q51" s="51" t="n"/>
+      <c r="R51" s="51" t="n"/>
+      <c r="S51" s="51" t="n"/>
+      <c r="T51" s="51" t="n"/>
+      <c r="U51" s="51" t="n"/>
+      <c r="V51" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W51" s="58" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="46" t="n"/>
-      <c r="D52" s="46" t="n"/>
+      <c r="C52" s="53" t="n"/>
+      <c r="D52" s="53" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G52" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G52" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H52" s="49" t="n"/>
       <c r="I52" s="49" t="n"/>
       <c r="J52" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="51" t="n"/>
-      <c r="N52" s="51" t="n"/>
-      <c r="O52" s="51" t="n"/>
-      <c r="P52" s="51" t="n"/>
-      <c r="Q52" s="51" t="n"/>
-      <c r="R52" s="51" t="n"/>
-      <c r="S52" s="51" t="n"/>
-      <c r="T52" s="51" t="n"/>
-      <c r="U52" s="51" t="n"/>
-      <c r="V52" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W52" s="58" t="n"/>
+      <c r="M52" s="55" t="n"/>
+      <c r="N52" s="55" t="n"/>
+      <c r="O52" s="55" t="n"/>
+      <c r="P52" s="55" t="n"/>
+      <c r="Q52" s="55" t="n"/>
+      <c r="R52" s="55" t="n"/>
+      <c r="S52" s="55" t="n"/>
+      <c r="T52" s="55" t="n"/>
+      <c r="U52" s="55" t="n"/>
+      <c r="V52" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W52" s="57" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="53" t="n"/>
-      <c r="D53" s="53" t="n"/>
+      <c r="C53" s="46" t="n"/>
+      <c r="D53" s="46" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G53" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G53" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H53" s="49" t="n"/>
       <c r="I53" s="49" t="n"/>
       <c r="J53" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="55" t="n"/>
-      <c r="N53" s="55" t="n"/>
-      <c r="O53" s="55" t="n"/>
-      <c r="P53" s="55" t="n"/>
-      <c r="Q53" s="55" t="n"/>
-      <c r="R53" s="55" t="n"/>
-      <c r="S53" s="55" t="n"/>
-      <c r="T53" s="55" t="n"/>
-      <c r="U53" s="55" t="n"/>
-      <c r="V53" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W53" s="57" t="n"/>
+      <c r="M53" s="51" t="n"/>
+      <c r="N53" s="51" t="n"/>
+      <c r="O53" s="51" t="n"/>
+      <c r="P53" s="51" t="n"/>
+      <c r="Q53" s="51" t="n"/>
+      <c r="R53" s="51" t="n"/>
+      <c r="S53" s="51" t="n"/>
+      <c r="T53" s="51" t="n"/>
+      <c r="U53" s="51" t="n"/>
+      <c r="V53" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W53" s="58" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="46" t="n"/>
-      <c r="D54" s="46" t="n"/>
+      <c r="C54" s="53" t="n"/>
+      <c r="D54" s="53" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G54" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G54" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="51" t="n"/>
-      <c r="N54" s="51" t="n"/>
-      <c r="O54" s="51" t="n"/>
-      <c r="P54" s="51" t="n"/>
-      <c r="Q54" s="51" t="n"/>
-      <c r="R54" s="51" t="n"/>
-      <c r="S54" s="51" t="n"/>
-      <c r="T54" s="51" t="n"/>
-      <c r="U54" s="51" t="n"/>
-      <c r="V54" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W54" s="58" t="n"/>
+      <c r="M54" s="55" t="n"/>
+      <c r="N54" s="55" t="n"/>
+      <c r="O54" s="55" t="n"/>
+      <c r="P54" s="55" t="n"/>
+      <c r="Q54" s="55" t="n"/>
+      <c r="R54" s="55" t="n"/>
+      <c r="S54" s="55" t="n"/>
+      <c r="T54" s="55" t="n"/>
+      <c r="U54" s="55" t="n"/>
+      <c r="V54" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W54" s="57" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="53" t="n"/>
-      <c r="D55" s="53" t="n"/>
+      <c r="C55" s="46" t="n"/>
+      <c r="D55" s="46" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G55" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G55" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="55" t="n"/>
-      <c r="N55" s="55" t="n"/>
-      <c r="O55" s="55" t="n"/>
-      <c r="P55" s="55" t="n"/>
-      <c r="Q55" s="55" t="n"/>
-      <c r="R55" s="55" t="n"/>
-      <c r="S55" s="55" t="n"/>
-      <c r="T55" s="55" t="n"/>
-      <c r="U55" s="55" t="n"/>
-      <c r="V55" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W55" s="57" t="n"/>
+      <c r="M55" s="51" t="n"/>
+      <c r="N55" s="51" t="n"/>
+      <c r="O55" s="51" t="n"/>
+      <c r="P55" s="51" t="n"/>
+      <c r="Q55" s="51" t="n"/>
+      <c r="R55" s="51" t="n"/>
+      <c r="S55" s="51" t="n"/>
+      <c r="T55" s="51" t="n"/>
+      <c r="U55" s="51" t="n"/>
+      <c r="V55" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W55" s="58" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="46" t="n"/>
-      <c r="D56" s="46" t="n"/>
+      <c r="C56" s="53" t="n"/>
+      <c r="D56" s="53" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G56" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G56" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="51" t="n"/>
-      <c r="N56" s="51" t="n"/>
-      <c r="O56" s="51" t="n"/>
-      <c r="P56" s="51" t="n"/>
-      <c r="Q56" s="51" t="n"/>
-      <c r="R56" s="51" t="n"/>
-      <c r="S56" s="51" t="n"/>
-      <c r="T56" s="51" t="n"/>
-      <c r="U56" s="51" t="n"/>
-      <c r="V56" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W56" s="58" t="n"/>
+      <c r="M56" s="55" t="n"/>
+      <c r="N56" s="55" t="n"/>
+      <c r="O56" s="55" t="n"/>
+      <c r="P56" s="55" t="n"/>
+      <c r="Q56" s="55" t="n"/>
+      <c r="R56" s="55" t="n"/>
+      <c r="S56" s="55" t="n"/>
+      <c r="T56" s="55" t="n"/>
+      <c r="U56" s="55" t="n"/>
+      <c r="V56" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W56" s="57" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="53" t="n"/>
-      <c r="D57" s="53" t="n"/>
+      <c r="C57" s="46" t="n"/>
+      <c r="D57" s="46" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G57" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G57" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="55" t="n"/>
-      <c r="N57" s="55" t="n"/>
-      <c r="O57" s="55" t="n"/>
-      <c r="P57" s="55" t="n"/>
-      <c r="Q57" s="55" t="n"/>
-      <c r="R57" s="55" t="n"/>
-      <c r="S57" s="55" t="n"/>
-      <c r="T57" s="55" t="n"/>
-      <c r="U57" s="55" t="n"/>
-      <c r="V57" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W57" s="57" t="n"/>
+      <c r="M57" s="51" t="n"/>
+      <c r="N57" s="51" t="n"/>
+      <c r="O57" s="51" t="n"/>
+      <c r="P57" s="51" t="n"/>
+      <c r="Q57" s="51" t="n"/>
+      <c r="R57" s="51" t="n"/>
+      <c r="S57" s="51" t="n"/>
+      <c r="T57" s="51" t="n"/>
+      <c r="U57" s="51" t="n"/>
+      <c r="V57" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W57" s="58" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="46" t="n"/>
-      <c r="D58" s="46" t="n"/>
+      <c r="C58" s="53" t="n"/>
+      <c r="D58" s="53" t="n"/>
       <c r="E58" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F58" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G58" s="48" t="n">
-        <v>24</v>
+      <c r="G58" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="51" t="n"/>
-      <c r="N58" s="51" t="n"/>
-      <c r="O58" s="51" t="n"/>
-      <c r="P58" s="51" t="n"/>
-      <c r="Q58" s="51" t="n"/>
-      <c r="R58" s="51" t="n"/>
-      <c r="S58" s="51" t="n"/>
-      <c r="T58" s="51" t="n"/>
-      <c r="U58" s="51" t="n"/>
-      <c r="V58" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W58" s="58" t="n"/>
+      <c r="M58" s="55" t="n"/>
+      <c r="N58" s="55" t="n"/>
+      <c r="O58" s="55" t="n"/>
+      <c r="P58" s="55" t="n"/>
+      <c r="Q58" s="55" t="n"/>
+      <c r="R58" s="55" t="n"/>
+      <c r="S58" s="55" t="n"/>
+      <c r="T58" s="55" t="n"/>
+      <c r="U58" s="55" t="n"/>
+      <c r="V58" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W58" s="57" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="53" t="n"/>
-      <c r="D59" s="53" t="n"/>
+      <c r="C59" s="46" t="n"/>
+      <c r="D59" s="46" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G59" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G59" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="55" t="n"/>
-      <c r="N59" s="55" t="n"/>
-      <c r="O59" s="55" t="n"/>
-      <c r="P59" s="55" t="n"/>
-      <c r="Q59" s="55" t="n"/>
-      <c r="R59" s="55" t="n"/>
-      <c r="S59" s="55" t="n"/>
-      <c r="T59" s="55" t="n"/>
-      <c r="U59" s="55" t="n"/>
-      <c r="V59" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W59" s="57" t="n"/>
+      <c r="M59" s="51" t="n"/>
+      <c r="N59" s="51" t="n"/>
+      <c r="O59" s="51" t="n"/>
+      <c r="P59" s="51" t="n"/>
+      <c r="Q59" s="51" t="n"/>
+      <c r="R59" s="51" t="n"/>
+      <c r="S59" s="51" t="n"/>
+      <c r="T59" s="51" t="n"/>
+      <c r="U59" s="51" t="n"/>
+      <c r="V59" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W59" s="58" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
+      <c r="C60" s="53" t="n"/>
+      <c r="D60" s="53" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G60" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G60" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="51" t="n"/>
-      <c r="N60" s="51" t="n"/>
-      <c r="O60" s="51" t="n"/>
-      <c r="P60" s="51" t="n"/>
-      <c r="Q60" s="51" t="n"/>
-      <c r="R60" s="51" t="n"/>
-      <c r="S60" s="51" t="n"/>
-      <c r="T60" s="51" t="n"/>
-      <c r="U60" s="51" t="n"/>
-      <c r="V60" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W60" s="58" t="n"/>
+      <c r="M60" s="55" t="n"/>
+      <c r="N60" s="55" t="n"/>
+      <c r="O60" s="55" t="n"/>
+      <c r="P60" s="55" t="n"/>
+      <c r="Q60" s="55" t="n"/>
+      <c r="R60" s="55" t="n"/>
+      <c r="S60" s="55" t="n"/>
+      <c r="T60" s="55" t="n"/>
+      <c r="U60" s="55" t="n"/>
+      <c r="V60" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W60" s="57" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="53" t="n"/>
-      <c r="D61" s="53" t="n"/>
+      <c r="C61" s="46" t="n"/>
+      <c r="D61" s="46" t="n"/>
       <c r="E61" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F61" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G61" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
@@ -4649,51 +4659,92 @@
         <v>59</v>
       </c>
       <c r="K61" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="55" t="n"/>
-      <c r="N61" s="55" t="n"/>
-      <c r="O61" s="55" t="n"/>
-      <c r="P61" s="55" t="n"/>
-      <c r="Q61" s="55" t="n"/>
-      <c r="R61" s="55" t="n"/>
-      <c r="S61" s="55" t="n"/>
-      <c r="T61" s="55" t="n"/>
-      <c r="U61" s="55" t="n"/>
-      <c r="V61" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W61" s="57" t="n"/>
+      <c r="M61" s="51" t="n"/>
+      <c r="N61" s="51" t="n"/>
+      <c r="O61" s="51" t="n"/>
+      <c r="P61" s="51" t="n"/>
+      <c r="Q61" s="51" t="n"/>
+      <c r="R61" s="51" t="n"/>
+      <c r="S61" s="51" t="n"/>
+      <c r="T61" s="51" t="n"/>
+      <c r="U61" s="51" t="n"/>
+      <c r="V61" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W61" s="58" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B62" s="45" t="n"/>
-      <c r="C62" s="46" t="n"/>
-      <c r="D62" s="46" t="n"/>
-      <c r="E62" s="47" t="n"/>
-      <c r="F62" s="47" t="n"/>
-      <c r="G62" s="60" t="n"/>
+      <c r="C62" s="53" t="n"/>
+      <c r="D62" s="53" t="n"/>
+      <c r="E62" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F62" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G62" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="49" t="n"/>
-      <c r="J62" s="50" t="n"/>
-      <c r="K62" s="50" t="n"/>
+      <c r="J62" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K62" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L62" s="50" t="n"/>
-      <c r="M62" s="51" t="n"/>
-      <c r="N62" s="51" t="n"/>
-      <c r="O62" s="51" t="n"/>
-      <c r="P62" s="51" t="n"/>
-      <c r="Q62" s="51" t="n"/>
-      <c r="R62" s="51" t="n"/>
-      <c r="S62" s="51" t="n"/>
-      <c r="T62" s="51" t="n"/>
-      <c r="U62" s="51" t="n"/>
-      <c r="V62" s="61" t="n"/>
-      <c r="W62" s="61" t="n"/>
+      <c r="M62" s="55" t="n"/>
+      <c r="N62" s="55" t="n"/>
+      <c r="O62" s="55" t="n"/>
+      <c r="P62" s="55" t="n"/>
+      <c r="Q62" s="55" t="n"/>
+      <c r="R62" s="55" t="n"/>
+      <c r="S62" s="55" t="n"/>
+      <c r="T62" s="55" t="n"/>
+      <c r="U62" s="55" t="n"/>
+      <c r="V62" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W62" s="57" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B63" s="45" t="n"/>
+      <c r="C63" s="46" t="n"/>
+      <c r="D63" s="46" t="n"/>
+      <c r="E63" s="47" t="n"/>
+      <c r="F63" s="47" t="n"/>
+      <c r="G63" s="60" t="n"/>
+      <c r="H63" s="49" t="n"/>
+      <c r="I63" s="49" t="n"/>
+      <c r="J63" s="50" t="n"/>
+      <c r="K63" s="50" t="n"/>
+      <c r="L63" s="50" t="n"/>
+      <c r="M63" s="51" t="n"/>
+      <c r="N63" s="51" t="n"/>
+      <c r="O63" s="51" t="n"/>
+      <c r="P63" s="51" t="n"/>
+      <c r="Q63" s="51" t="n"/>
+      <c r="R63" s="51" t="n"/>
+      <c r="S63" s="51" t="n"/>
+      <c r="T63" s="51" t="n"/>
+      <c r="U63" s="51" t="n"/>
+      <c r="V63" s="61" t="n"/>
+      <c r="W63" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W63"/>
+  <dimension ref="A1:W64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,7 +1982,7 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/03(五)</t>
+          <t>2026/04/06(一)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
@@ -2026,105 +2026,105 @@
       <c r="T4" s="69" t="inlineStr"/>
       <c r="U4" s="69" t="inlineStr"/>
       <c r="V4" s="69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W4" s="69" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
       <c r="C5" s="64" t="inlineStr"/>
       <c r="D5" s="64" t="inlineStr"/>
       <c r="E5" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G5" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I5" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J5" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L5" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M5" s="69" t="inlineStr"/>
       <c r="N5" s="69" t="inlineStr"/>
-      <c r="O5" s="69" t="inlineStr">
+      <c r="O5" s="69" t="inlineStr"/>
+      <c r="P5" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P5" s="69" t="inlineStr"/>
       <c r="Q5" s="69" t="inlineStr"/>
       <c r="R5" s="69" t="inlineStr"/>
       <c r="S5" s="69" t="inlineStr"/>
       <c r="T5" s="69" t="inlineStr"/>
       <c r="U5" s="69" t="inlineStr"/>
       <c r="V5" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W5" s="69" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
       <c r="C6" s="64" t="inlineStr"/>
       <c r="D6" s="64" t="inlineStr"/>
       <c r="E6" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G6" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G6" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H6" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K6" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L6" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M6" s="69" t="inlineStr"/>
-      <c r="N6" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M6" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N6" s="69" t="inlineStr"/>
+      <c r="O6" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O6" s="69" t="inlineStr"/>
       <c r="P6" s="69" t="inlineStr"/>
       <c r="Q6" s="69" t="inlineStr"/>
       <c r="R6" s="69" t="inlineStr"/>
@@ -2132,51 +2132,47 @@
       <c r="T6" s="69" t="inlineStr"/>
       <c r="U6" s="69" t="inlineStr"/>
       <c r="V6" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W6" s="69" t="inlineStr"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="64" t="inlineStr"/>
       <c r="D7" s="64" t="inlineStr"/>
       <c r="E7" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F7" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G7" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G7" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I7" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J7" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K7" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L7" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M7" s="69" t="inlineStr"/>
+      <c r="N7" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N7" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O7" s="69" t="inlineStr"/>
@@ -2187,254 +2183,250 @@
       <c r="T7" s="69" t="inlineStr"/>
       <c r="U7" s="69" t="inlineStr"/>
       <c r="V7" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W7" s="69" t="inlineStr"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B8" s="63" t="inlineStr"/>
+      <c r="C8" s="64" t="inlineStr"/>
+      <c r="D8" s="64" t="inlineStr"/>
+      <c r="E8" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F8" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G8" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H8" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L8" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N8" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O8" s="69" t="inlineStr"/>
+      <c r="P8" s="69" t="inlineStr"/>
+      <c r="Q8" s="69" t="inlineStr"/>
+      <c r="R8" s="69" t="inlineStr"/>
+      <c r="S8" s="69" t="inlineStr"/>
+      <c r="T8" s="69" t="inlineStr"/>
+      <c r="U8" s="69" t="inlineStr"/>
+      <c r="V8" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W7" s="69" t="inlineStr"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="W8" s="69" t="inlineStr"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E8" s="39" t="n">
+      <c r="E9" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F8" s="39" t="n">
+      <c r="F9" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G8" s="40" t="n">
+      <c r="G9" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H8" s="41" t="n">
+      <c r="H9" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I8" s="41" t="n">
+      <c r="I9" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J8" s="42" t="n">
+      <c r="J9" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K8" s="42" t="n">
+      <c r="K9" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L8" s="42" t="n">
+      <c r="L9" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M8" s="43" t="inlineStr">
+      <c r="M9" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N8" s="43" t="inlineStr"/>
-      <c r="O8" s="43" t="inlineStr">
+      <c r="N9" s="43" t="inlineStr"/>
+      <c r="O9" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P8" s="43" t="inlineStr"/>
-      <c r="Q8" s="43" t="inlineStr"/>
-      <c r="R8" s="43" t="inlineStr"/>
-      <c r="S8" s="43" t="inlineStr"/>
-      <c r="T8" s="43" t="inlineStr"/>
-      <c r="U8" s="43" t="inlineStr"/>
-      <c r="V8" s="43" t="n">
+      <c r="P9" s="43" t="inlineStr"/>
+      <c r="Q9" s="43" t="inlineStr"/>
+      <c r="R9" s="43" t="inlineStr"/>
+      <c r="S9" s="43" t="inlineStr"/>
+      <c r="T9" s="43" t="inlineStr"/>
+      <c r="U9" s="43" t="inlineStr"/>
+      <c r="V9" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W8" s="43" t="inlineStr"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B9" s="45" t="n"/>
-      <c r="C9" s="46" t="n"/>
-      <c r="D9" s="46" t="n"/>
-      <c r="E9" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F9" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G9" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H9" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L9" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" s="51" t="n"/>
-      <c r="N9" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O9" s="51" t="n"/>
-      <c r="P9" s="51" t="n"/>
-      <c r="Q9" s="51" t="n"/>
-      <c r="R9" s="51" t="n"/>
-      <c r="S9" s="51" t="n"/>
-      <c r="T9" s="51" t="n"/>
-      <c r="U9" s="51" t="n"/>
-      <c r="V9" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W9" s="43" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B10" s="45" t="n"/>
-      <c r="C10" s="53" t="n"/>
-      <c r="D10" s="53" t="n"/>
+      <c r="C10" s="46" t="n"/>
+      <c r="D10" s="46" t="n"/>
       <c r="E10" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F10" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G10" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G10" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H10" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I10" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J10" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K10" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L10" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M10" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N10" s="55" t="n"/>
-      <c r="O10" s="55" t="n"/>
-      <c r="P10" s="55" t="n"/>
-      <c r="Q10" s="55" t="n"/>
-      <c r="R10" s="55" t="n"/>
-      <c r="S10" s="55" t="n"/>
-      <c r="T10" s="55" t="n"/>
-      <c r="U10" s="55" t="n"/>
-      <c r="V10" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W10" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M10" s="51" t="n"/>
+      <c r="N10" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O10" s="51" t="n"/>
+      <c r="P10" s="51" t="n"/>
+      <c r="Q10" s="51" t="n"/>
+      <c r="R10" s="51" t="n"/>
+      <c r="S10" s="51" t="n"/>
+      <c r="T10" s="51" t="n"/>
+      <c r="U10" s="51" t="n"/>
+      <c r="V10" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B11" s="45" t="n"/>
-      <c r="C11" s="46" t="n"/>
-      <c r="D11" s="46" t="n"/>
+      <c r="C11" s="53" t="n"/>
+      <c r="D11" s="53" t="n"/>
       <c r="E11" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F11" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G11" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G11" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H11" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I11" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J11" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K11" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L11" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M11" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N11" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O11" s="51" t="n"/>
-      <c r="P11" s="51" t="n"/>
-      <c r="Q11" s="51" t="n"/>
-      <c r="R11" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S11" s="51" t="n"/>
-      <c r="T11" s="51" t="n"/>
-      <c r="U11" s="51" t="n"/>
-      <c r="V11" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W11" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M11" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N11" s="55" t="n"/>
+      <c r="O11" s="55" t="n"/>
+      <c r="P11" s="55" t="n"/>
+      <c r="Q11" s="55" t="n"/>
+      <c r="R11" s="55" t="n"/>
+      <c r="S11" s="55" t="n"/>
+      <c r="T11" s="55" t="n"/>
+      <c r="U11" s="55" t="n"/>
+      <c r="V11" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W11" s="57" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B12" s="45" t="n"/>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
+      <c r="C12" s="46" t="n"/>
+      <c r="D12" s="46" t="n"/>
       <c r="E12" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F12" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G12" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H12" s="49" t="n">
         <v>1</v>
@@ -2443,493 +2435,497 @@
         <v>1</v>
       </c>
       <c r="J12" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K12" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L12" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M12" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M12" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N12" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N12" s="55" t="n"/>
-      <c r="O12" s="55" t="n"/>
-      <c r="P12" s="55" t="n"/>
-      <c r="Q12" s="55" t="inlineStr">
+      <c r="O12" s="51" t="n"/>
+      <c r="P12" s="51" t="n"/>
+      <c r="Q12" s="51" t="n"/>
+      <c r="R12" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R12" s="55" t="n"/>
-      <c r="S12" s="55" t="n"/>
-      <c r="T12" s="55" t="n"/>
-      <c r="U12" s="55" t="n"/>
-      <c r="V12" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W12" s="57" t="n"/>
+      <c r="S12" s="51" t="n"/>
+      <c r="T12" s="51" t="n"/>
+      <c r="U12" s="51" t="n"/>
+      <c r="V12" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W12" s="58" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B13" s="45" t="n"/>
-      <c r="C13" s="46" t="n"/>
-      <c r="D13" s="46" t="n"/>
+      <c r="C13" s="53" t="n"/>
+      <c r="D13" s="53" t="n"/>
       <c r="E13" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F13" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G13" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G13" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H13" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I13" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J13" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K13" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L13" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N13" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O13" s="51" t="n"/>
-      <c r="P13" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M13" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N13" s="55" t="n"/>
+      <c r="O13" s="55" t="n"/>
+      <c r="P13" s="55" t="n"/>
+      <c r="Q13" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q13" s="51" t="n"/>
-      <c r="R13" s="51" t="n"/>
-      <c r="S13" s="51" t="n"/>
-      <c r="T13" s="51" t="n"/>
-      <c r="U13" s="51" t="n"/>
-      <c r="V13" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W13" s="58" t="n"/>
+      <c r="R13" s="55" t="n"/>
+      <c r="S13" s="55" t="n"/>
+      <c r="T13" s="55" t="n"/>
+      <c r="U13" s="55" t="n"/>
+      <c r="V13" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W13" s="57" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B14" s="45" t="n"/>
-      <c r="C14" s="53" t="n"/>
-      <c r="D14" s="53" t="n"/>
+      <c r="C14" s="46" t="n"/>
+      <c r="D14" s="46" t="n"/>
       <c r="E14" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F14" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G14" s="59" t="n">
-        <v>45.1</v>
+      <c r="G14" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H14" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I14" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J14" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K14" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L14" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N14" s="55" t="n"/>
-      <c r="O14" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P14" s="55" t="n"/>
-      <c r="Q14" s="55" t="n"/>
-      <c r="R14" s="55" t="n"/>
-      <c r="S14" s="55" t="n"/>
-      <c r="T14" s="55" t="n"/>
-      <c r="U14" s="55" t="n"/>
-      <c r="V14" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W14" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M14" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N14" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O14" s="51" t="n"/>
+      <c r="P14" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q14" s="51" t="n"/>
+      <c r="R14" s="51" t="n"/>
+      <c r="S14" s="51" t="n"/>
+      <c r="T14" s="51" t="n"/>
+      <c r="U14" s="51" t="n"/>
+      <c r="V14" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W14" s="58" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B15" s="45" t="n"/>
-      <c r="C15" s="46" t="n"/>
-      <c r="D15" s="46" t="n"/>
+      <c r="C15" s="53" t="n"/>
+      <c r="D15" s="53" t="n"/>
       <c r="E15" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F15" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G15" s="54" t="n">
-        <v>26.3</v>
+      <c r="G15" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H15" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I15" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J15" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K15" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L15" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M15" s="51" t="n"/>
-      <c r="N15" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M15" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N15" s="55" t="n"/>
+      <c r="O15" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O15" s="51" t="n"/>
-      <c r="P15" s="51" t="n"/>
-      <c r="Q15" s="51" t="n"/>
-      <c r="R15" s="51" t="n"/>
-      <c r="S15" s="51" t="n"/>
-      <c r="T15" s="51" t="n"/>
-      <c r="U15" s="51" t="n"/>
-      <c r="V15" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W15" s="58" t="n"/>
+      <c r="P15" s="55" t="n"/>
+      <c r="Q15" s="55" t="n"/>
+      <c r="R15" s="55" t="n"/>
+      <c r="S15" s="55" t="n"/>
+      <c r="T15" s="55" t="n"/>
+      <c r="U15" s="55" t="n"/>
+      <c r="V15" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W15" s="57" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B16" s="45" t="n"/>
-      <c r="C16" s="53" t="n"/>
-      <c r="D16" s="53" t="n"/>
+      <c r="C16" s="46" t="n"/>
+      <c r="D16" s="46" t="n"/>
       <c r="E16" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F16" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G16" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H16" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K16" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L16" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M16" s="51" t="n"/>
+      <c r="N16" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N16" s="55" t="n"/>
-      <c r="O16" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P16" s="55" t="n"/>
-      <c r="Q16" s="55" t="n"/>
-      <c r="R16" s="55" t="n"/>
-      <c r="S16" s="55" t="n"/>
-      <c r="T16" s="55" t="n"/>
-      <c r="U16" s="55" t="n"/>
-      <c r="V16" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W16" s="57" t="n"/>
+      <c r="O16" s="51" t="n"/>
+      <c r="P16" s="51" t="n"/>
+      <c r="Q16" s="51" t="n"/>
+      <c r="R16" s="51" t="n"/>
+      <c r="S16" s="51" t="n"/>
+      <c r="T16" s="51" t="n"/>
+      <c r="U16" s="51" t="n"/>
+      <c r="V16" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W16" s="58" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B17" s="45" t="n"/>
-      <c r="C17" s="46" t="n"/>
-      <c r="D17" s="46" t="n"/>
+      <c r="C17" s="53" t="n"/>
+      <c r="D17" s="53" t="n"/>
       <c r="E17" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F17" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G17" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H17" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J17" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K17" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L17" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M17" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N17" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O17" s="51" t="n"/>
-      <c r="P17" s="51" t="n"/>
-      <c r="Q17" s="51" t="n"/>
-      <c r="R17" s="51" t="n"/>
-      <c r="S17" s="51" t="n"/>
-      <c r="T17" s="51" t="n"/>
-      <c r="U17" s="51" t="n"/>
-      <c r="V17" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W17" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M17" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N17" s="55" t="n"/>
+      <c r="O17" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P17" s="55" t="n"/>
+      <c r="Q17" s="55" t="n"/>
+      <c r="R17" s="55" t="n"/>
+      <c r="S17" s="55" t="n"/>
+      <c r="T17" s="55" t="n"/>
+      <c r="U17" s="55" t="n"/>
+      <c r="V17" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W17" s="57" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B18" s="45" t="n"/>
-      <c r="C18" s="53" t="n"/>
-      <c r="D18" s="53" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="46" t="n"/>
       <c r="E18" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F18" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G18" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H18" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K18" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L18" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I18" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K18" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L18" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" s="55" t="inlineStr">
+      <c r="M18" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N18" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N18" s="55" t="n"/>
-      <c r="O18" s="55" t="n"/>
-      <c r="P18" s="55" t="n"/>
-      <c r="Q18" s="55" t="n"/>
-      <c r="R18" s="55" t="n"/>
-      <c r="S18" s="55" t="n"/>
-      <c r="T18" s="55" t="n"/>
-      <c r="U18" s="55" t="n"/>
-      <c r="V18" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W18" s="57" t="n"/>
+      <c r="O18" s="51" t="n"/>
+      <c r="P18" s="51" t="n"/>
+      <c r="Q18" s="51" t="n"/>
+      <c r="R18" s="51" t="n"/>
+      <c r="S18" s="51" t="n"/>
+      <c r="T18" s="51" t="n"/>
+      <c r="U18" s="51" t="n"/>
+      <c r="V18" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W18" s="58" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B19" s="45" t="n"/>
-      <c r="C19" s="46" t="n"/>
-      <c r="D19" s="46" t="n"/>
+      <c r="C19" s="53" t="n"/>
+      <c r="D19" s="53" t="n"/>
       <c r="E19" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F19" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G19" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G19" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H19" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J19" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K19" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L19" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N19" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O19" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P19" s="51" t="n"/>
-      <c r="Q19" s="51" t="n"/>
-      <c r="R19" s="51" t="n"/>
-      <c r="S19" s="51" t="n"/>
-      <c r="T19" s="51" t="n"/>
-      <c r="U19" s="51" t="n"/>
-      <c r="V19" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W19" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M19" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N19" s="55" t="n"/>
+      <c r="O19" s="55" t="n"/>
+      <c r="P19" s="55" t="n"/>
+      <c r="Q19" s="55" t="n"/>
+      <c r="R19" s="55" t="n"/>
+      <c r="S19" s="55" t="n"/>
+      <c r="T19" s="55" t="n"/>
+      <c r="U19" s="55" t="n"/>
+      <c r="V19" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W19" s="57" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B20" s="45" t="n"/>
-      <c r="C20" s="53" t="n"/>
-      <c r="D20" s="53" t="n"/>
+      <c r="C20" s="46" t="n"/>
+      <c r="D20" s="46" t="n"/>
       <c r="E20" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F20" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G20" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G20" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H20" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J20" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K20" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L20" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M20" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N20" s="55" t="inlineStr">
+      <c r="M20" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N20" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O20" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O20" s="55" t="n"/>
-      <c r="P20" s="55" t="n"/>
-      <c r="Q20" s="55" t="n"/>
-      <c r="R20" s="55" t="n"/>
-      <c r="S20" s="55" t="n"/>
-      <c r="T20" s="55" t="n"/>
-      <c r="U20" s="55" t="n"/>
-      <c r="V20" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W20" s="57" t="n"/>
+      <c r="P20" s="51" t="n"/>
+      <c r="Q20" s="51" t="n"/>
+      <c r="R20" s="51" t="n"/>
+      <c r="S20" s="51" t="n"/>
+      <c r="T20" s="51" t="n"/>
+      <c r="U20" s="51" t="n"/>
+      <c r="V20" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W20" s="58" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="46" t="n"/>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="53" t="n"/>
       <c r="E21" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F21" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G21" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H21" s="49" t="n">
         <v>2</v>
@@ -2938,208 +2934,218 @@
         <v>2</v>
       </c>
       <c r="J21" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K21" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L21" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M21" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M21" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N21" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N21" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O21" s="51" t="n"/>
-      <c r="P21" s="51" t="n"/>
-      <c r="Q21" s="51" t="n"/>
-      <c r="R21" s="51" t="n"/>
-      <c r="S21" s="51" t="n"/>
-      <c r="T21" s="51" t="n"/>
-      <c r="U21" s="51" t="n"/>
-      <c r="V21" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W21" s="58" t="n"/>
+      <c r="O21" s="55" t="n"/>
+      <c r="P21" s="55" t="n"/>
+      <c r="Q21" s="55" t="n"/>
+      <c r="R21" s="55" t="n"/>
+      <c r="S21" s="55" t="n"/>
+      <c r="T21" s="55" t="n"/>
+      <c r="U21" s="55" t="n"/>
+      <c r="V21" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W21" s="57" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="53" t="n"/>
+      <c r="C22" s="46" t="n"/>
+      <c r="D22" s="46" t="n"/>
       <c r="E22" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G22" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H22" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K22" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L22" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M22" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M22" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N22" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N22" s="55" t="n"/>
-      <c r="O22" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P22" s="55" t="n"/>
-      <c r="Q22" s="55" t="n"/>
-      <c r="R22" s="55" t="n"/>
-      <c r="S22" s="55" t="n"/>
-      <c r="T22" s="55" t="n"/>
-      <c r="U22" s="55" t="n"/>
-      <c r="V22" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W22" s="57" t="n"/>
+      <c r="O22" s="51" t="n"/>
+      <c r="P22" s="51" t="n"/>
+      <c r="Q22" s="51" t="n"/>
+      <c r="R22" s="51" t="n"/>
+      <c r="S22" s="51" t="n"/>
+      <c r="T22" s="51" t="n"/>
+      <c r="U22" s="51" t="n"/>
+      <c r="V22" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W22" s="58" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="46" t="n"/>
-      <c r="D23" s="46" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G23" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G23" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H23" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L23" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M23" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N23" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O23" s="51" t="n"/>
-      <c r="P23" s="51" t="n"/>
-      <c r="Q23" s="51" t="n"/>
-      <c r="R23" s="51" t="n"/>
-      <c r="S23" s="51" t="n"/>
-      <c r="T23" s="51" t="n"/>
-      <c r="U23" s="51" t="n"/>
-      <c r="V23" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W23" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M23" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N23" s="55" t="n"/>
+      <c r="O23" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P23" s="55" t="n"/>
+      <c r="Q23" s="55" t="n"/>
+      <c r="R23" s="55" t="n"/>
+      <c r="S23" s="55" t="n"/>
+      <c r="T23" s="55" t="n"/>
+      <c r="U23" s="55" t="n"/>
+      <c r="V23" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W23" s="57" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
+      <c r="C24" s="46" t="n"/>
+      <c r="D24" s="46" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G24" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G24" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H24" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L24" s="50" t="n"/>
-      <c r="M24" s="55" t="n"/>
-      <c r="N24" s="55" t="n"/>
-      <c r="O24" s="55" t="n"/>
-      <c r="P24" s="55" t="n"/>
-      <c r="Q24" s="55" t="n"/>
-      <c r="R24" s="55" t="n"/>
-      <c r="S24" s="55" t="n"/>
-      <c r="T24" s="55" t="n"/>
-      <c r="U24" s="55" t="n"/>
-      <c r="V24" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W24" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L24" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M24" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N24" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O24" s="51" t="n"/>
+      <c r="P24" s="51" t="n"/>
+      <c r="Q24" s="51" t="n"/>
+      <c r="R24" s="51" t="n"/>
+      <c r="S24" s="51" t="n"/>
+      <c r="T24" s="51" t="n"/>
+      <c r="U24" s="51" t="n"/>
+      <c r="V24" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W24" s="58" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="46" t="n"/>
-      <c r="D25" s="46" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G25" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H25" s="49" t="n">
         <v>0</v>
@@ -3148,43 +3154,43 @@
         <v>0</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L25" s="50" t="n"/>
-      <c r="M25" s="51" t="n"/>
-      <c r="N25" s="51" t="n"/>
-      <c r="O25" s="51" t="n"/>
-      <c r="P25" s="51" t="n"/>
-      <c r="Q25" s="51" t="n"/>
-      <c r="R25" s="51" t="n"/>
-      <c r="S25" s="51" t="n"/>
-      <c r="T25" s="51" t="n"/>
-      <c r="U25" s="51" t="n"/>
-      <c r="V25" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W25" s="58" t="n"/>
+      <c r="M25" s="55" t="n"/>
+      <c r="N25" s="55" t="n"/>
+      <c r="O25" s="55" t="n"/>
+      <c r="P25" s="55" t="n"/>
+      <c r="Q25" s="55" t="n"/>
+      <c r="R25" s="55" t="n"/>
+      <c r="S25" s="55" t="n"/>
+      <c r="T25" s="55" t="n"/>
+      <c r="U25" s="55" t="n"/>
+      <c r="V25" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W25" s="57" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="53" t="n"/>
-      <c r="D26" s="53" t="n"/>
+      <c r="C26" s="46" t="n"/>
+      <c r="D26" s="46" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G26" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H26" s="49" t="n">
         <v>0</v>
@@ -3193,43 +3199,43 @@
         <v>0</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L26" s="50" t="n"/>
-      <c r="M26" s="55" t="n"/>
-      <c r="N26" s="55" t="n"/>
-      <c r="O26" s="55" t="n"/>
-      <c r="P26" s="55" t="n"/>
-      <c r="Q26" s="55" t="n"/>
-      <c r="R26" s="55" t="n"/>
-      <c r="S26" s="55" t="n"/>
-      <c r="T26" s="55" t="n"/>
-      <c r="U26" s="55" t="n"/>
-      <c r="V26" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W26" s="57" t="n"/>
+      <c r="M26" s="51" t="n"/>
+      <c r="N26" s="51" t="n"/>
+      <c r="O26" s="51" t="n"/>
+      <c r="P26" s="51" t="n"/>
+      <c r="Q26" s="51" t="n"/>
+      <c r="R26" s="51" t="n"/>
+      <c r="S26" s="51" t="n"/>
+      <c r="T26" s="51" t="n"/>
+      <c r="U26" s="51" t="n"/>
+      <c r="V26" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W26" s="58" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="46" t="n"/>
-      <c r="D27" s="46" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G27" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G27" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H27" s="49" t="n">
         <v>0</v>
@@ -3238,43 +3244,43 @@
         <v>0</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L27" s="50" t="n"/>
-      <c r="M27" s="51" t="n"/>
-      <c r="N27" s="51" t="n"/>
-      <c r="O27" s="51" t="n"/>
-      <c r="P27" s="51" t="n"/>
-      <c r="Q27" s="51" t="n"/>
-      <c r="R27" s="51" t="n"/>
-      <c r="S27" s="51" t="n"/>
-      <c r="T27" s="51" t="n"/>
-      <c r="U27" s="51" t="n"/>
-      <c r="V27" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W27" s="58" t="n"/>
+      <c r="M27" s="55" t="n"/>
+      <c r="N27" s="55" t="n"/>
+      <c r="O27" s="55" t="n"/>
+      <c r="P27" s="55" t="n"/>
+      <c r="Q27" s="55" t="n"/>
+      <c r="R27" s="55" t="n"/>
+      <c r="S27" s="55" t="n"/>
+      <c r="T27" s="55" t="n"/>
+      <c r="U27" s="55" t="n"/>
+      <c r="V27" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W27" s="57" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="53" t="n"/>
-      <c r="D28" s="53" t="n"/>
+      <c r="C28" s="46" t="n"/>
+      <c r="D28" s="46" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G28" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H28" s="49" t="n">
         <v>0</v>
@@ -3283,43 +3289,43 @@
         <v>0</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L28" s="50" t="n"/>
-      <c r="M28" s="55" t="n"/>
-      <c r="N28" s="55" t="n"/>
-      <c r="O28" s="55" t="n"/>
-      <c r="P28" s="55" t="n"/>
-      <c r="Q28" s="55" t="n"/>
-      <c r="R28" s="55" t="n"/>
-      <c r="S28" s="55" t="n"/>
-      <c r="T28" s="55" t="n"/>
-      <c r="U28" s="55" t="n"/>
-      <c r="V28" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W28" s="57" t="n"/>
+      <c r="M28" s="51" t="n"/>
+      <c r="N28" s="51" t="n"/>
+      <c r="O28" s="51" t="n"/>
+      <c r="P28" s="51" t="n"/>
+      <c r="Q28" s="51" t="n"/>
+      <c r="R28" s="51" t="n"/>
+      <c r="S28" s="51" t="n"/>
+      <c r="T28" s="51" t="n"/>
+      <c r="U28" s="51" t="n"/>
+      <c r="V28" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W28" s="58" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="46" t="n"/>
-      <c r="D29" s="46" t="n"/>
+      <c r="C29" s="53" t="n"/>
+      <c r="D29" s="53" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G29" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H29" s="49" t="n">
         <v>0</v>
@@ -3328,1371 +3334,1375 @@
         <v>0</v>
       </c>
       <c r="J29" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L29" s="50" t="n"/>
-      <c r="M29" s="51" t="n"/>
-      <c r="N29" s="51" t="n"/>
-      <c r="O29" s="51" t="n"/>
-      <c r="P29" s="51" t="n"/>
-      <c r="Q29" s="51" t="n"/>
-      <c r="R29" s="51" t="n"/>
-      <c r="S29" s="51" t="n"/>
-      <c r="T29" s="51" t="n"/>
-      <c r="U29" s="51" t="n"/>
-      <c r="V29" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W29" s="58" t="n"/>
+      <c r="M29" s="55" t="n"/>
+      <c r="N29" s="55" t="n"/>
+      <c r="O29" s="55" t="n"/>
+      <c r="P29" s="55" t="n"/>
+      <c r="Q29" s="55" t="n"/>
+      <c r="R29" s="55" t="n"/>
+      <c r="S29" s="55" t="n"/>
+      <c r="T29" s="55" t="n"/>
+      <c r="U29" s="55" t="n"/>
+      <c r="V29" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W29" s="57" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="53" t="n"/>
-      <c r="D30" s="53" t="n"/>
+      <c r="C30" s="46" t="n"/>
+      <c r="D30" s="46" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G30" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H30" s="49" t="n"/>
-      <c r="I30" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G30" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H30" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J30" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L30" s="50" t="n"/>
-      <c r="M30" s="55" t="n"/>
-      <c r="N30" s="55" t="n"/>
-      <c r="O30" s="55" t="n"/>
-      <c r="P30" s="55" t="n"/>
-      <c r="Q30" s="55" t="n"/>
-      <c r="R30" s="55" t="n"/>
-      <c r="S30" s="55" t="n"/>
-      <c r="T30" s="55" t="n"/>
-      <c r="U30" s="55" t="n"/>
-      <c r="V30" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W30" s="57" t="n"/>
+      <c r="M30" s="51" t="n"/>
+      <c r="N30" s="51" t="n"/>
+      <c r="O30" s="51" t="n"/>
+      <c r="P30" s="51" t="n"/>
+      <c r="Q30" s="51" t="n"/>
+      <c r="R30" s="51" t="n"/>
+      <c r="S30" s="51" t="n"/>
+      <c r="T30" s="51" t="n"/>
+      <c r="U30" s="51" t="n"/>
+      <c r="V30" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W30" s="58" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="46" t="n"/>
-      <c r="D31" s="46" t="n"/>
+      <c r="C31" s="53" t="n"/>
+      <c r="D31" s="53" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G31" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H31" s="49" t="n"/>
       <c r="I31" s="49" t="n"/>
       <c r="J31" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L31" s="50" t="n"/>
-      <c r="M31" s="51" t="n"/>
-      <c r="N31" s="51" t="n"/>
-      <c r="O31" s="51" t="n"/>
-      <c r="P31" s="51" t="n"/>
-      <c r="Q31" s="51" t="n"/>
-      <c r="R31" s="51" t="n"/>
-      <c r="S31" s="51" t="n"/>
-      <c r="T31" s="51" t="n"/>
-      <c r="U31" s="51" t="n"/>
-      <c r="V31" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W31" s="58" t="n"/>
+      <c r="M31" s="55" t="n"/>
+      <c r="N31" s="55" t="n"/>
+      <c r="O31" s="55" t="n"/>
+      <c r="P31" s="55" t="n"/>
+      <c r="Q31" s="55" t="n"/>
+      <c r="R31" s="55" t="n"/>
+      <c r="S31" s="55" t="n"/>
+      <c r="T31" s="55" t="n"/>
+      <c r="U31" s="55" t="n"/>
+      <c r="V31" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W31" s="57" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="53" t="n"/>
-      <c r="D32" s="53" t="n"/>
+      <c r="C32" s="46" t="n"/>
+      <c r="D32" s="46" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G32" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H32" s="49" t="n"/>
       <c r="I32" s="49" t="n"/>
       <c r="J32" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L32" s="50" t="n"/>
-      <c r="M32" s="55" t="n"/>
-      <c r="N32" s="55" t="n"/>
-      <c r="O32" s="55" t="n"/>
-      <c r="P32" s="55" t="n"/>
-      <c r="Q32" s="55" t="n"/>
-      <c r="R32" s="55" t="n"/>
-      <c r="S32" s="55" t="n"/>
-      <c r="T32" s="55" t="n"/>
-      <c r="U32" s="55" t="n"/>
-      <c r="V32" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W32" s="57" t="n"/>
+      <c r="M32" s="51" t="n"/>
+      <c r="N32" s="51" t="n"/>
+      <c r="O32" s="51" t="n"/>
+      <c r="P32" s="51" t="n"/>
+      <c r="Q32" s="51" t="n"/>
+      <c r="R32" s="51" t="n"/>
+      <c r="S32" s="51" t="n"/>
+      <c r="T32" s="51" t="n"/>
+      <c r="U32" s="51" t="n"/>
+      <c r="V32" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W32" s="58" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="46" t="n"/>
-      <c r="D33" s="46" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G33" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H33" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I33" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H33" s="49" t="n"/>
+      <c r="I33" s="49" t="n"/>
       <c r="J33" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L33" s="50" t="n"/>
-      <c r="M33" s="51" t="n"/>
-      <c r="N33" s="51" t="n"/>
-      <c r="O33" s="51" t="n"/>
-      <c r="P33" s="51" t="n"/>
-      <c r="Q33" s="51" t="n"/>
-      <c r="R33" s="51" t="n"/>
-      <c r="S33" s="51" t="n"/>
-      <c r="T33" s="51" t="n"/>
-      <c r="U33" s="51" t="n"/>
-      <c r="V33" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W33" s="58" t="n"/>
+      <c r="M33" s="55" t="n"/>
+      <c r="N33" s="55" t="n"/>
+      <c r="O33" s="55" t="n"/>
+      <c r="P33" s="55" t="n"/>
+      <c r="Q33" s="55" t="n"/>
+      <c r="R33" s="55" t="n"/>
+      <c r="S33" s="55" t="n"/>
+      <c r="T33" s="55" t="n"/>
+      <c r="U33" s="55" t="n"/>
+      <c r="V33" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W33" s="57" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="53" t="n"/>
-      <c r="D34" s="53" t="n"/>
+      <c r="C34" s="46" t="n"/>
+      <c r="D34" s="46" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G34" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H34" s="49" t="n"/>
-      <c r="I34" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G34" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H34" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I34" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J34" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L34" s="50" t="n"/>
-      <c r="M34" s="55" t="n"/>
-      <c r="N34" s="55" t="n"/>
-      <c r="O34" s="55" t="n"/>
-      <c r="P34" s="55" t="n"/>
-      <c r="Q34" s="55" t="n"/>
-      <c r="R34" s="55" t="n"/>
-      <c r="S34" s="55" t="n"/>
-      <c r="T34" s="55" t="n"/>
-      <c r="U34" s="55" t="n"/>
-      <c r="V34" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W34" s="57" t="n"/>
+      <c r="M34" s="51" t="n"/>
+      <c r="N34" s="51" t="n"/>
+      <c r="O34" s="51" t="n"/>
+      <c r="P34" s="51" t="n"/>
+      <c r="Q34" s="51" t="n"/>
+      <c r="R34" s="51" t="n"/>
+      <c r="S34" s="51" t="n"/>
+      <c r="T34" s="51" t="n"/>
+      <c r="U34" s="51" t="n"/>
+      <c r="V34" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W34" s="58" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="46" t="n"/>
-      <c r="D35" s="46" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G35" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G35" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H35" s="49" t="n"/>
       <c r="I35" s="49" t="n"/>
       <c r="J35" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L35" s="50" t="n"/>
-      <c r="M35" s="51" t="n"/>
-      <c r="N35" s="51" t="n"/>
-      <c r="O35" s="51" t="n"/>
-      <c r="P35" s="51" t="n"/>
-      <c r="Q35" s="51" t="n"/>
-      <c r="R35" s="51" t="n"/>
-      <c r="S35" s="51" t="n"/>
-      <c r="T35" s="51" t="n"/>
-      <c r="U35" s="51" t="n"/>
-      <c r="V35" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W35" s="58" t="n"/>
+      <c r="M35" s="55" t="n"/>
+      <c r="N35" s="55" t="n"/>
+      <c r="O35" s="55" t="n"/>
+      <c r="P35" s="55" t="n"/>
+      <c r="Q35" s="55" t="n"/>
+      <c r="R35" s="55" t="n"/>
+      <c r="S35" s="55" t="n"/>
+      <c r="T35" s="55" t="n"/>
+      <c r="U35" s="55" t="n"/>
+      <c r="V35" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W35" s="57" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
+      <c r="C36" s="46" t="n"/>
+      <c r="D36" s="46" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G36" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G36" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H36" s="49" t="n"/>
       <c r="I36" s="49" t="n"/>
       <c r="J36" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K36" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K36" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="55" t="n"/>
-      <c r="N36" s="55" t="n"/>
-      <c r="O36" s="55" t="n"/>
-      <c r="P36" s="55" t="n"/>
-      <c r="Q36" s="55" t="n"/>
-      <c r="R36" s="55" t="n"/>
-      <c r="S36" s="55" t="n"/>
-      <c r="T36" s="55" t="n"/>
-      <c r="U36" s="55" t="n"/>
-      <c r="V36" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W36" s="57" t="n"/>
+      <c r="M36" s="51" t="n"/>
+      <c r="N36" s="51" t="n"/>
+      <c r="O36" s="51" t="n"/>
+      <c r="P36" s="51" t="n"/>
+      <c r="Q36" s="51" t="n"/>
+      <c r="R36" s="51" t="n"/>
+      <c r="S36" s="51" t="n"/>
+      <c r="T36" s="51" t="n"/>
+      <c r="U36" s="51" t="n"/>
+      <c r="V36" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W36" s="58" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="46" t="n"/>
-      <c r="D37" s="46" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G37" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H37" s="49" t="n"/>
       <c r="I37" s="49" t="n"/>
       <c r="J37" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="51" t="n"/>
-      <c r="N37" s="51" t="n"/>
-      <c r="O37" s="51" t="n"/>
-      <c r="P37" s="51" t="n"/>
-      <c r="Q37" s="51" t="n"/>
-      <c r="R37" s="51" t="n"/>
-      <c r="S37" s="51" t="n"/>
-      <c r="T37" s="51" t="n"/>
-      <c r="U37" s="51" t="n"/>
-      <c r="V37" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W37" s="58" t="n"/>
+      <c r="M37" s="55" t="n"/>
+      <c r="N37" s="55" t="n"/>
+      <c r="O37" s="55" t="n"/>
+      <c r="P37" s="55" t="n"/>
+      <c r="Q37" s="55" t="n"/>
+      <c r="R37" s="55" t="n"/>
+      <c r="S37" s="55" t="n"/>
+      <c r="T37" s="55" t="n"/>
+      <c r="U37" s="55" t="n"/>
+      <c r="V37" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W37" s="57" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="53" t="n"/>
-      <c r="D38" s="53" t="n"/>
+      <c r="C38" s="46" t="n"/>
+      <c r="D38" s="46" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G38" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G38" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H38" s="49" t="n"/>
       <c r="I38" s="49" t="n"/>
       <c r="J38" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="55" t="n"/>
-      <c r="N38" s="55" t="n"/>
-      <c r="O38" s="55" t="n"/>
-      <c r="P38" s="55" t="n"/>
-      <c r="Q38" s="55" t="n"/>
-      <c r="R38" s="55" t="n"/>
-      <c r="S38" s="55" t="n"/>
-      <c r="T38" s="55" t="n"/>
-      <c r="U38" s="55" t="n"/>
-      <c r="V38" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W38" s="57" t="n"/>
+      <c r="M38" s="51" t="n"/>
+      <c r="N38" s="51" t="n"/>
+      <c r="O38" s="51" t="n"/>
+      <c r="P38" s="51" t="n"/>
+      <c r="Q38" s="51" t="n"/>
+      <c r="R38" s="51" t="n"/>
+      <c r="S38" s="51" t="n"/>
+      <c r="T38" s="51" t="n"/>
+      <c r="U38" s="51" t="n"/>
+      <c r="V38" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W38" s="58" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="46" t="n"/>
-      <c r="D39" s="46" t="n"/>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G39" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H39" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I39" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G39" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H39" s="49" t="n"/>
+      <c r="I39" s="49" t="n"/>
       <c r="J39" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="51" t="n"/>
-      <c r="N39" s="51" t="n"/>
-      <c r="O39" s="51" t="n"/>
-      <c r="P39" s="51" t="n"/>
-      <c r="Q39" s="51" t="n"/>
-      <c r="R39" s="51" t="n"/>
-      <c r="S39" s="51" t="n"/>
-      <c r="T39" s="51" t="n"/>
-      <c r="U39" s="51" t="n"/>
-      <c r="V39" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W39" s="58" t="n"/>
+      <c r="M39" s="55" t="n"/>
+      <c r="N39" s="55" t="n"/>
+      <c r="O39" s="55" t="n"/>
+      <c r="P39" s="55" t="n"/>
+      <c r="Q39" s="55" t="n"/>
+      <c r="R39" s="55" t="n"/>
+      <c r="S39" s="55" t="n"/>
+      <c r="T39" s="55" t="n"/>
+      <c r="U39" s="55" t="n"/>
+      <c r="V39" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W39" s="57" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="53" t="n"/>
-      <c r="D40" s="53" t="n"/>
+      <c r="C40" s="46" t="n"/>
+      <c r="D40" s="46" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G40" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H40" s="49" t="n"/>
-      <c r="I40" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H40" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I40" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J40" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="55" t="n"/>
-      <c r="N40" s="55" t="n"/>
-      <c r="O40" s="55" t="n"/>
-      <c r="P40" s="55" t="n"/>
-      <c r="Q40" s="55" t="n"/>
-      <c r="R40" s="55" t="n"/>
-      <c r="S40" s="55" t="n"/>
-      <c r="T40" s="55" t="n"/>
-      <c r="U40" s="55" t="n"/>
-      <c r="V40" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W40" s="57" t="n"/>
+      <c r="M40" s="51" t="n"/>
+      <c r="N40" s="51" t="n"/>
+      <c r="O40" s="51" t="n"/>
+      <c r="P40" s="51" t="n"/>
+      <c r="Q40" s="51" t="n"/>
+      <c r="R40" s="51" t="n"/>
+      <c r="S40" s="51" t="n"/>
+      <c r="T40" s="51" t="n"/>
+      <c r="U40" s="51" t="n"/>
+      <c r="V40" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W40" s="58" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="46" t="n"/>
-      <c r="D41" s="46" t="n"/>
+      <c r="C41" s="53" t="n"/>
+      <c r="D41" s="53" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G41" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H41" s="49" t="n"/>
       <c r="I41" s="49" t="n"/>
       <c r="J41" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="51" t="n"/>
-      <c r="N41" s="51" t="n"/>
-      <c r="O41" s="51" t="n"/>
-      <c r="P41" s="51" t="n"/>
-      <c r="Q41" s="51" t="n"/>
-      <c r="R41" s="51" t="n"/>
-      <c r="S41" s="51" t="n"/>
-      <c r="T41" s="51" t="n"/>
-      <c r="U41" s="51" t="n"/>
-      <c r="V41" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W41" s="58" t="n"/>
+      <c r="M41" s="55" t="n"/>
+      <c r="N41" s="55" t="n"/>
+      <c r="O41" s="55" t="n"/>
+      <c r="P41" s="55" t="n"/>
+      <c r="Q41" s="55" t="n"/>
+      <c r="R41" s="55" t="n"/>
+      <c r="S41" s="55" t="n"/>
+      <c r="T41" s="55" t="n"/>
+      <c r="U41" s="55" t="n"/>
+      <c r="V41" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W41" s="57" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="53" t="n"/>
-      <c r="D42" s="53" t="n"/>
+      <c r="C42" s="46" t="n"/>
+      <c r="D42" s="46" t="n"/>
       <c r="E42" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F42" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G42" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H42" s="49" t="n"/>
+      <c r="I42" s="49" t="n"/>
+      <c r="J42" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F42" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G42" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H42" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I42" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J42" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K42" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="55" t="n"/>
-      <c r="N42" s="55" t="n"/>
-      <c r="O42" s="55" t="n"/>
-      <c r="P42" s="55" t="n"/>
-      <c r="Q42" s="55" t="n"/>
-      <c r="R42" s="55" t="n"/>
-      <c r="S42" s="55" t="n"/>
-      <c r="T42" s="55" t="n"/>
-      <c r="U42" s="55" t="n"/>
-      <c r="V42" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W42" s="57" t="n"/>
+      <c r="M42" s="51" t="n"/>
+      <c r="N42" s="51" t="n"/>
+      <c r="O42" s="51" t="n"/>
+      <c r="P42" s="51" t="n"/>
+      <c r="Q42" s="51" t="n"/>
+      <c r="R42" s="51" t="n"/>
+      <c r="S42" s="51" t="n"/>
+      <c r="T42" s="51" t="n"/>
+      <c r="U42" s="51" t="n"/>
+      <c r="V42" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W42" s="58" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="46" t="n"/>
-      <c r="D43" s="46" t="n"/>
+      <c r="C43" s="53" t="n"/>
+      <c r="D43" s="53" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G43" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H43" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I43" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J43" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K43" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="51" t="n"/>
-      <c r="N43" s="51" t="n"/>
-      <c r="O43" s="51" t="n"/>
-      <c r="P43" s="51" t="n"/>
-      <c r="Q43" s="51" t="n"/>
-      <c r="R43" s="51" t="n"/>
-      <c r="S43" s="51" t="n"/>
-      <c r="T43" s="51" t="n"/>
-      <c r="U43" s="51" t="n"/>
-      <c r="V43" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W43" s="58" t="n"/>
+      <c r="M43" s="55" t="n"/>
+      <c r="N43" s="55" t="n"/>
+      <c r="O43" s="55" t="n"/>
+      <c r="P43" s="55" t="n"/>
+      <c r="Q43" s="55" t="n"/>
+      <c r="R43" s="55" t="n"/>
+      <c r="S43" s="55" t="n"/>
+      <c r="T43" s="55" t="n"/>
+      <c r="U43" s="55" t="n"/>
+      <c r="V43" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W43" s="57" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="53" t="n"/>
-      <c r="D44" s="53" t="n"/>
+      <c r="C44" s="46" t="n"/>
+      <c r="D44" s="46" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G44" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H44" s="49" t="n"/>
-      <c r="I44" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H44" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I44" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J44" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K44" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="55" t="n"/>
-      <c r="N44" s="55" t="n"/>
-      <c r="O44" s="55" t="n"/>
-      <c r="P44" s="55" t="n"/>
-      <c r="Q44" s="55" t="n"/>
-      <c r="R44" s="55" t="n"/>
-      <c r="S44" s="55" t="n"/>
-      <c r="T44" s="55" t="n"/>
-      <c r="U44" s="55" t="n"/>
-      <c r="V44" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W44" s="57" t="n"/>
+      <c r="M44" s="51" t="n"/>
+      <c r="N44" s="51" t="n"/>
+      <c r="O44" s="51" t="n"/>
+      <c r="P44" s="51" t="n"/>
+      <c r="Q44" s="51" t="n"/>
+      <c r="R44" s="51" t="n"/>
+      <c r="S44" s="51" t="n"/>
+      <c r="T44" s="51" t="n"/>
+      <c r="U44" s="51" t="n"/>
+      <c r="V44" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W44" s="58" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="46" t="n"/>
-      <c r="D45" s="46" t="n"/>
+      <c r="C45" s="53" t="n"/>
+      <c r="D45" s="53" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G45" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G45" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H45" s="49" t="n"/>
       <c r="I45" s="49" t="n"/>
       <c r="J45" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K45" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="51" t="n"/>
-      <c r="N45" s="51" t="n"/>
-      <c r="O45" s="51" t="n"/>
-      <c r="P45" s="51" t="n"/>
-      <c r="Q45" s="51" t="n"/>
-      <c r="R45" s="51" t="n"/>
-      <c r="S45" s="51" t="n"/>
-      <c r="T45" s="51" t="n"/>
-      <c r="U45" s="51" t="n"/>
-      <c r="V45" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W45" s="58" t="n"/>
+      <c r="M45" s="55" t="n"/>
+      <c r="N45" s="55" t="n"/>
+      <c r="O45" s="55" t="n"/>
+      <c r="P45" s="55" t="n"/>
+      <c r="Q45" s="55" t="n"/>
+      <c r="R45" s="55" t="n"/>
+      <c r="S45" s="55" t="n"/>
+      <c r="T45" s="55" t="n"/>
+      <c r="U45" s="55" t="n"/>
+      <c r="V45" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W45" s="57" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="53" t="n"/>
-      <c r="D46" s="53" t="n"/>
+      <c r="C46" s="46" t="n"/>
+      <c r="D46" s="46" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G46" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G46" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H46" s="49" t="n"/>
       <c r="I46" s="49" t="n"/>
       <c r="J46" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K46" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="55" t="n"/>
-      <c r="N46" s="55" t="n"/>
-      <c r="O46" s="55" t="n"/>
-      <c r="P46" s="55" t="n"/>
-      <c r="Q46" s="55" t="n"/>
-      <c r="R46" s="55" t="n"/>
-      <c r="S46" s="55" t="n"/>
-      <c r="T46" s="55" t="n"/>
-      <c r="U46" s="55" t="n"/>
-      <c r="V46" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W46" s="57" t="n"/>
+      <c r="M46" s="51" t="n"/>
+      <c r="N46" s="51" t="n"/>
+      <c r="O46" s="51" t="n"/>
+      <c r="P46" s="51" t="n"/>
+      <c r="Q46" s="51" t="n"/>
+      <c r="R46" s="51" t="n"/>
+      <c r="S46" s="51" t="n"/>
+      <c r="T46" s="51" t="n"/>
+      <c r="U46" s="51" t="n"/>
+      <c r="V46" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W46" s="58" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="46" t="n"/>
-      <c r="D47" s="46" t="n"/>
+      <c r="C47" s="53" t="n"/>
+      <c r="D47" s="53" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G47" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H47" s="49" t="n"/>
       <c r="I47" s="49" t="n"/>
       <c r="J47" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K47" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="51" t="n"/>
-      <c r="N47" s="51" t="n"/>
-      <c r="O47" s="51" t="n"/>
-      <c r="P47" s="51" t="n"/>
-      <c r="Q47" s="51" t="n"/>
-      <c r="R47" s="51" t="n"/>
-      <c r="S47" s="51" t="n"/>
-      <c r="T47" s="51" t="n"/>
-      <c r="U47" s="51" t="n"/>
-      <c r="V47" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W47" s="58" t="n"/>
+      <c r="M47" s="55" t="n"/>
+      <c r="N47" s="55" t="n"/>
+      <c r="O47" s="55" t="n"/>
+      <c r="P47" s="55" t="n"/>
+      <c r="Q47" s="55" t="n"/>
+      <c r="R47" s="55" t="n"/>
+      <c r="S47" s="55" t="n"/>
+      <c r="T47" s="55" t="n"/>
+      <c r="U47" s="55" t="n"/>
+      <c r="V47" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W47" s="57" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
+      <c r="C48" s="46" t="n"/>
+      <c r="D48" s="46" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G48" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G48" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H48" s="49" t="n"/>
       <c r="I48" s="49" t="n"/>
       <c r="J48" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K48" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="55" t="n"/>
-      <c r="N48" s="55" t="n"/>
-      <c r="O48" s="55" t="n"/>
-      <c r="P48" s="55" t="n"/>
-      <c r="Q48" s="55" t="n"/>
-      <c r="R48" s="55" t="n"/>
-      <c r="S48" s="55" t="n"/>
-      <c r="T48" s="55" t="n"/>
-      <c r="U48" s="55" t="n"/>
-      <c r="V48" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W48" s="57" t="n"/>
+      <c r="M48" s="51" t="n"/>
+      <c r="N48" s="51" t="n"/>
+      <c r="O48" s="51" t="n"/>
+      <c r="P48" s="51" t="n"/>
+      <c r="Q48" s="51" t="n"/>
+      <c r="R48" s="51" t="n"/>
+      <c r="S48" s="51" t="n"/>
+      <c r="T48" s="51" t="n"/>
+      <c r="U48" s="51" t="n"/>
+      <c r="V48" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W48" s="58" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="46" t="n"/>
-      <c r="D49" s="46" t="n"/>
+      <c r="C49" s="53" t="n"/>
+      <c r="D49" s="53" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G49" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G49" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H49" s="49" t="n"/>
       <c r="I49" s="49" t="n"/>
       <c r="J49" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K49" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="51" t="n"/>
-      <c r="N49" s="51" t="n"/>
-      <c r="O49" s="51" t="n"/>
-      <c r="P49" s="51" t="n"/>
-      <c r="Q49" s="51" t="n"/>
-      <c r="R49" s="51" t="n"/>
-      <c r="S49" s="51" t="n"/>
-      <c r="T49" s="51" t="n"/>
-      <c r="U49" s="51" t="n"/>
-      <c r="V49" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W49" s="58" t="n"/>
+      <c r="M49" s="55" t="n"/>
+      <c r="N49" s="55" t="n"/>
+      <c r="O49" s="55" t="n"/>
+      <c r="P49" s="55" t="n"/>
+      <c r="Q49" s="55" t="n"/>
+      <c r="R49" s="55" t="n"/>
+      <c r="S49" s="55" t="n"/>
+      <c r="T49" s="55" t="n"/>
+      <c r="U49" s="55" t="n"/>
+      <c r="V49" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W49" s="57" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="53" t="n"/>
-      <c r="D50" s="53" t="n"/>
+      <c r="C50" s="46" t="n"/>
+      <c r="D50" s="46" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G50" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G50" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="49" t="n"/>
       <c r="J50" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="55" t="n"/>
-      <c r="N50" s="55" t="n"/>
-      <c r="O50" s="55" t="n"/>
-      <c r="P50" s="55" t="n"/>
-      <c r="Q50" s="55" t="n"/>
-      <c r="R50" s="55" t="n"/>
-      <c r="S50" s="55" t="n"/>
-      <c r="T50" s="55" t="n"/>
-      <c r="U50" s="55" t="n"/>
-      <c r="V50" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W50" s="57" t="n"/>
+      <c r="M50" s="51" t="n"/>
+      <c r="N50" s="51" t="n"/>
+      <c r="O50" s="51" t="n"/>
+      <c r="P50" s="51" t="n"/>
+      <c r="Q50" s="51" t="n"/>
+      <c r="R50" s="51" t="n"/>
+      <c r="S50" s="51" t="n"/>
+      <c r="T50" s="51" t="n"/>
+      <c r="U50" s="51" t="n"/>
+      <c r="V50" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W50" s="58" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="46" t="n"/>
-      <c r="D51" s="46" t="n"/>
+      <c r="C51" s="53" t="n"/>
+      <c r="D51" s="53" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G51" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H51" s="49" t="n"/>
       <c r="I51" s="49" t="n"/>
       <c r="J51" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="51" t="n"/>
-      <c r="N51" s="51" t="n"/>
-      <c r="O51" s="51" t="n"/>
-      <c r="P51" s="51" t="n"/>
-      <c r="Q51" s="51" t="n"/>
-      <c r="R51" s="51" t="n"/>
-      <c r="S51" s="51" t="n"/>
-      <c r="T51" s="51" t="n"/>
-      <c r="U51" s="51" t="n"/>
-      <c r="V51" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W51" s="58" t="n"/>
+      <c r="M51" s="55" t="n"/>
+      <c r="N51" s="55" t="n"/>
+      <c r="O51" s="55" t="n"/>
+      <c r="P51" s="55" t="n"/>
+      <c r="Q51" s="55" t="n"/>
+      <c r="R51" s="55" t="n"/>
+      <c r="S51" s="55" t="n"/>
+      <c r="T51" s="55" t="n"/>
+      <c r="U51" s="55" t="n"/>
+      <c r="V51" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W51" s="57" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="53" t="n"/>
-      <c r="D52" s="53" t="n"/>
+      <c r="C52" s="46" t="n"/>
+      <c r="D52" s="46" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G52" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H52" s="49" t="n"/>
       <c r="I52" s="49" t="n"/>
       <c r="J52" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="55" t="n"/>
-      <c r="N52" s="55" t="n"/>
-      <c r="O52" s="55" t="n"/>
-      <c r="P52" s="55" t="n"/>
-      <c r="Q52" s="55" t="n"/>
-      <c r="R52" s="55" t="n"/>
-      <c r="S52" s="55" t="n"/>
-      <c r="T52" s="55" t="n"/>
-      <c r="U52" s="55" t="n"/>
-      <c r="V52" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W52" s="57" t="n"/>
+      <c r="M52" s="51" t="n"/>
+      <c r="N52" s="51" t="n"/>
+      <c r="O52" s="51" t="n"/>
+      <c r="P52" s="51" t="n"/>
+      <c r="Q52" s="51" t="n"/>
+      <c r="R52" s="51" t="n"/>
+      <c r="S52" s="51" t="n"/>
+      <c r="T52" s="51" t="n"/>
+      <c r="U52" s="51" t="n"/>
+      <c r="V52" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W52" s="58" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="46" t="n"/>
-      <c r="D53" s="46" t="n"/>
+      <c r="C53" s="53" t="n"/>
+      <c r="D53" s="53" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G53" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G53" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H53" s="49" t="n"/>
       <c r="I53" s="49" t="n"/>
       <c r="J53" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="51" t="n"/>
-      <c r="N53" s="51" t="n"/>
-      <c r="O53" s="51" t="n"/>
-      <c r="P53" s="51" t="n"/>
-      <c r="Q53" s="51" t="n"/>
-      <c r="R53" s="51" t="n"/>
-      <c r="S53" s="51" t="n"/>
-      <c r="T53" s="51" t="n"/>
-      <c r="U53" s="51" t="n"/>
-      <c r="V53" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W53" s="58" t="n"/>
+      <c r="M53" s="55" t="n"/>
+      <c r="N53" s="55" t="n"/>
+      <c r="O53" s="55" t="n"/>
+      <c r="P53" s="55" t="n"/>
+      <c r="Q53" s="55" t="n"/>
+      <c r="R53" s="55" t="n"/>
+      <c r="S53" s="55" t="n"/>
+      <c r="T53" s="55" t="n"/>
+      <c r="U53" s="55" t="n"/>
+      <c r="V53" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W53" s="57" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="53" t="n"/>
-      <c r="D54" s="53" t="n"/>
+      <c r="C54" s="46" t="n"/>
+      <c r="D54" s="46" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G54" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G54" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="55" t="n"/>
-      <c r="N54" s="55" t="n"/>
-      <c r="O54" s="55" t="n"/>
-      <c r="P54" s="55" t="n"/>
-      <c r="Q54" s="55" t="n"/>
-      <c r="R54" s="55" t="n"/>
-      <c r="S54" s="55" t="n"/>
-      <c r="T54" s="55" t="n"/>
-      <c r="U54" s="55" t="n"/>
-      <c r="V54" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W54" s="57" t="n"/>
+      <c r="M54" s="51" t="n"/>
+      <c r="N54" s="51" t="n"/>
+      <c r="O54" s="51" t="n"/>
+      <c r="P54" s="51" t="n"/>
+      <c r="Q54" s="51" t="n"/>
+      <c r="R54" s="51" t="n"/>
+      <c r="S54" s="51" t="n"/>
+      <c r="T54" s="51" t="n"/>
+      <c r="U54" s="51" t="n"/>
+      <c r="V54" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W54" s="58" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="46" t="n"/>
-      <c r="D55" s="46" t="n"/>
+      <c r="C55" s="53" t="n"/>
+      <c r="D55" s="53" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G55" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G55" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="51" t="n"/>
-      <c r="N55" s="51" t="n"/>
-      <c r="O55" s="51" t="n"/>
-      <c r="P55" s="51" t="n"/>
-      <c r="Q55" s="51" t="n"/>
-      <c r="R55" s="51" t="n"/>
-      <c r="S55" s="51" t="n"/>
-      <c r="T55" s="51" t="n"/>
-      <c r="U55" s="51" t="n"/>
-      <c r="V55" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W55" s="58" t="n"/>
+      <c r="M55" s="55" t="n"/>
+      <c r="N55" s="55" t="n"/>
+      <c r="O55" s="55" t="n"/>
+      <c r="P55" s="55" t="n"/>
+      <c r="Q55" s="55" t="n"/>
+      <c r="R55" s="55" t="n"/>
+      <c r="S55" s="55" t="n"/>
+      <c r="T55" s="55" t="n"/>
+      <c r="U55" s="55" t="n"/>
+      <c r="V55" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W55" s="57" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="53" t="n"/>
-      <c r="D56" s="53" t="n"/>
+      <c r="C56" s="46" t="n"/>
+      <c r="D56" s="46" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G56" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G56" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="55" t="n"/>
-      <c r="N56" s="55" t="n"/>
-      <c r="O56" s="55" t="n"/>
-      <c r="P56" s="55" t="n"/>
-      <c r="Q56" s="55" t="n"/>
-      <c r="R56" s="55" t="n"/>
-      <c r="S56" s="55" t="n"/>
-      <c r="T56" s="55" t="n"/>
-      <c r="U56" s="55" t="n"/>
-      <c r="V56" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W56" s="57" t="n"/>
+      <c r="M56" s="51" t="n"/>
+      <c r="N56" s="51" t="n"/>
+      <c r="O56" s="51" t="n"/>
+      <c r="P56" s="51" t="n"/>
+      <c r="Q56" s="51" t="n"/>
+      <c r="R56" s="51" t="n"/>
+      <c r="S56" s="51" t="n"/>
+      <c r="T56" s="51" t="n"/>
+      <c r="U56" s="51" t="n"/>
+      <c r="V56" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W56" s="58" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="46" t="n"/>
-      <c r="D57" s="46" t="n"/>
+      <c r="C57" s="53" t="n"/>
+      <c r="D57" s="53" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G57" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G57" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="51" t="n"/>
-      <c r="N57" s="51" t="n"/>
-      <c r="O57" s="51" t="n"/>
-      <c r="P57" s="51" t="n"/>
-      <c r="Q57" s="51" t="n"/>
-      <c r="R57" s="51" t="n"/>
-      <c r="S57" s="51" t="n"/>
-      <c r="T57" s="51" t="n"/>
-      <c r="U57" s="51" t="n"/>
-      <c r="V57" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W57" s="58" t="n"/>
+      <c r="M57" s="55" t="n"/>
+      <c r="N57" s="55" t="n"/>
+      <c r="O57" s="55" t="n"/>
+      <c r="P57" s="55" t="n"/>
+      <c r="Q57" s="55" t="n"/>
+      <c r="R57" s="55" t="n"/>
+      <c r="S57" s="55" t="n"/>
+      <c r="T57" s="55" t="n"/>
+      <c r="U57" s="55" t="n"/>
+      <c r="V57" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W57" s="57" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="53" t="n"/>
-      <c r="D58" s="53" t="n"/>
+      <c r="C58" s="46" t="n"/>
+      <c r="D58" s="46" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G58" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G58" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="55" t="n"/>
-      <c r="N58" s="55" t="n"/>
-      <c r="O58" s="55" t="n"/>
-      <c r="P58" s="55" t="n"/>
-      <c r="Q58" s="55" t="n"/>
-      <c r="R58" s="55" t="n"/>
-      <c r="S58" s="55" t="n"/>
-      <c r="T58" s="55" t="n"/>
-      <c r="U58" s="55" t="n"/>
-      <c r="V58" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W58" s="57" t="n"/>
+      <c r="M58" s="51" t="n"/>
+      <c r="N58" s="51" t="n"/>
+      <c r="O58" s="51" t="n"/>
+      <c r="P58" s="51" t="n"/>
+      <c r="Q58" s="51" t="n"/>
+      <c r="R58" s="51" t="n"/>
+      <c r="S58" s="51" t="n"/>
+      <c r="T58" s="51" t="n"/>
+      <c r="U58" s="51" t="n"/>
+      <c r="V58" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W58" s="58" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="46" t="n"/>
-      <c r="D59" s="46" t="n"/>
+      <c r="C59" s="53" t="n"/>
+      <c r="D59" s="53" t="n"/>
       <c r="E59" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F59" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G59" s="48" t="n">
-        <v>24</v>
+      <c r="G59" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="51" t="n"/>
-      <c r="N59" s="51" t="n"/>
-      <c r="O59" s="51" t="n"/>
-      <c r="P59" s="51" t="n"/>
-      <c r="Q59" s="51" t="n"/>
-      <c r="R59" s="51" t="n"/>
-      <c r="S59" s="51" t="n"/>
-      <c r="T59" s="51" t="n"/>
-      <c r="U59" s="51" t="n"/>
-      <c r="V59" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W59" s="58" t="n"/>
+      <c r="M59" s="55" t="n"/>
+      <c r="N59" s="55" t="n"/>
+      <c r="O59" s="55" t="n"/>
+      <c r="P59" s="55" t="n"/>
+      <c r="Q59" s="55" t="n"/>
+      <c r="R59" s="55" t="n"/>
+      <c r="S59" s="55" t="n"/>
+      <c r="T59" s="55" t="n"/>
+      <c r="U59" s="55" t="n"/>
+      <c r="V59" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W59" s="57" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
+      <c r="C60" s="46" t="n"/>
+      <c r="D60" s="46" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G60" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G60" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="55" t="n"/>
-      <c r="N60" s="55" t="n"/>
-      <c r="O60" s="55" t="n"/>
-      <c r="P60" s="55" t="n"/>
-      <c r="Q60" s="55" t="n"/>
-      <c r="R60" s="55" t="n"/>
-      <c r="S60" s="55" t="n"/>
-      <c r="T60" s="55" t="n"/>
-      <c r="U60" s="55" t="n"/>
-      <c r="V60" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W60" s="57" t="n"/>
+      <c r="M60" s="51" t="n"/>
+      <c r="N60" s="51" t="n"/>
+      <c r="O60" s="51" t="n"/>
+      <c r="P60" s="51" t="n"/>
+      <c r="Q60" s="51" t="n"/>
+      <c r="R60" s="51" t="n"/>
+      <c r="S60" s="51" t="n"/>
+      <c r="T60" s="51" t="n"/>
+      <c r="U60" s="51" t="n"/>
+      <c r="V60" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W60" s="58" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="46" t="n"/>
-      <c r="D61" s="46" t="n"/>
+      <c r="C61" s="53" t="n"/>
+      <c r="D61" s="53" t="n"/>
       <c r="E61" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F61" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G61" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G61" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
       <c r="J61" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K61" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="51" t="n"/>
-      <c r="N61" s="51" t="n"/>
-      <c r="O61" s="51" t="n"/>
-      <c r="P61" s="51" t="n"/>
-      <c r="Q61" s="51" t="n"/>
-      <c r="R61" s="51" t="n"/>
-      <c r="S61" s="51" t="n"/>
-      <c r="T61" s="51" t="n"/>
-      <c r="U61" s="51" t="n"/>
-      <c r="V61" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W61" s="58" t="n"/>
+      <c r="M61" s="55" t="n"/>
+      <c r="N61" s="55" t="n"/>
+      <c r="O61" s="55" t="n"/>
+      <c r="P61" s="55" t="n"/>
+      <c r="Q61" s="55" t="n"/>
+      <c r="R61" s="55" t="n"/>
+      <c r="S61" s="55" t="n"/>
+      <c r="T61" s="55" t="n"/>
+      <c r="U61" s="55" t="n"/>
+      <c r="V61" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W61" s="57" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B62" s="45" t="n"/>
-      <c r="C62" s="53" t="n"/>
-      <c r="D62" s="53" t="n"/>
+      <c r="C62" s="46" t="n"/>
+      <c r="D62" s="46" t="n"/>
       <c r="E62" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F62" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G62" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="49" t="n"/>
@@ -4700,51 +4710,92 @@
         <v>59</v>
       </c>
       <c r="K62" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L62" s="50" t="n"/>
-      <c r="M62" s="55" t="n"/>
-      <c r="N62" s="55" t="n"/>
-      <c r="O62" s="55" t="n"/>
-      <c r="P62" s="55" t="n"/>
-      <c r="Q62" s="55" t="n"/>
-      <c r="R62" s="55" t="n"/>
-      <c r="S62" s="55" t="n"/>
-      <c r="T62" s="55" t="n"/>
-      <c r="U62" s="55" t="n"/>
-      <c r="V62" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W62" s="57" t="n"/>
+      <c r="M62" s="51" t="n"/>
+      <c r="N62" s="51" t="n"/>
+      <c r="O62" s="51" t="n"/>
+      <c r="P62" s="51" t="n"/>
+      <c r="Q62" s="51" t="n"/>
+      <c r="R62" s="51" t="n"/>
+      <c r="S62" s="51" t="n"/>
+      <c r="T62" s="51" t="n"/>
+      <c r="U62" s="51" t="n"/>
+      <c r="V62" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W62" s="58" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B63" s="45" t="n"/>
-      <c r="C63" s="46" t="n"/>
-      <c r="D63" s="46" t="n"/>
-      <c r="E63" s="47" t="n"/>
-      <c r="F63" s="47" t="n"/>
-      <c r="G63" s="60" t="n"/>
+      <c r="C63" s="53" t="n"/>
+      <c r="D63" s="53" t="n"/>
+      <c r="E63" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F63" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G63" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="49" t="n"/>
-      <c r="J63" s="50" t="n"/>
-      <c r="K63" s="50" t="n"/>
+      <c r="J63" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K63" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L63" s="50" t="n"/>
-      <c r="M63" s="51" t="n"/>
-      <c r="N63" s="51" t="n"/>
-      <c r="O63" s="51" t="n"/>
-      <c r="P63" s="51" t="n"/>
-      <c r="Q63" s="51" t="n"/>
-      <c r="R63" s="51" t="n"/>
-      <c r="S63" s="51" t="n"/>
-      <c r="T63" s="51" t="n"/>
-      <c r="U63" s="51" t="n"/>
-      <c r="V63" s="61" t="n"/>
-      <c r="W63" s="61" t="n"/>
+      <c r="M63" s="55" t="n"/>
+      <c r="N63" s="55" t="n"/>
+      <c r="O63" s="55" t="n"/>
+      <c r="P63" s="55" t="n"/>
+      <c r="Q63" s="55" t="n"/>
+      <c r="R63" s="55" t="n"/>
+      <c r="S63" s="55" t="n"/>
+      <c r="T63" s="55" t="n"/>
+      <c r="U63" s="55" t="n"/>
+      <c r="V63" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W63" s="57" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B64" s="45" t="n"/>
+      <c r="C64" s="46" t="n"/>
+      <c r="D64" s="46" t="n"/>
+      <c r="E64" s="47" t="n"/>
+      <c r="F64" s="47" t="n"/>
+      <c r="G64" s="60" t="n"/>
+      <c r="H64" s="49" t="n"/>
+      <c r="I64" s="49" t="n"/>
+      <c r="J64" s="50" t="n"/>
+      <c r="K64" s="50" t="n"/>
+      <c r="L64" s="50" t="n"/>
+      <c r="M64" s="51" t="n"/>
+      <c r="N64" s="51" t="n"/>
+      <c r="O64" s="51" t="n"/>
+      <c r="P64" s="51" t="n"/>
+      <c r="Q64" s="51" t="n"/>
+      <c r="R64" s="51" t="n"/>
+      <c r="S64" s="51" t="n"/>
+      <c r="T64" s="51" t="n"/>
+      <c r="U64" s="51" t="n"/>
+      <c r="V64" s="61" t="n"/>
+      <c r="W64" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W64"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,58 +1982,62 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/06(一)</t>
+          <t>2026/04/07(二)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>36</v>
-      </c>
-      <c r="G4" s="71" t="n">
-        <v>25</v>
+        <v>93</v>
+      </c>
+      <c r="G4" s="66" t="n">
+        <v>21.8</v>
       </c>
       <c r="H4" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I4" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J4" s="68" t="n">
+        <v>7</v>
+      </c>
+      <c r="K4" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="L4" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K4" s="68" t="n">
-        <v>32</v>
-      </c>
-      <c r="L4" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" s="69" t="inlineStr"/>
+      <c r="M4" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信、新能泰山</t>
+        </is>
+      </c>
       <c r="N4" s="69" t="inlineStr"/>
       <c r="O4" s="69" t="inlineStr"/>
-      <c r="P4" s="69" t="inlineStr">
+      <c r="P4" s="69" t="inlineStr"/>
+      <c r="Q4" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="Q4" s="69" t="inlineStr"/>
       <c r="R4" s="69" t="inlineStr"/>
       <c r="S4" s="69" t="inlineStr"/>
       <c r="T4" s="69" t="inlineStr"/>
       <c r="U4" s="69" t="inlineStr"/>
       <c r="V4" s="69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W4" s="69" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/03(五)</t>
+          <t>2026/04/06(一)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
@@ -2077,105 +2081,105 @@
       <c r="T5" s="69" t="inlineStr"/>
       <c r="U5" s="69" t="inlineStr"/>
       <c r="V5" s="69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W5" s="69" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
       <c r="C6" s="64" t="inlineStr"/>
       <c r="D6" s="64" t="inlineStr"/>
       <c r="E6" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G6" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H6" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I6" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J6" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K6" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L6" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M6" s="69" t="inlineStr"/>
       <c r="N6" s="69" t="inlineStr"/>
-      <c r="O6" s="69" t="inlineStr">
+      <c r="O6" s="69" t="inlineStr"/>
+      <c r="P6" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P6" s="69" t="inlineStr"/>
       <c r="Q6" s="69" t="inlineStr"/>
       <c r="R6" s="69" t="inlineStr"/>
       <c r="S6" s="69" t="inlineStr"/>
       <c r="T6" s="69" t="inlineStr"/>
       <c r="U6" s="69" t="inlineStr"/>
       <c r="V6" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W6" s="69" t="inlineStr"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="64" t="inlineStr"/>
       <c r="D7" s="64" t="inlineStr"/>
       <c r="E7" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F7" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G7" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G7" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H7" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I7" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K7" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L7" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" s="69" t="inlineStr"/>
-      <c r="N7" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M7" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N7" s="69" t="inlineStr"/>
+      <c r="O7" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O7" s="69" t="inlineStr"/>
       <c r="P7" s="69" t="inlineStr"/>
       <c r="Q7" s="69" t="inlineStr"/>
       <c r="R7" s="69" t="inlineStr"/>
@@ -2183,51 +2187,47 @@
       <c r="T7" s="69" t="inlineStr"/>
       <c r="U7" s="69" t="inlineStr"/>
       <c r="V7" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W7" s="69" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B8" s="63" t="inlineStr"/>
       <c r="C8" s="64" t="inlineStr"/>
       <c r="D8" s="64" t="inlineStr"/>
       <c r="E8" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F8" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G8" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G8" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H8" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I8" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J8" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K8" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L8" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M8" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M8" s="69" t="inlineStr"/>
+      <c r="N8" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N8" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O8" s="69" t="inlineStr"/>
@@ -2238,254 +2238,250 @@
       <c r="T8" s="69" t="inlineStr"/>
       <c r="U8" s="69" t="inlineStr"/>
       <c r="V8" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W8" s="69" t="inlineStr"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B9" s="63" t="inlineStr"/>
+      <c r="C9" s="64" t="inlineStr"/>
+      <c r="D9" s="64" t="inlineStr"/>
+      <c r="E9" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F9" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G9" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H9" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L9" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N9" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O9" s="69" t="inlineStr"/>
+      <c r="P9" s="69" t="inlineStr"/>
+      <c r="Q9" s="69" t="inlineStr"/>
+      <c r="R9" s="69" t="inlineStr"/>
+      <c r="S9" s="69" t="inlineStr"/>
+      <c r="T9" s="69" t="inlineStr"/>
+      <c r="U9" s="69" t="inlineStr"/>
+      <c r="V9" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="69" t="inlineStr"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="W9" s="69" t="inlineStr"/>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D9" s="38" t="inlineStr">
+      <c r="D10" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E9" s="39" t="n">
+      <c r="E10" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F9" s="39" t="n">
+      <c r="F10" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G9" s="40" t="n">
+      <c r="G10" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H9" s="41" t="n">
+      <c r="H10" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I9" s="41" t="n">
+      <c r="I10" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J9" s="42" t="n">
+      <c r="J10" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K9" s="42" t="n">
+      <c r="K10" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L9" s="42" t="n">
+      <c r="L10" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M9" s="43" t="inlineStr">
+      <c r="M10" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N9" s="43" t="inlineStr"/>
-      <c r="O9" s="43" t="inlineStr">
+      <c r="N10" s="43" t="inlineStr"/>
+      <c r="O10" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P9" s="43" t="inlineStr"/>
-      <c r="Q9" s="43" t="inlineStr"/>
-      <c r="R9" s="43" t="inlineStr"/>
-      <c r="S9" s="43" t="inlineStr"/>
-      <c r="T9" s="43" t="inlineStr"/>
-      <c r="U9" s="43" t="inlineStr"/>
-      <c r="V9" s="43" t="n">
+      <c r="P10" s="43" t="inlineStr"/>
+      <c r="Q10" s="43" t="inlineStr"/>
+      <c r="R10" s="43" t="inlineStr"/>
+      <c r="S10" s="43" t="inlineStr"/>
+      <c r="T10" s="43" t="inlineStr"/>
+      <c r="U10" s="43" t="inlineStr"/>
+      <c r="V10" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W9" s="43" t="inlineStr"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="n"/>
-      <c r="C10" s="46" t="n"/>
-      <c r="D10" s="46" t="n"/>
-      <c r="E10" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F10" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G10" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H10" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L10" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M10" s="51" t="n"/>
-      <c r="N10" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O10" s="51" t="n"/>
-      <c r="P10" s="51" t="n"/>
-      <c r="Q10" s="51" t="n"/>
-      <c r="R10" s="51" t="n"/>
-      <c r="S10" s="51" t="n"/>
-      <c r="T10" s="51" t="n"/>
-      <c r="U10" s="51" t="n"/>
-      <c r="V10" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W10" s="43" t="inlineStr"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B11" s="45" t="n"/>
-      <c r="C11" s="53" t="n"/>
-      <c r="D11" s="53" t="n"/>
+      <c r="C11" s="46" t="n"/>
+      <c r="D11" s="46" t="n"/>
       <c r="E11" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F11" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G11" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G11" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H11" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I11" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J11" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K11" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L11" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M11" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N11" s="55" t="n"/>
-      <c r="O11" s="55" t="n"/>
-      <c r="P11" s="55" t="n"/>
-      <c r="Q11" s="55" t="n"/>
-      <c r="R11" s="55" t="n"/>
-      <c r="S11" s="55" t="n"/>
-      <c r="T11" s="55" t="n"/>
-      <c r="U11" s="55" t="n"/>
-      <c r="V11" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W11" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M11" s="51" t="n"/>
+      <c r="N11" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O11" s="51" t="n"/>
+      <c r="P11" s="51" t="n"/>
+      <c r="Q11" s="51" t="n"/>
+      <c r="R11" s="51" t="n"/>
+      <c r="S11" s="51" t="n"/>
+      <c r="T11" s="51" t="n"/>
+      <c r="U11" s="51" t="n"/>
+      <c r="V11" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B12" s="45" t="n"/>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
+      <c r="C12" s="53" t="n"/>
+      <c r="D12" s="53" t="n"/>
       <c r="E12" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F12" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G12" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G12" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H12" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I12" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J12" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K12" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L12" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M12" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N12" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O12" s="51" t="n"/>
-      <c r="P12" s="51" t="n"/>
-      <c r="Q12" s="51" t="n"/>
-      <c r="R12" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S12" s="51" t="n"/>
-      <c r="T12" s="51" t="n"/>
-      <c r="U12" s="51" t="n"/>
-      <c r="V12" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W12" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M12" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N12" s="55" t="n"/>
+      <c r="O12" s="55" t="n"/>
+      <c r="P12" s="55" t="n"/>
+      <c r="Q12" s="55" t="n"/>
+      <c r="R12" s="55" t="n"/>
+      <c r="S12" s="55" t="n"/>
+      <c r="T12" s="55" t="n"/>
+      <c r="U12" s="55" t="n"/>
+      <c r="V12" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W12" s="57" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B13" s="45" t="n"/>
-      <c r="C13" s="53" t="n"/>
-      <c r="D13" s="53" t="n"/>
+      <c r="C13" s="46" t="n"/>
+      <c r="D13" s="46" t="n"/>
       <c r="E13" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F13" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G13" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H13" s="49" t="n">
         <v>1</v>
@@ -2494,493 +2490,497 @@
         <v>1</v>
       </c>
       <c r="J13" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K13" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L13" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M13" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N13" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N13" s="55" t="n"/>
-      <c r="O13" s="55" t="n"/>
-      <c r="P13" s="55" t="n"/>
-      <c r="Q13" s="55" t="inlineStr">
+      <c r="O13" s="51" t="n"/>
+      <c r="P13" s="51" t="n"/>
+      <c r="Q13" s="51" t="n"/>
+      <c r="R13" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R13" s="55" t="n"/>
-      <c r="S13" s="55" t="n"/>
-      <c r="T13" s="55" t="n"/>
-      <c r="U13" s="55" t="n"/>
-      <c r="V13" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W13" s="57" t="n"/>
+      <c r="S13" s="51" t="n"/>
+      <c r="T13" s="51" t="n"/>
+      <c r="U13" s="51" t="n"/>
+      <c r="V13" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W13" s="58" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B14" s="45" t="n"/>
-      <c r="C14" s="46" t="n"/>
-      <c r="D14" s="46" t="n"/>
+      <c r="C14" s="53" t="n"/>
+      <c r="D14" s="53" t="n"/>
       <c r="E14" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F14" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G14" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G14" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H14" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I14" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J14" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K14" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L14" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N14" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O14" s="51" t="n"/>
-      <c r="P14" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M14" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N14" s="55" t="n"/>
+      <c r="O14" s="55" t="n"/>
+      <c r="P14" s="55" t="n"/>
+      <c r="Q14" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q14" s="51" t="n"/>
-      <c r="R14" s="51" t="n"/>
-      <c r="S14" s="51" t="n"/>
-      <c r="T14" s="51" t="n"/>
-      <c r="U14" s="51" t="n"/>
-      <c r="V14" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W14" s="58" t="n"/>
+      <c r="R14" s="55" t="n"/>
+      <c r="S14" s="55" t="n"/>
+      <c r="T14" s="55" t="n"/>
+      <c r="U14" s="55" t="n"/>
+      <c r="V14" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W14" s="57" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B15" s="45" t="n"/>
-      <c r="C15" s="53" t="n"/>
-      <c r="D15" s="53" t="n"/>
+      <c r="C15" s="46" t="n"/>
+      <c r="D15" s="46" t="n"/>
       <c r="E15" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F15" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G15" s="59" t="n">
-        <v>45.1</v>
+      <c r="G15" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H15" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I15" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J15" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K15" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L15" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M15" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N15" s="55" t="n"/>
-      <c r="O15" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P15" s="55" t="n"/>
-      <c r="Q15" s="55" t="n"/>
-      <c r="R15" s="55" t="n"/>
-      <c r="S15" s="55" t="n"/>
-      <c r="T15" s="55" t="n"/>
-      <c r="U15" s="55" t="n"/>
-      <c r="V15" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W15" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M15" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N15" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O15" s="51" t="n"/>
+      <c r="P15" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q15" s="51" t="n"/>
+      <c r="R15" s="51" t="n"/>
+      <c r="S15" s="51" t="n"/>
+      <c r="T15" s="51" t="n"/>
+      <c r="U15" s="51" t="n"/>
+      <c r="V15" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W15" s="58" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B16" s="45" t="n"/>
-      <c r="C16" s="46" t="n"/>
-      <c r="D16" s="46" t="n"/>
+      <c r="C16" s="53" t="n"/>
+      <c r="D16" s="53" t="n"/>
       <c r="E16" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F16" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G16" s="54" t="n">
-        <v>26.3</v>
+      <c r="G16" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H16" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I16" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J16" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K16" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L16" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M16" s="51" t="n"/>
-      <c r="N16" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M16" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N16" s="55" t="n"/>
+      <c r="O16" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O16" s="51" t="n"/>
-      <c r="P16" s="51" t="n"/>
-      <c r="Q16" s="51" t="n"/>
-      <c r="R16" s="51" t="n"/>
-      <c r="S16" s="51" t="n"/>
-      <c r="T16" s="51" t="n"/>
-      <c r="U16" s="51" t="n"/>
-      <c r="V16" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W16" s="58" t="n"/>
+      <c r="P16" s="55" t="n"/>
+      <c r="Q16" s="55" t="n"/>
+      <c r="R16" s="55" t="n"/>
+      <c r="S16" s="55" t="n"/>
+      <c r="T16" s="55" t="n"/>
+      <c r="U16" s="55" t="n"/>
+      <c r="V16" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W16" s="57" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B17" s="45" t="n"/>
-      <c r="C17" s="53" t="n"/>
-      <c r="D17" s="53" t="n"/>
+      <c r="C17" s="46" t="n"/>
+      <c r="D17" s="46" t="n"/>
       <c r="E17" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F17" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G17" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H17" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J17" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K17" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L17" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M17" s="51" t="n"/>
+      <c r="N17" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N17" s="55" t="n"/>
-      <c r="O17" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P17" s="55" t="n"/>
-      <c r="Q17" s="55" t="n"/>
-      <c r="R17" s="55" t="n"/>
-      <c r="S17" s="55" t="n"/>
-      <c r="T17" s="55" t="n"/>
-      <c r="U17" s="55" t="n"/>
-      <c r="V17" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W17" s="57" t="n"/>
+      <c r="O17" s="51" t="n"/>
+      <c r="P17" s="51" t="n"/>
+      <c r="Q17" s="51" t="n"/>
+      <c r="R17" s="51" t="n"/>
+      <c r="S17" s="51" t="n"/>
+      <c r="T17" s="51" t="n"/>
+      <c r="U17" s="51" t="n"/>
+      <c r="V17" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W17" s="58" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B18" s="45" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="53" t="n"/>
       <c r="E18" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F18" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G18" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H18" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I18" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J18" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K18" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L18" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M18" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N18" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O18" s="51" t="n"/>
-      <c r="P18" s="51" t="n"/>
-      <c r="Q18" s="51" t="n"/>
-      <c r="R18" s="51" t="n"/>
-      <c r="S18" s="51" t="n"/>
-      <c r="T18" s="51" t="n"/>
-      <c r="U18" s="51" t="n"/>
-      <c r="V18" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W18" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M18" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N18" s="55" t="n"/>
+      <c r="O18" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P18" s="55" t="n"/>
+      <c r="Q18" s="55" t="n"/>
+      <c r="R18" s="55" t="n"/>
+      <c r="S18" s="55" t="n"/>
+      <c r="T18" s="55" t="n"/>
+      <c r="U18" s="55" t="n"/>
+      <c r="V18" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W18" s="57" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B19" s="45" t="n"/>
-      <c r="C19" s="53" t="n"/>
-      <c r="D19" s="53" t="n"/>
+      <c r="C19" s="46" t="n"/>
+      <c r="D19" s="46" t="n"/>
       <c r="E19" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F19" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G19" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H19" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I19" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K19" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L19" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I19" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J19" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K19" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L19" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M19" s="55" t="inlineStr">
+      <c r="M19" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N19" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N19" s="55" t="n"/>
-      <c r="O19" s="55" t="n"/>
-      <c r="P19" s="55" t="n"/>
-      <c r="Q19" s="55" t="n"/>
-      <c r="R19" s="55" t="n"/>
-      <c r="S19" s="55" t="n"/>
-      <c r="T19" s="55" t="n"/>
-      <c r="U19" s="55" t="n"/>
-      <c r="V19" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W19" s="57" t="n"/>
+      <c r="O19" s="51" t="n"/>
+      <c r="P19" s="51" t="n"/>
+      <c r="Q19" s="51" t="n"/>
+      <c r="R19" s="51" t="n"/>
+      <c r="S19" s="51" t="n"/>
+      <c r="T19" s="51" t="n"/>
+      <c r="U19" s="51" t="n"/>
+      <c r="V19" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W19" s="58" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B20" s="45" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="46" t="n"/>
+      <c r="C20" s="53" t="n"/>
+      <c r="D20" s="53" t="n"/>
       <c r="E20" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F20" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G20" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G20" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H20" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J20" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K20" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L20" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N20" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O20" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P20" s="51" t="n"/>
-      <c r="Q20" s="51" t="n"/>
-      <c r="R20" s="51" t="n"/>
-      <c r="S20" s="51" t="n"/>
-      <c r="T20" s="51" t="n"/>
-      <c r="U20" s="51" t="n"/>
-      <c r="V20" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W20" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M20" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N20" s="55" t="n"/>
+      <c r="O20" s="55" t="n"/>
+      <c r="P20" s="55" t="n"/>
+      <c r="Q20" s="55" t="n"/>
+      <c r="R20" s="55" t="n"/>
+      <c r="S20" s="55" t="n"/>
+      <c r="T20" s="55" t="n"/>
+      <c r="U20" s="55" t="n"/>
+      <c r="V20" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W20" s="57" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="53" t="n"/>
-      <c r="D21" s="53" t="n"/>
+      <c r="C21" s="46" t="n"/>
+      <c r="D21" s="46" t="n"/>
       <c r="E21" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F21" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G21" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G21" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H21" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J21" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K21" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L21" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M21" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N21" s="55" t="inlineStr">
+      <c r="M21" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N21" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O21" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O21" s="55" t="n"/>
-      <c r="P21" s="55" t="n"/>
-      <c r="Q21" s="55" t="n"/>
-      <c r="R21" s="55" t="n"/>
-      <c r="S21" s="55" t="n"/>
-      <c r="T21" s="55" t="n"/>
-      <c r="U21" s="55" t="n"/>
-      <c r="V21" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W21" s="57" t="n"/>
+      <c r="P21" s="51" t="n"/>
+      <c r="Q21" s="51" t="n"/>
+      <c r="R21" s="51" t="n"/>
+      <c r="S21" s="51" t="n"/>
+      <c r="T21" s="51" t="n"/>
+      <c r="U21" s="51" t="n"/>
+      <c r="V21" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W21" s="58" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="46" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
       <c r="E22" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G22" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H22" s="49" t="n">
         <v>2</v>
@@ -2989,208 +2989,218 @@
         <v>2</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K22" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L22" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M22" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M22" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N22" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N22" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O22" s="51" t="n"/>
-      <c r="P22" s="51" t="n"/>
-      <c r="Q22" s="51" t="n"/>
-      <c r="R22" s="51" t="n"/>
-      <c r="S22" s="51" t="n"/>
-      <c r="T22" s="51" t="n"/>
-      <c r="U22" s="51" t="n"/>
-      <c r="V22" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W22" s="58" t="n"/>
+      <c r="O22" s="55" t="n"/>
+      <c r="P22" s="55" t="n"/>
+      <c r="Q22" s="55" t="n"/>
+      <c r="R22" s="55" t="n"/>
+      <c r="S22" s="55" t="n"/>
+      <c r="T22" s="55" t="n"/>
+      <c r="U22" s="55" t="n"/>
+      <c r="V22" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W22" s="57" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="53" t="n"/>
-      <c r="D23" s="53" t="n"/>
+      <c r="C23" s="46" t="n"/>
+      <c r="D23" s="46" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G23" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H23" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L23" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M23" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M23" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N23" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N23" s="55" t="n"/>
-      <c r="O23" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P23" s="55" t="n"/>
-      <c r="Q23" s="55" t="n"/>
-      <c r="R23" s="55" t="n"/>
-      <c r="S23" s="55" t="n"/>
-      <c r="T23" s="55" t="n"/>
-      <c r="U23" s="55" t="n"/>
-      <c r="V23" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W23" s="57" t="n"/>
+      <c r="O23" s="51" t="n"/>
+      <c r="P23" s="51" t="n"/>
+      <c r="Q23" s="51" t="n"/>
+      <c r="R23" s="51" t="n"/>
+      <c r="S23" s="51" t="n"/>
+      <c r="T23" s="51" t="n"/>
+      <c r="U23" s="51" t="n"/>
+      <c r="V23" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W23" s="58" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G24" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G24" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H24" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L24" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M24" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N24" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O24" s="51" t="n"/>
-      <c r="P24" s="51" t="n"/>
-      <c r="Q24" s="51" t="n"/>
-      <c r="R24" s="51" t="n"/>
-      <c r="S24" s="51" t="n"/>
-      <c r="T24" s="51" t="n"/>
-      <c r="U24" s="51" t="n"/>
-      <c r="V24" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W24" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M24" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N24" s="55" t="n"/>
+      <c r="O24" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P24" s="55" t="n"/>
+      <c r="Q24" s="55" t="n"/>
+      <c r="R24" s="55" t="n"/>
+      <c r="S24" s="55" t="n"/>
+      <c r="T24" s="55" t="n"/>
+      <c r="U24" s="55" t="n"/>
+      <c r="V24" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W24" s="57" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="53" t="n"/>
-      <c r="D25" s="53" t="n"/>
+      <c r="C25" s="46" t="n"/>
+      <c r="D25" s="46" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G25" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G25" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H25" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L25" s="50" t="n"/>
-      <c r="M25" s="55" t="n"/>
-      <c r="N25" s="55" t="n"/>
-      <c r="O25" s="55" t="n"/>
-      <c r="P25" s="55" t="n"/>
-      <c r="Q25" s="55" t="n"/>
-      <c r="R25" s="55" t="n"/>
-      <c r="S25" s="55" t="n"/>
-      <c r="T25" s="55" t="n"/>
-      <c r="U25" s="55" t="n"/>
-      <c r="V25" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W25" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L25" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M25" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N25" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O25" s="51" t="n"/>
+      <c r="P25" s="51" t="n"/>
+      <c r="Q25" s="51" t="n"/>
+      <c r="R25" s="51" t="n"/>
+      <c r="S25" s="51" t="n"/>
+      <c r="T25" s="51" t="n"/>
+      <c r="U25" s="51" t="n"/>
+      <c r="V25" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W25" s="58" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="46" t="n"/>
-      <c r="D26" s="46" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G26" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H26" s="49" t="n">
         <v>0</v>
@@ -3199,43 +3209,43 @@
         <v>0</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L26" s="50" t="n"/>
-      <c r="M26" s="51" t="n"/>
-      <c r="N26" s="51" t="n"/>
-      <c r="O26" s="51" t="n"/>
-      <c r="P26" s="51" t="n"/>
-      <c r="Q26" s="51" t="n"/>
-      <c r="R26" s="51" t="n"/>
-      <c r="S26" s="51" t="n"/>
-      <c r="T26" s="51" t="n"/>
-      <c r="U26" s="51" t="n"/>
-      <c r="V26" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W26" s="58" t="n"/>
+      <c r="M26" s="55" t="n"/>
+      <c r="N26" s="55" t="n"/>
+      <c r="O26" s="55" t="n"/>
+      <c r="P26" s="55" t="n"/>
+      <c r="Q26" s="55" t="n"/>
+      <c r="R26" s="55" t="n"/>
+      <c r="S26" s="55" t="n"/>
+      <c r="T26" s="55" t="n"/>
+      <c r="U26" s="55" t="n"/>
+      <c r="V26" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W26" s="57" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="53" t="n"/>
-      <c r="D27" s="53" t="n"/>
+      <c r="C27" s="46" t="n"/>
+      <c r="D27" s="46" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G27" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H27" s="49" t="n">
         <v>0</v>
@@ -3244,43 +3254,43 @@
         <v>0</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L27" s="50" t="n"/>
-      <c r="M27" s="55" t="n"/>
-      <c r="N27" s="55" t="n"/>
-      <c r="O27" s="55" t="n"/>
-      <c r="P27" s="55" t="n"/>
-      <c r="Q27" s="55" t="n"/>
-      <c r="R27" s="55" t="n"/>
-      <c r="S27" s="55" t="n"/>
-      <c r="T27" s="55" t="n"/>
-      <c r="U27" s="55" t="n"/>
-      <c r="V27" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W27" s="57" t="n"/>
+      <c r="M27" s="51" t="n"/>
+      <c r="N27" s="51" t="n"/>
+      <c r="O27" s="51" t="n"/>
+      <c r="P27" s="51" t="n"/>
+      <c r="Q27" s="51" t="n"/>
+      <c r="R27" s="51" t="n"/>
+      <c r="S27" s="51" t="n"/>
+      <c r="T27" s="51" t="n"/>
+      <c r="U27" s="51" t="n"/>
+      <c r="V27" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W27" s="58" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="46" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="53" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G28" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G28" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H28" s="49" t="n">
         <v>0</v>
@@ -3289,43 +3299,43 @@
         <v>0</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L28" s="50" t="n"/>
-      <c r="M28" s="51" t="n"/>
-      <c r="N28" s="51" t="n"/>
-      <c r="O28" s="51" t="n"/>
-      <c r="P28" s="51" t="n"/>
-      <c r="Q28" s="51" t="n"/>
-      <c r="R28" s="51" t="n"/>
-      <c r="S28" s="51" t="n"/>
-      <c r="T28" s="51" t="n"/>
-      <c r="U28" s="51" t="n"/>
-      <c r="V28" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W28" s="58" t="n"/>
+      <c r="M28" s="55" t="n"/>
+      <c r="N28" s="55" t="n"/>
+      <c r="O28" s="55" t="n"/>
+      <c r="P28" s="55" t="n"/>
+      <c r="Q28" s="55" t="n"/>
+      <c r="R28" s="55" t="n"/>
+      <c r="S28" s="55" t="n"/>
+      <c r="T28" s="55" t="n"/>
+      <c r="U28" s="55" t="n"/>
+      <c r="V28" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W28" s="57" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="53" t="n"/>
-      <c r="D29" s="53" t="n"/>
+      <c r="C29" s="46" t="n"/>
+      <c r="D29" s="46" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G29" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H29" s="49" t="n">
         <v>0</v>
@@ -3334,43 +3344,43 @@
         <v>0</v>
       </c>
       <c r="J29" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L29" s="50" t="n"/>
-      <c r="M29" s="55" t="n"/>
-      <c r="N29" s="55" t="n"/>
-      <c r="O29" s="55" t="n"/>
-      <c r="P29" s="55" t="n"/>
-      <c r="Q29" s="55" t="n"/>
-      <c r="R29" s="55" t="n"/>
-      <c r="S29" s="55" t="n"/>
-      <c r="T29" s="55" t="n"/>
-      <c r="U29" s="55" t="n"/>
-      <c r="V29" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W29" s="57" t="n"/>
+      <c r="M29" s="51" t="n"/>
+      <c r="N29" s="51" t="n"/>
+      <c r="O29" s="51" t="n"/>
+      <c r="P29" s="51" t="n"/>
+      <c r="Q29" s="51" t="n"/>
+      <c r="R29" s="51" t="n"/>
+      <c r="S29" s="51" t="n"/>
+      <c r="T29" s="51" t="n"/>
+      <c r="U29" s="51" t="n"/>
+      <c r="V29" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W29" s="58" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="46" t="n"/>
-      <c r="D30" s="46" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="53" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G30" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H30" s="49" t="n">
         <v>0</v>
@@ -3379,1371 +3389,1375 @@
         <v>0</v>
       </c>
       <c r="J30" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L30" s="50" t="n"/>
-      <c r="M30" s="51" t="n"/>
-      <c r="N30" s="51" t="n"/>
-      <c r="O30" s="51" t="n"/>
-      <c r="P30" s="51" t="n"/>
-      <c r="Q30" s="51" t="n"/>
-      <c r="R30" s="51" t="n"/>
-      <c r="S30" s="51" t="n"/>
-      <c r="T30" s="51" t="n"/>
-      <c r="U30" s="51" t="n"/>
-      <c r="V30" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W30" s="58" t="n"/>
+      <c r="M30" s="55" t="n"/>
+      <c r="N30" s="55" t="n"/>
+      <c r="O30" s="55" t="n"/>
+      <c r="P30" s="55" t="n"/>
+      <c r="Q30" s="55" t="n"/>
+      <c r="R30" s="55" t="n"/>
+      <c r="S30" s="55" t="n"/>
+      <c r="T30" s="55" t="n"/>
+      <c r="U30" s="55" t="n"/>
+      <c r="V30" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W30" s="57" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="53" t="n"/>
-      <c r="D31" s="53" t="n"/>
+      <c r="C31" s="46" t="n"/>
+      <c r="D31" s="46" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G31" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H31" s="49" t="n"/>
-      <c r="I31" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G31" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H31" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J31" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L31" s="50" t="n"/>
-      <c r="M31" s="55" t="n"/>
-      <c r="N31" s="55" t="n"/>
-      <c r="O31" s="55" t="n"/>
-      <c r="P31" s="55" t="n"/>
-      <c r="Q31" s="55" t="n"/>
-      <c r="R31" s="55" t="n"/>
-      <c r="S31" s="55" t="n"/>
-      <c r="T31" s="55" t="n"/>
-      <c r="U31" s="55" t="n"/>
-      <c r="V31" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W31" s="57" t="n"/>
+      <c r="M31" s="51" t="n"/>
+      <c r="N31" s="51" t="n"/>
+      <c r="O31" s="51" t="n"/>
+      <c r="P31" s="51" t="n"/>
+      <c r="Q31" s="51" t="n"/>
+      <c r="R31" s="51" t="n"/>
+      <c r="S31" s="51" t="n"/>
+      <c r="T31" s="51" t="n"/>
+      <c r="U31" s="51" t="n"/>
+      <c r="V31" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W31" s="58" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="46" t="n"/>
-      <c r="D32" s="46" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G32" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H32" s="49" t="n"/>
       <c r="I32" s="49" t="n"/>
       <c r="J32" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L32" s="50" t="n"/>
-      <c r="M32" s="51" t="n"/>
-      <c r="N32" s="51" t="n"/>
-      <c r="O32" s="51" t="n"/>
-      <c r="P32" s="51" t="n"/>
-      <c r="Q32" s="51" t="n"/>
-      <c r="R32" s="51" t="n"/>
-      <c r="S32" s="51" t="n"/>
-      <c r="T32" s="51" t="n"/>
-      <c r="U32" s="51" t="n"/>
-      <c r="V32" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W32" s="58" t="n"/>
+      <c r="M32" s="55" t="n"/>
+      <c r="N32" s="55" t="n"/>
+      <c r="O32" s="55" t="n"/>
+      <c r="P32" s="55" t="n"/>
+      <c r="Q32" s="55" t="n"/>
+      <c r="R32" s="55" t="n"/>
+      <c r="S32" s="55" t="n"/>
+      <c r="T32" s="55" t="n"/>
+      <c r="U32" s="55" t="n"/>
+      <c r="V32" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W32" s="57" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="53" t="n"/>
-      <c r="D33" s="53" t="n"/>
+      <c r="C33" s="46" t="n"/>
+      <c r="D33" s="46" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G33" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H33" s="49" t="n"/>
       <c r="I33" s="49" t="n"/>
       <c r="J33" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L33" s="50" t="n"/>
-      <c r="M33" s="55" t="n"/>
-      <c r="N33" s="55" t="n"/>
-      <c r="O33" s="55" t="n"/>
-      <c r="P33" s="55" t="n"/>
-      <c r="Q33" s="55" t="n"/>
-      <c r="R33" s="55" t="n"/>
-      <c r="S33" s="55" t="n"/>
-      <c r="T33" s="55" t="n"/>
-      <c r="U33" s="55" t="n"/>
-      <c r="V33" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W33" s="57" t="n"/>
+      <c r="M33" s="51" t="n"/>
+      <c r="N33" s="51" t="n"/>
+      <c r="O33" s="51" t="n"/>
+      <c r="P33" s="51" t="n"/>
+      <c r="Q33" s="51" t="n"/>
+      <c r="R33" s="51" t="n"/>
+      <c r="S33" s="51" t="n"/>
+      <c r="T33" s="51" t="n"/>
+      <c r="U33" s="51" t="n"/>
+      <c r="V33" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W33" s="58" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="46" t="n"/>
-      <c r="D34" s="46" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G34" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H34" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I34" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H34" s="49" t="n"/>
+      <c r="I34" s="49" t="n"/>
       <c r="J34" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L34" s="50" t="n"/>
-      <c r="M34" s="51" t="n"/>
-      <c r="N34" s="51" t="n"/>
-      <c r="O34" s="51" t="n"/>
-      <c r="P34" s="51" t="n"/>
-      <c r="Q34" s="51" t="n"/>
-      <c r="R34" s="51" t="n"/>
-      <c r="S34" s="51" t="n"/>
-      <c r="T34" s="51" t="n"/>
-      <c r="U34" s="51" t="n"/>
-      <c r="V34" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W34" s="58" t="n"/>
+      <c r="M34" s="55" t="n"/>
+      <c r="N34" s="55" t="n"/>
+      <c r="O34" s="55" t="n"/>
+      <c r="P34" s="55" t="n"/>
+      <c r="Q34" s="55" t="n"/>
+      <c r="R34" s="55" t="n"/>
+      <c r="S34" s="55" t="n"/>
+      <c r="T34" s="55" t="n"/>
+      <c r="U34" s="55" t="n"/>
+      <c r="V34" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W34" s="57" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="53" t="n"/>
-      <c r="D35" s="53" t="n"/>
+      <c r="C35" s="46" t="n"/>
+      <c r="D35" s="46" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G35" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H35" s="49" t="n"/>
-      <c r="I35" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G35" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H35" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I35" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J35" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L35" s="50" t="n"/>
-      <c r="M35" s="55" t="n"/>
-      <c r="N35" s="55" t="n"/>
-      <c r="O35" s="55" t="n"/>
-      <c r="P35" s="55" t="n"/>
-      <c r="Q35" s="55" t="n"/>
-      <c r="R35" s="55" t="n"/>
-      <c r="S35" s="55" t="n"/>
-      <c r="T35" s="55" t="n"/>
-      <c r="U35" s="55" t="n"/>
-      <c r="V35" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W35" s="57" t="n"/>
+      <c r="M35" s="51" t="n"/>
+      <c r="N35" s="51" t="n"/>
+      <c r="O35" s="51" t="n"/>
+      <c r="P35" s="51" t="n"/>
+      <c r="Q35" s="51" t="n"/>
+      <c r="R35" s="51" t="n"/>
+      <c r="S35" s="51" t="n"/>
+      <c r="T35" s="51" t="n"/>
+      <c r="U35" s="51" t="n"/>
+      <c r="V35" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W35" s="58" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
+      <c r="C36" s="53" t="n"/>
+      <c r="D36" s="53" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G36" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G36" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H36" s="49" t="n"/>
       <c r="I36" s="49" t="n"/>
       <c r="J36" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="51" t="n"/>
-      <c r="N36" s="51" t="n"/>
-      <c r="O36" s="51" t="n"/>
-      <c r="P36" s="51" t="n"/>
-      <c r="Q36" s="51" t="n"/>
-      <c r="R36" s="51" t="n"/>
-      <c r="S36" s="51" t="n"/>
-      <c r="T36" s="51" t="n"/>
-      <c r="U36" s="51" t="n"/>
-      <c r="V36" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W36" s="58" t="n"/>
+      <c r="M36" s="55" t="n"/>
+      <c r="N36" s="55" t="n"/>
+      <c r="O36" s="55" t="n"/>
+      <c r="P36" s="55" t="n"/>
+      <c r="Q36" s="55" t="n"/>
+      <c r="R36" s="55" t="n"/>
+      <c r="S36" s="55" t="n"/>
+      <c r="T36" s="55" t="n"/>
+      <c r="U36" s="55" t="n"/>
+      <c r="V36" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W36" s="57" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="53" t="n"/>
-      <c r="D37" s="53" t="n"/>
+      <c r="C37" s="46" t="n"/>
+      <c r="D37" s="46" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G37" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G37" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H37" s="49" t="n"/>
       <c r="I37" s="49" t="n"/>
       <c r="J37" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K37" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K37" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="55" t="n"/>
-      <c r="N37" s="55" t="n"/>
-      <c r="O37" s="55" t="n"/>
-      <c r="P37" s="55" t="n"/>
-      <c r="Q37" s="55" t="n"/>
-      <c r="R37" s="55" t="n"/>
-      <c r="S37" s="55" t="n"/>
-      <c r="T37" s="55" t="n"/>
-      <c r="U37" s="55" t="n"/>
-      <c r="V37" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W37" s="57" t="n"/>
+      <c r="M37" s="51" t="n"/>
+      <c r="N37" s="51" t="n"/>
+      <c r="O37" s="51" t="n"/>
+      <c r="P37" s="51" t="n"/>
+      <c r="Q37" s="51" t="n"/>
+      <c r="R37" s="51" t="n"/>
+      <c r="S37" s="51" t="n"/>
+      <c r="T37" s="51" t="n"/>
+      <c r="U37" s="51" t="n"/>
+      <c r="V37" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W37" s="58" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="46" t="n"/>
-      <c r="D38" s="46" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G38" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H38" s="49" t="n"/>
       <c r="I38" s="49" t="n"/>
       <c r="J38" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="51" t="n"/>
-      <c r="N38" s="51" t="n"/>
-      <c r="O38" s="51" t="n"/>
-      <c r="P38" s="51" t="n"/>
-      <c r="Q38" s="51" t="n"/>
-      <c r="R38" s="51" t="n"/>
-      <c r="S38" s="51" t="n"/>
-      <c r="T38" s="51" t="n"/>
-      <c r="U38" s="51" t="n"/>
-      <c r="V38" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W38" s="58" t="n"/>
+      <c r="M38" s="55" t="n"/>
+      <c r="N38" s="55" t="n"/>
+      <c r="O38" s="55" t="n"/>
+      <c r="P38" s="55" t="n"/>
+      <c r="Q38" s="55" t="n"/>
+      <c r="R38" s="55" t="n"/>
+      <c r="S38" s="55" t="n"/>
+      <c r="T38" s="55" t="n"/>
+      <c r="U38" s="55" t="n"/>
+      <c r="V38" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W38" s="57" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="53" t="n"/>
-      <c r="D39" s="53" t="n"/>
+      <c r="C39" s="46" t="n"/>
+      <c r="D39" s="46" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G39" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G39" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H39" s="49" t="n"/>
       <c r="I39" s="49" t="n"/>
       <c r="J39" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="55" t="n"/>
-      <c r="N39" s="55" t="n"/>
-      <c r="O39" s="55" t="n"/>
-      <c r="P39" s="55" t="n"/>
-      <c r="Q39" s="55" t="n"/>
-      <c r="R39" s="55" t="n"/>
-      <c r="S39" s="55" t="n"/>
-      <c r="T39" s="55" t="n"/>
-      <c r="U39" s="55" t="n"/>
-      <c r="V39" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W39" s="57" t="n"/>
+      <c r="M39" s="51" t="n"/>
+      <c r="N39" s="51" t="n"/>
+      <c r="O39" s="51" t="n"/>
+      <c r="P39" s="51" t="n"/>
+      <c r="Q39" s="51" t="n"/>
+      <c r="R39" s="51" t="n"/>
+      <c r="S39" s="51" t="n"/>
+      <c r="T39" s="51" t="n"/>
+      <c r="U39" s="51" t="n"/>
+      <c r="V39" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W39" s="58" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="46" t="n"/>
-      <c r="D40" s="46" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G40" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H40" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I40" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G40" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H40" s="49" t="n"/>
+      <c r="I40" s="49" t="n"/>
       <c r="J40" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="51" t="n"/>
-      <c r="N40" s="51" t="n"/>
-      <c r="O40" s="51" t="n"/>
-      <c r="P40" s="51" t="n"/>
-      <c r="Q40" s="51" t="n"/>
-      <c r="R40" s="51" t="n"/>
-      <c r="S40" s="51" t="n"/>
-      <c r="T40" s="51" t="n"/>
-      <c r="U40" s="51" t="n"/>
-      <c r="V40" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W40" s="58" t="n"/>
+      <c r="M40" s="55" t="n"/>
+      <c r="N40" s="55" t="n"/>
+      <c r="O40" s="55" t="n"/>
+      <c r="P40" s="55" t="n"/>
+      <c r="Q40" s="55" t="n"/>
+      <c r="R40" s="55" t="n"/>
+      <c r="S40" s="55" t="n"/>
+      <c r="T40" s="55" t="n"/>
+      <c r="U40" s="55" t="n"/>
+      <c r="V40" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W40" s="57" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="53" t="n"/>
-      <c r="D41" s="53" t="n"/>
+      <c r="C41" s="46" t="n"/>
+      <c r="D41" s="46" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G41" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H41" s="49" t="n"/>
-      <c r="I41" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H41" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I41" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J41" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="55" t="n"/>
-      <c r="N41" s="55" t="n"/>
-      <c r="O41" s="55" t="n"/>
-      <c r="P41" s="55" t="n"/>
-      <c r="Q41" s="55" t="n"/>
-      <c r="R41" s="55" t="n"/>
-      <c r="S41" s="55" t="n"/>
-      <c r="T41" s="55" t="n"/>
-      <c r="U41" s="55" t="n"/>
-      <c r="V41" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W41" s="57" t="n"/>
+      <c r="M41" s="51" t="n"/>
+      <c r="N41" s="51" t="n"/>
+      <c r="O41" s="51" t="n"/>
+      <c r="P41" s="51" t="n"/>
+      <c r="Q41" s="51" t="n"/>
+      <c r="R41" s="51" t="n"/>
+      <c r="S41" s="51" t="n"/>
+      <c r="T41" s="51" t="n"/>
+      <c r="U41" s="51" t="n"/>
+      <c r="V41" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W41" s="58" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="46" t="n"/>
-      <c r="D42" s="46" t="n"/>
+      <c r="C42" s="53" t="n"/>
+      <c r="D42" s="53" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G42" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H42" s="49" t="n"/>
       <c r="I42" s="49" t="n"/>
       <c r="J42" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K42" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="51" t="n"/>
-      <c r="N42" s="51" t="n"/>
-      <c r="O42" s="51" t="n"/>
-      <c r="P42" s="51" t="n"/>
-      <c r="Q42" s="51" t="n"/>
-      <c r="R42" s="51" t="n"/>
-      <c r="S42" s="51" t="n"/>
-      <c r="T42" s="51" t="n"/>
-      <c r="U42" s="51" t="n"/>
-      <c r="V42" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W42" s="58" t="n"/>
+      <c r="M42" s="55" t="n"/>
+      <c r="N42" s="55" t="n"/>
+      <c r="O42" s="55" t="n"/>
+      <c r="P42" s="55" t="n"/>
+      <c r="Q42" s="55" t="n"/>
+      <c r="R42" s="55" t="n"/>
+      <c r="S42" s="55" t="n"/>
+      <c r="T42" s="55" t="n"/>
+      <c r="U42" s="55" t="n"/>
+      <c r="V42" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W42" s="57" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="53" t="n"/>
-      <c r="D43" s="53" t="n"/>
+      <c r="C43" s="46" t="n"/>
+      <c r="D43" s="46" t="n"/>
       <c r="E43" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F43" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G43" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H43" s="49" t="n"/>
+      <c r="I43" s="49" t="n"/>
+      <c r="J43" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F43" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G43" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H43" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I43" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J43" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K43" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="55" t="n"/>
-      <c r="N43" s="55" t="n"/>
-      <c r="O43" s="55" t="n"/>
-      <c r="P43" s="55" t="n"/>
-      <c r="Q43" s="55" t="n"/>
-      <c r="R43" s="55" t="n"/>
-      <c r="S43" s="55" t="n"/>
-      <c r="T43" s="55" t="n"/>
-      <c r="U43" s="55" t="n"/>
-      <c r="V43" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W43" s="57" t="n"/>
+      <c r="M43" s="51" t="n"/>
+      <c r="N43" s="51" t="n"/>
+      <c r="O43" s="51" t="n"/>
+      <c r="P43" s="51" t="n"/>
+      <c r="Q43" s="51" t="n"/>
+      <c r="R43" s="51" t="n"/>
+      <c r="S43" s="51" t="n"/>
+      <c r="T43" s="51" t="n"/>
+      <c r="U43" s="51" t="n"/>
+      <c r="V43" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W43" s="58" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="46" t="n"/>
-      <c r="D44" s="46" t="n"/>
+      <c r="C44" s="53" t="n"/>
+      <c r="D44" s="53" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G44" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H44" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I44" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J44" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K44" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="51" t="n"/>
-      <c r="N44" s="51" t="n"/>
-      <c r="O44" s="51" t="n"/>
-      <c r="P44" s="51" t="n"/>
-      <c r="Q44" s="51" t="n"/>
-      <c r="R44" s="51" t="n"/>
-      <c r="S44" s="51" t="n"/>
-      <c r="T44" s="51" t="n"/>
-      <c r="U44" s="51" t="n"/>
-      <c r="V44" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W44" s="58" t="n"/>
+      <c r="M44" s="55" t="n"/>
+      <c r="N44" s="55" t="n"/>
+      <c r="O44" s="55" t="n"/>
+      <c r="P44" s="55" t="n"/>
+      <c r="Q44" s="55" t="n"/>
+      <c r="R44" s="55" t="n"/>
+      <c r="S44" s="55" t="n"/>
+      <c r="T44" s="55" t="n"/>
+      <c r="U44" s="55" t="n"/>
+      <c r="V44" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W44" s="57" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="53" t="n"/>
-      <c r="D45" s="53" t="n"/>
+      <c r="C45" s="46" t="n"/>
+      <c r="D45" s="46" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G45" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H45" s="49" t="n"/>
-      <c r="I45" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H45" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I45" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J45" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K45" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="55" t="n"/>
-      <c r="N45" s="55" t="n"/>
-      <c r="O45" s="55" t="n"/>
-      <c r="P45" s="55" t="n"/>
-      <c r="Q45" s="55" t="n"/>
-      <c r="R45" s="55" t="n"/>
-      <c r="S45" s="55" t="n"/>
-      <c r="T45" s="55" t="n"/>
-      <c r="U45" s="55" t="n"/>
-      <c r="V45" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W45" s="57" t="n"/>
+      <c r="M45" s="51" t="n"/>
+      <c r="N45" s="51" t="n"/>
+      <c r="O45" s="51" t="n"/>
+      <c r="P45" s="51" t="n"/>
+      <c r="Q45" s="51" t="n"/>
+      <c r="R45" s="51" t="n"/>
+      <c r="S45" s="51" t="n"/>
+      <c r="T45" s="51" t="n"/>
+      <c r="U45" s="51" t="n"/>
+      <c r="V45" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W45" s="58" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="46" t="n"/>
-      <c r="D46" s="46" t="n"/>
+      <c r="C46" s="53" t="n"/>
+      <c r="D46" s="53" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G46" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G46" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H46" s="49" t="n"/>
       <c r="I46" s="49" t="n"/>
       <c r="J46" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K46" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="51" t="n"/>
-      <c r="N46" s="51" t="n"/>
-      <c r="O46" s="51" t="n"/>
-      <c r="P46" s="51" t="n"/>
-      <c r="Q46" s="51" t="n"/>
-      <c r="R46" s="51" t="n"/>
-      <c r="S46" s="51" t="n"/>
-      <c r="T46" s="51" t="n"/>
-      <c r="U46" s="51" t="n"/>
-      <c r="V46" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W46" s="58" t="n"/>
+      <c r="M46" s="55" t="n"/>
+      <c r="N46" s="55" t="n"/>
+      <c r="O46" s="55" t="n"/>
+      <c r="P46" s="55" t="n"/>
+      <c r="Q46" s="55" t="n"/>
+      <c r="R46" s="55" t="n"/>
+      <c r="S46" s="55" t="n"/>
+      <c r="T46" s="55" t="n"/>
+      <c r="U46" s="55" t="n"/>
+      <c r="V46" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W46" s="57" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="53" t="n"/>
-      <c r="D47" s="53" t="n"/>
+      <c r="C47" s="46" t="n"/>
+      <c r="D47" s="46" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G47" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G47" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H47" s="49" t="n"/>
       <c r="I47" s="49" t="n"/>
       <c r="J47" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K47" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="55" t="n"/>
-      <c r="N47" s="55" t="n"/>
-      <c r="O47" s="55" t="n"/>
-      <c r="P47" s="55" t="n"/>
-      <c r="Q47" s="55" t="n"/>
-      <c r="R47" s="55" t="n"/>
-      <c r="S47" s="55" t="n"/>
-      <c r="T47" s="55" t="n"/>
-      <c r="U47" s="55" t="n"/>
-      <c r="V47" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W47" s="57" t="n"/>
+      <c r="M47" s="51" t="n"/>
+      <c r="N47" s="51" t="n"/>
+      <c r="O47" s="51" t="n"/>
+      <c r="P47" s="51" t="n"/>
+      <c r="Q47" s="51" t="n"/>
+      <c r="R47" s="51" t="n"/>
+      <c r="S47" s="51" t="n"/>
+      <c r="T47" s="51" t="n"/>
+      <c r="U47" s="51" t="n"/>
+      <c r="V47" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W47" s="58" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
+      <c r="C48" s="53" t="n"/>
+      <c r="D48" s="53" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G48" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H48" s="49" t="n"/>
       <c r="I48" s="49" t="n"/>
       <c r="J48" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K48" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="51" t="n"/>
-      <c r="N48" s="51" t="n"/>
-      <c r="O48" s="51" t="n"/>
-      <c r="P48" s="51" t="n"/>
-      <c r="Q48" s="51" t="n"/>
-      <c r="R48" s="51" t="n"/>
-      <c r="S48" s="51" t="n"/>
-      <c r="T48" s="51" t="n"/>
-      <c r="U48" s="51" t="n"/>
-      <c r="V48" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W48" s="58" t="n"/>
+      <c r="M48" s="55" t="n"/>
+      <c r="N48" s="55" t="n"/>
+      <c r="O48" s="55" t="n"/>
+      <c r="P48" s="55" t="n"/>
+      <c r="Q48" s="55" t="n"/>
+      <c r="R48" s="55" t="n"/>
+      <c r="S48" s="55" t="n"/>
+      <c r="T48" s="55" t="n"/>
+      <c r="U48" s="55" t="n"/>
+      <c r="V48" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W48" s="57" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="53" t="n"/>
-      <c r="D49" s="53" t="n"/>
+      <c r="C49" s="46" t="n"/>
+      <c r="D49" s="46" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G49" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G49" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H49" s="49" t="n"/>
       <c r="I49" s="49" t="n"/>
       <c r="J49" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K49" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="55" t="n"/>
-      <c r="N49" s="55" t="n"/>
-      <c r="O49" s="55" t="n"/>
-      <c r="P49" s="55" t="n"/>
-      <c r="Q49" s="55" t="n"/>
-      <c r="R49" s="55" t="n"/>
-      <c r="S49" s="55" t="n"/>
-      <c r="T49" s="55" t="n"/>
-      <c r="U49" s="55" t="n"/>
-      <c r="V49" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W49" s="57" t="n"/>
+      <c r="M49" s="51" t="n"/>
+      <c r="N49" s="51" t="n"/>
+      <c r="O49" s="51" t="n"/>
+      <c r="P49" s="51" t="n"/>
+      <c r="Q49" s="51" t="n"/>
+      <c r="R49" s="51" t="n"/>
+      <c r="S49" s="51" t="n"/>
+      <c r="T49" s="51" t="n"/>
+      <c r="U49" s="51" t="n"/>
+      <c r="V49" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W49" s="58" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
+      <c r="C50" s="53" t="n"/>
+      <c r="D50" s="53" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G50" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G50" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="49" t="n"/>
       <c r="J50" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="51" t="n"/>
-      <c r="N50" s="51" t="n"/>
-      <c r="O50" s="51" t="n"/>
-      <c r="P50" s="51" t="n"/>
-      <c r="Q50" s="51" t="n"/>
-      <c r="R50" s="51" t="n"/>
-      <c r="S50" s="51" t="n"/>
-      <c r="T50" s="51" t="n"/>
-      <c r="U50" s="51" t="n"/>
-      <c r="V50" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W50" s="58" t="n"/>
+      <c r="M50" s="55" t="n"/>
+      <c r="N50" s="55" t="n"/>
+      <c r="O50" s="55" t="n"/>
+      <c r="P50" s="55" t="n"/>
+      <c r="Q50" s="55" t="n"/>
+      <c r="R50" s="55" t="n"/>
+      <c r="S50" s="55" t="n"/>
+      <c r="T50" s="55" t="n"/>
+      <c r="U50" s="55" t="n"/>
+      <c r="V50" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W50" s="57" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="53" t="n"/>
-      <c r="D51" s="53" t="n"/>
+      <c r="C51" s="46" t="n"/>
+      <c r="D51" s="46" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G51" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G51" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H51" s="49" t="n"/>
       <c r="I51" s="49" t="n"/>
       <c r="J51" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="55" t="n"/>
-      <c r="N51" s="55" t="n"/>
-      <c r="O51" s="55" t="n"/>
-      <c r="P51" s="55" t="n"/>
-      <c r="Q51" s="55" t="n"/>
-      <c r="R51" s="55" t="n"/>
-      <c r="S51" s="55" t="n"/>
-      <c r="T51" s="55" t="n"/>
-      <c r="U51" s="55" t="n"/>
-      <c r="V51" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W51" s="57" t="n"/>
+      <c r="M51" s="51" t="n"/>
+      <c r="N51" s="51" t="n"/>
+      <c r="O51" s="51" t="n"/>
+      <c r="P51" s="51" t="n"/>
+      <c r="Q51" s="51" t="n"/>
+      <c r="R51" s="51" t="n"/>
+      <c r="S51" s="51" t="n"/>
+      <c r="T51" s="51" t="n"/>
+      <c r="U51" s="51" t="n"/>
+      <c r="V51" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W51" s="58" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="46" t="n"/>
-      <c r="D52" s="46" t="n"/>
+      <c r="C52" s="53" t="n"/>
+      <c r="D52" s="53" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G52" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H52" s="49" t="n"/>
       <c r="I52" s="49" t="n"/>
       <c r="J52" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="51" t="n"/>
-      <c r="N52" s="51" t="n"/>
-      <c r="O52" s="51" t="n"/>
-      <c r="P52" s="51" t="n"/>
-      <c r="Q52" s="51" t="n"/>
-      <c r="R52" s="51" t="n"/>
-      <c r="S52" s="51" t="n"/>
-      <c r="T52" s="51" t="n"/>
-      <c r="U52" s="51" t="n"/>
-      <c r="V52" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W52" s="58" t="n"/>
+      <c r="M52" s="55" t="n"/>
+      <c r="N52" s="55" t="n"/>
+      <c r="O52" s="55" t="n"/>
+      <c r="P52" s="55" t="n"/>
+      <c r="Q52" s="55" t="n"/>
+      <c r="R52" s="55" t="n"/>
+      <c r="S52" s="55" t="n"/>
+      <c r="T52" s="55" t="n"/>
+      <c r="U52" s="55" t="n"/>
+      <c r="V52" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W52" s="57" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="53" t="n"/>
-      <c r="D53" s="53" t="n"/>
+      <c r="C53" s="46" t="n"/>
+      <c r="D53" s="46" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G53" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H53" s="49" t="n"/>
       <c r="I53" s="49" t="n"/>
       <c r="J53" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="55" t="n"/>
-      <c r="N53" s="55" t="n"/>
-      <c r="O53" s="55" t="n"/>
-      <c r="P53" s="55" t="n"/>
-      <c r="Q53" s="55" t="n"/>
-      <c r="R53" s="55" t="n"/>
-      <c r="S53" s="55" t="n"/>
-      <c r="T53" s="55" t="n"/>
-      <c r="U53" s="55" t="n"/>
-      <c r="V53" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W53" s="57" t="n"/>
+      <c r="M53" s="51" t="n"/>
+      <c r="N53" s="51" t="n"/>
+      <c r="O53" s="51" t="n"/>
+      <c r="P53" s="51" t="n"/>
+      <c r="Q53" s="51" t="n"/>
+      <c r="R53" s="51" t="n"/>
+      <c r="S53" s="51" t="n"/>
+      <c r="T53" s="51" t="n"/>
+      <c r="U53" s="51" t="n"/>
+      <c r="V53" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W53" s="58" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="46" t="n"/>
-      <c r="D54" s="46" t="n"/>
+      <c r="C54" s="53" t="n"/>
+      <c r="D54" s="53" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G54" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G54" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="51" t="n"/>
-      <c r="N54" s="51" t="n"/>
-      <c r="O54" s="51" t="n"/>
-      <c r="P54" s="51" t="n"/>
-      <c r="Q54" s="51" t="n"/>
-      <c r="R54" s="51" t="n"/>
-      <c r="S54" s="51" t="n"/>
-      <c r="T54" s="51" t="n"/>
-      <c r="U54" s="51" t="n"/>
-      <c r="V54" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W54" s="58" t="n"/>
+      <c r="M54" s="55" t="n"/>
+      <c r="N54" s="55" t="n"/>
+      <c r="O54" s="55" t="n"/>
+      <c r="P54" s="55" t="n"/>
+      <c r="Q54" s="55" t="n"/>
+      <c r="R54" s="55" t="n"/>
+      <c r="S54" s="55" t="n"/>
+      <c r="T54" s="55" t="n"/>
+      <c r="U54" s="55" t="n"/>
+      <c r="V54" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W54" s="57" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="53" t="n"/>
-      <c r="D55" s="53" t="n"/>
+      <c r="C55" s="46" t="n"/>
+      <c r="D55" s="46" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G55" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G55" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="55" t="n"/>
-      <c r="N55" s="55" t="n"/>
-      <c r="O55" s="55" t="n"/>
-      <c r="P55" s="55" t="n"/>
-      <c r="Q55" s="55" t="n"/>
-      <c r="R55" s="55" t="n"/>
-      <c r="S55" s="55" t="n"/>
-      <c r="T55" s="55" t="n"/>
-      <c r="U55" s="55" t="n"/>
-      <c r="V55" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W55" s="57" t="n"/>
+      <c r="M55" s="51" t="n"/>
+      <c r="N55" s="51" t="n"/>
+      <c r="O55" s="51" t="n"/>
+      <c r="P55" s="51" t="n"/>
+      <c r="Q55" s="51" t="n"/>
+      <c r="R55" s="51" t="n"/>
+      <c r="S55" s="51" t="n"/>
+      <c r="T55" s="51" t="n"/>
+      <c r="U55" s="51" t="n"/>
+      <c r="V55" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W55" s="58" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="46" t="n"/>
-      <c r="D56" s="46" t="n"/>
+      <c r="C56" s="53" t="n"/>
+      <c r="D56" s="53" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G56" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G56" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="51" t="n"/>
-      <c r="N56" s="51" t="n"/>
-      <c r="O56" s="51" t="n"/>
-      <c r="P56" s="51" t="n"/>
-      <c r="Q56" s="51" t="n"/>
-      <c r="R56" s="51" t="n"/>
-      <c r="S56" s="51" t="n"/>
-      <c r="T56" s="51" t="n"/>
-      <c r="U56" s="51" t="n"/>
-      <c r="V56" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W56" s="58" t="n"/>
+      <c r="M56" s="55" t="n"/>
+      <c r="N56" s="55" t="n"/>
+      <c r="O56" s="55" t="n"/>
+      <c r="P56" s="55" t="n"/>
+      <c r="Q56" s="55" t="n"/>
+      <c r="R56" s="55" t="n"/>
+      <c r="S56" s="55" t="n"/>
+      <c r="T56" s="55" t="n"/>
+      <c r="U56" s="55" t="n"/>
+      <c r="V56" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W56" s="57" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="53" t="n"/>
-      <c r="D57" s="53" t="n"/>
+      <c r="C57" s="46" t="n"/>
+      <c r="D57" s="46" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G57" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G57" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="55" t="n"/>
-      <c r="N57" s="55" t="n"/>
-      <c r="O57" s="55" t="n"/>
-      <c r="P57" s="55" t="n"/>
-      <c r="Q57" s="55" t="n"/>
-      <c r="R57" s="55" t="n"/>
-      <c r="S57" s="55" t="n"/>
-      <c r="T57" s="55" t="n"/>
-      <c r="U57" s="55" t="n"/>
-      <c r="V57" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W57" s="57" t="n"/>
+      <c r="M57" s="51" t="n"/>
+      <c r="N57" s="51" t="n"/>
+      <c r="O57" s="51" t="n"/>
+      <c r="P57" s="51" t="n"/>
+      <c r="Q57" s="51" t="n"/>
+      <c r="R57" s="51" t="n"/>
+      <c r="S57" s="51" t="n"/>
+      <c r="T57" s="51" t="n"/>
+      <c r="U57" s="51" t="n"/>
+      <c r="V57" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W57" s="58" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="46" t="n"/>
-      <c r="D58" s="46" t="n"/>
+      <c r="C58" s="53" t="n"/>
+      <c r="D58" s="53" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G58" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G58" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="51" t="n"/>
-      <c r="N58" s="51" t="n"/>
-      <c r="O58" s="51" t="n"/>
-      <c r="P58" s="51" t="n"/>
-      <c r="Q58" s="51" t="n"/>
-      <c r="R58" s="51" t="n"/>
-      <c r="S58" s="51" t="n"/>
-      <c r="T58" s="51" t="n"/>
-      <c r="U58" s="51" t="n"/>
-      <c r="V58" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W58" s="58" t="n"/>
+      <c r="M58" s="55" t="n"/>
+      <c r="N58" s="55" t="n"/>
+      <c r="O58" s="55" t="n"/>
+      <c r="P58" s="55" t="n"/>
+      <c r="Q58" s="55" t="n"/>
+      <c r="R58" s="55" t="n"/>
+      <c r="S58" s="55" t="n"/>
+      <c r="T58" s="55" t="n"/>
+      <c r="U58" s="55" t="n"/>
+      <c r="V58" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W58" s="57" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="53" t="n"/>
-      <c r="D59" s="53" t="n"/>
+      <c r="C59" s="46" t="n"/>
+      <c r="D59" s="46" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G59" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G59" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="55" t="n"/>
-      <c r="N59" s="55" t="n"/>
-      <c r="O59" s="55" t="n"/>
-      <c r="P59" s="55" t="n"/>
-      <c r="Q59" s="55" t="n"/>
-      <c r="R59" s="55" t="n"/>
-      <c r="S59" s="55" t="n"/>
-      <c r="T59" s="55" t="n"/>
-      <c r="U59" s="55" t="n"/>
-      <c r="V59" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W59" s="57" t="n"/>
+      <c r="M59" s="51" t="n"/>
+      <c r="N59" s="51" t="n"/>
+      <c r="O59" s="51" t="n"/>
+      <c r="P59" s="51" t="n"/>
+      <c r="Q59" s="51" t="n"/>
+      <c r="R59" s="51" t="n"/>
+      <c r="S59" s="51" t="n"/>
+      <c r="T59" s="51" t="n"/>
+      <c r="U59" s="51" t="n"/>
+      <c r="V59" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W59" s="58" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
+      <c r="C60" s="53" t="n"/>
+      <c r="D60" s="53" t="n"/>
       <c r="E60" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F60" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G60" s="48" t="n">
-        <v>24</v>
+      <c r="G60" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="51" t="n"/>
-      <c r="N60" s="51" t="n"/>
-      <c r="O60" s="51" t="n"/>
-      <c r="P60" s="51" t="n"/>
-      <c r="Q60" s="51" t="n"/>
-      <c r="R60" s="51" t="n"/>
-      <c r="S60" s="51" t="n"/>
-      <c r="T60" s="51" t="n"/>
-      <c r="U60" s="51" t="n"/>
-      <c r="V60" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W60" s="58" t="n"/>
+      <c r="M60" s="55" t="n"/>
+      <c r="N60" s="55" t="n"/>
+      <c r="O60" s="55" t="n"/>
+      <c r="P60" s="55" t="n"/>
+      <c r="Q60" s="55" t="n"/>
+      <c r="R60" s="55" t="n"/>
+      <c r="S60" s="55" t="n"/>
+      <c r="T60" s="55" t="n"/>
+      <c r="U60" s="55" t="n"/>
+      <c r="V60" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W60" s="57" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="53" t="n"/>
-      <c r="D61" s="53" t="n"/>
+      <c r="C61" s="46" t="n"/>
+      <c r="D61" s="46" t="n"/>
       <c r="E61" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F61" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G61" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G61" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
       <c r="J61" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K61" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="55" t="n"/>
-      <c r="N61" s="55" t="n"/>
-      <c r="O61" s="55" t="n"/>
-      <c r="P61" s="55" t="n"/>
-      <c r="Q61" s="55" t="n"/>
-      <c r="R61" s="55" t="n"/>
-      <c r="S61" s="55" t="n"/>
-      <c r="T61" s="55" t="n"/>
-      <c r="U61" s="55" t="n"/>
-      <c r="V61" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W61" s="57" t="n"/>
+      <c r="M61" s="51" t="n"/>
+      <c r="N61" s="51" t="n"/>
+      <c r="O61" s="51" t="n"/>
+      <c r="P61" s="51" t="n"/>
+      <c r="Q61" s="51" t="n"/>
+      <c r="R61" s="51" t="n"/>
+      <c r="S61" s="51" t="n"/>
+      <c r="T61" s="51" t="n"/>
+      <c r="U61" s="51" t="n"/>
+      <c r="V61" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W61" s="58" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B62" s="45" t="n"/>
-      <c r="C62" s="46" t="n"/>
-      <c r="D62" s="46" t="n"/>
+      <c r="C62" s="53" t="n"/>
+      <c r="D62" s="53" t="n"/>
       <c r="E62" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F62" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G62" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G62" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="49" t="n"/>
       <c r="J62" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K62" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L62" s="50" t="n"/>
-      <c r="M62" s="51" t="n"/>
-      <c r="N62" s="51" t="n"/>
-      <c r="O62" s="51" t="n"/>
-      <c r="P62" s="51" t="n"/>
-      <c r="Q62" s="51" t="n"/>
-      <c r="R62" s="51" t="n"/>
-      <c r="S62" s="51" t="n"/>
-      <c r="T62" s="51" t="n"/>
-      <c r="U62" s="51" t="n"/>
-      <c r="V62" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W62" s="58" t="n"/>
+      <c r="M62" s="55" t="n"/>
+      <c r="N62" s="55" t="n"/>
+      <c r="O62" s="55" t="n"/>
+      <c r="P62" s="55" t="n"/>
+      <c r="Q62" s="55" t="n"/>
+      <c r="R62" s="55" t="n"/>
+      <c r="S62" s="55" t="n"/>
+      <c r="T62" s="55" t="n"/>
+      <c r="U62" s="55" t="n"/>
+      <c r="V62" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W62" s="57" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B63" s="45" t="n"/>
-      <c r="C63" s="53" t="n"/>
-      <c r="D63" s="53" t="n"/>
+      <c r="C63" s="46" t="n"/>
+      <c r="D63" s="46" t="n"/>
       <c r="E63" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F63" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G63" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="49" t="n"/>
@@ -4751,51 +4765,92 @@
         <v>59</v>
       </c>
       <c r="K63" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L63" s="50" t="n"/>
-      <c r="M63" s="55" t="n"/>
-      <c r="N63" s="55" t="n"/>
-      <c r="O63" s="55" t="n"/>
-      <c r="P63" s="55" t="n"/>
-      <c r="Q63" s="55" t="n"/>
-      <c r="R63" s="55" t="n"/>
-      <c r="S63" s="55" t="n"/>
-      <c r="T63" s="55" t="n"/>
-      <c r="U63" s="55" t="n"/>
-      <c r="V63" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W63" s="57" t="n"/>
+      <c r="M63" s="51" t="n"/>
+      <c r="N63" s="51" t="n"/>
+      <c r="O63" s="51" t="n"/>
+      <c r="P63" s="51" t="n"/>
+      <c r="Q63" s="51" t="n"/>
+      <c r="R63" s="51" t="n"/>
+      <c r="S63" s="51" t="n"/>
+      <c r="T63" s="51" t="n"/>
+      <c r="U63" s="51" t="n"/>
+      <c r="V63" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W63" s="58" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B64" s="45" t="n"/>
-      <c r="C64" s="46" t="n"/>
-      <c r="D64" s="46" t="n"/>
-      <c r="E64" s="47" t="n"/>
-      <c r="F64" s="47" t="n"/>
-      <c r="G64" s="60" t="n"/>
+      <c r="C64" s="53" t="n"/>
+      <c r="D64" s="53" t="n"/>
+      <c r="E64" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F64" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G64" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="49" t="n"/>
-      <c r="J64" s="50" t="n"/>
-      <c r="K64" s="50" t="n"/>
+      <c r="J64" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K64" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L64" s="50" t="n"/>
-      <c r="M64" s="51" t="n"/>
-      <c r="N64" s="51" t="n"/>
-      <c r="O64" s="51" t="n"/>
-      <c r="P64" s="51" t="n"/>
-      <c r="Q64" s="51" t="n"/>
-      <c r="R64" s="51" t="n"/>
-      <c r="S64" s="51" t="n"/>
-      <c r="T64" s="51" t="n"/>
-      <c r="U64" s="51" t="n"/>
-      <c r="V64" s="61" t="n"/>
-      <c r="W64" s="61" t="n"/>
+      <c r="M64" s="55" t="n"/>
+      <c r="N64" s="55" t="n"/>
+      <c r="O64" s="55" t="n"/>
+      <c r="P64" s="55" t="n"/>
+      <c r="Q64" s="55" t="n"/>
+      <c r="R64" s="55" t="n"/>
+      <c r="S64" s="55" t="n"/>
+      <c r="T64" s="55" t="n"/>
+      <c r="U64" s="55" t="n"/>
+      <c r="V64" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W64" s="57" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B65" s="45" t="n"/>
+      <c r="C65" s="46" t="n"/>
+      <c r="D65" s="46" t="n"/>
+      <c r="E65" s="47" t="n"/>
+      <c r="F65" s="47" t="n"/>
+      <c r="G65" s="60" t="n"/>
+      <c r="H65" s="49" t="n"/>
+      <c r="I65" s="49" t="n"/>
+      <c r="J65" s="50" t="n"/>
+      <c r="K65" s="50" t="n"/>
+      <c r="L65" s="50" t="n"/>
+      <c r="M65" s="51" t="n"/>
+      <c r="N65" s="51" t="n"/>
+      <c r="O65" s="51" t="n"/>
+      <c r="P65" s="51" t="n"/>
+      <c r="Q65" s="51" t="n"/>
+      <c r="R65" s="51" t="n"/>
+      <c r="S65" s="51" t="n"/>
+      <c r="T65" s="51" t="n"/>
+      <c r="U65" s="51" t="n"/>
+      <c r="V65" s="61" t="n"/>
+      <c r="W65" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W65"/>
+  <dimension ref="A1:W66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,20 +1982,20 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/07(二)</t>
+          <t>2026/04/08(三)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G4" s="66" t="n">
-        <v>21.8</v>
+        <v>11.5</v>
       </c>
       <c r="H4" s="67" t="n">
         <v>4</v>
@@ -2004,91 +2004,95 @@
         <v>4</v>
       </c>
       <c r="J4" s="68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K4" s="68" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="L4" s="68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M4" s="69" t="inlineStr">
         <is>
-          <t>汇源通信、新能泰山</t>
-        </is>
-      </c>
-      <c r="N4" s="69" t="inlineStr"/>
+          <t>中安科</t>
+        </is>
+      </c>
+      <c r="N4" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信</t>
+        </is>
+      </c>
       <c r="O4" s="69" t="inlineStr"/>
       <c r="P4" s="69" t="inlineStr"/>
-      <c r="Q4" s="69" t="inlineStr">
-        <is>
-          <t>津药药业</t>
-        </is>
-      </c>
+      <c r="Q4" s="69" t="inlineStr"/>
       <c r="R4" s="69" t="inlineStr"/>
       <c r="S4" s="69" t="inlineStr"/>
       <c r="T4" s="69" t="inlineStr"/>
       <c r="U4" s="69" t="inlineStr"/>
       <c r="V4" s="69" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W4" s="69" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/06(一)</t>
+          <t>2026/04/07(二)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
       <c r="C5" s="64" t="inlineStr"/>
       <c r="D5" s="64" t="inlineStr"/>
       <c r="E5" s="65" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>36</v>
-      </c>
-      <c r="G5" s="71" t="n">
-        <v>25</v>
+        <v>93</v>
+      </c>
+      <c r="G5" s="66" t="n">
+        <v>21.8</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I5" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J5" s="68" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="L5" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K5" s="68" t="n">
-        <v>32</v>
-      </c>
-      <c r="L5" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" s="69" t="inlineStr"/>
+      <c r="M5" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信、新能泰山</t>
+        </is>
+      </c>
       <c r="N5" s="69" t="inlineStr"/>
       <c r="O5" s="69" t="inlineStr"/>
-      <c r="P5" s="69" t="inlineStr">
+      <c r="P5" s="69" t="inlineStr"/>
+      <c r="Q5" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="Q5" s="69" t="inlineStr"/>
       <c r="R5" s="69" t="inlineStr"/>
       <c r="S5" s="69" t="inlineStr"/>
       <c r="T5" s="69" t="inlineStr"/>
       <c r="U5" s="69" t="inlineStr"/>
       <c r="V5" s="69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W5" s="69" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/04/03(五)</t>
+          <t>2026/04/06(一)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
@@ -2132,105 +2136,105 @@
       <c r="T6" s="69" t="inlineStr"/>
       <c r="U6" s="69" t="inlineStr"/>
       <c r="V6" s="69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W6" s="69" t="inlineStr"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="64" t="inlineStr"/>
       <c r="D7" s="64" t="inlineStr"/>
       <c r="E7" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F7" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G7" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I7" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J7" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K7" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L7" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M7" s="69" t="inlineStr"/>
       <c r="N7" s="69" t="inlineStr"/>
-      <c r="O7" s="69" t="inlineStr">
+      <c r="O7" s="69" t="inlineStr"/>
+      <c r="P7" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P7" s="69" t="inlineStr"/>
       <c r="Q7" s="69" t="inlineStr"/>
       <c r="R7" s="69" t="inlineStr"/>
       <c r="S7" s="69" t="inlineStr"/>
       <c r="T7" s="69" t="inlineStr"/>
       <c r="U7" s="69" t="inlineStr"/>
       <c r="V7" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W7" s="69" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B8" s="63" t="inlineStr"/>
       <c r="C8" s="64" t="inlineStr"/>
       <c r="D8" s="64" t="inlineStr"/>
       <c r="E8" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F8" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G8" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G8" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H8" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I8" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K8" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L8" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" s="69" t="inlineStr"/>
-      <c r="N8" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M8" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N8" s="69" t="inlineStr"/>
+      <c r="O8" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O8" s="69" t="inlineStr"/>
       <c r="P8" s="69" t="inlineStr"/>
       <c r="Q8" s="69" t="inlineStr"/>
       <c r="R8" s="69" t="inlineStr"/>
@@ -2238,51 +2242,47 @@
       <c r="T8" s="69" t="inlineStr"/>
       <c r="U8" s="69" t="inlineStr"/>
       <c r="V8" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W8" s="69" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B9" s="63" t="inlineStr"/>
       <c r="C9" s="64" t="inlineStr"/>
       <c r="D9" s="64" t="inlineStr"/>
       <c r="E9" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F9" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G9" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G9" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H9" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I9" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J9" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K9" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L9" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M9" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M9" s="69" t="inlineStr"/>
+      <c r="N9" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N9" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O9" s="69" t="inlineStr"/>
@@ -2293,254 +2293,250 @@
       <c r="T9" s="69" t="inlineStr"/>
       <c r="U9" s="69" t="inlineStr"/>
       <c r="V9" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W9" s="69" t="inlineStr"/>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B10" s="63" t="inlineStr"/>
+      <c r="C10" s="64" t="inlineStr"/>
+      <c r="D10" s="64" t="inlineStr"/>
+      <c r="E10" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F10" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G10" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H10" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L10" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N10" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O10" s="69" t="inlineStr"/>
+      <c r="P10" s="69" t="inlineStr"/>
+      <c r="Q10" s="69" t="inlineStr"/>
+      <c r="R10" s="69" t="inlineStr"/>
+      <c r="S10" s="69" t="inlineStr"/>
+      <c r="T10" s="69" t="inlineStr"/>
+      <c r="U10" s="69" t="inlineStr"/>
+      <c r="V10" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W9" s="69" t="inlineStr"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="W10" s="69" t="inlineStr"/>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D10" s="38" t="inlineStr">
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E10" s="39" t="n">
+      <c r="E11" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F10" s="39" t="n">
+      <c r="F11" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G10" s="40" t="n">
+      <c r="G11" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H10" s="41" t="n">
+      <c r="H11" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I10" s="41" t="n">
+      <c r="I11" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J10" s="42" t="n">
+      <c r="J11" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K10" s="42" t="n">
+      <c r="K11" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L10" s="42" t="n">
+      <c r="L11" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M10" s="43" t="inlineStr">
+      <c r="M11" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N10" s="43" t="inlineStr"/>
-      <c r="O10" s="43" t="inlineStr">
+      <c r="N11" s="43" t="inlineStr"/>
+      <c r="O11" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P10" s="43" t="inlineStr"/>
-      <c r="Q10" s="43" t="inlineStr"/>
-      <c r="R10" s="43" t="inlineStr"/>
-      <c r="S10" s="43" t="inlineStr"/>
-      <c r="T10" s="43" t="inlineStr"/>
-      <c r="U10" s="43" t="inlineStr"/>
-      <c r="V10" s="43" t="n">
+      <c r="P11" s="43" t="inlineStr"/>
+      <c r="Q11" s="43" t="inlineStr"/>
+      <c r="R11" s="43" t="inlineStr"/>
+      <c r="S11" s="43" t="inlineStr"/>
+      <c r="T11" s="43" t="inlineStr"/>
+      <c r="U11" s="43" t="inlineStr"/>
+      <c r="V11" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W10" s="43" t="inlineStr"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="n"/>
-      <c r="C11" s="46" t="n"/>
-      <c r="D11" s="46" t="n"/>
-      <c r="E11" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F11" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G11" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H11" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K11" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L11" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M11" s="51" t="n"/>
-      <c r="N11" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O11" s="51" t="n"/>
-      <c r="P11" s="51" t="n"/>
-      <c r="Q11" s="51" t="n"/>
-      <c r="R11" s="51" t="n"/>
-      <c r="S11" s="51" t="n"/>
-      <c r="T11" s="51" t="n"/>
-      <c r="U11" s="51" t="n"/>
-      <c r="V11" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W11" s="43" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B12" s="45" t="n"/>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
+      <c r="C12" s="46" t="n"/>
+      <c r="D12" s="46" t="n"/>
       <c r="E12" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F12" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G12" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G12" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H12" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I12" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J12" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K12" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L12" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M12" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N12" s="55" t="n"/>
-      <c r="O12" s="55" t="n"/>
-      <c r="P12" s="55" t="n"/>
-      <c r="Q12" s="55" t="n"/>
-      <c r="R12" s="55" t="n"/>
-      <c r="S12" s="55" t="n"/>
-      <c r="T12" s="55" t="n"/>
-      <c r="U12" s="55" t="n"/>
-      <c r="V12" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W12" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M12" s="51" t="n"/>
+      <c r="N12" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O12" s="51" t="n"/>
+      <c r="P12" s="51" t="n"/>
+      <c r="Q12" s="51" t="n"/>
+      <c r="R12" s="51" t="n"/>
+      <c r="S12" s="51" t="n"/>
+      <c r="T12" s="51" t="n"/>
+      <c r="U12" s="51" t="n"/>
+      <c r="V12" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B13" s="45" t="n"/>
-      <c r="C13" s="46" t="n"/>
-      <c r="D13" s="46" t="n"/>
+      <c r="C13" s="53" t="n"/>
+      <c r="D13" s="53" t="n"/>
       <c r="E13" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F13" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G13" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G13" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H13" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I13" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J13" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K13" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L13" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M13" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N13" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O13" s="51" t="n"/>
-      <c r="P13" s="51" t="n"/>
-      <c r="Q13" s="51" t="n"/>
-      <c r="R13" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S13" s="51" t="n"/>
-      <c r="T13" s="51" t="n"/>
-      <c r="U13" s="51" t="n"/>
-      <c r="V13" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W13" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M13" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N13" s="55" t="n"/>
+      <c r="O13" s="55" t="n"/>
+      <c r="P13" s="55" t="n"/>
+      <c r="Q13" s="55" t="n"/>
+      <c r="R13" s="55" t="n"/>
+      <c r="S13" s="55" t="n"/>
+      <c r="T13" s="55" t="n"/>
+      <c r="U13" s="55" t="n"/>
+      <c r="V13" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W13" s="57" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B14" s="45" t="n"/>
-      <c r="C14" s="53" t="n"/>
-      <c r="D14" s="53" t="n"/>
+      <c r="C14" s="46" t="n"/>
+      <c r="D14" s="46" t="n"/>
       <c r="E14" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F14" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G14" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H14" s="49" t="n">
         <v>1</v>
@@ -2549,493 +2545,497 @@
         <v>1</v>
       </c>
       <c r="J14" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K14" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L14" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M14" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M14" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N14" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N14" s="55" t="n"/>
-      <c r="O14" s="55" t="n"/>
-      <c r="P14" s="55" t="n"/>
-      <c r="Q14" s="55" t="inlineStr">
+      <c r="O14" s="51" t="n"/>
+      <c r="P14" s="51" t="n"/>
+      <c r="Q14" s="51" t="n"/>
+      <c r="R14" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R14" s="55" t="n"/>
-      <c r="S14" s="55" t="n"/>
-      <c r="T14" s="55" t="n"/>
-      <c r="U14" s="55" t="n"/>
-      <c r="V14" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W14" s="57" t="n"/>
+      <c r="S14" s="51" t="n"/>
+      <c r="T14" s="51" t="n"/>
+      <c r="U14" s="51" t="n"/>
+      <c r="V14" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W14" s="58" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B15" s="45" t="n"/>
-      <c r="C15" s="46" t="n"/>
-      <c r="D15" s="46" t="n"/>
+      <c r="C15" s="53" t="n"/>
+      <c r="D15" s="53" t="n"/>
       <c r="E15" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F15" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G15" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G15" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H15" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I15" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J15" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K15" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L15" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N15" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O15" s="51" t="n"/>
-      <c r="P15" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M15" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N15" s="55" t="n"/>
+      <c r="O15" s="55" t="n"/>
+      <c r="P15" s="55" t="n"/>
+      <c r="Q15" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q15" s="51" t="n"/>
-      <c r="R15" s="51" t="n"/>
-      <c r="S15" s="51" t="n"/>
-      <c r="T15" s="51" t="n"/>
-      <c r="U15" s="51" t="n"/>
-      <c r="V15" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W15" s="58" t="n"/>
+      <c r="R15" s="55" t="n"/>
+      <c r="S15" s="55" t="n"/>
+      <c r="T15" s="55" t="n"/>
+      <c r="U15" s="55" t="n"/>
+      <c r="V15" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W15" s="57" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B16" s="45" t="n"/>
-      <c r="C16" s="53" t="n"/>
-      <c r="D16" s="53" t="n"/>
+      <c r="C16" s="46" t="n"/>
+      <c r="D16" s="46" t="n"/>
       <c r="E16" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F16" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G16" s="59" t="n">
-        <v>45.1</v>
+      <c r="G16" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H16" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I16" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J16" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K16" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L16" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M16" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N16" s="55" t="n"/>
-      <c r="O16" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P16" s="55" t="n"/>
-      <c r="Q16" s="55" t="n"/>
-      <c r="R16" s="55" t="n"/>
-      <c r="S16" s="55" t="n"/>
-      <c r="T16" s="55" t="n"/>
-      <c r="U16" s="55" t="n"/>
-      <c r="V16" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W16" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M16" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N16" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O16" s="51" t="n"/>
+      <c r="P16" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q16" s="51" t="n"/>
+      <c r="R16" s="51" t="n"/>
+      <c r="S16" s="51" t="n"/>
+      <c r="T16" s="51" t="n"/>
+      <c r="U16" s="51" t="n"/>
+      <c r="V16" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W16" s="58" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B17" s="45" t="n"/>
-      <c r="C17" s="46" t="n"/>
-      <c r="D17" s="46" t="n"/>
+      <c r="C17" s="53" t="n"/>
+      <c r="D17" s="53" t="n"/>
       <c r="E17" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F17" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G17" s="54" t="n">
-        <v>26.3</v>
+      <c r="G17" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H17" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J17" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K17" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L17" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M17" s="51" t="n"/>
-      <c r="N17" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M17" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N17" s="55" t="n"/>
+      <c r="O17" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O17" s="51" t="n"/>
-      <c r="P17" s="51" t="n"/>
-      <c r="Q17" s="51" t="n"/>
-      <c r="R17" s="51" t="n"/>
-      <c r="S17" s="51" t="n"/>
-      <c r="T17" s="51" t="n"/>
-      <c r="U17" s="51" t="n"/>
-      <c r="V17" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W17" s="58" t="n"/>
+      <c r="P17" s="55" t="n"/>
+      <c r="Q17" s="55" t="n"/>
+      <c r="R17" s="55" t="n"/>
+      <c r="S17" s="55" t="n"/>
+      <c r="T17" s="55" t="n"/>
+      <c r="U17" s="55" t="n"/>
+      <c r="V17" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W17" s="57" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B18" s="45" t="n"/>
-      <c r="C18" s="53" t="n"/>
-      <c r="D18" s="53" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="46" t="n"/>
       <c r="E18" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F18" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G18" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H18" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K18" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L18" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M18" s="51" t="n"/>
+      <c r="N18" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N18" s="55" t="n"/>
-      <c r="O18" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P18" s="55" t="n"/>
-      <c r="Q18" s="55" t="n"/>
-      <c r="R18" s="55" t="n"/>
-      <c r="S18" s="55" t="n"/>
-      <c r="T18" s="55" t="n"/>
-      <c r="U18" s="55" t="n"/>
-      <c r="V18" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W18" s="57" t="n"/>
+      <c r="O18" s="51" t="n"/>
+      <c r="P18" s="51" t="n"/>
+      <c r="Q18" s="51" t="n"/>
+      <c r="R18" s="51" t="n"/>
+      <c r="S18" s="51" t="n"/>
+      <c r="T18" s="51" t="n"/>
+      <c r="U18" s="51" t="n"/>
+      <c r="V18" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W18" s="58" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B19" s="45" t="n"/>
-      <c r="C19" s="46" t="n"/>
-      <c r="D19" s="46" t="n"/>
+      <c r="C19" s="53" t="n"/>
+      <c r="D19" s="53" t="n"/>
       <c r="E19" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F19" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G19" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H19" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J19" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K19" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L19" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N19" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O19" s="51" t="n"/>
-      <c r="P19" s="51" t="n"/>
-      <c r="Q19" s="51" t="n"/>
-      <c r="R19" s="51" t="n"/>
-      <c r="S19" s="51" t="n"/>
-      <c r="T19" s="51" t="n"/>
-      <c r="U19" s="51" t="n"/>
-      <c r="V19" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W19" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M19" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N19" s="55" t="n"/>
+      <c r="O19" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P19" s="55" t="n"/>
+      <c r="Q19" s="55" t="n"/>
+      <c r="R19" s="55" t="n"/>
+      <c r="S19" s="55" t="n"/>
+      <c r="T19" s="55" t="n"/>
+      <c r="U19" s="55" t="n"/>
+      <c r="V19" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W19" s="57" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B20" s="45" t="n"/>
-      <c r="C20" s="53" t="n"/>
-      <c r="D20" s="53" t="n"/>
+      <c r="C20" s="46" t="n"/>
+      <c r="D20" s="46" t="n"/>
       <c r="E20" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F20" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G20" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H20" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K20" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L20" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I20" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K20" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L20" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M20" s="55" t="inlineStr">
+      <c r="M20" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N20" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N20" s="55" t="n"/>
-      <c r="O20" s="55" t="n"/>
-      <c r="P20" s="55" t="n"/>
-      <c r="Q20" s="55" t="n"/>
-      <c r="R20" s="55" t="n"/>
-      <c r="S20" s="55" t="n"/>
-      <c r="T20" s="55" t="n"/>
-      <c r="U20" s="55" t="n"/>
-      <c r="V20" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W20" s="57" t="n"/>
+      <c r="O20" s="51" t="n"/>
+      <c r="P20" s="51" t="n"/>
+      <c r="Q20" s="51" t="n"/>
+      <c r="R20" s="51" t="n"/>
+      <c r="S20" s="51" t="n"/>
+      <c r="T20" s="51" t="n"/>
+      <c r="U20" s="51" t="n"/>
+      <c r="V20" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W20" s="58" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="46" t="n"/>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="53" t="n"/>
       <c r="E21" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F21" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G21" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G21" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H21" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J21" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K21" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L21" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N21" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O21" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P21" s="51" t="n"/>
-      <c r="Q21" s="51" t="n"/>
-      <c r="R21" s="51" t="n"/>
-      <c r="S21" s="51" t="n"/>
-      <c r="T21" s="51" t="n"/>
-      <c r="U21" s="51" t="n"/>
-      <c r="V21" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W21" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M21" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N21" s="55" t="n"/>
+      <c r="O21" s="55" t="n"/>
+      <c r="P21" s="55" t="n"/>
+      <c r="Q21" s="55" t="n"/>
+      <c r="R21" s="55" t="n"/>
+      <c r="S21" s="55" t="n"/>
+      <c r="T21" s="55" t="n"/>
+      <c r="U21" s="55" t="n"/>
+      <c r="V21" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W21" s="57" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="53" t="n"/>
+      <c r="C22" s="46" t="n"/>
+      <c r="D22" s="46" t="n"/>
       <c r="E22" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G22" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G22" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H22" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K22" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L22" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M22" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N22" s="55" t="inlineStr">
+      <c r="M22" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N22" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O22" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O22" s="55" t="n"/>
-      <c r="P22" s="55" t="n"/>
-      <c r="Q22" s="55" t="n"/>
-      <c r="R22" s="55" t="n"/>
-      <c r="S22" s="55" t="n"/>
-      <c r="T22" s="55" t="n"/>
-      <c r="U22" s="55" t="n"/>
-      <c r="V22" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W22" s="57" t="n"/>
+      <c r="P22" s="51" t="n"/>
+      <c r="Q22" s="51" t="n"/>
+      <c r="R22" s="51" t="n"/>
+      <c r="S22" s="51" t="n"/>
+      <c r="T22" s="51" t="n"/>
+      <c r="U22" s="51" t="n"/>
+      <c r="V22" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W22" s="58" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="46" t="n"/>
-      <c r="D23" s="46" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G23" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H23" s="49" t="n">
         <v>2</v>
@@ -3044,208 +3044,218 @@
         <v>2</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K23" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L23" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M23" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M23" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N23" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N23" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O23" s="51" t="n"/>
-      <c r="P23" s="51" t="n"/>
-      <c r="Q23" s="51" t="n"/>
-      <c r="R23" s="51" t="n"/>
-      <c r="S23" s="51" t="n"/>
-      <c r="T23" s="51" t="n"/>
-      <c r="U23" s="51" t="n"/>
-      <c r="V23" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W23" s="58" t="n"/>
+      <c r="O23" s="55" t="n"/>
+      <c r="P23" s="55" t="n"/>
+      <c r="Q23" s="55" t="n"/>
+      <c r="R23" s="55" t="n"/>
+      <c r="S23" s="55" t="n"/>
+      <c r="T23" s="55" t="n"/>
+      <c r="U23" s="55" t="n"/>
+      <c r="V23" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W23" s="57" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
+      <c r="C24" s="46" t="n"/>
+      <c r="D24" s="46" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G24" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H24" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L24" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M24" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M24" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N24" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N24" s="55" t="n"/>
-      <c r="O24" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P24" s="55" t="n"/>
-      <c r="Q24" s="55" t="n"/>
-      <c r="R24" s="55" t="n"/>
-      <c r="S24" s="55" t="n"/>
-      <c r="T24" s="55" t="n"/>
-      <c r="U24" s="55" t="n"/>
-      <c r="V24" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W24" s="57" t="n"/>
+      <c r="O24" s="51" t="n"/>
+      <c r="P24" s="51" t="n"/>
+      <c r="Q24" s="51" t="n"/>
+      <c r="R24" s="51" t="n"/>
+      <c r="S24" s="51" t="n"/>
+      <c r="T24" s="51" t="n"/>
+      <c r="U24" s="51" t="n"/>
+      <c r="V24" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W24" s="58" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="46" t="n"/>
-      <c r="D25" s="46" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G25" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G25" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H25" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L25" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M25" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N25" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O25" s="51" t="n"/>
-      <c r="P25" s="51" t="n"/>
-      <c r="Q25" s="51" t="n"/>
-      <c r="R25" s="51" t="n"/>
-      <c r="S25" s="51" t="n"/>
-      <c r="T25" s="51" t="n"/>
-      <c r="U25" s="51" t="n"/>
-      <c r="V25" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W25" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M25" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N25" s="55" t="n"/>
+      <c r="O25" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P25" s="55" t="n"/>
+      <c r="Q25" s="55" t="n"/>
+      <c r="R25" s="55" t="n"/>
+      <c r="S25" s="55" t="n"/>
+      <c r="T25" s="55" t="n"/>
+      <c r="U25" s="55" t="n"/>
+      <c r="V25" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W25" s="57" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="53" t="n"/>
-      <c r="D26" s="53" t="n"/>
+      <c r="C26" s="46" t="n"/>
+      <c r="D26" s="46" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G26" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G26" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H26" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L26" s="50" t="n"/>
-      <c r="M26" s="55" t="n"/>
-      <c r="N26" s="55" t="n"/>
-      <c r="O26" s="55" t="n"/>
-      <c r="P26" s="55" t="n"/>
-      <c r="Q26" s="55" t="n"/>
-      <c r="R26" s="55" t="n"/>
-      <c r="S26" s="55" t="n"/>
-      <c r="T26" s="55" t="n"/>
-      <c r="U26" s="55" t="n"/>
-      <c r="V26" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W26" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L26" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M26" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N26" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O26" s="51" t="n"/>
+      <c r="P26" s="51" t="n"/>
+      <c r="Q26" s="51" t="n"/>
+      <c r="R26" s="51" t="n"/>
+      <c r="S26" s="51" t="n"/>
+      <c r="T26" s="51" t="n"/>
+      <c r="U26" s="51" t="n"/>
+      <c r="V26" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W26" s="58" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="46" t="n"/>
-      <c r="D27" s="46" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G27" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H27" s="49" t="n">
         <v>0</v>
@@ -3254,43 +3264,43 @@
         <v>0</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L27" s="50" t="n"/>
-      <c r="M27" s="51" t="n"/>
-      <c r="N27" s="51" t="n"/>
-      <c r="O27" s="51" t="n"/>
-      <c r="P27" s="51" t="n"/>
-      <c r="Q27" s="51" t="n"/>
-      <c r="R27" s="51" t="n"/>
-      <c r="S27" s="51" t="n"/>
-      <c r="T27" s="51" t="n"/>
-      <c r="U27" s="51" t="n"/>
-      <c r="V27" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W27" s="58" t="n"/>
+      <c r="M27" s="55" t="n"/>
+      <c r="N27" s="55" t="n"/>
+      <c r="O27" s="55" t="n"/>
+      <c r="P27" s="55" t="n"/>
+      <c r="Q27" s="55" t="n"/>
+      <c r="R27" s="55" t="n"/>
+      <c r="S27" s="55" t="n"/>
+      <c r="T27" s="55" t="n"/>
+      <c r="U27" s="55" t="n"/>
+      <c r="V27" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W27" s="57" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="53" t="n"/>
-      <c r="D28" s="53" t="n"/>
+      <c r="C28" s="46" t="n"/>
+      <c r="D28" s="46" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G28" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H28" s="49" t="n">
         <v>0</v>
@@ -3299,43 +3309,43 @@
         <v>0</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L28" s="50" t="n"/>
-      <c r="M28" s="55" t="n"/>
-      <c r="N28" s="55" t="n"/>
-      <c r="O28" s="55" t="n"/>
-      <c r="P28" s="55" t="n"/>
-      <c r="Q28" s="55" t="n"/>
-      <c r="R28" s="55" t="n"/>
-      <c r="S28" s="55" t="n"/>
-      <c r="T28" s="55" t="n"/>
-      <c r="U28" s="55" t="n"/>
-      <c r="V28" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W28" s="57" t="n"/>
+      <c r="M28" s="51" t="n"/>
+      <c r="N28" s="51" t="n"/>
+      <c r="O28" s="51" t="n"/>
+      <c r="P28" s="51" t="n"/>
+      <c r="Q28" s="51" t="n"/>
+      <c r="R28" s="51" t="n"/>
+      <c r="S28" s="51" t="n"/>
+      <c r="T28" s="51" t="n"/>
+      <c r="U28" s="51" t="n"/>
+      <c r="V28" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W28" s="58" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="46" t="n"/>
-      <c r="D29" s="46" t="n"/>
+      <c r="C29" s="53" t="n"/>
+      <c r="D29" s="53" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G29" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G29" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H29" s="49" t="n">
         <v>0</v>
@@ -3344,43 +3354,43 @@
         <v>0</v>
       </c>
       <c r="J29" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L29" s="50" t="n"/>
-      <c r="M29" s="51" t="n"/>
-      <c r="N29" s="51" t="n"/>
-      <c r="O29" s="51" t="n"/>
-      <c r="P29" s="51" t="n"/>
-      <c r="Q29" s="51" t="n"/>
-      <c r="R29" s="51" t="n"/>
-      <c r="S29" s="51" t="n"/>
-      <c r="T29" s="51" t="n"/>
-      <c r="U29" s="51" t="n"/>
-      <c r="V29" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W29" s="58" t="n"/>
+      <c r="M29" s="55" t="n"/>
+      <c r="N29" s="55" t="n"/>
+      <c r="O29" s="55" t="n"/>
+      <c r="P29" s="55" t="n"/>
+      <c r="Q29" s="55" t="n"/>
+      <c r="R29" s="55" t="n"/>
+      <c r="S29" s="55" t="n"/>
+      <c r="T29" s="55" t="n"/>
+      <c r="U29" s="55" t="n"/>
+      <c r="V29" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W29" s="57" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="53" t="n"/>
-      <c r="D30" s="53" t="n"/>
+      <c r="C30" s="46" t="n"/>
+      <c r="D30" s="46" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G30" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H30" s="49" t="n">
         <v>0</v>
@@ -3389,43 +3399,43 @@
         <v>0</v>
       </c>
       <c r="J30" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L30" s="50" t="n"/>
-      <c r="M30" s="55" t="n"/>
-      <c r="N30" s="55" t="n"/>
-      <c r="O30" s="55" t="n"/>
-      <c r="P30" s="55" t="n"/>
-      <c r="Q30" s="55" t="n"/>
-      <c r="R30" s="55" t="n"/>
-      <c r="S30" s="55" t="n"/>
-      <c r="T30" s="55" t="n"/>
-      <c r="U30" s="55" t="n"/>
-      <c r="V30" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W30" s="57" t="n"/>
+      <c r="M30" s="51" t="n"/>
+      <c r="N30" s="51" t="n"/>
+      <c r="O30" s="51" t="n"/>
+      <c r="P30" s="51" t="n"/>
+      <c r="Q30" s="51" t="n"/>
+      <c r="R30" s="51" t="n"/>
+      <c r="S30" s="51" t="n"/>
+      <c r="T30" s="51" t="n"/>
+      <c r="U30" s="51" t="n"/>
+      <c r="V30" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W30" s="58" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="46" t="n"/>
-      <c r="D31" s="46" t="n"/>
+      <c r="C31" s="53" t="n"/>
+      <c r="D31" s="53" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G31" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H31" s="49" t="n">
         <v>0</v>
@@ -3434,1371 +3444,1375 @@
         <v>0</v>
       </c>
       <c r="J31" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L31" s="50" t="n"/>
-      <c r="M31" s="51" t="n"/>
-      <c r="N31" s="51" t="n"/>
-      <c r="O31" s="51" t="n"/>
-      <c r="P31" s="51" t="n"/>
-      <c r="Q31" s="51" t="n"/>
-      <c r="R31" s="51" t="n"/>
-      <c r="S31" s="51" t="n"/>
-      <c r="T31" s="51" t="n"/>
-      <c r="U31" s="51" t="n"/>
-      <c r="V31" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W31" s="58" t="n"/>
+      <c r="M31" s="55" t="n"/>
+      <c r="N31" s="55" t="n"/>
+      <c r="O31" s="55" t="n"/>
+      <c r="P31" s="55" t="n"/>
+      <c r="Q31" s="55" t="n"/>
+      <c r="R31" s="55" t="n"/>
+      <c r="S31" s="55" t="n"/>
+      <c r="T31" s="55" t="n"/>
+      <c r="U31" s="55" t="n"/>
+      <c r="V31" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W31" s="57" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="53" t="n"/>
-      <c r="D32" s="53" t="n"/>
+      <c r="C32" s="46" t="n"/>
+      <c r="D32" s="46" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G32" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H32" s="49" t="n"/>
-      <c r="I32" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G32" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H32" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J32" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L32" s="50" t="n"/>
-      <c r="M32" s="55" t="n"/>
-      <c r="N32" s="55" t="n"/>
-      <c r="O32" s="55" t="n"/>
-      <c r="P32" s="55" t="n"/>
-      <c r="Q32" s="55" t="n"/>
-      <c r="R32" s="55" t="n"/>
-      <c r="S32" s="55" t="n"/>
-      <c r="T32" s="55" t="n"/>
-      <c r="U32" s="55" t="n"/>
-      <c r="V32" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W32" s="57" t="n"/>
+      <c r="M32" s="51" t="n"/>
+      <c r="N32" s="51" t="n"/>
+      <c r="O32" s="51" t="n"/>
+      <c r="P32" s="51" t="n"/>
+      <c r="Q32" s="51" t="n"/>
+      <c r="R32" s="51" t="n"/>
+      <c r="S32" s="51" t="n"/>
+      <c r="T32" s="51" t="n"/>
+      <c r="U32" s="51" t="n"/>
+      <c r="V32" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W32" s="58" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="46" t="n"/>
-      <c r="D33" s="46" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G33" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H33" s="49" t="n"/>
       <c r="I33" s="49" t="n"/>
       <c r="J33" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L33" s="50" t="n"/>
-      <c r="M33" s="51" t="n"/>
-      <c r="N33" s="51" t="n"/>
-      <c r="O33" s="51" t="n"/>
-      <c r="P33" s="51" t="n"/>
-      <c r="Q33" s="51" t="n"/>
-      <c r="R33" s="51" t="n"/>
-      <c r="S33" s="51" t="n"/>
-      <c r="T33" s="51" t="n"/>
-      <c r="U33" s="51" t="n"/>
-      <c r="V33" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W33" s="58" t="n"/>
+      <c r="M33" s="55" t="n"/>
+      <c r="N33" s="55" t="n"/>
+      <c r="O33" s="55" t="n"/>
+      <c r="P33" s="55" t="n"/>
+      <c r="Q33" s="55" t="n"/>
+      <c r="R33" s="55" t="n"/>
+      <c r="S33" s="55" t="n"/>
+      <c r="T33" s="55" t="n"/>
+      <c r="U33" s="55" t="n"/>
+      <c r="V33" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W33" s="57" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="53" t="n"/>
-      <c r="D34" s="53" t="n"/>
+      <c r="C34" s="46" t="n"/>
+      <c r="D34" s="46" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G34" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H34" s="49" t="n"/>
       <c r="I34" s="49" t="n"/>
       <c r="J34" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L34" s="50" t="n"/>
-      <c r="M34" s="55" t="n"/>
-      <c r="N34" s="55" t="n"/>
-      <c r="O34" s="55" t="n"/>
-      <c r="P34" s="55" t="n"/>
-      <c r="Q34" s="55" t="n"/>
-      <c r="R34" s="55" t="n"/>
-      <c r="S34" s="55" t="n"/>
-      <c r="T34" s="55" t="n"/>
-      <c r="U34" s="55" t="n"/>
-      <c r="V34" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W34" s="57" t="n"/>
+      <c r="M34" s="51" t="n"/>
+      <c r="N34" s="51" t="n"/>
+      <c r="O34" s="51" t="n"/>
+      <c r="P34" s="51" t="n"/>
+      <c r="Q34" s="51" t="n"/>
+      <c r="R34" s="51" t="n"/>
+      <c r="S34" s="51" t="n"/>
+      <c r="T34" s="51" t="n"/>
+      <c r="U34" s="51" t="n"/>
+      <c r="V34" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W34" s="58" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="46" t="n"/>
-      <c r="D35" s="46" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G35" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H35" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I35" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H35" s="49" t="n"/>
+      <c r="I35" s="49" t="n"/>
       <c r="J35" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L35" s="50" t="n"/>
-      <c r="M35" s="51" t="n"/>
-      <c r="N35" s="51" t="n"/>
-      <c r="O35" s="51" t="n"/>
-      <c r="P35" s="51" t="n"/>
-      <c r="Q35" s="51" t="n"/>
-      <c r="R35" s="51" t="n"/>
-      <c r="S35" s="51" t="n"/>
-      <c r="T35" s="51" t="n"/>
-      <c r="U35" s="51" t="n"/>
-      <c r="V35" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W35" s="58" t="n"/>
+      <c r="M35" s="55" t="n"/>
+      <c r="N35" s="55" t="n"/>
+      <c r="O35" s="55" t="n"/>
+      <c r="P35" s="55" t="n"/>
+      <c r="Q35" s="55" t="n"/>
+      <c r="R35" s="55" t="n"/>
+      <c r="S35" s="55" t="n"/>
+      <c r="T35" s="55" t="n"/>
+      <c r="U35" s="55" t="n"/>
+      <c r="V35" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W35" s="57" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
+      <c r="C36" s="46" t="n"/>
+      <c r="D36" s="46" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G36" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H36" s="49" t="n"/>
-      <c r="I36" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G36" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H36" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I36" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J36" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="55" t="n"/>
-      <c r="N36" s="55" t="n"/>
-      <c r="O36" s="55" t="n"/>
-      <c r="P36" s="55" t="n"/>
-      <c r="Q36" s="55" t="n"/>
-      <c r="R36" s="55" t="n"/>
-      <c r="S36" s="55" t="n"/>
-      <c r="T36" s="55" t="n"/>
-      <c r="U36" s="55" t="n"/>
-      <c r="V36" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W36" s="57" t="n"/>
+      <c r="M36" s="51" t="n"/>
+      <c r="N36" s="51" t="n"/>
+      <c r="O36" s="51" t="n"/>
+      <c r="P36" s="51" t="n"/>
+      <c r="Q36" s="51" t="n"/>
+      <c r="R36" s="51" t="n"/>
+      <c r="S36" s="51" t="n"/>
+      <c r="T36" s="51" t="n"/>
+      <c r="U36" s="51" t="n"/>
+      <c r="V36" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W36" s="58" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="46" t="n"/>
-      <c r="D37" s="46" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G37" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G37" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H37" s="49" t="n"/>
       <c r="I37" s="49" t="n"/>
       <c r="J37" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="51" t="n"/>
-      <c r="N37" s="51" t="n"/>
-      <c r="O37" s="51" t="n"/>
-      <c r="P37" s="51" t="n"/>
-      <c r="Q37" s="51" t="n"/>
-      <c r="R37" s="51" t="n"/>
-      <c r="S37" s="51" t="n"/>
-      <c r="T37" s="51" t="n"/>
-      <c r="U37" s="51" t="n"/>
-      <c r="V37" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W37" s="58" t="n"/>
+      <c r="M37" s="55" t="n"/>
+      <c r="N37" s="55" t="n"/>
+      <c r="O37" s="55" t="n"/>
+      <c r="P37" s="55" t="n"/>
+      <c r="Q37" s="55" t="n"/>
+      <c r="R37" s="55" t="n"/>
+      <c r="S37" s="55" t="n"/>
+      <c r="T37" s="55" t="n"/>
+      <c r="U37" s="55" t="n"/>
+      <c r="V37" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W37" s="57" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="53" t="n"/>
-      <c r="D38" s="53" t="n"/>
+      <c r="C38" s="46" t="n"/>
+      <c r="D38" s="46" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G38" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G38" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H38" s="49" t="n"/>
       <c r="I38" s="49" t="n"/>
       <c r="J38" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K38" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K38" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="55" t="n"/>
-      <c r="N38" s="55" t="n"/>
-      <c r="O38" s="55" t="n"/>
-      <c r="P38" s="55" t="n"/>
-      <c r="Q38" s="55" t="n"/>
-      <c r="R38" s="55" t="n"/>
-      <c r="S38" s="55" t="n"/>
-      <c r="T38" s="55" t="n"/>
-      <c r="U38" s="55" t="n"/>
-      <c r="V38" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W38" s="57" t="n"/>
+      <c r="M38" s="51" t="n"/>
+      <c r="N38" s="51" t="n"/>
+      <c r="O38" s="51" t="n"/>
+      <c r="P38" s="51" t="n"/>
+      <c r="Q38" s="51" t="n"/>
+      <c r="R38" s="51" t="n"/>
+      <c r="S38" s="51" t="n"/>
+      <c r="T38" s="51" t="n"/>
+      <c r="U38" s="51" t="n"/>
+      <c r="V38" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W38" s="58" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="46" t="n"/>
-      <c r="D39" s="46" t="n"/>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G39" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H39" s="49" t="n"/>
       <c r="I39" s="49" t="n"/>
       <c r="J39" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="51" t="n"/>
-      <c r="N39" s="51" t="n"/>
-      <c r="O39" s="51" t="n"/>
-      <c r="P39" s="51" t="n"/>
-      <c r="Q39" s="51" t="n"/>
-      <c r="R39" s="51" t="n"/>
-      <c r="S39" s="51" t="n"/>
-      <c r="T39" s="51" t="n"/>
-      <c r="U39" s="51" t="n"/>
-      <c r="V39" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W39" s="58" t="n"/>
+      <c r="M39" s="55" t="n"/>
+      <c r="N39" s="55" t="n"/>
+      <c r="O39" s="55" t="n"/>
+      <c r="P39" s="55" t="n"/>
+      <c r="Q39" s="55" t="n"/>
+      <c r="R39" s="55" t="n"/>
+      <c r="S39" s="55" t="n"/>
+      <c r="T39" s="55" t="n"/>
+      <c r="U39" s="55" t="n"/>
+      <c r="V39" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W39" s="57" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="53" t="n"/>
-      <c r="D40" s="53" t="n"/>
+      <c r="C40" s="46" t="n"/>
+      <c r="D40" s="46" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G40" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G40" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H40" s="49" t="n"/>
       <c r="I40" s="49" t="n"/>
       <c r="J40" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="55" t="n"/>
-      <c r="N40" s="55" t="n"/>
-      <c r="O40" s="55" t="n"/>
-      <c r="P40" s="55" t="n"/>
-      <c r="Q40" s="55" t="n"/>
-      <c r="R40" s="55" t="n"/>
-      <c r="S40" s="55" t="n"/>
-      <c r="T40" s="55" t="n"/>
-      <c r="U40" s="55" t="n"/>
-      <c r="V40" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W40" s="57" t="n"/>
+      <c r="M40" s="51" t="n"/>
+      <c r="N40" s="51" t="n"/>
+      <c r="O40" s="51" t="n"/>
+      <c r="P40" s="51" t="n"/>
+      <c r="Q40" s="51" t="n"/>
+      <c r="R40" s="51" t="n"/>
+      <c r="S40" s="51" t="n"/>
+      <c r="T40" s="51" t="n"/>
+      <c r="U40" s="51" t="n"/>
+      <c r="V40" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W40" s="58" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="46" t="n"/>
-      <c r="D41" s="46" t="n"/>
+      <c r="C41" s="53" t="n"/>
+      <c r="D41" s="53" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G41" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H41" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I41" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G41" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H41" s="49" t="n"/>
+      <c r="I41" s="49" t="n"/>
       <c r="J41" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="51" t="n"/>
-      <c r="N41" s="51" t="n"/>
-      <c r="O41" s="51" t="n"/>
-      <c r="P41" s="51" t="n"/>
-      <c r="Q41" s="51" t="n"/>
-      <c r="R41" s="51" t="n"/>
-      <c r="S41" s="51" t="n"/>
-      <c r="T41" s="51" t="n"/>
-      <c r="U41" s="51" t="n"/>
-      <c r="V41" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W41" s="58" t="n"/>
+      <c r="M41" s="55" t="n"/>
+      <c r="N41" s="55" t="n"/>
+      <c r="O41" s="55" t="n"/>
+      <c r="P41" s="55" t="n"/>
+      <c r="Q41" s="55" t="n"/>
+      <c r="R41" s="55" t="n"/>
+      <c r="S41" s="55" t="n"/>
+      <c r="T41" s="55" t="n"/>
+      <c r="U41" s="55" t="n"/>
+      <c r="V41" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W41" s="57" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="53" t="n"/>
-      <c r="D42" s="53" t="n"/>
+      <c r="C42" s="46" t="n"/>
+      <c r="D42" s="46" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G42" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H42" s="49" t="n"/>
-      <c r="I42" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H42" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I42" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J42" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K42" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="55" t="n"/>
-      <c r="N42" s="55" t="n"/>
-      <c r="O42" s="55" t="n"/>
-      <c r="P42" s="55" t="n"/>
-      <c r="Q42" s="55" t="n"/>
-      <c r="R42" s="55" t="n"/>
-      <c r="S42" s="55" t="n"/>
-      <c r="T42" s="55" t="n"/>
-      <c r="U42" s="55" t="n"/>
-      <c r="V42" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W42" s="57" t="n"/>
+      <c r="M42" s="51" t="n"/>
+      <c r="N42" s="51" t="n"/>
+      <c r="O42" s="51" t="n"/>
+      <c r="P42" s="51" t="n"/>
+      <c r="Q42" s="51" t="n"/>
+      <c r="R42" s="51" t="n"/>
+      <c r="S42" s="51" t="n"/>
+      <c r="T42" s="51" t="n"/>
+      <c r="U42" s="51" t="n"/>
+      <c r="V42" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W42" s="58" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="46" t="n"/>
-      <c r="D43" s="46" t="n"/>
+      <c r="C43" s="53" t="n"/>
+      <c r="D43" s="53" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G43" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H43" s="49" t="n"/>
       <c r="I43" s="49" t="n"/>
       <c r="J43" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K43" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="51" t="n"/>
-      <c r="N43" s="51" t="n"/>
-      <c r="O43" s="51" t="n"/>
-      <c r="P43" s="51" t="n"/>
-      <c r="Q43" s="51" t="n"/>
-      <c r="R43" s="51" t="n"/>
-      <c r="S43" s="51" t="n"/>
-      <c r="T43" s="51" t="n"/>
-      <c r="U43" s="51" t="n"/>
-      <c r="V43" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W43" s="58" t="n"/>
+      <c r="M43" s="55" t="n"/>
+      <c r="N43" s="55" t="n"/>
+      <c r="O43" s="55" t="n"/>
+      <c r="P43" s="55" t="n"/>
+      <c r="Q43" s="55" t="n"/>
+      <c r="R43" s="55" t="n"/>
+      <c r="S43" s="55" t="n"/>
+      <c r="T43" s="55" t="n"/>
+      <c r="U43" s="55" t="n"/>
+      <c r="V43" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W43" s="57" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="53" t="n"/>
-      <c r="D44" s="53" t="n"/>
+      <c r="C44" s="46" t="n"/>
+      <c r="D44" s="46" t="n"/>
       <c r="E44" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F44" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G44" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H44" s="49" t="n"/>
+      <c r="I44" s="49" t="n"/>
+      <c r="J44" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F44" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G44" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H44" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I44" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J44" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K44" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="55" t="n"/>
-      <c r="N44" s="55" t="n"/>
-      <c r="O44" s="55" t="n"/>
-      <c r="P44" s="55" t="n"/>
-      <c r="Q44" s="55" t="n"/>
-      <c r="R44" s="55" t="n"/>
-      <c r="S44" s="55" t="n"/>
-      <c r="T44" s="55" t="n"/>
-      <c r="U44" s="55" t="n"/>
-      <c r="V44" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W44" s="57" t="n"/>
+      <c r="M44" s="51" t="n"/>
+      <c r="N44" s="51" t="n"/>
+      <c r="O44" s="51" t="n"/>
+      <c r="P44" s="51" t="n"/>
+      <c r="Q44" s="51" t="n"/>
+      <c r="R44" s="51" t="n"/>
+      <c r="S44" s="51" t="n"/>
+      <c r="T44" s="51" t="n"/>
+      <c r="U44" s="51" t="n"/>
+      <c r="V44" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W44" s="58" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="46" t="n"/>
-      <c r="D45" s="46" t="n"/>
+      <c r="C45" s="53" t="n"/>
+      <c r="D45" s="53" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G45" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H45" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I45" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J45" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K45" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="51" t="n"/>
-      <c r="N45" s="51" t="n"/>
-      <c r="O45" s="51" t="n"/>
-      <c r="P45" s="51" t="n"/>
-      <c r="Q45" s="51" t="n"/>
-      <c r="R45" s="51" t="n"/>
-      <c r="S45" s="51" t="n"/>
-      <c r="T45" s="51" t="n"/>
-      <c r="U45" s="51" t="n"/>
-      <c r="V45" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W45" s="58" t="n"/>
+      <c r="M45" s="55" t="n"/>
+      <c r="N45" s="55" t="n"/>
+      <c r="O45" s="55" t="n"/>
+      <c r="P45" s="55" t="n"/>
+      <c r="Q45" s="55" t="n"/>
+      <c r="R45" s="55" t="n"/>
+      <c r="S45" s="55" t="n"/>
+      <c r="T45" s="55" t="n"/>
+      <c r="U45" s="55" t="n"/>
+      <c r="V45" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W45" s="57" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="53" t="n"/>
-      <c r="D46" s="53" t="n"/>
+      <c r="C46" s="46" t="n"/>
+      <c r="D46" s="46" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G46" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H46" s="49" t="n"/>
-      <c r="I46" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H46" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I46" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J46" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K46" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="55" t="n"/>
-      <c r="N46" s="55" t="n"/>
-      <c r="O46" s="55" t="n"/>
-      <c r="P46" s="55" t="n"/>
-      <c r="Q46" s="55" t="n"/>
-      <c r="R46" s="55" t="n"/>
-      <c r="S46" s="55" t="n"/>
-      <c r="T46" s="55" t="n"/>
-      <c r="U46" s="55" t="n"/>
-      <c r="V46" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W46" s="57" t="n"/>
+      <c r="M46" s="51" t="n"/>
+      <c r="N46" s="51" t="n"/>
+      <c r="O46" s="51" t="n"/>
+      <c r="P46" s="51" t="n"/>
+      <c r="Q46" s="51" t="n"/>
+      <c r="R46" s="51" t="n"/>
+      <c r="S46" s="51" t="n"/>
+      <c r="T46" s="51" t="n"/>
+      <c r="U46" s="51" t="n"/>
+      <c r="V46" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W46" s="58" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="46" t="n"/>
-      <c r="D47" s="46" t="n"/>
+      <c r="C47" s="53" t="n"/>
+      <c r="D47" s="53" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G47" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G47" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H47" s="49" t="n"/>
       <c r="I47" s="49" t="n"/>
       <c r="J47" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K47" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="51" t="n"/>
-      <c r="N47" s="51" t="n"/>
-      <c r="O47" s="51" t="n"/>
-      <c r="P47" s="51" t="n"/>
-      <c r="Q47" s="51" t="n"/>
-      <c r="R47" s="51" t="n"/>
-      <c r="S47" s="51" t="n"/>
-      <c r="T47" s="51" t="n"/>
-      <c r="U47" s="51" t="n"/>
-      <c r="V47" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W47" s="58" t="n"/>
+      <c r="M47" s="55" t="n"/>
+      <c r="N47" s="55" t="n"/>
+      <c r="O47" s="55" t="n"/>
+      <c r="P47" s="55" t="n"/>
+      <c r="Q47" s="55" t="n"/>
+      <c r="R47" s="55" t="n"/>
+      <c r="S47" s="55" t="n"/>
+      <c r="T47" s="55" t="n"/>
+      <c r="U47" s="55" t="n"/>
+      <c r="V47" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W47" s="57" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
+      <c r="C48" s="46" t="n"/>
+      <c r="D48" s="46" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G48" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G48" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H48" s="49" t="n"/>
       <c r="I48" s="49" t="n"/>
       <c r="J48" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K48" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="55" t="n"/>
-      <c r="N48" s="55" t="n"/>
-      <c r="O48" s="55" t="n"/>
-      <c r="P48" s="55" t="n"/>
-      <c r="Q48" s="55" t="n"/>
-      <c r="R48" s="55" t="n"/>
-      <c r="S48" s="55" t="n"/>
-      <c r="T48" s="55" t="n"/>
-      <c r="U48" s="55" t="n"/>
-      <c r="V48" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W48" s="57" t="n"/>
+      <c r="M48" s="51" t="n"/>
+      <c r="N48" s="51" t="n"/>
+      <c r="O48" s="51" t="n"/>
+      <c r="P48" s="51" t="n"/>
+      <c r="Q48" s="51" t="n"/>
+      <c r="R48" s="51" t="n"/>
+      <c r="S48" s="51" t="n"/>
+      <c r="T48" s="51" t="n"/>
+      <c r="U48" s="51" t="n"/>
+      <c r="V48" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W48" s="58" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="46" t="n"/>
-      <c r="D49" s="46" t="n"/>
+      <c r="C49" s="53" t="n"/>
+      <c r="D49" s="53" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G49" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H49" s="49" t="n"/>
       <c r="I49" s="49" t="n"/>
       <c r="J49" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K49" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="51" t="n"/>
-      <c r="N49" s="51" t="n"/>
-      <c r="O49" s="51" t="n"/>
-      <c r="P49" s="51" t="n"/>
-      <c r="Q49" s="51" t="n"/>
-      <c r="R49" s="51" t="n"/>
-      <c r="S49" s="51" t="n"/>
-      <c r="T49" s="51" t="n"/>
-      <c r="U49" s="51" t="n"/>
-      <c r="V49" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W49" s="58" t="n"/>
+      <c r="M49" s="55" t="n"/>
+      <c r="N49" s="55" t="n"/>
+      <c r="O49" s="55" t="n"/>
+      <c r="P49" s="55" t="n"/>
+      <c r="Q49" s="55" t="n"/>
+      <c r="R49" s="55" t="n"/>
+      <c r="S49" s="55" t="n"/>
+      <c r="T49" s="55" t="n"/>
+      <c r="U49" s="55" t="n"/>
+      <c r="V49" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W49" s="57" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="53" t="n"/>
-      <c r="D50" s="53" t="n"/>
+      <c r="C50" s="46" t="n"/>
+      <c r="D50" s="46" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G50" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G50" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="49" t="n"/>
       <c r="J50" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="55" t="n"/>
-      <c r="N50" s="55" t="n"/>
-      <c r="O50" s="55" t="n"/>
-      <c r="P50" s="55" t="n"/>
-      <c r="Q50" s="55" t="n"/>
-      <c r="R50" s="55" t="n"/>
-      <c r="S50" s="55" t="n"/>
-      <c r="T50" s="55" t="n"/>
-      <c r="U50" s="55" t="n"/>
-      <c r="V50" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W50" s="57" t="n"/>
+      <c r="M50" s="51" t="n"/>
+      <c r="N50" s="51" t="n"/>
+      <c r="O50" s="51" t="n"/>
+      <c r="P50" s="51" t="n"/>
+      <c r="Q50" s="51" t="n"/>
+      <c r="R50" s="51" t="n"/>
+      <c r="S50" s="51" t="n"/>
+      <c r="T50" s="51" t="n"/>
+      <c r="U50" s="51" t="n"/>
+      <c r="V50" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W50" s="58" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="46" t="n"/>
-      <c r="D51" s="46" t="n"/>
+      <c r="C51" s="53" t="n"/>
+      <c r="D51" s="53" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G51" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G51" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H51" s="49" t="n"/>
       <c r="I51" s="49" t="n"/>
       <c r="J51" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="51" t="n"/>
-      <c r="N51" s="51" t="n"/>
-      <c r="O51" s="51" t="n"/>
-      <c r="P51" s="51" t="n"/>
-      <c r="Q51" s="51" t="n"/>
-      <c r="R51" s="51" t="n"/>
-      <c r="S51" s="51" t="n"/>
-      <c r="T51" s="51" t="n"/>
-      <c r="U51" s="51" t="n"/>
-      <c r="V51" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W51" s="58" t="n"/>
+      <c r="M51" s="55" t="n"/>
+      <c r="N51" s="55" t="n"/>
+      <c r="O51" s="55" t="n"/>
+      <c r="P51" s="55" t="n"/>
+      <c r="Q51" s="55" t="n"/>
+      <c r="R51" s="55" t="n"/>
+      <c r="S51" s="55" t="n"/>
+      <c r="T51" s="55" t="n"/>
+      <c r="U51" s="55" t="n"/>
+      <c r="V51" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W51" s="57" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="53" t="n"/>
-      <c r="D52" s="53" t="n"/>
+      <c r="C52" s="46" t="n"/>
+      <c r="D52" s="46" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G52" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G52" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H52" s="49" t="n"/>
       <c r="I52" s="49" t="n"/>
       <c r="J52" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="55" t="n"/>
-      <c r="N52" s="55" t="n"/>
-      <c r="O52" s="55" t="n"/>
-      <c r="P52" s="55" t="n"/>
-      <c r="Q52" s="55" t="n"/>
-      <c r="R52" s="55" t="n"/>
-      <c r="S52" s="55" t="n"/>
-      <c r="T52" s="55" t="n"/>
-      <c r="U52" s="55" t="n"/>
-      <c r="V52" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W52" s="57" t="n"/>
+      <c r="M52" s="51" t="n"/>
+      <c r="N52" s="51" t="n"/>
+      <c r="O52" s="51" t="n"/>
+      <c r="P52" s="51" t="n"/>
+      <c r="Q52" s="51" t="n"/>
+      <c r="R52" s="51" t="n"/>
+      <c r="S52" s="51" t="n"/>
+      <c r="T52" s="51" t="n"/>
+      <c r="U52" s="51" t="n"/>
+      <c r="V52" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W52" s="58" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="46" t="n"/>
-      <c r="D53" s="46" t="n"/>
+      <c r="C53" s="53" t="n"/>
+      <c r="D53" s="53" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G53" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H53" s="49" t="n"/>
       <c r="I53" s="49" t="n"/>
       <c r="J53" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="51" t="n"/>
-      <c r="N53" s="51" t="n"/>
-      <c r="O53" s="51" t="n"/>
-      <c r="P53" s="51" t="n"/>
-      <c r="Q53" s="51" t="n"/>
-      <c r="R53" s="51" t="n"/>
-      <c r="S53" s="51" t="n"/>
-      <c r="T53" s="51" t="n"/>
-      <c r="U53" s="51" t="n"/>
-      <c r="V53" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W53" s="58" t="n"/>
+      <c r="M53" s="55" t="n"/>
+      <c r="N53" s="55" t="n"/>
+      <c r="O53" s="55" t="n"/>
+      <c r="P53" s="55" t="n"/>
+      <c r="Q53" s="55" t="n"/>
+      <c r="R53" s="55" t="n"/>
+      <c r="S53" s="55" t="n"/>
+      <c r="T53" s="55" t="n"/>
+      <c r="U53" s="55" t="n"/>
+      <c r="V53" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W53" s="57" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="53" t="n"/>
-      <c r="D54" s="53" t="n"/>
+      <c r="C54" s="46" t="n"/>
+      <c r="D54" s="46" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G54" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="55" t="n"/>
-      <c r="N54" s="55" t="n"/>
-      <c r="O54" s="55" t="n"/>
-      <c r="P54" s="55" t="n"/>
-      <c r="Q54" s="55" t="n"/>
-      <c r="R54" s="55" t="n"/>
-      <c r="S54" s="55" t="n"/>
-      <c r="T54" s="55" t="n"/>
-      <c r="U54" s="55" t="n"/>
-      <c r="V54" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W54" s="57" t="n"/>
+      <c r="M54" s="51" t="n"/>
+      <c r="N54" s="51" t="n"/>
+      <c r="O54" s="51" t="n"/>
+      <c r="P54" s="51" t="n"/>
+      <c r="Q54" s="51" t="n"/>
+      <c r="R54" s="51" t="n"/>
+      <c r="S54" s="51" t="n"/>
+      <c r="T54" s="51" t="n"/>
+      <c r="U54" s="51" t="n"/>
+      <c r="V54" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W54" s="58" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="46" t="n"/>
-      <c r="D55" s="46" t="n"/>
+      <c r="C55" s="53" t="n"/>
+      <c r="D55" s="53" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G55" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G55" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="51" t="n"/>
-      <c r="N55" s="51" t="n"/>
-      <c r="O55" s="51" t="n"/>
-      <c r="P55" s="51" t="n"/>
-      <c r="Q55" s="51" t="n"/>
-      <c r="R55" s="51" t="n"/>
-      <c r="S55" s="51" t="n"/>
-      <c r="T55" s="51" t="n"/>
-      <c r="U55" s="51" t="n"/>
-      <c r="V55" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W55" s="58" t="n"/>
+      <c r="M55" s="55" t="n"/>
+      <c r="N55" s="55" t="n"/>
+      <c r="O55" s="55" t="n"/>
+      <c r="P55" s="55" t="n"/>
+      <c r="Q55" s="55" t="n"/>
+      <c r="R55" s="55" t="n"/>
+      <c r="S55" s="55" t="n"/>
+      <c r="T55" s="55" t="n"/>
+      <c r="U55" s="55" t="n"/>
+      <c r="V55" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W55" s="57" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="53" t="n"/>
-      <c r="D56" s="53" t="n"/>
+      <c r="C56" s="46" t="n"/>
+      <c r="D56" s="46" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G56" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G56" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="55" t="n"/>
-      <c r="N56" s="55" t="n"/>
-      <c r="O56" s="55" t="n"/>
-      <c r="P56" s="55" t="n"/>
-      <c r="Q56" s="55" t="n"/>
-      <c r="R56" s="55" t="n"/>
-      <c r="S56" s="55" t="n"/>
-      <c r="T56" s="55" t="n"/>
-      <c r="U56" s="55" t="n"/>
-      <c r="V56" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W56" s="57" t="n"/>
+      <c r="M56" s="51" t="n"/>
+      <c r="N56" s="51" t="n"/>
+      <c r="O56" s="51" t="n"/>
+      <c r="P56" s="51" t="n"/>
+      <c r="Q56" s="51" t="n"/>
+      <c r="R56" s="51" t="n"/>
+      <c r="S56" s="51" t="n"/>
+      <c r="T56" s="51" t="n"/>
+      <c r="U56" s="51" t="n"/>
+      <c r="V56" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W56" s="58" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="46" t="n"/>
-      <c r="D57" s="46" t="n"/>
+      <c r="C57" s="53" t="n"/>
+      <c r="D57" s="53" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G57" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G57" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="51" t="n"/>
-      <c r="N57" s="51" t="n"/>
-      <c r="O57" s="51" t="n"/>
-      <c r="P57" s="51" t="n"/>
-      <c r="Q57" s="51" t="n"/>
-      <c r="R57" s="51" t="n"/>
-      <c r="S57" s="51" t="n"/>
-      <c r="T57" s="51" t="n"/>
-      <c r="U57" s="51" t="n"/>
-      <c r="V57" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W57" s="58" t="n"/>
+      <c r="M57" s="55" t="n"/>
+      <c r="N57" s="55" t="n"/>
+      <c r="O57" s="55" t="n"/>
+      <c r="P57" s="55" t="n"/>
+      <c r="Q57" s="55" t="n"/>
+      <c r="R57" s="55" t="n"/>
+      <c r="S57" s="55" t="n"/>
+      <c r="T57" s="55" t="n"/>
+      <c r="U57" s="55" t="n"/>
+      <c r="V57" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W57" s="57" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="53" t="n"/>
-      <c r="D58" s="53" t="n"/>
+      <c r="C58" s="46" t="n"/>
+      <c r="D58" s="46" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G58" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G58" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="55" t="n"/>
-      <c r="N58" s="55" t="n"/>
-      <c r="O58" s="55" t="n"/>
-      <c r="P58" s="55" t="n"/>
-      <c r="Q58" s="55" t="n"/>
-      <c r="R58" s="55" t="n"/>
-      <c r="S58" s="55" t="n"/>
-      <c r="T58" s="55" t="n"/>
-      <c r="U58" s="55" t="n"/>
-      <c r="V58" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W58" s="57" t="n"/>
+      <c r="M58" s="51" t="n"/>
+      <c r="N58" s="51" t="n"/>
+      <c r="O58" s="51" t="n"/>
+      <c r="P58" s="51" t="n"/>
+      <c r="Q58" s="51" t="n"/>
+      <c r="R58" s="51" t="n"/>
+      <c r="S58" s="51" t="n"/>
+      <c r="T58" s="51" t="n"/>
+      <c r="U58" s="51" t="n"/>
+      <c r="V58" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W58" s="58" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="46" t="n"/>
-      <c r="D59" s="46" t="n"/>
+      <c r="C59" s="53" t="n"/>
+      <c r="D59" s="53" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G59" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G59" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="51" t="n"/>
-      <c r="N59" s="51" t="n"/>
-      <c r="O59" s="51" t="n"/>
-      <c r="P59" s="51" t="n"/>
-      <c r="Q59" s="51" t="n"/>
-      <c r="R59" s="51" t="n"/>
-      <c r="S59" s="51" t="n"/>
-      <c r="T59" s="51" t="n"/>
-      <c r="U59" s="51" t="n"/>
-      <c r="V59" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W59" s="58" t="n"/>
+      <c r="M59" s="55" t="n"/>
+      <c r="N59" s="55" t="n"/>
+      <c r="O59" s="55" t="n"/>
+      <c r="P59" s="55" t="n"/>
+      <c r="Q59" s="55" t="n"/>
+      <c r="R59" s="55" t="n"/>
+      <c r="S59" s="55" t="n"/>
+      <c r="T59" s="55" t="n"/>
+      <c r="U59" s="55" t="n"/>
+      <c r="V59" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W59" s="57" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
+      <c r="C60" s="46" t="n"/>
+      <c r="D60" s="46" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G60" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G60" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="55" t="n"/>
-      <c r="N60" s="55" t="n"/>
-      <c r="O60" s="55" t="n"/>
-      <c r="P60" s="55" t="n"/>
-      <c r="Q60" s="55" t="n"/>
-      <c r="R60" s="55" t="n"/>
-      <c r="S60" s="55" t="n"/>
-      <c r="T60" s="55" t="n"/>
-      <c r="U60" s="55" t="n"/>
-      <c r="V60" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W60" s="57" t="n"/>
+      <c r="M60" s="51" t="n"/>
+      <c r="N60" s="51" t="n"/>
+      <c r="O60" s="51" t="n"/>
+      <c r="P60" s="51" t="n"/>
+      <c r="Q60" s="51" t="n"/>
+      <c r="R60" s="51" t="n"/>
+      <c r="S60" s="51" t="n"/>
+      <c r="T60" s="51" t="n"/>
+      <c r="U60" s="51" t="n"/>
+      <c r="V60" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W60" s="58" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="46" t="n"/>
-      <c r="D61" s="46" t="n"/>
+      <c r="C61" s="53" t="n"/>
+      <c r="D61" s="53" t="n"/>
       <c r="E61" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F61" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G61" s="48" t="n">
-        <v>24</v>
+      <c r="G61" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
       <c r="J61" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K61" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="51" t="n"/>
-      <c r="N61" s="51" t="n"/>
-      <c r="O61" s="51" t="n"/>
-      <c r="P61" s="51" t="n"/>
-      <c r="Q61" s="51" t="n"/>
-      <c r="R61" s="51" t="n"/>
-      <c r="S61" s="51" t="n"/>
-      <c r="T61" s="51" t="n"/>
-      <c r="U61" s="51" t="n"/>
-      <c r="V61" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W61" s="58" t="n"/>
+      <c r="M61" s="55" t="n"/>
+      <c r="N61" s="55" t="n"/>
+      <c r="O61" s="55" t="n"/>
+      <c r="P61" s="55" t="n"/>
+      <c r="Q61" s="55" t="n"/>
+      <c r="R61" s="55" t="n"/>
+      <c r="S61" s="55" t="n"/>
+      <c r="T61" s="55" t="n"/>
+      <c r="U61" s="55" t="n"/>
+      <c r="V61" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W61" s="57" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B62" s="45" t="n"/>
-      <c r="C62" s="53" t="n"/>
-      <c r="D62" s="53" t="n"/>
+      <c r="C62" s="46" t="n"/>
+      <c r="D62" s="46" t="n"/>
       <c r="E62" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F62" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G62" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G62" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="49" t="n"/>
       <c r="J62" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K62" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L62" s="50" t="n"/>
-      <c r="M62" s="55" t="n"/>
-      <c r="N62" s="55" t="n"/>
-      <c r="O62" s="55" t="n"/>
-      <c r="P62" s="55" t="n"/>
-      <c r="Q62" s="55" t="n"/>
-      <c r="R62" s="55" t="n"/>
-      <c r="S62" s="55" t="n"/>
-      <c r="T62" s="55" t="n"/>
-      <c r="U62" s="55" t="n"/>
-      <c r="V62" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W62" s="57" t="n"/>
+      <c r="M62" s="51" t="n"/>
+      <c r="N62" s="51" t="n"/>
+      <c r="O62" s="51" t="n"/>
+      <c r="P62" s="51" t="n"/>
+      <c r="Q62" s="51" t="n"/>
+      <c r="R62" s="51" t="n"/>
+      <c r="S62" s="51" t="n"/>
+      <c r="T62" s="51" t="n"/>
+      <c r="U62" s="51" t="n"/>
+      <c r="V62" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W62" s="58" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B63" s="45" t="n"/>
-      <c r="C63" s="46" t="n"/>
-      <c r="D63" s="46" t="n"/>
+      <c r="C63" s="53" t="n"/>
+      <c r="D63" s="53" t="n"/>
       <c r="E63" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F63" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G63" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G63" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="49" t="n"/>
       <c r="J63" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K63" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L63" s="50" t="n"/>
-      <c r="M63" s="51" t="n"/>
-      <c r="N63" s="51" t="n"/>
-      <c r="O63" s="51" t="n"/>
-      <c r="P63" s="51" t="n"/>
-      <c r="Q63" s="51" t="n"/>
-      <c r="R63" s="51" t="n"/>
-      <c r="S63" s="51" t="n"/>
-      <c r="T63" s="51" t="n"/>
-      <c r="U63" s="51" t="n"/>
-      <c r="V63" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W63" s="58" t="n"/>
+      <c r="M63" s="55" t="n"/>
+      <c r="N63" s="55" t="n"/>
+      <c r="O63" s="55" t="n"/>
+      <c r="P63" s="55" t="n"/>
+      <c r="Q63" s="55" t="n"/>
+      <c r="R63" s="55" t="n"/>
+      <c r="S63" s="55" t="n"/>
+      <c r="T63" s="55" t="n"/>
+      <c r="U63" s="55" t="n"/>
+      <c r="V63" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W63" s="57" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B64" s="45" t="n"/>
-      <c r="C64" s="53" t="n"/>
-      <c r="D64" s="53" t="n"/>
+      <c r="C64" s="46" t="n"/>
+      <c r="D64" s="46" t="n"/>
       <c r="E64" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F64" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G64" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="49" t="n"/>
@@ -4806,51 +4820,92 @@
         <v>59</v>
       </c>
       <c r="K64" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L64" s="50" t="n"/>
-      <c r="M64" s="55" t="n"/>
-      <c r="N64" s="55" t="n"/>
-      <c r="O64" s="55" t="n"/>
-      <c r="P64" s="55" t="n"/>
-      <c r="Q64" s="55" t="n"/>
-      <c r="R64" s="55" t="n"/>
-      <c r="S64" s="55" t="n"/>
-      <c r="T64" s="55" t="n"/>
-      <c r="U64" s="55" t="n"/>
-      <c r="V64" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W64" s="57" t="n"/>
+      <c r="M64" s="51" t="n"/>
+      <c r="N64" s="51" t="n"/>
+      <c r="O64" s="51" t="n"/>
+      <c r="P64" s="51" t="n"/>
+      <c r="Q64" s="51" t="n"/>
+      <c r="R64" s="51" t="n"/>
+      <c r="S64" s="51" t="n"/>
+      <c r="T64" s="51" t="n"/>
+      <c r="U64" s="51" t="n"/>
+      <c r="V64" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W64" s="58" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B65" s="45" t="n"/>
-      <c r="C65" s="46" t="n"/>
-      <c r="D65" s="46" t="n"/>
-      <c r="E65" s="47" t="n"/>
-      <c r="F65" s="47" t="n"/>
-      <c r="G65" s="60" t="n"/>
+      <c r="C65" s="53" t="n"/>
+      <c r="D65" s="53" t="n"/>
+      <c r="E65" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F65" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G65" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H65" s="49" t="n"/>
       <c r="I65" s="49" t="n"/>
-      <c r="J65" s="50" t="n"/>
-      <c r="K65" s="50" t="n"/>
+      <c r="J65" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K65" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L65" s="50" t="n"/>
-      <c r="M65" s="51" t="n"/>
-      <c r="N65" s="51" t="n"/>
-      <c r="O65" s="51" t="n"/>
-      <c r="P65" s="51" t="n"/>
-      <c r="Q65" s="51" t="n"/>
-      <c r="R65" s="51" t="n"/>
-      <c r="S65" s="51" t="n"/>
-      <c r="T65" s="51" t="n"/>
-      <c r="U65" s="51" t="n"/>
-      <c r="V65" s="61" t="n"/>
-      <c r="W65" s="61" t="n"/>
+      <c r="M65" s="55" t="n"/>
+      <c r="N65" s="55" t="n"/>
+      <c r="O65" s="55" t="n"/>
+      <c r="P65" s="55" t="n"/>
+      <c r="Q65" s="55" t="n"/>
+      <c r="R65" s="55" t="n"/>
+      <c r="S65" s="55" t="n"/>
+      <c r="T65" s="55" t="n"/>
+      <c r="U65" s="55" t="n"/>
+      <c r="V65" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W65" s="57" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B66" s="45" t="n"/>
+      <c r="C66" s="46" t="n"/>
+      <c r="D66" s="46" t="n"/>
+      <c r="E66" s="47" t="n"/>
+      <c r="F66" s="47" t="n"/>
+      <c r="G66" s="60" t="n"/>
+      <c r="H66" s="49" t="n"/>
+      <c r="I66" s="49" t="n"/>
+      <c r="J66" s="50" t="n"/>
+      <c r="K66" s="50" t="n"/>
+      <c r="L66" s="50" t="n"/>
+      <c r="M66" s="51" t="n"/>
+      <c r="N66" s="51" t="n"/>
+      <c r="O66" s="51" t="n"/>
+      <c r="P66" s="51" t="n"/>
+      <c r="Q66" s="51" t="n"/>
+      <c r="R66" s="51" t="n"/>
+      <c r="S66" s="51" t="n"/>
+      <c r="T66" s="51" t="n"/>
+      <c r="U66" s="51" t="n"/>
+      <c r="V66" s="61" t="n"/>
+      <c r="W66" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W66"/>
+  <dimension ref="A1:W67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,47 +1982,47 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/08(三)</t>
+          <t>2026/04/09(四)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="G4" s="66" t="n">
-        <v>11.5</v>
+        <v>23.2</v>
       </c>
       <c r="H4" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4" s="68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K4" s="68" t="n">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="L4" s="68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M4" s="69" t="inlineStr">
         <is>
-          <t>中安科</t>
-        </is>
-      </c>
-      <c r="N4" s="69" t="inlineStr">
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="N4" s="69" t="inlineStr"/>
+      <c r="O4" s="69" t="inlineStr">
         <is>
           <t>汇源通信</t>
         </is>
       </c>
-      <c r="O4" s="69" t="inlineStr"/>
       <c r="P4" s="69" t="inlineStr"/>
       <c r="Q4" s="69" t="inlineStr"/>
       <c r="R4" s="69" t="inlineStr"/>
@@ -2037,20 +2037,20 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/07(二)</t>
+          <t>2026/04/08(三)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
       <c r="C5" s="64" t="inlineStr"/>
       <c r="D5" s="64" t="inlineStr"/>
       <c r="E5" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G5" s="66" t="n">
-        <v>21.8</v>
+        <v>11.5</v>
       </c>
       <c r="H5" s="67" t="n">
         <v>4</v>
@@ -2059,91 +2059,95 @@
         <v>4</v>
       </c>
       <c r="J5" s="68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K5" s="68" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="L5" s="68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M5" s="69" t="inlineStr">
         <is>
-          <t>汇源通信、新能泰山</t>
-        </is>
-      </c>
-      <c r="N5" s="69" t="inlineStr"/>
+          <t>中安科</t>
+        </is>
+      </c>
+      <c r="N5" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信</t>
+        </is>
+      </c>
       <c r="O5" s="69" t="inlineStr"/>
       <c r="P5" s="69" t="inlineStr"/>
-      <c r="Q5" s="69" t="inlineStr">
-        <is>
-          <t>津药药业</t>
-        </is>
-      </c>
+      <c r="Q5" s="69" t="inlineStr"/>
       <c r="R5" s="69" t="inlineStr"/>
       <c r="S5" s="69" t="inlineStr"/>
       <c r="T5" s="69" t="inlineStr"/>
       <c r="U5" s="69" t="inlineStr"/>
       <c r="V5" s="69" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W5" s="69" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/04/06(一)</t>
+          <t>2026/04/07(二)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
       <c r="C6" s="64" t="inlineStr"/>
       <c r="D6" s="64" t="inlineStr"/>
       <c r="E6" s="65" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>36</v>
-      </c>
-      <c r="G6" s="71" t="n">
-        <v>25</v>
+        <v>93</v>
+      </c>
+      <c r="G6" s="66" t="n">
+        <v>21.8</v>
       </c>
       <c r="H6" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I6" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J6" s="68" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="L6" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K6" s="68" t="n">
-        <v>32</v>
-      </c>
-      <c r="L6" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" s="69" t="inlineStr"/>
+      <c r="M6" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信、新能泰山</t>
+        </is>
+      </c>
       <c r="N6" s="69" t="inlineStr"/>
       <c r="O6" s="69" t="inlineStr"/>
-      <c r="P6" s="69" t="inlineStr">
+      <c r="P6" s="69" t="inlineStr"/>
+      <c r="Q6" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="Q6" s="69" t="inlineStr"/>
       <c r="R6" s="69" t="inlineStr"/>
       <c r="S6" s="69" t="inlineStr"/>
       <c r="T6" s="69" t="inlineStr"/>
       <c r="U6" s="69" t="inlineStr"/>
       <c r="V6" s="69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W6" s="69" t="inlineStr"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="62" t="inlineStr">
         <is>
-          <t>2026/04/03(五)</t>
+          <t>2026/04/06(一)</t>
         </is>
       </c>
       <c r="B7" s="63" t="inlineStr"/>
@@ -2187,105 +2191,105 @@
       <c r="T7" s="69" t="inlineStr"/>
       <c r="U7" s="69" t="inlineStr"/>
       <c r="V7" s="69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W7" s="69" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B8" s="63" t="inlineStr"/>
       <c r="C8" s="64" t="inlineStr"/>
       <c r="D8" s="64" t="inlineStr"/>
       <c r="E8" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F8" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G8" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H8" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I8" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J8" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K8" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L8" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M8" s="69" t="inlineStr"/>
       <c r="N8" s="69" t="inlineStr"/>
-      <c r="O8" s="69" t="inlineStr">
+      <c r="O8" s="69" t="inlineStr"/>
+      <c r="P8" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P8" s="69" t="inlineStr"/>
       <c r="Q8" s="69" t="inlineStr"/>
       <c r="R8" s="69" t="inlineStr"/>
       <c r="S8" s="69" t="inlineStr"/>
       <c r="T8" s="69" t="inlineStr"/>
       <c r="U8" s="69" t="inlineStr"/>
       <c r="V8" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W8" s="69" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B9" s="63" t="inlineStr"/>
       <c r="C9" s="64" t="inlineStr"/>
       <c r="D9" s="64" t="inlineStr"/>
       <c r="E9" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F9" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G9" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G9" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H9" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I9" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K9" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L9" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" s="69" t="inlineStr"/>
-      <c r="N9" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M9" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N9" s="69" t="inlineStr"/>
+      <c r="O9" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O9" s="69" t="inlineStr"/>
       <c r="P9" s="69" t="inlineStr"/>
       <c r="Q9" s="69" t="inlineStr"/>
       <c r="R9" s="69" t="inlineStr"/>
@@ -2293,51 +2297,47 @@
       <c r="T9" s="69" t="inlineStr"/>
       <c r="U9" s="69" t="inlineStr"/>
       <c r="V9" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W9" s="69" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B10" s="63" t="inlineStr"/>
       <c r="C10" s="64" t="inlineStr"/>
       <c r="D10" s="64" t="inlineStr"/>
       <c r="E10" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F10" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G10" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G10" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H10" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I10" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J10" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K10" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L10" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M10" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M10" s="69" t="inlineStr"/>
+      <c r="N10" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N10" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O10" s="69" t="inlineStr"/>
@@ -2348,254 +2348,250 @@
       <c r="T10" s="69" t="inlineStr"/>
       <c r="U10" s="69" t="inlineStr"/>
       <c r="V10" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W10" s="69" t="inlineStr"/>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B11" s="63" t="inlineStr"/>
+      <c r="C11" s="64" t="inlineStr"/>
+      <c r="D11" s="64" t="inlineStr"/>
+      <c r="E11" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F11" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G11" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H11" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L11" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N11" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O11" s="69" t="inlineStr"/>
+      <c r="P11" s="69" t="inlineStr"/>
+      <c r="Q11" s="69" t="inlineStr"/>
+      <c r="R11" s="69" t="inlineStr"/>
+      <c r="S11" s="69" t="inlineStr"/>
+      <c r="T11" s="69" t="inlineStr"/>
+      <c r="U11" s="69" t="inlineStr"/>
+      <c r="V11" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W10" s="69" t="inlineStr"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="W11" s="69" t="inlineStr"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C11" s="38" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D11" s="38" t="inlineStr">
+      <c r="D12" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E11" s="39" t="n">
+      <c r="E12" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F11" s="39" t="n">
+      <c r="F12" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G11" s="40" t="n">
+      <c r="G12" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H11" s="41" t="n">
+      <c r="H12" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I11" s="41" t="n">
+      <c r="I12" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J11" s="42" t="n">
+      <c r="J12" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K11" s="42" t="n">
+      <c r="K12" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L11" s="42" t="n">
+      <c r="L12" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M11" s="43" t="inlineStr">
+      <c r="M12" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N11" s="43" t="inlineStr"/>
-      <c r="O11" s="43" t="inlineStr">
+      <c r="N12" s="43" t="inlineStr"/>
+      <c r="O12" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P11" s="43" t="inlineStr"/>
-      <c r="Q11" s="43" t="inlineStr"/>
-      <c r="R11" s="43" t="inlineStr"/>
-      <c r="S11" s="43" t="inlineStr"/>
-      <c r="T11" s="43" t="inlineStr"/>
-      <c r="U11" s="43" t="inlineStr"/>
-      <c r="V11" s="43" t="n">
+      <c r="P12" s="43" t="inlineStr"/>
+      <c r="Q12" s="43" t="inlineStr"/>
+      <c r="R12" s="43" t="inlineStr"/>
+      <c r="S12" s="43" t="inlineStr"/>
+      <c r="T12" s="43" t="inlineStr"/>
+      <c r="U12" s="43" t="inlineStr"/>
+      <c r="V12" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W11" s="43" t="inlineStr"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B12" s="45" t="n"/>
-      <c r="C12" s="46" t="n"/>
-      <c r="D12" s="46" t="n"/>
-      <c r="E12" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F12" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G12" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H12" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K12" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L12" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" s="51" t="n"/>
-      <c r="N12" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O12" s="51" t="n"/>
-      <c r="P12" s="51" t="n"/>
-      <c r="Q12" s="51" t="n"/>
-      <c r="R12" s="51" t="n"/>
-      <c r="S12" s="51" t="n"/>
-      <c r="T12" s="51" t="n"/>
-      <c r="U12" s="51" t="n"/>
-      <c r="V12" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W12" s="43" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B13" s="45" t="n"/>
-      <c r="C13" s="53" t="n"/>
-      <c r="D13" s="53" t="n"/>
+      <c r="C13" s="46" t="n"/>
+      <c r="D13" s="46" t="n"/>
       <c r="E13" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F13" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G13" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G13" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H13" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I13" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J13" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K13" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L13" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M13" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N13" s="55" t="n"/>
-      <c r="O13" s="55" t="n"/>
-      <c r="P13" s="55" t="n"/>
-      <c r="Q13" s="55" t="n"/>
-      <c r="R13" s="55" t="n"/>
-      <c r="S13" s="55" t="n"/>
-      <c r="T13" s="55" t="n"/>
-      <c r="U13" s="55" t="n"/>
-      <c r="V13" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W13" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M13" s="51" t="n"/>
+      <c r="N13" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O13" s="51" t="n"/>
+      <c r="P13" s="51" t="n"/>
+      <c r="Q13" s="51" t="n"/>
+      <c r="R13" s="51" t="n"/>
+      <c r="S13" s="51" t="n"/>
+      <c r="T13" s="51" t="n"/>
+      <c r="U13" s="51" t="n"/>
+      <c r="V13" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B14" s="45" t="n"/>
-      <c r="C14" s="46" t="n"/>
-      <c r="D14" s="46" t="n"/>
+      <c r="C14" s="53" t="n"/>
+      <c r="D14" s="53" t="n"/>
       <c r="E14" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F14" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G14" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G14" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H14" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I14" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J14" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K14" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L14" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M14" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N14" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O14" s="51" t="n"/>
-      <c r="P14" s="51" t="n"/>
-      <c r="Q14" s="51" t="n"/>
-      <c r="R14" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S14" s="51" t="n"/>
-      <c r="T14" s="51" t="n"/>
-      <c r="U14" s="51" t="n"/>
-      <c r="V14" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W14" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M14" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N14" s="55" t="n"/>
+      <c r="O14" s="55" t="n"/>
+      <c r="P14" s="55" t="n"/>
+      <c r="Q14" s="55" t="n"/>
+      <c r="R14" s="55" t="n"/>
+      <c r="S14" s="55" t="n"/>
+      <c r="T14" s="55" t="n"/>
+      <c r="U14" s="55" t="n"/>
+      <c r="V14" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W14" s="57" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B15" s="45" t="n"/>
-      <c r="C15" s="53" t="n"/>
-      <c r="D15" s="53" t="n"/>
+      <c r="C15" s="46" t="n"/>
+      <c r="D15" s="46" t="n"/>
       <c r="E15" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F15" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G15" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H15" s="49" t="n">
         <v>1</v>
@@ -2604,493 +2600,497 @@
         <v>1</v>
       </c>
       <c r="J15" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K15" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L15" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M15" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M15" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N15" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N15" s="55" t="n"/>
-      <c r="O15" s="55" t="n"/>
-      <c r="P15" s="55" t="n"/>
-      <c r="Q15" s="55" t="inlineStr">
+      <c r="O15" s="51" t="n"/>
+      <c r="P15" s="51" t="n"/>
+      <c r="Q15" s="51" t="n"/>
+      <c r="R15" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R15" s="55" t="n"/>
-      <c r="S15" s="55" t="n"/>
-      <c r="T15" s="55" t="n"/>
-      <c r="U15" s="55" t="n"/>
-      <c r="V15" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W15" s="57" t="n"/>
+      <c r="S15" s="51" t="n"/>
+      <c r="T15" s="51" t="n"/>
+      <c r="U15" s="51" t="n"/>
+      <c r="V15" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W15" s="58" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B16" s="45" t="n"/>
-      <c r="C16" s="46" t="n"/>
-      <c r="D16" s="46" t="n"/>
+      <c r="C16" s="53" t="n"/>
+      <c r="D16" s="53" t="n"/>
       <c r="E16" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F16" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G16" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G16" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H16" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I16" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J16" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K16" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L16" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N16" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O16" s="51" t="n"/>
-      <c r="P16" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M16" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N16" s="55" t="n"/>
+      <c r="O16" s="55" t="n"/>
+      <c r="P16" s="55" t="n"/>
+      <c r="Q16" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q16" s="51" t="n"/>
-      <c r="R16" s="51" t="n"/>
-      <c r="S16" s="51" t="n"/>
-      <c r="T16" s="51" t="n"/>
-      <c r="U16" s="51" t="n"/>
-      <c r="V16" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W16" s="58" t="n"/>
+      <c r="R16" s="55" t="n"/>
+      <c r="S16" s="55" t="n"/>
+      <c r="T16" s="55" t="n"/>
+      <c r="U16" s="55" t="n"/>
+      <c r="V16" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W16" s="57" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B17" s="45" t="n"/>
-      <c r="C17" s="53" t="n"/>
-      <c r="D17" s="53" t="n"/>
+      <c r="C17" s="46" t="n"/>
+      <c r="D17" s="46" t="n"/>
       <c r="E17" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F17" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G17" s="59" t="n">
-        <v>45.1</v>
+      <c r="G17" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H17" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J17" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K17" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L17" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M17" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N17" s="55" t="n"/>
-      <c r="O17" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P17" s="55" t="n"/>
-      <c r="Q17" s="55" t="n"/>
-      <c r="R17" s="55" t="n"/>
-      <c r="S17" s="55" t="n"/>
-      <c r="T17" s="55" t="n"/>
-      <c r="U17" s="55" t="n"/>
-      <c r="V17" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W17" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M17" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N17" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O17" s="51" t="n"/>
+      <c r="P17" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q17" s="51" t="n"/>
+      <c r="R17" s="51" t="n"/>
+      <c r="S17" s="51" t="n"/>
+      <c r="T17" s="51" t="n"/>
+      <c r="U17" s="51" t="n"/>
+      <c r="V17" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W17" s="58" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B18" s="45" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="53" t="n"/>
       <c r="E18" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F18" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G18" s="54" t="n">
-        <v>26.3</v>
+      <c r="G18" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H18" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I18" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J18" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K18" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L18" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M18" s="51" t="n"/>
-      <c r="N18" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M18" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N18" s="55" t="n"/>
+      <c r="O18" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O18" s="51" t="n"/>
-      <c r="P18" s="51" t="n"/>
-      <c r="Q18" s="51" t="n"/>
-      <c r="R18" s="51" t="n"/>
-      <c r="S18" s="51" t="n"/>
-      <c r="T18" s="51" t="n"/>
-      <c r="U18" s="51" t="n"/>
-      <c r="V18" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W18" s="58" t="n"/>
+      <c r="P18" s="55" t="n"/>
+      <c r="Q18" s="55" t="n"/>
+      <c r="R18" s="55" t="n"/>
+      <c r="S18" s="55" t="n"/>
+      <c r="T18" s="55" t="n"/>
+      <c r="U18" s="55" t="n"/>
+      <c r="V18" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W18" s="57" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B19" s="45" t="n"/>
-      <c r="C19" s="53" t="n"/>
-      <c r="D19" s="53" t="n"/>
+      <c r="C19" s="46" t="n"/>
+      <c r="D19" s="46" t="n"/>
       <c r="E19" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F19" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G19" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H19" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J19" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K19" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L19" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M19" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M19" s="51" t="n"/>
+      <c r="N19" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N19" s="55" t="n"/>
-      <c r="O19" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P19" s="55" t="n"/>
-      <c r="Q19" s="55" t="n"/>
-      <c r="R19" s="55" t="n"/>
-      <c r="S19" s="55" t="n"/>
-      <c r="T19" s="55" t="n"/>
-      <c r="U19" s="55" t="n"/>
-      <c r="V19" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W19" s="57" t="n"/>
+      <c r="O19" s="51" t="n"/>
+      <c r="P19" s="51" t="n"/>
+      <c r="Q19" s="51" t="n"/>
+      <c r="R19" s="51" t="n"/>
+      <c r="S19" s="51" t="n"/>
+      <c r="T19" s="51" t="n"/>
+      <c r="U19" s="51" t="n"/>
+      <c r="V19" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W19" s="58" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B20" s="45" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="46" t="n"/>
+      <c r="C20" s="53" t="n"/>
+      <c r="D20" s="53" t="n"/>
       <c r="E20" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F20" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G20" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H20" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J20" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K20" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L20" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N20" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O20" s="51" t="n"/>
-      <c r="P20" s="51" t="n"/>
-      <c r="Q20" s="51" t="n"/>
-      <c r="R20" s="51" t="n"/>
-      <c r="S20" s="51" t="n"/>
-      <c r="T20" s="51" t="n"/>
-      <c r="U20" s="51" t="n"/>
-      <c r="V20" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W20" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M20" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N20" s="55" t="n"/>
+      <c r="O20" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P20" s="55" t="n"/>
+      <c r="Q20" s="55" t="n"/>
+      <c r="R20" s="55" t="n"/>
+      <c r="S20" s="55" t="n"/>
+      <c r="T20" s="55" t="n"/>
+      <c r="U20" s="55" t="n"/>
+      <c r="V20" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W20" s="57" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="53" t="n"/>
-      <c r="D21" s="53" t="n"/>
+      <c r="C21" s="46" t="n"/>
+      <c r="D21" s="46" t="n"/>
       <c r="E21" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F21" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G21" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H21" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K21" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L21" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I21" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J21" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K21" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L21" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" s="55" t="inlineStr">
+      <c r="M21" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N21" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N21" s="55" t="n"/>
-      <c r="O21" s="55" t="n"/>
-      <c r="P21" s="55" t="n"/>
-      <c r="Q21" s="55" t="n"/>
-      <c r="R21" s="55" t="n"/>
-      <c r="S21" s="55" t="n"/>
-      <c r="T21" s="55" t="n"/>
-      <c r="U21" s="55" t="n"/>
-      <c r="V21" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W21" s="57" t="n"/>
+      <c r="O21" s="51" t="n"/>
+      <c r="P21" s="51" t="n"/>
+      <c r="Q21" s="51" t="n"/>
+      <c r="R21" s="51" t="n"/>
+      <c r="S21" s="51" t="n"/>
+      <c r="T21" s="51" t="n"/>
+      <c r="U21" s="51" t="n"/>
+      <c r="V21" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W21" s="58" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="46" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
       <c r="E22" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G22" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G22" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H22" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K22" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L22" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M22" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N22" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O22" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P22" s="51" t="n"/>
-      <c r="Q22" s="51" t="n"/>
-      <c r="R22" s="51" t="n"/>
-      <c r="S22" s="51" t="n"/>
-      <c r="T22" s="51" t="n"/>
-      <c r="U22" s="51" t="n"/>
-      <c r="V22" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W22" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M22" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N22" s="55" t="n"/>
+      <c r="O22" s="55" t="n"/>
+      <c r="P22" s="55" t="n"/>
+      <c r="Q22" s="55" t="n"/>
+      <c r="R22" s="55" t="n"/>
+      <c r="S22" s="55" t="n"/>
+      <c r="T22" s="55" t="n"/>
+      <c r="U22" s="55" t="n"/>
+      <c r="V22" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W22" s="57" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="53" t="n"/>
-      <c r="D23" s="53" t="n"/>
+      <c r="C23" s="46" t="n"/>
+      <c r="D23" s="46" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G23" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G23" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H23" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L23" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M23" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N23" s="55" t="inlineStr">
+      <c r="M23" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N23" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O23" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O23" s="55" t="n"/>
-      <c r="P23" s="55" t="n"/>
-      <c r="Q23" s="55" t="n"/>
-      <c r="R23" s="55" t="n"/>
-      <c r="S23" s="55" t="n"/>
-      <c r="T23" s="55" t="n"/>
-      <c r="U23" s="55" t="n"/>
-      <c r="V23" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W23" s="57" t="n"/>
+      <c r="P23" s="51" t="n"/>
+      <c r="Q23" s="51" t="n"/>
+      <c r="R23" s="51" t="n"/>
+      <c r="S23" s="51" t="n"/>
+      <c r="T23" s="51" t="n"/>
+      <c r="U23" s="51" t="n"/>
+      <c r="V23" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W23" s="58" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G24" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H24" s="49" t="n">
         <v>2</v>
@@ -3099,208 +3099,218 @@
         <v>2</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K24" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L24" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M24" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M24" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N24" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N24" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O24" s="51" t="n"/>
-      <c r="P24" s="51" t="n"/>
-      <c r="Q24" s="51" t="n"/>
-      <c r="R24" s="51" t="n"/>
-      <c r="S24" s="51" t="n"/>
-      <c r="T24" s="51" t="n"/>
-      <c r="U24" s="51" t="n"/>
-      <c r="V24" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W24" s="58" t="n"/>
+      <c r="O24" s="55" t="n"/>
+      <c r="P24" s="55" t="n"/>
+      <c r="Q24" s="55" t="n"/>
+      <c r="R24" s="55" t="n"/>
+      <c r="S24" s="55" t="n"/>
+      <c r="T24" s="55" t="n"/>
+      <c r="U24" s="55" t="n"/>
+      <c r="V24" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W24" s="57" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="53" t="n"/>
-      <c r="D25" s="53" t="n"/>
+      <c r="C25" s="46" t="n"/>
+      <c r="D25" s="46" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G25" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H25" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L25" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M25" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M25" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N25" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N25" s="55" t="n"/>
-      <c r="O25" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P25" s="55" t="n"/>
-      <c r="Q25" s="55" t="n"/>
-      <c r="R25" s="55" t="n"/>
-      <c r="S25" s="55" t="n"/>
-      <c r="T25" s="55" t="n"/>
-      <c r="U25" s="55" t="n"/>
-      <c r="V25" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W25" s="57" t="n"/>
+      <c r="O25" s="51" t="n"/>
+      <c r="P25" s="51" t="n"/>
+      <c r="Q25" s="51" t="n"/>
+      <c r="R25" s="51" t="n"/>
+      <c r="S25" s="51" t="n"/>
+      <c r="T25" s="51" t="n"/>
+      <c r="U25" s="51" t="n"/>
+      <c r="V25" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W25" s="58" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="46" t="n"/>
-      <c r="D26" s="46" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G26" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G26" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H26" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I26" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L26" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M26" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N26" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O26" s="51" t="n"/>
-      <c r="P26" s="51" t="n"/>
-      <c r="Q26" s="51" t="n"/>
-      <c r="R26" s="51" t="n"/>
-      <c r="S26" s="51" t="n"/>
-      <c r="T26" s="51" t="n"/>
-      <c r="U26" s="51" t="n"/>
-      <c r="V26" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W26" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M26" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N26" s="55" t="n"/>
+      <c r="O26" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P26" s="55" t="n"/>
+      <c r="Q26" s="55" t="n"/>
+      <c r="R26" s="55" t="n"/>
+      <c r="S26" s="55" t="n"/>
+      <c r="T26" s="55" t="n"/>
+      <c r="U26" s="55" t="n"/>
+      <c r="V26" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W26" s="57" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="53" t="n"/>
-      <c r="D27" s="53" t="n"/>
+      <c r="C27" s="46" t="n"/>
+      <c r="D27" s="46" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G27" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G27" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H27" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L27" s="50" t="n"/>
-      <c r="M27" s="55" t="n"/>
-      <c r="N27" s="55" t="n"/>
-      <c r="O27" s="55" t="n"/>
-      <c r="P27" s="55" t="n"/>
-      <c r="Q27" s="55" t="n"/>
-      <c r="R27" s="55" t="n"/>
-      <c r="S27" s="55" t="n"/>
-      <c r="T27" s="55" t="n"/>
-      <c r="U27" s="55" t="n"/>
-      <c r="V27" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W27" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L27" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M27" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N27" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O27" s="51" t="n"/>
+      <c r="P27" s="51" t="n"/>
+      <c r="Q27" s="51" t="n"/>
+      <c r="R27" s="51" t="n"/>
+      <c r="S27" s="51" t="n"/>
+      <c r="T27" s="51" t="n"/>
+      <c r="U27" s="51" t="n"/>
+      <c r="V27" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W27" s="58" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="46" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="53" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G28" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H28" s="49" t="n">
         <v>0</v>
@@ -3309,43 +3319,43 @@
         <v>0</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L28" s="50" t="n"/>
-      <c r="M28" s="51" t="n"/>
-      <c r="N28" s="51" t="n"/>
-      <c r="O28" s="51" t="n"/>
-      <c r="P28" s="51" t="n"/>
-      <c r="Q28" s="51" t="n"/>
-      <c r="R28" s="51" t="n"/>
-      <c r="S28" s="51" t="n"/>
-      <c r="T28" s="51" t="n"/>
-      <c r="U28" s="51" t="n"/>
-      <c r="V28" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W28" s="58" t="n"/>
+      <c r="M28" s="55" t="n"/>
+      <c r="N28" s="55" t="n"/>
+      <c r="O28" s="55" t="n"/>
+      <c r="P28" s="55" t="n"/>
+      <c r="Q28" s="55" t="n"/>
+      <c r="R28" s="55" t="n"/>
+      <c r="S28" s="55" t="n"/>
+      <c r="T28" s="55" t="n"/>
+      <c r="U28" s="55" t="n"/>
+      <c r="V28" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W28" s="57" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="53" t="n"/>
-      <c r="D29" s="53" t="n"/>
+      <c r="C29" s="46" t="n"/>
+      <c r="D29" s="46" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G29" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H29" s="49" t="n">
         <v>0</v>
@@ -3354,43 +3364,43 @@
         <v>0</v>
       </c>
       <c r="J29" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L29" s="50" t="n"/>
-      <c r="M29" s="55" t="n"/>
-      <c r="N29" s="55" t="n"/>
-      <c r="O29" s="55" t="n"/>
-      <c r="P29" s="55" t="n"/>
-      <c r="Q29" s="55" t="n"/>
-      <c r="R29" s="55" t="n"/>
-      <c r="S29" s="55" t="n"/>
-      <c r="T29" s="55" t="n"/>
-      <c r="U29" s="55" t="n"/>
-      <c r="V29" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W29" s="57" t="n"/>
+      <c r="M29" s="51" t="n"/>
+      <c r="N29" s="51" t="n"/>
+      <c r="O29" s="51" t="n"/>
+      <c r="P29" s="51" t="n"/>
+      <c r="Q29" s="51" t="n"/>
+      <c r="R29" s="51" t="n"/>
+      <c r="S29" s="51" t="n"/>
+      <c r="T29" s="51" t="n"/>
+      <c r="U29" s="51" t="n"/>
+      <c r="V29" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W29" s="58" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="46" t="n"/>
-      <c r="D30" s="46" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="53" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G30" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G30" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H30" s="49" t="n">
         <v>0</v>
@@ -3399,43 +3409,43 @@
         <v>0</v>
       </c>
       <c r="J30" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L30" s="50" t="n"/>
-      <c r="M30" s="51" t="n"/>
-      <c r="N30" s="51" t="n"/>
-      <c r="O30" s="51" t="n"/>
-      <c r="P30" s="51" t="n"/>
-      <c r="Q30" s="51" t="n"/>
-      <c r="R30" s="51" t="n"/>
-      <c r="S30" s="51" t="n"/>
-      <c r="T30" s="51" t="n"/>
-      <c r="U30" s="51" t="n"/>
-      <c r="V30" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W30" s="58" t="n"/>
+      <c r="M30" s="55" t="n"/>
+      <c r="N30" s="55" t="n"/>
+      <c r="O30" s="55" t="n"/>
+      <c r="P30" s="55" t="n"/>
+      <c r="Q30" s="55" t="n"/>
+      <c r="R30" s="55" t="n"/>
+      <c r="S30" s="55" t="n"/>
+      <c r="T30" s="55" t="n"/>
+      <c r="U30" s="55" t="n"/>
+      <c r="V30" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W30" s="57" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="53" t="n"/>
-      <c r="D31" s="53" t="n"/>
+      <c r="C31" s="46" t="n"/>
+      <c r="D31" s="46" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G31" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H31" s="49" t="n">
         <v>0</v>
@@ -3444,43 +3454,43 @@
         <v>0</v>
       </c>
       <c r="J31" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L31" s="50" t="n"/>
-      <c r="M31" s="55" t="n"/>
-      <c r="N31" s="55" t="n"/>
-      <c r="O31" s="55" t="n"/>
-      <c r="P31" s="55" t="n"/>
-      <c r="Q31" s="55" t="n"/>
-      <c r="R31" s="55" t="n"/>
-      <c r="S31" s="55" t="n"/>
-      <c r="T31" s="55" t="n"/>
-      <c r="U31" s="55" t="n"/>
-      <c r="V31" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W31" s="57" t="n"/>
+      <c r="M31" s="51" t="n"/>
+      <c r="N31" s="51" t="n"/>
+      <c r="O31" s="51" t="n"/>
+      <c r="P31" s="51" t="n"/>
+      <c r="Q31" s="51" t="n"/>
+      <c r="R31" s="51" t="n"/>
+      <c r="S31" s="51" t="n"/>
+      <c r="T31" s="51" t="n"/>
+      <c r="U31" s="51" t="n"/>
+      <c r="V31" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W31" s="58" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="46" t="n"/>
-      <c r="D32" s="46" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G32" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H32" s="49" t="n">
         <v>0</v>
@@ -3489,1371 +3499,1375 @@
         <v>0</v>
       </c>
       <c r="J32" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L32" s="50" t="n"/>
-      <c r="M32" s="51" t="n"/>
-      <c r="N32" s="51" t="n"/>
-      <c r="O32" s="51" t="n"/>
-      <c r="P32" s="51" t="n"/>
-      <c r="Q32" s="51" t="n"/>
-      <c r="R32" s="51" t="n"/>
-      <c r="S32" s="51" t="n"/>
-      <c r="T32" s="51" t="n"/>
-      <c r="U32" s="51" t="n"/>
-      <c r="V32" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W32" s="58" t="n"/>
+      <c r="M32" s="55" t="n"/>
+      <c r="N32" s="55" t="n"/>
+      <c r="O32" s="55" t="n"/>
+      <c r="P32" s="55" t="n"/>
+      <c r="Q32" s="55" t="n"/>
+      <c r="R32" s="55" t="n"/>
+      <c r="S32" s="55" t="n"/>
+      <c r="T32" s="55" t="n"/>
+      <c r="U32" s="55" t="n"/>
+      <c r="V32" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W32" s="57" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="53" t="n"/>
-      <c r="D33" s="53" t="n"/>
+      <c r="C33" s="46" t="n"/>
+      <c r="D33" s="46" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G33" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H33" s="49" t="n"/>
-      <c r="I33" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G33" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H33" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J33" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L33" s="50" t="n"/>
-      <c r="M33" s="55" t="n"/>
-      <c r="N33" s="55" t="n"/>
-      <c r="O33" s="55" t="n"/>
-      <c r="P33" s="55" t="n"/>
-      <c r="Q33" s="55" t="n"/>
-      <c r="R33" s="55" t="n"/>
-      <c r="S33" s="55" t="n"/>
-      <c r="T33" s="55" t="n"/>
-      <c r="U33" s="55" t="n"/>
-      <c r="V33" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W33" s="57" t="n"/>
+      <c r="M33" s="51" t="n"/>
+      <c r="N33" s="51" t="n"/>
+      <c r="O33" s="51" t="n"/>
+      <c r="P33" s="51" t="n"/>
+      <c r="Q33" s="51" t="n"/>
+      <c r="R33" s="51" t="n"/>
+      <c r="S33" s="51" t="n"/>
+      <c r="T33" s="51" t="n"/>
+      <c r="U33" s="51" t="n"/>
+      <c r="V33" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W33" s="58" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="46" t="n"/>
-      <c r="D34" s="46" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G34" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H34" s="49" t="n"/>
       <c r="I34" s="49" t="n"/>
       <c r="J34" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L34" s="50" t="n"/>
-      <c r="M34" s="51" t="n"/>
-      <c r="N34" s="51" t="n"/>
-      <c r="O34" s="51" t="n"/>
-      <c r="P34" s="51" t="n"/>
-      <c r="Q34" s="51" t="n"/>
-      <c r="R34" s="51" t="n"/>
-      <c r="S34" s="51" t="n"/>
-      <c r="T34" s="51" t="n"/>
-      <c r="U34" s="51" t="n"/>
-      <c r="V34" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W34" s="58" t="n"/>
+      <c r="M34" s="55" t="n"/>
+      <c r="N34" s="55" t="n"/>
+      <c r="O34" s="55" t="n"/>
+      <c r="P34" s="55" t="n"/>
+      <c r="Q34" s="55" t="n"/>
+      <c r="R34" s="55" t="n"/>
+      <c r="S34" s="55" t="n"/>
+      <c r="T34" s="55" t="n"/>
+      <c r="U34" s="55" t="n"/>
+      <c r="V34" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W34" s="57" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="53" t="n"/>
-      <c r="D35" s="53" t="n"/>
+      <c r="C35" s="46" t="n"/>
+      <c r="D35" s="46" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G35" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H35" s="49" t="n"/>
       <c r="I35" s="49" t="n"/>
       <c r="J35" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L35" s="50" t="n"/>
-      <c r="M35" s="55" t="n"/>
-      <c r="N35" s="55" t="n"/>
-      <c r="O35" s="55" t="n"/>
-      <c r="P35" s="55" t="n"/>
-      <c r="Q35" s="55" t="n"/>
-      <c r="R35" s="55" t="n"/>
-      <c r="S35" s="55" t="n"/>
-      <c r="T35" s="55" t="n"/>
-      <c r="U35" s="55" t="n"/>
-      <c r="V35" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W35" s="57" t="n"/>
+      <c r="M35" s="51" t="n"/>
+      <c r="N35" s="51" t="n"/>
+      <c r="O35" s="51" t="n"/>
+      <c r="P35" s="51" t="n"/>
+      <c r="Q35" s="51" t="n"/>
+      <c r="R35" s="51" t="n"/>
+      <c r="S35" s="51" t="n"/>
+      <c r="T35" s="51" t="n"/>
+      <c r="U35" s="51" t="n"/>
+      <c r="V35" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W35" s="58" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
+      <c r="C36" s="53" t="n"/>
+      <c r="D36" s="53" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G36" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H36" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I36" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H36" s="49" t="n"/>
+      <c r="I36" s="49" t="n"/>
       <c r="J36" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="51" t="n"/>
-      <c r="N36" s="51" t="n"/>
-      <c r="O36" s="51" t="n"/>
-      <c r="P36" s="51" t="n"/>
-      <c r="Q36" s="51" t="n"/>
-      <c r="R36" s="51" t="n"/>
-      <c r="S36" s="51" t="n"/>
-      <c r="T36" s="51" t="n"/>
-      <c r="U36" s="51" t="n"/>
-      <c r="V36" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W36" s="58" t="n"/>
+      <c r="M36" s="55" t="n"/>
+      <c r="N36" s="55" t="n"/>
+      <c r="O36" s="55" t="n"/>
+      <c r="P36" s="55" t="n"/>
+      <c r="Q36" s="55" t="n"/>
+      <c r="R36" s="55" t="n"/>
+      <c r="S36" s="55" t="n"/>
+      <c r="T36" s="55" t="n"/>
+      <c r="U36" s="55" t="n"/>
+      <c r="V36" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W36" s="57" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="53" t="n"/>
-      <c r="D37" s="53" t="n"/>
+      <c r="C37" s="46" t="n"/>
+      <c r="D37" s="46" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G37" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H37" s="49" t="n"/>
-      <c r="I37" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G37" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H37" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I37" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J37" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="55" t="n"/>
-      <c r="N37" s="55" t="n"/>
-      <c r="O37" s="55" t="n"/>
-      <c r="P37" s="55" t="n"/>
-      <c r="Q37" s="55" t="n"/>
-      <c r="R37" s="55" t="n"/>
-      <c r="S37" s="55" t="n"/>
-      <c r="T37" s="55" t="n"/>
-      <c r="U37" s="55" t="n"/>
-      <c r="V37" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W37" s="57" t="n"/>
+      <c r="M37" s="51" t="n"/>
+      <c r="N37" s="51" t="n"/>
+      <c r="O37" s="51" t="n"/>
+      <c r="P37" s="51" t="n"/>
+      <c r="Q37" s="51" t="n"/>
+      <c r="R37" s="51" t="n"/>
+      <c r="S37" s="51" t="n"/>
+      <c r="T37" s="51" t="n"/>
+      <c r="U37" s="51" t="n"/>
+      <c r="V37" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W37" s="58" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="46" t="n"/>
-      <c r="D38" s="46" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G38" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G38" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H38" s="49" t="n"/>
       <c r="I38" s="49" t="n"/>
       <c r="J38" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="51" t="n"/>
-      <c r="N38" s="51" t="n"/>
-      <c r="O38" s="51" t="n"/>
-      <c r="P38" s="51" t="n"/>
-      <c r="Q38" s="51" t="n"/>
-      <c r="R38" s="51" t="n"/>
-      <c r="S38" s="51" t="n"/>
-      <c r="T38" s="51" t="n"/>
-      <c r="U38" s="51" t="n"/>
-      <c r="V38" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W38" s="58" t="n"/>
+      <c r="M38" s="55" t="n"/>
+      <c r="N38" s="55" t="n"/>
+      <c r="O38" s="55" t="n"/>
+      <c r="P38" s="55" t="n"/>
+      <c r="Q38" s="55" t="n"/>
+      <c r="R38" s="55" t="n"/>
+      <c r="S38" s="55" t="n"/>
+      <c r="T38" s="55" t="n"/>
+      <c r="U38" s="55" t="n"/>
+      <c r="V38" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W38" s="57" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="53" t="n"/>
-      <c r="D39" s="53" t="n"/>
+      <c r="C39" s="46" t="n"/>
+      <c r="D39" s="46" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G39" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G39" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H39" s="49" t="n"/>
       <c r="I39" s="49" t="n"/>
       <c r="J39" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K39" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K39" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="55" t="n"/>
-      <c r="N39" s="55" t="n"/>
-      <c r="O39" s="55" t="n"/>
-      <c r="P39" s="55" t="n"/>
-      <c r="Q39" s="55" t="n"/>
-      <c r="R39" s="55" t="n"/>
-      <c r="S39" s="55" t="n"/>
-      <c r="T39" s="55" t="n"/>
-      <c r="U39" s="55" t="n"/>
-      <c r="V39" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W39" s="57" t="n"/>
+      <c r="M39" s="51" t="n"/>
+      <c r="N39" s="51" t="n"/>
+      <c r="O39" s="51" t="n"/>
+      <c r="P39" s="51" t="n"/>
+      <c r="Q39" s="51" t="n"/>
+      <c r="R39" s="51" t="n"/>
+      <c r="S39" s="51" t="n"/>
+      <c r="T39" s="51" t="n"/>
+      <c r="U39" s="51" t="n"/>
+      <c r="V39" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W39" s="58" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="46" t="n"/>
-      <c r="D40" s="46" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G40" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H40" s="49" t="n"/>
       <c r="I40" s="49" t="n"/>
       <c r="J40" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="51" t="n"/>
-      <c r="N40" s="51" t="n"/>
-      <c r="O40" s="51" t="n"/>
-      <c r="P40" s="51" t="n"/>
-      <c r="Q40" s="51" t="n"/>
-      <c r="R40" s="51" t="n"/>
-      <c r="S40" s="51" t="n"/>
-      <c r="T40" s="51" t="n"/>
-      <c r="U40" s="51" t="n"/>
-      <c r="V40" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W40" s="58" t="n"/>
+      <c r="M40" s="55" t="n"/>
+      <c r="N40" s="55" t="n"/>
+      <c r="O40" s="55" t="n"/>
+      <c r="P40" s="55" t="n"/>
+      <c r="Q40" s="55" t="n"/>
+      <c r="R40" s="55" t="n"/>
+      <c r="S40" s="55" t="n"/>
+      <c r="T40" s="55" t="n"/>
+      <c r="U40" s="55" t="n"/>
+      <c r="V40" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W40" s="57" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="53" t="n"/>
-      <c r="D41" s="53" t="n"/>
+      <c r="C41" s="46" t="n"/>
+      <c r="D41" s="46" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G41" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G41" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H41" s="49" t="n"/>
       <c r="I41" s="49" t="n"/>
       <c r="J41" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="55" t="n"/>
-      <c r="N41" s="55" t="n"/>
-      <c r="O41" s="55" t="n"/>
-      <c r="P41" s="55" t="n"/>
-      <c r="Q41" s="55" t="n"/>
-      <c r="R41" s="55" t="n"/>
-      <c r="S41" s="55" t="n"/>
-      <c r="T41" s="55" t="n"/>
-      <c r="U41" s="55" t="n"/>
-      <c r="V41" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W41" s="57" t="n"/>
+      <c r="M41" s="51" t="n"/>
+      <c r="N41" s="51" t="n"/>
+      <c r="O41" s="51" t="n"/>
+      <c r="P41" s="51" t="n"/>
+      <c r="Q41" s="51" t="n"/>
+      <c r="R41" s="51" t="n"/>
+      <c r="S41" s="51" t="n"/>
+      <c r="T41" s="51" t="n"/>
+      <c r="U41" s="51" t="n"/>
+      <c r="V41" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W41" s="58" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="46" t="n"/>
-      <c r="D42" s="46" t="n"/>
+      <c r="C42" s="53" t="n"/>
+      <c r="D42" s="53" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G42" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H42" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I42" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G42" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H42" s="49" t="n"/>
+      <c r="I42" s="49" t="n"/>
       <c r="J42" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K42" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="51" t="n"/>
-      <c r="N42" s="51" t="n"/>
-      <c r="O42" s="51" t="n"/>
-      <c r="P42" s="51" t="n"/>
-      <c r="Q42" s="51" t="n"/>
-      <c r="R42" s="51" t="n"/>
-      <c r="S42" s="51" t="n"/>
-      <c r="T42" s="51" t="n"/>
-      <c r="U42" s="51" t="n"/>
-      <c r="V42" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W42" s="58" t="n"/>
+      <c r="M42" s="55" t="n"/>
+      <c r="N42" s="55" t="n"/>
+      <c r="O42" s="55" t="n"/>
+      <c r="P42" s="55" t="n"/>
+      <c r="Q42" s="55" t="n"/>
+      <c r="R42" s="55" t="n"/>
+      <c r="S42" s="55" t="n"/>
+      <c r="T42" s="55" t="n"/>
+      <c r="U42" s="55" t="n"/>
+      <c r="V42" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W42" s="57" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="53" t="n"/>
-      <c r="D43" s="53" t="n"/>
+      <c r="C43" s="46" t="n"/>
+      <c r="D43" s="46" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G43" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H43" s="49" t="n"/>
-      <c r="I43" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H43" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I43" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J43" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K43" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="55" t="n"/>
-      <c r="N43" s="55" t="n"/>
-      <c r="O43" s="55" t="n"/>
-      <c r="P43" s="55" t="n"/>
-      <c r="Q43" s="55" t="n"/>
-      <c r="R43" s="55" t="n"/>
-      <c r="S43" s="55" t="n"/>
-      <c r="T43" s="55" t="n"/>
-      <c r="U43" s="55" t="n"/>
-      <c r="V43" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W43" s="57" t="n"/>
+      <c r="M43" s="51" t="n"/>
+      <c r="N43" s="51" t="n"/>
+      <c r="O43" s="51" t="n"/>
+      <c r="P43" s="51" t="n"/>
+      <c r="Q43" s="51" t="n"/>
+      <c r="R43" s="51" t="n"/>
+      <c r="S43" s="51" t="n"/>
+      <c r="T43" s="51" t="n"/>
+      <c r="U43" s="51" t="n"/>
+      <c r="V43" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W43" s="58" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="46" t="n"/>
-      <c r="D44" s="46" t="n"/>
+      <c r="C44" s="53" t="n"/>
+      <c r="D44" s="53" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G44" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H44" s="49" t="n"/>
       <c r="I44" s="49" t="n"/>
       <c r="J44" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K44" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="51" t="n"/>
-      <c r="N44" s="51" t="n"/>
-      <c r="O44" s="51" t="n"/>
-      <c r="P44" s="51" t="n"/>
-      <c r="Q44" s="51" t="n"/>
-      <c r="R44" s="51" t="n"/>
-      <c r="S44" s="51" t="n"/>
-      <c r="T44" s="51" t="n"/>
-      <c r="U44" s="51" t="n"/>
-      <c r="V44" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W44" s="58" t="n"/>
+      <c r="M44" s="55" t="n"/>
+      <c r="N44" s="55" t="n"/>
+      <c r="O44" s="55" t="n"/>
+      <c r="P44" s="55" t="n"/>
+      <c r="Q44" s="55" t="n"/>
+      <c r="R44" s="55" t="n"/>
+      <c r="S44" s="55" t="n"/>
+      <c r="T44" s="55" t="n"/>
+      <c r="U44" s="55" t="n"/>
+      <c r="V44" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W44" s="57" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="53" t="n"/>
-      <c r="D45" s="53" t="n"/>
+      <c r="C45" s="46" t="n"/>
+      <c r="D45" s="46" t="n"/>
       <c r="E45" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F45" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G45" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H45" s="49" t="n"/>
+      <c r="I45" s="49" t="n"/>
+      <c r="J45" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F45" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G45" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H45" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I45" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J45" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K45" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="55" t="n"/>
-      <c r="N45" s="55" t="n"/>
-      <c r="O45" s="55" t="n"/>
-      <c r="P45" s="55" t="n"/>
-      <c r="Q45" s="55" t="n"/>
-      <c r="R45" s="55" t="n"/>
-      <c r="S45" s="55" t="n"/>
-      <c r="T45" s="55" t="n"/>
-      <c r="U45" s="55" t="n"/>
-      <c r="V45" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W45" s="57" t="n"/>
+      <c r="M45" s="51" t="n"/>
+      <c r="N45" s="51" t="n"/>
+      <c r="O45" s="51" t="n"/>
+      <c r="P45" s="51" t="n"/>
+      <c r="Q45" s="51" t="n"/>
+      <c r="R45" s="51" t="n"/>
+      <c r="S45" s="51" t="n"/>
+      <c r="T45" s="51" t="n"/>
+      <c r="U45" s="51" t="n"/>
+      <c r="V45" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W45" s="58" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="46" t="n"/>
-      <c r="D46" s="46" t="n"/>
+      <c r="C46" s="53" t="n"/>
+      <c r="D46" s="53" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G46" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H46" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I46" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J46" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K46" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="51" t="n"/>
-      <c r="N46" s="51" t="n"/>
-      <c r="O46" s="51" t="n"/>
-      <c r="P46" s="51" t="n"/>
-      <c r="Q46" s="51" t="n"/>
-      <c r="R46" s="51" t="n"/>
-      <c r="S46" s="51" t="n"/>
-      <c r="T46" s="51" t="n"/>
-      <c r="U46" s="51" t="n"/>
-      <c r="V46" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W46" s="58" t="n"/>
+      <c r="M46" s="55" t="n"/>
+      <c r="N46" s="55" t="n"/>
+      <c r="O46" s="55" t="n"/>
+      <c r="P46" s="55" t="n"/>
+      <c r="Q46" s="55" t="n"/>
+      <c r="R46" s="55" t="n"/>
+      <c r="S46" s="55" t="n"/>
+      <c r="T46" s="55" t="n"/>
+      <c r="U46" s="55" t="n"/>
+      <c r="V46" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W46" s="57" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="53" t="n"/>
-      <c r="D47" s="53" t="n"/>
+      <c r="C47" s="46" t="n"/>
+      <c r="D47" s="46" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G47" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H47" s="49" t="n"/>
-      <c r="I47" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H47" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I47" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J47" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K47" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="55" t="n"/>
-      <c r="N47" s="55" t="n"/>
-      <c r="O47" s="55" t="n"/>
-      <c r="P47" s="55" t="n"/>
-      <c r="Q47" s="55" t="n"/>
-      <c r="R47" s="55" t="n"/>
-      <c r="S47" s="55" t="n"/>
-      <c r="T47" s="55" t="n"/>
-      <c r="U47" s="55" t="n"/>
-      <c r="V47" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W47" s="57" t="n"/>
+      <c r="M47" s="51" t="n"/>
+      <c r="N47" s="51" t="n"/>
+      <c r="O47" s="51" t="n"/>
+      <c r="P47" s="51" t="n"/>
+      <c r="Q47" s="51" t="n"/>
+      <c r="R47" s="51" t="n"/>
+      <c r="S47" s="51" t="n"/>
+      <c r="T47" s="51" t="n"/>
+      <c r="U47" s="51" t="n"/>
+      <c r="V47" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W47" s="58" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
+      <c r="C48" s="53" t="n"/>
+      <c r="D48" s="53" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G48" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G48" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H48" s="49" t="n"/>
       <c r="I48" s="49" t="n"/>
       <c r="J48" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K48" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="51" t="n"/>
-      <c r="N48" s="51" t="n"/>
-      <c r="O48" s="51" t="n"/>
-      <c r="P48" s="51" t="n"/>
-      <c r="Q48" s="51" t="n"/>
-      <c r="R48" s="51" t="n"/>
-      <c r="S48" s="51" t="n"/>
-      <c r="T48" s="51" t="n"/>
-      <c r="U48" s="51" t="n"/>
-      <c r="V48" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W48" s="58" t="n"/>
+      <c r="M48" s="55" t="n"/>
+      <c r="N48" s="55" t="n"/>
+      <c r="O48" s="55" t="n"/>
+      <c r="P48" s="55" t="n"/>
+      <c r="Q48" s="55" t="n"/>
+      <c r="R48" s="55" t="n"/>
+      <c r="S48" s="55" t="n"/>
+      <c r="T48" s="55" t="n"/>
+      <c r="U48" s="55" t="n"/>
+      <c r="V48" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W48" s="57" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="53" t="n"/>
-      <c r="D49" s="53" t="n"/>
+      <c r="C49" s="46" t="n"/>
+      <c r="D49" s="46" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G49" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G49" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H49" s="49" t="n"/>
       <c r="I49" s="49" t="n"/>
       <c r="J49" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K49" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="55" t="n"/>
-      <c r="N49" s="55" t="n"/>
-      <c r="O49" s="55" t="n"/>
-      <c r="P49" s="55" t="n"/>
-      <c r="Q49" s="55" t="n"/>
-      <c r="R49" s="55" t="n"/>
-      <c r="S49" s="55" t="n"/>
-      <c r="T49" s="55" t="n"/>
-      <c r="U49" s="55" t="n"/>
-      <c r="V49" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W49" s="57" t="n"/>
+      <c r="M49" s="51" t="n"/>
+      <c r="N49" s="51" t="n"/>
+      <c r="O49" s="51" t="n"/>
+      <c r="P49" s="51" t="n"/>
+      <c r="Q49" s="51" t="n"/>
+      <c r="R49" s="51" t="n"/>
+      <c r="S49" s="51" t="n"/>
+      <c r="T49" s="51" t="n"/>
+      <c r="U49" s="51" t="n"/>
+      <c r="V49" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W49" s="58" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
+      <c r="C50" s="53" t="n"/>
+      <c r="D50" s="53" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G50" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="49" t="n"/>
       <c r="J50" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="51" t="n"/>
-      <c r="N50" s="51" t="n"/>
-      <c r="O50" s="51" t="n"/>
-      <c r="P50" s="51" t="n"/>
-      <c r="Q50" s="51" t="n"/>
-      <c r="R50" s="51" t="n"/>
-      <c r="S50" s="51" t="n"/>
-      <c r="T50" s="51" t="n"/>
-      <c r="U50" s="51" t="n"/>
-      <c r="V50" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W50" s="58" t="n"/>
+      <c r="M50" s="55" t="n"/>
+      <c r="N50" s="55" t="n"/>
+      <c r="O50" s="55" t="n"/>
+      <c r="P50" s="55" t="n"/>
+      <c r="Q50" s="55" t="n"/>
+      <c r="R50" s="55" t="n"/>
+      <c r="S50" s="55" t="n"/>
+      <c r="T50" s="55" t="n"/>
+      <c r="U50" s="55" t="n"/>
+      <c r="V50" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W50" s="57" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="53" t="n"/>
-      <c r="D51" s="53" t="n"/>
+      <c r="C51" s="46" t="n"/>
+      <c r="D51" s="46" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G51" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G51" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H51" s="49" t="n"/>
       <c r="I51" s="49" t="n"/>
       <c r="J51" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="55" t="n"/>
-      <c r="N51" s="55" t="n"/>
-      <c r="O51" s="55" t="n"/>
-      <c r="P51" s="55" t="n"/>
-      <c r="Q51" s="55" t="n"/>
-      <c r="R51" s="55" t="n"/>
-      <c r="S51" s="55" t="n"/>
-      <c r="T51" s="55" t="n"/>
-      <c r="U51" s="55" t="n"/>
-      <c r="V51" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W51" s="57" t="n"/>
+      <c r="M51" s="51" t="n"/>
+      <c r="N51" s="51" t="n"/>
+      <c r="O51" s="51" t="n"/>
+      <c r="P51" s="51" t="n"/>
+      <c r="Q51" s="51" t="n"/>
+      <c r="R51" s="51" t="n"/>
+      <c r="S51" s="51" t="n"/>
+      <c r="T51" s="51" t="n"/>
+      <c r="U51" s="51" t="n"/>
+      <c r="V51" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W51" s="58" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="46" t="n"/>
-      <c r="D52" s="46" t="n"/>
+      <c r="C52" s="53" t="n"/>
+      <c r="D52" s="53" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G52" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G52" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H52" s="49" t="n"/>
       <c r="I52" s="49" t="n"/>
       <c r="J52" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="51" t="n"/>
-      <c r="N52" s="51" t="n"/>
-      <c r="O52" s="51" t="n"/>
-      <c r="P52" s="51" t="n"/>
-      <c r="Q52" s="51" t="n"/>
-      <c r="R52" s="51" t="n"/>
-      <c r="S52" s="51" t="n"/>
-      <c r="T52" s="51" t="n"/>
-      <c r="U52" s="51" t="n"/>
-      <c r="V52" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W52" s="58" t="n"/>
+      <c r="M52" s="55" t="n"/>
+      <c r="N52" s="55" t="n"/>
+      <c r="O52" s="55" t="n"/>
+      <c r="P52" s="55" t="n"/>
+      <c r="Q52" s="55" t="n"/>
+      <c r="R52" s="55" t="n"/>
+      <c r="S52" s="55" t="n"/>
+      <c r="T52" s="55" t="n"/>
+      <c r="U52" s="55" t="n"/>
+      <c r="V52" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W52" s="57" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="53" t="n"/>
-      <c r="D53" s="53" t="n"/>
+      <c r="C53" s="46" t="n"/>
+      <c r="D53" s="46" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G53" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G53" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H53" s="49" t="n"/>
       <c r="I53" s="49" t="n"/>
       <c r="J53" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="55" t="n"/>
-      <c r="N53" s="55" t="n"/>
-      <c r="O53" s="55" t="n"/>
-      <c r="P53" s="55" t="n"/>
-      <c r="Q53" s="55" t="n"/>
-      <c r="R53" s="55" t="n"/>
-      <c r="S53" s="55" t="n"/>
-      <c r="T53" s="55" t="n"/>
-      <c r="U53" s="55" t="n"/>
-      <c r="V53" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W53" s="57" t="n"/>
+      <c r="M53" s="51" t="n"/>
+      <c r="N53" s="51" t="n"/>
+      <c r="O53" s="51" t="n"/>
+      <c r="P53" s="51" t="n"/>
+      <c r="Q53" s="51" t="n"/>
+      <c r="R53" s="51" t="n"/>
+      <c r="S53" s="51" t="n"/>
+      <c r="T53" s="51" t="n"/>
+      <c r="U53" s="51" t="n"/>
+      <c r="V53" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W53" s="58" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="46" t="n"/>
-      <c r="D54" s="46" t="n"/>
+      <c r="C54" s="53" t="n"/>
+      <c r="D54" s="53" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G54" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="51" t="n"/>
-      <c r="N54" s="51" t="n"/>
-      <c r="O54" s="51" t="n"/>
-      <c r="P54" s="51" t="n"/>
-      <c r="Q54" s="51" t="n"/>
-      <c r="R54" s="51" t="n"/>
-      <c r="S54" s="51" t="n"/>
-      <c r="T54" s="51" t="n"/>
-      <c r="U54" s="51" t="n"/>
-      <c r="V54" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W54" s="58" t="n"/>
+      <c r="M54" s="55" t="n"/>
+      <c r="N54" s="55" t="n"/>
+      <c r="O54" s="55" t="n"/>
+      <c r="P54" s="55" t="n"/>
+      <c r="Q54" s="55" t="n"/>
+      <c r="R54" s="55" t="n"/>
+      <c r="S54" s="55" t="n"/>
+      <c r="T54" s="55" t="n"/>
+      <c r="U54" s="55" t="n"/>
+      <c r="V54" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W54" s="57" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="53" t="n"/>
-      <c r="D55" s="53" t="n"/>
+      <c r="C55" s="46" t="n"/>
+      <c r="D55" s="46" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G55" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="55" t="n"/>
-      <c r="N55" s="55" t="n"/>
-      <c r="O55" s="55" t="n"/>
-      <c r="P55" s="55" t="n"/>
-      <c r="Q55" s="55" t="n"/>
-      <c r="R55" s="55" t="n"/>
-      <c r="S55" s="55" t="n"/>
-      <c r="T55" s="55" t="n"/>
-      <c r="U55" s="55" t="n"/>
-      <c r="V55" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W55" s="57" t="n"/>
+      <c r="M55" s="51" t="n"/>
+      <c r="N55" s="51" t="n"/>
+      <c r="O55" s="51" t="n"/>
+      <c r="P55" s="51" t="n"/>
+      <c r="Q55" s="51" t="n"/>
+      <c r="R55" s="51" t="n"/>
+      <c r="S55" s="51" t="n"/>
+      <c r="T55" s="51" t="n"/>
+      <c r="U55" s="51" t="n"/>
+      <c r="V55" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W55" s="58" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="46" t="n"/>
-      <c r="D56" s="46" t="n"/>
+      <c r="C56" s="53" t="n"/>
+      <c r="D56" s="53" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G56" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G56" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="51" t="n"/>
-      <c r="N56" s="51" t="n"/>
-      <c r="O56" s="51" t="n"/>
-      <c r="P56" s="51" t="n"/>
-      <c r="Q56" s="51" t="n"/>
-      <c r="R56" s="51" t="n"/>
-      <c r="S56" s="51" t="n"/>
-      <c r="T56" s="51" t="n"/>
-      <c r="U56" s="51" t="n"/>
-      <c r="V56" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W56" s="58" t="n"/>
+      <c r="M56" s="55" t="n"/>
+      <c r="N56" s="55" t="n"/>
+      <c r="O56" s="55" t="n"/>
+      <c r="P56" s="55" t="n"/>
+      <c r="Q56" s="55" t="n"/>
+      <c r="R56" s="55" t="n"/>
+      <c r="S56" s="55" t="n"/>
+      <c r="T56" s="55" t="n"/>
+      <c r="U56" s="55" t="n"/>
+      <c r="V56" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W56" s="57" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="53" t="n"/>
-      <c r="D57" s="53" t="n"/>
+      <c r="C57" s="46" t="n"/>
+      <c r="D57" s="46" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G57" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G57" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="55" t="n"/>
-      <c r="N57" s="55" t="n"/>
-      <c r="O57" s="55" t="n"/>
-      <c r="P57" s="55" t="n"/>
-      <c r="Q57" s="55" t="n"/>
-      <c r="R57" s="55" t="n"/>
-      <c r="S57" s="55" t="n"/>
-      <c r="T57" s="55" t="n"/>
-      <c r="U57" s="55" t="n"/>
-      <c r="V57" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W57" s="57" t="n"/>
+      <c r="M57" s="51" t="n"/>
+      <c r="N57" s="51" t="n"/>
+      <c r="O57" s="51" t="n"/>
+      <c r="P57" s="51" t="n"/>
+      <c r="Q57" s="51" t="n"/>
+      <c r="R57" s="51" t="n"/>
+      <c r="S57" s="51" t="n"/>
+      <c r="T57" s="51" t="n"/>
+      <c r="U57" s="51" t="n"/>
+      <c r="V57" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W57" s="58" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="46" t="n"/>
-      <c r="D58" s="46" t="n"/>
+      <c r="C58" s="53" t="n"/>
+      <c r="D58" s="53" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G58" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G58" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="51" t="n"/>
-      <c r="N58" s="51" t="n"/>
-      <c r="O58" s="51" t="n"/>
-      <c r="P58" s="51" t="n"/>
-      <c r="Q58" s="51" t="n"/>
-      <c r="R58" s="51" t="n"/>
-      <c r="S58" s="51" t="n"/>
-      <c r="T58" s="51" t="n"/>
-      <c r="U58" s="51" t="n"/>
-      <c r="V58" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W58" s="58" t="n"/>
+      <c r="M58" s="55" t="n"/>
+      <c r="N58" s="55" t="n"/>
+      <c r="O58" s="55" t="n"/>
+      <c r="P58" s="55" t="n"/>
+      <c r="Q58" s="55" t="n"/>
+      <c r="R58" s="55" t="n"/>
+      <c r="S58" s="55" t="n"/>
+      <c r="T58" s="55" t="n"/>
+      <c r="U58" s="55" t="n"/>
+      <c r="V58" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W58" s="57" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="53" t="n"/>
-      <c r="D59" s="53" t="n"/>
+      <c r="C59" s="46" t="n"/>
+      <c r="D59" s="46" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G59" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G59" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="55" t="n"/>
-      <c r="N59" s="55" t="n"/>
-      <c r="O59" s="55" t="n"/>
-      <c r="P59" s="55" t="n"/>
-      <c r="Q59" s="55" t="n"/>
-      <c r="R59" s="55" t="n"/>
-      <c r="S59" s="55" t="n"/>
-      <c r="T59" s="55" t="n"/>
-      <c r="U59" s="55" t="n"/>
-      <c r="V59" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W59" s="57" t="n"/>
+      <c r="M59" s="51" t="n"/>
+      <c r="N59" s="51" t="n"/>
+      <c r="O59" s="51" t="n"/>
+      <c r="P59" s="51" t="n"/>
+      <c r="Q59" s="51" t="n"/>
+      <c r="R59" s="51" t="n"/>
+      <c r="S59" s="51" t="n"/>
+      <c r="T59" s="51" t="n"/>
+      <c r="U59" s="51" t="n"/>
+      <c r="V59" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W59" s="58" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
+      <c r="C60" s="53" t="n"/>
+      <c r="D60" s="53" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G60" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G60" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="51" t="n"/>
-      <c r="N60" s="51" t="n"/>
-      <c r="O60" s="51" t="n"/>
-      <c r="P60" s="51" t="n"/>
-      <c r="Q60" s="51" t="n"/>
-      <c r="R60" s="51" t="n"/>
-      <c r="S60" s="51" t="n"/>
-      <c r="T60" s="51" t="n"/>
-      <c r="U60" s="51" t="n"/>
-      <c r="V60" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W60" s="58" t="n"/>
+      <c r="M60" s="55" t="n"/>
+      <c r="N60" s="55" t="n"/>
+      <c r="O60" s="55" t="n"/>
+      <c r="P60" s="55" t="n"/>
+      <c r="Q60" s="55" t="n"/>
+      <c r="R60" s="55" t="n"/>
+      <c r="S60" s="55" t="n"/>
+      <c r="T60" s="55" t="n"/>
+      <c r="U60" s="55" t="n"/>
+      <c r="V60" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W60" s="57" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="53" t="n"/>
-      <c r="D61" s="53" t="n"/>
+      <c r="C61" s="46" t="n"/>
+      <c r="D61" s="46" t="n"/>
       <c r="E61" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F61" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G61" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G61" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
       <c r="J61" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K61" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="55" t="n"/>
-      <c r="N61" s="55" t="n"/>
-      <c r="O61" s="55" t="n"/>
-      <c r="P61" s="55" t="n"/>
-      <c r="Q61" s="55" t="n"/>
-      <c r="R61" s="55" t="n"/>
-      <c r="S61" s="55" t="n"/>
-      <c r="T61" s="55" t="n"/>
-      <c r="U61" s="55" t="n"/>
-      <c r="V61" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W61" s="57" t="n"/>
+      <c r="M61" s="51" t="n"/>
+      <c r="N61" s="51" t="n"/>
+      <c r="O61" s="51" t="n"/>
+      <c r="P61" s="51" t="n"/>
+      <c r="Q61" s="51" t="n"/>
+      <c r="R61" s="51" t="n"/>
+      <c r="S61" s="51" t="n"/>
+      <c r="T61" s="51" t="n"/>
+      <c r="U61" s="51" t="n"/>
+      <c r="V61" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W61" s="58" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B62" s="45" t="n"/>
-      <c r="C62" s="46" t="n"/>
-      <c r="D62" s="46" t="n"/>
+      <c r="C62" s="53" t="n"/>
+      <c r="D62" s="53" t="n"/>
       <c r="E62" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F62" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G62" s="48" t="n">
-        <v>24</v>
+      <c r="G62" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="49" t="n"/>
       <c r="J62" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K62" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L62" s="50" t="n"/>
-      <c r="M62" s="51" t="n"/>
-      <c r="N62" s="51" t="n"/>
-      <c r="O62" s="51" t="n"/>
-      <c r="P62" s="51" t="n"/>
-      <c r="Q62" s="51" t="n"/>
-      <c r="R62" s="51" t="n"/>
-      <c r="S62" s="51" t="n"/>
-      <c r="T62" s="51" t="n"/>
-      <c r="U62" s="51" t="n"/>
-      <c r="V62" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W62" s="58" t="n"/>
+      <c r="M62" s="55" t="n"/>
+      <c r="N62" s="55" t="n"/>
+      <c r="O62" s="55" t="n"/>
+      <c r="P62" s="55" t="n"/>
+      <c r="Q62" s="55" t="n"/>
+      <c r="R62" s="55" t="n"/>
+      <c r="S62" s="55" t="n"/>
+      <c r="T62" s="55" t="n"/>
+      <c r="U62" s="55" t="n"/>
+      <c r="V62" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W62" s="57" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B63" s="45" t="n"/>
-      <c r="C63" s="53" t="n"/>
-      <c r="D63" s="53" t="n"/>
+      <c r="C63" s="46" t="n"/>
+      <c r="D63" s="46" t="n"/>
       <c r="E63" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F63" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G63" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G63" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="49" t="n"/>
       <c r="J63" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K63" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L63" s="50" t="n"/>
-      <c r="M63" s="55" t="n"/>
-      <c r="N63" s="55" t="n"/>
-      <c r="O63" s="55" t="n"/>
-      <c r="P63" s="55" t="n"/>
-      <c r="Q63" s="55" t="n"/>
-      <c r="R63" s="55" t="n"/>
-      <c r="S63" s="55" t="n"/>
-      <c r="T63" s="55" t="n"/>
-      <c r="U63" s="55" t="n"/>
-      <c r="V63" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W63" s="57" t="n"/>
+      <c r="M63" s="51" t="n"/>
+      <c r="N63" s="51" t="n"/>
+      <c r="O63" s="51" t="n"/>
+      <c r="P63" s="51" t="n"/>
+      <c r="Q63" s="51" t="n"/>
+      <c r="R63" s="51" t="n"/>
+      <c r="S63" s="51" t="n"/>
+      <c r="T63" s="51" t="n"/>
+      <c r="U63" s="51" t="n"/>
+      <c r="V63" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W63" s="58" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B64" s="45" t="n"/>
-      <c r="C64" s="46" t="n"/>
-      <c r="D64" s="46" t="n"/>
+      <c r="C64" s="53" t="n"/>
+      <c r="D64" s="53" t="n"/>
       <c r="E64" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F64" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G64" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G64" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="49" t="n"/>
       <c r="J64" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K64" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L64" s="50" t="n"/>
-      <c r="M64" s="51" t="n"/>
-      <c r="N64" s="51" t="n"/>
-      <c r="O64" s="51" t="n"/>
-      <c r="P64" s="51" t="n"/>
-      <c r="Q64" s="51" t="n"/>
-      <c r="R64" s="51" t="n"/>
-      <c r="S64" s="51" t="n"/>
-      <c r="T64" s="51" t="n"/>
-      <c r="U64" s="51" t="n"/>
-      <c r="V64" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W64" s="58" t="n"/>
+      <c r="M64" s="55" t="n"/>
+      <c r="N64" s="55" t="n"/>
+      <c r="O64" s="55" t="n"/>
+      <c r="P64" s="55" t="n"/>
+      <c r="Q64" s="55" t="n"/>
+      <c r="R64" s="55" t="n"/>
+      <c r="S64" s="55" t="n"/>
+      <c r="T64" s="55" t="n"/>
+      <c r="U64" s="55" t="n"/>
+      <c r="V64" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W64" s="57" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B65" s="45" t="n"/>
-      <c r="C65" s="53" t="n"/>
-      <c r="D65" s="53" t="n"/>
+      <c r="C65" s="46" t="n"/>
+      <c r="D65" s="46" t="n"/>
       <c r="E65" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F65" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G65" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H65" s="49" t="n"/>
       <c r="I65" s="49" t="n"/>
@@ -4861,51 +4875,92 @@
         <v>59</v>
       </c>
       <c r="K65" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L65" s="50" t="n"/>
-      <c r="M65" s="55" t="n"/>
-      <c r="N65" s="55" t="n"/>
-      <c r="O65" s="55" t="n"/>
-      <c r="P65" s="55" t="n"/>
-      <c r="Q65" s="55" t="n"/>
-      <c r="R65" s="55" t="n"/>
-      <c r="S65" s="55" t="n"/>
-      <c r="T65" s="55" t="n"/>
-      <c r="U65" s="55" t="n"/>
-      <c r="V65" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W65" s="57" t="n"/>
+      <c r="M65" s="51" t="n"/>
+      <c r="N65" s="51" t="n"/>
+      <c r="O65" s="51" t="n"/>
+      <c r="P65" s="51" t="n"/>
+      <c r="Q65" s="51" t="n"/>
+      <c r="R65" s="51" t="n"/>
+      <c r="S65" s="51" t="n"/>
+      <c r="T65" s="51" t="n"/>
+      <c r="U65" s="51" t="n"/>
+      <c r="V65" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W65" s="58" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B66" s="45" t="n"/>
-      <c r="C66" s="46" t="n"/>
-      <c r="D66" s="46" t="n"/>
-      <c r="E66" s="47" t="n"/>
-      <c r="F66" s="47" t="n"/>
-      <c r="G66" s="60" t="n"/>
+      <c r="C66" s="53" t="n"/>
+      <c r="D66" s="53" t="n"/>
+      <c r="E66" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F66" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G66" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H66" s="49" t="n"/>
       <c r="I66" s="49" t="n"/>
-      <c r="J66" s="50" t="n"/>
-      <c r="K66" s="50" t="n"/>
+      <c r="J66" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K66" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L66" s="50" t="n"/>
-      <c r="M66" s="51" t="n"/>
-      <c r="N66" s="51" t="n"/>
-      <c r="O66" s="51" t="n"/>
-      <c r="P66" s="51" t="n"/>
-      <c r="Q66" s="51" t="n"/>
-      <c r="R66" s="51" t="n"/>
-      <c r="S66" s="51" t="n"/>
-      <c r="T66" s="51" t="n"/>
-      <c r="U66" s="51" t="n"/>
-      <c r="V66" s="61" t="n"/>
-      <c r="W66" s="61" t="n"/>
+      <c r="M66" s="55" t="n"/>
+      <c r="N66" s="55" t="n"/>
+      <c r="O66" s="55" t="n"/>
+      <c r="P66" s="55" t="n"/>
+      <c r="Q66" s="55" t="n"/>
+      <c r="R66" s="55" t="n"/>
+      <c r="S66" s="55" t="n"/>
+      <c r="T66" s="55" t="n"/>
+      <c r="U66" s="55" t="n"/>
+      <c r="V66" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W66" s="57" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B67" s="45" t="n"/>
+      <c r="C67" s="46" t="n"/>
+      <c r="D67" s="46" t="n"/>
+      <c r="E67" s="47" t="n"/>
+      <c r="F67" s="47" t="n"/>
+      <c r="G67" s="60" t="n"/>
+      <c r="H67" s="49" t="n"/>
+      <c r="I67" s="49" t="n"/>
+      <c r="J67" s="50" t="n"/>
+      <c r="K67" s="50" t="n"/>
+      <c r="L67" s="50" t="n"/>
+      <c r="M67" s="51" t="n"/>
+      <c r="N67" s="51" t="n"/>
+      <c r="O67" s="51" t="n"/>
+      <c r="P67" s="51" t="n"/>
+      <c r="Q67" s="51" t="n"/>
+      <c r="R67" s="51" t="n"/>
+      <c r="S67" s="51" t="n"/>
+      <c r="T67" s="51" t="n"/>
+      <c r="U67" s="51" t="n"/>
+      <c r="V67" s="61" t="n"/>
+      <c r="W67" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W67"/>
+  <dimension ref="A1:W68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,47 +1982,47 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/09(四)</t>
+          <t>2026/04/10(五)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G4" s="66" t="n">
-        <v>23.2</v>
+        <v>59</v>
+      </c>
+      <c r="G4" s="71" t="n">
+        <v>31.4</v>
       </c>
       <c r="H4" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I4" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J4" s="68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" s="68" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L4" s="68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M4" s="69" t="inlineStr">
         <is>
+          <t>中嘉博创、长源东谷、来伊份</t>
+        </is>
+      </c>
+      <c r="N4" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="N4" s="69" t="inlineStr"/>
-      <c r="O4" s="69" t="inlineStr">
-        <is>
-          <t>汇源通信</t>
-        </is>
-      </c>
+      <c r="O4" s="69" t="inlineStr"/>
       <c r="P4" s="69" t="inlineStr"/>
       <c r="Q4" s="69" t="inlineStr"/>
       <c r="R4" s="69" t="inlineStr"/>
@@ -2030,54 +2030,54 @@
       <c r="T4" s="69" t="inlineStr"/>
       <c r="U4" s="69" t="inlineStr"/>
       <c r="V4" s="69" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="W4" s="69" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/08(三)</t>
+          <t>2026/04/09(四)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
       <c r="C5" s="64" t="inlineStr"/>
       <c r="D5" s="64" t="inlineStr"/>
       <c r="E5" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="G5" s="66" t="n">
-        <v>11.5</v>
+        <v>23.2</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5" s="68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K5" s="68" t="n">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="L5" s="68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M5" s="69" t="inlineStr">
         <is>
-          <t>中安科</t>
-        </is>
-      </c>
-      <c r="N5" s="69" t="inlineStr">
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="N5" s="69" t="inlineStr"/>
+      <c r="O5" s="69" t="inlineStr">
         <is>
           <t>汇源通信</t>
         </is>
       </c>
-      <c r="O5" s="69" t="inlineStr"/>
       <c r="P5" s="69" t="inlineStr"/>
       <c r="Q5" s="69" t="inlineStr"/>
       <c r="R5" s="69" t="inlineStr"/>
@@ -2092,20 +2092,20 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/04/07(二)</t>
+          <t>2026/04/08(三)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
       <c r="C6" s="64" t="inlineStr"/>
       <c r="D6" s="64" t="inlineStr"/>
       <c r="E6" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G6" s="66" t="n">
-        <v>21.8</v>
+        <v>11.5</v>
       </c>
       <c r="H6" s="67" t="n">
         <v>4</v>
@@ -2114,91 +2114,95 @@
         <v>4</v>
       </c>
       <c r="J6" s="68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K6" s="68" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="L6" s="68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M6" s="69" t="inlineStr">
         <is>
-          <t>汇源通信、新能泰山</t>
-        </is>
-      </c>
-      <c r="N6" s="69" t="inlineStr"/>
+          <t>中安科</t>
+        </is>
+      </c>
+      <c r="N6" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信</t>
+        </is>
+      </c>
       <c r="O6" s="69" t="inlineStr"/>
       <c r="P6" s="69" t="inlineStr"/>
-      <c r="Q6" s="69" t="inlineStr">
-        <is>
-          <t>津药药业</t>
-        </is>
-      </c>
+      <c r="Q6" s="69" t="inlineStr"/>
       <c r="R6" s="69" t="inlineStr"/>
       <c r="S6" s="69" t="inlineStr"/>
       <c r="T6" s="69" t="inlineStr"/>
       <c r="U6" s="69" t="inlineStr"/>
       <c r="V6" s="69" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W6" s="69" t="inlineStr"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="62" t="inlineStr">
         <is>
-          <t>2026/04/06(一)</t>
+          <t>2026/04/07(二)</t>
         </is>
       </c>
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="64" t="inlineStr"/>
       <c r="D7" s="64" t="inlineStr"/>
       <c r="E7" s="65" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F7" s="65" t="n">
-        <v>36</v>
-      </c>
-      <c r="G7" s="71" t="n">
-        <v>25</v>
+        <v>93</v>
+      </c>
+      <c r="G7" s="66" t="n">
+        <v>21.8</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I7" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J7" s="68" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="L7" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="68" t="n">
-        <v>32</v>
-      </c>
-      <c r="L7" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" s="69" t="inlineStr"/>
+      <c r="M7" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信、新能泰山</t>
+        </is>
+      </c>
       <c r="N7" s="69" t="inlineStr"/>
       <c r="O7" s="69" t="inlineStr"/>
-      <c r="P7" s="69" t="inlineStr">
+      <c r="P7" s="69" t="inlineStr"/>
+      <c r="Q7" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="Q7" s="69" t="inlineStr"/>
       <c r="R7" s="69" t="inlineStr"/>
       <c r="S7" s="69" t="inlineStr"/>
       <c r="T7" s="69" t="inlineStr"/>
       <c r="U7" s="69" t="inlineStr"/>
       <c r="V7" s="69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W7" s="69" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="62" t="inlineStr">
         <is>
-          <t>2026/04/03(五)</t>
+          <t>2026/04/06(一)</t>
         </is>
       </c>
       <c r="B8" s="63" t="inlineStr"/>
@@ -2242,105 +2246,105 @@
       <c r="T8" s="69" t="inlineStr"/>
       <c r="U8" s="69" t="inlineStr"/>
       <c r="V8" s="69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W8" s="69" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B9" s="63" t="inlineStr"/>
       <c r="C9" s="64" t="inlineStr"/>
       <c r="D9" s="64" t="inlineStr"/>
       <c r="E9" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F9" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G9" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H9" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I9" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J9" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L9" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M9" s="69" t="inlineStr"/>
       <c r="N9" s="69" t="inlineStr"/>
-      <c r="O9" s="69" t="inlineStr">
+      <c r="O9" s="69" t="inlineStr"/>
+      <c r="P9" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P9" s="69" t="inlineStr"/>
       <c r="Q9" s="69" t="inlineStr"/>
       <c r="R9" s="69" t="inlineStr"/>
       <c r="S9" s="69" t="inlineStr"/>
       <c r="T9" s="69" t="inlineStr"/>
       <c r="U9" s="69" t="inlineStr"/>
       <c r="V9" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W9" s="69" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B10" s="63" t="inlineStr"/>
       <c r="C10" s="64" t="inlineStr"/>
       <c r="D10" s="64" t="inlineStr"/>
       <c r="E10" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F10" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G10" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G10" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H10" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I10" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K10" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L10" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M10" s="69" t="inlineStr"/>
-      <c r="N10" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M10" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N10" s="69" t="inlineStr"/>
+      <c r="O10" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O10" s="69" t="inlineStr"/>
       <c r="P10" s="69" t="inlineStr"/>
       <c r="Q10" s="69" t="inlineStr"/>
       <c r="R10" s="69" t="inlineStr"/>
@@ -2348,51 +2352,47 @@
       <c r="T10" s="69" t="inlineStr"/>
       <c r="U10" s="69" t="inlineStr"/>
       <c r="V10" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W10" s="69" t="inlineStr"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B11" s="63" t="inlineStr"/>
       <c r="C11" s="64" t="inlineStr"/>
       <c r="D11" s="64" t="inlineStr"/>
       <c r="E11" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F11" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G11" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G11" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I11" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J11" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K11" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L11" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M11" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M11" s="69" t="inlineStr"/>
+      <c r="N11" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N11" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O11" s="69" t="inlineStr"/>
@@ -2403,254 +2403,250 @@
       <c r="T11" s="69" t="inlineStr"/>
       <c r="U11" s="69" t="inlineStr"/>
       <c r="V11" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W11" s="69" t="inlineStr"/>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B12" s="63" t="inlineStr"/>
+      <c r="C12" s="64" t="inlineStr"/>
+      <c r="D12" s="64" t="inlineStr"/>
+      <c r="E12" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F12" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G12" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H12" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K12" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L12" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M12" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N12" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O12" s="69" t="inlineStr"/>
+      <c r="P12" s="69" t="inlineStr"/>
+      <c r="Q12" s="69" t="inlineStr"/>
+      <c r="R12" s="69" t="inlineStr"/>
+      <c r="S12" s="69" t="inlineStr"/>
+      <c r="T12" s="69" t="inlineStr"/>
+      <c r="U12" s="69" t="inlineStr"/>
+      <c r="V12" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W11" s="69" t="inlineStr"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="W12" s="69" t="inlineStr"/>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D12" s="38" t="inlineStr">
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E13" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F12" s="39" t="n">
+      <c r="F13" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G12" s="40" t="n">
+      <c r="G13" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H12" s="41" t="n">
+      <c r="H13" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I12" s="41" t="n">
+      <c r="I13" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J12" s="42" t="n">
+      <c r="J13" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K12" s="42" t="n">
+      <c r="K13" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L12" s="42" t="n">
+      <c r="L13" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M12" s="43" t="inlineStr">
+      <c r="M13" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N12" s="43" t="inlineStr"/>
-      <c r="O12" s="43" t="inlineStr">
+      <c r="N13" s="43" t="inlineStr"/>
+      <c r="O13" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P12" s="43" t="inlineStr"/>
-      <c r="Q12" s="43" t="inlineStr"/>
-      <c r="R12" s="43" t="inlineStr"/>
-      <c r="S12" s="43" t="inlineStr"/>
-      <c r="T12" s="43" t="inlineStr"/>
-      <c r="U12" s="43" t="inlineStr"/>
-      <c r="V12" s="43" t="n">
+      <c r="P13" s="43" t="inlineStr"/>
+      <c r="Q13" s="43" t="inlineStr"/>
+      <c r="R13" s="43" t="inlineStr"/>
+      <c r="S13" s="43" t="inlineStr"/>
+      <c r="T13" s="43" t="inlineStr"/>
+      <c r="U13" s="43" t="inlineStr"/>
+      <c r="V13" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W12" s="43" t="inlineStr"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B13" s="45" t="n"/>
-      <c r="C13" s="46" t="n"/>
-      <c r="D13" s="46" t="n"/>
-      <c r="E13" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F13" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G13" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H13" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K13" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L13" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" s="51" t="n"/>
-      <c r="N13" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O13" s="51" t="n"/>
-      <c r="P13" s="51" t="n"/>
-      <c r="Q13" s="51" t="n"/>
-      <c r="R13" s="51" t="n"/>
-      <c r="S13" s="51" t="n"/>
-      <c r="T13" s="51" t="n"/>
-      <c r="U13" s="51" t="n"/>
-      <c r="V13" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W13" s="43" t="inlineStr"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B14" s="45" t="n"/>
-      <c r="C14" s="53" t="n"/>
-      <c r="D14" s="53" t="n"/>
+      <c r="C14" s="46" t="n"/>
+      <c r="D14" s="46" t="n"/>
       <c r="E14" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F14" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G14" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G14" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H14" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I14" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J14" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K14" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L14" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M14" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N14" s="55" t="n"/>
-      <c r="O14" s="55" t="n"/>
-      <c r="P14" s="55" t="n"/>
-      <c r="Q14" s="55" t="n"/>
-      <c r="R14" s="55" t="n"/>
-      <c r="S14" s="55" t="n"/>
-      <c r="T14" s="55" t="n"/>
-      <c r="U14" s="55" t="n"/>
-      <c r="V14" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W14" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M14" s="51" t="n"/>
+      <c r="N14" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O14" s="51" t="n"/>
+      <c r="P14" s="51" t="n"/>
+      <c r="Q14" s="51" t="n"/>
+      <c r="R14" s="51" t="n"/>
+      <c r="S14" s="51" t="n"/>
+      <c r="T14" s="51" t="n"/>
+      <c r="U14" s="51" t="n"/>
+      <c r="V14" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B15" s="45" t="n"/>
-      <c r="C15" s="46" t="n"/>
-      <c r="D15" s="46" t="n"/>
+      <c r="C15" s="53" t="n"/>
+      <c r="D15" s="53" t="n"/>
       <c r="E15" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F15" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G15" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G15" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H15" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I15" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J15" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K15" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L15" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M15" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N15" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O15" s="51" t="n"/>
-      <c r="P15" s="51" t="n"/>
-      <c r="Q15" s="51" t="n"/>
-      <c r="R15" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S15" s="51" t="n"/>
-      <c r="T15" s="51" t="n"/>
-      <c r="U15" s="51" t="n"/>
-      <c r="V15" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W15" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M15" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N15" s="55" t="n"/>
+      <c r="O15" s="55" t="n"/>
+      <c r="P15" s="55" t="n"/>
+      <c r="Q15" s="55" t="n"/>
+      <c r="R15" s="55" t="n"/>
+      <c r="S15" s="55" t="n"/>
+      <c r="T15" s="55" t="n"/>
+      <c r="U15" s="55" t="n"/>
+      <c r="V15" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W15" s="57" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B16" s="45" t="n"/>
-      <c r="C16" s="53" t="n"/>
-      <c r="D16" s="53" t="n"/>
+      <c r="C16" s="46" t="n"/>
+      <c r="D16" s="46" t="n"/>
       <c r="E16" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F16" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G16" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H16" s="49" t="n">
         <v>1</v>
@@ -2659,493 +2655,497 @@
         <v>1</v>
       </c>
       <c r="J16" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K16" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L16" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M16" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N16" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N16" s="55" t="n"/>
-      <c r="O16" s="55" t="n"/>
-      <c r="P16" s="55" t="n"/>
-      <c r="Q16" s="55" t="inlineStr">
+      <c r="O16" s="51" t="n"/>
+      <c r="P16" s="51" t="n"/>
+      <c r="Q16" s="51" t="n"/>
+      <c r="R16" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R16" s="55" t="n"/>
-      <c r="S16" s="55" t="n"/>
-      <c r="T16" s="55" t="n"/>
-      <c r="U16" s="55" t="n"/>
-      <c r="V16" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W16" s="57" t="n"/>
+      <c r="S16" s="51" t="n"/>
+      <c r="T16" s="51" t="n"/>
+      <c r="U16" s="51" t="n"/>
+      <c r="V16" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W16" s="58" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B17" s="45" t="n"/>
-      <c r="C17" s="46" t="n"/>
-      <c r="D17" s="46" t="n"/>
+      <c r="C17" s="53" t="n"/>
+      <c r="D17" s="53" t="n"/>
       <c r="E17" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F17" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G17" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G17" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H17" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J17" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K17" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L17" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N17" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O17" s="51" t="n"/>
-      <c r="P17" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M17" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N17" s="55" t="n"/>
+      <c r="O17" s="55" t="n"/>
+      <c r="P17" s="55" t="n"/>
+      <c r="Q17" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q17" s="51" t="n"/>
-      <c r="R17" s="51" t="n"/>
-      <c r="S17" s="51" t="n"/>
-      <c r="T17" s="51" t="n"/>
-      <c r="U17" s="51" t="n"/>
-      <c r="V17" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W17" s="58" t="n"/>
+      <c r="R17" s="55" t="n"/>
+      <c r="S17" s="55" t="n"/>
+      <c r="T17" s="55" t="n"/>
+      <c r="U17" s="55" t="n"/>
+      <c r="V17" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W17" s="57" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B18" s="45" t="n"/>
-      <c r="C18" s="53" t="n"/>
-      <c r="D18" s="53" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="46" t="n"/>
       <c r="E18" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F18" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G18" s="59" t="n">
-        <v>45.1</v>
+      <c r="G18" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H18" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I18" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J18" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K18" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L18" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N18" s="55" t="n"/>
-      <c r="O18" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P18" s="55" t="n"/>
-      <c r="Q18" s="55" t="n"/>
-      <c r="R18" s="55" t="n"/>
-      <c r="S18" s="55" t="n"/>
-      <c r="T18" s="55" t="n"/>
-      <c r="U18" s="55" t="n"/>
-      <c r="V18" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W18" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M18" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N18" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O18" s="51" t="n"/>
+      <c r="P18" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q18" s="51" t="n"/>
+      <c r="R18" s="51" t="n"/>
+      <c r="S18" s="51" t="n"/>
+      <c r="T18" s="51" t="n"/>
+      <c r="U18" s="51" t="n"/>
+      <c r="V18" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W18" s="58" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B19" s="45" t="n"/>
-      <c r="C19" s="46" t="n"/>
-      <c r="D19" s="46" t="n"/>
+      <c r="C19" s="53" t="n"/>
+      <c r="D19" s="53" t="n"/>
       <c r="E19" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F19" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G19" s="54" t="n">
-        <v>26.3</v>
+      <c r="G19" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H19" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J19" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K19" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L19" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M19" s="51" t="n"/>
-      <c r="N19" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M19" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N19" s="55" t="n"/>
+      <c r="O19" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O19" s="51" t="n"/>
-      <c r="P19" s="51" t="n"/>
-      <c r="Q19" s="51" t="n"/>
-      <c r="R19" s="51" t="n"/>
-      <c r="S19" s="51" t="n"/>
-      <c r="T19" s="51" t="n"/>
-      <c r="U19" s="51" t="n"/>
-      <c r="V19" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W19" s="58" t="n"/>
+      <c r="P19" s="55" t="n"/>
+      <c r="Q19" s="55" t="n"/>
+      <c r="R19" s="55" t="n"/>
+      <c r="S19" s="55" t="n"/>
+      <c r="T19" s="55" t="n"/>
+      <c r="U19" s="55" t="n"/>
+      <c r="V19" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W19" s="57" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B20" s="45" t="n"/>
-      <c r="C20" s="53" t="n"/>
-      <c r="D20" s="53" t="n"/>
+      <c r="C20" s="46" t="n"/>
+      <c r="D20" s="46" t="n"/>
       <c r="E20" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F20" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G20" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H20" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K20" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L20" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M20" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M20" s="51" t="n"/>
+      <c r="N20" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N20" s="55" t="n"/>
-      <c r="O20" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P20" s="55" t="n"/>
-      <c r="Q20" s="55" t="n"/>
-      <c r="R20" s="55" t="n"/>
-      <c r="S20" s="55" t="n"/>
-      <c r="T20" s="55" t="n"/>
-      <c r="U20" s="55" t="n"/>
-      <c r="V20" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W20" s="57" t="n"/>
+      <c r="O20" s="51" t="n"/>
+      <c r="P20" s="51" t="n"/>
+      <c r="Q20" s="51" t="n"/>
+      <c r="R20" s="51" t="n"/>
+      <c r="S20" s="51" t="n"/>
+      <c r="T20" s="51" t="n"/>
+      <c r="U20" s="51" t="n"/>
+      <c r="V20" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W20" s="58" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="46" t="n"/>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="53" t="n"/>
       <c r="E21" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F21" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G21" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H21" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J21" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K21" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L21" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M21" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N21" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O21" s="51" t="n"/>
-      <c r="P21" s="51" t="n"/>
-      <c r="Q21" s="51" t="n"/>
-      <c r="R21" s="51" t="n"/>
-      <c r="S21" s="51" t="n"/>
-      <c r="T21" s="51" t="n"/>
-      <c r="U21" s="51" t="n"/>
-      <c r="V21" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W21" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M21" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N21" s="55" t="n"/>
+      <c r="O21" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P21" s="55" t="n"/>
+      <c r="Q21" s="55" t="n"/>
+      <c r="R21" s="55" t="n"/>
+      <c r="S21" s="55" t="n"/>
+      <c r="T21" s="55" t="n"/>
+      <c r="U21" s="55" t="n"/>
+      <c r="V21" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W21" s="57" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="53" t="n"/>
+      <c r="C22" s="46" t="n"/>
+      <c r="D22" s="46" t="n"/>
       <c r="E22" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G22" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H22" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K22" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L22" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I22" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K22" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L22" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M22" s="55" t="inlineStr">
+      <c r="M22" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N22" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N22" s="55" t="n"/>
-      <c r="O22" s="55" t="n"/>
-      <c r="P22" s="55" t="n"/>
-      <c r="Q22" s="55" t="n"/>
-      <c r="R22" s="55" t="n"/>
-      <c r="S22" s="55" t="n"/>
-      <c r="T22" s="55" t="n"/>
-      <c r="U22" s="55" t="n"/>
-      <c r="V22" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W22" s="57" t="n"/>
+      <c r="O22" s="51" t="n"/>
+      <c r="P22" s="51" t="n"/>
+      <c r="Q22" s="51" t="n"/>
+      <c r="R22" s="51" t="n"/>
+      <c r="S22" s="51" t="n"/>
+      <c r="T22" s="51" t="n"/>
+      <c r="U22" s="51" t="n"/>
+      <c r="V22" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W22" s="58" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="46" t="n"/>
-      <c r="D23" s="46" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G23" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G23" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H23" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L23" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M23" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N23" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O23" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P23" s="51" t="n"/>
-      <c r="Q23" s="51" t="n"/>
-      <c r="R23" s="51" t="n"/>
-      <c r="S23" s="51" t="n"/>
-      <c r="T23" s="51" t="n"/>
-      <c r="U23" s="51" t="n"/>
-      <c r="V23" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W23" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M23" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N23" s="55" t="n"/>
+      <c r="O23" s="55" t="n"/>
+      <c r="P23" s="55" t="n"/>
+      <c r="Q23" s="55" t="n"/>
+      <c r="R23" s="55" t="n"/>
+      <c r="S23" s="55" t="n"/>
+      <c r="T23" s="55" t="n"/>
+      <c r="U23" s="55" t="n"/>
+      <c r="V23" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W23" s="57" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
+      <c r="C24" s="46" t="n"/>
+      <c r="D24" s="46" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G24" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G24" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H24" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L24" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M24" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N24" s="55" t="inlineStr">
+      <c r="M24" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N24" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O24" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O24" s="55" t="n"/>
-      <c r="P24" s="55" t="n"/>
-      <c r="Q24" s="55" t="n"/>
-      <c r="R24" s="55" t="n"/>
-      <c r="S24" s="55" t="n"/>
-      <c r="T24" s="55" t="n"/>
-      <c r="U24" s="55" t="n"/>
-      <c r="V24" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W24" s="57" t="n"/>
+      <c r="P24" s="51" t="n"/>
+      <c r="Q24" s="51" t="n"/>
+      <c r="R24" s="51" t="n"/>
+      <c r="S24" s="51" t="n"/>
+      <c r="T24" s="51" t="n"/>
+      <c r="U24" s="51" t="n"/>
+      <c r="V24" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W24" s="58" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="46" t="n"/>
-      <c r="D25" s="46" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G25" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H25" s="49" t="n">
         <v>2</v>
@@ -3154,208 +3154,218 @@
         <v>2</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K25" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L25" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M25" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M25" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N25" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N25" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O25" s="51" t="n"/>
-      <c r="P25" s="51" t="n"/>
-      <c r="Q25" s="51" t="n"/>
-      <c r="R25" s="51" t="n"/>
-      <c r="S25" s="51" t="n"/>
-      <c r="T25" s="51" t="n"/>
-      <c r="U25" s="51" t="n"/>
-      <c r="V25" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W25" s="58" t="n"/>
+      <c r="O25" s="55" t="n"/>
+      <c r="P25" s="55" t="n"/>
+      <c r="Q25" s="55" t="n"/>
+      <c r="R25" s="55" t="n"/>
+      <c r="S25" s="55" t="n"/>
+      <c r="T25" s="55" t="n"/>
+      <c r="U25" s="55" t="n"/>
+      <c r="V25" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W25" s="57" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="53" t="n"/>
-      <c r="D26" s="53" t="n"/>
+      <c r="C26" s="46" t="n"/>
+      <c r="D26" s="46" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G26" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H26" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I26" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L26" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M26" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M26" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N26" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N26" s="55" t="n"/>
-      <c r="O26" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P26" s="55" t="n"/>
-      <c r="Q26" s="55" t="n"/>
-      <c r="R26" s="55" t="n"/>
-      <c r="S26" s="55" t="n"/>
-      <c r="T26" s="55" t="n"/>
-      <c r="U26" s="55" t="n"/>
-      <c r="V26" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W26" s="57" t="n"/>
+      <c r="O26" s="51" t="n"/>
+      <c r="P26" s="51" t="n"/>
+      <c r="Q26" s="51" t="n"/>
+      <c r="R26" s="51" t="n"/>
+      <c r="S26" s="51" t="n"/>
+      <c r="T26" s="51" t="n"/>
+      <c r="U26" s="51" t="n"/>
+      <c r="V26" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W26" s="58" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="46" t="n"/>
-      <c r="D27" s="46" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G27" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G27" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H27" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L27" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M27" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N27" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O27" s="51" t="n"/>
-      <c r="P27" s="51" t="n"/>
-      <c r="Q27" s="51" t="n"/>
-      <c r="R27" s="51" t="n"/>
-      <c r="S27" s="51" t="n"/>
-      <c r="T27" s="51" t="n"/>
-      <c r="U27" s="51" t="n"/>
-      <c r="V27" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W27" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M27" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N27" s="55" t="n"/>
+      <c r="O27" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P27" s="55" t="n"/>
+      <c r="Q27" s="55" t="n"/>
+      <c r="R27" s="55" t="n"/>
+      <c r="S27" s="55" t="n"/>
+      <c r="T27" s="55" t="n"/>
+      <c r="U27" s="55" t="n"/>
+      <c r="V27" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W27" s="57" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="53" t="n"/>
-      <c r="D28" s="53" t="n"/>
+      <c r="C28" s="46" t="n"/>
+      <c r="D28" s="46" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G28" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G28" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H28" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I28" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L28" s="50" t="n"/>
-      <c r="M28" s="55" t="n"/>
-      <c r="N28" s="55" t="n"/>
-      <c r="O28" s="55" t="n"/>
-      <c r="P28" s="55" t="n"/>
-      <c r="Q28" s="55" t="n"/>
-      <c r="R28" s="55" t="n"/>
-      <c r="S28" s="55" t="n"/>
-      <c r="T28" s="55" t="n"/>
-      <c r="U28" s="55" t="n"/>
-      <c r="V28" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W28" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L28" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M28" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N28" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O28" s="51" t="n"/>
+      <c r="P28" s="51" t="n"/>
+      <c r="Q28" s="51" t="n"/>
+      <c r="R28" s="51" t="n"/>
+      <c r="S28" s="51" t="n"/>
+      <c r="T28" s="51" t="n"/>
+      <c r="U28" s="51" t="n"/>
+      <c r="V28" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W28" s="58" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="46" t="n"/>
-      <c r="D29" s="46" t="n"/>
+      <c r="C29" s="53" t="n"/>
+      <c r="D29" s="53" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G29" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H29" s="49" t="n">
         <v>0</v>
@@ -3364,43 +3374,43 @@
         <v>0</v>
       </c>
       <c r="J29" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L29" s="50" t="n"/>
-      <c r="M29" s="51" t="n"/>
-      <c r="N29" s="51" t="n"/>
-      <c r="O29" s="51" t="n"/>
-      <c r="P29" s="51" t="n"/>
-      <c r="Q29" s="51" t="n"/>
-      <c r="R29" s="51" t="n"/>
-      <c r="S29" s="51" t="n"/>
-      <c r="T29" s="51" t="n"/>
-      <c r="U29" s="51" t="n"/>
-      <c r="V29" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W29" s="58" t="n"/>
+      <c r="M29" s="55" t="n"/>
+      <c r="N29" s="55" t="n"/>
+      <c r="O29" s="55" t="n"/>
+      <c r="P29" s="55" t="n"/>
+      <c r="Q29" s="55" t="n"/>
+      <c r="R29" s="55" t="n"/>
+      <c r="S29" s="55" t="n"/>
+      <c r="T29" s="55" t="n"/>
+      <c r="U29" s="55" t="n"/>
+      <c r="V29" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W29" s="57" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="53" t="n"/>
-      <c r="D30" s="53" t="n"/>
+      <c r="C30" s="46" t="n"/>
+      <c r="D30" s="46" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G30" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H30" s="49" t="n">
         <v>0</v>
@@ -3409,43 +3419,43 @@
         <v>0</v>
       </c>
       <c r="J30" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L30" s="50" t="n"/>
-      <c r="M30" s="55" t="n"/>
-      <c r="N30" s="55" t="n"/>
-      <c r="O30" s="55" t="n"/>
-      <c r="P30" s="55" t="n"/>
-      <c r="Q30" s="55" t="n"/>
-      <c r="R30" s="55" t="n"/>
-      <c r="S30" s="55" t="n"/>
-      <c r="T30" s="55" t="n"/>
-      <c r="U30" s="55" t="n"/>
-      <c r="V30" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W30" s="57" t="n"/>
+      <c r="M30" s="51" t="n"/>
+      <c r="N30" s="51" t="n"/>
+      <c r="O30" s="51" t="n"/>
+      <c r="P30" s="51" t="n"/>
+      <c r="Q30" s="51" t="n"/>
+      <c r="R30" s="51" t="n"/>
+      <c r="S30" s="51" t="n"/>
+      <c r="T30" s="51" t="n"/>
+      <c r="U30" s="51" t="n"/>
+      <c r="V30" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W30" s="58" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="46" t="n"/>
-      <c r="D31" s="46" t="n"/>
+      <c r="C31" s="53" t="n"/>
+      <c r="D31" s="53" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G31" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G31" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H31" s="49" t="n">
         <v>0</v>
@@ -3454,43 +3464,43 @@
         <v>0</v>
       </c>
       <c r="J31" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L31" s="50" t="n"/>
-      <c r="M31" s="51" t="n"/>
-      <c r="N31" s="51" t="n"/>
-      <c r="O31" s="51" t="n"/>
-      <c r="P31" s="51" t="n"/>
-      <c r="Q31" s="51" t="n"/>
-      <c r="R31" s="51" t="n"/>
-      <c r="S31" s="51" t="n"/>
-      <c r="T31" s="51" t="n"/>
-      <c r="U31" s="51" t="n"/>
-      <c r="V31" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W31" s="58" t="n"/>
+      <c r="M31" s="55" t="n"/>
+      <c r="N31" s="55" t="n"/>
+      <c r="O31" s="55" t="n"/>
+      <c r="P31" s="55" t="n"/>
+      <c r="Q31" s="55" t="n"/>
+      <c r="R31" s="55" t="n"/>
+      <c r="S31" s="55" t="n"/>
+      <c r="T31" s="55" t="n"/>
+      <c r="U31" s="55" t="n"/>
+      <c r="V31" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W31" s="57" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="53" t="n"/>
-      <c r="D32" s="53" t="n"/>
+      <c r="C32" s="46" t="n"/>
+      <c r="D32" s="46" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G32" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H32" s="49" t="n">
         <v>0</v>
@@ -3499,43 +3509,43 @@
         <v>0</v>
       </c>
       <c r="J32" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L32" s="50" t="n"/>
-      <c r="M32" s="55" t="n"/>
-      <c r="N32" s="55" t="n"/>
-      <c r="O32" s="55" t="n"/>
-      <c r="P32" s="55" t="n"/>
-      <c r="Q32" s="55" t="n"/>
-      <c r="R32" s="55" t="n"/>
-      <c r="S32" s="55" t="n"/>
-      <c r="T32" s="55" t="n"/>
-      <c r="U32" s="55" t="n"/>
-      <c r="V32" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W32" s="57" t="n"/>
+      <c r="M32" s="51" t="n"/>
+      <c r="N32" s="51" t="n"/>
+      <c r="O32" s="51" t="n"/>
+      <c r="P32" s="51" t="n"/>
+      <c r="Q32" s="51" t="n"/>
+      <c r="R32" s="51" t="n"/>
+      <c r="S32" s="51" t="n"/>
+      <c r="T32" s="51" t="n"/>
+      <c r="U32" s="51" t="n"/>
+      <c r="V32" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W32" s="58" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="46" t="n"/>
-      <c r="D33" s="46" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G33" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H33" s="49" t="n">
         <v>0</v>
@@ -3544,1371 +3554,1375 @@
         <v>0</v>
       </c>
       <c r="J33" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L33" s="50" t="n"/>
-      <c r="M33" s="51" t="n"/>
-      <c r="N33" s="51" t="n"/>
-      <c r="O33" s="51" t="n"/>
-      <c r="P33" s="51" t="n"/>
-      <c r="Q33" s="51" t="n"/>
-      <c r="R33" s="51" t="n"/>
-      <c r="S33" s="51" t="n"/>
-      <c r="T33" s="51" t="n"/>
-      <c r="U33" s="51" t="n"/>
-      <c r="V33" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W33" s="58" t="n"/>
+      <c r="M33" s="55" t="n"/>
+      <c r="N33" s="55" t="n"/>
+      <c r="O33" s="55" t="n"/>
+      <c r="P33" s="55" t="n"/>
+      <c r="Q33" s="55" t="n"/>
+      <c r="R33" s="55" t="n"/>
+      <c r="S33" s="55" t="n"/>
+      <c r="T33" s="55" t="n"/>
+      <c r="U33" s="55" t="n"/>
+      <c r="V33" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W33" s="57" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="53" t="n"/>
-      <c r="D34" s="53" t="n"/>
+      <c r="C34" s="46" t="n"/>
+      <c r="D34" s="46" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G34" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H34" s="49" t="n"/>
-      <c r="I34" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G34" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H34" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J34" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L34" s="50" t="n"/>
-      <c r="M34" s="55" t="n"/>
-      <c r="N34" s="55" t="n"/>
-      <c r="O34" s="55" t="n"/>
-      <c r="P34" s="55" t="n"/>
-      <c r="Q34" s="55" t="n"/>
-      <c r="R34" s="55" t="n"/>
-      <c r="S34" s="55" t="n"/>
-      <c r="T34" s="55" t="n"/>
-      <c r="U34" s="55" t="n"/>
-      <c r="V34" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W34" s="57" t="n"/>
+      <c r="M34" s="51" t="n"/>
+      <c r="N34" s="51" t="n"/>
+      <c r="O34" s="51" t="n"/>
+      <c r="P34" s="51" t="n"/>
+      <c r="Q34" s="51" t="n"/>
+      <c r="R34" s="51" t="n"/>
+      <c r="S34" s="51" t="n"/>
+      <c r="T34" s="51" t="n"/>
+      <c r="U34" s="51" t="n"/>
+      <c r="V34" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W34" s="58" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="46" t="n"/>
-      <c r="D35" s="46" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G35" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H35" s="49" t="n"/>
       <c r="I35" s="49" t="n"/>
       <c r="J35" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L35" s="50" t="n"/>
-      <c r="M35" s="51" t="n"/>
-      <c r="N35" s="51" t="n"/>
-      <c r="O35" s="51" t="n"/>
-      <c r="P35" s="51" t="n"/>
-      <c r="Q35" s="51" t="n"/>
-      <c r="R35" s="51" t="n"/>
-      <c r="S35" s="51" t="n"/>
-      <c r="T35" s="51" t="n"/>
-      <c r="U35" s="51" t="n"/>
-      <c r="V35" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W35" s="58" t="n"/>
+      <c r="M35" s="55" t="n"/>
+      <c r="N35" s="55" t="n"/>
+      <c r="O35" s="55" t="n"/>
+      <c r="P35" s="55" t="n"/>
+      <c r="Q35" s="55" t="n"/>
+      <c r="R35" s="55" t="n"/>
+      <c r="S35" s="55" t="n"/>
+      <c r="T35" s="55" t="n"/>
+      <c r="U35" s="55" t="n"/>
+      <c r="V35" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W35" s="57" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
+      <c r="C36" s="46" t="n"/>
+      <c r="D36" s="46" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G36" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H36" s="49" t="n"/>
       <c r="I36" s="49" t="n"/>
       <c r="J36" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="55" t="n"/>
-      <c r="N36" s="55" t="n"/>
-      <c r="O36" s="55" t="n"/>
-      <c r="P36" s="55" t="n"/>
-      <c r="Q36" s="55" t="n"/>
-      <c r="R36" s="55" t="n"/>
-      <c r="S36" s="55" t="n"/>
-      <c r="T36" s="55" t="n"/>
-      <c r="U36" s="55" t="n"/>
-      <c r="V36" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W36" s="57" t="n"/>
+      <c r="M36" s="51" t="n"/>
+      <c r="N36" s="51" t="n"/>
+      <c r="O36" s="51" t="n"/>
+      <c r="P36" s="51" t="n"/>
+      <c r="Q36" s="51" t="n"/>
+      <c r="R36" s="51" t="n"/>
+      <c r="S36" s="51" t="n"/>
+      <c r="T36" s="51" t="n"/>
+      <c r="U36" s="51" t="n"/>
+      <c r="V36" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W36" s="58" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="46" t="n"/>
-      <c r="D37" s="46" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G37" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H37" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I37" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H37" s="49" t="n"/>
+      <c r="I37" s="49" t="n"/>
       <c r="J37" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="51" t="n"/>
-      <c r="N37" s="51" t="n"/>
-      <c r="O37" s="51" t="n"/>
-      <c r="P37" s="51" t="n"/>
-      <c r="Q37" s="51" t="n"/>
-      <c r="R37" s="51" t="n"/>
-      <c r="S37" s="51" t="n"/>
-      <c r="T37" s="51" t="n"/>
-      <c r="U37" s="51" t="n"/>
-      <c r="V37" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W37" s="58" t="n"/>
+      <c r="M37" s="55" t="n"/>
+      <c r="N37" s="55" t="n"/>
+      <c r="O37" s="55" t="n"/>
+      <c r="P37" s="55" t="n"/>
+      <c r="Q37" s="55" t="n"/>
+      <c r="R37" s="55" t="n"/>
+      <c r="S37" s="55" t="n"/>
+      <c r="T37" s="55" t="n"/>
+      <c r="U37" s="55" t="n"/>
+      <c r="V37" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W37" s="57" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="53" t="n"/>
-      <c r="D38" s="53" t="n"/>
+      <c r="C38" s="46" t="n"/>
+      <c r="D38" s="46" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G38" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H38" s="49" t="n"/>
-      <c r="I38" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G38" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H38" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I38" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J38" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="55" t="n"/>
-      <c r="N38" s="55" t="n"/>
-      <c r="O38" s="55" t="n"/>
-      <c r="P38" s="55" t="n"/>
-      <c r="Q38" s="55" t="n"/>
-      <c r="R38" s="55" t="n"/>
-      <c r="S38" s="55" t="n"/>
-      <c r="T38" s="55" t="n"/>
-      <c r="U38" s="55" t="n"/>
-      <c r="V38" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W38" s="57" t="n"/>
+      <c r="M38" s="51" t="n"/>
+      <c r="N38" s="51" t="n"/>
+      <c r="O38" s="51" t="n"/>
+      <c r="P38" s="51" t="n"/>
+      <c r="Q38" s="51" t="n"/>
+      <c r="R38" s="51" t="n"/>
+      <c r="S38" s="51" t="n"/>
+      <c r="T38" s="51" t="n"/>
+      <c r="U38" s="51" t="n"/>
+      <c r="V38" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W38" s="58" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="46" t="n"/>
-      <c r="D39" s="46" t="n"/>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G39" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G39" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H39" s="49" t="n"/>
       <c r="I39" s="49" t="n"/>
       <c r="J39" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="51" t="n"/>
-      <c r="N39" s="51" t="n"/>
-      <c r="O39" s="51" t="n"/>
-      <c r="P39" s="51" t="n"/>
-      <c r="Q39" s="51" t="n"/>
-      <c r="R39" s="51" t="n"/>
-      <c r="S39" s="51" t="n"/>
-      <c r="T39" s="51" t="n"/>
-      <c r="U39" s="51" t="n"/>
-      <c r="V39" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W39" s="58" t="n"/>
+      <c r="M39" s="55" t="n"/>
+      <c r="N39" s="55" t="n"/>
+      <c r="O39" s="55" t="n"/>
+      <c r="P39" s="55" t="n"/>
+      <c r="Q39" s="55" t="n"/>
+      <c r="R39" s="55" t="n"/>
+      <c r="S39" s="55" t="n"/>
+      <c r="T39" s="55" t="n"/>
+      <c r="U39" s="55" t="n"/>
+      <c r="V39" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W39" s="57" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="53" t="n"/>
-      <c r="D40" s="53" t="n"/>
+      <c r="C40" s="46" t="n"/>
+      <c r="D40" s="46" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G40" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G40" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H40" s="49" t="n"/>
       <c r="I40" s="49" t="n"/>
       <c r="J40" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K40" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K40" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="55" t="n"/>
-      <c r="N40" s="55" t="n"/>
-      <c r="O40" s="55" t="n"/>
-      <c r="P40" s="55" t="n"/>
-      <c r="Q40" s="55" t="n"/>
-      <c r="R40" s="55" t="n"/>
-      <c r="S40" s="55" t="n"/>
-      <c r="T40" s="55" t="n"/>
-      <c r="U40" s="55" t="n"/>
-      <c r="V40" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W40" s="57" t="n"/>
+      <c r="M40" s="51" t="n"/>
+      <c r="N40" s="51" t="n"/>
+      <c r="O40" s="51" t="n"/>
+      <c r="P40" s="51" t="n"/>
+      <c r="Q40" s="51" t="n"/>
+      <c r="R40" s="51" t="n"/>
+      <c r="S40" s="51" t="n"/>
+      <c r="T40" s="51" t="n"/>
+      <c r="U40" s="51" t="n"/>
+      <c r="V40" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W40" s="58" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="46" t="n"/>
-      <c r="D41" s="46" t="n"/>
+      <c r="C41" s="53" t="n"/>
+      <c r="D41" s="53" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G41" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H41" s="49" t="n"/>
       <c r="I41" s="49" t="n"/>
       <c r="J41" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="51" t="n"/>
-      <c r="N41" s="51" t="n"/>
-      <c r="O41" s="51" t="n"/>
-      <c r="P41" s="51" t="n"/>
-      <c r="Q41" s="51" t="n"/>
-      <c r="R41" s="51" t="n"/>
-      <c r="S41" s="51" t="n"/>
-      <c r="T41" s="51" t="n"/>
-      <c r="U41" s="51" t="n"/>
-      <c r="V41" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W41" s="58" t="n"/>
+      <c r="M41" s="55" t="n"/>
+      <c r="N41" s="55" t="n"/>
+      <c r="O41" s="55" t="n"/>
+      <c r="P41" s="55" t="n"/>
+      <c r="Q41" s="55" t="n"/>
+      <c r="R41" s="55" t="n"/>
+      <c r="S41" s="55" t="n"/>
+      <c r="T41" s="55" t="n"/>
+      <c r="U41" s="55" t="n"/>
+      <c r="V41" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W41" s="57" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="53" t="n"/>
-      <c r="D42" s="53" t="n"/>
+      <c r="C42" s="46" t="n"/>
+      <c r="D42" s="46" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G42" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G42" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H42" s="49" t="n"/>
       <c r="I42" s="49" t="n"/>
       <c r="J42" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K42" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="55" t="n"/>
-      <c r="N42" s="55" t="n"/>
-      <c r="O42" s="55" t="n"/>
-      <c r="P42" s="55" t="n"/>
-      <c r="Q42" s="55" t="n"/>
-      <c r="R42" s="55" t="n"/>
-      <c r="S42" s="55" t="n"/>
-      <c r="T42" s="55" t="n"/>
-      <c r="U42" s="55" t="n"/>
-      <c r="V42" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W42" s="57" t="n"/>
+      <c r="M42" s="51" t="n"/>
+      <c r="N42" s="51" t="n"/>
+      <c r="O42" s="51" t="n"/>
+      <c r="P42" s="51" t="n"/>
+      <c r="Q42" s="51" t="n"/>
+      <c r="R42" s="51" t="n"/>
+      <c r="S42" s="51" t="n"/>
+      <c r="T42" s="51" t="n"/>
+      <c r="U42" s="51" t="n"/>
+      <c r="V42" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W42" s="58" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="46" t="n"/>
-      <c r="D43" s="46" t="n"/>
+      <c r="C43" s="53" t="n"/>
+      <c r="D43" s="53" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G43" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H43" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I43" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G43" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H43" s="49" t="n"/>
+      <c r="I43" s="49" t="n"/>
       <c r="J43" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K43" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="51" t="n"/>
-      <c r="N43" s="51" t="n"/>
-      <c r="O43" s="51" t="n"/>
-      <c r="P43" s="51" t="n"/>
-      <c r="Q43" s="51" t="n"/>
-      <c r="R43" s="51" t="n"/>
-      <c r="S43" s="51" t="n"/>
-      <c r="T43" s="51" t="n"/>
-      <c r="U43" s="51" t="n"/>
-      <c r="V43" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W43" s="58" t="n"/>
+      <c r="M43" s="55" t="n"/>
+      <c r="N43" s="55" t="n"/>
+      <c r="O43" s="55" t="n"/>
+      <c r="P43" s="55" t="n"/>
+      <c r="Q43" s="55" t="n"/>
+      <c r="R43" s="55" t="n"/>
+      <c r="S43" s="55" t="n"/>
+      <c r="T43" s="55" t="n"/>
+      <c r="U43" s="55" t="n"/>
+      <c r="V43" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W43" s="57" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="53" t="n"/>
-      <c r="D44" s="53" t="n"/>
+      <c r="C44" s="46" t="n"/>
+      <c r="D44" s="46" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G44" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H44" s="49" t="n"/>
-      <c r="I44" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H44" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I44" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J44" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K44" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="55" t="n"/>
-      <c r="N44" s="55" t="n"/>
-      <c r="O44" s="55" t="n"/>
-      <c r="P44" s="55" t="n"/>
-      <c r="Q44" s="55" t="n"/>
-      <c r="R44" s="55" t="n"/>
-      <c r="S44" s="55" t="n"/>
-      <c r="T44" s="55" t="n"/>
-      <c r="U44" s="55" t="n"/>
-      <c r="V44" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W44" s="57" t="n"/>
+      <c r="M44" s="51" t="n"/>
+      <c r="N44" s="51" t="n"/>
+      <c r="O44" s="51" t="n"/>
+      <c r="P44" s="51" t="n"/>
+      <c r="Q44" s="51" t="n"/>
+      <c r="R44" s="51" t="n"/>
+      <c r="S44" s="51" t="n"/>
+      <c r="T44" s="51" t="n"/>
+      <c r="U44" s="51" t="n"/>
+      <c r="V44" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W44" s="58" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="46" t="n"/>
-      <c r="D45" s="46" t="n"/>
+      <c r="C45" s="53" t="n"/>
+      <c r="D45" s="53" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G45" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H45" s="49" t="n"/>
       <c r="I45" s="49" t="n"/>
       <c r="J45" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K45" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="51" t="n"/>
-      <c r="N45" s="51" t="n"/>
-      <c r="O45" s="51" t="n"/>
-      <c r="P45" s="51" t="n"/>
-      <c r="Q45" s="51" t="n"/>
-      <c r="R45" s="51" t="n"/>
-      <c r="S45" s="51" t="n"/>
-      <c r="T45" s="51" t="n"/>
-      <c r="U45" s="51" t="n"/>
-      <c r="V45" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W45" s="58" t="n"/>
+      <c r="M45" s="55" t="n"/>
+      <c r="N45" s="55" t="n"/>
+      <c r="O45" s="55" t="n"/>
+      <c r="P45" s="55" t="n"/>
+      <c r="Q45" s="55" t="n"/>
+      <c r="R45" s="55" t="n"/>
+      <c r="S45" s="55" t="n"/>
+      <c r="T45" s="55" t="n"/>
+      <c r="U45" s="55" t="n"/>
+      <c r="V45" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W45" s="57" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="53" t="n"/>
-      <c r="D46" s="53" t="n"/>
+      <c r="C46" s="46" t="n"/>
+      <c r="D46" s="46" t="n"/>
       <c r="E46" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F46" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G46" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H46" s="49" t="n"/>
+      <c r="I46" s="49" t="n"/>
+      <c r="J46" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F46" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G46" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H46" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I46" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J46" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K46" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="55" t="n"/>
-      <c r="N46" s="55" t="n"/>
-      <c r="O46" s="55" t="n"/>
-      <c r="P46" s="55" t="n"/>
-      <c r="Q46" s="55" t="n"/>
-      <c r="R46" s="55" t="n"/>
-      <c r="S46" s="55" t="n"/>
-      <c r="T46" s="55" t="n"/>
-      <c r="U46" s="55" t="n"/>
-      <c r="V46" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W46" s="57" t="n"/>
+      <c r="M46" s="51" t="n"/>
+      <c r="N46" s="51" t="n"/>
+      <c r="O46" s="51" t="n"/>
+      <c r="P46" s="51" t="n"/>
+      <c r="Q46" s="51" t="n"/>
+      <c r="R46" s="51" t="n"/>
+      <c r="S46" s="51" t="n"/>
+      <c r="T46" s="51" t="n"/>
+      <c r="U46" s="51" t="n"/>
+      <c r="V46" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W46" s="58" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="46" t="n"/>
-      <c r="D47" s="46" t="n"/>
+      <c r="C47" s="53" t="n"/>
+      <c r="D47" s="53" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G47" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H47" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I47" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J47" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K47" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="51" t="n"/>
-      <c r="N47" s="51" t="n"/>
-      <c r="O47" s="51" t="n"/>
-      <c r="P47" s="51" t="n"/>
-      <c r="Q47" s="51" t="n"/>
-      <c r="R47" s="51" t="n"/>
-      <c r="S47" s="51" t="n"/>
-      <c r="T47" s="51" t="n"/>
-      <c r="U47" s="51" t="n"/>
-      <c r="V47" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W47" s="58" t="n"/>
+      <c r="M47" s="55" t="n"/>
+      <c r="N47" s="55" t="n"/>
+      <c r="O47" s="55" t="n"/>
+      <c r="P47" s="55" t="n"/>
+      <c r="Q47" s="55" t="n"/>
+      <c r="R47" s="55" t="n"/>
+      <c r="S47" s="55" t="n"/>
+      <c r="T47" s="55" t="n"/>
+      <c r="U47" s="55" t="n"/>
+      <c r="V47" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W47" s="57" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
+      <c r="C48" s="46" t="n"/>
+      <c r="D48" s="46" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G48" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H48" s="49" t="n"/>
-      <c r="I48" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H48" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I48" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J48" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K48" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="55" t="n"/>
-      <c r="N48" s="55" t="n"/>
-      <c r="O48" s="55" t="n"/>
-      <c r="P48" s="55" t="n"/>
-      <c r="Q48" s="55" t="n"/>
-      <c r="R48" s="55" t="n"/>
-      <c r="S48" s="55" t="n"/>
-      <c r="T48" s="55" t="n"/>
-      <c r="U48" s="55" t="n"/>
-      <c r="V48" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W48" s="57" t="n"/>
+      <c r="M48" s="51" t="n"/>
+      <c r="N48" s="51" t="n"/>
+      <c r="O48" s="51" t="n"/>
+      <c r="P48" s="51" t="n"/>
+      <c r="Q48" s="51" t="n"/>
+      <c r="R48" s="51" t="n"/>
+      <c r="S48" s="51" t="n"/>
+      <c r="T48" s="51" t="n"/>
+      <c r="U48" s="51" t="n"/>
+      <c r="V48" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W48" s="58" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="46" t="n"/>
-      <c r="D49" s="46" t="n"/>
+      <c r="C49" s="53" t="n"/>
+      <c r="D49" s="53" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G49" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G49" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H49" s="49" t="n"/>
       <c r="I49" s="49" t="n"/>
       <c r="J49" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K49" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="51" t="n"/>
-      <c r="N49" s="51" t="n"/>
-      <c r="O49" s="51" t="n"/>
-      <c r="P49" s="51" t="n"/>
-      <c r="Q49" s="51" t="n"/>
-      <c r="R49" s="51" t="n"/>
-      <c r="S49" s="51" t="n"/>
-      <c r="T49" s="51" t="n"/>
-      <c r="U49" s="51" t="n"/>
-      <c r="V49" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W49" s="58" t="n"/>
+      <c r="M49" s="55" t="n"/>
+      <c r="N49" s="55" t="n"/>
+      <c r="O49" s="55" t="n"/>
+      <c r="P49" s="55" t="n"/>
+      <c r="Q49" s="55" t="n"/>
+      <c r="R49" s="55" t="n"/>
+      <c r="S49" s="55" t="n"/>
+      <c r="T49" s="55" t="n"/>
+      <c r="U49" s="55" t="n"/>
+      <c r="V49" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W49" s="57" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="53" t="n"/>
-      <c r="D50" s="53" t="n"/>
+      <c r="C50" s="46" t="n"/>
+      <c r="D50" s="46" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G50" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G50" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="49" t="n"/>
       <c r="J50" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="55" t="n"/>
-      <c r="N50" s="55" t="n"/>
-      <c r="O50" s="55" t="n"/>
-      <c r="P50" s="55" t="n"/>
-      <c r="Q50" s="55" t="n"/>
-      <c r="R50" s="55" t="n"/>
-      <c r="S50" s="55" t="n"/>
-      <c r="T50" s="55" t="n"/>
-      <c r="U50" s="55" t="n"/>
-      <c r="V50" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W50" s="57" t="n"/>
+      <c r="M50" s="51" t="n"/>
+      <c r="N50" s="51" t="n"/>
+      <c r="O50" s="51" t="n"/>
+      <c r="P50" s="51" t="n"/>
+      <c r="Q50" s="51" t="n"/>
+      <c r="R50" s="51" t="n"/>
+      <c r="S50" s="51" t="n"/>
+      <c r="T50" s="51" t="n"/>
+      <c r="U50" s="51" t="n"/>
+      <c r="V50" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W50" s="58" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="46" t="n"/>
-      <c r="D51" s="46" t="n"/>
+      <c r="C51" s="53" t="n"/>
+      <c r="D51" s="53" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G51" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H51" s="49" t="n"/>
       <c r="I51" s="49" t="n"/>
       <c r="J51" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="51" t="n"/>
-      <c r="N51" s="51" t="n"/>
-      <c r="O51" s="51" t="n"/>
-      <c r="P51" s="51" t="n"/>
-      <c r="Q51" s="51" t="n"/>
-      <c r="R51" s="51" t="n"/>
-      <c r="S51" s="51" t="n"/>
-      <c r="T51" s="51" t="n"/>
-      <c r="U51" s="51" t="n"/>
-      <c r="V51" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W51" s="58" t="n"/>
+      <c r="M51" s="55" t="n"/>
+      <c r="N51" s="55" t="n"/>
+      <c r="O51" s="55" t="n"/>
+      <c r="P51" s="55" t="n"/>
+      <c r="Q51" s="55" t="n"/>
+      <c r="R51" s="55" t="n"/>
+      <c r="S51" s="55" t="n"/>
+      <c r="T51" s="55" t="n"/>
+      <c r="U51" s="55" t="n"/>
+      <c r="V51" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W51" s="57" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="53" t="n"/>
-      <c r="D52" s="53" t="n"/>
+      <c r="C52" s="46" t="n"/>
+      <c r="D52" s="46" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G52" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G52" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H52" s="49" t="n"/>
       <c r="I52" s="49" t="n"/>
       <c r="J52" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="55" t="n"/>
-      <c r="N52" s="55" t="n"/>
-      <c r="O52" s="55" t="n"/>
-      <c r="P52" s="55" t="n"/>
-      <c r="Q52" s="55" t="n"/>
-      <c r="R52" s="55" t="n"/>
-      <c r="S52" s="55" t="n"/>
-      <c r="T52" s="55" t="n"/>
-      <c r="U52" s="55" t="n"/>
-      <c r="V52" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W52" s="57" t="n"/>
+      <c r="M52" s="51" t="n"/>
+      <c r="N52" s="51" t="n"/>
+      <c r="O52" s="51" t="n"/>
+      <c r="P52" s="51" t="n"/>
+      <c r="Q52" s="51" t="n"/>
+      <c r="R52" s="51" t="n"/>
+      <c r="S52" s="51" t="n"/>
+      <c r="T52" s="51" t="n"/>
+      <c r="U52" s="51" t="n"/>
+      <c r="V52" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W52" s="58" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="46" t="n"/>
-      <c r="D53" s="46" t="n"/>
+      <c r="C53" s="53" t="n"/>
+      <c r="D53" s="53" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G53" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G53" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H53" s="49" t="n"/>
       <c r="I53" s="49" t="n"/>
       <c r="J53" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="51" t="n"/>
-      <c r="N53" s="51" t="n"/>
-      <c r="O53" s="51" t="n"/>
-      <c r="P53" s="51" t="n"/>
-      <c r="Q53" s="51" t="n"/>
-      <c r="R53" s="51" t="n"/>
-      <c r="S53" s="51" t="n"/>
-      <c r="T53" s="51" t="n"/>
-      <c r="U53" s="51" t="n"/>
-      <c r="V53" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W53" s="58" t="n"/>
+      <c r="M53" s="55" t="n"/>
+      <c r="N53" s="55" t="n"/>
+      <c r="O53" s="55" t="n"/>
+      <c r="P53" s="55" t="n"/>
+      <c r="Q53" s="55" t="n"/>
+      <c r="R53" s="55" t="n"/>
+      <c r="S53" s="55" t="n"/>
+      <c r="T53" s="55" t="n"/>
+      <c r="U53" s="55" t="n"/>
+      <c r="V53" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W53" s="57" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="53" t="n"/>
-      <c r="D54" s="53" t="n"/>
+      <c r="C54" s="46" t="n"/>
+      <c r="D54" s="46" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G54" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G54" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="55" t="n"/>
-      <c r="N54" s="55" t="n"/>
-      <c r="O54" s="55" t="n"/>
-      <c r="P54" s="55" t="n"/>
-      <c r="Q54" s="55" t="n"/>
-      <c r="R54" s="55" t="n"/>
-      <c r="S54" s="55" t="n"/>
-      <c r="T54" s="55" t="n"/>
-      <c r="U54" s="55" t="n"/>
-      <c r="V54" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W54" s="57" t="n"/>
+      <c r="M54" s="51" t="n"/>
+      <c r="N54" s="51" t="n"/>
+      <c r="O54" s="51" t="n"/>
+      <c r="P54" s="51" t="n"/>
+      <c r="Q54" s="51" t="n"/>
+      <c r="R54" s="51" t="n"/>
+      <c r="S54" s="51" t="n"/>
+      <c r="T54" s="51" t="n"/>
+      <c r="U54" s="51" t="n"/>
+      <c r="V54" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W54" s="58" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="46" t="n"/>
-      <c r="D55" s="46" t="n"/>
+      <c r="C55" s="53" t="n"/>
+      <c r="D55" s="53" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G55" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="51" t="n"/>
-      <c r="N55" s="51" t="n"/>
-      <c r="O55" s="51" t="n"/>
-      <c r="P55" s="51" t="n"/>
-      <c r="Q55" s="51" t="n"/>
-      <c r="R55" s="51" t="n"/>
-      <c r="S55" s="51" t="n"/>
-      <c r="T55" s="51" t="n"/>
-      <c r="U55" s="51" t="n"/>
-      <c r="V55" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W55" s="58" t="n"/>
+      <c r="M55" s="55" t="n"/>
+      <c r="N55" s="55" t="n"/>
+      <c r="O55" s="55" t="n"/>
+      <c r="P55" s="55" t="n"/>
+      <c r="Q55" s="55" t="n"/>
+      <c r="R55" s="55" t="n"/>
+      <c r="S55" s="55" t="n"/>
+      <c r="T55" s="55" t="n"/>
+      <c r="U55" s="55" t="n"/>
+      <c r="V55" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W55" s="57" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="53" t="n"/>
-      <c r="D56" s="53" t="n"/>
+      <c r="C56" s="46" t="n"/>
+      <c r="D56" s="46" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G56" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="55" t="n"/>
-      <c r="N56" s="55" t="n"/>
-      <c r="O56" s="55" t="n"/>
-      <c r="P56" s="55" t="n"/>
-      <c r="Q56" s="55" t="n"/>
-      <c r="R56" s="55" t="n"/>
-      <c r="S56" s="55" t="n"/>
-      <c r="T56" s="55" t="n"/>
-      <c r="U56" s="55" t="n"/>
-      <c r="V56" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W56" s="57" t="n"/>
+      <c r="M56" s="51" t="n"/>
+      <c r="N56" s="51" t="n"/>
+      <c r="O56" s="51" t="n"/>
+      <c r="P56" s="51" t="n"/>
+      <c r="Q56" s="51" t="n"/>
+      <c r="R56" s="51" t="n"/>
+      <c r="S56" s="51" t="n"/>
+      <c r="T56" s="51" t="n"/>
+      <c r="U56" s="51" t="n"/>
+      <c r="V56" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W56" s="58" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="46" t="n"/>
-      <c r="D57" s="46" t="n"/>
+      <c r="C57" s="53" t="n"/>
+      <c r="D57" s="53" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G57" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G57" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="51" t="n"/>
-      <c r="N57" s="51" t="n"/>
-      <c r="O57" s="51" t="n"/>
-      <c r="P57" s="51" t="n"/>
-      <c r="Q57" s="51" t="n"/>
-      <c r="R57" s="51" t="n"/>
-      <c r="S57" s="51" t="n"/>
-      <c r="T57" s="51" t="n"/>
-      <c r="U57" s="51" t="n"/>
-      <c r="V57" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W57" s="58" t="n"/>
+      <c r="M57" s="55" t="n"/>
+      <c r="N57" s="55" t="n"/>
+      <c r="O57" s="55" t="n"/>
+      <c r="P57" s="55" t="n"/>
+      <c r="Q57" s="55" t="n"/>
+      <c r="R57" s="55" t="n"/>
+      <c r="S57" s="55" t="n"/>
+      <c r="T57" s="55" t="n"/>
+      <c r="U57" s="55" t="n"/>
+      <c r="V57" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W57" s="57" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="53" t="n"/>
-      <c r="D58" s="53" t="n"/>
+      <c r="C58" s="46" t="n"/>
+      <c r="D58" s="46" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G58" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G58" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="55" t="n"/>
-      <c r="N58" s="55" t="n"/>
-      <c r="O58" s="55" t="n"/>
-      <c r="P58" s="55" t="n"/>
-      <c r="Q58" s="55" t="n"/>
-      <c r="R58" s="55" t="n"/>
-      <c r="S58" s="55" t="n"/>
-      <c r="T58" s="55" t="n"/>
-      <c r="U58" s="55" t="n"/>
-      <c r="V58" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W58" s="57" t="n"/>
+      <c r="M58" s="51" t="n"/>
+      <c r="N58" s="51" t="n"/>
+      <c r="O58" s="51" t="n"/>
+      <c r="P58" s="51" t="n"/>
+      <c r="Q58" s="51" t="n"/>
+      <c r="R58" s="51" t="n"/>
+      <c r="S58" s="51" t="n"/>
+      <c r="T58" s="51" t="n"/>
+      <c r="U58" s="51" t="n"/>
+      <c r="V58" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W58" s="58" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="46" t="n"/>
-      <c r="D59" s="46" t="n"/>
+      <c r="C59" s="53" t="n"/>
+      <c r="D59" s="53" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G59" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G59" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="51" t="n"/>
-      <c r="N59" s="51" t="n"/>
-      <c r="O59" s="51" t="n"/>
-      <c r="P59" s="51" t="n"/>
-      <c r="Q59" s="51" t="n"/>
-      <c r="R59" s="51" t="n"/>
-      <c r="S59" s="51" t="n"/>
-      <c r="T59" s="51" t="n"/>
-      <c r="U59" s="51" t="n"/>
-      <c r="V59" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W59" s="58" t="n"/>
+      <c r="M59" s="55" t="n"/>
+      <c r="N59" s="55" t="n"/>
+      <c r="O59" s="55" t="n"/>
+      <c r="P59" s="55" t="n"/>
+      <c r="Q59" s="55" t="n"/>
+      <c r="R59" s="55" t="n"/>
+      <c r="S59" s="55" t="n"/>
+      <c r="T59" s="55" t="n"/>
+      <c r="U59" s="55" t="n"/>
+      <c r="V59" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W59" s="57" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
+      <c r="C60" s="46" t="n"/>
+      <c r="D60" s="46" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G60" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G60" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="55" t="n"/>
-      <c r="N60" s="55" t="n"/>
-      <c r="O60" s="55" t="n"/>
-      <c r="P60" s="55" t="n"/>
-      <c r="Q60" s="55" t="n"/>
-      <c r="R60" s="55" t="n"/>
-      <c r="S60" s="55" t="n"/>
-      <c r="T60" s="55" t="n"/>
-      <c r="U60" s="55" t="n"/>
-      <c r="V60" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W60" s="57" t="n"/>
+      <c r="M60" s="51" t="n"/>
+      <c r="N60" s="51" t="n"/>
+      <c r="O60" s="51" t="n"/>
+      <c r="P60" s="51" t="n"/>
+      <c r="Q60" s="51" t="n"/>
+      <c r="R60" s="51" t="n"/>
+      <c r="S60" s="51" t="n"/>
+      <c r="T60" s="51" t="n"/>
+      <c r="U60" s="51" t="n"/>
+      <c r="V60" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W60" s="58" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="46" t="n"/>
-      <c r="D61" s="46" t="n"/>
+      <c r="C61" s="53" t="n"/>
+      <c r="D61" s="53" t="n"/>
       <c r="E61" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F61" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G61" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G61" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
       <c r="J61" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K61" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="51" t="n"/>
-      <c r="N61" s="51" t="n"/>
-      <c r="O61" s="51" t="n"/>
-      <c r="P61" s="51" t="n"/>
-      <c r="Q61" s="51" t="n"/>
-      <c r="R61" s="51" t="n"/>
-      <c r="S61" s="51" t="n"/>
-      <c r="T61" s="51" t="n"/>
-      <c r="U61" s="51" t="n"/>
-      <c r="V61" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W61" s="58" t="n"/>
+      <c r="M61" s="55" t="n"/>
+      <c r="N61" s="55" t="n"/>
+      <c r="O61" s="55" t="n"/>
+      <c r="P61" s="55" t="n"/>
+      <c r="Q61" s="55" t="n"/>
+      <c r="R61" s="55" t="n"/>
+      <c r="S61" s="55" t="n"/>
+      <c r="T61" s="55" t="n"/>
+      <c r="U61" s="55" t="n"/>
+      <c r="V61" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W61" s="57" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B62" s="45" t="n"/>
-      <c r="C62" s="53" t="n"/>
-      <c r="D62" s="53" t="n"/>
+      <c r="C62" s="46" t="n"/>
+      <c r="D62" s="46" t="n"/>
       <c r="E62" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F62" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G62" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G62" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="49" t="n"/>
       <c r="J62" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K62" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L62" s="50" t="n"/>
-      <c r="M62" s="55" t="n"/>
-      <c r="N62" s="55" t="n"/>
-      <c r="O62" s="55" t="n"/>
-      <c r="P62" s="55" t="n"/>
-      <c r="Q62" s="55" t="n"/>
-      <c r="R62" s="55" t="n"/>
-      <c r="S62" s="55" t="n"/>
-      <c r="T62" s="55" t="n"/>
-      <c r="U62" s="55" t="n"/>
-      <c r="V62" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W62" s="57" t="n"/>
+      <c r="M62" s="51" t="n"/>
+      <c r="N62" s="51" t="n"/>
+      <c r="O62" s="51" t="n"/>
+      <c r="P62" s="51" t="n"/>
+      <c r="Q62" s="51" t="n"/>
+      <c r="R62" s="51" t="n"/>
+      <c r="S62" s="51" t="n"/>
+      <c r="T62" s="51" t="n"/>
+      <c r="U62" s="51" t="n"/>
+      <c r="V62" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W62" s="58" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B63" s="45" t="n"/>
-      <c r="C63" s="46" t="n"/>
-      <c r="D63" s="46" t="n"/>
+      <c r="C63" s="53" t="n"/>
+      <c r="D63" s="53" t="n"/>
       <c r="E63" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F63" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G63" s="48" t="n">
-        <v>24</v>
+      <c r="G63" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="49" t="n"/>
       <c r="J63" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K63" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L63" s="50" t="n"/>
-      <c r="M63" s="51" t="n"/>
-      <c r="N63" s="51" t="n"/>
-      <c r="O63" s="51" t="n"/>
-      <c r="P63" s="51" t="n"/>
-      <c r="Q63" s="51" t="n"/>
-      <c r="R63" s="51" t="n"/>
-      <c r="S63" s="51" t="n"/>
-      <c r="T63" s="51" t="n"/>
-      <c r="U63" s="51" t="n"/>
-      <c r="V63" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W63" s="58" t="n"/>
+      <c r="M63" s="55" t="n"/>
+      <c r="N63" s="55" t="n"/>
+      <c r="O63" s="55" t="n"/>
+      <c r="P63" s="55" t="n"/>
+      <c r="Q63" s="55" t="n"/>
+      <c r="R63" s="55" t="n"/>
+      <c r="S63" s="55" t="n"/>
+      <c r="T63" s="55" t="n"/>
+      <c r="U63" s="55" t="n"/>
+      <c r="V63" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W63" s="57" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B64" s="45" t="n"/>
-      <c r="C64" s="53" t="n"/>
-      <c r="D64" s="53" t="n"/>
+      <c r="C64" s="46" t="n"/>
+      <c r="D64" s="46" t="n"/>
       <c r="E64" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F64" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G64" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G64" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="49" t="n"/>
       <c r="J64" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K64" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L64" s="50" t="n"/>
-      <c r="M64" s="55" t="n"/>
-      <c r="N64" s="55" t="n"/>
-      <c r="O64" s="55" t="n"/>
-      <c r="P64" s="55" t="n"/>
-      <c r="Q64" s="55" t="n"/>
-      <c r="R64" s="55" t="n"/>
-      <c r="S64" s="55" t="n"/>
-      <c r="T64" s="55" t="n"/>
-      <c r="U64" s="55" t="n"/>
-      <c r="V64" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W64" s="57" t="n"/>
+      <c r="M64" s="51" t="n"/>
+      <c r="N64" s="51" t="n"/>
+      <c r="O64" s="51" t="n"/>
+      <c r="P64" s="51" t="n"/>
+      <c r="Q64" s="51" t="n"/>
+      <c r="R64" s="51" t="n"/>
+      <c r="S64" s="51" t="n"/>
+      <c r="T64" s="51" t="n"/>
+      <c r="U64" s="51" t="n"/>
+      <c r="V64" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W64" s="58" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B65" s="45" t="n"/>
-      <c r="C65" s="46" t="n"/>
-      <c r="D65" s="46" t="n"/>
+      <c r="C65" s="53" t="n"/>
+      <c r="D65" s="53" t="n"/>
       <c r="E65" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F65" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G65" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G65" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H65" s="49" t="n"/>
       <c r="I65" s="49" t="n"/>
       <c r="J65" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K65" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L65" s="50" t="n"/>
-      <c r="M65" s="51" t="n"/>
-      <c r="N65" s="51" t="n"/>
-      <c r="O65" s="51" t="n"/>
-      <c r="P65" s="51" t="n"/>
-      <c r="Q65" s="51" t="n"/>
-      <c r="R65" s="51" t="n"/>
-      <c r="S65" s="51" t="n"/>
-      <c r="T65" s="51" t="n"/>
-      <c r="U65" s="51" t="n"/>
-      <c r="V65" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W65" s="58" t="n"/>
+      <c r="M65" s="55" t="n"/>
+      <c r="N65" s="55" t="n"/>
+      <c r="O65" s="55" t="n"/>
+      <c r="P65" s="55" t="n"/>
+      <c r="Q65" s="55" t="n"/>
+      <c r="R65" s="55" t="n"/>
+      <c r="S65" s="55" t="n"/>
+      <c r="T65" s="55" t="n"/>
+      <c r="U65" s="55" t="n"/>
+      <c r="V65" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W65" s="57" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B66" s="45" t="n"/>
-      <c r="C66" s="53" t="n"/>
-      <c r="D66" s="53" t="n"/>
+      <c r="C66" s="46" t="n"/>
+      <c r="D66" s="46" t="n"/>
       <c r="E66" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F66" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G66" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H66" s="49" t="n"/>
       <c r="I66" s="49" t="n"/>
@@ -4916,51 +4930,92 @@
         <v>59</v>
       </c>
       <c r="K66" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L66" s="50" t="n"/>
-      <c r="M66" s="55" t="n"/>
-      <c r="N66" s="55" t="n"/>
-      <c r="O66" s="55" t="n"/>
-      <c r="P66" s="55" t="n"/>
-      <c r="Q66" s="55" t="n"/>
-      <c r="R66" s="55" t="n"/>
-      <c r="S66" s="55" t="n"/>
-      <c r="T66" s="55" t="n"/>
-      <c r="U66" s="55" t="n"/>
-      <c r="V66" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W66" s="57" t="n"/>
+      <c r="M66" s="51" t="n"/>
+      <c r="N66" s="51" t="n"/>
+      <c r="O66" s="51" t="n"/>
+      <c r="P66" s="51" t="n"/>
+      <c r="Q66" s="51" t="n"/>
+      <c r="R66" s="51" t="n"/>
+      <c r="S66" s="51" t="n"/>
+      <c r="T66" s="51" t="n"/>
+      <c r="U66" s="51" t="n"/>
+      <c r="V66" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W66" s="58" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B67" s="45" t="n"/>
-      <c r="C67" s="46" t="n"/>
-      <c r="D67" s="46" t="n"/>
-      <c r="E67" s="47" t="n"/>
-      <c r="F67" s="47" t="n"/>
-      <c r="G67" s="60" t="n"/>
+      <c r="C67" s="53" t="n"/>
+      <c r="D67" s="53" t="n"/>
+      <c r="E67" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F67" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G67" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H67" s="49" t="n"/>
       <c r="I67" s="49" t="n"/>
-      <c r="J67" s="50" t="n"/>
-      <c r="K67" s="50" t="n"/>
+      <c r="J67" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K67" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L67" s="50" t="n"/>
-      <c r="M67" s="51" t="n"/>
-      <c r="N67" s="51" t="n"/>
-      <c r="O67" s="51" t="n"/>
-      <c r="P67" s="51" t="n"/>
-      <c r="Q67" s="51" t="n"/>
-      <c r="R67" s="51" t="n"/>
-      <c r="S67" s="51" t="n"/>
-      <c r="T67" s="51" t="n"/>
-      <c r="U67" s="51" t="n"/>
-      <c r="V67" s="61" t="n"/>
-      <c r="W67" s="61" t="n"/>
+      <c r="M67" s="55" t="n"/>
+      <c r="N67" s="55" t="n"/>
+      <c r="O67" s="55" t="n"/>
+      <c r="P67" s="55" t="n"/>
+      <c r="Q67" s="55" t="n"/>
+      <c r="R67" s="55" t="n"/>
+      <c r="S67" s="55" t="n"/>
+      <c r="T67" s="55" t="n"/>
+      <c r="U67" s="55" t="n"/>
+      <c r="V67" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W67" s="57" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B68" s="45" t="n"/>
+      <c r="C68" s="46" t="n"/>
+      <c r="D68" s="46" t="n"/>
+      <c r="E68" s="47" t="n"/>
+      <c r="F68" s="47" t="n"/>
+      <c r="G68" s="60" t="n"/>
+      <c r="H68" s="49" t="n"/>
+      <c r="I68" s="49" t="n"/>
+      <c r="J68" s="50" t="n"/>
+      <c r="K68" s="50" t="n"/>
+      <c r="L68" s="50" t="n"/>
+      <c r="M68" s="51" t="n"/>
+      <c r="N68" s="51" t="n"/>
+      <c r="O68" s="51" t="n"/>
+      <c r="P68" s="51" t="n"/>
+      <c r="Q68" s="51" t="n"/>
+      <c r="R68" s="51" t="n"/>
+      <c r="S68" s="51" t="n"/>
+      <c r="T68" s="51" t="n"/>
+      <c r="U68" s="51" t="n"/>
+      <c r="V68" s="61" t="n"/>
+      <c r="W68" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W68"/>
+  <dimension ref="A1:W69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,7 +1982,7 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/10(五)</t>
+          <t>2026/04/13(一)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
@@ -1994,35 +1994,39 @@
       <c r="F4" s="65" t="n">
         <v>59</v>
       </c>
-      <c r="G4" s="71" t="n">
-        <v>31.4</v>
+      <c r="G4" s="66" t="n">
+        <v>20.3</v>
       </c>
       <c r="H4" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I4" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J4" s="68" t="n">
-        <v>13</v>
-      </c>
       <c r="K4" s="68" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L4" s="68" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M4" s="69" t="inlineStr">
         <is>
-          <t>中嘉博创、长源东谷、来伊份</t>
+          <t>中恒电气、圣阳股份</t>
         </is>
       </c>
       <c r="N4" s="69" t="inlineStr">
         <is>
+          <t>长源东谷</t>
+        </is>
+      </c>
+      <c r="O4" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="O4" s="69" t="inlineStr"/>
       <c r="P4" s="69" t="inlineStr"/>
       <c r="Q4" s="69" t="inlineStr"/>
       <c r="R4" s="69" t="inlineStr"/>
@@ -2030,54 +2034,54 @@
       <c r="T4" s="69" t="inlineStr"/>
       <c r="U4" s="69" t="inlineStr"/>
       <c r="V4" s="69" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="W4" s="69" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/09(四)</t>
+          <t>2026/04/10(五)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
       <c r="C5" s="64" t="inlineStr"/>
       <c r="D5" s="64" t="inlineStr"/>
       <c r="E5" s="65" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G5" s="66" t="n">
-        <v>23.2</v>
+        <v>59</v>
+      </c>
+      <c r="G5" s="71" t="n">
+        <v>31.4</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I5" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J5" s="68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K5" s="68" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L5" s="68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M5" s="69" t="inlineStr">
         <is>
+          <t>中嘉博创、长源东谷、来伊份</t>
+        </is>
+      </c>
+      <c r="N5" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="N5" s="69" t="inlineStr"/>
-      <c r="O5" s="69" t="inlineStr">
-        <is>
-          <t>汇源通信</t>
-        </is>
-      </c>
+      <c r="O5" s="69" t="inlineStr"/>
       <c r="P5" s="69" t="inlineStr"/>
       <c r="Q5" s="69" t="inlineStr"/>
       <c r="R5" s="69" t="inlineStr"/>
@@ -2085,54 +2089,54 @@
       <c r="T5" s="69" t="inlineStr"/>
       <c r="U5" s="69" t="inlineStr"/>
       <c r="V5" s="69" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="W5" s="69" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/04/08(三)</t>
+          <t>2026/04/09(四)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
       <c r="C6" s="64" t="inlineStr"/>
       <c r="D6" s="64" t="inlineStr"/>
       <c r="E6" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="G6" s="66" t="n">
-        <v>11.5</v>
+        <v>23.2</v>
       </c>
       <c r="H6" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I6" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J6" s="68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6" s="68" t="n">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="L6" s="68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M6" s="69" t="inlineStr">
         <is>
-          <t>中安科</t>
-        </is>
-      </c>
-      <c r="N6" s="69" t="inlineStr">
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="N6" s="69" t="inlineStr"/>
+      <c r="O6" s="69" t="inlineStr">
         <is>
           <t>汇源通信</t>
         </is>
       </c>
-      <c r="O6" s="69" t="inlineStr"/>
       <c r="P6" s="69" t="inlineStr"/>
       <c r="Q6" s="69" t="inlineStr"/>
       <c r="R6" s="69" t="inlineStr"/>
@@ -2147,20 +2151,20 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="62" t="inlineStr">
         <is>
-          <t>2026/04/07(二)</t>
+          <t>2026/04/08(三)</t>
         </is>
       </c>
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="64" t="inlineStr"/>
       <c r="D7" s="64" t="inlineStr"/>
       <c r="E7" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F7" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G7" s="66" t="n">
-        <v>21.8</v>
+        <v>11.5</v>
       </c>
       <c r="H7" s="67" t="n">
         <v>4</v>
@@ -2169,91 +2173,95 @@
         <v>4</v>
       </c>
       <c r="J7" s="68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K7" s="68" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="L7" s="68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M7" s="69" t="inlineStr">
         <is>
-          <t>汇源通信、新能泰山</t>
-        </is>
-      </c>
-      <c r="N7" s="69" t="inlineStr"/>
+          <t>中安科</t>
+        </is>
+      </c>
+      <c r="N7" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信</t>
+        </is>
+      </c>
       <c r="O7" s="69" t="inlineStr"/>
       <c r="P7" s="69" t="inlineStr"/>
-      <c r="Q7" s="69" t="inlineStr">
-        <is>
-          <t>津药药业</t>
-        </is>
-      </c>
+      <c r="Q7" s="69" t="inlineStr"/>
       <c r="R7" s="69" t="inlineStr"/>
       <c r="S7" s="69" t="inlineStr"/>
       <c r="T7" s="69" t="inlineStr"/>
       <c r="U7" s="69" t="inlineStr"/>
       <c r="V7" s="69" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W7" s="69" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="62" t="inlineStr">
         <is>
-          <t>2026/04/06(一)</t>
+          <t>2026/04/07(二)</t>
         </is>
       </c>
       <c r="B8" s="63" t="inlineStr"/>
       <c r="C8" s="64" t="inlineStr"/>
       <c r="D8" s="64" t="inlineStr"/>
       <c r="E8" s="65" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F8" s="65" t="n">
-        <v>36</v>
-      </c>
-      <c r="G8" s="71" t="n">
-        <v>25</v>
+        <v>93</v>
+      </c>
+      <c r="G8" s="66" t="n">
+        <v>21.8</v>
       </c>
       <c r="H8" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I8" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J8" s="68" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="L8" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K8" s="68" t="n">
-        <v>32</v>
-      </c>
-      <c r="L8" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" s="69" t="inlineStr"/>
+      <c r="M8" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信、新能泰山</t>
+        </is>
+      </c>
       <c r="N8" s="69" t="inlineStr"/>
       <c r="O8" s="69" t="inlineStr"/>
-      <c r="P8" s="69" t="inlineStr">
+      <c r="P8" s="69" t="inlineStr"/>
+      <c r="Q8" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="Q8" s="69" t="inlineStr"/>
       <c r="R8" s="69" t="inlineStr"/>
       <c r="S8" s="69" t="inlineStr"/>
       <c r="T8" s="69" t="inlineStr"/>
       <c r="U8" s="69" t="inlineStr"/>
       <c r="V8" s="69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W8" s="69" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="62" t="inlineStr">
         <is>
-          <t>2026/04/03(五)</t>
+          <t>2026/04/06(一)</t>
         </is>
       </c>
       <c r="B9" s="63" t="inlineStr"/>
@@ -2297,105 +2305,105 @@
       <c r="T9" s="69" t="inlineStr"/>
       <c r="U9" s="69" t="inlineStr"/>
       <c r="V9" s="69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W9" s="69" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B10" s="63" t="inlineStr"/>
       <c r="C10" s="64" t="inlineStr"/>
       <c r="D10" s="64" t="inlineStr"/>
       <c r="E10" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F10" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G10" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H10" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I10" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J10" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K10" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L10" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M10" s="69" t="inlineStr"/>
       <c r="N10" s="69" t="inlineStr"/>
-      <c r="O10" s="69" t="inlineStr">
+      <c r="O10" s="69" t="inlineStr"/>
+      <c r="P10" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P10" s="69" t="inlineStr"/>
       <c r="Q10" s="69" t="inlineStr"/>
       <c r="R10" s="69" t="inlineStr"/>
       <c r="S10" s="69" t="inlineStr"/>
       <c r="T10" s="69" t="inlineStr"/>
       <c r="U10" s="69" t="inlineStr"/>
       <c r="V10" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W10" s="69" t="inlineStr"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B11" s="63" t="inlineStr"/>
       <c r="C11" s="64" t="inlineStr"/>
       <c r="D11" s="64" t="inlineStr"/>
       <c r="E11" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F11" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G11" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G11" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H11" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I11" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J11" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K11" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L11" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" s="69" t="inlineStr"/>
-      <c r="N11" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M11" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N11" s="69" t="inlineStr"/>
+      <c r="O11" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O11" s="69" t="inlineStr"/>
       <c r="P11" s="69" t="inlineStr"/>
       <c r="Q11" s="69" t="inlineStr"/>
       <c r="R11" s="69" t="inlineStr"/>
@@ -2403,51 +2411,47 @@
       <c r="T11" s="69" t="inlineStr"/>
       <c r="U11" s="69" t="inlineStr"/>
       <c r="V11" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W11" s="69" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B12" s="63" t="inlineStr"/>
       <c r="C12" s="64" t="inlineStr"/>
       <c r="D12" s="64" t="inlineStr"/>
       <c r="E12" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F12" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G12" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G12" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H12" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I12" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J12" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K12" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L12" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M12" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M12" s="69" t="inlineStr"/>
+      <c r="N12" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N12" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O12" s="69" t="inlineStr"/>
@@ -2458,254 +2462,250 @@
       <c r="T12" s="69" t="inlineStr"/>
       <c r="U12" s="69" t="inlineStr"/>
       <c r="V12" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W12" s="69" t="inlineStr"/>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B13" s="63" t="inlineStr"/>
+      <c r="C13" s="64" t="inlineStr"/>
+      <c r="D13" s="64" t="inlineStr"/>
+      <c r="E13" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F13" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G13" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H13" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L13" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M13" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N13" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O13" s="69" t="inlineStr"/>
+      <c r="P13" s="69" t="inlineStr"/>
+      <c r="Q13" s="69" t="inlineStr"/>
+      <c r="R13" s="69" t="inlineStr"/>
+      <c r="S13" s="69" t="inlineStr"/>
+      <c r="T13" s="69" t="inlineStr"/>
+      <c r="U13" s="69" t="inlineStr"/>
+      <c r="V13" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W12" s="69" t="inlineStr"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="W13" s="69" t="inlineStr"/>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D13" s="38" t="inlineStr">
+      <c r="D14" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E13" s="39" t="n">
+      <c r="E14" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F13" s="39" t="n">
+      <c r="F14" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G13" s="40" t="n">
+      <c r="G14" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H13" s="41" t="n">
+      <c r="H14" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I13" s="41" t="n">
+      <c r="I14" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J13" s="42" t="n">
+      <c r="J14" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K13" s="42" t="n">
+      <c r="K14" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L13" s="42" t="n">
+      <c r="L14" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M13" s="43" t="inlineStr">
+      <c r="M14" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N13" s="43" t="inlineStr"/>
-      <c r="O13" s="43" t="inlineStr">
+      <c r="N14" s="43" t="inlineStr"/>
+      <c r="O14" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P13" s="43" t="inlineStr"/>
-      <c r="Q13" s="43" t="inlineStr"/>
-      <c r="R13" s="43" t="inlineStr"/>
-      <c r="S13" s="43" t="inlineStr"/>
-      <c r="T13" s="43" t="inlineStr"/>
-      <c r="U13" s="43" t="inlineStr"/>
-      <c r="V13" s="43" t="n">
+      <c r="P14" s="43" t="inlineStr"/>
+      <c r="Q14" s="43" t="inlineStr"/>
+      <c r="R14" s="43" t="inlineStr"/>
+      <c r="S14" s="43" t="inlineStr"/>
+      <c r="T14" s="43" t="inlineStr"/>
+      <c r="U14" s="43" t="inlineStr"/>
+      <c r="V14" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W13" s="43" t="inlineStr"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B14" s="45" t="n"/>
-      <c r="C14" s="46" t="n"/>
-      <c r="D14" s="46" t="n"/>
-      <c r="E14" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F14" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G14" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H14" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K14" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L14" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M14" s="51" t="n"/>
-      <c r="N14" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O14" s="51" t="n"/>
-      <c r="P14" s="51" t="n"/>
-      <c r="Q14" s="51" t="n"/>
-      <c r="R14" s="51" t="n"/>
-      <c r="S14" s="51" t="n"/>
-      <c r="T14" s="51" t="n"/>
-      <c r="U14" s="51" t="n"/>
-      <c r="V14" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W14" s="43" t="inlineStr"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B15" s="45" t="n"/>
-      <c r="C15" s="53" t="n"/>
-      <c r="D15" s="53" t="n"/>
+      <c r="C15" s="46" t="n"/>
+      <c r="D15" s="46" t="n"/>
       <c r="E15" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F15" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G15" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G15" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H15" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I15" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J15" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K15" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L15" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M15" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N15" s="55" t="n"/>
-      <c r="O15" s="55" t="n"/>
-      <c r="P15" s="55" t="n"/>
-      <c r="Q15" s="55" t="n"/>
-      <c r="R15" s="55" t="n"/>
-      <c r="S15" s="55" t="n"/>
-      <c r="T15" s="55" t="n"/>
-      <c r="U15" s="55" t="n"/>
-      <c r="V15" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W15" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M15" s="51" t="n"/>
+      <c r="N15" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O15" s="51" t="n"/>
+      <c r="P15" s="51" t="n"/>
+      <c r="Q15" s="51" t="n"/>
+      <c r="R15" s="51" t="n"/>
+      <c r="S15" s="51" t="n"/>
+      <c r="T15" s="51" t="n"/>
+      <c r="U15" s="51" t="n"/>
+      <c r="V15" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B16" s="45" t="n"/>
-      <c r="C16" s="46" t="n"/>
-      <c r="D16" s="46" t="n"/>
+      <c r="C16" s="53" t="n"/>
+      <c r="D16" s="53" t="n"/>
       <c r="E16" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F16" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G16" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G16" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H16" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I16" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J16" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K16" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L16" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M16" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N16" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O16" s="51" t="n"/>
-      <c r="P16" s="51" t="n"/>
-      <c r="Q16" s="51" t="n"/>
-      <c r="R16" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S16" s="51" t="n"/>
-      <c r="T16" s="51" t="n"/>
-      <c r="U16" s="51" t="n"/>
-      <c r="V16" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W16" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M16" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N16" s="55" t="n"/>
+      <c r="O16" s="55" t="n"/>
+      <c r="P16" s="55" t="n"/>
+      <c r="Q16" s="55" t="n"/>
+      <c r="R16" s="55" t="n"/>
+      <c r="S16" s="55" t="n"/>
+      <c r="T16" s="55" t="n"/>
+      <c r="U16" s="55" t="n"/>
+      <c r="V16" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W16" s="57" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B17" s="45" t="n"/>
-      <c r="C17" s="53" t="n"/>
-      <c r="D17" s="53" t="n"/>
+      <c r="C17" s="46" t="n"/>
+      <c r="D17" s="46" t="n"/>
       <c r="E17" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F17" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G17" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H17" s="49" t="n">
         <v>1</v>
@@ -2714,493 +2714,497 @@
         <v>1</v>
       </c>
       <c r="J17" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K17" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L17" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M17" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N17" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N17" s="55" t="n"/>
-      <c r="O17" s="55" t="n"/>
-      <c r="P17" s="55" t="n"/>
-      <c r="Q17" s="55" t="inlineStr">
+      <c r="O17" s="51" t="n"/>
+      <c r="P17" s="51" t="n"/>
+      <c r="Q17" s="51" t="n"/>
+      <c r="R17" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R17" s="55" t="n"/>
-      <c r="S17" s="55" t="n"/>
-      <c r="T17" s="55" t="n"/>
-      <c r="U17" s="55" t="n"/>
-      <c r="V17" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W17" s="57" t="n"/>
+      <c r="S17" s="51" t="n"/>
+      <c r="T17" s="51" t="n"/>
+      <c r="U17" s="51" t="n"/>
+      <c r="V17" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W17" s="58" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B18" s="45" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="53" t="n"/>
       <c r="E18" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F18" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G18" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G18" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H18" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I18" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J18" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K18" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L18" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N18" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O18" s="51" t="n"/>
-      <c r="P18" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M18" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N18" s="55" t="n"/>
+      <c r="O18" s="55" t="n"/>
+      <c r="P18" s="55" t="n"/>
+      <c r="Q18" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q18" s="51" t="n"/>
-      <c r="R18" s="51" t="n"/>
-      <c r="S18" s="51" t="n"/>
-      <c r="T18" s="51" t="n"/>
-      <c r="U18" s="51" t="n"/>
-      <c r="V18" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W18" s="58" t="n"/>
+      <c r="R18" s="55" t="n"/>
+      <c r="S18" s="55" t="n"/>
+      <c r="T18" s="55" t="n"/>
+      <c r="U18" s="55" t="n"/>
+      <c r="V18" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W18" s="57" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B19" s="45" t="n"/>
-      <c r="C19" s="53" t="n"/>
-      <c r="D19" s="53" t="n"/>
+      <c r="C19" s="46" t="n"/>
+      <c r="D19" s="46" t="n"/>
       <c r="E19" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F19" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G19" s="59" t="n">
-        <v>45.1</v>
+      <c r="G19" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H19" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J19" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K19" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L19" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M19" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N19" s="55" t="n"/>
-      <c r="O19" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P19" s="55" t="n"/>
-      <c r="Q19" s="55" t="n"/>
-      <c r="R19" s="55" t="n"/>
-      <c r="S19" s="55" t="n"/>
-      <c r="T19" s="55" t="n"/>
-      <c r="U19" s="55" t="n"/>
-      <c r="V19" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W19" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M19" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N19" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O19" s="51" t="n"/>
+      <c r="P19" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q19" s="51" t="n"/>
+      <c r="R19" s="51" t="n"/>
+      <c r="S19" s="51" t="n"/>
+      <c r="T19" s="51" t="n"/>
+      <c r="U19" s="51" t="n"/>
+      <c r="V19" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W19" s="58" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B20" s="45" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="46" t="n"/>
+      <c r="C20" s="53" t="n"/>
+      <c r="D20" s="53" t="n"/>
       <c r="E20" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F20" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G20" s="54" t="n">
-        <v>26.3</v>
+      <c r="G20" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H20" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J20" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K20" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L20" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M20" s="51" t="n"/>
-      <c r="N20" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M20" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N20" s="55" t="n"/>
+      <c r="O20" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O20" s="51" t="n"/>
-      <c r="P20" s="51" t="n"/>
-      <c r="Q20" s="51" t="n"/>
-      <c r="R20" s="51" t="n"/>
-      <c r="S20" s="51" t="n"/>
-      <c r="T20" s="51" t="n"/>
-      <c r="U20" s="51" t="n"/>
-      <c r="V20" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W20" s="58" t="n"/>
+      <c r="P20" s="55" t="n"/>
+      <c r="Q20" s="55" t="n"/>
+      <c r="R20" s="55" t="n"/>
+      <c r="S20" s="55" t="n"/>
+      <c r="T20" s="55" t="n"/>
+      <c r="U20" s="55" t="n"/>
+      <c r="V20" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W20" s="57" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="53" t="n"/>
-      <c r="D21" s="53" t="n"/>
+      <c r="C21" s="46" t="n"/>
+      <c r="D21" s="46" t="n"/>
       <c r="E21" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F21" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G21" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H21" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K21" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L21" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M21" s="51" t="n"/>
+      <c r="N21" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N21" s="55" t="n"/>
-      <c r="O21" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P21" s="55" t="n"/>
-      <c r="Q21" s="55" t="n"/>
-      <c r="R21" s="55" t="n"/>
-      <c r="S21" s="55" t="n"/>
-      <c r="T21" s="55" t="n"/>
-      <c r="U21" s="55" t="n"/>
-      <c r="V21" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W21" s="57" t="n"/>
+      <c r="O21" s="51" t="n"/>
+      <c r="P21" s="51" t="n"/>
+      <c r="Q21" s="51" t="n"/>
+      <c r="R21" s="51" t="n"/>
+      <c r="S21" s="51" t="n"/>
+      <c r="T21" s="51" t="n"/>
+      <c r="U21" s="51" t="n"/>
+      <c r="V21" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W21" s="58" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="46" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
       <c r="E22" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G22" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H22" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K22" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L22" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M22" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N22" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O22" s="51" t="n"/>
-      <c r="P22" s="51" t="n"/>
-      <c r="Q22" s="51" t="n"/>
-      <c r="R22" s="51" t="n"/>
-      <c r="S22" s="51" t="n"/>
-      <c r="T22" s="51" t="n"/>
-      <c r="U22" s="51" t="n"/>
-      <c r="V22" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W22" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M22" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N22" s="55" t="n"/>
+      <c r="O22" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P22" s="55" t="n"/>
+      <c r="Q22" s="55" t="n"/>
+      <c r="R22" s="55" t="n"/>
+      <c r="S22" s="55" t="n"/>
+      <c r="T22" s="55" t="n"/>
+      <c r="U22" s="55" t="n"/>
+      <c r="V22" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W22" s="57" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="53" t="n"/>
-      <c r="D23" s="53" t="n"/>
+      <c r="C23" s="46" t="n"/>
+      <c r="D23" s="46" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G23" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H23" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K23" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L23" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I23" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J23" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K23" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L23" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M23" s="55" t="inlineStr">
+      <c r="M23" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N23" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N23" s="55" t="n"/>
-      <c r="O23" s="55" t="n"/>
-      <c r="P23" s="55" t="n"/>
-      <c r="Q23" s="55" t="n"/>
-      <c r="R23" s="55" t="n"/>
-      <c r="S23" s="55" t="n"/>
-      <c r="T23" s="55" t="n"/>
-      <c r="U23" s="55" t="n"/>
-      <c r="V23" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W23" s="57" t="n"/>
+      <c r="O23" s="51" t="n"/>
+      <c r="P23" s="51" t="n"/>
+      <c r="Q23" s="51" t="n"/>
+      <c r="R23" s="51" t="n"/>
+      <c r="S23" s="51" t="n"/>
+      <c r="T23" s="51" t="n"/>
+      <c r="U23" s="51" t="n"/>
+      <c r="V23" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W23" s="58" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G24" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G24" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H24" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L24" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M24" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N24" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O24" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P24" s="51" t="n"/>
-      <c r="Q24" s="51" t="n"/>
-      <c r="R24" s="51" t="n"/>
-      <c r="S24" s="51" t="n"/>
-      <c r="T24" s="51" t="n"/>
-      <c r="U24" s="51" t="n"/>
-      <c r="V24" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W24" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M24" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N24" s="55" t="n"/>
+      <c r="O24" s="55" t="n"/>
+      <c r="P24" s="55" t="n"/>
+      <c r="Q24" s="55" t="n"/>
+      <c r="R24" s="55" t="n"/>
+      <c r="S24" s="55" t="n"/>
+      <c r="T24" s="55" t="n"/>
+      <c r="U24" s="55" t="n"/>
+      <c r="V24" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W24" s="57" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="53" t="n"/>
-      <c r="D25" s="53" t="n"/>
+      <c r="C25" s="46" t="n"/>
+      <c r="D25" s="46" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G25" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G25" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H25" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L25" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M25" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N25" s="55" t="inlineStr">
+      <c r="M25" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N25" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O25" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O25" s="55" t="n"/>
-      <c r="P25" s="55" t="n"/>
-      <c r="Q25" s="55" t="n"/>
-      <c r="R25" s="55" t="n"/>
-      <c r="S25" s="55" t="n"/>
-      <c r="T25" s="55" t="n"/>
-      <c r="U25" s="55" t="n"/>
-      <c r="V25" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W25" s="57" t="n"/>
+      <c r="P25" s="51" t="n"/>
+      <c r="Q25" s="51" t="n"/>
+      <c r="R25" s="51" t="n"/>
+      <c r="S25" s="51" t="n"/>
+      <c r="T25" s="51" t="n"/>
+      <c r="U25" s="51" t="n"/>
+      <c r="V25" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W25" s="58" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="46" t="n"/>
-      <c r="D26" s="46" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G26" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H26" s="49" t="n">
         <v>2</v>
@@ -3209,208 +3213,218 @@
         <v>2</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K26" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L26" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M26" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M26" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N26" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N26" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O26" s="51" t="n"/>
-      <c r="P26" s="51" t="n"/>
-      <c r="Q26" s="51" t="n"/>
-      <c r="R26" s="51" t="n"/>
-      <c r="S26" s="51" t="n"/>
-      <c r="T26" s="51" t="n"/>
-      <c r="U26" s="51" t="n"/>
-      <c r="V26" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W26" s="58" t="n"/>
+      <c r="O26" s="55" t="n"/>
+      <c r="P26" s="55" t="n"/>
+      <c r="Q26" s="55" t="n"/>
+      <c r="R26" s="55" t="n"/>
+      <c r="S26" s="55" t="n"/>
+      <c r="T26" s="55" t="n"/>
+      <c r="U26" s="55" t="n"/>
+      <c r="V26" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W26" s="57" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="53" t="n"/>
-      <c r="D27" s="53" t="n"/>
+      <c r="C27" s="46" t="n"/>
+      <c r="D27" s="46" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G27" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H27" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I27" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L27" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M27" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M27" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N27" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N27" s="55" t="n"/>
-      <c r="O27" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P27" s="55" t="n"/>
-      <c r="Q27" s="55" t="n"/>
-      <c r="R27" s="55" t="n"/>
-      <c r="S27" s="55" t="n"/>
-      <c r="T27" s="55" t="n"/>
-      <c r="U27" s="55" t="n"/>
-      <c r="V27" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W27" s="57" t="n"/>
+      <c r="O27" s="51" t="n"/>
+      <c r="P27" s="51" t="n"/>
+      <c r="Q27" s="51" t="n"/>
+      <c r="R27" s="51" t="n"/>
+      <c r="S27" s="51" t="n"/>
+      <c r="T27" s="51" t="n"/>
+      <c r="U27" s="51" t="n"/>
+      <c r="V27" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W27" s="58" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="46" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="53" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G28" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G28" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H28" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I28" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L28" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M28" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N28" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O28" s="51" t="n"/>
-      <c r="P28" s="51" t="n"/>
-      <c r="Q28" s="51" t="n"/>
-      <c r="R28" s="51" t="n"/>
-      <c r="S28" s="51" t="n"/>
-      <c r="T28" s="51" t="n"/>
-      <c r="U28" s="51" t="n"/>
-      <c r="V28" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W28" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M28" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N28" s="55" t="n"/>
+      <c r="O28" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P28" s="55" t="n"/>
+      <c r="Q28" s="55" t="n"/>
+      <c r="R28" s="55" t="n"/>
+      <c r="S28" s="55" t="n"/>
+      <c r="T28" s="55" t="n"/>
+      <c r="U28" s="55" t="n"/>
+      <c r="V28" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W28" s="57" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="53" t="n"/>
-      <c r="D29" s="53" t="n"/>
+      <c r="C29" s="46" t="n"/>
+      <c r="D29" s="46" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G29" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G29" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H29" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L29" s="50" t="n"/>
-      <c r="M29" s="55" t="n"/>
-      <c r="N29" s="55" t="n"/>
-      <c r="O29" s="55" t="n"/>
-      <c r="P29" s="55" t="n"/>
-      <c r="Q29" s="55" t="n"/>
-      <c r="R29" s="55" t="n"/>
-      <c r="S29" s="55" t="n"/>
-      <c r="T29" s="55" t="n"/>
-      <c r="U29" s="55" t="n"/>
-      <c r="V29" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W29" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L29" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M29" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N29" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O29" s="51" t="n"/>
+      <c r="P29" s="51" t="n"/>
+      <c r="Q29" s="51" t="n"/>
+      <c r="R29" s="51" t="n"/>
+      <c r="S29" s="51" t="n"/>
+      <c r="T29" s="51" t="n"/>
+      <c r="U29" s="51" t="n"/>
+      <c r="V29" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W29" s="58" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="46" t="n"/>
-      <c r="D30" s="46" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="53" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G30" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H30" s="49" t="n">
         <v>0</v>
@@ -3419,43 +3433,43 @@
         <v>0</v>
       </c>
       <c r="J30" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L30" s="50" t="n"/>
-      <c r="M30" s="51" t="n"/>
-      <c r="N30" s="51" t="n"/>
-      <c r="O30" s="51" t="n"/>
-      <c r="P30" s="51" t="n"/>
-      <c r="Q30" s="51" t="n"/>
-      <c r="R30" s="51" t="n"/>
-      <c r="S30" s="51" t="n"/>
-      <c r="T30" s="51" t="n"/>
-      <c r="U30" s="51" t="n"/>
-      <c r="V30" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W30" s="58" t="n"/>
+      <c r="M30" s="55" t="n"/>
+      <c r="N30" s="55" t="n"/>
+      <c r="O30" s="55" t="n"/>
+      <c r="P30" s="55" t="n"/>
+      <c r="Q30" s="55" t="n"/>
+      <c r="R30" s="55" t="n"/>
+      <c r="S30" s="55" t="n"/>
+      <c r="T30" s="55" t="n"/>
+      <c r="U30" s="55" t="n"/>
+      <c r="V30" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W30" s="57" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="53" t="n"/>
-      <c r="D31" s="53" t="n"/>
+      <c r="C31" s="46" t="n"/>
+      <c r="D31" s="46" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G31" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H31" s="49" t="n">
         <v>0</v>
@@ -3464,43 +3478,43 @@
         <v>0</v>
       </c>
       <c r="J31" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L31" s="50" t="n"/>
-      <c r="M31" s="55" t="n"/>
-      <c r="N31" s="55" t="n"/>
-      <c r="O31" s="55" t="n"/>
-      <c r="P31" s="55" t="n"/>
-      <c r="Q31" s="55" t="n"/>
-      <c r="R31" s="55" t="n"/>
-      <c r="S31" s="55" t="n"/>
-      <c r="T31" s="55" t="n"/>
-      <c r="U31" s="55" t="n"/>
-      <c r="V31" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W31" s="57" t="n"/>
+      <c r="M31" s="51" t="n"/>
+      <c r="N31" s="51" t="n"/>
+      <c r="O31" s="51" t="n"/>
+      <c r="P31" s="51" t="n"/>
+      <c r="Q31" s="51" t="n"/>
+      <c r="R31" s="51" t="n"/>
+      <c r="S31" s="51" t="n"/>
+      <c r="T31" s="51" t="n"/>
+      <c r="U31" s="51" t="n"/>
+      <c r="V31" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W31" s="58" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="46" t="n"/>
-      <c r="D32" s="46" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G32" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G32" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H32" s="49" t="n">
         <v>0</v>
@@ -3509,43 +3523,43 @@
         <v>0</v>
       </c>
       <c r="J32" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L32" s="50" t="n"/>
-      <c r="M32" s="51" t="n"/>
-      <c r="N32" s="51" t="n"/>
-      <c r="O32" s="51" t="n"/>
-      <c r="P32" s="51" t="n"/>
-      <c r="Q32" s="51" t="n"/>
-      <c r="R32" s="51" t="n"/>
-      <c r="S32" s="51" t="n"/>
-      <c r="T32" s="51" t="n"/>
-      <c r="U32" s="51" t="n"/>
-      <c r="V32" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W32" s="58" t="n"/>
+      <c r="M32" s="55" t="n"/>
+      <c r="N32" s="55" t="n"/>
+      <c r="O32" s="55" t="n"/>
+      <c r="P32" s="55" t="n"/>
+      <c r="Q32" s="55" t="n"/>
+      <c r="R32" s="55" t="n"/>
+      <c r="S32" s="55" t="n"/>
+      <c r="T32" s="55" t="n"/>
+      <c r="U32" s="55" t="n"/>
+      <c r="V32" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W32" s="57" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="53" t="n"/>
-      <c r="D33" s="53" t="n"/>
+      <c r="C33" s="46" t="n"/>
+      <c r="D33" s="46" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G33" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H33" s="49" t="n">
         <v>0</v>
@@ -3554,43 +3568,43 @@
         <v>0</v>
       </c>
       <c r="J33" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L33" s="50" t="n"/>
-      <c r="M33" s="55" t="n"/>
-      <c r="N33" s="55" t="n"/>
-      <c r="O33" s="55" t="n"/>
-      <c r="P33" s="55" t="n"/>
-      <c r="Q33" s="55" t="n"/>
-      <c r="R33" s="55" t="n"/>
-      <c r="S33" s="55" t="n"/>
-      <c r="T33" s="55" t="n"/>
-      <c r="U33" s="55" t="n"/>
-      <c r="V33" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W33" s="57" t="n"/>
+      <c r="M33" s="51" t="n"/>
+      <c r="N33" s="51" t="n"/>
+      <c r="O33" s="51" t="n"/>
+      <c r="P33" s="51" t="n"/>
+      <c r="Q33" s="51" t="n"/>
+      <c r="R33" s="51" t="n"/>
+      <c r="S33" s="51" t="n"/>
+      <c r="T33" s="51" t="n"/>
+      <c r="U33" s="51" t="n"/>
+      <c r="V33" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W33" s="58" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="46" t="n"/>
-      <c r="D34" s="46" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G34" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H34" s="49" t="n">
         <v>0</v>
@@ -3599,1371 +3613,1375 @@
         <v>0</v>
       </c>
       <c r="J34" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L34" s="50" t="n"/>
-      <c r="M34" s="51" t="n"/>
-      <c r="N34" s="51" t="n"/>
-      <c r="O34" s="51" t="n"/>
-      <c r="P34" s="51" t="n"/>
-      <c r="Q34" s="51" t="n"/>
-      <c r="R34" s="51" t="n"/>
-      <c r="S34" s="51" t="n"/>
-      <c r="T34" s="51" t="n"/>
-      <c r="U34" s="51" t="n"/>
-      <c r="V34" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W34" s="58" t="n"/>
+      <c r="M34" s="55" t="n"/>
+      <c r="N34" s="55" t="n"/>
+      <c r="O34" s="55" t="n"/>
+      <c r="P34" s="55" t="n"/>
+      <c r="Q34" s="55" t="n"/>
+      <c r="R34" s="55" t="n"/>
+      <c r="S34" s="55" t="n"/>
+      <c r="T34" s="55" t="n"/>
+      <c r="U34" s="55" t="n"/>
+      <c r="V34" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W34" s="57" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="53" t="n"/>
-      <c r="D35" s="53" t="n"/>
+      <c r="C35" s="46" t="n"/>
+      <c r="D35" s="46" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G35" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H35" s="49" t="n"/>
-      <c r="I35" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G35" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H35" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J35" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L35" s="50" t="n"/>
-      <c r="M35" s="55" t="n"/>
-      <c r="N35" s="55" t="n"/>
-      <c r="O35" s="55" t="n"/>
-      <c r="P35" s="55" t="n"/>
-      <c r="Q35" s="55" t="n"/>
-      <c r="R35" s="55" t="n"/>
-      <c r="S35" s="55" t="n"/>
-      <c r="T35" s="55" t="n"/>
-      <c r="U35" s="55" t="n"/>
-      <c r="V35" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W35" s="57" t="n"/>
+      <c r="M35" s="51" t="n"/>
+      <c r="N35" s="51" t="n"/>
+      <c r="O35" s="51" t="n"/>
+      <c r="P35" s="51" t="n"/>
+      <c r="Q35" s="51" t="n"/>
+      <c r="R35" s="51" t="n"/>
+      <c r="S35" s="51" t="n"/>
+      <c r="T35" s="51" t="n"/>
+      <c r="U35" s="51" t="n"/>
+      <c r="V35" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W35" s="58" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
+      <c r="C36" s="53" t="n"/>
+      <c r="D36" s="53" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G36" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H36" s="49" t="n"/>
       <c r="I36" s="49" t="n"/>
       <c r="J36" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="51" t="n"/>
-      <c r="N36" s="51" t="n"/>
-      <c r="O36" s="51" t="n"/>
-      <c r="P36" s="51" t="n"/>
-      <c r="Q36" s="51" t="n"/>
-      <c r="R36" s="51" t="n"/>
-      <c r="S36" s="51" t="n"/>
-      <c r="T36" s="51" t="n"/>
-      <c r="U36" s="51" t="n"/>
-      <c r="V36" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W36" s="58" t="n"/>
+      <c r="M36" s="55" t="n"/>
+      <c r="N36" s="55" t="n"/>
+      <c r="O36" s="55" t="n"/>
+      <c r="P36" s="55" t="n"/>
+      <c r="Q36" s="55" t="n"/>
+      <c r="R36" s="55" t="n"/>
+      <c r="S36" s="55" t="n"/>
+      <c r="T36" s="55" t="n"/>
+      <c r="U36" s="55" t="n"/>
+      <c r="V36" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W36" s="57" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="53" t="n"/>
-      <c r="D37" s="53" t="n"/>
+      <c r="C37" s="46" t="n"/>
+      <c r="D37" s="46" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G37" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H37" s="49" t="n"/>
       <c r="I37" s="49" t="n"/>
       <c r="J37" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="55" t="n"/>
-      <c r="N37" s="55" t="n"/>
-      <c r="O37" s="55" t="n"/>
-      <c r="P37" s="55" t="n"/>
-      <c r="Q37" s="55" t="n"/>
-      <c r="R37" s="55" t="n"/>
-      <c r="S37" s="55" t="n"/>
-      <c r="T37" s="55" t="n"/>
-      <c r="U37" s="55" t="n"/>
-      <c r="V37" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W37" s="57" t="n"/>
+      <c r="M37" s="51" t="n"/>
+      <c r="N37" s="51" t="n"/>
+      <c r="O37" s="51" t="n"/>
+      <c r="P37" s="51" t="n"/>
+      <c r="Q37" s="51" t="n"/>
+      <c r="R37" s="51" t="n"/>
+      <c r="S37" s="51" t="n"/>
+      <c r="T37" s="51" t="n"/>
+      <c r="U37" s="51" t="n"/>
+      <c r="V37" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W37" s="58" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="46" t="n"/>
-      <c r="D38" s="46" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G38" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H38" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I38" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H38" s="49" t="n"/>
+      <c r="I38" s="49" t="n"/>
       <c r="J38" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="51" t="n"/>
-      <c r="N38" s="51" t="n"/>
-      <c r="O38" s="51" t="n"/>
-      <c r="P38" s="51" t="n"/>
-      <c r="Q38" s="51" t="n"/>
-      <c r="R38" s="51" t="n"/>
-      <c r="S38" s="51" t="n"/>
-      <c r="T38" s="51" t="n"/>
-      <c r="U38" s="51" t="n"/>
-      <c r="V38" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W38" s="58" t="n"/>
+      <c r="M38" s="55" t="n"/>
+      <c r="N38" s="55" t="n"/>
+      <c r="O38" s="55" t="n"/>
+      <c r="P38" s="55" t="n"/>
+      <c r="Q38" s="55" t="n"/>
+      <c r="R38" s="55" t="n"/>
+      <c r="S38" s="55" t="n"/>
+      <c r="T38" s="55" t="n"/>
+      <c r="U38" s="55" t="n"/>
+      <c r="V38" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W38" s="57" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="53" t="n"/>
-      <c r="D39" s="53" t="n"/>
+      <c r="C39" s="46" t="n"/>
+      <c r="D39" s="46" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G39" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H39" s="49" t="n"/>
-      <c r="I39" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G39" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H39" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I39" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J39" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="55" t="n"/>
-      <c r="N39" s="55" t="n"/>
-      <c r="O39" s="55" t="n"/>
-      <c r="P39" s="55" t="n"/>
-      <c r="Q39" s="55" t="n"/>
-      <c r="R39" s="55" t="n"/>
-      <c r="S39" s="55" t="n"/>
-      <c r="T39" s="55" t="n"/>
-      <c r="U39" s="55" t="n"/>
-      <c r="V39" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W39" s="57" t="n"/>
+      <c r="M39" s="51" t="n"/>
+      <c r="N39" s="51" t="n"/>
+      <c r="O39" s="51" t="n"/>
+      <c r="P39" s="51" t="n"/>
+      <c r="Q39" s="51" t="n"/>
+      <c r="R39" s="51" t="n"/>
+      <c r="S39" s="51" t="n"/>
+      <c r="T39" s="51" t="n"/>
+      <c r="U39" s="51" t="n"/>
+      <c r="V39" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W39" s="58" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="46" t="n"/>
-      <c r="D40" s="46" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G40" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G40" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H40" s="49" t="n"/>
       <c r="I40" s="49" t="n"/>
       <c r="J40" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="51" t="n"/>
-      <c r="N40" s="51" t="n"/>
-      <c r="O40" s="51" t="n"/>
-      <c r="P40" s="51" t="n"/>
-      <c r="Q40" s="51" t="n"/>
-      <c r="R40" s="51" t="n"/>
-      <c r="S40" s="51" t="n"/>
-      <c r="T40" s="51" t="n"/>
-      <c r="U40" s="51" t="n"/>
-      <c r="V40" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W40" s="58" t="n"/>
+      <c r="M40" s="55" t="n"/>
+      <c r="N40" s="55" t="n"/>
+      <c r="O40" s="55" t="n"/>
+      <c r="P40" s="55" t="n"/>
+      <c r="Q40" s="55" t="n"/>
+      <c r="R40" s="55" t="n"/>
+      <c r="S40" s="55" t="n"/>
+      <c r="T40" s="55" t="n"/>
+      <c r="U40" s="55" t="n"/>
+      <c r="V40" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W40" s="57" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="53" t="n"/>
-      <c r="D41" s="53" t="n"/>
+      <c r="C41" s="46" t="n"/>
+      <c r="D41" s="46" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G41" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G41" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H41" s="49" t="n"/>
       <c r="I41" s="49" t="n"/>
       <c r="J41" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K41" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K41" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="55" t="n"/>
-      <c r="N41" s="55" t="n"/>
-      <c r="O41" s="55" t="n"/>
-      <c r="P41" s="55" t="n"/>
-      <c r="Q41" s="55" t="n"/>
-      <c r="R41" s="55" t="n"/>
-      <c r="S41" s="55" t="n"/>
-      <c r="T41" s="55" t="n"/>
-      <c r="U41" s="55" t="n"/>
-      <c r="V41" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W41" s="57" t="n"/>
+      <c r="M41" s="51" t="n"/>
+      <c r="N41" s="51" t="n"/>
+      <c r="O41" s="51" t="n"/>
+      <c r="P41" s="51" t="n"/>
+      <c r="Q41" s="51" t="n"/>
+      <c r="R41" s="51" t="n"/>
+      <c r="S41" s="51" t="n"/>
+      <c r="T41" s="51" t="n"/>
+      <c r="U41" s="51" t="n"/>
+      <c r="V41" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W41" s="58" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="46" t="n"/>
-      <c r="D42" s="46" t="n"/>
+      <c r="C42" s="53" t="n"/>
+      <c r="D42" s="53" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G42" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H42" s="49" t="n"/>
       <c r="I42" s="49" t="n"/>
       <c r="J42" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K42" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="51" t="n"/>
-      <c r="N42" s="51" t="n"/>
-      <c r="O42" s="51" t="n"/>
-      <c r="P42" s="51" t="n"/>
-      <c r="Q42" s="51" t="n"/>
-      <c r="R42" s="51" t="n"/>
-      <c r="S42" s="51" t="n"/>
-      <c r="T42" s="51" t="n"/>
-      <c r="U42" s="51" t="n"/>
-      <c r="V42" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W42" s="58" t="n"/>
+      <c r="M42" s="55" t="n"/>
+      <c r="N42" s="55" t="n"/>
+      <c r="O42" s="55" t="n"/>
+      <c r="P42" s="55" t="n"/>
+      <c r="Q42" s="55" t="n"/>
+      <c r="R42" s="55" t="n"/>
+      <c r="S42" s="55" t="n"/>
+      <c r="T42" s="55" t="n"/>
+      <c r="U42" s="55" t="n"/>
+      <c r="V42" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W42" s="57" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="53" t="n"/>
-      <c r="D43" s="53" t="n"/>
+      <c r="C43" s="46" t="n"/>
+      <c r="D43" s="46" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G43" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G43" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H43" s="49" t="n"/>
       <c r="I43" s="49" t="n"/>
       <c r="J43" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K43" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="55" t="n"/>
-      <c r="N43" s="55" t="n"/>
-      <c r="O43" s="55" t="n"/>
-      <c r="P43" s="55" t="n"/>
-      <c r="Q43" s="55" t="n"/>
-      <c r="R43" s="55" t="n"/>
-      <c r="S43" s="55" t="n"/>
-      <c r="T43" s="55" t="n"/>
-      <c r="U43" s="55" t="n"/>
-      <c r="V43" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W43" s="57" t="n"/>
+      <c r="M43" s="51" t="n"/>
+      <c r="N43" s="51" t="n"/>
+      <c r="O43" s="51" t="n"/>
+      <c r="P43" s="51" t="n"/>
+      <c r="Q43" s="51" t="n"/>
+      <c r="R43" s="51" t="n"/>
+      <c r="S43" s="51" t="n"/>
+      <c r="T43" s="51" t="n"/>
+      <c r="U43" s="51" t="n"/>
+      <c r="V43" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W43" s="58" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="46" t="n"/>
-      <c r="D44" s="46" t="n"/>
+      <c r="C44" s="53" t="n"/>
+      <c r="D44" s="53" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G44" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H44" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I44" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G44" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H44" s="49" t="n"/>
+      <c r="I44" s="49" t="n"/>
       <c r="J44" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K44" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="51" t="n"/>
-      <c r="N44" s="51" t="n"/>
-      <c r="O44" s="51" t="n"/>
-      <c r="P44" s="51" t="n"/>
-      <c r="Q44" s="51" t="n"/>
-      <c r="R44" s="51" t="n"/>
-      <c r="S44" s="51" t="n"/>
-      <c r="T44" s="51" t="n"/>
-      <c r="U44" s="51" t="n"/>
-      <c r="V44" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W44" s="58" t="n"/>
+      <c r="M44" s="55" t="n"/>
+      <c r="N44" s="55" t="n"/>
+      <c r="O44" s="55" t="n"/>
+      <c r="P44" s="55" t="n"/>
+      <c r="Q44" s="55" t="n"/>
+      <c r="R44" s="55" t="n"/>
+      <c r="S44" s="55" t="n"/>
+      <c r="T44" s="55" t="n"/>
+      <c r="U44" s="55" t="n"/>
+      <c r="V44" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W44" s="57" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="53" t="n"/>
-      <c r="D45" s="53" t="n"/>
+      <c r="C45" s="46" t="n"/>
+      <c r="D45" s="46" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G45" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H45" s="49" t="n"/>
-      <c r="I45" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H45" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I45" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J45" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K45" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="55" t="n"/>
-      <c r="N45" s="55" t="n"/>
-      <c r="O45" s="55" t="n"/>
-      <c r="P45" s="55" t="n"/>
-      <c r="Q45" s="55" t="n"/>
-      <c r="R45" s="55" t="n"/>
-      <c r="S45" s="55" t="n"/>
-      <c r="T45" s="55" t="n"/>
-      <c r="U45" s="55" t="n"/>
-      <c r="V45" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W45" s="57" t="n"/>
+      <c r="M45" s="51" t="n"/>
+      <c r="N45" s="51" t="n"/>
+      <c r="O45" s="51" t="n"/>
+      <c r="P45" s="51" t="n"/>
+      <c r="Q45" s="51" t="n"/>
+      <c r="R45" s="51" t="n"/>
+      <c r="S45" s="51" t="n"/>
+      <c r="T45" s="51" t="n"/>
+      <c r="U45" s="51" t="n"/>
+      <c r="V45" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W45" s="58" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="46" t="n"/>
-      <c r="D46" s="46" t="n"/>
+      <c r="C46" s="53" t="n"/>
+      <c r="D46" s="53" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G46" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H46" s="49" t="n"/>
       <c r="I46" s="49" t="n"/>
       <c r="J46" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K46" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="51" t="n"/>
-      <c r="N46" s="51" t="n"/>
-      <c r="O46" s="51" t="n"/>
-      <c r="P46" s="51" t="n"/>
-      <c r="Q46" s="51" t="n"/>
-      <c r="R46" s="51" t="n"/>
-      <c r="S46" s="51" t="n"/>
-      <c r="T46" s="51" t="n"/>
-      <c r="U46" s="51" t="n"/>
-      <c r="V46" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W46" s="58" t="n"/>
+      <c r="M46" s="55" t="n"/>
+      <c r="N46" s="55" t="n"/>
+      <c r="O46" s="55" t="n"/>
+      <c r="P46" s="55" t="n"/>
+      <c r="Q46" s="55" t="n"/>
+      <c r="R46" s="55" t="n"/>
+      <c r="S46" s="55" t="n"/>
+      <c r="T46" s="55" t="n"/>
+      <c r="U46" s="55" t="n"/>
+      <c r="V46" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W46" s="57" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="53" t="n"/>
-      <c r="D47" s="53" t="n"/>
+      <c r="C47" s="46" t="n"/>
+      <c r="D47" s="46" t="n"/>
       <c r="E47" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F47" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G47" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H47" s="49" t="n"/>
+      <c r="I47" s="49" t="n"/>
+      <c r="J47" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F47" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G47" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H47" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I47" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J47" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K47" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="55" t="n"/>
-      <c r="N47" s="55" t="n"/>
-      <c r="O47" s="55" t="n"/>
-      <c r="P47" s="55" t="n"/>
-      <c r="Q47" s="55" t="n"/>
-      <c r="R47" s="55" t="n"/>
-      <c r="S47" s="55" t="n"/>
-      <c r="T47" s="55" t="n"/>
-      <c r="U47" s="55" t="n"/>
-      <c r="V47" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W47" s="57" t="n"/>
+      <c r="M47" s="51" t="n"/>
+      <c r="N47" s="51" t="n"/>
+      <c r="O47" s="51" t="n"/>
+      <c r="P47" s="51" t="n"/>
+      <c r="Q47" s="51" t="n"/>
+      <c r="R47" s="51" t="n"/>
+      <c r="S47" s="51" t="n"/>
+      <c r="T47" s="51" t="n"/>
+      <c r="U47" s="51" t="n"/>
+      <c r="V47" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W47" s="58" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
+      <c r="C48" s="53" t="n"/>
+      <c r="D48" s="53" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G48" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H48" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I48" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J48" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K48" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="51" t="n"/>
-      <c r="N48" s="51" t="n"/>
-      <c r="O48" s="51" t="n"/>
-      <c r="P48" s="51" t="n"/>
-      <c r="Q48" s="51" t="n"/>
-      <c r="R48" s="51" t="n"/>
-      <c r="S48" s="51" t="n"/>
-      <c r="T48" s="51" t="n"/>
-      <c r="U48" s="51" t="n"/>
-      <c r="V48" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W48" s="58" t="n"/>
+      <c r="M48" s="55" t="n"/>
+      <c r="N48" s="55" t="n"/>
+      <c r="O48" s="55" t="n"/>
+      <c r="P48" s="55" t="n"/>
+      <c r="Q48" s="55" t="n"/>
+      <c r="R48" s="55" t="n"/>
+      <c r="S48" s="55" t="n"/>
+      <c r="T48" s="55" t="n"/>
+      <c r="U48" s="55" t="n"/>
+      <c r="V48" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W48" s="57" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="53" t="n"/>
-      <c r="D49" s="53" t="n"/>
+      <c r="C49" s="46" t="n"/>
+      <c r="D49" s="46" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G49" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H49" s="49" t="n"/>
-      <c r="I49" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H49" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I49" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J49" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K49" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="55" t="n"/>
-      <c r="N49" s="55" t="n"/>
-      <c r="O49" s="55" t="n"/>
-      <c r="P49" s="55" t="n"/>
-      <c r="Q49" s="55" t="n"/>
-      <c r="R49" s="55" t="n"/>
-      <c r="S49" s="55" t="n"/>
-      <c r="T49" s="55" t="n"/>
-      <c r="U49" s="55" t="n"/>
-      <c r="V49" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W49" s="57" t="n"/>
+      <c r="M49" s="51" t="n"/>
+      <c r="N49" s="51" t="n"/>
+      <c r="O49" s="51" t="n"/>
+      <c r="P49" s="51" t="n"/>
+      <c r="Q49" s="51" t="n"/>
+      <c r="R49" s="51" t="n"/>
+      <c r="S49" s="51" t="n"/>
+      <c r="T49" s="51" t="n"/>
+      <c r="U49" s="51" t="n"/>
+      <c r="V49" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W49" s="58" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
+      <c r="C50" s="53" t="n"/>
+      <c r="D50" s="53" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G50" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G50" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="49" t="n"/>
       <c r="J50" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K50" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="51" t="n"/>
-      <c r="N50" s="51" t="n"/>
-      <c r="O50" s="51" t="n"/>
-      <c r="P50" s="51" t="n"/>
-      <c r="Q50" s="51" t="n"/>
-      <c r="R50" s="51" t="n"/>
-      <c r="S50" s="51" t="n"/>
-      <c r="T50" s="51" t="n"/>
-      <c r="U50" s="51" t="n"/>
-      <c r="V50" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W50" s="58" t="n"/>
+      <c r="M50" s="55" t="n"/>
+      <c r="N50" s="55" t="n"/>
+      <c r="O50" s="55" t="n"/>
+      <c r="P50" s="55" t="n"/>
+      <c r="Q50" s="55" t="n"/>
+      <c r="R50" s="55" t="n"/>
+      <c r="S50" s="55" t="n"/>
+      <c r="T50" s="55" t="n"/>
+      <c r="U50" s="55" t="n"/>
+      <c r="V50" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W50" s="57" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="53" t="n"/>
-      <c r="D51" s="53" t="n"/>
+      <c r="C51" s="46" t="n"/>
+      <c r="D51" s="46" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G51" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G51" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H51" s="49" t="n"/>
       <c r="I51" s="49" t="n"/>
       <c r="J51" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="55" t="n"/>
-      <c r="N51" s="55" t="n"/>
-      <c r="O51" s="55" t="n"/>
-      <c r="P51" s="55" t="n"/>
-      <c r="Q51" s="55" t="n"/>
-      <c r="R51" s="55" t="n"/>
-      <c r="S51" s="55" t="n"/>
-      <c r="T51" s="55" t="n"/>
-      <c r="U51" s="55" t="n"/>
-      <c r="V51" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W51" s="57" t="n"/>
+      <c r="M51" s="51" t="n"/>
+      <c r="N51" s="51" t="n"/>
+      <c r="O51" s="51" t="n"/>
+      <c r="P51" s="51" t="n"/>
+      <c r="Q51" s="51" t="n"/>
+      <c r="R51" s="51" t="n"/>
+      <c r="S51" s="51" t="n"/>
+      <c r="T51" s="51" t="n"/>
+      <c r="U51" s="51" t="n"/>
+      <c r="V51" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W51" s="58" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="46" t="n"/>
-      <c r="D52" s="46" t="n"/>
+      <c r="C52" s="53" t="n"/>
+      <c r="D52" s="53" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G52" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H52" s="49" t="n"/>
       <c r="I52" s="49" t="n"/>
       <c r="J52" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="51" t="n"/>
-      <c r="N52" s="51" t="n"/>
-      <c r="O52" s="51" t="n"/>
-      <c r="P52" s="51" t="n"/>
-      <c r="Q52" s="51" t="n"/>
-      <c r="R52" s="51" t="n"/>
-      <c r="S52" s="51" t="n"/>
-      <c r="T52" s="51" t="n"/>
-      <c r="U52" s="51" t="n"/>
-      <c r="V52" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W52" s="58" t="n"/>
+      <c r="M52" s="55" t="n"/>
+      <c r="N52" s="55" t="n"/>
+      <c r="O52" s="55" t="n"/>
+      <c r="P52" s="55" t="n"/>
+      <c r="Q52" s="55" t="n"/>
+      <c r="R52" s="55" t="n"/>
+      <c r="S52" s="55" t="n"/>
+      <c r="T52" s="55" t="n"/>
+      <c r="U52" s="55" t="n"/>
+      <c r="V52" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W52" s="57" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="53" t="n"/>
-      <c r="D53" s="53" t="n"/>
+      <c r="C53" s="46" t="n"/>
+      <c r="D53" s="46" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G53" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G53" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H53" s="49" t="n"/>
       <c r="I53" s="49" t="n"/>
       <c r="J53" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="55" t="n"/>
-      <c r="N53" s="55" t="n"/>
-      <c r="O53" s="55" t="n"/>
-      <c r="P53" s="55" t="n"/>
-      <c r="Q53" s="55" t="n"/>
-      <c r="R53" s="55" t="n"/>
-      <c r="S53" s="55" t="n"/>
-      <c r="T53" s="55" t="n"/>
-      <c r="U53" s="55" t="n"/>
-      <c r="V53" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W53" s="57" t="n"/>
+      <c r="M53" s="51" t="n"/>
+      <c r="N53" s="51" t="n"/>
+      <c r="O53" s="51" t="n"/>
+      <c r="P53" s="51" t="n"/>
+      <c r="Q53" s="51" t="n"/>
+      <c r="R53" s="51" t="n"/>
+      <c r="S53" s="51" t="n"/>
+      <c r="T53" s="51" t="n"/>
+      <c r="U53" s="51" t="n"/>
+      <c r="V53" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W53" s="58" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="46" t="n"/>
-      <c r="D54" s="46" t="n"/>
+      <c r="C54" s="53" t="n"/>
+      <c r="D54" s="53" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G54" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G54" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="51" t="n"/>
-      <c r="N54" s="51" t="n"/>
-      <c r="O54" s="51" t="n"/>
-      <c r="P54" s="51" t="n"/>
-      <c r="Q54" s="51" t="n"/>
-      <c r="R54" s="51" t="n"/>
-      <c r="S54" s="51" t="n"/>
-      <c r="T54" s="51" t="n"/>
-      <c r="U54" s="51" t="n"/>
-      <c r="V54" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W54" s="58" t="n"/>
+      <c r="M54" s="55" t="n"/>
+      <c r="N54" s="55" t="n"/>
+      <c r="O54" s="55" t="n"/>
+      <c r="P54" s="55" t="n"/>
+      <c r="Q54" s="55" t="n"/>
+      <c r="R54" s="55" t="n"/>
+      <c r="S54" s="55" t="n"/>
+      <c r="T54" s="55" t="n"/>
+      <c r="U54" s="55" t="n"/>
+      <c r="V54" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W54" s="57" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="53" t="n"/>
-      <c r="D55" s="53" t="n"/>
+      <c r="C55" s="46" t="n"/>
+      <c r="D55" s="46" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G55" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G55" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="55" t="n"/>
-      <c r="N55" s="55" t="n"/>
-      <c r="O55" s="55" t="n"/>
-      <c r="P55" s="55" t="n"/>
-      <c r="Q55" s="55" t="n"/>
-      <c r="R55" s="55" t="n"/>
-      <c r="S55" s="55" t="n"/>
-      <c r="T55" s="55" t="n"/>
-      <c r="U55" s="55" t="n"/>
-      <c r="V55" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W55" s="57" t="n"/>
+      <c r="M55" s="51" t="n"/>
+      <c r="N55" s="51" t="n"/>
+      <c r="O55" s="51" t="n"/>
+      <c r="P55" s="51" t="n"/>
+      <c r="Q55" s="51" t="n"/>
+      <c r="R55" s="51" t="n"/>
+      <c r="S55" s="51" t="n"/>
+      <c r="T55" s="51" t="n"/>
+      <c r="U55" s="51" t="n"/>
+      <c r="V55" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W55" s="58" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="46" t="n"/>
-      <c r="D56" s="46" t="n"/>
+      <c r="C56" s="53" t="n"/>
+      <c r="D56" s="53" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G56" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="51" t="n"/>
-      <c r="N56" s="51" t="n"/>
-      <c r="O56" s="51" t="n"/>
-      <c r="P56" s="51" t="n"/>
-      <c r="Q56" s="51" t="n"/>
-      <c r="R56" s="51" t="n"/>
-      <c r="S56" s="51" t="n"/>
-      <c r="T56" s="51" t="n"/>
-      <c r="U56" s="51" t="n"/>
-      <c r="V56" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W56" s="58" t="n"/>
+      <c r="M56" s="55" t="n"/>
+      <c r="N56" s="55" t="n"/>
+      <c r="O56" s="55" t="n"/>
+      <c r="P56" s="55" t="n"/>
+      <c r="Q56" s="55" t="n"/>
+      <c r="R56" s="55" t="n"/>
+      <c r="S56" s="55" t="n"/>
+      <c r="T56" s="55" t="n"/>
+      <c r="U56" s="55" t="n"/>
+      <c r="V56" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W56" s="57" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="53" t="n"/>
-      <c r="D57" s="53" t="n"/>
+      <c r="C57" s="46" t="n"/>
+      <c r="D57" s="46" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G57" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="55" t="n"/>
-      <c r="N57" s="55" t="n"/>
-      <c r="O57" s="55" t="n"/>
-      <c r="P57" s="55" t="n"/>
-      <c r="Q57" s="55" t="n"/>
-      <c r="R57" s="55" t="n"/>
-      <c r="S57" s="55" t="n"/>
-      <c r="T57" s="55" t="n"/>
-      <c r="U57" s="55" t="n"/>
-      <c r="V57" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W57" s="57" t="n"/>
+      <c r="M57" s="51" t="n"/>
+      <c r="N57" s="51" t="n"/>
+      <c r="O57" s="51" t="n"/>
+      <c r="P57" s="51" t="n"/>
+      <c r="Q57" s="51" t="n"/>
+      <c r="R57" s="51" t="n"/>
+      <c r="S57" s="51" t="n"/>
+      <c r="T57" s="51" t="n"/>
+      <c r="U57" s="51" t="n"/>
+      <c r="V57" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W57" s="58" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="46" t="n"/>
-      <c r="D58" s="46" t="n"/>
+      <c r="C58" s="53" t="n"/>
+      <c r="D58" s="53" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G58" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G58" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="51" t="n"/>
-      <c r="N58" s="51" t="n"/>
-      <c r="O58" s="51" t="n"/>
-      <c r="P58" s="51" t="n"/>
-      <c r="Q58" s="51" t="n"/>
-      <c r="R58" s="51" t="n"/>
-      <c r="S58" s="51" t="n"/>
-      <c r="T58" s="51" t="n"/>
-      <c r="U58" s="51" t="n"/>
-      <c r="V58" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W58" s="58" t="n"/>
+      <c r="M58" s="55" t="n"/>
+      <c r="N58" s="55" t="n"/>
+      <c r="O58" s="55" t="n"/>
+      <c r="P58" s="55" t="n"/>
+      <c r="Q58" s="55" t="n"/>
+      <c r="R58" s="55" t="n"/>
+      <c r="S58" s="55" t="n"/>
+      <c r="T58" s="55" t="n"/>
+      <c r="U58" s="55" t="n"/>
+      <c r="V58" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W58" s="57" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="53" t="n"/>
-      <c r="D59" s="53" t="n"/>
+      <c r="C59" s="46" t="n"/>
+      <c r="D59" s="46" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G59" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G59" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="55" t="n"/>
-      <c r="N59" s="55" t="n"/>
-      <c r="O59" s="55" t="n"/>
-      <c r="P59" s="55" t="n"/>
-      <c r="Q59" s="55" t="n"/>
-      <c r="R59" s="55" t="n"/>
-      <c r="S59" s="55" t="n"/>
-      <c r="T59" s="55" t="n"/>
-      <c r="U59" s="55" t="n"/>
-      <c r="V59" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W59" s="57" t="n"/>
+      <c r="M59" s="51" t="n"/>
+      <c r="N59" s="51" t="n"/>
+      <c r="O59" s="51" t="n"/>
+      <c r="P59" s="51" t="n"/>
+      <c r="Q59" s="51" t="n"/>
+      <c r="R59" s="51" t="n"/>
+      <c r="S59" s="51" t="n"/>
+      <c r="T59" s="51" t="n"/>
+      <c r="U59" s="51" t="n"/>
+      <c r="V59" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W59" s="58" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
+      <c r="C60" s="53" t="n"/>
+      <c r="D60" s="53" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G60" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G60" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="51" t="n"/>
-      <c r="N60" s="51" t="n"/>
-      <c r="O60" s="51" t="n"/>
-      <c r="P60" s="51" t="n"/>
-      <c r="Q60" s="51" t="n"/>
-      <c r="R60" s="51" t="n"/>
-      <c r="S60" s="51" t="n"/>
-      <c r="T60" s="51" t="n"/>
-      <c r="U60" s="51" t="n"/>
-      <c r="V60" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W60" s="58" t="n"/>
+      <c r="M60" s="55" t="n"/>
+      <c r="N60" s="55" t="n"/>
+      <c r="O60" s="55" t="n"/>
+      <c r="P60" s="55" t="n"/>
+      <c r="Q60" s="55" t="n"/>
+      <c r="R60" s="55" t="n"/>
+      <c r="S60" s="55" t="n"/>
+      <c r="T60" s="55" t="n"/>
+      <c r="U60" s="55" t="n"/>
+      <c r="V60" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W60" s="57" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="53" t="n"/>
-      <c r="D61" s="53" t="n"/>
+      <c r="C61" s="46" t="n"/>
+      <c r="D61" s="46" t="n"/>
       <c r="E61" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F61" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G61" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G61" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
       <c r="J61" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K61" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="55" t="n"/>
-      <c r="N61" s="55" t="n"/>
-      <c r="O61" s="55" t="n"/>
-      <c r="P61" s="55" t="n"/>
-      <c r="Q61" s="55" t="n"/>
-      <c r="R61" s="55" t="n"/>
-      <c r="S61" s="55" t="n"/>
-      <c r="T61" s="55" t="n"/>
-      <c r="U61" s="55" t="n"/>
-      <c r="V61" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W61" s="57" t="n"/>
+      <c r="M61" s="51" t="n"/>
+      <c r="N61" s="51" t="n"/>
+      <c r="O61" s="51" t="n"/>
+      <c r="P61" s="51" t="n"/>
+      <c r="Q61" s="51" t="n"/>
+      <c r="R61" s="51" t="n"/>
+      <c r="S61" s="51" t="n"/>
+      <c r="T61" s="51" t="n"/>
+      <c r="U61" s="51" t="n"/>
+      <c r="V61" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W61" s="58" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B62" s="45" t="n"/>
-      <c r="C62" s="46" t="n"/>
-      <c r="D62" s="46" t="n"/>
+      <c r="C62" s="53" t="n"/>
+      <c r="D62" s="53" t="n"/>
       <c r="E62" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F62" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G62" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G62" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="49" t="n"/>
       <c r="J62" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K62" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L62" s="50" t="n"/>
-      <c r="M62" s="51" t="n"/>
-      <c r="N62" s="51" t="n"/>
-      <c r="O62" s="51" t="n"/>
-      <c r="P62" s="51" t="n"/>
-      <c r="Q62" s="51" t="n"/>
-      <c r="R62" s="51" t="n"/>
-      <c r="S62" s="51" t="n"/>
-      <c r="T62" s="51" t="n"/>
-      <c r="U62" s="51" t="n"/>
-      <c r="V62" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W62" s="58" t="n"/>
+      <c r="M62" s="55" t="n"/>
+      <c r="N62" s="55" t="n"/>
+      <c r="O62" s="55" t="n"/>
+      <c r="P62" s="55" t="n"/>
+      <c r="Q62" s="55" t="n"/>
+      <c r="R62" s="55" t="n"/>
+      <c r="S62" s="55" t="n"/>
+      <c r="T62" s="55" t="n"/>
+      <c r="U62" s="55" t="n"/>
+      <c r="V62" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W62" s="57" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B63" s="45" t="n"/>
-      <c r="C63" s="53" t="n"/>
-      <c r="D63" s="53" t="n"/>
+      <c r="C63" s="46" t="n"/>
+      <c r="D63" s="46" t="n"/>
       <c r="E63" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F63" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G63" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G63" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="49" t="n"/>
       <c r="J63" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K63" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L63" s="50" t="n"/>
-      <c r="M63" s="55" t="n"/>
-      <c r="N63" s="55" t="n"/>
-      <c r="O63" s="55" t="n"/>
-      <c r="P63" s="55" t="n"/>
-      <c r="Q63" s="55" t="n"/>
-      <c r="R63" s="55" t="n"/>
-      <c r="S63" s="55" t="n"/>
-      <c r="T63" s="55" t="n"/>
-      <c r="U63" s="55" t="n"/>
-      <c r="V63" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W63" s="57" t="n"/>
+      <c r="M63" s="51" t="n"/>
+      <c r="N63" s="51" t="n"/>
+      <c r="O63" s="51" t="n"/>
+      <c r="P63" s="51" t="n"/>
+      <c r="Q63" s="51" t="n"/>
+      <c r="R63" s="51" t="n"/>
+      <c r="S63" s="51" t="n"/>
+      <c r="T63" s="51" t="n"/>
+      <c r="U63" s="51" t="n"/>
+      <c r="V63" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W63" s="58" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B64" s="45" t="n"/>
-      <c r="C64" s="46" t="n"/>
-      <c r="D64" s="46" t="n"/>
+      <c r="C64" s="53" t="n"/>
+      <c r="D64" s="53" t="n"/>
       <c r="E64" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F64" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G64" s="48" t="n">
-        <v>24</v>
+      <c r="G64" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="49" t="n"/>
       <c r="J64" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K64" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L64" s="50" t="n"/>
-      <c r="M64" s="51" t="n"/>
-      <c r="N64" s="51" t="n"/>
-      <c r="O64" s="51" t="n"/>
-      <c r="P64" s="51" t="n"/>
-      <c r="Q64" s="51" t="n"/>
-      <c r="R64" s="51" t="n"/>
-      <c r="S64" s="51" t="n"/>
-      <c r="T64" s="51" t="n"/>
-      <c r="U64" s="51" t="n"/>
-      <c r="V64" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W64" s="58" t="n"/>
+      <c r="M64" s="55" t="n"/>
+      <c r="N64" s="55" t="n"/>
+      <c r="O64" s="55" t="n"/>
+      <c r="P64" s="55" t="n"/>
+      <c r="Q64" s="55" t="n"/>
+      <c r="R64" s="55" t="n"/>
+      <c r="S64" s="55" t="n"/>
+      <c r="T64" s="55" t="n"/>
+      <c r="U64" s="55" t="n"/>
+      <c r="V64" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W64" s="57" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B65" s="45" t="n"/>
-      <c r="C65" s="53" t="n"/>
-      <c r="D65" s="53" t="n"/>
+      <c r="C65" s="46" t="n"/>
+      <c r="D65" s="46" t="n"/>
       <c r="E65" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F65" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G65" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G65" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H65" s="49" t="n"/>
       <c r="I65" s="49" t="n"/>
       <c r="J65" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K65" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L65" s="50" t="n"/>
-      <c r="M65" s="55" t="n"/>
-      <c r="N65" s="55" t="n"/>
-      <c r="O65" s="55" t="n"/>
-      <c r="P65" s="55" t="n"/>
-      <c r="Q65" s="55" t="n"/>
-      <c r="R65" s="55" t="n"/>
-      <c r="S65" s="55" t="n"/>
-      <c r="T65" s="55" t="n"/>
-      <c r="U65" s="55" t="n"/>
-      <c r="V65" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W65" s="57" t="n"/>
+      <c r="M65" s="51" t="n"/>
+      <c r="N65" s="51" t="n"/>
+      <c r="O65" s="51" t="n"/>
+      <c r="P65" s="51" t="n"/>
+      <c r="Q65" s="51" t="n"/>
+      <c r="R65" s="51" t="n"/>
+      <c r="S65" s="51" t="n"/>
+      <c r="T65" s="51" t="n"/>
+      <c r="U65" s="51" t="n"/>
+      <c r="V65" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W65" s="58" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B66" s="45" t="n"/>
-      <c r="C66" s="46" t="n"/>
-      <c r="D66" s="46" t="n"/>
+      <c r="C66" s="53" t="n"/>
+      <c r="D66" s="53" t="n"/>
       <c r="E66" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F66" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G66" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G66" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H66" s="49" t="n"/>
       <c r="I66" s="49" t="n"/>
       <c r="J66" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K66" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L66" s="50" t="n"/>
-      <c r="M66" s="51" t="n"/>
-      <c r="N66" s="51" t="n"/>
-      <c r="O66" s="51" t="n"/>
-      <c r="P66" s="51" t="n"/>
-      <c r="Q66" s="51" t="n"/>
-      <c r="R66" s="51" t="n"/>
-      <c r="S66" s="51" t="n"/>
-      <c r="T66" s="51" t="n"/>
-      <c r="U66" s="51" t="n"/>
-      <c r="V66" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W66" s="58" t="n"/>
+      <c r="M66" s="55" t="n"/>
+      <c r="N66" s="55" t="n"/>
+      <c r="O66" s="55" t="n"/>
+      <c r="P66" s="55" t="n"/>
+      <c r="Q66" s="55" t="n"/>
+      <c r="R66" s="55" t="n"/>
+      <c r="S66" s="55" t="n"/>
+      <c r="T66" s="55" t="n"/>
+      <c r="U66" s="55" t="n"/>
+      <c r="V66" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W66" s="57" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B67" s="45" t="n"/>
-      <c r="C67" s="53" t="n"/>
-      <c r="D67" s="53" t="n"/>
+      <c r="C67" s="46" t="n"/>
+      <c r="D67" s="46" t="n"/>
       <c r="E67" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F67" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G67" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H67" s="49" t="n"/>
       <c r="I67" s="49" t="n"/>
@@ -4971,51 +4989,92 @@
         <v>59</v>
       </c>
       <c r="K67" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L67" s="50" t="n"/>
-      <c r="M67" s="55" t="n"/>
-      <c r="N67" s="55" t="n"/>
-      <c r="O67" s="55" t="n"/>
-      <c r="P67" s="55" t="n"/>
-      <c r="Q67" s="55" t="n"/>
-      <c r="R67" s="55" t="n"/>
-      <c r="S67" s="55" t="n"/>
-      <c r="T67" s="55" t="n"/>
-      <c r="U67" s="55" t="n"/>
-      <c r="V67" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W67" s="57" t="n"/>
+      <c r="M67" s="51" t="n"/>
+      <c r="N67" s="51" t="n"/>
+      <c r="O67" s="51" t="n"/>
+      <c r="P67" s="51" t="n"/>
+      <c r="Q67" s="51" t="n"/>
+      <c r="R67" s="51" t="n"/>
+      <c r="S67" s="51" t="n"/>
+      <c r="T67" s="51" t="n"/>
+      <c r="U67" s="51" t="n"/>
+      <c r="V67" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W67" s="58" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B68" s="45" t="n"/>
-      <c r="C68" s="46" t="n"/>
-      <c r="D68" s="46" t="n"/>
-      <c r="E68" s="47" t="n"/>
-      <c r="F68" s="47" t="n"/>
-      <c r="G68" s="60" t="n"/>
+      <c r="C68" s="53" t="n"/>
+      <c r="D68" s="53" t="n"/>
+      <c r="E68" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F68" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G68" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H68" s="49" t="n"/>
       <c r="I68" s="49" t="n"/>
-      <c r="J68" s="50" t="n"/>
-      <c r="K68" s="50" t="n"/>
+      <c r="J68" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K68" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L68" s="50" t="n"/>
-      <c r="M68" s="51" t="n"/>
-      <c r="N68" s="51" t="n"/>
-      <c r="O68" s="51" t="n"/>
-      <c r="P68" s="51" t="n"/>
-      <c r="Q68" s="51" t="n"/>
-      <c r="R68" s="51" t="n"/>
-      <c r="S68" s="51" t="n"/>
-      <c r="T68" s="51" t="n"/>
-      <c r="U68" s="51" t="n"/>
-      <c r="V68" s="61" t="n"/>
-      <c r="W68" s="61" t="n"/>
+      <c r="M68" s="55" t="n"/>
+      <c r="N68" s="55" t="n"/>
+      <c r="O68" s="55" t="n"/>
+      <c r="P68" s="55" t="n"/>
+      <c r="Q68" s="55" t="n"/>
+      <c r="R68" s="55" t="n"/>
+      <c r="S68" s="55" t="n"/>
+      <c r="T68" s="55" t="n"/>
+      <c r="U68" s="55" t="n"/>
+      <c r="V68" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W68" s="57" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B69" s="45" t="n"/>
+      <c r="C69" s="46" t="n"/>
+      <c r="D69" s="46" t="n"/>
+      <c r="E69" s="47" t="n"/>
+      <c r="F69" s="47" t="n"/>
+      <c r="G69" s="60" t="n"/>
+      <c r="H69" s="49" t="n"/>
+      <c r="I69" s="49" t="n"/>
+      <c r="J69" s="50" t="n"/>
+      <c r="K69" s="50" t="n"/>
+      <c r="L69" s="50" t="n"/>
+      <c r="M69" s="51" t="n"/>
+      <c r="N69" s="51" t="n"/>
+      <c r="O69" s="51" t="n"/>
+      <c r="P69" s="51" t="n"/>
+      <c r="Q69" s="51" t="n"/>
+      <c r="R69" s="51" t="n"/>
+      <c r="S69" s="51" t="n"/>
+      <c r="T69" s="51" t="n"/>
+      <c r="U69" s="51" t="n"/>
+      <c r="V69" s="61" t="n"/>
+      <c r="W69" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W69"/>
+  <dimension ref="A1:W70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,20 +1982,20 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/13(一)</t>
+          <t>2026/04/14(二)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G4" s="66" t="n">
-        <v>20.3</v>
+        <v>24.7</v>
       </c>
       <c r="H4" s="67" t="n">
         <v>4</v>
@@ -2004,30 +2004,30 @@
         <v>4</v>
       </c>
       <c r="J4" s="68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K4" s="68" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L4" s="68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M4" s="69" t="inlineStr">
         <is>
+          <t>美能能源</t>
+        </is>
+      </c>
+      <c r="N4" s="69" t="inlineStr">
+        <is>
           <t>中恒电气、圣阳股份</t>
         </is>
       </c>
-      <c r="N4" s="69" t="inlineStr">
-        <is>
-          <t>长源东谷</t>
-        </is>
-      </c>
-      <c r="O4" s="69" t="inlineStr">
+      <c r="O4" s="69" t="inlineStr"/>
+      <c r="P4" s="69" t="inlineStr">
         <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="P4" s="69" t="inlineStr"/>
       <c r="Q4" s="69" t="inlineStr"/>
       <c r="R4" s="69" t="inlineStr"/>
       <c r="S4" s="69" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/10(五)</t>
+          <t>2026/04/13(一)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
@@ -2053,35 +2053,39 @@
       <c r="F5" s="65" t="n">
         <v>59</v>
       </c>
-      <c r="G5" s="71" t="n">
-        <v>31.4</v>
+      <c r="G5" s="66" t="n">
+        <v>20.3</v>
       </c>
       <c r="H5" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I5" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" s="68" t="n">
-        <v>13</v>
-      </c>
       <c r="K5" s="68" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L5" s="68" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M5" s="69" t="inlineStr">
         <is>
-          <t>中嘉博创、长源东谷、来伊份</t>
+          <t>中恒电气、圣阳股份</t>
         </is>
       </c>
       <c r="N5" s="69" t="inlineStr">
         <is>
+          <t>长源东谷</t>
+        </is>
+      </c>
+      <c r="O5" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="O5" s="69" t="inlineStr"/>
       <c r="P5" s="69" t="inlineStr"/>
       <c r="Q5" s="69" t="inlineStr"/>
       <c r="R5" s="69" t="inlineStr"/>
@@ -2089,54 +2093,54 @@
       <c r="T5" s="69" t="inlineStr"/>
       <c r="U5" s="69" t="inlineStr"/>
       <c r="V5" s="69" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="W5" s="69" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/04/09(四)</t>
+          <t>2026/04/10(五)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
       <c r="C6" s="64" t="inlineStr"/>
       <c r="D6" s="64" t="inlineStr"/>
       <c r="E6" s="65" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G6" s="66" t="n">
-        <v>23.2</v>
+        <v>59</v>
+      </c>
+      <c r="G6" s="71" t="n">
+        <v>31.4</v>
       </c>
       <c r="H6" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I6" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J6" s="68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6" s="68" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L6" s="68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M6" s="69" t="inlineStr">
         <is>
+          <t>中嘉博创、长源东谷、来伊份</t>
+        </is>
+      </c>
+      <c r="N6" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="N6" s="69" t="inlineStr"/>
-      <c r="O6" s="69" t="inlineStr">
-        <is>
-          <t>汇源通信</t>
-        </is>
-      </c>
+      <c r="O6" s="69" t="inlineStr"/>
       <c r="P6" s="69" t="inlineStr"/>
       <c r="Q6" s="69" t="inlineStr"/>
       <c r="R6" s="69" t="inlineStr"/>
@@ -2144,54 +2148,54 @@
       <c r="T6" s="69" t="inlineStr"/>
       <c r="U6" s="69" t="inlineStr"/>
       <c r="V6" s="69" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="W6" s="69" t="inlineStr"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="62" t="inlineStr">
         <is>
-          <t>2026/04/08(三)</t>
+          <t>2026/04/09(四)</t>
         </is>
       </c>
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="64" t="inlineStr"/>
       <c r="D7" s="64" t="inlineStr"/>
       <c r="E7" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="F7" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="G7" s="66" t="n">
-        <v>11.5</v>
+        <v>23.2</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I7" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J7" s="68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K7" s="68" t="n">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="L7" s="68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M7" s="69" t="inlineStr">
         <is>
-          <t>中安科</t>
-        </is>
-      </c>
-      <c r="N7" s="69" t="inlineStr">
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="N7" s="69" t="inlineStr"/>
+      <c r="O7" s="69" t="inlineStr">
         <is>
           <t>汇源通信</t>
         </is>
       </c>
-      <c r="O7" s="69" t="inlineStr"/>
       <c r="P7" s="69" t="inlineStr"/>
       <c r="Q7" s="69" t="inlineStr"/>
       <c r="R7" s="69" t="inlineStr"/>
@@ -2206,20 +2210,20 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="62" t="inlineStr">
         <is>
-          <t>2026/04/07(二)</t>
+          <t>2026/04/08(三)</t>
         </is>
       </c>
       <c r="B8" s="63" t="inlineStr"/>
       <c r="C8" s="64" t="inlineStr"/>
       <c r="D8" s="64" t="inlineStr"/>
       <c r="E8" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F8" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G8" s="66" t="n">
-        <v>21.8</v>
+        <v>11.5</v>
       </c>
       <c r="H8" s="67" t="n">
         <v>4</v>
@@ -2228,91 +2232,95 @@
         <v>4</v>
       </c>
       <c r="J8" s="68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K8" s="68" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="L8" s="68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M8" s="69" t="inlineStr">
         <is>
-          <t>汇源通信、新能泰山</t>
-        </is>
-      </c>
-      <c r="N8" s="69" t="inlineStr"/>
+          <t>中安科</t>
+        </is>
+      </c>
+      <c r="N8" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信</t>
+        </is>
+      </c>
       <c r="O8" s="69" t="inlineStr"/>
       <c r="P8" s="69" t="inlineStr"/>
-      <c r="Q8" s="69" t="inlineStr">
-        <is>
-          <t>津药药业</t>
-        </is>
-      </c>
+      <c r="Q8" s="69" t="inlineStr"/>
       <c r="R8" s="69" t="inlineStr"/>
       <c r="S8" s="69" t="inlineStr"/>
       <c r="T8" s="69" t="inlineStr"/>
       <c r="U8" s="69" t="inlineStr"/>
       <c r="V8" s="69" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W8" s="69" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="62" t="inlineStr">
         <is>
-          <t>2026/04/06(一)</t>
+          <t>2026/04/07(二)</t>
         </is>
       </c>
       <c r="B9" s="63" t="inlineStr"/>
       <c r="C9" s="64" t="inlineStr"/>
       <c r="D9" s="64" t="inlineStr"/>
       <c r="E9" s="65" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F9" s="65" t="n">
-        <v>36</v>
-      </c>
-      <c r="G9" s="71" t="n">
-        <v>25</v>
+        <v>93</v>
+      </c>
+      <c r="G9" s="66" t="n">
+        <v>21.8</v>
       </c>
       <c r="H9" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I9" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J9" s="68" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="L9" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K9" s="68" t="n">
-        <v>32</v>
-      </c>
-      <c r="L9" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" s="69" t="inlineStr"/>
+      <c r="M9" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信、新能泰山</t>
+        </is>
+      </c>
       <c r="N9" s="69" t="inlineStr"/>
       <c r="O9" s="69" t="inlineStr"/>
-      <c r="P9" s="69" t="inlineStr">
+      <c r="P9" s="69" t="inlineStr"/>
+      <c r="Q9" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="Q9" s="69" t="inlineStr"/>
       <c r="R9" s="69" t="inlineStr"/>
       <c r="S9" s="69" t="inlineStr"/>
       <c r="T9" s="69" t="inlineStr"/>
       <c r="U9" s="69" t="inlineStr"/>
       <c r="V9" s="69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W9" s="69" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="62" t="inlineStr">
         <is>
-          <t>2026/04/03(五)</t>
+          <t>2026/04/06(一)</t>
         </is>
       </c>
       <c r="B10" s="63" t="inlineStr"/>
@@ -2356,105 +2364,105 @@
       <c r="T10" s="69" t="inlineStr"/>
       <c r="U10" s="69" t="inlineStr"/>
       <c r="V10" s="69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W10" s="69" t="inlineStr"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B11" s="63" t="inlineStr"/>
       <c r="C11" s="64" t="inlineStr"/>
       <c r="D11" s="64" t="inlineStr"/>
       <c r="E11" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F11" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G11" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I11" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J11" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K11" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L11" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M11" s="69" t="inlineStr"/>
       <c r="N11" s="69" t="inlineStr"/>
-      <c r="O11" s="69" t="inlineStr">
+      <c r="O11" s="69" t="inlineStr"/>
+      <c r="P11" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P11" s="69" t="inlineStr"/>
       <c r="Q11" s="69" t="inlineStr"/>
       <c r="R11" s="69" t="inlineStr"/>
       <c r="S11" s="69" t="inlineStr"/>
       <c r="T11" s="69" t="inlineStr"/>
       <c r="U11" s="69" t="inlineStr"/>
       <c r="V11" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W11" s="69" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B12" s="63" t="inlineStr"/>
       <c r="C12" s="64" t="inlineStr"/>
       <c r="D12" s="64" t="inlineStr"/>
       <c r="E12" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F12" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G12" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G12" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H12" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I12" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K12" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L12" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M12" s="69" t="inlineStr"/>
-      <c r="N12" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M12" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N12" s="69" t="inlineStr"/>
+      <c r="O12" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O12" s="69" t="inlineStr"/>
       <c r="P12" s="69" t="inlineStr"/>
       <c r="Q12" s="69" t="inlineStr"/>
       <c r="R12" s="69" t="inlineStr"/>
@@ -2462,51 +2470,47 @@
       <c r="T12" s="69" t="inlineStr"/>
       <c r="U12" s="69" t="inlineStr"/>
       <c r="V12" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W12" s="69" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B13" s="63" t="inlineStr"/>
       <c r="C13" s="64" t="inlineStr"/>
       <c r="D13" s="64" t="inlineStr"/>
       <c r="E13" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F13" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G13" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G13" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H13" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I13" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J13" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K13" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L13" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M13" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M13" s="69" t="inlineStr"/>
+      <c r="N13" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N13" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O13" s="69" t="inlineStr"/>
@@ -2517,254 +2521,250 @@
       <c r="T13" s="69" t="inlineStr"/>
       <c r="U13" s="69" t="inlineStr"/>
       <c r="V13" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W13" s="69" t="inlineStr"/>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B14" s="63" t="inlineStr"/>
+      <c r="C14" s="64" t="inlineStr"/>
+      <c r="D14" s="64" t="inlineStr"/>
+      <c r="E14" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F14" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G14" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H14" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L14" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N14" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O14" s="69" t="inlineStr"/>
+      <c r="P14" s="69" t="inlineStr"/>
+      <c r="Q14" s="69" t="inlineStr"/>
+      <c r="R14" s="69" t="inlineStr"/>
+      <c r="S14" s="69" t="inlineStr"/>
+      <c r="T14" s="69" t="inlineStr"/>
+      <c r="U14" s="69" t="inlineStr"/>
+      <c r="V14" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="69" t="inlineStr"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="W14" s="69" t="inlineStr"/>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D14" s="38" t="inlineStr">
+      <c r="D15" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E14" s="39" t="n">
+      <c r="E15" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F14" s="39" t="n">
+      <c r="F15" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G14" s="40" t="n">
+      <c r="G15" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H14" s="41" t="n">
+      <c r="H15" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I14" s="41" t="n">
+      <c r="I15" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J14" s="42" t="n">
+      <c r="J15" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K14" s="42" t="n">
+      <c r="K15" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L14" s="42" t="n">
+      <c r="L15" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M14" s="43" t="inlineStr">
+      <c r="M15" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N14" s="43" t="inlineStr"/>
-      <c r="O14" s="43" t="inlineStr">
+      <c r="N15" s="43" t="inlineStr"/>
+      <c r="O15" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P14" s="43" t="inlineStr"/>
-      <c r="Q14" s="43" t="inlineStr"/>
-      <c r="R14" s="43" t="inlineStr"/>
-      <c r="S14" s="43" t="inlineStr"/>
-      <c r="T14" s="43" t="inlineStr"/>
-      <c r="U14" s="43" t="inlineStr"/>
-      <c r="V14" s="43" t="n">
+      <c r="P15" s="43" t="inlineStr"/>
+      <c r="Q15" s="43" t="inlineStr"/>
+      <c r="R15" s="43" t="inlineStr"/>
+      <c r="S15" s="43" t="inlineStr"/>
+      <c r="T15" s="43" t="inlineStr"/>
+      <c r="U15" s="43" t="inlineStr"/>
+      <c r="V15" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W14" s="43" t="inlineStr"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B15" s="45" t="n"/>
-      <c r="C15" s="46" t="n"/>
-      <c r="D15" s="46" t="n"/>
-      <c r="E15" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F15" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G15" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H15" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K15" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L15" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M15" s="51" t="n"/>
-      <c r="N15" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O15" s="51" t="n"/>
-      <c r="P15" s="51" t="n"/>
-      <c r="Q15" s="51" t="n"/>
-      <c r="R15" s="51" t="n"/>
-      <c r="S15" s="51" t="n"/>
-      <c r="T15" s="51" t="n"/>
-      <c r="U15" s="51" t="n"/>
-      <c r="V15" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W15" s="43" t="inlineStr"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B16" s="45" t="n"/>
-      <c r="C16" s="53" t="n"/>
-      <c r="D16" s="53" t="n"/>
+      <c r="C16" s="46" t="n"/>
+      <c r="D16" s="46" t="n"/>
       <c r="E16" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F16" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G16" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G16" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H16" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I16" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J16" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K16" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L16" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M16" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N16" s="55" t="n"/>
-      <c r="O16" s="55" t="n"/>
-      <c r="P16" s="55" t="n"/>
-      <c r="Q16" s="55" t="n"/>
-      <c r="R16" s="55" t="n"/>
-      <c r="S16" s="55" t="n"/>
-      <c r="T16" s="55" t="n"/>
-      <c r="U16" s="55" t="n"/>
-      <c r="V16" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W16" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M16" s="51" t="n"/>
+      <c r="N16" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O16" s="51" t="n"/>
+      <c r="P16" s="51" t="n"/>
+      <c r="Q16" s="51" t="n"/>
+      <c r="R16" s="51" t="n"/>
+      <c r="S16" s="51" t="n"/>
+      <c r="T16" s="51" t="n"/>
+      <c r="U16" s="51" t="n"/>
+      <c r="V16" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B17" s="45" t="n"/>
-      <c r="C17" s="46" t="n"/>
-      <c r="D17" s="46" t="n"/>
+      <c r="C17" s="53" t="n"/>
+      <c r="D17" s="53" t="n"/>
       <c r="E17" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F17" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G17" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G17" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H17" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J17" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K17" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L17" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M17" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N17" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O17" s="51" t="n"/>
-      <c r="P17" s="51" t="n"/>
-      <c r="Q17" s="51" t="n"/>
-      <c r="R17" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S17" s="51" t="n"/>
-      <c r="T17" s="51" t="n"/>
-      <c r="U17" s="51" t="n"/>
-      <c r="V17" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W17" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M17" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N17" s="55" t="n"/>
+      <c r="O17" s="55" t="n"/>
+      <c r="P17" s="55" t="n"/>
+      <c r="Q17" s="55" t="n"/>
+      <c r="R17" s="55" t="n"/>
+      <c r="S17" s="55" t="n"/>
+      <c r="T17" s="55" t="n"/>
+      <c r="U17" s="55" t="n"/>
+      <c r="V17" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W17" s="57" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B18" s="45" t="n"/>
-      <c r="C18" s="53" t="n"/>
-      <c r="D18" s="53" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="46" t="n"/>
       <c r="E18" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F18" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G18" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H18" s="49" t="n">
         <v>1</v>
@@ -2773,493 +2773,497 @@
         <v>1</v>
       </c>
       <c r="J18" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K18" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L18" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M18" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N18" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N18" s="55" t="n"/>
-      <c r="O18" s="55" t="n"/>
-      <c r="P18" s="55" t="n"/>
-      <c r="Q18" s="55" t="inlineStr">
+      <c r="O18" s="51" t="n"/>
+      <c r="P18" s="51" t="n"/>
+      <c r="Q18" s="51" t="n"/>
+      <c r="R18" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R18" s="55" t="n"/>
-      <c r="S18" s="55" t="n"/>
-      <c r="T18" s="55" t="n"/>
-      <c r="U18" s="55" t="n"/>
-      <c r="V18" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W18" s="57" t="n"/>
+      <c r="S18" s="51" t="n"/>
+      <c r="T18" s="51" t="n"/>
+      <c r="U18" s="51" t="n"/>
+      <c r="V18" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W18" s="58" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B19" s="45" t="n"/>
-      <c r="C19" s="46" t="n"/>
-      <c r="D19" s="46" t="n"/>
+      <c r="C19" s="53" t="n"/>
+      <c r="D19" s="53" t="n"/>
       <c r="E19" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F19" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G19" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G19" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H19" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J19" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K19" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L19" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N19" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O19" s="51" t="n"/>
-      <c r="P19" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M19" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N19" s="55" t="n"/>
+      <c r="O19" s="55" t="n"/>
+      <c r="P19" s="55" t="n"/>
+      <c r="Q19" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q19" s="51" t="n"/>
-      <c r="R19" s="51" t="n"/>
-      <c r="S19" s="51" t="n"/>
-      <c r="T19" s="51" t="n"/>
-      <c r="U19" s="51" t="n"/>
-      <c r="V19" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W19" s="58" t="n"/>
+      <c r="R19" s="55" t="n"/>
+      <c r="S19" s="55" t="n"/>
+      <c r="T19" s="55" t="n"/>
+      <c r="U19" s="55" t="n"/>
+      <c r="V19" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W19" s="57" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B20" s="45" t="n"/>
-      <c r="C20" s="53" t="n"/>
-      <c r="D20" s="53" t="n"/>
+      <c r="C20" s="46" t="n"/>
+      <c r="D20" s="46" t="n"/>
       <c r="E20" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F20" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G20" s="59" t="n">
-        <v>45.1</v>
+      <c r="G20" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H20" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J20" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K20" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L20" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M20" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N20" s="55" t="n"/>
-      <c r="O20" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P20" s="55" t="n"/>
-      <c r="Q20" s="55" t="n"/>
-      <c r="R20" s="55" t="n"/>
-      <c r="S20" s="55" t="n"/>
-      <c r="T20" s="55" t="n"/>
-      <c r="U20" s="55" t="n"/>
-      <c r="V20" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W20" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M20" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N20" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O20" s="51" t="n"/>
+      <c r="P20" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q20" s="51" t="n"/>
+      <c r="R20" s="51" t="n"/>
+      <c r="S20" s="51" t="n"/>
+      <c r="T20" s="51" t="n"/>
+      <c r="U20" s="51" t="n"/>
+      <c r="V20" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W20" s="58" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="46" t="n"/>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="53" t="n"/>
       <c r="E21" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F21" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G21" s="54" t="n">
-        <v>26.3</v>
+      <c r="G21" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H21" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J21" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K21" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L21" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M21" s="51" t="n"/>
-      <c r="N21" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M21" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N21" s="55" t="n"/>
+      <c r="O21" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O21" s="51" t="n"/>
-      <c r="P21" s="51" t="n"/>
-      <c r="Q21" s="51" t="n"/>
-      <c r="R21" s="51" t="n"/>
-      <c r="S21" s="51" t="n"/>
-      <c r="T21" s="51" t="n"/>
-      <c r="U21" s="51" t="n"/>
-      <c r="V21" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W21" s="58" t="n"/>
+      <c r="P21" s="55" t="n"/>
+      <c r="Q21" s="55" t="n"/>
+      <c r="R21" s="55" t="n"/>
+      <c r="S21" s="55" t="n"/>
+      <c r="T21" s="55" t="n"/>
+      <c r="U21" s="55" t="n"/>
+      <c r="V21" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W21" s="57" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="53" t="n"/>
+      <c r="C22" s="46" t="n"/>
+      <c r="D22" s="46" t="n"/>
       <c r="E22" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G22" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H22" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K22" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L22" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M22" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M22" s="51" t="n"/>
+      <c r="N22" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N22" s="55" t="n"/>
-      <c r="O22" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P22" s="55" t="n"/>
-      <c r="Q22" s="55" t="n"/>
-      <c r="R22" s="55" t="n"/>
-      <c r="S22" s="55" t="n"/>
-      <c r="T22" s="55" t="n"/>
-      <c r="U22" s="55" t="n"/>
-      <c r="V22" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W22" s="57" t="n"/>
+      <c r="O22" s="51" t="n"/>
+      <c r="P22" s="51" t="n"/>
+      <c r="Q22" s="51" t="n"/>
+      <c r="R22" s="51" t="n"/>
+      <c r="S22" s="51" t="n"/>
+      <c r="T22" s="51" t="n"/>
+      <c r="U22" s="51" t="n"/>
+      <c r="V22" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W22" s="58" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="46" t="n"/>
-      <c r="D23" s="46" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G23" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H23" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L23" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M23" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N23" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O23" s="51" t="n"/>
-      <c r="P23" s="51" t="n"/>
-      <c r="Q23" s="51" t="n"/>
-      <c r="R23" s="51" t="n"/>
-      <c r="S23" s="51" t="n"/>
-      <c r="T23" s="51" t="n"/>
-      <c r="U23" s="51" t="n"/>
-      <c r="V23" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W23" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M23" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N23" s="55" t="n"/>
+      <c r="O23" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P23" s="55" t="n"/>
+      <c r="Q23" s="55" t="n"/>
+      <c r="R23" s="55" t="n"/>
+      <c r="S23" s="55" t="n"/>
+      <c r="T23" s="55" t="n"/>
+      <c r="U23" s="55" t="n"/>
+      <c r="V23" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W23" s="57" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
+      <c r="C24" s="46" t="n"/>
+      <c r="D24" s="46" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G24" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H24" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K24" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L24" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I24" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K24" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L24" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M24" s="55" t="inlineStr">
+      <c r="M24" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N24" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N24" s="55" t="n"/>
-      <c r="O24" s="55" t="n"/>
-      <c r="P24" s="55" t="n"/>
-      <c r="Q24" s="55" t="n"/>
-      <c r="R24" s="55" t="n"/>
-      <c r="S24" s="55" t="n"/>
-      <c r="T24" s="55" t="n"/>
-      <c r="U24" s="55" t="n"/>
-      <c r="V24" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W24" s="57" t="n"/>
+      <c r="O24" s="51" t="n"/>
+      <c r="P24" s="51" t="n"/>
+      <c r="Q24" s="51" t="n"/>
+      <c r="R24" s="51" t="n"/>
+      <c r="S24" s="51" t="n"/>
+      <c r="T24" s="51" t="n"/>
+      <c r="U24" s="51" t="n"/>
+      <c r="V24" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W24" s="58" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="46" t="n"/>
-      <c r="D25" s="46" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G25" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G25" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H25" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L25" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M25" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N25" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O25" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P25" s="51" t="n"/>
-      <c r="Q25" s="51" t="n"/>
-      <c r="R25" s="51" t="n"/>
-      <c r="S25" s="51" t="n"/>
-      <c r="T25" s="51" t="n"/>
-      <c r="U25" s="51" t="n"/>
-      <c r="V25" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W25" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M25" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N25" s="55" t="n"/>
+      <c r="O25" s="55" t="n"/>
+      <c r="P25" s="55" t="n"/>
+      <c r="Q25" s="55" t="n"/>
+      <c r="R25" s="55" t="n"/>
+      <c r="S25" s="55" t="n"/>
+      <c r="T25" s="55" t="n"/>
+      <c r="U25" s="55" t="n"/>
+      <c r="V25" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W25" s="57" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="53" t="n"/>
-      <c r="D26" s="53" t="n"/>
+      <c r="C26" s="46" t="n"/>
+      <c r="D26" s="46" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G26" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G26" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H26" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I26" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L26" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M26" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N26" s="55" t="inlineStr">
+      <c r="M26" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N26" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O26" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O26" s="55" t="n"/>
-      <c r="P26" s="55" t="n"/>
-      <c r="Q26" s="55" t="n"/>
-      <c r="R26" s="55" t="n"/>
-      <c r="S26" s="55" t="n"/>
-      <c r="T26" s="55" t="n"/>
-      <c r="U26" s="55" t="n"/>
-      <c r="V26" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W26" s="57" t="n"/>
+      <c r="P26" s="51" t="n"/>
+      <c r="Q26" s="51" t="n"/>
+      <c r="R26" s="51" t="n"/>
+      <c r="S26" s="51" t="n"/>
+      <c r="T26" s="51" t="n"/>
+      <c r="U26" s="51" t="n"/>
+      <c r="V26" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W26" s="58" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="46" t="n"/>
-      <c r="D27" s="46" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G27" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H27" s="49" t="n">
         <v>2</v>
@@ -3268,208 +3272,218 @@
         <v>2</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K27" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L27" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M27" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M27" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N27" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N27" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O27" s="51" t="n"/>
-      <c r="P27" s="51" t="n"/>
-      <c r="Q27" s="51" t="n"/>
-      <c r="R27" s="51" t="n"/>
-      <c r="S27" s="51" t="n"/>
-      <c r="T27" s="51" t="n"/>
-      <c r="U27" s="51" t="n"/>
-      <c r="V27" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W27" s="58" t="n"/>
+      <c r="O27" s="55" t="n"/>
+      <c r="P27" s="55" t="n"/>
+      <c r="Q27" s="55" t="n"/>
+      <c r="R27" s="55" t="n"/>
+      <c r="S27" s="55" t="n"/>
+      <c r="T27" s="55" t="n"/>
+      <c r="U27" s="55" t="n"/>
+      <c r="V27" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W27" s="57" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="53" t="n"/>
-      <c r="D28" s="53" t="n"/>
+      <c r="C28" s="46" t="n"/>
+      <c r="D28" s="46" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G28" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H28" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I28" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L28" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M28" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M28" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N28" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N28" s="55" t="n"/>
-      <c r="O28" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P28" s="55" t="n"/>
-      <c r="Q28" s="55" t="n"/>
-      <c r="R28" s="55" t="n"/>
-      <c r="S28" s="55" t="n"/>
-      <c r="T28" s="55" t="n"/>
-      <c r="U28" s="55" t="n"/>
-      <c r="V28" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W28" s="57" t="n"/>
+      <c r="O28" s="51" t="n"/>
+      <c r="P28" s="51" t="n"/>
+      <c r="Q28" s="51" t="n"/>
+      <c r="R28" s="51" t="n"/>
+      <c r="S28" s="51" t="n"/>
+      <c r="T28" s="51" t="n"/>
+      <c r="U28" s="51" t="n"/>
+      <c r="V28" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W28" s="58" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="46" t="n"/>
-      <c r="D29" s="46" t="n"/>
+      <c r="C29" s="53" t="n"/>
+      <c r="D29" s="53" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G29" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G29" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H29" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L29" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M29" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N29" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O29" s="51" t="n"/>
-      <c r="P29" s="51" t="n"/>
-      <c r="Q29" s="51" t="n"/>
-      <c r="R29" s="51" t="n"/>
-      <c r="S29" s="51" t="n"/>
-      <c r="T29" s="51" t="n"/>
-      <c r="U29" s="51" t="n"/>
-      <c r="V29" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W29" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M29" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N29" s="55" t="n"/>
+      <c r="O29" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P29" s="55" t="n"/>
+      <c r="Q29" s="55" t="n"/>
+      <c r="R29" s="55" t="n"/>
+      <c r="S29" s="55" t="n"/>
+      <c r="T29" s="55" t="n"/>
+      <c r="U29" s="55" t="n"/>
+      <c r="V29" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W29" s="57" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="53" t="n"/>
-      <c r="D30" s="53" t="n"/>
+      <c r="C30" s="46" t="n"/>
+      <c r="D30" s="46" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G30" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G30" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H30" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I30" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L30" s="50" t="n"/>
-      <c r="M30" s="55" t="n"/>
-      <c r="N30" s="55" t="n"/>
-      <c r="O30" s="55" t="n"/>
-      <c r="P30" s="55" t="n"/>
-      <c r="Q30" s="55" t="n"/>
-      <c r="R30" s="55" t="n"/>
-      <c r="S30" s="55" t="n"/>
-      <c r="T30" s="55" t="n"/>
-      <c r="U30" s="55" t="n"/>
-      <c r="V30" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W30" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L30" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M30" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N30" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O30" s="51" t="n"/>
+      <c r="P30" s="51" t="n"/>
+      <c r="Q30" s="51" t="n"/>
+      <c r="R30" s="51" t="n"/>
+      <c r="S30" s="51" t="n"/>
+      <c r="T30" s="51" t="n"/>
+      <c r="U30" s="51" t="n"/>
+      <c r="V30" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W30" s="58" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="46" t="n"/>
-      <c r="D31" s="46" t="n"/>
+      <c r="C31" s="53" t="n"/>
+      <c r="D31" s="53" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G31" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H31" s="49" t="n">
         <v>0</v>
@@ -3478,43 +3492,43 @@
         <v>0</v>
       </c>
       <c r="J31" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L31" s="50" t="n"/>
-      <c r="M31" s="51" t="n"/>
-      <c r="N31" s="51" t="n"/>
-      <c r="O31" s="51" t="n"/>
-      <c r="P31" s="51" t="n"/>
-      <c r="Q31" s="51" t="n"/>
-      <c r="R31" s="51" t="n"/>
-      <c r="S31" s="51" t="n"/>
-      <c r="T31" s="51" t="n"/>
-      <c r="U31" s="51" t="n"/>
-      <c r="V31" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W31" s="58" t="n"/>
+      <c r="M31" s="55" t="n"/>
+      <c r="N31" s="55" t="n"/>
+      <c r="O31" s="55" t="n"/>
+      <c r="P31" s="55" t="n"/>
+      <c r="Q31" s="55" t="n"/>
+      <c r="R31" s="55" t="n"/>
+      <c r="S31" s="55" t="n"/>
+      <c r="T31" s="55" t="n"/>
+      <c r="U31" s="55" t="n"/>
+      <c r="V31" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W31" s="57" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="53" t="n"/>
-      <c r="D32" s="53" t="n"/>
+      <c r="C32" s="46" t="n"/>
+      <c r="D32" s="46" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G32" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H32" s="49" t="n">
         <v>0</v>
@@ -3523,43 +3537,43 @@
         <v>0</v>
       </c>
       <c r="J32" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L32" s="50" t="n"/>
-      <c r="M32" s="55" t="n"/>
-      <c r="N32" s="55" t="n"/>
-      <c r="O32" s="55" t="n"/>
-      <c r="P32" s="55" t="n"/>
-      <c r="Q32" s="55" t="n"/>
-      <c r="R32" s="55" t="n"/>
-      <c r="S32" s="55" t="n"/>
-      <c r="T32" s="55" t="n"/>
-      <c r="U32" s="55" t="n"/>
-      <c r="V32" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W32" s="57" t="n"/>
+      <c r="M32" s="51" t="n"/>
+      <c r="N32" s="51" t="n"/>
+      <c r="O32" s="51" t="n"/>
+      <c r="P32" s="51" t="n"/>
+      <c r="Q32" s="51" t="n"/>
+      <c r="R32" s="51" t="n"/>
+      <c r="S32" s="51" t="n"/>
+      <c r="T32" s="51" t="n"/>
+      <c r="U32" s="51" t="n"/>
+      <c r="V32" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W32" s="58" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="46" t="n"/>
-      <c r="D33" s="46" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G33" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G33" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H33" s="49" t="n">
         <v>0</v>
@@ -3568,43 +3582,43 @@
         <v>0</v>
       </c>
       <c r="J33" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L33" s="50" t="n"/>
-      <c r="M33" s="51" t="n"/>
-      <c r="N33" s="51" t="n"/>
-      <c r="O33" s="51" t="n"/>
-      <c r="P33" s="51" t="n"/>
-      <c r="Q33" s="51" t="n"/>
-      <c r="R33" s="51" t="n"/>
-      <c r="S33" s="51" t="n"/>
-      <c r="T33" s="51" t="n"/>
-      <c r="U33" s="51" t="n"/>
-      <c r="V33" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W33" s="58" t="n"/>
+      <c r="M33" s="55" t="n"/>
+      <c r="N33" s="55" t="n"/>
+      <c r="O33" s="55" t="n"/>
+      <c r="P33" s="55" t="n"/>
+      <c r="Q33" s="55" t="n"/>
+      <c r="R33" s="55" t="n"/>
+      <c r="S33" s="55" t="n"/>
+      <c r="T33" s="55" t="n"/>
+      <c r="U33" s="55" t="n"/>
+      <c r="V33" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W33" s="57" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="53" t="n"/>
-      <c r="D34" s="53" t="n"/>
+      <c r="C34" s="46" t="n"/>
+      <c r="D34" s="46" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G34" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H34" s="49" t="n">
         <v>0</v>
@@ -3613,43 +3627,43 @@
         <v>0</v>
       </c>
       <c r="J34" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L34" s="50" t="n"/>
-      <c r="M34" s="55" t="n"/>
-      <c r="N34" s="55" t="n"/>
-      <c r="O34" s="55" t="n"/>
-      <c r="P34" s="55" t="n"/>
-      <c r="Q34" s="55" t="n"/>
-      <c r="R34" s="55" t="n"/>
-      <c r="S34" s="55" t="n"/>
-      <c r="T34" s="55" t="n"/>
-      <c r="U34" s="55" t="n"/>
-      <c r="V34" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W34" s="57" t="n"/>
+      <c r="M34" s="51" t="n"/>
+      <c r="N34" s="51" t="n"/>
+      <c r="O34" s="51" t="n"/>
+      <c r="P34" s="51" t="n"/>
+      <c r="Q34" s="51" t="n"/>
+      <c r="R34" s="51" t="n"/>
+      <c r="S34" s="51" t="n"/>
+      <c r="T34" s="51" t="n"/>
+      <c r="U34" s="51" t="n"/>
+      <c r="V34" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W34" s="58" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="46" t="n"/>
-      <c r="D35" s="46" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G35" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H35" s="49" t="n">
         <v>0</v>
@@ -3658,1371 +3672,1375 @@
         <v>0</v>
       </c>
       <c r="J35" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L35" s="50" t="n"/>
-      <c r="M35" s="51" t="n"/>
-      <c r="N35" s="51" t="n"/>
-      <c r="O35" s="51" t="n"/>
-      <c r="P35" s="51" t="n"/>
-      <c r="Q35" s="51" t="n"/>
-      <c r="R35" s="51" t="n"/>
-      <c r="S35" s="51" t="n"/>
-      <c r="T35" s="51" t="n"/>
-      <c r="U35" s="51" t="n"/>
-      <c r="V35" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W35" s="58" t="n"/>
+      <c r="M35" s="55" t="n"/>
+      <c r="N35" s="55" t="n"/>
+      <c r="O35" s="55" t="n"/>
+      <c r="P35" s="55" t="n"/>
+      <c r="Q35" s="55" t="n"/>
+      <c r="R35" s="55" t="n"/>
+      <c r="S35" s="55" t="n"/>
+      <c r="T35" s="55" t="n"/>
+      <c r="U35" s="55" t="n"/>
+      <c r="V35" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W35" s="57" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
+      <c r="C36" s="46" t="n"/>
+      <c r="D36" s="46" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G36" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H36" s="49" t="n"/>
-      <c r="I36" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G36" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H36" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J36" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="55" t="n"/>
-      <c r="N36" s="55" t="n"/>
-      <c r="O36" s="55" t="n"/>
-      <c r="P36" s="55" t="n"/>
-      <c r="Q36" s="55" t="n"/>
-      <c r="R36" s="55" t="n"/>
-      <c r="S36" s="55" t="n"/>
-      <c r="T36" s="55" t="n"/>
-      <c r="U36" s="55" t="n"/>
-      <c r="V36" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W36" s="57" t="n"/>
+      <c r="M36" s="51" t="n"/>
+      <c r="N36" s="51" t="n"/>
+      <c r="O36" s="51" t="n"/>
+      <c r="P36" s="51" t="n"/>
+      <c r="Q36" s="51" t="n"/>
+      <c r="R36" s="51" t="n"/>
+      <c r="S36" s="51" t="n"/>
+      <c r="T36" s="51" t="n"/>
+      <c r="U36" s="51" t="n"/>
+      <c r="V36" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W36" s="58" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="46" t="n"/>
-      <c r="D37" s="46" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G37" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H37" s="49" t="n"/>
       <c r="I37" s="49" t="n"/>
       <c r="J37" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="51" t="n"/>
-      <c r="N37" s="51" t="n"/>
-      <c r="O37" s="51" t="n"/>
-      <c r="P37" s="51" t="n"/>
-      <c r="Q37" s="51" t="n"/>
-      <c r="R37" s="51" t="n"/>
-      <c r="S37" s="51" t="n"/>
-      <c r="T37" s="51" t="n"/>
-      <c r="U37" s="51" t="n"/>
-      <c r="V37" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W37" s="58" t="n"/>
+      <c r="M37" s="55" t="n"/>
+      <c r="N37" s="55" t="n"/>
+      <c r="O37" s="55" t="n"/>
+      <c r="P37" s="55" t="n"/>
+      <c r="Q37" s="55" t="n"/>
+      <c r="R37" s="55" t="n"/>
+      <c r="S37" s="55" t="n"/>
+      <c r="T37" s="55" t="n"/>
+      <c r="U37" s="55" t="n"/>
+      <c r="V37" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W37" s="57" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="53" t="n"/>
-      <c r="D38" s="53" t="n"/>
+      <c r="C38" s="46" t="n"/>
+      <c r="D38" s="46" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G38" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H38" s="49" t="n"/>
       <c r="I38" s="49" t="n"/>
       <c r="J38" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="55" t="n"/>
-      <c r="N38" s="55" t="n"/>
-      <c r="O38" s="55" t="n"/>
-      <c r="P38" s="55" t="n"/>
-      <c r="Q38" s="55" t="n"/>
-      <c r="R38" s="55" t="n"/>
-      <c r="S38" s="55" t="n"/>
-      <c r="T38" s="55" t="n"/>
-      <c r="U38" s="55" t="n"/>
-      <c r="V38" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W38" s="57" t="n"/>
+      <c r="M38" s="51" t="n"/>
+      <c r="N38" s="51" t="n"/>
+      <c r="O38" s="51" t="n"/>
+      <c r="P38" s="51" t="n"/>
+      <c r="Q38" s="51" t="n"/>
+      <c r="R38" s="51" t="n"/>
+      <c r="S38" s="51" t="n"/>
+      <c r="T38" s="51" t="n"/>
+      <c r="U38" s="51" t="n"/>
+      <c r="V38" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W38" s="58" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="46" t="n"/>
-      <c r="D39" s="46" t="n"/>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G39" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H39" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I39" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H39" s="49" t="n"/>
+      <c r="I39" s="49" t="n"/>
       <c r="J39" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="51" t="n"/>
-      <c r="N39" s="51" t="n"/>
-      <c r="O39" s="51" t="n"/>
-      <c r="P39" s="51" t="n"/>
-      <c r="Q39" s="51" t="n"/>
-      <c r="R39" s="51" t="n"/>
-      <c r="S39" s="51" t="n"/>
-      <c r="T39" s="51" t="n"/>
-      <c r="U39" s="51" t="n"/>
-      <c r="V39" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W39" s="58" t="n"/>
+      <c r="M39" s="55" t="n"/>
+      <c r="N39" s="55" t="n"/>
+      <c r="O39" s="55" t="n"/>
+      <c r="P39" s="55" t="n"/>
+      <c r="Q39" s="55" t="n"/>
+      <c r="R39" s="55" t="n"/>
+      <c r="S39" s="55" t="n"/>
+      <c r="T39" s="55" t="n"/>
+      <c r="U39" s="55" t="n"/>
+      <c r="V39" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W39" s="57" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="53" t="n"/>
-      <c r="D40" s="53" t="n"/>
+      <c r="C40" s="46" t="n"/>
+      <c r="D40" s="46" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G40" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H40" s="49" t="n"/>
-      <c r="I40" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G40" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H40" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I40" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J40" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="55" t="n"/>
-      <c r="N40" s="55" t="n"/>
-      <c r="O40" s="55" t="n"/>
-      <c r="P40" s="55" t="n"/>
-      <c r="Q40" s="55" t="n"/>
-      <c r="R40" s="55" t="n"/>
-      <c r="S40" s="55" t="n"/>
-      <c r="T40" s="55" t="n"/>
-      <c r="U40" s="55" t="n"/>
-      <c r="V40" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W40" s="57" t="n"/>
+      <c r="M40" s="51" t="n"/>
+      <c r="N40" s="51" t="n"/>
+      <c r="O40" s="51" t="n"/>
+      <c r="P40" s="51" t="n"/>
+      <c r="Q40" s="51" t="n"/>
+      <c r="R40" s="51" t="n"/>
+      <c r="S40" s="51" t="n"/>
+      <c r="T40" s="51" t="n"/>
+      <c r="U40" s="51" t="n"/>
+      <c r="V40" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W40" s="58" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="46" t="n"/>
-      <c r="D41" s="46" t="n"/>
+      <c r="C41" s="53" t="n"/>
+      <c r="D41" s="53" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G41" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G41" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H41" s="49" t="n"/>
       <c r="I41" s="49" t="n"/>
       <c r="J41" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="51" t="n"/>
-      <c r="N41" s="51" t="n"/>
-      <c r="O41" s="51" t="n"/>
-      <c r="P41" s="51" t="n"/>
-      <c r="Q41" s="51" t="n"/>
-      <c r="R41" s="51" t="n"/>
-      <c r="S41" s="51" t="n"/>
-      <c r="T41" s="51" t="n"/>
-      <c r="U41" s="51" t="n"/>
-      <c r="V41" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W41" s="58" t="n"/>
+      <c r="M41" s="55" t="n"/>
+      <c r="N41" s="55" t="n"/>
+      <c r="O41" s="55" t="n"/>
+      <c r="P41" s="55" t="n"/>
+      <c r="Q41" s="55" t="n"/>
+      <c r="R41" s="55" t="n"/>
+      <c r="S41" s="55" t="n"/>
+      <c r="T41" s="55" t="n"/>
+      <c r="U41" s="55" t="n"/>
+      <c r="V41" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W41" s="57" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="53" t="n"/>
-      <c r="D42" s="53" t="n"/>
+      <c r="C42" s="46" t="n"/>
+      <c r="D42" s="46" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G42" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G42" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H42" s="49" t="n"/>
       <c r="I42" s="49" t="n"/>
       <c r="J42" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K42" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K42" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="55" t="n"/>
-      <c r="N42" s="55" t="n"/>
-      <c r="O42" s="55" t="n"/>
-      <c r="P42" s="55" t="n"/>
-      <c r="Q42" s="55" t="n"/>
-      <c r="R42" s="55" t="n"/>
-      <c r="S42" s="55" t="n"/>
-      <c r="T42" s="55" t="n"/>
-      <c r="U42" s="55" t="n"/>
-      <c r="V42" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W42" s="57" t="n"/>
+      <c r="M42" s="51" t="n"/>
+      <c r="N42" s="51" t="n"/>
+      <c r="O42" s="51" t="n"/>
+      <c r="P42" s="51" t="n"/>
+      <c r="Q42" s="51" t="n"/>
+      <c r="R42" s="51" t="n"/>
+      <c r="S42" s="51" t="n"/>
+      <c r="T42" s="51" t="n"/>
+      <c r="U42" s="51" t="n"/>
+      <c r="V42" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W42" s="58" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="46" t="n"/>
-      <c r="D43" s="46" t="n"/>
+      <c r="C43" s="53" t="n"/>
+      <c r="D43" s="53" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G43" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H43" s="49" t="n"/>
       <c r="I43" s="49" t="n"/>
       <c r="J43" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K43" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="51" t="n"/>
-      <c r="N43" s="51" t="n"/>
-      <c r="O43" s="51" t="n"/>
-      <c r="P43" s="51" t="n"/>
-      <c r="Q43" s="51" t="n"/>
-      <c r="R43" s="51" t="n"/>
-      <c r="S43" s="51" t="n"/>
-      <c r="T43" s="51" t="n"/>
-      <c r="U43" s="51" t="n"/>
-      <c r="V43" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W43" s="58" t="n"/>
+      <c r="M43" s="55" t="n"/>
+      <c r="N43" s="55" t="n"/>
+      <c r="O43" s="55" t="n"/>
+      <c r="P43" s="55" t="n"/>
+      <c r="Q43" s="55" t="n"/>
+      <c r="R43" s="55" t="n"/>
+      <c r="S43" s="55" t="n"/>
+      <c r="T43" s="55" t="n"/>
+      <c r="U43" s="55" t="n"/>
+      <c r="V43" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W43" s="57" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="53" t="n"/>
-      <c r="D44" s="53" t="n"/>
+      <c r="C44" s="46" t="n"/>
+      <c r="D44" s="46" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G44" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G44" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H44" s="49" t="n"/>
       <c r="I44" s="49" t="n"/>
       <c r="J44" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K44" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="55" t="n"/>
-      <c r="N44" s="55" t="n"/>
-      <c r="O44" s="55" t="n"/>
-      <c r="P44" s="55" t="n"/>
-      <c r="Q44" s="55" t="n"/>
-      <c r="R44" s="55" t="n"/>
-      <c r="S44" s="55" t="n"/>
-      <c r="T44" s="55" t="n"/>
-      <c r="U44" s="55" t="n"/>
-      <c r="V44" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W44" s="57" t="n"/>
+      <c r="M44" s="51" t="n"/>
+      <c r="N44" s="51" t="n"/>
+      <c r="O44" s="51" t="n"/>
+      <c r="P44" s="51" t="n"/>
+      <c r="Q44" s="51" t="n"/>
+      <c r="R44" s="51" t="n"/>
+      <c r="S44" s="51" t="n"/>
+      <c r="T44" s="51" t="n"/>
+      <c r="U44" s="51" t="n"/>
+      <c r="V44" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W44" s="58" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="46" t="n"/>
-      <c r="D45" s="46" t="n"/>
+      <c r="C45" s="53" t="n"/>
+      <c r="D45" s="53" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G45" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H45" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I45" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G45" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H45" s="49" t="n"/>
+      <c r="I45" s="49" t="n"/>
       <c r="J45" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K45" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="51" t="n"/>
-      <c r="N45" s="51" t="n"/>
-      <c r="O45" s="51" t="n"/>
-      <c r="P45" s="51" t="n"/>
-      <c r="Q45" s="51" t="n"/>
-      <c r="R45" s="51" t="n"/>
-      <c r="S45" s="51" t="n"/>
-      <c r="T45" s="51" t="n"/>
-      <c r="U45" s="51" t="n"/>
-      <c r="V45" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W45" s="58" t="n"/>
+      <c r="M45" s="55" t="n"/>
+      <c r="N45" s="55" t="n"/>
+      <c r="O45" s="55" t="n"/>
+      <c r="P45" s="55" t="n"/>
+      <c r="Q45" s="55" t="n"/>
+      <c r="R45" s="55" t="n"/>
+      <c r="S45" s="55" t="n"/>
+      <c r="T45" s="55" t="n"/>
+      <c r="U45" s="55" t="n"/>
+      <c r="V45" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W45" s="57" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="53" t="n"/>
-      <c r="D46" s="53" t="n"/>
+      <c r="C46" s="46" t="n"/>
+      <c r="D46" s="46" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G46" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H46" s="49" t="n"/>
-      <c r="I46" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H46" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I46" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J46" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K46" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="55" t="n"/>
-      <c r="N46" s="55" t="n"/>
-      <c r="O46" s="55" t="n"/>
-      <c r="P46" s="55" t="n"/>
-      <c r="Q46" s="55" t="n"/>
-      <c r="R46" s="55" t="n"/>
-      <c r="S46" s="55" t="n"/>
-      <c r="T46" s="55" t="n"/>
-      <c r="U46" s="55" t="n"/>
-      <c r="V46" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W46" s="57" t="n"/>
+      <c r="M46" s="51" t="n"/>
+      <c r="N46" s="51" t="n"/>
+      <c r="O46" s="51" t="n"/>
+      <c r="P46" s="51" t="n"/>
+      <c r="Q46" s="51" t="n"/>
+      <c r="R46" s="51" t="n"/>
+      <c r="S46" s="51" t="n"/>
+      <c r="T46" s="51" t="n"/>
+      <c r="U46" s="51" t="n"/>
+      <c r="V46" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W46" s="58" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="46" t="n"/>
-      <c r="D47" s="46" t="n"/>
+      <c r="C47" s="53" t="n"/>
+      <c r="D47" s="53" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G47" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H47" s="49" t="n"/>
       <c r="I47" s="49" t="n"/>
       <c r="J47" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K47" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="51" t="n"/>
-      <c r="N47" s="51" t="n"/>
-      <c r="O47" s="51" t="n"/>
-      <c r="P47" s="51" t="n"/>
-      <c r="Q47" s="51" t="n"/>
-      <c r="R47" s="51" t="n"/>
-      <c r="S47" s="51" t="n"/>
-      <c r="T47" s="51" t="n"/>
-      <c r="U47" s="51" t="n"/>
-      <c r="V47" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W47" s="58" t="n"/>
+      <c r="M47" s="55" t="n"/>
+      <c r="N47" s="55" t="n"/>
+      <c r="O47" s="55" t="n"/>
+      <c r="P47" s="55" t="n"/>
+      <c r="Q47" s="55" t="n"/>
+      <c r="R47" s="55" t="n"/>
+      <c r="S47" s="55" t="n"/>
+      <c r="T47" s="55" t="n"/>
+      <c r="U47" s="55" t="n"/>
+      <c r="V47" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W47" s="57" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
+      <c r="C48" s="46" t="n"/>
+      <c r="D48" s="46" t="n"/>
       <c r="E48" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F48" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G48" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H48" s="49" t="n"/>
+      <c r="I48" s="49" t="n"/>
+      <c r="J48" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F48" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G48" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H48" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I48" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J48" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K48" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="55" t="n"/>
-      <c r="N48" s="55" t="n"/>
-      <c r="O48" s="55" t="n"/>
-      <c r="P48" s="55" t="n"/>
-      <c r="Q48" s="55" t="n"/>
-      <c r="R48" s="55" t="n"/>
-      <c r="S48" s="55" t="n"/>
-      <c r="T48" s="55" t="n"/>
-      <c r="U48" s="55" t="n"/>
-      <c r="V48" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W48" s="57" t="n"/>
+      <c r="M48" s="51" t="n"/>
+      <c r="N48" s="51" t="n"/>
+      <c r="O48" s="51" t="n"/>
+      <c r="P48" s="51" t="n"/>
+      <c r="Q48" s="51" t="n"/>
+      <c r="R48" s="51" t="n"/>
+      <c r="S48" s="51" t="n"/>
+      <c r="T48" s="51" t="n"/>
+      <c r="U48" s="51" t="n"/>
+      <c r="V48" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W48" s="58" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="46" t="n"/>
-      <c r="D49" s="46" t="n"/>
+      <c r="C49" s="53" t="n"/>
+      <c r="D49" s="53" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G49" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H49" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I49" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J49" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K49" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="51" t="n"/>
-      <c r="N49" s="51" t="n"/>
-      <c r="O49" s="51" t="n"/>
-      <c r="P49" s="51" t="n"/>
-      <c r="Q49" s="51" t="n"/>
-      <c r="R49" s="51" t="n"/>
-      <c r="S49" s="51" t="n"/>
-      <c r="T49" s="51" t="n"/>
-      <c r="U49" s="51" t="n"/>
-      <c r="V49" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W49" s="58" t="n"/>
+      <c r="M49" s="55" t="n"/>
+      <c r="N49" s="55" t="n"/>
+      <c r="O49" s="55" t="n"/>
+      <c r="P49" s="55" t="n"/>
+      <c r="Q49" s="55" t="n"/>
+      <c r="R49" s="55" t="n"/>
+      <c r="S49" s="55" t="n"/>
+      <c r="T49" s="55" t="n"/>
+      <c r="U49" s="55" t="n"/>
+      <c r="V49" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W49" s="57" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="53" t="n"/>
-      <c r="D50" s="53" t="n"/>
+      <c r="C50" s="46" t="n"/>
+      <c r="D50" s="46" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G50" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H50" s="49" t="n"/>
-      <c r="I50" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H50" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I50" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J50" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="55" t="n"/>
-      <c r="N50" s="55" t="n"/>
-      <c r="O50" s="55" t="n"/>
-      <c r="P50" s="55" t="n"/>
-      <c r="Q50" s="55" t="n"/>
-      <c r="R50" s="55" t="n"/>
-      <c r="S50" s="55" t="n"/>
-      <c r="T50" s="55" t="n"/>
-      <c r="U50" s="55" t="n"/>
-      <c r="V50" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W50" s="57" t="n"/>
+      <c r="M50" s="51" t="n"/>
+      <c r="N50" s="51" t="n"/>
+      <c r="O50" s="51" t="n"/>
+      <c r="P50" s="51" t="n"/>
+      <c r="Q50" s="51" t="n"/>
+      <c r="R50" s="51" t="n"/>
+      <c r="S50" s="51" t="n"/>
+      <c r="T50" s="51" t="n"/>
+      <c r="U50" s="51" t="n"/>
+      <c r="V50" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W50" s="58" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="46" t="n"/>
-      <c r="D51" s="46" t="n"/>
+      <c r="C51" s="53" t="n"/>
+      <c r="D51" s="53" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G51" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G51" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H51" s="49" t="n"/>
       <c r="I51" s="49" t="n"/>
       <c r="J51" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K51" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="51" t="n"/>
-      <c r="N51" s="51" t="n"/>
-      <c r="O51" s="51" t="n"/>
-      <c r="P51" s="51" t="n"/>
-      <c r="Q51" s="51" t="n"/>
-      <c r="R51" s="51" t="n"/>
-      <c r="S51" s="51" t="n"/>
-      <c r="T51" s="51" t="n"/>
-      <c r="U51" s="51" t="n"/>
-      <c r="V51" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W51" s="58" t="n"/>
+      <c r="M51" s="55" t="n"/>
+      <c r="N51" s="55" t="n"/>
+      <c r="O51" s="55" t="n"/>
+      <c r="P51" s="55" t="n"/>
+      <c r="Q51" s="55" t="n"/>
+      <c r="R51" s="55" t="n"/>
+      <c r="S51" s="55" t="n"/>
+      <c r="T51" s="55" t="n"/>
+      <c r="U51" s="55" t="n"/>
+      <c r="V51" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W51" s="57" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="53" t="n"/>
-      <c r="D52" s="53" t="n"/>
+      <c r="C52" s="46" t="n"/>
+      <c r="D52" s="46" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G52" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G52" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H52" s="49" t="n"/>
       <c r="I52" s="49" t="n"/>
       <c r="J52" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="55" t="n"/>
-      <c r="N52" s="55" t="n"/>
-      <c r="O52" s="55" t="n"/>
-      <c r="P52" s="55" t="n"/>
-      <c r="Q52" s="55" t="n"/>
-      <c r="R52" s="55" t="n"/>
-      <c r="S52" s="55" t="n"/>
-      <c r="T52" s="55" t="n"/>
-      <c r="U52" s="55" t="n"/>
-      <c r="V52" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W52" s="57" t="n"/>
+      <c r="M52" s="51" t="n"/>
+      <c r="N52" s="51" t="n"/>
+      <c r="O52" s="51" t="n"/>
+      <c r="P52" s="51" t="n"/>
+      <c r="Q52" s="51" t="n"/>
+      <c r="R52" s="51" t="n"/>
+      <c r="S52" s="51" t="n"/>
+      <c r="T52" s="51" t="n"/>
+      <c r="U52" s="51" t="n"/>
+      <c r="V52" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W52" s="58" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="46" t="n"/>
-      <c r="D53" s="46" t="n"/>
+      <c r="C53" s="53" t="n"/>
+      <c r="D53" s="53" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G53" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H53" s="49" t="n"/>
       <c r="I53" s="49" t="n"/>
       <c r="J53" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="51" t="n"/>
-      <c r="N53" s="51" t="n"/>
-      <c r="O53" s="51" t="n"/>
-      <c r="P53" s="51" t="n"/>
-      <c r="Q53" s="51" t="n"/>
-      <c r="R53" s="51" t="n"/>
-      <c r="S53" s="51" t="n"/>
-      <c r="T53" s="51" t="n"/>
-      <c r="U53" s="51" t="n"/>
-      <c r="V53" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W53" s="58" t="n"/>
+      <c r="M53" s="55" t="n"/>
+      <c r="N53" s="55" t="n"/>
+      <c r="O53" s="55" t="n"/>
+      <c r="P53" s="55" t="n"/>
+      <c r="Q53" s="55" t="n"/>
+      <c r="R53" s="55" t="n"/>
+      <c r="S53" s="55" t="n"/>
+      <c r="T53" s="55" t="n"/>
+      <c r="U53" s="55" t="n"/>
+      <c r="V53" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W53" s="57" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="53" t="n"/>
-      <c r="D54" s="53" t="n"/>
+      <c r="C54" s="46" t="n"/>
+      <c r="D54" s="46" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G54" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G54" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="55" t="n"/>
-      <c r="N54" s="55" t="n"/>
-      <c r="O54" s="55" t="n"/>
-      <c r="P54" s="55" t="n"/>
-      <c r="Q54" s="55" t="n"/>
-      <c r="R54" s="55" t="n"/>
-      <c r="S54" s="55" t="n"/>
-      <c r="T54" s="55" t="n"/>
-      <c r="U54" s="55" t="n"/>
-      <c r="V54" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W54" s="57" t="n"/>
+      <c r="M54" s="51" t="n"/>
+      <c r="N54" s="51" t="n"/>
+      <c r="O54" s="51" t="n"/>
+      <c r="P54" s="51" t="n"/>
+      <c r="Q54" s="51" t="n"/>
+      <c r="R54" s="51" t="n"/>
+      <c r="S54" s="51" t="n"/>
+      <c r="T54" s="51" t="n"/>
+      <c r="U54" s="51" t="n"/>
+      <c r="V54" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W54" s="58" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="46" t="n"/>
-      <c r="D55" s="46" t="n"/>
+      <c r="C55" s="53" t="n"/>
+      <c r="D55" s="53" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G55" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G55" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="51" t="n"/>
-      <c r="N55" s="51" t="n"/>
-      <c r="O55" s="51" t="n"/>
-      <c r="P55" s="51" t="n"/>
-      <c r="Q55" s="51" t="n"/>
-      <c r="R55" s="51" t="n"/>
-      <c r="S55" s="51" t="n"/>
-      <c r="T55" s="51" t="n"/>
-      <c r="U55" s="51" t="n"/>
-      <c r="V55" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W55" s="58" t="n"/>
+      <c r="M55" s="55" t="n"/>
+      <c r="N55" s="55" t="n"/>
+      <c r="O55" s="55" t="n"/>
+      <c r="P55" s="55" t="n"/>
+      <c r="Q55" s="55" t="n"/>
+      <c r="R55" s="55" t="n"/>
+      <c r="S55" s="55" t="n"/>
+      <c r="T55" s="55" t="n"/>
+      <c r="U55" s="55" t="n"/>
+      <c r="V55" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W55" s="57" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="53" t="n"/>
-      <c r="D56" s="53" t="n"/>
+      <c r="C56" s="46" t="n"/>
+      <c r="D56" s="46" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G56" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G56" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="55" t="n"/>
-      <c r="N56" s="55" t="n"/>
-      <c r="O56" s="55" t="n"/>
-      <c r="P56" s="55" t="n"/>
-      <c r="Q56" s="55" t="n"/>
-      <c r="R56" s="55" t="n"/>
-      <c r="S56" s="55" t="n"/>
-      <c r="T56" s="55" t="n"/>
-      <c r="U56" s="55" t="n"/>
-      <c r="V56" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W56" s="57" t="n"/>
+      <c r="M56" s="51" t="n"/>
+      <c r="N56" s="51" t="n"/>
+      <c r="O56" s="51" t="n"/>
+      <c r="P56" s="51" t="n"/>
+      <c r="Q56" s="51" t="n"/>
+      <c r="R56" s="51" t="n"/>
+      <c r="S56" s="51" t="n"/>
+      <c r="T56" s="51" t="n"/>
+      <c r="U56" s="51" t="n"/>
+      <c r="V56" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W56" s="58" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="46" t="n"/>
-      <c r="D57" s="46" t="n"/>
+      <c r="C57" s="53" t="n"/>
+      <c r="D57" s="53" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G57" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="51" t="n"/>
-      <c r="N57" s="51" t="n"/>
-      <c r="O57" s="51" t="n"/>
-      <c r="P57" s="51" t="n"/>
-      <c r="Q57" s="51" t="n"/>
-      <c r="R57" s="51" t="n"/>
-      <c r="S57" s="51" t="n"/>
-      <c r="T57" s="51" t="n"/>
-      <c r="U57" s="51" t="n"/>
-      <c r="V57" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W57" s="58" t="n"/>
+      <c r="M57" s="55" t="n"/>
+      <c r="N57" s="55" t="n"/>
+      <c r="O57" s="55" t="n"/>
+      <c r="P57" s="55" t="n"/>
+      <c r="Q57" s="55" t="n"/>
+      <c r="R57" s="55" t="n"/>
+      <c r="S57" s="55" t="n"/>
+      <c r="T57" s="55" t="n"/>
+      <c r="U57" s="55" t="n"/>
+      <c r="V57" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W57" s="57" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="53" t="n"/>
-      <c r="D58" s="53" t="n"/>
+      <c r="C58" s="46" t="n"/>
+      <c r="D58" s="46" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G58" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="55" t="n"/>
-      <c r="N58" s="55" t="n"/>
-      <c r="O58" s="55" t="n"/>
-      <c r="P58" s="55" t="n"/>
-      <c r="Q58" s="55" t="n"/>
-      <c r="R58" s="55" t="n"/>
-      <c r="S58" s="55" t="n"/>
-      <c r="T58" s="55" t="n"/>
-      <c r="U58" s="55" t="n"/>
-      <c r="V58" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W58" s="57" t="n"/>
+      <c r="M58" s="51" t="n"/>
+      <c r="N58" s="51" t="n"/>
+      <c r="O58" s="51" t="n"/>
+      <c r="P58" s="51" t="n"/>
+      <c r="Q58" s="51" t="n"/>
+      <c r="R58" s="51" t="n"/>
+      <c r="S58" s="51" t="n"/>
+      <c r="T58" s="51" t="n"/>
+      <c r="U58" s="51" t="n"/>
+      <c r="V58" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W58" s="58" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="46" t="n"/>
-      <c r="D59" s="46" t="n"/>
+      <c r="C59" s="53" t="n"/>
+      <c r="D59" s="53" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G59" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G59" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="51" t="n"/>
-      <c r="N59" s="51" t="n"/>
-      <c r="O59" s="51" t="n"/>
-      <c r="P59" s="51" t="n"/>
-      <c r="Q59" s="51" t="n"/>
-      <c r="R59" s="51" t="n"/>
-      <c r="S59" s="51" t="n"/>
-      <c r="T59" s="51" t="n"/>
-      <c r="U59" s="51" t="n"/>
-      <c r="V59" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W59" s="58" t="n"/>
+      <c r="M59" s="55" t="n"/>
+      <c r="N59" s="55" t="n"/>
+      <c r="O59" s="55" t="n"/>
+      <c r="P59" s="55" t="n"/>
+      <c r="Q59" s="55" t="n"/>
+      <c r="R59" s="55" t="n"/>
+      <c r="S59" s="55" t="n"/>
+      <c r="T59" s="55" t="n"/>
+      <c r="U59" s="55" t="n"/>
+      <c r="V59" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W59" s="57" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
+      <c r="C60" s="46" t="n"/>
+      <c r="D60" s="46" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G60" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G60" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="55" t="n"/>
-      <c r="N60" s="55" t="n"/>
-      <c r="O60" s="55" t="n"/>
-      <c r="P60" s="55" t="n"/>
-      <c r="Q60" s="55" t="n"/>
-      <c r="R60" s="55" t="n"/>
-      <c r="S60" s="55" t="n"/>
-      <c r="T60" s="55" t="n"/>
-      <c r="U60" s="55" t="n"/>
-      <c r="V60" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W60" s="57" t="n"/>
+      <c r="M60" s="51" t="n"/>
+      <c r="N60" s="51" t="n"/>
+      <c r="O60" s="51" t="n"/>
+      <c r="P60" s="51" t="n"/>
+      <c r="Q60" s="51" t="n"/>
+      <c r="R60" s="51" t="n"/>
+      <c r="S60" s="51" t="n"/>
+      <c r="T60" s="51" t="n"/>
+      <c r="U60" s="51" t="n"/>
+      <c r="V60" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W60" s="58" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="46" t="n"/>
-      <c r="D61" s="46" t="n"/>
+      <c r="C61" s="53" t="n"/>
+      <c r="D61" s="53" t="n"/>
       <c r="E61" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F61" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G61" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G61" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
       <c r="J61" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K61" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="51" t="n"/>
-      <c r="N61" s="51" t="n"/>
-      <c r="O61" s="51" t="n"/>
-      <c r="P61" s="51" t="n"/>
-      <c r="Q61" s="51" t="n"/>
-      <c r="R61" s="51" t="n"/>
-      <c r="S61" s="51" t="n"/>
-      <c r="T61" s="51" t="n"/>
-      <c r="U61" s="51" t="n"/>
-      <c r="V61" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W61" s="58" t="n"/>
+      <c r="M61" s="55" t="n"/>
+      <c r="N61" s="55" t="n"/>
+      <c r="O61" s="55" t="n"/>
+      <c r="P61" s="55" t="n"/>
+      <c r="Q61" s="55" t="n"/>
+      <c r="R61" s="55" t="n"/>
+      <c r="S61" s="55" t="n"/>
+      <c r="T61" s="55" t="n"/>
+      <c r="U61" s="55" t="n"/>
+      <c r="V61" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W61" s="57" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B62" s="45" t="n"/>
-      <c r="C62" s="53" t="n"/>
-      <c r="D62" s="53" t="n"/>
+      <c r="C62" s="46" t="n"/>
+      <c r="D62" s="46" t="n"/>
       <c r="E62" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F62" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G62" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G62" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="49" t="n"/>
       <c r="J62" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K62" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L62" s="50" t="n"/>
-      <c r="M62" s="55" t="n"/>
-      <c r="N62" s="55" t="n"/>
-      <c r="O62" s="55" t="n"/>
-      <c r="P62" s="55" t="n"/>
-      <c r="Q62" s="55" t="n"/>
-      <c r="R62" s="55" t="n"/>
-      <c r="S62" s="55" t="n"/>
-      <c r="T62" s="55" t="n"/>
-      <c r="U62" s="55" t="n"/>
-      <c r="V62" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W62" s="57" t="n"/>
+      <c r="M62" s="51" t="n"/>
+      <c r="N62" s="51" t="n"/>
+      <c r="O62" s="51" t="n"/>
+      <c r="P62" s="51" t="n"/>
+      <c r="Q62" s="51" t="n"/>
+      <c r="R62" s="51" t="n"/>
+      <c r="S62" s="51" t="n"/>
+      <c r="T62" s="51" t="n"/>
+      <c r="U62" s="51" t="n"/>
+      <c r="V62" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W62" s="58" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B63" s="45" t="n"/>
-      <c r="C63" s="46" t="n"/>
-      <c r="D63" s="46" t="n"/>
+      <c r="C63" s="53" t="n"/>
+      <c r="D63" s="53" t="n"/>
       <c r="E63" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F63" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G63" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G63" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="49" t="n"/>
       <c r="J63" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K63" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L63" s="50" t="n"/>
-      <c r="M63" s="51" t="n"/>
-      <c r="N63" s="51" t="n"/>
-      <c r="O63" s="51" t="n"/>
-      <c r="P63" s="51" t="n"/>
-      <c r="Q63" s="51" t="n"/>
-      <c r="R63" s="51" t="n"/>
-      <c r="S63" s="51" t="n"/>
-      <c r="T63" s="51" t="n"/>
-      <c r="U63" s="51" t="n"/>
-      <c r="V63" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W63" s="58" t="n"/>
+      <c r="M63" s="55" t="n"/>
+      <c r="N63" s="55" t="n"/>
+      <c r="O63" s="55" t="n"/>
+      <c r="P63" s="55" t="n"/>
+      <c r="Q63" s="55" t="n"/>
+      <c r="R63" s="55" t="n"/>
+      <c r="S63" s="55" t="n"/>
+      <c r="T63" s="55" t="n"/>
+      <c r="U63" s="55" t="n"/>
+      <c r="V63" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W63" s="57" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B64" s="45" t="n"/>
-      <c r="C64" s="53" t="n"/>
-      <c r="D64" s="53" t="n"/>
+      <c r="C64" s="46" t="n"/>
+      <c r="D64" s="46" t="n"/>
       <c r="E64" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F64" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G64" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G64" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="49" t="n"/>
       <c r="J64" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K64" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L64" s="50" t="n"/>
-      <c r="M64" s="55" t="n"/>
-      <c r="N64" s="55" t="n"/>
-      <c r="O64" s="55" t="n"/>
-      <c r="P64" s="55" t="n"/>
-      <c r="Q64" s="55" t="n"/>
-      <c r="R64" s="55" t="n"/>
-      <c r="S64" s="55" t="n"/>
-      <c r="T64" s="55" t="n"/>
-      <c r="U64" s="55" t="n"/>
-      <c r="V64" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W64" s="57" t="n"/>
+      <c r="M64" s="51" t="n"/>
+      <c r="N64" s="51" t="n"/>
+      <c r="O64" s="51" t="n"/>
+      <c r="P64" s="51" t="n"/>
+      <c r="Q64" s="51" t="n"/>
+      <c r="R64" s="51" t="n"/>
+      <c r="S64" s="51" t="n"/>
+      <c r="T64" s="51" t="n"/>
+      <c r="U64" s="51" t="n"/>
+      <c r="V64" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W64" s="58" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B65" s="45" t="n"/>
-      <c r="C65" s="46" t="n"/>
-      <c r="D65" s="46" t="n"/>
+      <c r="C65" s="53" t="n"/>
+      <c r="D65" s="53" t="n"/>
       <c r="E65" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F65" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G65" s="48" t="n">
-        <v>24</v>
+      <c r="G65" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H65" s="49" t="n"/>
       <c r="I65" s="49" t="n"/>
       <c r="J65" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K65" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L65" s="50" t="n"/>
-      <c r="M65" s="51" t="n"/>
-      <c r="N65" s="51" t="n"/>
-      <c r="O65" s="51" t="n"/>
-      <c r="P65" s="51" t="n"/>
-      <c r="Q65" s="51" t="n"/>
-      <c r="R65" s="51" t="n"/>
-      <c r="S65" s="51" t="n"/>
-      <c r="T65" s="51" t="n"/>
-      <c r="U65" s="51" t="n"/>
-      <c r="V65" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W65" s="58" t="n"/>
+      <c r="M65" s="55" t="n"/>
+      <c r="N65" s="55" t="n"/>
+      <c r="O65" s="55" t="n"/>
+      <c r="P65" s="55" t="n"/>
+      <c r="Q65" s="55" t="n"/>
+      <c r="R65" s="55" t="n"/>
+      <c r="S65" s="55" t="n"/>
+      <c r="T65" s="55" t="n"/>
+      <c r="U65" s="55" t="n"/>
+      <c r="V65" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W65" s="57" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B66" s="45" t="n"/>
-      <c r="C66" s="53" t="n"/>
-      <c r="D66" s="53" t="n"/>
+      <c r="C66" s="46" t="n"/>
+      <c r="D66" s="46" t="n"/>
       <c r="E66" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F66" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G66" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G66" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H66" s="49" t="n"/>
       <c r="I66" s="49" t="n"/>
       <c r="J66" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K66" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L66" s="50" t="n"/>
-      <c r="M66" s="55" t="n"/>
-      <c r="N66" s="55" t="n"/>
-      <c r="O66" s="55" t="n"/>
-      <c r="P66" s="55" t="n"/>
-      <c r="Q66" s="55" t="n"/>
-      <c r="R66" s="55" t="n"/>
-      <c r="S66" s="55" t="n"/>
-      <c r="T66" s="55" t="n"/>
-      <c r="U66" s="55" t="n"/>
-      <c r="V66" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W66" s="57" t="n"/>
+      <c r="M66" s="51" t="n"/>
+      <c r="N66" s="51" t="n"/>
+      <c r="O66" s="51" t="n"/>
+      <c r="P66" s="51" t="n"/>
+      <c r="Q66" s="51" t="n"/>
+      <c r="R66" s="51" t="n"/>
+      <c r="S66" s="51" t="n"/>
+      <c r="T66" s="51" t="n"/>
+      <c r="U66" s="51" t="n"/>
+      <c r="V66" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W66" s="58" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B67" s="45" t="n"/>
-      <c r="C67" s="46" t="n"/>
-      <c r="D67" s="46" t="n"/>
+      <c r="C67" s="53" t="n"/>
+      <c r="D67" s="53" t="n"/>
       <c r="E67" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F67" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G67" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G67" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H67" s="49" t="n"/>
       <c r="I67" s="49" t="n"/>
       <c r="J67" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K67" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L67" s="50" t="n"/>
-      <c r="M67" s="51" t="n"/>
-      <c r="N67" s="51" t="n"/>
-      <c r="O67" s="51" t="n"/>
-      <c r="P67" s="51" t="n"/>
-      <c r="Q67" s="51" t="n"/>
-      <c r="R67" s="51" t="n"/>
-      <c r="S67" s="51" t="n"/>
-      <c r="T67" s="51" t="n"/>
-      <c r="U67" s="51" t="n"/>
-      <c r="V67" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W67" s="58" t="n"/>
+      <c r="M67" s="55" t="n"/>
+      <c r="N67" s="55" t="n"/>
+      <c r="O67" s="55" t="n"/>
+      <c r="P67" s="55" t="n"/>
+      <c r="Q67" s="55" t="n"/>
+      <c r="R67" s="55" t="n"/>
+      <c r="S67" s="55" t="n"/>
+      <c r="T67" s="55" t="n"/>
+      <c r="U67" s="55" t="n"/>
+      <c r="V67" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W67" s="57" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B68" s="45" t="n"/>
-      <c r="C68" s="53" t="n"/>
-      <c r="D68" s="53" t="n"/>
+      <c r="C68" s="46" t="n"/>
+      <c r="D68" s="46" t="n"/>
       <c r="E68" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F68" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G68" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H68" s="49" t="n"/>
       <c r="I68" s="49" t="n"/>
@@ -5030,51 +5048,92 @@
         <v>59</v>
       </c>
       <c r="K68" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L68" s="50" t="n"/>
-      <c r="M68" s="55" t="n"/>
-      <c r="N68" s="55" t="n"/>
-      <c r="O68" s="55" t="n"/>
-      <c r="P68" s="55" t="n"/>
-      <c r="Q68" s="55" t="n"/>
-      <c r="R68" s="55" t="n"/>
-      <c r="S68" s="55" t="n"/>
-      <c r="T68" s="55" t="n"/>
-      <c r="U68" s="55" t="n"/>
-      <c r="V68" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W68" s="57" t="n"/>
+      <c r="M68" s="51" t="n"/>
+      <c r="N68" s="51" t="n"/>
+      <c r="O68" s="51" t="n"/>
+      <c r="P68" s="51" t="n"/>
+      <c r="Q68" s="51" t="n"/>
+      <c r="R68" s="51" t="n"/>
+      <c r="S68" s="51" t="n"/>
+      <c r="T68" s="51" t="n"/>
+      <c r="U68" s="51" t="n"/>
+      <c r="V68" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W68" s="58" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B69" s="45" t="n"/>
-      <c r="C69" s="46" t="n"/>
-      <c r="D69" s="46" t="n"/>
-      <c r="E69" s="47" t="n"/>
-      <c r="F69" s="47" t="n"/>
-      <c r="G69" s="60" t="n"/>
+      <c r="C69" s="53" t="n"/>
+      <c r="D69" s="53" t="n"/>
+      <c r="E69" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F69" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G69" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H69" s="49" t="n"/>
       <c r="I69" s="49" t="n"/>
-      <c r="J69" s="50" t="n"/>
-      <c r="K69" s="50" t="n"/>
+      <c r="J69" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K69" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L69" s="50" t="n"/>
-      <c r="M69" s="51" t="n"/>
-      <c r="N69" s="51" t="n"/>
-      <c r="O69" s="51" t="n"/>
-      <c r="P69" s="51" t="n"/>
-      <c r="Q69" s="51" t="n"/>
-      <c r="R69" s="51" t="n"/>
-      <c r="S69" s="51" t="n"/>
-      <c r="T69" s="51" t="n"/>
-      <c r="U69" s="51" t="n"/>
-      <c r="V69" s="61" t="n"/>
-      <c r="W69" s="61" t="n"/>
+      <c r="M69" s="55" t="n"/>
+      <c r="N69" s="55" t="n"/>
+      <c r="O69" s="55" t="n"/>
+      <c r="P69" s="55" t="n"/>
+      <c r="Q69" s="55" t="n"/>
+      <c r="R69" s="55" t="n"/>
+      <c r="S69" s="55" t="n"/>
+      <c r="T69" s="55" t="n"/>
+      <c r="U69" s="55" t="n"/>
+      <c r="V69" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W69" s="57" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B70" s="45" t="n"/>
+      <c r="C70" s="46" t="n"/>
+      <c r="D70" s="46" t="n"/>
+      <c r="E70" s="47" t="n"/>
+      <c r="F70" s="47" t="n"/>
+      <c r="G70" s="60" t="n"/>
+      <c r="H70" s="49" t="n"/>
+      <c r="I70" s="49" t="n"/>
+      <c r="J70" s="50" t="n"/>
+      <c r="K70" s="50" t="n"/>
+      <c r="L70" s="50" t="n"/>
+      <c r="M70" s="51" t="n"/>
+      <c r="N70" s="51" t="n"/>
+      <c r="O70" s="51" t="n"/>
+      <c r="P70" s="51" t="n"/>
+      <c r="Q70" s="51" t="n"/>
+      <c r="R70" s="51" t="n"/>
+      <c r="S70" s="51" t="n"/>
+      <c r="T70" s="51" t="n"/>
+      <c r="U70" s="51" t="n"/>
+      <c r="V70" s="61" t="n"/>
+      <c r="W70" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W70"/>
+  <dimension ref="A1:W71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,79 +1982,75 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/14(二)</t>
+          <t>2026/04/15(三)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>55</v>
-      </c>
-      <c r="G4" s="66" t="n">
-        <v>24.7</v>
+        <v>57</v>
+      </c>
+      <c r="G4" s="71" t="n">
+        <v>29.6</v>
       </c>
       <c r="H4" s="67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I4" s="67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J4" s="68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K4" s="68" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L4" s="68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M4" s="69" t="inlineStr">
         <is>
-          <t>美能能源</t>
-        </is>
-      </c>
-      <c r="N4" s="69" t="inlineStr">
-        <is>
-          <t>中恒电气、圣阳股份</t>
-        </is>
-      </c>
-      <c r="O4" s="69" t="inlineStr"/>
-      <c r="P4" s="69" t="inlineStr">
-        <is>
-          <t>华远控股</t>
-        </is>
-      </c>
+          <t>博云新材、天邦食品</t>
+        </is>
+      </c>
+      <c r="N4" s="69" t="inlineStr"/>
+      <c r="O4" s="69" t="inlineStr">
+        <is>
+          <t>圣阳股份</t>
+        </is>
+      </c>
+      <c r="P4" s="69" t="inlineStr"/>
       <c r="Q4" s="69" t="inlineStr"/>
       <c r="R4" s="69" t="inlineStr"/>
       <c r="S4" s="69" t="inlineStr"/>
       <c r="T4" s="69" t="inlineStr"/>
       <c r="U4" s="69" t="inlineStr"/>
       <c r="V4" s="69" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="W4" s="69" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/13(一)</t>
+          <t>2026/04/14(二)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
       <c r="C5" s="64" t="inlineStr"/>
       <c r="D5" s="64" t="inlineStr"/>
       <c r="E5" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G5" s="66" t="n">
-        <v>20.3</v>
+        <v>24.7</v>
       </c>
       <c r="H5" s="67" t="n">
         <v>4</v>
@@ -2063,30 +2059,30 @@
         <v>4</v>
       </c>
       <c r="J5" s="68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K5" s="68" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L5" s="68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M5" s="69" t="inlineStr">
         <is>
+          <t>美能能源</t>
+        </is>
+      </c>
+      <c r="N5" s="69" t="inlineStr">
+        <is>
           <t>中恒电气、圣阳股份</t>
         </is>
       </c>
-      <c r="N5" s="69" t="inlineStr">
-        <is>
-          <t>长源东谷</t>
-        </is>
-      </c>
-      <c r="O5" s="69" t="inlineStr">
+      <c r="O5" s="69" t="inlineStr"/>
+      <c r="P5" s="69" t="inlineStr">
         <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="P5" s="69" t="inlineStr"/>
       <c r="Q5" s="69" t="inlineStr"/>
       <c r="R5" s="69" t="inlineStr"/>
       <c r="S5" s="69" t="inlineStr"/>
@@ -2100,7 +2096,7 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/04/10(五)</t>
+          <t>2026/04/13(一)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
@@ -2112,35 +2108,39 @@
       <c r="F6" s="65" t="n">
         <v>59</v>
       </c>
-      <c r="G6" s="71" t="n">
-        <v>31.4</v>
+      <c r="G6" s="66" t="n">
+        <v>20.3</v>
       </c>
       <c r="H6" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I6" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" s="68" t="n">
-        <v>13</v>
-      </c>
       <c r="K6" s="68" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L6" s="68" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M6" s="69" t="inlineStr">
         <is>
-          <t>中嘉博创、长源东谷、来伊份</t>
+          <t>中恒电气、圣阳股份</t>
         </is>
       </c>
       <c r="N6" s="69" t="inlineStr">
         <is>
+          <t>长源东谷</t>
+        </is>
+      </c>
+      <c r="O6" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="O6" s="69" t="inlineStr"/>
       <c r="P6" s="69" t="inlineStr"/>
       <c r="Q6" s="69" t="inlineStr"/>
       <c r="R6" s="69" t="inlineStr"/>
@@ -2148,54 +2148,54 @@
       <c r="T6" s="69" t="inlineStr"/>
       <c r="U6" s="69" t="inlineStr"/>
       <c r="V6" s="69" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="W6" s="69" t="inlineStr"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="62" t="inlineStr">
         <is>
-          <t>2026/04/09(四)</t>
+          <t>2026/04/10(五)</t>
         </is>
       </c>
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="64" t="inlineStr"/>
       <c r="D7" s="64" t="inlineStr"/>
       <c r="E7" s="65" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F7" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G7" s="66" t="n">
-        <v>23.2</v>
+        <v>59</v>
+      </c>
+      <c r="G7" s="71" t="n">
+        <v>31.4</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I7" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J7" s="68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K7" s="68" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L7" s="68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M7" s="69" t="inlineStr">
         <is>
+          <t>中嘉博创、长源东谷、来伊份</t>
+        </is>
+      </c>
+      <c r="N7" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="N7" s="69" t="inlineStr"/>
-      <c r="O7" s="69" t="inlineStr">
-        <is>
-          <t>汇源通信</t>
-        </is>
-      </c>
+      <c r="O7" s="69" t="inlineStr"/>
       <c r="P7" s="69" t="inlineStr"/>
       <c r="Q7" s="69" t="inlineStr"/>
       <c r="R7" s="69" t="inlineStr"/>
@@ -2203,54 +2203,54 @@
       <c r="T7" s="69" t="inlineStr"/>
       <c r="U7" s="69" t="inlineStr"/>
       <c r="V7" s="69" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="W7" s="69" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="62" t="inlineStr">
         <is>
-          <t>2026/04/08(三)</t>
+          <t>2026/04/09(四)</t>
         </is>
       </c>
       <c r="B8" s="63" t="inlineStr"/>
       <c r="C8" s="64" t="inlineStr"/>
       <c r="D8" s="64" t="inlineStr"/>
       <c r="E8" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="F8" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="G8" s="66" t="n">
-        <v>11.5</v>
+        <v>23.2</v>
       </c>
       <c r="H8" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I8" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J8" s="68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K8" s="68" t="n">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="L8" s="68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M8" s="69" t="inlineStr">
         <is>
-          <t>中安科</t>
-        </is>
-      </c>
-      <c r="N8" s="69" t="inlineStr">
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="N8" s="69" t="inlineStr"/>
+      <c r="O8" s="69" t="inlineStr">
         <is>
           <t>汇源通信</t>
         </is>
       </c>
-      <c r="O8" s="69" t="inlineStr"/>
       <c r="P8" s="69" t="inlineStr"/>
       <c r="Q8" s="69" t="inlineStr"/>
       <c r="R8" s="69" t="inlineStr"/>
@@ -2265,20 +2265,20 @@
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="62" t="inlineStr">
         <is>
-          <t>2026/04/07(二)</t>
+          <t>2026/04/08(三)</t>
         </is>
       </c>
       <c r="B9" s="63" t="inlineStr"/>
       <c r="C9" s="64" t="inlineStr"/>
       <c r="D9" s="64" t="inlineStr"/>
       <c r="E9" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F9" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G9" s="66" t="n">
-        <v>21.8</v>
+        <v>11.5</v>
       </c>
       <c r="H9" s="67" t="n">
         <v>4</v>
@@ -2287,91 +2287,95 @@
         <v>4</v>
       </c>
       <c r="J9" s="68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K9" s="68" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="L9" s="68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M9" s="69" t="inlineStr">
         <is>
-          <t>汇源通信、新能泰山</t>
-        </is>
-      </c>
-      <c r="N9" s="69" t="inlineStr"/>
+          <t>中安科</t>
+        </is>
+      </c>
+      <c r="N9" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信</t>
+        </is>
+      </c>
       <c r="O9" s="69" t="inlineStr"/>
       <c r="P9" s="69" t="inlineStr"/>
-      <c r="Q9" s="69" t="inlineStr">
-        <is>
-          <t>津药药业</t>
-        </is>
-      </c>
+      <c r="Q9" s="69" t="inlineStr"/>
       <c r="R9" s="69" t="inlineStr"/>
       <c r="S9" s="69" t="inlineStr"/>
       <c r="T9" s="69" t="inlineStr"/>
       <c r="U9" s="69" t="inlineStr"/>
       <c r="V9" s="69" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W9" s="69" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="62" t="inlineStr">
         <is>
-          <t>2026/04/06(一)</t>
+          <t>2026/04/07(二)</t>
         </is>
       </c>
       <c r="B10" s="63" t="inlineStr"/>
       <c r="C10" s="64" t="inlineStr"/>
       <c r="D10" s="64" t="inlineStr"/>
       <c r="E10" s="65" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F10" s="65" t="n">
-        <v>36</v>
-      </c>
-      <c r="G10" s="71" t="n">
-        <v>25</v>
+        <v>93</v>
+      </c>
+      <c r="G10" s="66" t="n">
+        <v>21.8</v>
       </c>
       <c r="H10" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I10" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J10" s="68" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="L10" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K10" s="68" t="n">
-        <v>32</v>
-      </c>
-      <c r="L10" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" s="69" t="inlineStr"/>
+      <c r="M10" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信、新能泰山</t>
+        </is>
+      </c>
       <c r="N10" s="69" t="inlineStr"/>
       <c r="O10" s="69" t="inlineStr"/>
-      <c r="P10" s="69" t="inlineStr">
+      <c r="P10" s="69" t="inlineStr"/>
+      <c r="Q10" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="Q10" s="69" t="inlineStr"/>
       <c r="R10" s="69" t="inlineStr"/>
       <c r="S10" s="69" t="inlineStr"/>
       <c r="T10" s="69" t="inlineStr"/>
       <c r="U10" s="69" t="inlineStr"/>
       <c r="V10" s="69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W10" s="69" t="inlineStr"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="62" t="inlineStr">
         <is>
-          <t>2026/04/03(五)</t>
+          <t>2026/04/06(一)</t>
         </is>
       </c>
       <c r="B11" s="63" t="inlineStr"/>
@@ -2415,105 +2419,105 @@
       <c r="T11" s="69" t="inlineStr"/>
       <c r="U11" s="69" t="inlineStr"/>
       <c r="V11" s="69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W11" s="69" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B12" s="63" t="inlineStr"/>
       <c r="C12" s="64" t="inlineStr"/>
       <c r="D12" s="64" t="inlineStr"/>
       <c r="E12" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F12" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G12" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H12" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I12" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J12" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K12" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L12" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M12" s="69" t="inlineStr"/>
       <c r="N12" s="69" t="inlineStr"/>
-      <c r="O12" s="69" t="inlineStr">
+      <c r="O12" s="69" t="inlineStr"/>
+      <c r="P12" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P12" s="69" t="inlineStr"/>
       <c r="Q12" s="69" t="inlineStr"/>
       <c r="R12" s="69" t="inlineStr"/>
       <c r="S12" s="69" t="inlineStr"/>
       <c r="T12" s="69" t="inlineStr"/>
       <c r="U12" s="69" t="inlineStr"/>
       <c r="V12" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W12" s="69" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B13" s="63" t="inlineStr"/>
       <c r="C13" s="64" t="inlineStr"/>
       <c r="D13" s="64" t="inlineStr"/>
       <c r="E13" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F13" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G13" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G13" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H13" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I13" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K13" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L13" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M13" s="69" t="inlineStr"/>
-      <c r="N13" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M13" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N13" s="69" t="inlineStr"/>
+      <c r="O13" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O13" s="69" t="inlineStr"/>
       <c r="P13" s="69" t="inlineStr"/>
       <c r="Q13" s="69" t="inlineStr"/>
       <c r="R13" s="69" t="inlineStr"/>
@@ -2521,51 +2525,47 @@
       <c r="T13" s="69" t="inlineStr"/>
       <c r="U13" s="69" t="inlineStr"/>
       <c r="V13" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W13" s="69" t="inlineStr"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B14" s="63" t="inlineStr"/>
       <c r="C14" s="64" t="inlineStr"/>
       <c r="D14" s="64" t="inlineStr"/>
       <c r="E14" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F14" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G14" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G14" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H14" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I14" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J14" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K14" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L14" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M14" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M14" s="69" t="inlineStr"/>
+      <c r="N14" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N14" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O14" s="69" t="inlineStr"/>
@@ -2576,254 +2576,250 @@
       <c r="T14" s="69" t="inlineStr"/>
       <c r="U14" s="69" t="inlineStr"/>
       <c r="V14" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W14" s="69" t="inlineStr"/>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B15" s="63" t="inlineStr"/>
+      <c r="C15" s="64" t="inlineStr"/>
+      <c r="D15" s="64" t="inlineStr"/>
+      <c r="E15" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F15" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G15" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H15" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L15" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M15" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N15" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O15" s="69" t="inlineStr"/>
+      <c r="P15" s="69" t="inlineStr"/>
+      <c r="Q15" s="69" t="inlineStr"/>
+      <c r="R15" s="69" t="inlineStr"/>
+      <c r="S15" s="69" t="inlineStr"/>
+      <c r="T15" s="69" t="inlineStr"/>
+      <c r="U15" s="69" t="inlineStr"/>
+      <c r="V15" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="69" t="inlineStr"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="W15" s="69" t="inlineStr"/>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D15" s="38" t="inlineStr">
+      <c r="D16" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E15" s="39" t="n">
+      <c r="E16" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F15" s="39" t="n">
+      <c r="F16" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G15" s="40" t="n">
+      <c r="G16" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H15" s="41" t="n">
+      <c r="H16" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I15" s="41" t="n">
+      <c r="I16" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="42" t="n">
+      <c r="J16" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K15" s="42" t="n">
+      <c r="K16" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L15" s="42" t="n">
+      <c r="L16" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M15" s="43" t="inlineStr">
+      <c r="M16" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N15" s="43" t="inlineStr"/>
-      <c r="O15" s="43" t="inlineStr">
+      <c r="N16" s="43" t="inlineStr"/>
+      <c r="O16" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P15" s="43" t="inlineStr"/>
-      <c r="Q15" s="43" t="inlineStr"/>
-      <c r="R15" s="43" t="inlineStr"/>
-      <c r="S15" s="43" t="inlineStr"/>
-      <c r="T15" s="43" t="inlineStr"/>
-      <c r="U15" s="43" t="inlineStr"/>
-      <c r="V15" s="43" t="n">
+      <c r="P16" s="43" t="inlineStr"/>
+      <c r="Q16" s="43" t="inlineStr"/>
+      <c r="R16" s="43" t="inlineStr"/>
+      <c r="S16" s="43" t="inlineStr"/>
+      <c r="T16" s="43" t="inlineStr"/>
+      <c r="U16" s="43" t="inlineStr"/>
+      <c r="V16" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W15" s="43" t="inlineStr"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B16" s="45" t="n"/>
-      <c r="C16" s="46" t="n"/>
-      <c r="D16" s="46" t="n"/>
-      <c r="E16" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F16" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G16" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H16" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K16" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L16" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M16" s="51" t="n"/>
-      <c r="N16" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O16" s="51" t="n"/>
-      <c r="P16" s="51" t="n"/>
-      <c r="Q16" s="51" t="n"/>
-      <c r="R16" s="51" t="n"/>
-      <c r="S16" s="51" t="n"/>
-      <c r="T16" s="51" t="n"/>
-      <c r="U16" s="51" t="n"/>
-      <c r="V16" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W16" s="43" t="inlineStr"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B17" s="45" t="n"/>
-      <c r="C17" s="53" t="n"/>
-      <c r="D17" s="53" t="n"/>
+      <c r="C17" s="46" t="n"/>
+      <c r="D17" s="46" t="n"/>
       <c r="E17" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F17" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G17" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G17" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H17" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J17" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K17" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L17" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M17" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N17" s="55" t="n"/>
-      <c r="O17" s="55" t="n"/>
-      <c r="P17" s="55" t="n"/>
-      <c r="Q17" s="55" t="n"/>
-      <c r="R17" s="55" t="n"/>
-      <c r="S17" s="55" t="n"/>
-      <c r="T17" s="55" t="n"/>
-      <c r="U17" s="55" t="n"/>
-      <c r="V17" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W17" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M17" s="51" t="n"/>
+      <c r="N17" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O17" s="51" t="n"/>
+      <c r="P17" s="51" t="n"/>
+      <c r="Q17" s="51" t="n"/>
+      <c r="R17" s="51" t="n"/>
+      <c r="S17" s="51" t="n"/>
+      <c r="T17" s="51" t="n"/>
+      <c r="U17" s="51" t="n"/>
+      <c r="V17" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B18" s="45" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="53" t="n"/>
       <c r="E18" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F18" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G18" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G18" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H18" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I18" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J18" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K18" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L18" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M18" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N18" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O18" s="51" t="n"/>
-      <c r="P18" s="51" t="n"/>
-      <c r="Q18" s="51" t="n"/>
-      <c r="R18" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S18" s="51" t="n"/>
-      <c r="T18" s="51" t="n"/>
-      <c r="U18" s="51" t="n"/>
-      <c r="V18" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W18" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M18" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N18" s="55" t="n"/>
+      <c r="O18" s="55" t="n"/>
+      <c r="P18" s="55" t="n"/>
+      <c r="Q18" s="55" t="n"/>
+      <c r="R18" s="55" t="n"/>
+      <c r="S18" s="55" t="n"/>
+      <c r="T18" s="55" t="n"/>
+      <c r="U18" s="55" t="n"/>
+      <c r="V18" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W18" s="57" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B19" s="45" t="n"/>
-      <c r="C19" s="53" t="n"/>
-      <c r="D19" s="53" t="n"/>
+      <c r="C19" s="46" t="n"/>
+      <c r="D19" s="46" t="n"/>
       <c r="E19" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G19" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H19" s="49" t="n">
         <v>1</v>
@@ -2832,493 +2828,497 @@
         <v>1</v>
       </c>
       <c r="J19" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K19" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L19" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M19" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M19" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N19" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N19" s="55" t="n"/>
-      <c r="O19" s="55" t="n"/>
-      <c r="P19" s="55" t="n"/>
-      <c r="Q19" s="55" t="inlineStr">
+      <c r="O19" s="51" t="n"/>
+      <c r="P19" s="51" t="n"/>
+      <c r="Q19" s="51" t="n"/>
+      <c r="R19" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R19" s="55" t="n"/>
-      <c r="S19" s="55" t="n"/>
-      <c r="T19" s="55" t="n"/>
-      <c r="U19" s="55" t="n"/>
-      <c r="V19" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W19" s="57" t="n"/>
+      <c r="S19" s="51" t="n"/>
+      <c r="T19" s="51" t="n"/>
+      <c r="U19" s="51" t="n"/>
+      <c r="V19" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W19" s="58" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B20" s="45" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="46" t="n"/>
+      <c r="C20" s="53" t="n"/>
+      <c r="D20" s="53" t="n"/>
       <c r="E20" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F20" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G20" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G20" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H20" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J20" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K20" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L20" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N20" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O20" s="51" t="n"/>
-      <c r="P20" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M20" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N20" s="55" t="n"/>
+      <c r="O20" s="55" t="n"/>
+      <c r="P20" s="55" t="n"/>
+      <c r="Q20" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q20" s="51" t="n"/>
-      <c r="R20" s="51" t="n"/>
-      <c r="S20" s="51" t="n"/>
-      <c r="T20" s="51" t="n"/>
-      <c r="U20" s="51" t="n"/>
-      <c r="V20" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W20" s="58" t="n"/>
+      <c r="R20" s="55" t="n"/>
+      <c r="S20" s="55" t="n"/>
+      <c r="T20" s="55" t="n"/>
+      <c r="U20" s="55" t="n"/>
+      <c r="V20" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W20" s="57" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="53" t="n"/>
-      <c r="D21" s="53" t="n"/>
+      <c r="C21" s="46" t="n"/>
+      <c r="D21" s="46" t="n"/>
       <c r="E21" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F21" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G21" s="59" t="n">
-        <v>45.1</v>
+      <c r="G21" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H21" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J21" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K21" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L21" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M21" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N21" s="55" t="n"/>
-      <c r="O21" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P21" s="55" t="n"/>
-      <c r="Q21" s="55" t="n"/>
-      <c r="R21" s="55" t="n"/>
-      <c r="S21" s="55" t="n"/>
-      <c r="T21" s="55" t="n"/>
-      <c r="U21" s="55" t="n"/>
-      <c r="V21" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W21" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M21" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N21" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O21" s="51" t="n"/>
+      <c r="P21" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q21" s="51" t="n"/>
+      <c r="R21" s="51" t="n"/>
+      <c r="S21" s="51" t="n"/>
+      <c r="T21" s="51" t="n"/>
+      <c r="U21" s="51" t="n"/>
+      <c r="V21" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W21" s="58" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="46" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
       <c r="E22" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F22" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G22" s="54" t="n">
-        <v>26.3</v>
+      <c r="G22" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H22" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K22" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L22" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M22" s="51" t="n"/>
-      <c r="N22" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M22" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N22" s="55" t="n"/>
+      <c r="O22" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O22" s="51" t="n"/>
-      <c r="P22" s="51" t="n"/>
-      <c r="Q22" s="51" t="n"/>
-      <c r="R22" s="51" t="n"/>
-      <c r="S22" s="51" t="n"/>
-      <c r="T22" s="51" t="n"/>
-      <c r="U22" s="51" t="n"/>
-      <c r="V22" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W22" s="58" t="n"/>
+      <c r="P22" s="55" t="n"/>
+      <c r="Q22" s="55" t="n"/>
+      <c r="R22" s="55" t="n"/>
+      <c r="S22" s="55" t="n"/>
+      <c r="T22" s="55" t="n"/>
+      <c r="U22" s="55" t="n"/>
+      <c r="V22" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W22" s="57" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="53" t="n"/>
-      <c r="D23" s="53" t="n"/>
+      <c r="C23" s="46" t="n"/>
+      <c r="D23" s="46" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G23" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H23" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L23" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M23" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M23" s="51" t="n"/>
+      <c r="N23" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N23" s="55" t="n"/>
-      <c r="O23" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P23" s="55" t="n"/>
-      <c r="Q23" s="55" t="n"/>
-      <c r="R23" s="55" t="n"/>
-      <c r="S23" s="55" t="n"/>
-      <c r="T23" s="55" t="n"/>
-      <c r="U23" s="55" t="n"/>
-      <c r="V23" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W23" s="57" t="n"/>
+      <c r="O23" s="51" t="n"/>
+      <c r="P23" s="51" t="n"/>
+      <c r="Q23" s="51" t="n"/>
+      <c r="R23" s="51" t="n"/>
+      <c r="S23" s="51" t="n"/>
+      <c r="T23" s="51" t="n"/>
+      <c r="U23" s="51" t="n"/>
+      <c r="V23" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W23" s="58" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G24" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H24" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L24" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M24" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N24" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O24" s="51" t="n"/>
-      <c r="P24" s="51" t="n"/>
-      <c r="Q24" s="51" t="n"/>
-      <c r="R24" s="51" t="n"/>
-      <c r="S24" s="51" t="n"/>
-      <c r="T24" s="51" t="n"/>
-      <c r="U24" s="51" t="n"/>
-      <c r="V24" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W24" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M24" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N24" s="55" t="n"/>
+      <c r="O24" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P24" s="55" t="n"/>
+      <c r="Q24" s="55" t="n"/>
+      <c r="R24" s="55" t="n"/>
+      <c r="S24" s="55" t="n"/>
+      <c r="T24" s="55" t="n"/>
+      <c r="U24" s="55" t="n"/>
+      <c r="V24" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W24" s="57" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="53" t="n"/>
-      <c r="D25" s="53" t="n"/>
+      <c r="C25" s="46" t="n"/>
+      <c r="D25" s="46" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G25" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H25" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K25" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L25" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I25" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J25" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K25" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L25" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M25" s="55" t="inlineStr">
+      <c r="M25" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N25" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N25" s="55" t="n"/>
-      <c r="O25" s="55" t="n"/>
-      <c r="P25" s="55" t="n"/>
-      <c r="Q25" s="55" t="n"/>
-      <c r="R25" s="55" t="n"/>
-      <c r="S25" s="55" t="n"/>
-      <c r="T25" s="55" t="n"/>
-      <c r="U25" s="55" t="n"/>
-      <c r="V25" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W25" s="57" t="n"/>
+      <c r="O25" s="51" t="n"/>
+      <c r="P25" s="51" t="n"/>
+      <c r="Q25" s="51" t="n"/>
+      <c r="R25" s="51" t="n"/>
+      <c r="S25" s="51" t="n"/>
+      <c r="T25" s="51" t="n"/>
+      <c r="U25" s="51" t="n"/>
+      <c r="V25" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W25" s="58" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="46" t="n"/>
-      <c r="D26" s="46" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G26" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G26" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H26" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I26" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L26" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M26" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N26" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O26" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P26" s="51" t="n"/>
-      <c r="Q26" s="51" t="n"/>
-      <c r="R26" s="51" t="n"/>
-      <c r="S26" s="51" t="n"/>
-      <c r="T26" s="51" t="n"/>
-      <c r="U26" s="51" t="n"/>
-      <c r="V26" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W26" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M26" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N26" s="55" t="n"/>
+      <c r="O26" s="55" t="n"/>
+      <c r="P26" s="55" t="n"/>
+      <c r="Q26" s="55" t="n"/>
+      <c r="R26" s="55" t="n"/>
+      <c r="S26" s="55" t="n"/>
+      <c r="T26" s="55" t="n"/>
+      <c r="U26" s="55" t="n"/>
+      <c r="V26" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W26" s="57" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="53" t="n"/>
-      <c r="D27" s="53" t="n"/>
+      <c r="C27" s="46" t="n"/>
+      <c r="D27" s="46" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G27" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G27" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H27" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I27" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L27" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M27" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N27" s="55" t="inlineStr">
+      <c r="M27" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N27" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O27" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O27" s="55" t="n"/>
-      <c r="P27" s="55" t="n"/>
-      <c r="Q27" s="55" t="n"/>
-      <c r="R27" s="55" t="n"/>
-      <c r="S27" s="55" t="n"/>
-      <c r="T27" s="55" t="n"/>
-      <c r="U27" s="55" t="n"/>
-      <c r="V27" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W27" s="57" t="n"/>
+      <c r="P27" s="51" t="n"/>
+      <c r="Q27" s="51" t="n"/>
+      <c r="R27" s="51" t="n"/>
+      <c r="S27" s="51" t="n"/>
+      <c r="T27" s="51" t="n"/>
+      <c r="U27" s="51" t="n"/>
+      <c r="V27" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W27" s="58" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="46" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="53" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G28" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H28" s="49" t="n">
         <v>2</v>
@@ -3327,208 +3327,218 @@
         <v>2</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K28" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L28" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M28" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M28" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N28" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N28" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O28" s="51" t="n"/>
-      <c r="P28" s="51" t="n"/>
-      <c r="Q28" s="51" t="n"/>
-      <c r="R28" s="51" t="n"/>
-      <c r="S28" s="51" t="n"/>
-      <c r="T28" s="51" t="n"/>
-      <c r="U28" s="51" t="n"/>
-      <c r="V28" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W28" s="58" t="n"/>
+      <c r="O28" s="55" t="n"/>
+      <c r="P28" s="55" t="n"/>
+      <c r="Q28" s="55" t="n"/>
+      <c r="R28" s="55" t="n"/>
+      <c r="S28" s="55" t="n"/>
+      <c r="T28" s="55" t="n"/>
+      <c r="U28" s="55" t="n"/>
+      <c r="V28" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W28" s="57" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="53" t="n"/>
-      <c r="D29" s="53" t="n"/>
+      <c r="C29" s="46" t="n"/>
+      <c r="D29" s="46" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G29" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H29" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I29" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J29" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L29" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M29" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M29" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N29" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N29" s="55" t="n"/>
-      <c r="O29" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P29" s="55" t="n"/>
-      <c r="Q29" s="55" t="n"/>
-      <c r="R29" s="55" t="n"/>
-      <c r="S29" s="55" t="n"/>
-      <c r="T29" s="55" t="n"/>
-      <c r="U29" s="55" t="n"/>
-      <c r="V29" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W29" s="57" t="n"/>
+      <c r="O29" s="51" t="n"/>
+      <c r="P29" s="51" t="n"/>
+      <c r="Q29" s="51" t="n"/>
+      <c r="R29" s="51" t="n"/>
+      <c r="S29" s="51" t="n"/>
+      <c r="T29" s="51" t="n"/>
+      <c r="U29" s="51" t="n"/>
+      <c r="V29" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W29" s="58" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="46" t="n"/>
-      <c r="D30" s="46" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="53" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G30" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G30" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H30" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L30" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M30" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N30" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O30" s="51" t="n"/>
-      <c r="P30" s="51" t="n"/>
-      <c r="Q30" s="51" t="n"/>
-      <c r="R30" s="51" t="n"/>
-      <c r="S30" s="51" t="n"/>
-      <c r="T30" s="51" t="n"/>
-      <c r="U30" s="51" t="n"/>
-      <c r="V30" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W30" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M30" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N30" s="55" t="n"/>
+      <c r="O30" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P30" s="55" t="n"/>
+      <c r="Q30" s="55" t="n"/>
+      <c r="R30" s="55" t="n"/>
+      <c r="S30" s="55" t="n"/>
+      <c r="T30" s="55" t="n"/>
+      <c r="U30" s="55" t="n"/>
+      <c r="V30" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W30" s="57" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="53" t="n"/>
-      <c r="D31" s="53" t="n"/>
+      <c r="C31" s="46" t="n"/>
+      <c r="D31" s="46" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G31" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G31" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H31" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I31" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J31" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L31" s="50" t="n"/>
-      <c r="M31" s="55" t="n"/>
-      <c r="N31" s="55" t="n"/>
-      <c r="O31" s="55" t="n"/>
-      <c r="P31" s="55" t="n"/>
-      <c r="Q31" s="55" t="n"/>
-      <c r="R31" s="55" t="n"/>
-      <c r="S31" s="55" t="n"/>
-      <c r="T31" s="55" t="n"/>
-      <c r="U31" s="55" t="n"/>
-      <c r="V31" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W31" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L31" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M31" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N31" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O31" s="51" t="n"/>
+      <c r="P31" s="51" t="n"/>
+      <c r="Q31" s="51" t="n"/>
+      <c r="R31" s="51" t="n"/>
+      <c r="S31" s="51" t="n"/>
+      <c r="T31" s="51" t="n"/>
+      <c r="U31" s="51" t="n"/>
+      <c r="V31" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W31" s="58" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="46" t="n"/>
-      <c r="D32" s="46" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G32" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H32" s="49" t="n">
         <v>0</v>
@@ -3537,43 +3547,43 @@
         <v>0</v>
       </c>
       <c r="J32" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L32" s="50" t="n"/>
-      <c r="M32" s="51" t="n"/>
-      <c r="N32" s="51" t="n"/>
-      <c r="O32" s="51" t="n"/>
-      <c r="P32" s="51" t="n"/>
-      <c r="Q32" s="51" t="n"/>
-      <c r="R32" s="51" t="n"/>
-      <c r="S32" s="51" t="n"/>
-      <c r="T32" s="51" t="n"/>
-      <c r="U32" s="51" t="n"/>
-      <c r="V32" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W32" s="58" t="n"/>
+      <c r="M32" s="55" t="n"/>
+      <c r="N32" s="55" t="n"/>
+      <c r="O32" s="55" t="n"/>
+      <c r="P32" s="55" t="n"/>
+      <c r="Q32" s="55" t="n"/>
+      <c r="R32" s="55" t="n"/>
+      <c r="S32" s="55" t="n"/>
+      <c r="T32" s="55" t="n"/>
+      <c r="U32" s="55" t="n"/>
+      <c r="V32" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W32" s="57" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="53" t="n"/>
-      <c r="D33" s="53" t="n"/>
+      <c r="C33" s="46" t="n"/>
+      <c r="D33" s="46" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G33" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H33" s="49" t="n">
         <v>0</v>
@@ -3582,43 +3592,43 @@
         <v>0</v>
       </c>
       <c r="J33" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L33" s="50" t="n"/>
-      <c r="M33" s="55" t="n"/>
-      <c r="N33" s="55" t="n"/>
-      <c r="O33" s="55" t="n"/>
-      <c r="P33" s="55" t="n"/>
-      <c r="Q33" s="55" t="n"/>
-      <c r="R33" s="55" t="n"/>
-      <c r="S33" s="55" t="n"/>
-      <c r="T33" s="55" t="n"/>
-      <c r="U33" s="55" t="n"/>
-      <c r="V33" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W33" s="57" t="n"/>
+      <c r="M33" s="51" t="n"/>
+      <c r="N33" s="51" t="n"/>
+      <c r="O33" s="51" t="n"/>
+      <c r="P33" s="51" t="n"/>
+      <c r="Q33" s="51" t="n"/>
+      <c r="R33" s="51" t="n"/>
+      <c r="S33" s="51" t="n"/>
+      <c r="T33" s="51" t="n"/>
+      <c r="U33" s="51" t="n"/>
+      <c r="V33" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W33" s="58" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="46" t="n"/>
-      <c r="D34" s="46" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G34" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G34" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H34" s="49" t="n">
         <v>0</v>
@@ -3627,43 +3637,43 @@
         <v>0</v>
       </c>
       <c r="J34" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L34" s="50" t="n"/>
-      <c r="M34" s="51" t="n"/>
-      <c r="N34" s="51" t="n"/>
-      <c r="O34" s="51" t="n"/>
-      <c r="P34" s="51" t="n"/>
-      <c r="Q34" s="51" t="n"/>
-      <c r="R34" s="51" t="n"/>
-      <c r="S34" s="51" t="n"/>
-      <c r="T34" s="51" t="n"/>
-      <c r="U34" s="51" t="n"/>
-      <c r="V34" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W34" s="58" t="n"/>
+      <c r="M34" s="55" t="n"/>
+      <c r="N34" s="55" t="n"/>
+      <c r="O34" s="55" t="n"/>
+      <c r="P34" s="55" t="n"/>
+      <c r="Q34" s="55" t="n"/>
+      <c r="R34" s="55" t="n"/>
+      <c r="S34" s="55" t="n"/>
+      <c r="T34" s="55" t="n"/>
+      <c r="U34" s="55" t="n"/>
+      <c r="V34" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W34" s="57" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="53" t="n"/>
-      <c r="D35" s="53" t="n"/>
+      <c r="C35" s="46" t="n"/>
+      <c r="D35" s="46" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G35" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H35" s="49" t="n">
         <v>0</v>
@@ -3672,43 +3682,43 @@
         <v>0</v>
       </c>
       <c r="J35" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L35" s="50" t="n"/>
-      <c r="M35" s="55" t="n"/>
-      <c r="N35" s="55" t="n"/>
-      <c r="O35" s="55" t="n"/>
-      <c r="P35" s="55" t="n"/>
-      <c r="Q35" s="55" t="n"/>
-      <c r="R35" s="55" t="n"/>
-      <c r="S35" s="55" t="n"/>
-      <c r="T35" s="55" t="n"/>
-      <c r="U35" s="55" t="n"/>
-      <c r="V35" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W35" s="57" t="n"/>
+      <c r="M35" s="51" t="n"/>
+      <c r="N35" s="51" t="n"/>
+      <c r="O35" s="51" t="n"/>
+      <c r="P35" s="51" t="n"/>
+      <c r="Q35" s="51" t="n"/>
+      <c r="R35" s="51" t="n"/>
+      <c r="S35" s="51" t="n"/>
+      <c r="T35" s="51" t="n"/>
+      <c r="U35" s="51" t="n"/>
+      <c r="V35" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W35" s="58" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
+      <c r="C36" s="53" t="n"/>
+      <c r="D36" s="53" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G36" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H36" s="49" t="n">
         <v>0</v>
@@ -3717,1371 +3727,1375 @@
         <v>0</v>
       </c>
       <c r="J36" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="51" t="n"/>
-      <c r="N36" s="51" t="n"/>
-      <c r="O36" s="51" t="n"/>
-      <c r="P36" s="51" t="n"/>
-      <c r="Q36" s="51" t="n"/>
-      <c r="R36" s="51" t="n"/>
-      <c r="S36" s="51" t="n"/>
-      <c r="T36" s="51" t="n"/>
-      <c r="U36" s="51" t="n"/>
-      <c r="V36" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W36" s="58" t="n"/>
+      <c r="M36" s="55" t="n"/>
+      <c r="N36" s="55" t="n"/>
+      <c r="O36" s="55" t="n"/>
+      <c r="P36" s="55" t="n"/>
+      <c r="Q36" s="55" t="n"/>
+      <c r="R36" s="55" t="n"/>
+      <c r="S36" s="55" t="n"/>
+      <c r="T36" s="55" t="n"/>
+      <c r="U36" s="55" t="n"/>
+      <c r="V36" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W36" s="57" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="53" t="n"/>
-      <c r="D37" s="53" t="n"/>
+      <c r="C37" s="46" t="n"/>
+      <c r="D37" s="46" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G37" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H37" s="49" t="n"/>
-      <c r="I37" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G37" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H37" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J37" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="55" t="n"/>
-      <c r="N37" s="55" t="n"/>
-      <c r="O37" s="55" t="n"/>
-      <c r="P37" s="55" t="n"/>
-      <c r="Q37" s="55" t="n"/>
-      <c r="R37" s="55" t="n"/>
-      <c r="S37" s="55" t="n"/>
-      <c r="T37" s="55" t="n"/>
-      <c r="U37" s="55" t="n"/>
-      <c r="V37" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W37" s="57" t="n"/>
+      <c r="M37" s="51" t="n"/>
+      <c r="N37" s="51" t="n"/>
+      <c r="O37" s="51" t="n"/>
+      <c r="P37" s="51" t="n"/>
+      <c r="Q37" s="51" t="n"/>
+      <c r="R37" s="51" t="n"/>
+      <c r="S37" s="51" t="n"/>
+      <c r="T37" s="51" t="n"/>
+      <c r="U37" s="51" t="n"/>
+      <c r="V37" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W37" s="58" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="46" t="n"/>
-      <c r="D38" s="46" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G38" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H38" s="49" t="n"/>
       <c r="I38" s="49" t="n"/>
       <c r="J38" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="51" t="n"/>
-      <c r="N38" s="51" t="n"/>
-      <c r="O38" s="51" t="n"/>
-      <c r="P38" s="51" t="n"/>
-      <c r="Q38" s="51" t="n"/>
-      <c r="R38" s="51" t="n"/>
-      <c r="S38" s="51" t="n"/>
-      <c r="T38" s="51" t="n"/>
-      <c r="U38" s="51" t="n"/>
-      <c r="V38" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W38" s="58" t="n"/>
+      <c r="M38" s="55" t="n"/>
+      <c r="N38" s="55" t="n"/>
+      <c r="O38" s="55" t="n"/>
+      <c r="P38" s="55" t="n"/>
+      <c r="Q38" s="55" t="n"/>
+      <c r="R38" s="55" t="n"/>
+      <c r="S38" s="55" t="n"/>
+      <c r="T38" s="55" t="n"/>
+      <c r="U38" s="55" t="n"/>
+      <c r="V38" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W38" s="57" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="53" t="n"/>
-      <c r="D39" s="53" t="n"/>
+      <c r="C39" s="46" t="n"/>
+      <c r="D39" s="46" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G39" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H39" s="49" t="n"/>
       <c r="I39" s="49" t="n"/>
       <c r="J39" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="55" t="n"/>
-      <c r="N39" s="55" t="n"/>
-      <c r="O39" s="55" t="n"/>
-      <c r="P39" s="55" t="n"/>
-      <c r="Q39" s="55" t="n"/>
-      <c r="R39" s="55" t="n"/>
-      <c r="S39" s="55" t="n"/>
-      <c r="T39" s="55" t="n"/>
-      <c r="U39" s="55" t="n"/>
-      <c r="V39" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W39" s="57" t="n"/>
+      <c r="M39" s="51" t="n"/>
+      <c r="N39" s="51" t="n"/>
+      <c r="O39" s="51" t="n"/>
+      <c r="P39" s="51" t="n"/>
+      <c r="Q39" s="51" t="n"/>
+      <c r="R39" s="51" t="n"/>
+      <c r="S39" s="51" t="n"/>
+      <c r="T39" s="51" t="n"/>
+      <c r="U39" s="51" t="n"/>
+      <c r="V39" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W39" s="58" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="46" t="n"/>
-      <c r="D40" s="46" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G40" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H40" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I40" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H40" s="49" t="n"/>
+      <c r="I40" s="49" t="n"/>
       <c r="J40" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="51" t="n"/>
-      <c r="N40" s="51" t="n"/>
-      <c r="O40" s="51" t="n"/>
-      <c r="P40" s="51" t="n"/>
-      <c r="Q40" s="51" t="n"/>
-      <c r="R40" s="51" t="n"/>
-      <c r="S40" s="51" t="n"/>
-      <c r="T40" s="51" t="n"/>
-      <c r="U40" s="51" t="n"/>
-      <c r="V40" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W40" s="58" t="n"/>
+      <c r="M40" s="55" t="n"/>
+      <c r="N40" s="55" t="n"/>
+      <c r="O40" s="55" t="n"/>
+      <c r="P40" s="55" t="n"/>
+      <c r="Q40" s="55" t="n"/>
+      <c r="R40" s="55" t="n"/>
+      <c r="S40" s="55" t="n"/>
+      <c r="T40" s="55" t="n"/>
+      <c r="U40" s="55" t="n"/>
+      <c r="V40" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W40" s="57" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="53" t="n"/>
-      <c r="D41" s="53" t="n"/>
+      <c r="C41" s="46" t="n"/>
+      <c r="D41" s="46" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G41" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H41" s="49" t="n"/>
-      <c r="I41" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G41" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H41" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I41" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J41" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="55" t="n"/>
-      <c r="N41" s="55" t="n"/>
-      <c r="O41" s="55" t="n"/>
-      <c r="P41" s="55" t="n"/>
-      <c r="Q41" s="55" t="n"/>
-      <c r="R41" s="55" t="n"/>
-      <c r="S41" s="55" t="n"/>
-      <c r="T41" s="55" t="n"/>
-      <c r="U41" s="55" t="n"/>
-      <c r="V41" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W41" s="57" t="n"/>
+      <c r="M41" s="51" t="n"/>
+      <c r="N41" s="51" t="n"/>
+      <c r="O41" s="51" t="n"/>
+      <c r="P41" s="51" t="n"/>
+      <c r="Q41" s="51" t="n"/>
+      <c r="R41" s="51" t="n"/>
+      <c r="S41" s="51" t="n"/>
+      <c r="T41" s="51" t="n"/>
+      <c r="U41" s="51" t="n"/>
+      <c r="V41" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W41" s="58" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="46" t="n"/>
-      <c r="D42" s="46" t="n"/>
+      <c r="C42" s="53" t="n"/>
+      <c r="D42" s="53" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G42" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G42" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H42" s="49" t="n"/>
       <c r="I42" s="49" t="n"/>
       <c r="J42" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K42" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="51" t="n"/>
-      <c r="N42" s="51" t="n"/>
-      <c r="O42" s="51" t="n"/>
-      <c r="P42" s="51" t="n"/>
-      <c r="Q42" s="51" t="n"/>
-      <c r="R42" s="51" t="n"/>
-      <c r="S42" s="51" t="n"/>
-      <c r="T42" s="51" t="n"/>
-      <c r="U42" s="51" t="n"/>
-      <c r="V42" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W42" s="58" t="n"/>
+      <c r="M42" s="55" t="n"/>
+      <c r="N42" s="55" t="n"/>
+      <c r="O42" s="55" t="n"/>
+      <c r="P42" s="55" t="n"/>
+      <c r="Q42" s="55" t="n"/>
+      <c r="R42" s="55" t="n"/>
+      <c r="S42" s="55" t="n"/>
+      <c r="T42" s="55" t="n"/>
+      <c r="U42" s="55" t="n"/>
+      <c r="V42" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W42" s="57" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="53" t="n"/>
-      <c r="D43" s="53" t="n"/>
+      <c r="C43" s="46" t="n"/>
+      <c r="D43" s="46" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G43" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G43" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H43" s="49" t="n"/>
       <c r="I43" s="49" t="n"/>
       <c r="J43" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K43" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K43" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="55" t="n"/>
-      <c r="N43" s="55" t="n"/>
-      <c r="O43" s="55" t="n"/>
-      <c r="P43" s="55" t="n"/>
-      <c r="Q43" s="55" t="n"/>
-      <c r="R43" s="55" t="n"/>
-      <c r="S43" s="55" t="n"/>
-      <c r="T43" s="55" t="n"/>
-      <c r="U43" s="55" t="n"/>
-      <c r="V43" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W43" s="57" t="n"/>
+      <c r="M43" s="51" t="n"/>
+      <c r="N43" s="51" t="n"/>
+      <c r="O43" s="51" t="n"/>
+      <c r="P43" s="51" t="n"/>
+      <c r="Q43" s="51" t="n"/>
+      <c r="R43" s="51" t="n"/>
+      <c r="S43" s="51" t="n"/>
+      <c r="T43" s="51" t="n"/>
+      <c r="U43" s="51" t="n"/>
+      <c r="V43" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W43" s="58" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="46" t="n"/>
-      <c r="D44" s="46" t="n"/>
+      <c r="C44" s="53" t="n"/>
+      <c r="D44" s="53" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G44" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H44" s="49" t="n"/>
       <c r="I44" s="49" t="n"/>
       <c r="J44" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K44" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="51" t="n"/>
-      <c r="N44" s="51" t="n"/>
-      <c r="O44" s="51" t="n"/>
-      <c r="P44" s="51" t="n"/>
-      <c r="Q44" s="51" t="n"/>
-      <c r="R44" s="51" t="n"/>
-      <c r="S44" s="51" t="n"/>
-      <c r="T44" s="51" t="n"/>
-      <c r="U44" s="51" t="n"/>
-      <c r="V44" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W44" s="58" t="n"/>
+      <c r="M44" s="55" t="n"/>
+      <c r="N44" s="55" t="n"/>
+      <c r="O44" s="55" t="n"/>
+      <c r="P44" s="55" t="n"/>
+      <c r="Q44" s="55" t="n"/>
+      <c r="R44" s="55" t="n"/>
+      <c r="S44" s="55" t="n"/>
+      <c r="T44" s="55" t="n"/>
+      <c r="U44" s="55" t="n"/>
+      <c r="V44" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W44" s="57" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="53" t="n"/>
-      <c r="D45" s="53" t="n"/>
+      <c r="C45" s="46" t="n"/>
+      <c r="D45" s="46" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G45" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G45" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H45" s="49" t="n"/>
       <c r="I45" s="49" t="n"/>
       <c r="J45" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K45" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="55" t="n"/>
-      <c r="N45" s="55" t="n"/>
-      <c r="O45" s="55" t="n"/>
-      <c r="P45" s="55" t="n"/>
-      <c r="Q45" s="55" t="n"/>
-      <c r="R45" s="55" t="n"/>
-      <c r="S45" s="55" t="n"/>
-      <c r="T45" s="55" t="n"/>
-      <c r="U45" s="55" t="n"/>
-      <c r="V45" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W45" s="57" t="n"/>
+      <c r="M45" s="51" t="n"/>
+      <c r="N45" s="51" t="n"/>
+      <c r="O45" s="51" t="n"/>
+      <c r="P45" s="51" t="n"/>
+      <c r="Q45" s="51" t="n"/>
+      <c r="R45" s="51" t="n"/>
+      <c r="S45" s="51" t="n"/>
+      <c r="T45" s="51" t="n"/>
+      <c r="U45" s="51" t="n"/>
+      <c r="V45" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W45" s="58" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="46" t="n"/>
-      <c r="D46" s="46" t="n"/>
+      <c r="C46" s="53" t="n"/>
+      <c r="D46" s="53" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G46" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H46" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I46" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G46" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H46" s="49" t="n"/>
+      <c r="I46" s="49" t="n"/>
       <c r="J46" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K46" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="51" t="n"/>
-      <c r="N46" s="51" t="n"/>
-      <c r="O46" s="51" t="n"/>
-      <c r="P46" s="51" t="n"/>
-      <c r="Q46" s="51" t="n"/>
-      <c r="R46" s="51" t="n"/>
-      <c r="S46" s="51" t="n"/>
-      <c r="T46" s="51" t="n"/>
-      <c r="U46" s="51" t="n"/>
-      <c r="V46" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W46" s="58" t="n"/>
+      <c r="M46" s="55" t="n"/>
+      <c r="N46" s="55" t="n"/>
+      <c r="O46" s="55" t="n"/>
+      <c r="P46" s="55" t="n"/>
+      <c r="Q46" s="55" t="n"/>
+      <c r="R46" s="55" t="n"/>
+      <c r="S46" s="55" t="n"/>
+      <c r="T46" s="55" t="n"/>
+      <c r="U46" s="55" t="n"/>
+      <c r="V46" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W46" s="57" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="53" t="n"/>
-      <c r="D47" s="53" t="n"/>
+      <c r="C47" s="46" t="n"/>
+      <c r="D47" s="46" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G47" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H47" s="49" t="n"/>
-      <c r="I47" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H47" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I47" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J47" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K47" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="55" t="n"/>
-      <c r="N47" s="55" t="n"/>
-      <c r="O47" s="55" t="n"/>
-      <c r="P47" s="55" t="n"/>
-      <c r="Q47" s="55" t="n"/>
-      <c r="R47" s="55" t="n"/>
-      <c r="S47" s="55" t="n"/>
-      <c r="T47" s="55" t="n"/>
-      <c r="U47" s="55" t="n"/>
-      <c r="V47" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W47" s="57" t="n"/>
+      <c r="M47" s="51" t="n"/>
+      <c r="N47" s="51" t="n"/>
+      <c r="O47" s="51" t="n"/>
+      <c r="P47" s="51" t="n"/>
+      <c r="Q47" s="51" t="n"/>
+      <c r="R47" s="51" t="n"/>
+      <c r="S47" s="51" t="n"/>
+      <c r="T47" s="51" t="n"/>
+      <c r="U47" s="51" t="n"/>
+      <c r="V47" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W47" s="58" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
+      <c r="C48" s="53" t="n"/>
+      <c r="D48" s="53" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G48" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H48" s="49" t="n"/>
       <c r="I48" s="49" t="n"/>
       <c r="J48" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K48" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="51" t="n"/>
-      <c r="N48" s="51" t="n"/>
-      <c r="O48" s="51" t="n"/>
-      <c r="P48" s="51" t="n"/>
-      <c r="Q48" s="51" t="n"/>
-      <c r="R48" s="51" t="n"/>
-      <c r="S48" s="51" t="n"/>
-      <c r="T48" s="51" t="n"/>
-      <c r="U48" s="51" t="n"/>
-      <c r="V48" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W48" s="58" t="n"/>
+      <c r="M48" s="55" t="n"/>
+      <c r="N48" s="55" t="n"/>
+      <c r="O48" s="55" t="n"/>
+      <c r="P48" s="55" t="n"/>
+      <c r="Q48" s="55" t="n"/>
+      <c r="R48" s="55" t="n"/>
+      <c r="S48" s="55" t="n"/>
+      <c r="T48" s="55" t="n"/>
+      <c r="U48" s="55" t="n"/>
+      <c r="V48" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W48" s="57" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="53" t="n"/>
-      <c r="D49" s="53" t="n"/>
+      <c r="C49" s="46" t="n"/>
+      <c r="D49" s="46" t="n"/>
       <c r="E49" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F49" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G49" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H49" s="49" t="n"/>
+      <c r="I49" s="49" t="n"/>
+      <c r="J49" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F49" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G49" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H49" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I49" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J49" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K49" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="55" t="n"/>
-      <c r="N49" s="55" t="n"/>
-      <c r="O49" s="55" t="n"/>
-      <c r="P49" s="55" t="n"/>
-      <c r="Q49" s="55" t="n"/>
-      <c r="R49" s="55" t="n"/>
-      <c r="S49" s="55" t="n"/>
-      <c r="T49" s="55" t="n"/>
-      <c r="U49" s="55" t="n"/>
-      <c r="V49" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W49" s="57" t="n"/>
+      <c r="M49" s="51" t="n"/>
+      <c r="N49" s="51" t="n"/>
+      <c r="O49" s="51" t="n"/>
+      <c r="P49" s="51" t="n"/>
+      <c r="Q49" s="51" t="n"/>
+      <c r="R49" s="51" t="n"/>
+      <c r="S49" s="51" t="n"/>
+      <c r="T49" s="51" t="n"/>
+      <c r="U49" s="51" t="n"/>
+      <c r="V49" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W49" s="58" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
+      <c r="C50" s="53" t="n"/>
+      <c r="D50" s="53" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G50" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H50" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I50" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J50" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="51" t="n"/>
-      <c r="N50" s="51" t="n"/>
-      <c r="O50" s="51" t="n"/>
-      <c r="P50" s="51" t="n"/>
-      <c r="Q50" s="51" t="n"/>
-      <c r="R50" s="51" t="n"/>
-      <c r="S50" s="51" t="n"/>
-      <c r="T50" s="51" t="n"/>
-      <c r="U50" s="51" t="n"/>
-      <c r="V50" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W50" s="58" t="n"/>
+      <c r="M50" s="55" t="n"/>
+      <c r="N50" s="55" t="n"/>
+      <c r="O50" s="55" t="n"/>
+      <c r="P50" s="55" t="n"/>
+      <c r="Q50" s="55" t="n"/>
+      <c r="R50" s="55" t="n"/>
+      <c r="S50" s="55" t="n"/>
+      <c r="T50" s="55" t="n"/>
+      <c r="U50" s="55" t="n"/>
+      <c r="V50" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W50" s="57" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="53" t="n"/>
-      <c r="D51" s="53" t="n"/>
+      <c r="C51" s="46" t="n"/>
+      <c r="D51" s="46" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G51" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H51" s="49" t="n"/>
-      <c r="I51" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H51" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I51" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J51" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="55" t="n"/>
-      <c r="N51" s="55" t="n"/>
-      <c r="O51" s="55" t="n"/>
-      <c r="P51" s="55" t="n"/>
-      <c r="Q51" s="55" t="n"/>
-      <c r="R51" s="55" t="n"/>
-      <c r="S51" s="55" t="n"/>
-      <c r="T51" s="55" t="n"/>
-      <c r="U51" s="55" t="n"/>
-      <c r="V51" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W51" s="57" t="n"/>
+      <c r="M51" s="51" t="n"/>
+      <c r="N51" s="51" t="n"/>
+      <c r="O51" s="51" t="n"/>
+      <c r="P51" s="51" t="n"/>
+      <c r="Q51" s="51" t="n"/>
+      <c r="R51" s="51" t="n"/>
+      <c r="S51" s="51" t="n"/>
+      <c r="T51" s="51" t="n"/>
+      <c r="U51" s="51" t="n"/>
+      <c r="V51" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W51" s="58" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="46" t="n"/>
-      <c r="D52" s="46" t="n"/>
+      <c r="C52" s="53" t="n"/>
+      <c r="D52" s="53" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G52" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G52" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H52" s="49" t="n"/>
       <c r="I52" s="49" t="n"/>
       <c r="J52" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K52" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="51" t="n"/>
-      <c r="N52" s="51" t="n"/>
-      <c r="O52" s="51" t="n"/>
-      <c r="P52" s="51" t="n"/>
-      <c r="Q52" s="51" t="n"/>
-      <c r="R52" s="51" t="n"/>
-      <c r="S52" s="51" t="n"/>
-      <c r="T52" s="51" t="n"/>
-      <c r="U52" s="51" t="n"/>
-      <c r="V52" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W52" s="58" t="n"/>
+      <c r="M52" s="55" t="n"/>
+      <c r="N52" s="55" t="n"/>
+      <c r="O52" s="55" t="n"/>
+      <c r="P52" s="55" t="n"/>
+      <c r="Q52" s="55" t="n"/>
+      <c r="R52" s="55" t="n"/>
+      <c r="S52" s="55" t="n"/>
+      <c r="T52" s="55" t="n"/>
+      <c r="U52" s="55" t="n"/>
+      <c r="V52" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W52" s="57" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="53" t="n"/>
-      <c r="D53" s="53" t="n"/>
+      <c r="C53" s="46" t="n"/>
+      <c r="D53" s="46" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G53" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G53" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H53" s="49" t="n"/>
       <c r="I53" s="49" t="n"/>
       <c r="J53" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="55" t="n"/>
-      <c r="N53" s="55" t="n"/>
-      <c r="O53" s="55" t="n"/>
-      <c r="P53" s="55" t="n"/>
-      <c r="Q53" s="55" t="n"/>
-      <c r="R53" s="55" t="n"/>
-      <c r="S53" s="55" t="n"/>
-      <c r="T53" s="55" t="n"/>
-      <c r="U53" s="55" t="n"/>
-      <c r="V53" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W53" s="57" t="n"/>
+      <c r="M53" s="51" t="n"/>
+      <c r="N53" s="51" t="n"/>
+      <c r="O53" s="51" t="n"/>
+      <c r="P53" s="51" t="n"/>
+      <c r="Q53" s="51" t="n"/>
+      <c r="R53" s="51" t="n"/>
+      <c r="S53" s="51" t="n"/>
+      <c r="T53" s="51" t="n"/>
+      <c r="U53" s="51" t="n"/>
+      <c r="V53" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W53" s="58" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="46" t="n"/>
-      <c r="D54" s="46" t="n"/>
+      <c r="C54" s="53" t="n"/>
+      <c r="D54" s="53" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G54" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="51" t="n"/>
-      <c r="N54" s="51" t="n"/>
-      <c r="O54" s="51" t="n"/>
-      <c r="P54" s="51" t="n"/>
-      <c r="Q54" s="51" t="n"/>
-      <c r="R54" s="51" t="n"/>
-      <c r="S54" s="51" t="n"/>
-      <c r="T54" s="51" t="n"/>
-      <c r="U54" s="51" t="n"/>
-      <c r="V54" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W54" s="58" t="n"/>
+      <c r="M54" s="55" t="n"/>
+      <c r="N54" s="55" t="n"/>
+      <c r="O54" s="55" t="n"/>
+      <c r="P54" s="55" t="n"/>
+      <c r="Q54" s="55" t="n"/>
+      <c r="R54" s="55" t="n"/>
+      <c r="S54" s="55" t="n"/>
+      <c r="T54" s="55" t="n"/>
+      <c r="U54" s="55" t="n"/>
+      <c r="V54" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W54" s="57" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="53" t="n"/>
-      <c r="D55" s="53" t="n"/>
+      <c r="C55" s="46" t="n"/>
+      <c r="D55" s="46" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G55" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G55" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="55" t="n"/>
-      <c r="N55" s="55" t="n"/>
-      <c r="O55" s="55" t="n"/>
-      <c r="P55" s="55" t="n"/>
-      <c r="Q55" s="55" t="n"/>
-      <c r="R55" s="55" t="n"/>
-      <c r="S55" s="55" t="n"/>
-      <c r="T55" s="55" t="n"/>
-      <c r="U55" s="55" t="n"/>
-      <c r="V55" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W55" s="57" t="n"/>
+      <c r="M55" s="51" t="n"/>
+      <c r="N55" s="51" t="n"/>
+      <c r="O55" s="51" t="n"/>
+      <c r="P55" s="51" t="n"/>
+      <c r="Q55" s="51" t="n"/>
+      <c r="R55" s="51" t="n"/>
+      <c r="S55" s="51" t="n"/>
+      <c r="T55" s="51" t="n"/>
+      <c r="U55" s="51" t="n"/>
+      <c r="V55" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W55" s="58" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="46" t="n"/>
-      <c r="D56" s="46" t="n"/>
+      <c r="C56" s="53" t="n"/>
+      <c r="D56" s="53" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G56" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G56" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="51" t="n"/>
-      <c r="N56" s="51" t="n"/>
-      <c r="O56" s="51" t="n"/>
-      <c r="P56" s="51" t="n"/>
-      <c r="Q56" s="51" t="n"/>
-      <c r="R56" s="51" t="n"/>
-      <c r="S56" s="51" t="n"/>
-      <c r="T56" s="51" t="n"/>
-      <c r="U56" s="51" t="n"/>
-      <c r="V56" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W56" s="58" t="n"/>
+      <c r="M56" s="55" t="n"/>
+      <c r="N56" s="55" t="n"/>
+      <c r="O56" s="55" t="n"/>
+      <c r="P56" s="55" t="n"/>
+      <c r="Q56" s="55" t="n"/>
+      <c r="R56" s="55" t="n"/>
+      <c r="S56" s="55" t="n"/>
+      <c r="T56" s="55" t="n"/>
+      <c r="U56" s="55" t="n"/>
+      <c r="V56" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W56" s="57" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="53" t="n"/>
-      <c r="D57" s="53" t="n"/>
+      <c r="C57" s="46" t="n"/>
+      <c r="D57" s="46" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G57" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G57" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="55" t="n"/>
-      <c r="N57" s="55" t="n"/>
-      <c r="O57" s="55" t="n"/>
-      <c r="P57" s="55" t="n"/>
-      <c r="Q57" s="55" t="n"/>
-      <c r="R57" s="55" t="n"/>
-      <c r="S57" s="55" t="n"/>
-      <c r="T57" s="55" t="n"/>
-      <c r="U57" s="55" t="n"/>
-      <c r="V57" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W57" s="57" t="n"/>
+      <c r="M57" s="51" t="n"/>
+      <c r="N57" s="51" t="n"/>
+      <c r="O57" s="51" t="n"/>
+      <c r="P57" s="51" t="n"/>
+      <c r="Q57" s="51" t="n"/>
+      <c r="R57" s="51" t="n"/>
+      <c r="S57" s="51" t="n"/>
+      <c r="T57" s="51" t="n"/>
+      <c r="U57" s="51" t="n"/>
+      <c r="V57" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W57" s="58" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="46" t="n"/>
-      <c r="D58" s="46" t="n"/>
+      <c r="C58" s="53" t="n"/>
+      <c r="D58" s="53" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G58" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="51" t="n"/>
-      <c r="N58" s="51" t="n"/>
-      <c r="O58" s="51" t="n"/>
-      <c r="P58" s="51" t="n"/>
-      <c r="Q58" s="51" t="n"/>
-      <c r="R58" s="51" t="n"/>
-      <c r="S58" s="51" t="n"/>
-      <c r="T58" s="51" t="n"/>
-      <c r="U58" s="51" t="n"/>
-      <c r="V58" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W58" s="58" t="n"/>
+      <c r="M58" s="55" t="n"/>
+      <c r="N58" s="55" t="n"/>
+      <c r="O58" s="55" t="n"/>
+      <c r="P58" s="55" t="n"/>
+      <c r="Q58" s="55" t="n"/>
+      <c r="R58" s="55" t="n"/>
+      <c r="S58" s="55" t="n"/>
+      <c r="T58" s="55" t="n"/>
+      <c r="U58" s="55" t="n"/>
+      <c r="V58" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W58" s="57" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="53" t="n"/>
-      <c r="D59" s="53" t="n"/>
+      <c r="C59" s="46" t="n"/>
+      <c r="D59" s="46" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G59" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="55" t="n"/>
-      <c r="N59" s="55" t="n"/>
-      <c r="O59" s="55" t="n"/>
-      <c r="P59" s="55" t="n"/>
-      <c r="Q59" s="55" t="n"/>
-      <c r="R59" s="55" t="n"/>
-      <c r="S59" s="55" t="n"/>
-      <c r="T59" s="55" t="n"/>
-      <c r="U59" s="55" t="n"/>
-      <c r="V59" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W59" s="57" t="n"/>
+      <c r="M59" s="51" t="n"/>
+      <c r="N59" s="51" t="n"/>
+      <c r="O59" s="51" t="n"/>
+      <c r="P59" s="51" t="n"/>
+      <c r="Q59" s="51" t="n"/>
+      <c r="R59" s="51" t="n"/>
+      <c r="S59" s="51" t="n"/>
+      <c r="T59" s="51" t="n"/>
+      <c r="U59" s="51" t="n"/>
+      <c r="V59" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W59" s="58" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
+      <c r="C60" s="53" t="n"/>
+      <c r="D60" s="53" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G60" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G60" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="51" t="n"/>
-      <c r="N60" s="51" t="n"/>
-      <c r="O60" s="51" t="n"/>
-      <c r="P60" s="51" t="n"/>
-      <c r="Q60" s="51" t="n"/>
-      <c r="R60" s="51" t="n"/>
-      <c r="S60" s="51" t="n"/>
-      <c r="T60" s="51" t="n"/>
-      <c r="U60" s="51" t="n"/>
-      <c r="V60" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W60" s="58" t="n"/>
+      <c r="M60" s="55" t="n"/>
+      <c r="N60" s="55" t="n"/>
+      <c r="O60" s="55" t="n"/>
+      <c r="P60" s="55" t="n"/>
+      <c r="Q60" s="55" t="n"/>
+      <c r="R60" s="55" t="n"/>
+      <c r="S60" s="55" t="n"/>
+      <c r="T60" s="55" t="n"/>
+      <c r="U60" s="55" t="n"/>
+      <c r="V60" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W60" s="57" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="53" t="n"/>
-      <c r="D61" s="53" t="n"/>
+      <c r="C61" s="46" t="n"/>
+      <c r="D61" s="46" t="n"/>
       <c r="E61" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F61" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G61" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G61" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
       <c r="J61" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K61" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="55" t="n"/>
-      <c r="N61" s="55" t="n"/>
-      <c r="O61" s="55" t="n"/>
-      <c r="P61" s="55" t="n"/>
-      <c r="Q61" s="55" t="n"/>
-      <c r="R61" s="55" t="n"/>
-      <c r="S61" s="55" t="n"/>
-      <c r="T61" s="55" t="n"/>
-      <c r="U61" s="55" t="n"/>
-      <c r="V61" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W61" s="57" t="n"/>
+      <c r="M61" s="51" t="n"/>
+      <c r="N61" s="51" t="n"/>
+      <c r="O61" s="51" t="n"/>
+      <c r="P61" s="51" t="n"/>
+      <c r="Q61" s="51" t="n"/>
+      <c r="R61" s="51" t="n"/>
+      <c r="S61" s="51" t="n"/>
+      <c r="T61" s="51" t="n"/>
+      <c r="U61" s="51" t="n"/>
+      <c r="V61" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W61" s="58" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B62" s="45" t="n"/>
-      <c r="C62" s="46" t="n"/>
-      <c r="D62" s="46" t="n"/>
+      <c r="C62" s="53" t="n"/>
+      <c r="D62" s="53" t="n"/>
       <c r="E62" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F62" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G62" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G62" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="49" t="n"/>
       <c r="J62" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K62" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L62" s="50" t="n"/>
-      <c r="M62" s="51" t="n"/>
-      <c r="N62" s="51" t="n"/>
-      <c r="O62" s="51" t="n"/>
-      <c r="P62" s="51" t="n"/>
-      <c r="Q62" s="51" t="n"/>
-      <c r="R62" s="51" t="n"/>
-      <c r="S62" s="51" t="n"/>
-      <c r="T62" s="51" t="n"/>
-      <c r="U62" s="51" t="n"/>
-      <c r="V62" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W62" s="58" t="n"/>
+      <c r="M62" s="55" t="n"/>
+      <c r="N62" s="55" t="n"/>
+      <c r="O62" s="55" t="n"/>
+      <c r="P62" s="55" t="n"/>
+      <c r="Q62" s="55" t="n"/>
+      <c r="R62" s="55" t="n"/>
+      <c r="S62" s="55" t="n"/>
+      <c r="T62" s="55" t="n"/>
+      <c r="U62" s="55" t="n"/>
+      <c r="V62" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W62" s="57" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B63" s="45" t="n"/>
-      <c r="C63" s="53" t="n"/>
-      <c r="D63" s="53" t="n"/>
+      <c r="C63" s="46" t="n"/>
+      <c r="D63" s="46" t="n"/>
       <c r="E63" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F63" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G63" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G63" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="49" t="n"/>
       <c r="J63" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K63" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L63" s="50" t="n"/>
-      <c r="M63" s="55" t="n"/>
-      <c r="N63" s="55" t="n"/>
-      <c r="O63" s="55" t="n"/>
-      <c r="P63" s="55" t="n"/>
-      <c r="Q63" s="55" t="n"/>
-      <c r="R63" s="55" t="n"/>
-      <c r="S63" s="55" t="n"/>
-      <c r="T63" s="55" t="n"/>
-      <c r="U63" s="55" t="n"/>
-      <c r="V63" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W63" s="57" t="n"/>
+      <c r="M63" s="51" t="n"/>
+      <c r="N63" s="51" t="n"/>
+      <c r="O63" s="51" t="n"/>
+      <c r="P63" s="51" t="n"/>
+      <c r="Q63" s="51" t="n"/>
+      <c r="R63" s="51" t="n"/>
+      <c r="S63" s="51" t="n"/>
+      <c r="T63" s="51" t="n"/>
+      <c r="U63" s="51" t="n"/>
+      <c r="V63" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W63" s="58" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B64" s="45" t="n"/>
-      <c r="C64" s="46" t="n"/>
-      <c r="D64" s="46" t="n"/>
+      <c r="C64" s="53" t="n"/>
+      <c r="D64" s="53" t="n"/>
       <c r="E64" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F64" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G64" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G64" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="49" t="n"/>
       <c r="J64" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K64" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L64" s="50" t="n"/>
-      <c r="M64" s="51" t="n"/>
-      <c r="N64" s="51" t="n"/>
-      <c r="O64" s="51" t="n"/>
-      <c r="P64" s="51" t="n"/>
-      <c r="Q64" s="51" t="n"/>
-      <c r="R64" s="51" t="n"/>
-      <c r="S64" s="51" t="n"/>
-      <c r="T64" s="51" t="n"/>
-      <c r="U64" s="51" t="n"/>
-      <c r="V64" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W64" s="58" t="n"/>
+      <c r="M64" s="55" t="n"/>
+      <c r="N64" s="55" t="n"/>
+      <c r="O64" s="55" t="n"/>
+      <c r="P64" s="55" t="n"/>
+      <c r="Q64" s="55" t="n"/>
+      <c r="R64" s="55" t="n"/>
+      <c r="S64" s="55" t="n"/>
+      <c r="T64" s="55" t="n"/>
+      <c r="U64" s="55" t="n"/>
+      <c r="V64" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W64" s="57" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B65" s="45" t="n"/>
-      <c r="C65" s="53" t="n"/>
-      <c r="D65" s="53" t="n"/>
+      <c r="C65" s="46" t="n"/>
+      <c r="D65" s="46" t="n"/>
       <c r="E65" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F65" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G65" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G65" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H65" s="49" t="n"/>
       <c r="I65" s="49" t="n"/>
       <c r="J65" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K65" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L65" s="50" t="n"/>
-      <c r="M65" s="55" t="n"/>
-      <c r="N65" s="55" t="n"/>
-      <c r="O65" s="55" t="n"/>
-      <c r="P65" s="55" t="n"/>
-      <c r="Q65" s="55" t="n"/>
-      <c r="R65" s="55" t="n"/>
-      <c r="S65" s="55" t="n"/>
-      <c r="T65" s="55" t="n"/>
-      <c r="U65" s="55" t="n"/>
-      <c r="V65" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W65" s="57" t="n"/>
+      <c r="M65" s="51" t="n"/>
+      <c r="N65" s="51" t="n"/>
+      <c r="O65" s="51" t="n"/>
+      <c r="P65" s="51" t="n"/>
+      <c r="Q65" s="51" t="n"/>
+      <c r="R65" s="51" t="n"/>
+      <c r="S65" s="51" t="n"/>
+      <c r="T65" s="51" t="n"/>
+      <c r="U65" s="51" t="n"/>
+      <c r="V65" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W65" s="58" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B66" s="45" t="n"/>
-      <c r="C66" s="46" t="n"/>
-      <c r="D66" s="46" t="n"/>
+      <c r="C66" s="53" t="n"/>
+      <c r="D66" s="53" t="n"/>
       <c r="E66" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F66" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G66" s="48" t="n">
-        <v>24</v>
+      <c r="G66" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H66" s="49" t="n"/>
       <c r="I66" s="49" t="n"/>
       <c r="J66" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K66" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L66" s="50" t="n"/>
-      <c r="M66" s="51" t="n"/>
-      <c r="N66" s="51" t="n"/>
-      <c r="O66" s="51" t="n"/>
-      <c r="P66" s="51" t="n"/>
-      <c r="Q66" s="51" t="n"/>
-      <c r="R66" s="51" t="n"/>
-      <c r="S66" s="51" t="n"/>
-      <c r="T66" s="51" t="n"/>
-      <c r="U66" s="51" t="n"/>
-      <c r="V66" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W66" s="58" t="n"/>
+      <c r="M66" s="55" t="n"/>
+      <c r="N66" s="55" t="n"/>
+      <c r="O66" s="55" t="n"/>
+      <c r="P66" s="55" t="n"/>
+      <c r="Q66" s="55" t="n"/>
+      <c r="R66" s="55" t="n"/>
+      <c r="S66" s="55" t="n"/>
+      <c r="T66" s="55" t="n"/>
+      <c r="U66" s="55" t="n"/>
+      <c r="V66" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W66" s="57" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B67" s="45" t="n"/>
-      <c r="C67" s="53" t="n"/>
-      <c r="D67" s="53" t="n"/>
+      <c r="C67" s="46" t="n"/>
+      <c r="D67" s="46" t="n"/>
       <c r="E67" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F67" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G67" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G67" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H67" s="49" t="n"/>
       <c r="I67" s="49" t="n"/>
       <c r="J67" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K67" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L67" s="50" t="n"/>
-      <c r="M67" s="55" t="n"/>
-      <c r="N67" s="55" t="n"/>
-      <c r="O67" s="55" t="n"/>
-      <c r="P67" s="55" t="n"/>
-      <c r="Q67" s="55" t="n"/>
-      <c r="R67" s="55" t="n"/>
-      <c r="S67" s="55" t="n"/>
-      <c r="T67" s="55" t="n"/>
-      <c r="U67" s="55" t="n"/>
-      <c r="V67" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W67" s="57" t="n"/>
+      <c r="M67" s="51" t="n"/>
+      <c r="N67" s="51" t="n"/>
+      <c r="O67" s="51" t="n"/>
+      <c r="P67" s="51" t="n"/>
+      <c r="Q67" s="51" t="n"/>
+      <c r="R67" s="51" t="n"/>
+      <c r="S67" s="51" t="n"/>
+      <c r="T67" s="51" t="n"/>
+      <c r="U67" s="51" t="n"/>
+      <c r="V67" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W67" s="58" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B68" s="45" t="n"/>
-      <c r="C68" s="46" t="n"/>
-      <c r="D68" s="46" t="n"/>
+      <c r="C68" s="53" t="n"/>
+      <c r="D68" s="53" t="n"/>
       <c r="E68" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F68" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G68" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G68" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H68" s="49" t="n"/>
       <c r="I68" s="49" t="n"/>
       <c r="J68" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K68" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L68" s="50" t="n"/>
-      <c r="M68" s="51" t="n"/>
-      <c r="N68" s="51" t="n"/>
-      <c r="O68" s="51" t="n"/>
-      <c r="P68" s="51" t="n"/>
-      <c r="Q68" s="51" t="n"/>
-      <c r="R68" s="51" t="n"/>
-      <c r="S68" s="51" t="n"/>
-      <c r="T68" s="51" t="n"/>
-      <c r="U68" s="51" t="n"/>
-      <c r="V68" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W68" s="58" t="n"/>
+      <c r="M68" s="55" t="n"/>
+      <c r="N68" s="55" t="n"/>
+      <c r="O68" s="55" t="n"/>
+      <c r="P68" s="55" t="n"/>
+      <c r="Q68" s="55" t="n"/>
+      <c r="R68" s="55" t="n"/>
+      <c r="S68" s="55" t="n"/>
+      <c r="T68" s="55" t="n"/>
+      <c r="U68" s="55" t="n"/>
+      <c r="V68" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W68" s="57" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B69" s="45" t="n"/>
-      <c r="C69" s="53" t="n"/>
-      <c r="D69" s="53" t="n"/>
+      <c r="C69" s="46" t="n"/>
+      <c r="D69" s="46" t="n"/>
       <c r="E69" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F69" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G69" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H69" s="49" t="n"/>
       <c r="I69" s="49" t="n"/>
@@ -5089,51 +5103,92 @@
         <v>59</v>
       </c>
       <c r="K69" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L69" s="50" t="n"/>
-      <c r="M69" s="55" t="n"/>
-      <c r="N69" s="55" t="n"/>
-      <c r="O69" s="55" t="n"/>
-      <c r="P69" s="55" t="n"/>
-      <c r="Q69" s="55" t="n"/>
-      <c r="R69" s="55" t="n"/>
-      <c r="S69" s="55" t="n"/>
-      <c r="T69" s="55" t="n"/>
-      <c r="U69" s="55" t="n"/>
-      <c r="V69" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W69" s="57" t="n"/>
+      <c r="M69" s="51" t="n"/>
+      <c r="N69" s="51" t="n"/>
+      <c r="O69" s="51" t="n"/>
+      <c r="P69" s="51" t="n"/>
+      <c r="Q69" s="51" t="n"/>
+      <c r="R69" s="51" t="n"/>
+      <c r="S69" s="51" t="n"/>
+      <c r="T69" s="51" t="n"/>
+      <c r="U69" s="51" t="n"/>
+      <c r="V69" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W69" s="58" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B70" s="45" t="n"/>
-      <c r="C70" s="46" t="n"/>
-      <c r="D70" s="46" t="n"/>
-      <c r="E70" s="47" t="n"/>
-      <c r="F70" s="47" t="n"/>
-      <c r="G70" s="60" t="n"/>
+      <c r="C70" s="53" t="n"/>
+      <c r="D70" s="53" t="n"/>
+      <c r="E70" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F70" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G70" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H70" s="49" t="n"/>
       <c r="I70" s="49" t="n"/>
-      <c r="J70" s="50" t="n"/>
-      <c r="K70" s="50" t="n"/>
+      <c r="J70" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K70" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L70" s="50" t="n"/>
-      <c r="M70" s="51" t="n"/>
-      <c r="N70" s="51" t="n"/>
-      <c r="O70" s="51" t="n"/>
-      <c r="P70" s="51" t="n"/>
-      <c r="Q70" s="51" t="n"/>
-      <c r="R70" s="51" t="n"/>
-      <c r="S70" s="51" t="n"/>
-      <c r="T70" s="51" t="n"/>
-      <c r="U70" s="51" t="n"/>
-      <c r="V70" s="61" t="n"/>
-      <c r="W70" s="61" t="n"/>
+      <c r="M70" s="55" t="n"/>
+      <c r="N70" s="55" t="n"/>
+      <c r="O70" s="55" t="n"/>
+      <c r="P70" s="55" t="n"/>
+      <c r="Q70" s="55" t="n"/>
+      <c r="R70" s="55" t="n"/>
+      <c r="S70" s="55" t="n"/>
+      <c r="T70" s="55" t="n"/>
+      <c r="U70" s="55" t="n"/>
+      <c r="V70" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W70" s="57" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B71" s="45" t="n"/>
+      <c r="C71" s="46" t="n"/>
+      <c r="D71" s="46" t="n"/>
+      <c r="E71" s="47" t="n"/>
+      <c r="F71" s="47" t="n"/>
+      <c r="G71" s="60" t="n"/>
+      <c r="H71" s="49" t="n"/>
+      <c r="I71" s="49" t="n"/>
+      <c r="J71" s="50" t="n"/>
+      <c r="K71" s="50" t="n"/>
+      <c r="L71" s="50" t="n"/>
+      <c r="M71" s="51" t="n"/>
+      <c r="N71" s="51" t="n"/>
+      <c r="O71" s="51" t="n"/>
+      <c r="P71" s="51" t="n"/>
+      <c r="Q71" s="51" t="n"/>
+      <c r="R71" s="51" t="n"/>
+      <c r="S71" s="51" t="n"/>
+      <c r="T71" s="51" t="n"/>
+      <c r="U71" s="51" t="n"/>
+      <c r="V71" s="61" t="n"/>
+      <c r="W71" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W71"/>
+  <dimension ref="A1:W72"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,134 +1982,134 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/15(三)</t>
+          <t>2026/04/16(四)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>57</v>
-      </c>
-      <c r="G4" s="71" t="n">
-        <v>29.6</v>
+        <v>79</v>
+      </c>
+      <c r="G4" s="66" t="n">
+        <v>22.5</v>
       </c>
       <c r="H4" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I4" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J4" s="68" t="n">
-        <v>11</v>
-      </c>
       <c r="K4" s="68" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="L4" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M4" s="69" t="inlineStr">
         <is>
-          <t>博云新材、天邦食品</t>
-        </is>
-      </c>
-      <c r="N4" s="69" t="inlineStr"/>
-      <c r="O4" s="69" t="inlineStr">
+          <t>盛视科技</t>
+        </is>
+      </c>
+      <c r="N4" s="69" t="inlineStr">
+        <is>
+          <t>博云新材</t>
+        </is>
+      </c>
+      <c r="O4" s="69" t="inlineStr"/>
+      <c r="P4" s="69" t="inlineStr">
         <is>
           <t>圣阳股份</t>
         </is>
       </c>
-      <c r="P4" s="69" t="inlineStr"/>
       <c r="Q4" s="69" t="inlineStr"/>
       <c r="R4" s="69" t="inlineStr"/>
       <c r="S4" s="69" t="inlineStr"/>
       <c r="T4" s="69" t="inlineStr"/>
       <c r="U4" s="69" t="inlineStr"/>
       <c r="V4" s="69" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="W4" s="69" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/14(二)</t>
+          <t>2026/04/15(三)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
       <c r="C5" s="64" t="inlineStr"/>
       <c r="D5" s="64" t="inlineStr"/>
       <c r="E5" s="65" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>55</v>
-      </c>
-      <c r="G5" s="66" t="n">
-        <v>24.7</v>
+        <v>57</v>
+      </c>
+      <c r="G5" s="71" t="n">
+        <v>29.6</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I5" s="67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J5" s="68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K5" s="68" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L5" s="68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M5" s="69" t="inlineStr">
         <is>
-          <t>美能能源</t>
-        </is>
-      </c>
-      <c r="N5" s="69" t="inlineStr">
-        <is>
-          <t>中恒电气、圣阳股份</t>
-        </is>
-      </c>
-      <c r="O5" s="69" t="inlineStr"/>
-      <c r="P5" s="69" t="inlineStr">
-        <is>
-          <t>华远控股</t>
-        </is>
-      </c>
+          <t>博云新材、天邦食品</t>
+        </is>
+      </c>
+      <c r="N5" s="69" t="inlineStr"/>
+      <c r="O5" s="69" t="inlineStr">
+        <is>
+          <t>圣阳股份</t>
+        </is>
+      </c>
+      <c r="P5" s="69" t="inlineStr"/>
       <c r="Q5" s="69" t="inlineStr"/>
       <c r="R5" s="69" t="inlineStr"/>
       <c r="S5" s="69" t="inlineStr"/>
       <c r="T5" s="69" t="inlineStr"/>
       <c r="U5" s="69" t="inlineStr"/>
       <c r="V5" s="69" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="W5" s="69" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/04/13(一)</t>
+          <t>2026/04/14(二)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
       <c r="C6" s="64" t="inlineStr"/>
       <c r="D6" s="64" t="inlineStr"/>
       <c r="E6" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G6" s="66" t="n">
-        <v>20.3</v>
+        <v>24.7</v>
       </c>
       <c r="H6" s="67" t="n">
         <v>4</v>
@@ -2118,30 +2118,30 @@
         <v>4</v>
       </c>
       <c r="J6" s="68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K6" s="68" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L6" s="68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M6" s="69" t="inlineStr">
         <is>
+          <t>美能能源</t>
+        </is>
+      </c>
+      <c r="N6" s="69" t="inlineStr">
+        <is>
           <t>中恒电气、圣阳股份</t>
         </is>
       </c>
-      <c r="N6" s="69" t="inlineStr">
-        <is>
-          <t>长源东谷</t>
-        </is>
-      </c>
-      <c r="O6" s="69" t="inlineStr">
+      <c r="O6" s="69" t="inlineStr"/>
+      <c r="P6" s="69" t="inlineStr">
         <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="P6" s="69" t="inlineStr"/>
       <c r="Q6" s="69" t="inlineStr"/>
       <c r="R6" s="69" t="inlineStr"/>
       <c r="S6" s="69" t="inlineStr"/>
@@ -2155,7 +2155,7 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="62" t="inlineStr">
         <is>
-          <t>2026/04/10(五)</t>
+          <t>2026/04/13(一)</t>
         </is>
       </c>
       <c r="B7" s="63" t="inlineStr"/>
@@ -2167,35 +2167,39 @@
       <c r="F7" s="65" t="n">
         <v>59</v>
       </c>
-      <c r="G7" s="71" t="n">
-        <v>31.4</v>
+      <c r="G7" s="66" t="n">
+        <v>20.3</v>
       </c>
       <c r="H7" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I7" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" s="68" t="n">
-        <v>13</v>
-      </c>
       <c r="K7" s="68" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L7" s="68" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M7" s="69" t="inlineStr">
         <is>
-          <t>中嘉博创、长源东谷、来伊份</t>
+          <t>中恒电气、圣阳股份</t>
         </is>
       </c>
       <c r="N7" s="69" t="inlineStr">
         <is>
+          <t>长源东谷</t>
+        </is>
+      </c>
+      <c r="O7" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="O7" s="69" t="inlineStr"/>
       <c r="P7" s="69" t="inlineStr"/>
       <c r="Q7" s="69" t="inlineStr"/>
       <c r="R7" s="69" t="inlineStr"/>
@@ -2203,54 +2207,54 @@
       <c r="T7" s="69" t="inlineStr"/>
       <c r="U7" s="69" t="inlineStr"/>
       <c r="V7" s="69" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="W7" s="69" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="62" t="inlineStr">
         <is>
-          <t>2026/04/09(四)</t>
+          <t>2026/04/10(五)</t>
         </is>
       </c>
       <c r="B8" s="63" t="inlineStr"/>
       <c r="C8" s="64" t="inlineStr"/>
       <c r="D8" s="64" t="inlineStr"/>
       <c r="E8" s="65" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F8" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G8" s="66" t="n">
-        <v>23.2</v>
+        <v>59</v>
+      </c>
+      <c r="G8" s="71" t="n">
+        <v>31.4</v>
       </c>
       <c r="H8" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I8" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J8" s="68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" s="68" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L8" s="68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M8" s="69" t="inlineStr">
         <is>
+          <t>中嘉博创、长源东谷、来伊份</t>
+        </is>
+      </c>
+      <c r="N8" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="N8" s="69" t="inlineStr"/>
-      <c r="O8" s="69" t="inlineStr">
-        <is>
-          <t>汇源通信</t>
-        </is>
-      </c>
+      <c r="O8" s="69" t="inlineStr"/>
       <c r="P8" s="69" t="inlineStr"/>
       <c r="Q8" s="69" t="inlineStr"/>
       <c r="R8" s="69" t="inlineStr"/>
@@ -2258,54 +2262,54 @@
       <c r="T8" s="69" t="inlineStr"/>
       <c r="U8" s="69" t="inlineStr"/>
       <c r="V8" s="69" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="W8" s="69" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="62" t="inlineStr">
         <is>
-          <t>2026/04/08(三)</t>
+          <t>2026/04/09(四)</t>
         </is>
       </c>
       <c r="B9" s="63" t="inlineStr"/>
       <c r="C9" s="64" t="inlineStr"/>
       <c r="D9" s="64" t="inlineStr"/>
       <c r="E9" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="F9" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="G9" s="66" t="n">
-        <v>11.5</v>
+        <v>23.2</v>
       </c>
       <c r="H9" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I9" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9" s="68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K9" s="68" t="n">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="L9" s="68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M9" s="69" t="inlineStr">
         <is>
-          <t>中安科</t>
-        </is>
-      </c>
-      <c r="N9" s="69" t="inlineStr">
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="N9" s="69" t="inlineStr"/>
+      <c r="O9" s="69" t="inlineStr">
         <is>
           <t>汇源通信</t>
         </is>
       </c>
-      <c r="O9" s="69" t="inlineStr"/>
       <c r="P9" s="69" t="inlineStr"/>
       <c r="Q9" s="69" t="inlineStr"/>
       <c r="R9" s="69" t="inlineStr"/>
@@ -2320,20 +2324,20 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="62" t="inlineStr">
         <is>
-          <t>2026/04/07(二)</t>
+          <t>2026/04/08(三)</t>
         </is>
       </c>
       <c r="B10" s="63" t="inlineStr"/>
       <c r="C10" s="64" t="inlineStr"/>
       <c r="D10" s="64" t="inlineStr"/>
       <c r="E10" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F10" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G10" s="66" t="n">
-        <v>21.8</v>
+        <v>11.5</v>
       </c>
       <c r="H10" s="67" t="n">
         <v>4</v>
@@ -2342,91 +2346,95 @@
         <v>4</v>
       </c>
       <c r="J10" s="68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K10" s="68" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="L10" s="68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M10" s="69" t="inlineStr">
         <is>
-          <t>汇源通信、新能泰山</t>
-        </is>
-      </c>
-      <c r="N10" s="69" t="inlineStr"/>
+          <t>中安科</t>
+        </is>
+      </c>
+      <c r="N10" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信</t>
+        </is>
+      </c>
       <c r="O10" s="69" t="inlineStr"/>
       <c r="P10" s="69" t="inlineStr"/>
-      <c r="Q10" s="69" t="inlineStr">
-        <is>
-          <t>津药药业</t>
-        </is>
-      </c>
+      <c r="Q10" s="69" t="inlineStr"/>
       <c r="R10" s="69" t="inlineStr"/>
       <c r="S10" s="69" t="inlineStr"/>
       <c r="T10" s="69" t="inlineStr"/>
       <c r="U10" s="69" t="inlineStr"/>
       <c r="V10" s="69" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W10" s="69" t="inlineStr"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="62" t="inlineStr">
         <is>
-          <t>2026/04/06(一)</t>
+          <t>2026/04/07(二)</t>
         </is>
       </c>
       <c r="B11" s="63" t="inlineStr"/>
       <c r="C11" s="64" t="inlineStr"/>
       <c r="D11" s="64" t="inlineStr"/>
       <c r="E11" s="65" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F11" s="65" t="n">
-        <v>36</v>
-      </c>
-      <c r="G11" s="71" t="n">
-        <v>25</v>
+        <v>93</v>
+      </c>
+      <c r="G11" s="66" t="n">
+        <v>21.8</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I11" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J11" s="68" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="L11" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K11" s="68" t="n">
-        <v>32</v>
-      </c>
-      <c r="L11" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" s="69" t="inlineStr"/>
+      <c r="M11" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信、新能泰山</t>
+        </is>
+      </c>
       <c r="N11" s="69" t="inlineStr"/>
       <c r="O11" s="69" t="inlineStr"/>
-      <c r="P11" s="69" t="inlineStr">
+      <c r="P11" s="69" t="inlineStr"/>
+      <c r="Q11" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="Q11" s="69" t="inlineStr"/>
       <c r="R11" s="69" t="inlineStr"/>
       <c r="S11" s="69" t="inlineStr"/>
       <c r="T11" s="69" t="inlineStr"/>
       <c r="U11" s="69" t="inlineStr"/>
       <c r="V11" s="69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W11" s="69" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="62" t="inlineStr">
         <is>
-          <t>2026/04/03(五)</t>
+          <t>2026/04/06(一)</t>
         </is>
       </c>
       <c r="B12" s="63" t="inlineStr"/>
@@ -2470,105 +2478,105 @@
       <c r="T12" s="69" t="inlineStr"/>
       <c r="U12" s="69" t="inlineStr"/>
       <c r="V12" s="69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W12" s="69" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B13" s="63" t="inlineStr"/>
       <c r="C13" s="64" t="inlineStr"/>
       <c r="D13" s="64" t="inlineStr"/>
       <c r="E13" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F13" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G13" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H13" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I13" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J13" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K13" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L13" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M13" s="69" t="inlineStr"/>
       <c r="N13" s="69" t="inlineStr"/>
-      <c r="O13" s="69" t="inlineStr">
+      <c r="O13" s="69" t="inlineStr"/>
+      <c r="P13" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P13" s="69" t="inlineStr"/>
       <c r="Q13" s="69" t="inlineStr"/>
       <c r="R13" s="69" t="inlineStr"/>
       <c r="S13" s="69" t="inlineStr"/>
       <c r="T13" s="69" t="inlineStr"/>
       <c r="U13" s="69" t="inlineStr"/>
       <c r="V13" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W13" s="69" t="inlineStr"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B14" s="63" t="inlineStr"/>
       <c r="C14" s="64" t="inlineStr"/>
       <c r="D14" s="64" t="inlineStr"/>
       <c r="E14" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F14" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G14" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G14" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H14" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I14" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K14" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L14" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M14" s="69" t="inlineStr"/>
-      <c r="N14" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M14" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N14" s="69" t="inlineStr"/>
+      <c r="O14" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O14" s="69" t="inlineStr"/>
       <c r="P14" s="69" t="inlineStr"/>
       <c r="Q14" s="69" t="inlineStr"/>
       <c r="R14" s="69" t="inlineStr"/>
@@ -2576,51 +2584,47 @@
       <c r="T14" s="69" t="inlineStr"/>
       <c r="U14" s="69" t="inlineStr"/>
       <c r="V14" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W14" s="69" t="inlineStr"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B15" s="63" t="inlineStr"/>
       <c r="C15" s="64" t="inlineStr"/>
       <c r="D15" s="64" t="inlineStr"/>
       <c r="E15" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F15" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G15" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G15" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H15" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I15" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J15" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K15" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L15" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M15" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M15" s="69" t="inlineStr"/>
+      <c r="N15" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N15" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O15" s="69" t="inlineStr"/>
@@ -2631,254 +2635,250 @@
       <c r="T15" s="69" t="inlineStr"/>
       <c r="U15" s="69" t="inlineStr"/>
       <c r="V15" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W15" s="69" t="inlineStr"/>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr"/>
+      <c r="C16" s="64" t="inlineStr"/>
+      <c r="D16" s="64" t="inlineStr"/>
+      <c r="E16" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F16" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G16" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H16" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L16" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M16" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N16" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O16" s="69" t="inlineStr"/>
+      <c r="P16" s="69" t="inlineStr"/>
+      <c r="Q16" s="69" t="inlineStr"/>
+      <c r="R16" s="69" t="inlineStr"/>
+      <c r="S16" s="69" t="inlineStr"/>
+      <c r="T16" s="69" t="inlineStr"/>
+      <c r="U16" s="69" t="inlineStr"/>
+      <c r="V16" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W15" s="69" t="inlineStr"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="W16" s="69" t="inlineStr"/>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D16" s="38" t="inlineStr">
+      <c r="D17" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E16" s="39" t="n">
+      <c r="E17" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F16" s="39" t="n">
+      <c r="F17" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G16" s="40" t="n">
+      <c r="G17" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H16" s="41" t="n">
+      <c r="H17" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I16" s="41" t="n">
+      <c r="I17" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J16" s="42" t="n">
+      <c r="J17" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K16" s="42" t="n">
+      <c r="K17" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L16" s="42" t="n">
+      <c r="L17" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M16" s="43" t="inlineStr">
+      <c r="M17" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N16" s="43" t="inlineStr"/>
-      <c r="O16" s="43" t="inlineStr">
+      <c r="N17" s="43" t="inlineStr"/>
+      <c r="O17" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P16" s="43" t="inlineStr"/>
-      <c r="Q16" s="43" t="inlineStr"/>
-      <c r="R16" s="43" t="inlineStr"/>
-      <c r="S16" s="43" t="inlineStr"/>
-      <c r="T16" s="43" t="inlineStr"/>
-      <c r="U16" s="43" t="inlineStr"/>
-      <c r="V16" s="43" t="n">
+      <c r="P17" s="43" t="inlineStr"/>
+      <c r="Q17" s="43" t="inlineStr"/>
+      <c r="R17" s="43" t="inlineStr"/>
+      <c r="S17" s="43" t="inlineStr"/>
+      <c r="T17" s="43" t="inlineStr"/>
+      <c r="U17" s="43" t="inlineStr"/>
+      <c r="V17" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W16" s="43" t="inlineStr"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B17" s="45" t="n"/>
-      <c r="C17" s="46" t="n"/>
-      <c r="D17" s="46" t="n"/>
-      <c r="E17" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F17" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G17" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H17" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K17" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L17" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" s="51" t="n"/>
-      <c r="N17" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O17" s="51" t="n"/>
-      <c r="P17" s="51" t="n"/>
-      <c r="Q17" s="51" t="n"/>
-      <c r="R17" s="51" t="n"/>
-      <c r="S17" s="51" t="n"/>
-      <c r="T17" s="51" t="n"/>
-      <c r="U17" s="51" t="n"/>
-      <c r="V17" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W17" s="43" t="inlineStr"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B18" s="45" t="n"/>
-      <c r="C18" s="53" t="n"/>
-      <c r="D18" s="53" t="n"/>
+      <c r="C18" s="46" t="n"/>
+      <c r="D18" s="46" t="n"/>
       <c r="E18" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F18" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G18" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G18" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H18" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I18" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J18" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K18" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L18" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M18" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N18" s="55" t="n"/>
-      <c r="O18" s="55" t="n"/>
-      <c r="P18" s="55" t="n"/>
-      <c r="Q18" s="55" t="n"/>
-      <c r="R18" s="55" t="n"/>
-      <c r="S18" s="55" t="n"/>
-      <c r="T18" s="55" t="n"/>
-      <c r="U18" s="55" t="n"/>
-      <c r="V18" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W18" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M18" s="51" t="n"/>
+      <c r="N18" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O18" s="51" t="n"/>
+      <c r="P18" s="51" t="n"/>
+      <c r="Q18" s="51" t="n"/>
+      <c r="R18" s="51" t="n"/>
+      <c r="S18" s="51" t="n"/>
+      <c r="T18" s="51" t="n"/>
+      <c r="U18" s="51" t="n"/>
+      <c r="V18" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B19" s="45" t="n"/>
-      <c r="C19" s="46" t="n"/>
-      <c r="D19" s="46" t="n"/>
+      <c r="C19" s="53" t="n"/>
+      <c r="D19" s="53" t="n"/>
       <c r="E19" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F19" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G19" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G19" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H19" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J19" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K19" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L19" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M19" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N19" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O19" s="51" t="n"/>
-      <c r="P19" s="51" t="n"/>
-      <c r="Q19" s="51" t="n"/>
-      <c r="R19" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S19" s="51" t="n"/>
-      <c r="T19" s="51" t="n"/>
-      <c r="U19" s="51" t="n"/>
-      <c r="V19" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W19" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M19" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N19" s="55" t="n"/>
+      <c r="O19" s="55" t="n"/>
+      <c r="P19" s="55" t="n"/>
+      <c r="Q19" s="55" t="n"/>
+      <c r="R19" s="55" t="n"/>
+      <c r="S19" s="55" t="n"/>
+      <c r="T19" s="55" t="n"/>
+      <c r="U19" s="55" t="n"/>
+      <c r="V19" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W19" s="57" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B20" s="45" t="n"/>
-      <c r="C20" s="53" t="n"/>
-      <c r="D20" s="53" t="n"/>
+      <c r="C20" s="46" t="n"/>
+      <c r="D20" s="46" t="n"/>
       <c r="E20" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G20" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H20" s="49" t="n">
         <v>1</v>
@@ -2887,493 +2887,497 @@
         <v>1</v>
       </c>
       <c r="J20" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K20" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L20" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M20" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M20" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N20" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N20" s="55" t="n"/>
-      <c r="O20" s="55" t="n"/>
-      <c r="P20" s="55" t="n"/>
-      <c r="Q20" s="55" t="inlineStr">
+      <c r="O20" s="51" t="n"/>
+      <c r="P20" s="51" t="n"/>
+      <c r="Q20" s="51" t="n"/>
+      <c r="R20" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R20" s="55" t="n"/>
-      <c r="S20" s="55" t="n"/>
-      <c r="T20" s="55" t="n"/>
-      <c r="U20" s="55" t="n"/>
-      <c r="V20" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W20" s="57" t="n"/>
+      <c r="S20" s="51" t="n"/>
+      <c r="T20" s="51" t="n"/>
+      <c r="U20" s="51" t="n"/>
+      <c r="V20" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W20" s="58" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="46" t="n"/>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="53" t="n"/>
       <c r="E21" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F21" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G21" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G21" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H21" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J21" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K21" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L21" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N21" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O21" s="51" t="n"/>
-      <c r="P21" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M21" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N21" s="55" t="n"/>
+      <c r="O21" s="55" t="n"/>
+      <c r="P21" s="55" t="n"/>
+      <c r="Q21" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q21" s="51" t="n"/>
-      <c r="R21" s="51" t="n"/>
-      <c r="S21" s="51" t="n"/>
-      <c r="T21" s="51" t="n"/>
-      <c r="U21" s="51" t="n"/>
-      <c r="V21" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W21" s="58" t="n"/>
+      <c r="R21" s="55" t="n"/>
+      <c r="S21" s="55" t="n"/>
+      <c r="T21" s="55" t="n"/>
+      <c r="U21" s="55" t="n"/>
+      <c r="V21" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W21" s="57" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="53" t="n"/>
+      <c r="C22" s="46" t="n"/>
+      <c r="D22" s="46" t="n"/>
       <c r="E22" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F22" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G22" s="59" t="n">
-        <v>45.1</v>
+      <c r="G22" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H22" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K22" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L22" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M22" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N22" s="55" t="n"/>
-      <c r="O22" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P22" s="55" t="n"/>
-      <c r="Q22" s="55" t="n"/>
-      <c r="R22" s="55" t="n"/>
-      <c r="S22" s="55" t="n"/>
-      <c r="T22" s="55" t="n"/>
-      <c r="U22" s="55" t="n"/>
-      <c r="V22" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W22" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M22" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N22" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O22" s="51" t="n"/>
+      <c r="P22" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q22" s="51" t="n"/>
+      <c r="R22" s="51" t="n"/>
+      <c r="S22" s="51" t="n"/>
+      <c r="T22" s="51" t="n"/>
+      <c r="U22" s="51" t="n"/>
+      <c r="V22" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W22" s="58" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="46" t="n"/>
-      <c r="D23" s="46" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
       <c r="E23" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F23" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G23" s="54" t="n">
-        <v>26.3</v>
+      <c r="G23" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H23" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L23" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M23" s="51" t="n"/>
-      <c r="N23" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M23" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N23" s="55" t="n"/>
+      <c r="O23" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O23" s="51" t="n"/>
-      <c r="P23" s="51" t="n"/>
-      <c r="Q23" s="51" t="n"/>
-      <c r="R23" s="51" t="n"/>
-      <c r="S23" s="51" t="n"/>
-      <c r="T23" s="51" t="n"/>
-      <c r="U23" s="51" t="n"/>
-      <c r="V23" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W23" s="58" t="n"/>
+      <c r="P23" s="55" t="n"/>
+      <c r="Q23" s="55" t="n"/>
+      <c r="R23" s="55" t="n"/>
+      <c r="S23" s="55" t="n"/>
+      <c r="T23" s="55" t="n"/>
+      <c r="U23" s="55" t="n"/>
+      <c r="V23" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W23" s="57" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
+      <c r="C24" s="46" t="n"/>
+      <c r="D24" s="46" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G24" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H24" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L24" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M24" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M24" s="51" t="n"/>
+      <c r="N24" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N24" s="55" t="n"/>
-      <c r="O24" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P24" s="55" t="n"/>
-      <c r="Q24" s="55" t="n"/>
-      <c r="R24" s="55" t="n"/>
-      <c r="S24" s="55" t="n"/>
-      <c r="T24" s="55" t="n"/>
-      <c r="U24" s="55" t="n"/>
-      <c r="V24" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W24" s="57" t="n"/>
+      <c r="O24" s="51" t="n"/>
+      <c r="P24" s="51" t="n"/>
+      <c r="Q24" s="51" t="n"/>
+      <c r="R24" s="51" t="n"/>
+      <c r="S24" s="51" t="n"/>
+      <c r="T24" s="51" t="n"/>
+      <c r="U24" s="51" t="n"/>
+      <c r="V24" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W24" s="58" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="46" t="n"/>
-      <c r="D25" s="46" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G25" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H25" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L25" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M25" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N25" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O25" s="51" t="n"/>
-      <c r="P25" s="51" t="n"/>
-      <c r="Q25" s="51" t="n"/>
-      <c r="R25" s="51" t="n"/>
-      <c r="S25" s="51" t="n"/>
-      <c r="T25" s="51" t="n"/>
-      <c r="U25" s="51" t="n"/>
-      <c r="V25" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W25" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M25" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N25" s="55" t="n"/>
+      <c r="O25" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P25" s="55" t="n"/>
+      <c r="Q25" s="55" t="n"/>
+      <c r="R25" s="55" t="n"/>
+      <c r="S25" s="55" t="n"/>
+      <c r="T25" s="55" t="n"/>
+      <c r="U25" s="55" t="n"/>
+      <c r="V25" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W25" s="57" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="53" t="n"/>
-      <c r="D26" s="53" t="n"/>
+      <c r="C26" s="46" t="n"/>
+      <c r="D26" s="46" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G26" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H26" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K26" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L26" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I26" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K26" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L26" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M26" s="55" t="inlineStr">
+      <c r="M26" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N26" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N26" s="55" t="n"/>
-      <c r="O26" s="55" t="n"/>
-      <c r="P26" s="55" t="n"/>
-      <c r="Q26" s="55" t="n"/>
-      <c r="R26" s="55" t="n"/>
-      <c r="S26" s="55" t="n"/>
-      <c r="T26" s="55" t="n"/>
-      <c r="U26" s="55" t="n"/>
-      <c r="V26" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W26" s="57" t="n"/>
+      <c r="O26" s="51" t="n"/>
+      <c r="P26" s="51" t="n"/>
+      <c r="Q26" s="51" t="n"/>
+      <c r="R26" s="51" t="n"/>
+      <c r="S26" s="51" t="n"/>
+      <c r="T26" s="51" t="n"/>
+      <c r="U26" s="51" t="n"/>
+      <c r="V26" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W26" s="58" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="46" t="n"/>
-      <c r="D27" s="46" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G27" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G27" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H27" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I27" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L27" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M27" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N27" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O27" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P27" s="51" t="n"/>
-      <c r="Q27" s="51" t="n"/>
-      <c r="R27" s="51" t="n"/>
-      <c r="S27" s="51" t="n"/>
-      <c r="T27" s="51" t="n"/>
-      <c r="U27" s="51" t="n"/>
-      <c r="V27" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W27" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M27" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N27" s="55" t="n"/>
+      <c r="O27" s="55" t="n"/>
+      <c r="P27" s="55" t="n"/>
+      <c r="Q27" s="55" t="n"/>
+      <c r="R27" s="55" t="n"/>
+      <c r="S27" s="55" t="n"/>
+      <c r="T27" s="55" t="n"/>
+      <c r="U27" s="55" t="n"/>
+      <c r="V27" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W27" s="57" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="53" t="n"/>
-      <c r="D28" s="53" t="n"/>
+      <c r="C28" s="46" t="n"/>
+      <c r="D28" s="46" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G28" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G28" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H28" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I28" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L28" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M28" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N28" s="55" t="inlineStr">
+      <c r="M28" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N28" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O28" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O28" s="55" t="n"/>
-      <c r="P28" s="55" t="n"/>
-      <c r="Q28" s="55" t="n"/>
-      <c r="R28" s="55" t="n"/>
-      <c r="S28" s="55" t="n"/>
-      <c r="T28" s="55" t="n"/>
-      <c r="U28" s="55" t="n"/>
-      <c r="V28" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W28" s="57" t="n"/>
+      <c r="P28" s="51" t="n"/>
+      <c r="Q28" s="51" t="n"/>
+      <c r="R28" s="51" t="n"/>
+      <c r="S28" s="51" t="n"/>
+      <c r="T28" s="51" t="n"/>
+      <c r="U28" s="51" t="n"/>
+      <c r="V28" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W28" s="58" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="46" t="n"/>
-      <c r="D29" s="46" t="n"/>
+      <c r="C29" s="53" t="n"/>
+      <c r="D29" s="53" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G29" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H29" s="49" t="n">
         <v>2</v>
@@ -3382,208 +3386,218 @@
         <v>2</v>
       </c>
       <c r="J29" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K29" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L29" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M29" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M29" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N29" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N29" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O29" s="51" t="n"/>
-      <c r="P29" s="51" t="n"/>
-      <c r="Q29" s="51" t="n"/>
-      <c r="R29" s="51" t="n"/>
-      <c r="S29" s="51" t="n"/>
-      <c r="T29" s="51" t="n"/>
-      <c r="U29" s="51" t="n"/>
-      <c r="V29" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W29" s="58" t="n"/>
+      <c r="O29" s="55" t="n"/>
+      <c r="P29" s="55" t="n"/>
+      <c r="Q29" s="55" t="n"/>
+      <c r="R29" s="55" t="n"/>
+      <c r="S29" s="55" t="n"/>
+      <c r="T29" s="55" t="n"/>
+      <c r="U29" s="55" t="n"/>
+      <c r="V29" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W29" s="57" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="53" t="n"/>
-      <c r="D30" s="53" t="n"/>
+      <c r="C30" s="46" t="n"/>
+      <c r="D30" s="46" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G30" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H30" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I30" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J30" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L30" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M30" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M30" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N30" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N30" s="55" t="n"/>
-      <c r="O30" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P30" s="55" t="n"/>
-      <c r="Q30" s="55" t="n"/>
-      <c r="R30" s="55" t="n"/>
-      <c r="S30" s="55" t="n"/>
-      <c r="T30" s="55" t="n"/>
-      <c r="U30" s="55" t="n"/>
-      <c r="V30" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W30" s="57" t="n"/>
+      <c r="O30" s="51" t="n"/>
+      <c r="P30" s="51" t="n"/>
+      <c r="Q30" s="51" t="n"/>
+      <c r="R30" s="51" t="n"/>
+      <c r="S30" s="51" t="n"/>
+      <c r="T30" s="51" t="n"/>
+      <c r="U30" s="51" t="n"/>
+      <c r="V30" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W30" s="58" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="46" t="n"/>
-      <c r="D31" s="46" t="n"/>
+      <c r="C31" s="53" t="n"/>
+      <c r="D31" s="53" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G31" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G31" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H31" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L31" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M31" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N31" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O31" s="51" t="n"/>
-      <c r="P31" s="51" t="n"/>
-      <c r="Q31" s="51" t="n"/>
-      <c r="R31" s="51" t="n"/>
-      <c r="S31" s="51" t="n"/>
-      <c r="T31" s="51" t="n"/>
-      <c r="U31" s="51" t="n"/>
-      <c r="V31" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W31" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M31" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N31" s="55" t="n"/>
+      <c r="O31" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P31" s="55" t="n"/>
+      <c r="Q31" s="55" t="n"/>
+      <c r="R31" s="55" t="n"/>
+      <c r="S31" s="55" t="n"/>
+      <c r="T31" s="55" t="n"/>
+      <c r="U31" s="55" t="n"/>
+      <c r="V31" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W31" s="57" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="53" t="n"/>
-      <c r="D32" s="53" t="n"/>
+      <c r="C32" s="46" t="n"/>
+      <c r="D32" s="46" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G32" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G32" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H32" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L32" s="50" t="n"/>
-      <c r="M32" s="55" t="n"/>
-      <c r="N32" s="55" t="n"/>
-      <c r="O32" s="55" t="n"/>
-      <c r="P32" s="55" t="n"/>
-      <c r="Q32" s="55" t="n"/>
-      <c r="R32" s="55" t="n"/>
-      <c r="S32" s="55" t="n"/>
-      <c r="T32" s="55" t="n"/>
-      <c r="U32" s="55" t="n"/>
-      <c r="V32" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W32" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L32" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M32" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N32" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O32" s="51" t="n"/>
+      <c r="P32" s="51" t="n"/>
+      <c r="Q32" s="51" t="n"/>
+      <c r="R32" s="51" t="n"/>
+      <c r="S32" s="51" t="n"/>
+      <c r="T32" s="51" t="n"/>
+      <c r="U32" s="51" t="n"/>
+      <c r="V32" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W32" s="58" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="46" t="n"/>
-      <c r="D33" s="46" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G33" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H33" s="49" t="n">
         <v>0</v>
@@ -3592,43 +3606,43 @@
         <v>0</v>
       </c>
       <c r="J33" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L33" s="50" t="n"/>
-      <c r="M33" s="51" t="n"/>
-      <c r="N33" s="51" t="n"/>
-      <c r="O33" s="51" t="n"/>
-      <c r="P33" s="51" t="n"/>
-      <c r="Q33" s="51" t="n"/>
-      <c r="R33" s="51" t="n"/>
-      <c r="S33" s="51" t="n"/>
-      <c r="T33" s="51" t="n"/>
-      <c r="U33" s="51" t="n"/>
-      <c r="V33" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W33" s="58" t="n"/>
+      <c r="M33" s="55" t="n"/>
+      <c r="N33" s="55" t="n"/>
+      <c r="O33" s="55" t="n"/>
+      <c r="P33" s="55" t="n"/>
+      <c r="Q33" s="55" t="n"/>
+      <c r="R33" s="55" t="n"/>
+      <c r="S33" s="55" t="n"/>
+      <c r="T33" s="55" t="n"/>
+      <c r="U33" s="55" t="n"/>
+      <c r="V33" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W33" s="57" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="53" t="n"/>
-      <c r="D34" s="53" t="n"/>
+      <c r="C34" s="46" t="n"/>
+      <c r="D34" s="46" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G34" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H34" s="49" t="n">
         <v>0</v>
@@ -3637,43 +3651,43 @@
         <v>0</v>
       </c>
       <c r="J34" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L34" s="50" t="n"/>
-      <c r="M34" s="55" t="n"/>
-      <c r="N34" s="55" t="n"/>
-      <c r="O34" s="55" t="n"/>
-      <c r="P34" s="55" t="n"/>
-      <c r="Q34" s="55" t="n"/>
-      <c r="R34" s="55" t="n"/>
-      <c r="S34" s="55" t="n"/>
-      <c r="T34" s="55" t="n"/>
-      <c r="U34" s="55" t="n"/>
-      <c r="V34" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W34" s="57" t="n"/>
+      <c r="M34" s="51" t="n"/>
+      <c r="N34" s="51" t="n"/>
+      <c r="O34" s="51" t="n"/>
+      <c r="P34" s="51" t="n"/>
+      <c r="Q34" s="51" t="n"/>
+      <c r="R34" s="51" t="n"/>
+      <c r="S34" s="51" t="n"/>
+      <c r="T34" s="51" t="n"/>
+      <c r="U34" s="51" t="n"/>
+      <c r="V34" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W34" s="58" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="46" t="n"/>
-      <c r="D35" s="46" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G35" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G35" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H35" s="49" t="n">
         <v>0</v>
@@ -3682,43 +3696,43 @@
         <v>0</v>
       </c>
       <c r="J35" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L35" s="50" t="n"/>
-      <c r="M35" s="51" t="n"/>
-      <c r="N35" s="51" t="n"/>
-      <c r="O35" s="51" t="n"/>
-      <c r="P35" s="51" t="n"/>
-      <c r="Q35" s="51" t="n"/>
-      <c r="R35" s="51" t="n"/>
-      <c r="S35" s="51" t="n"/>
-      <c r="T35" s="51" t="n"/>
-      <c r="U35" s="51" t="n"/>
-      <c r="V35" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W35" s="58" t="n"/>
+      <c r="M35" s="55" t="n"/>
+      <c r="N35" s="55" t="n"/>
+      <c r="O35" s="55" t="n"/>
+      <c r="P35" s="55" t="n"/>
+      <c r="Q35" s="55" t="n"/>
+      <c r="R35" s="55" t="n"/>
+      <c r="S35" s="55" t="n"/>
+      <c r="T35" s="55" t="n"/>
+      <c r="U35" s="55" t="n"/>
+      <c r="V35" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W35" s="57" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
+      <c r="C36" s="46" t="n"/>
+      <c r="D36" s="46" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G36" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H36" s="49" t="n">
         <v>0</v>
@@ -3727,43 +3741,43 @@
         <v>0</v>
       </c>
       <c r="J36" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="55" t="n"/>
-      <c r="N36" s="55" t="n"/>
-      <c r="O36" s="55" t="n"/>
-      <c r="P36" s="55" t="n"/>
-      <c r="Q36" s="55" t="n"/>
-      <c r="R36" s="55" t="n"/>
-      <c r="S36" s="55" t="n"/>
-      <c r="T36" s="55" t="n"/>
-      <c r="U36" s="55" t="n"/>
-      <c r="V36" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W36" s="57" t="n"/>
+      <c r="M36" s="51" t="n"/>
+      <c r="N36" s="51" t="n"/>
+      <c r="O36" s="51" t="n"/>
+      <c r="P36" s="51" t="n"/>
+      <c r="Q36" s="51" t="n"/>
+      <c r="R36" s="51" t="n"/>
+      <c r="S36" s="51" t="n"/>
+      <c r="T36" s="51" t="n"/>
+      <c r="U36" s="51" t="n"/>
+      <c r="V36" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W36" s="58" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="46" t="n"/>
-      <c r="D37" s="46" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G37" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H37" s="49" t="n">
         <v>0</v>
@@ -3772,1371 +3786,1375 @@
         <v>0</v>
       </c>
       <c r="J37" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="51" t="n"/>
-      <c r="N37" s="51" t="n"/>
-      <c r="O37" s="51" t="n"/>
-      <c r="P37" s="51" t="n"/>
-      <c r="Q37" s="51" t="n"/>
-      <c r="R37" s="51" t="n"/>
-      <c r="S37" s="51" t="n"/>
-      <c r="T37" s="51" t="n"/>
-      <c r="U37" s="51" t="n"/>
-      <c r="V37" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W37" s="58" t="n"/>
+      <c r="M37" s="55" t="n"/>
+      <c r="N37" s="55" t="n"/>
+      <c r="O37" s="55" t="n"/>
+      <c r="P37" s="55" t="n"/>
+      <c r="Q37" s="55" t="n"/>
+      <c r="R37" s="55" t="n"/>
+      <c r="S37" s="55" t="n"/>
+      <c r="T37" s="55" t="n"/>
+      <c r="U37" s="55" t="n"/>
+      <c r="V37" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W37" s="57" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="53" t="n"/>
-      <c r="D38" s="53" t="n"/>
+      <c r="C38" s="46" t="n"/>
+      <c r="D38" s="46" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G38" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H38" s="49" t="n"/>
-      <c r="I38" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G38" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H38" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J38" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="55" t="n"/>
-      <c r="N38" s="55" t="n"/>
-      <c r="O38" s="55" t="n"/>
-      <c r="P38" s="55" t="n"/>
-      <c r="Q38" s="55" t="n"/>
-      <c r="R38" s="55" t="n"/>
-      <c r="S38" s="55" t="n"/>
-      <c r="T38" s="55" t="n"/>
-      <c r="U38" s="55" t="n"/>
-      <c r="V38" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W38" s="57" t="n"/>
+      <c r="M38" s="51" t="n"/>
+      <c r="N38" s="51" t="n"/>
+      <c r="O38" s="51" t="n"/>
+      <c r="P38" s="51" t="n"/>
+      <c r="Q38" s="51" t="n"/>
+      <c r="R38" s="51" t="n"/>
+      <c r="S38" s="51" t="n"/>
+      <c r="T38" s="51" t="n"/>
+      <c r="U38" s="51" t="n"/>
+      <c r="V38" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W38" s="58" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="46" t="n"/>
-      <c r="D39" s="46" t="n"/>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G39" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H39" s="49" t="n"/>
       <c r="I39" s="49" t="n"/>
       <c r="J39" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="51" t="n"/>
-      <c r="N39" s="51" t="n"/>
-      <c r="O39" s="51" t="n"/>
-      <c r="P39" s="51" t="n"/>
-      <c r="Q39" s="51" t="n"/>
-      <c r="R39" s="51" t="n"/>
-      <c r="S39" s="51" t="n"/>
-      <c r="T39" s="51" t="n"/>
-      <c r="U39" s="51" t="n"/>
-      <c r="V39" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W39" s="58" t="n"/>
+      <c r="M39" s="55" t="n"/>
+      <c r="N39" s="55" t="n"/>
+      <c r="O39" s="55" t="n"/>
+      <c r="P39" s="55" t="n"/>
+      <c r="Q39" s="55" t="n"/>
+      <c r="R39" s="55" t="n"/>
+      <c r="S39" s="55" t="n"/>
+      <c r="T39" s="55" t="n"/>
+      <c r="U39" s="55" t="n"/>
+      <c r="V39" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W39" s="57" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="53" t="n"/>
-      <c r="D40" s="53" t="n"/>
+      <c r="C40" s="46" t="n"/>
+      <c r="D40" s="46" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G40" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H40" s="49" t="n"/>
       <c r="I40" s="49" t="n"/>
       <c r="J40" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="55" t="n"/>
-      <c r="N40" s="55" t="n"/>
-      <c r="O40" s="55" t="n"/>
-      <c r="P40" s="55" t="n"/>
-      <c r="Q40" s="55" t="n"/>
-      <c r="R40" s="55" t="n"/>
-      <c r="S40" s="55" t="n"/>
-      <c r="T40" s="55" t="n"/>
-      <c r="U40" s="55" t="n"/>
-      <c r="V40" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W40" s="57" t="n"/>
+      <c r="M40" s="51" t="n"/>
+      <c r="N40" s="51" t="n"/>
+      <c r="O40" s="51" t="n"/>
+      <c r="P40" s="51" t="n"/>
+      <c r="Q40" s="51" t="n"/>
+      <c r="R40" s="51" t="n"/>
+      <c r="S40" s="51" t="n"/>
+      <c r="T40" s="51" t="n"/>
+      <c r="U40" s="51" t="n"/>
+      <c r="V40" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W40" s="58" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="46" t="n"/>
-      <c r="D41" s="46" t="n"/>
+      <c r="C41" s="53" t="n"/>
+      <c r="D41" s="53" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G41" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H41" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I41" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H41" s="49" t="n"/>
+      <c r="I41" s="49" t="n"/>
       <c r="J41" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="51" t="n"/>
-      <c r="N41" s="51" t="n"/>
-      <c r="O41" s="51" t="n"/>
-      <c r="P41" s="51" t="n"/>
-      <c r="Q41" s="51" t="n"/>
-      <c r="R41" s="51" t="n"/>
-      <c r="S41" s="51" t="n"/>
-      <c r="T41" s="51" t="n"/>
-      <c r="U41" s="51" t="n"/>
-      <c r="V41" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W41" s="58" t="n"/>
+      <c r="M41" s="55" t="n"/>
+      <c r="N41" s="55" t="n"/>
+      <c r="O41" s="55" t="n"/>
+      <c r="P41" s="55" t="n"/>
+      <c r="Q41" s="55" t="n"/>
+      <c r="R41" s="55" t="n"/>
+      <c r="S41" s="55" t="n"/>
+      <c r="T41" s="55" t="n"/>
+      <c r="U41" s="55" t="n"/>
+      <c r="V41" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W41" s="57" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="53" t="n"/>
-      <c r="D42" s="53" t="n"/>
+      <c r="C42" s="46" t="n"/>
+      <c r="D42" s="46" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G42" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H42" s="49" t="n"/>
-      <c r="I42" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G42" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H42" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I42" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J42" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K42" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="55" t="n"/>
-      <c r="N42" s="55" t="n"/>
-      <c r="O42" s="55" t="n"/>
-      <c r="P42" s="55" t="n"/>
-      <c r="Q42" s="55" t="n"/>
-      <c r="R42" s="55" t="n"/>
-      <c r="S42" s="55" t="n"/>
-      <c r="T42" s="55" t="n"/>
-      <c r="U42" s="55" t="n"/>
-      <c r="V42" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W42" s="57" t="n"/>
+      <c r="M42" s="51" t="n"/>
+      <c r="N42" s="51" t="n"/>
+      <c r="O42" s="51" t="n"/>
+      <c r="P42" s="51" t="n"/>
+      <c r="Q42" s="51" t="n"/>
+      <c r="R42" s="51" t="n"/>
+      <c r="S42" s="51" t="n"/>
+      <c r="T42" s="51" t="n"/>
+      <c r="U42" s="51" t="n"/>
+      <c r="V42" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W42" s="58" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="46" t="n"/>
-      <c r="D43" s="46" t="n"/>
+      <c r="C43" s="53" t="n"/>
+      <c r="D43" s="53" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G43" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G43" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H43" s="49" t="n"/>
       <c r="I43" s="49" t="n"/>
       <c r="J43" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K43" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="51" t="n"/>
-      <c r="N43" s="51" t="n"/>
-      <c r="O43" s="51" t="n"/>
-      <c r="P43" s="51" t="n"/>
-      <c r="Q43" s="51" t="n"/>
-      <c r="R43" s="51" t="n"/>
-      <c r="S43" s="51" t="n"/>
-      <c r="T43" s="51" t="n"/>
-      <c r="U43" s="51" t="n"/>
-      <c r="V43" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W43" s="58" t="n"/>
+      <c r="M43" s="55" t="n"/>
+      <c r="N43" s="55" t="n"/>
+      <c r="O43" s="55" t="n"/>
+      <c r="P43" s="55" t="n"/>
+      <c r="Q43" s="55" t="n"/>
+      <c r="R43" s="55" t="n"/>
+      <c r="S43" s="55" t="n"/>
+      <c r="T43" s="55" t="n"/>
+      <c r="U43" s="55" t="n"/>
+      <c r="V43" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W43" s="57" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="53" t="n"/>
-      <c r="D44" s="53" t="n"/>
+      <c r="C44" s="46" t="n"/>
+      <c r="D44" s="46" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G44" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G44" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H44" s="49" t="n"/>
       <c r="I44" s="49" t="n"/>
       <c r="J44" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K44" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K44" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="55" t="n"/>
-      <c r="N44" s="55" t="n"/>
-      <c r="O44" s="55" t="n"/>
-      <c r="P44" s="55" t="n"/>
-      <c r="Q44" s="55" t="n"/>
-      <c r="R44" s="55" t="n"/>
-      <c r="S44" s="55" t="n"/>
-      <c r="T44" s="55" t="n"/>
-      <c r="U44" s="55" t="n"/>
-      <c r="V44" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W44" s="57" t="n"/>
+      <c r="M44" s="51" t="n"/>
+      <c r="N44" s="51" t="n"/>
+      <c r="O44" s="51" t="n"/>
+      <c r="P44" s="51" t="n"/>
+      <c r="Q44" s="51" t="n"/>
+      <c r="R44" s="51" t="n"/>
+      <c r="S44" s="51" t="n"/>
+      <c r="T44" s="51" t="n"/>
+      <c r="U44" s="51" t="n"/>
+      <c r="V44" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W44" s="58" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="46" t="n"/>
-      <c r="D45" s="46" t="n"/>
+      <c r="C45" s="53" t="n"/>
+      <c r="D45" s="53" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G45" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H45" s="49" t="n"/>
       <c r="I45" s="49" t="n"/>
       <c r="J45" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K45" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="51" t="n"/>
-      <c r="N45" s="51" t="n"/>
-      <c r="O45" s="51" t="n"/>
-      <c r="P45" s="51" t="n"/>
-      <c r="Q45" s="51" t="n"/>
-      <c r="R45" s="51" t="n"/>
-      <c r="S45" s="51" t="n"/>
-      <c r="T45" s="51" t="n"/>
-      <c r="U45" s="51" t="n"/>
-      <c r="V45" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W45" s="58" t="n"/>
+      <c r="M45" s="55" t="n"/>
+      <c r="N45" s="55" t="n"/>
+      <c r="O45" s="55" t="n"/>
+      <c r="P45" s="55" t="n"/>
+      <c r="Q45" s="55" t="n"/>
+      <c r="R45" s="55" t="n"/>
+      <c r="S45" s="55" t="n"/>
+      <c r="T45" s="55" t="n"/>
+      <c r="U45" s="55" t="n"/>
+      <c r="V45" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W45" s="57" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="53" t="n"/>
-      <c r="D46" s="53" t="n"/>
+      <c r="C46" s="46" t="n"/>
+      <c r="D46" s="46" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G46" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G46" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H46" s="49" t="n"/>
       <c r="I46" s="49" t="n"/>
       <c r="J46" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K46" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="55" t="n"/>
-      <c r="N46" s="55" t="n"/>
-      <c r="O46" s="55" t="n"/>
-      <c r="P46" s="55" t="n"/>
-      <c r="Q46" s="55" t="n"/>
-      <c r="R46" s="55" t="n"/>
-      <c r="S46" s="55" t="n"/>
-      <c r="T46" s="55" t="n"/>
-      <c r="U46" s="55" t="n"/>
-      <c r="V46" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W46" s="57" t="n"/>
+      <c r="M46" s="51" t="n"/>
+      <c r="N46" s="51" t="n"/>
+      <c r="O46" s="51" t="n"/>
+      <c r="P46" s="51" t="n"/>
+      <c r="Q46" s="51" t="n"/>
+      <c r="R46" s="51" t="n"/>
+      <c r="S46" s="51" t="n"/>
+      <c r="T46" s="51" t="n"/>
+      <c r="U46" s="51" t="n"/>
+      <c r="V46" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W46" s="58" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="46" t="n"/>
-      <c r="D47" s="46" t="n"/>
+      <c r="C47" s="53" t="n"/>
+      <c r="D47" s="53" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G47" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H47" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I47" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G47" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H47" s="49" t="n"/>
+      <c r="I47" s="49" t="n"/>
       <c r="J47" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K47" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="51" t="n"/>
-      <c r="N47" s="51" t="n"/>
-      <c r="O47" s="51" t="n"/>
-      <c r="P47" s="51" t="n"/>
-      <c r="Q47" s="51" t="n"/>
-      <c r="R47" s="51" t="n"/>
-      <c r="S47" s="51" t="n"/>
-      <c r="T47" s="51" t="n"/>
-      <c r="U47" s="51" t="n"/>
-      <c r="V47" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W47" s="58" t="n"/>
+      <c r="M47" s="55" t="n"/>
+      <c r="N47" s="55" t="n"/>
+      <c r="O47" s="55" t="n"/>
+      <c r="P47" s="55" t="n"/>
+      <c r="Q47" s="55" t="n"/>
+      <c r="R47" s="55" t="n"/>
+      <c r="S47" s="55" t="n"/>
+      <c r="T47" s="55" t="n"/>
+      <c r="U47" s="55" t="n"/>
+      <c r="V47" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W47" s="57" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
+      <c r="C48" s="46" t="n"/>
+      <c r="D48" s="46" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G48" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H48" s="49" t="n"/>
-      <c r="I48" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H48" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I48" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J48" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K48" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="55" t="n"/>
-      <c r="N48" s="55" t="n"/>
-      <c r="O48" s="55" t="n"/>
-      <c r="P48" s="55" t="n"/>
-      <c r="Q48" s="55" t="n"/>
-      <c r="R48" s="55" t="n"/>
-      <c r="S48" s="55" t="n"/>
-      <c r="T48" s="55" t="n"/>
-      <c r="U48" s="55" t="n"/>
-      <c r="V48" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W48" s="57" t="n"/>
+      <c r="M48" s="51" t="n"/>
+      <c r="N48" s="51" t="n"/>
+      <c r="O48" s="51" t="n"/>
+      <c r="P48" s="51" t="n"/>
+      <c r="Q48" s="51" t="n"/>
+      <c r="R48" s="51" t="n"/>
+      <c r="S48" s="51" t="n"/>
+      <c r="T48" s="51" t="n"/>
+      <c r="U48" s="51" t="n"/>
+      <c r="V48" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W48" s="58" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="46" t="n"/>
-      <c r="D49" s="46" t="n"/>
+      <c r="C49" s="53" t="n"/>
+      <c r="D49" s="53" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G49" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H49" s="49" t="n"/>
       <c r="I49" s="49" t="n"/>
       <c r="J49" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K49" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="51" t="n"/>
-      <c r="N49" s="51" t="n"/>
-      <c r="O49" s="51" t="n"/>
-      <c r="P49" s="51" t="n"/>
-      <c r="Q49" s="51" t="n"/>
-      <c r="R49" s="51" t="n"/>
-      <c r="S49" s="51" t="n"/>
-      <c r="T49" s="51" t="n"/>
-      <c r="U49" s="51" t="n"/>
-      <c r="V49" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W49" s="58" t="n"/>
+      <c r="M49" s="55" t="n"/>
+      <c r="N49" s="55" t="n"/>
+      <c r="O49" s="55" t="n"/>
+      <c r="P49" s="55" t="n"/>
+      <c r="Q49" s="55" t="n"/>
+      <c r="R49" s="55" t="n"/>
+      <c r="S49" s="55" t="n"/>
+      <c r="T49" s="55" t="n"/>
+      <c r="U49" s="55" t="n"/>
+      <c r="V49" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W49" s="57" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="53" t="n"/>
-      <c r="D50" s="53" t="n"/>
+      <c r="C50" s="46" t="n"/>
+      <c r="D50" s="46" t="n"/>
       <c r="E50" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F50" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G50" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H50" s="49" t="n"/>
+      <c r="I50" s="49" t="n"/>
+      <c r="J50" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F50" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G50" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H50" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I50" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J50" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K50" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="55" t="n"/>
-      <c r="N50" s="55" t="n"/>
-      <c r="O50" s="55" t="n"/>
-      <c r="P50" s="55" t="n"/>
-      <c r="Q50" s="55" t="n"/>
-      <c r="R50" s="55" t="n"/>
-      <c r="S50" s="55" t="n"/>
-      <c r="T50" s="55" t="n"/>
-      <c r="U50" s="55" t="n"/>
-      <c r="V50" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W50" s="57" t="n"/>
+      <c r="M50" s="51" t="n"/>
+      <c r="N50" s="51" t="n"/>
+      <c r="O50" s="51" t="n"/>
+      <c r="P50" s="51" t="n"/>
+      <c r="Q50" s="51" t="n"/>
+      <c r="R50" s="51" t="n"/>
+      <c r="S50" s="51" t="n"/>
+      <c r="T50" s="51" t="n"/>
+      <c r="U50" s="51" t="n"/>
+      <c r="V50" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W50" s="58" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="46" t="n"/>
-      <c r="D51" s="46" t="n"/>
+      <c r="C51" s="53" t="n"/>
+      <c r="D51" s="53" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G51" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H51" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I51" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J51" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="51" t="n"/>
-      <c r="N51" s="51" t="n"/>
-      <c r="O51" s="51" t="n"/>
-      <c r="P51" s="51" t="n"/>
-      <c r="Q51" s="51" t="n"/>
-      <c r="R51" s="51" t="n"/>
-      <c r="S51" s="51" t="n"/>
-      <c r="T51" s="51" t="n"/>
-      <c r="U51" s="51" t="n"/>
-      <c r="V51" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W51" s="58" t="n"/>
+      <c r="M51" s="55" t="n"/>
+      <c r="N51" s="55" t="n"/>
+      <c r="O51" s="55" t="n"/>
+      <c r="P51" s="55" t="n"/>
+      <c r="Q51" s="55" t="n"/>
+      <c r="R51" s="55" t="n"/>
+      <c r="S51" s="55" t="n"/>
+      <c r="T51" s="55" t="n"/>
+      <c r="U51" s="55" t="n"/>
+      <c r="V51" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W51" s="57" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="53" t="n"/>
-      <c r="D52" s="53" t="n"/>
+      <c r="C52" s="46" t="n"/>
+      <c r="D52" s="46" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G52" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H52" s="49" t="n"/>
-      <c r="I52" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H52" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I52" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J52" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="55" t="n"/>
-      <c r="N52" s="55" t="n"/>
-      <c r="O52" s="55" t="n"/>
-      <c r="P52" s="55" t="n"/>
-      <c r="Q52" s="55" t="n"/>
-      <c r="R52" s="55" t="n"/>
-      <c r="S52" s="55" t="n"/>
-      <c r="T52" s="55" t="n"/>
-      <c r="U52" s="55" t="n"/>
-      <c r="V52" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W52" s="57" t="n"/>
+      <c r="M52" s="51" t="n"/>
+      <c r="N52" s="51" t="n"/>
+      <c r="O52" s="51" t="n"/>
+      <c r="P52" s="51" t="n"/>
+      <c r="Q52" s="51" t="n"/>
+      <c r="R52" s="51" t="n"/>
+      <c r="S52" s="51" t="n"/>
+      <c r="T52" s="51" t="n"/>
+      <c r="U52" s="51" t="n"/>
+      <c r="V52" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W52" s="58" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="46" t="n"/>
-      <c r="D53" s="46" t="n"/>
+      <c r="C53" s="53" t="n"/>
+      <c r="D53" s="53" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G53" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G53" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H53" s="49" t="n"/>
       <c r="I53" s="49" t="n"/>
       <c r="J53" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K53" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="51" t="n"/>
-      <c r="N53" s="51" t="n"/>
-      <c r="O53" s="51" t="n"/>
-      <c r="P53" s="51" t="n"/>
-      <c r="Q53" s="51" t="n"/>
-      <c r="R53" s="51" t="n"/>
-      <c r="S53" s="51" t="n"/>
-      <c r="T53" s="51" t="n"/>
-      <c r="U53" s="51" t="n"/>
-      <c r="V53" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W53" s="58" t="n"/>
+      <c r="M53" s="55" t="n"/>
+      <c r="N53" s="55" t="n"/>
+      <c r="O53" s="55" t="n"/>
+      <c r="P53" s="55" t="n"/>
+      <c r="Q53" s="55" t="n"/>
+      <c r="R53" s="55" t="n"/>
+      <c r="S53" s="55" t="n"/>
+      <c r="T53" s="55" t="n"/>
+      <c r="U53" s="55" t="n"/>
+      <c r="V53" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W53" s="57" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="53" t="n"/>
-      <c r="D54" s="53" t="n"/>
+      <c r="C54" s="46" t="n"/>
+      <c r="D54" s="46" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G54" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G54" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="55" t="n"/>
-      <c r="N54" s="55" t="n"/>
-      <c r="O54" s="55" t="n"/>
-      <c r="P54" s="55" t="n"/>
-      <c r="Q54" s="55" t="n"/>
-      <c r="R54" s="55" t="n"/>
-      <c r="S54" s="55" t="n"/>
-      <c r="T54" s="55" t="n"/>
-      <c r="U54" s="55" t="n"/>
-      <c r="V54" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W54" s="57" t="n"/>
+      <c r="M54" s="51" t="n"/>
+      <c r="N54" s="51" t="n"/>
+      <c r="O54" s="51" t="n"/>
+      <c r="P54" s="51" t="n"/>
+      <c r="Q54" s="51" t="n"/>
+      <c r="R54" s="51" t="n"/>
+      <c r="S54" s="51" t="n"/>
+      <c r="T54" s="51" t="n"/>
+      <c r="U54" s="51" t="n"/>
+      <c r="V54" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W54" s="58" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="46" t="n"/>
-      <c r="D55" s="46" t="n"/>
+      <c r="C55" s="53" t="n"/>
+      <c r="D55" s="53" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G55" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="51" t="n"/>
-      <c r="N55" s="51" t="n"/>
-      <c r="O55" s="51" t="n"/>
-      <c r="P55" s="51" t="n"/>
-      <c r="Q55" s="51" t="n"/>
-      <c r="R55" s="51" t="n"/>
-      <c r="S55" s="51" t="n"/>
-      <c r="T55" s="51" t="n"/>
-      <c r="U55" s="51" t="n"/>
-      <c r="V55" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W55" s="58" t="n"/>
+      <c r="M55" s="55" t="n"/>
+      <c r="N55" s="55" t="n"/>
+      <c r="O55" s="55" t="n"/>
+      <c r="P55" s="55" t="n"/>
+      <c r="Q55" s="55" t="n"/>
+      <c r="R55" s="55" t="n"/>
+      <c r="S55" s="55" t="n"/>
+      <c r="T55" s="55" t="n"/>
+      <c r="U55" s="55" t="n"/>
+      <c r="V55" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W55" s="57" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="53" t="n"/>
-      <c r="D56" s="53" t="n"/>
+      <c r="C56" s="46" t="n"/>
+      <c r="D56" s="46" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G56" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G56" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="55" t="n"/>
-      <c r="N56" s="55" t="n"/>
-      <c r="O56" s="55" t="n"/>
-      <c r="P56" s="55" t="n"/>
-      <c r="Q56" s="55" t="n"/>
-      <c r="R56" s="55" t="n"/>
-      <c r="S56" s="55" t="n"/>
-      <c r="T56" s="55" t="n"/>
-      <c r="U56" s="55" t="n"/>
-      <c r="V56" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W56" s="57" t="n"/>
+      <c r="M56" s="51" t="n"/>
+      <c r="N56" s="51" t="n"/>
+      <c r="O56" s="51" t="n"/>
+      <c r="P56" s="51" t="n"/>
+      <c r="Q56" s="51" t="n"/>
+      <c r="R56" s="51" t="n"/>
+      <c r="S56" s="51" t="n"/>
+      <c r="T56" s="51" t="n"/>
+      <c r="U56" s="51" t="n"/>
+      <c r="V56" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W56" s="58" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="46" t="n"/>
-      <c r="D57" s="46" t="n"/>
+      <c r="C57" s="53" t="n"/>
+      <c r="D57" s="53" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G57" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G57" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="51" t="n"/>
-      <c r="N57" s="51" t="n"/>
-      <c r="O57" s="51" t="n"/>
-      <c r="P57" s="51" t="n"/>
-      <c r="Q57" s="51" t="n"/>
-      <c r="R57" s="51" t="n"/>
-      <c r="S57" s="51" t="n"/>
-      <c r="T57" s="51" t="n"/>
-      <c r="U57" s="51" t="n"/>
-      <c r="V57" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W57" s="58" t="n"/>
+      <c r="M57" s="55" t="n"/>
+      <c r="N57" s="55" t="n"/>
+      <c r="O57" s="55" t="n"/>
+      <c r="P57" s="55" t="n"/>
+      <c r="Q57" s="55" t="n"/>
+      <c r="R57" s="55" t="n"/>
+      <c r="S57" s="55" t="n"/>
+      <c r="T57" s="55" t="n"/>
+      <c r="U57" s="55" t="n"/>
+      <c r="V57" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W57" s="57" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="53" t="n"/>
-      <c r="D58" s="53" t="n"/>
+      <c r="C58" s="46" t="n"/>
+      <c r="D58" s="46" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G58" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G58" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="55" t="n"/>
-      <c r="N58" s="55" t="n"/>
-      <c r="O58" s="55" t="n"/>
-      <c r="P58" s="55" t="n"/>
-      <c r="Q58" s="55" t="n"/>
-      <c r="R58" s="55" t="n"/>
-      <c r="S58" s="55" t="n"/>
-      <c r="T58" s="55" t="n"/>
-      <c r="U58" s="55" t="n"/>
-      <c r="V58" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W58" s="57" t="n"/>
+      <c r="M58" s="51" t="n"/>
+      <c r="N58" s="51" t="n"/>
+      <c r="O58" s="51" t="n"/>
+      <c r="P58" s="51" t="n"/>
+      <c r="Q58" s="51" t="n"/>
+      <c r="R58" s="51" t="n"/>
+      <c r="S58" s="51" t="n"/>
+      <c r="T58" s="51" t="n"/>
+      <c r="U58" s="51" t="n"/>
+      <c r="V58" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W58" s="58" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="46" t="n"/>
-      <c r="D59" s="46" t="n"/>
+      <c r="C59" s="53" t="n"/>
+      <c r="D59" s="53" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G59" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="51" t="n"/>
-      <c r="N59" s="51" t="n"/>
-      <c r="O59" s="51" t="n"/>
-      <c r="P59" s="51" t="n"/>
-      <c r="Q59" s="51" t="n"/>
-      <c r="R59" s="51" t="n"/>
-      <c r="S59" s="51" t="n"/>
-      <c r="T59" s="51" t="n"/>
-      <c r="U59" s="51" t="n"/>
-      <c r="V59" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W59" s="58" t="n"/>
+      <c r="M59" s="55" t="n"/>
+      <c r="N59" s="55" t="n"/>
+      <c r="O59" s="55" t="n"/>
+      <c r="P59" s="55" t="n"/>
+      <c r="Q59" s="55" t="n"/>
+      <c r="R59" s="55" t="n"/>
+      <c r="S59" s="55" t="n"/>
+      <c r="T59" s="55" t="n"/>
+      <c r="U59" s="55" t="n"/>
+      <c r="V59" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W59" s="57" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
+      <c r="C60" s="46" t="n"/>
+      <c r="D60" s="46" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G60" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="55" t="n"/>
-      <c r="N60" s="55" t="n"/>
-      <c r="O60" s="55" t="n"/>
-      <c r="P60" s="55" t="n"/>
-      <c r="Q60" s="55" t="n"/>
-      <c r="R60" s="55" t="n"/>
-      <c r="S60" s="55" t="n"/>
-      <c r="T60" s="55" t="n"/>
-      <c r="U60" s="55" t="n"/>
-      <c r="V60" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W60" s="57" t="n"/>
+      <c r="M60" s="51" t="n"/>
+      <c r="N60" s="51" t="n"/>
+      <c r="O60" s="51" t="n"/>
+      <c r="P60" s="51" t="n"/>
+      <c r="Q60" s="51" t="n"/>
+      <c r="R60" s="51" t="n"/>
+      <c r="S60" s="51" t="n"/>
+      <c r="T60" s="51" t="n"/>
+      <c r="U60" s="51" t="n"/>
+      <c r="V60" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W60" s="58" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="46" t="n"/>
-      <c r="D61" s="46" t="n"/>
+      <c r="C61" s="53" t="n"/>
+      <c r="D61" s="53" t="n"/>
       <c r="E61" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F61" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G61" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G61" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
       <c r="J61" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K61" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="51" t="n"/>
-      <c r="N61" s="51" t="n"/>
-      <c r="O61" s="51" t="n"/>
-      <c r="P61" s="51" t="n"/>
-      <c r="Q61" s="51" t="n"/>
-      <c r="R61" s="51" t="n"/>
-      <c r="S61" s="51" t="n"/>
-      <c r="T61" s="51" t="n"/>
-      <c r="U61" s="51" t="n"/>
-      <c r="V61" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W61" s="58" t="n"/>
+      <c r="M61" s="55" t="n"/>
+      <c r="N61" s="55" t="n"/>
+      <c r="O61" s="55" t="n"/>
+      <c r="P61" s="55" t="n"/>
+      <c r="Q61" s="55" t="n"/>
+      <c r="R61" s="55" t="n"/>
+      <c r="S61" s="55" t="n"/>
+      <c r="T61" s="55" t="n"/>
+      <c r="U61" s="55" t="n"/>
+      <c r="V61" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W61" s="57" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B62" s="45" t="n"/>
-      <c r="C62" s="53" t="n"/>
-      <c r="D62" s="53" t="n"/>
+      <c r="C62" s="46" t="n"/>
+      <c r="D62" s="46" t="n"/>
       <c r="E62" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F62" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G62" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G62" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="49" t="n"/>
       <c r="J62" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K62" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L62" s="50" t="n"/>
-      <c r="M62" s="55" t="n"/>
-      <c r="N62" s="55" t="n"/>
-      <c r="O62" s="55" t="n"/>
-      <c r="P62" s="55" t="n"/>
-      <c r="Q62" s="55" t="n"/>
-      <c r="R62" s="55" t="n"/>
-      <c r="S62" s="55" t="n"/>
-      <c r="T62" s="55" t="n"/>
-      <c r="U62" s="55" t="n"/>
-      <c r="V62" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W62" s="57" t="n"/>
+      <c r="M62" s="51" t="n"/>
+      <c r="N62" s="51" t="n"/>
+      <c r="O62" s="51" t="n"/>
+      <c r="P62" s="51" t="n"/>
+      <c r="Q62" s="51" t="n"/>
+      <c r="R62" s="51" t="n"/>
+      <c r="S62" s="51" t="n"/>
+      <c r="T62" s="51" t="n"/>
+      <c r="U62" s="51" t="n"/>
+      <c r="V62" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W62" s="58" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B63" s="45" t="n"/>
-      <c r="C63" s="46" t="n"/>
-      <c r="D63" s="46" t="n"/>
+      <c r="C63" s="53" t="n"/>
+      <c r="D63" s="53" t="n"/>
       <c r="E63" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F63" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G63" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G63" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="49" t="n"/>
       <c r="J63" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K63" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L63" s="50" t="n"/>
-      <c r="M63" s="51" t="n"/>
-      <c r="N63" s="51" t="n"/>
-      <c r="O63" s="51" t="n"/>
-      <c r="P63" s="51" t="n"/>
-      <c r="Q63" s="51" t="n"/>
-      <c r="R63" s="51" t="n"/>
-      <c r="S63" s="51" t="n"/>
-      <c r="T63" s="51" t="n"/>
-      <c r="U63" s="51" t="n"/>
-      <c r="V63" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W63" s="58" t="n"/>
+      <c r="M63" s="55" t="n"/>
+      <c r="N63" s="55" t="n"/>
+      <c r="O63" s="55" t="n"/>
+      <c r="P63" s="55" t="n"/>
+      <c r="Q63" s="55" t="n"/>
+      <c r="R63" s="55" t="n"/>
+      <c r="S63" s="55" t="n"/>
+      <c r="T63" s="55" t="n"/>
+      <c r="U63" s="55" t="n"/>
+      <c r="V63" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W63" s="57" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B64" s="45" t="n"/>
-      <c r="C64" s="53" t="n"/>
-      <c r="D64" s="53" t="n"/>
+      <c r="C64" s="46" t="n"/>
+      <c r="D64" s="46" t="n"/>
       <c r="E64" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F64" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G64" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G64" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="49" t="n"/>
       <c r="J64" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K64" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L64" s="50" t="n"/>
-      <c r="M64" s="55" t="n"/>
-      <c r="N64" s="55" t="n"/>
-      <c r="O64" s="55" t="n"/>
-      <c r="P64" s="55" t="n"/>
-      <c r="Q64" s="55" t="n"/>
-      <c r="R64" s="55" t="n"/>
-      <c r="S64" s="55" t="n"/>
-      <c r="T64" s="55" t="n"/>
-      <c r="U64" s="55" t="n"/>
-      <c r="V64" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W64" s="57" t="n"/>
+      <c r="M64" s="51" t="n"/>
+      <c r="N64" s="51" t="n"/>
+      <c r="O64" s="51" t="n"/>
+      <c r="P64" s="51" t="n"/>
+      <c r="Q64" s="51" t="n"/>
+      <c r="R64" s="51" t="n"/>
+      <c r="S64" s="51" t="n"/>
+      <c r="T64" s="51" t="n"/>
+      <c r="U64" s="51" t="n"/>
+      <c r="V64" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W64" s="58" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B65" s="45" t="n"/>
-      <c r="C65" s="46" t="n"/>
-      <c r="D65" s="46" t="n"/>
+      <c r="C65" s="53" t="n"/>
+      <c r="D65" s="53" t="n"/>
       <c r="E65" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F65" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G65" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G65" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H65" s="49" t="n"/>
       <c r="I65" s="49" t="n"/>
       <c r="J65" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K65" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L65" s="50" t="n"/>
-      <c r="M65" s="51" t="n"/>
-      <c r="N65" s="51" t="n"/>
-      <c r="O65" s="51" t="n"/>
-      <c r="P65" s="51" t="n"/>
-      <c r="Q65" s="51" t="n"/>
-      <c r="R65" s="51" t="n"/>
-      <c r="S65" s="51" t="n"/>
-      <c r="T65" s="51" t="n"/>
-      <c r="U65" s="51" t="n"/>
-      <c r="V65" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W65" s="58" t="n"/>
+      <c r="M65" s="55" t="n"/>
+      <c r="N65" s="55" t="n"/>
+      <c r="O65" s="55" t="n"/>
+      <c r="P65" s="55" t="n"/>
+      <c r="Q65" s="55" t="n"/>
+      <c r="R65" s="55" t="n"/>
+      <c r="S65" s="55" t="n"/>
+      <c r="T65" s="55" t="n"/>
+      <c r="U65" s="55" t="n"/>
+      <c r="V65" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W65" s="57" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B66" s="45" t="n"/>
-      <c r="C66" s="53" t="n"/>
-      <c r="D66" s="53" t="n"/>
+      <c r="C66" s="46" t="n"/>
+      <c r="D66" s="46" t="n"/>
       <c r="E66" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F66" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G66" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G66" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H66" s="49" t="n"/>
       <c r="I66" s="49" t="n"/>
       <c r="J66" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K66" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L66" s="50" t="n"/>
-      <c r="M66" s="55" t="n"/>
-      <c r="N66" s="55" t="n"/>
-      <c r="O66" s="55" t="n"/>
-      <c r="P66" s="55" t="n"/>
-      <c r="Q66" s="55" t="n"/>
-      <c r="R66" s="55" t="n"/>
-      <c r="S66" s="55" t="n"/>
-      <c r="T66" s="55" t="n"/>
-      <c r="U66" s="55" t="n"/>
-      <c r="V66" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W66" s="57" t="n"/>
+      <c r="M66" s="51" t="n"/>
+      <c r="N66" s="51" t="n"/>
+      <c r="O66" s="51" t="n"/>
+      <c r="P66" s="51" t="n"/>
+      <c r="Q66" s="51" t="n"/>
+      <c r="R66" s="51" t="n"/>
+      <c r="S66" s="51" t="n"/>
+      <c r="T66" s="51" t="n"/>
+      <c r="U66" s="51" t="n"/>
+      <c r="V66" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W66" s="58" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B67" s="45" t="n"/>
-      <c r="C67" s="46" t="n"/>
-      <c r="D67" s="46" t="n"/>
+      <c r="C67" s="53" t="n"/>
+      <c r="D67" s="53" t="n"/>
       <c r="E67" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F67" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G67" s="48" t="n">
-        <v>24</v>
+      <c r="G67" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H67" s="49" t="n"/>
       <c r="I67" s="49" t="n"/>
       <c r="J67" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K67" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L67" s="50" t="n"/>
-      <c r="M67" s="51" t="n"/>
-      <c r="N67" s="51" t="n"/>
-      <c r="O67" s="51" t="n"/>
-      <c r="P67" s="51" t="n"/>
-      <c r="Q67" s="51" t="n"/>
-      <c r="R67" s="51" t="n"/>
-      <c r="S67" s="51" t="n"/>
-      <c r="T67" s="51" t="n"/>
-      <c r="U67" s="51" t="n"/>
-      <c r="V67" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W67" s="58" t="n"/>
+      <c r="M67" s="55" t="n"/>
+      <c r="N67" s="55" t="n"/>
+      <c r="O67" s="55" t="n"/>
+      <c r="P67" s="55" t="n"/>
+      <c r="Q67" s="55" t="n"/>
+      <c r="R67" s="55" t="n"/>
+      <c r="S67" s="55" t="n"/>
+      <c r="T67" s="55" t="n"/>
+      <c r="U67" s="55" t="n"/>
+      <c r="V67" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W67" s="57" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B68" s="45" t="n"/>
-      <c r="C68" s="53" t="n"/>
-      <c r="D68" s="53" t="n"/>
+      <c r="C68" s="46" t="n"/>
+      <c r="D68" s="46" t="n"/>
       <c r="E68" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F68" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G68" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G68" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H68" s="49" t="n"/>
       <c r="I68" s="49" t="n"/>
       <c r="J68" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K68" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L68" s="50" t="n"/>
-      <c r="M68" s="55" t="n"/>
-      <c r="N68" s="55" t="n"/>
-      <c r="O68" s="55" t="n"/>
-      <c r="P68" s="55" t="n"/>
-      <c r="Q68" s="55" t="n"/>
-      <c r="R68" s="55" t="n"/>
-      <c r="S68" s="55" t="n"/>
-      <c r="T68" s="55" t="n"/>
-      <c r="U68" s="55" t="n"/>
-      <c r="V68" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W68" s="57" t="n"/>
+      <c r="M68" s="51" t="n"/>
+      <c r="N68" s="51" t="n"/>
+      <c r="O68" s="51" t="n"/>
+      <c r="P68" s="51" t="n"/>
+      <c r="Q68" s="51" t="n"/>
+      <c r="R68" s="51" t="n"/>
+      <c r="S68" s="51" t="n"/>
+      <c r="T68" s="51" t="n"/>
+      <c r="U68" s="51" t="n"/>
+      <c r="V68" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W68" s="58" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B69" s="45" t="n"/>
-      <c r="C69" s="46" t="n"/>
-      <c r="D69" s="46" t="n"/>
+      <c r="C69" s="53" t="n"/>
+      <c r="D69" s="53" t="n"/>
       <c r="E69" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F69" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G69" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G69" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H69" s="49" t="n"/>
       <c r="I69" s="49" t="n"/>
       <c r="J69" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K69" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L69" s="50" t="n"/>
-      <c r="M69" s="51" t="n"/>
-      <c r="N69" s="51" t="n"/>
-      <c r="O69" s="51" t="n"/>
-      <c r="P69" s="51" t="n"/>
-      <c r="Q69" s="51" t="n"/>
-      <c r="R69" s="51" t="n"/>
-      <c r="S69" s="51" t="n"/>
-      <c r="T69" s="51" t="n"/>
-      <c r="U69" s="51" t="n"/>
-      <c r="V69" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W69" s="58" t="n"/>
+      <c r="M69" s="55" t="n"/>
+      <c r="N69" s="55" t="n"/>
+      <c r="O69" s="55" t="n"/>
+      <c r="P69" s="55" t="n"/>
+      <c r="Q69" s="55" t="n"/>
+      <c r="R69" s="55" t="n"/>
+      <c r="S69" s="55" t="n"/>
+      <c r="T69" s="55" t="n"/>
+      <c r="U69" s="55" t="n"/>
+      <c r="V69" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W69" s="57" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B70" s="45" t="n"/>
-      <c r="C70" s="53" t="n"/>
-      <c r="D70" s="53" t="n"/>
+      <c r="C70" s="46" t="n"/>
+      <c r="D70" s="46" t="n"/>
       <c r="E70" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F70" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G70" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H70" s="49" t="n"/>
       <c r="I70" s="49" t="n"/>
@@ -5144,51 +5162,92 @@
         <v>59</v>
       </c>
       <c r="K70" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L70" s="50" t="n"/>
-      <c r="M70" s="55" t="n"/>
-      <c r="N70" s="55" t="n"/>
-      <c r="O70" s="55" t="n"/>
-      <c r="P70" s="55" t="n"/>
-      <c r="Q70" s="55" t="n"/>
-      <c r="R70" s="55" t="n"/>
-      <c r="S70" s="55" t="n"/>
-      <c r="T70" s="55" t="n"/>
-      <c r="U70" s="55" t="n"/>
-      <c r="V70" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W70" s="57" t="n"/>
+      <c r="M70" s="51" t="n"/>
+      <c r="N70" s="51" t="n"/>
+      <c r="O70" s="51" t="n"/>
+      <c r="P70" s="51" t="n"/>
+      <c r="Q70" s="51" t="n"/>
+      <c r="R70" s="51" t="n"/>
+      <c r="S70" s="51" t="n"/>
+      <c r="T70" s="51" t="n"/>
+      <c r="U70" s="51" t="n"/>
+      <c r="V70" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W70" s="58" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B71" s="45" t="n"/>
-      <c r="C71" s="46" t="n"/>
-      <c r="D71" s="46" t="n"/>
-      <c r="E71" s="47" t="n"/>
-      <c r="F71" s="47" t="n"/>
-      <c r="G71" s="60" t="n"/>
+      <c r="C71" s="53" t="n"/>
+      <c r="D71" s="53" t="n"/>
+      <c r="E71" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F71" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G71" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H71" s="49" t="n"/>
       <c r="I71" s="49" t="n"/>
-      <c r="J71" s="50" t="n"/>
-      <c r="K71" s="50" t="n"/>
+      <c r="J71" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K71" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L71" s="50" t="n"/>
-      <c r="M71" s="51" t="n"/>
-      <c r="N71" s="51" t="n"/>
-      <c r="O71" s="51" t="n"/>
-      <c r="P71" s="51" t="n"/>
-      <c r="Q71" s="51" t="n"/>
-      <c r="R71" s="51" t="n"/>
-      <c r="S71" s="51" t="n"/>
-      <c r="T71" s="51" t="n"/>
-      <c r="U71" s="51" t="n"/>
-      <c r="V71" s="61" t="n"/>
-      <c r="W71" s="61" t="n"/>
+      <c r="M71" s="55" t="n"/>
+      <c r="N71" s="55" t="n"/>
+      <c r="O71" s="55" t="n"/>
+      <c r="P71" s="55" t="n"/>
+      <c r="Q71" s="55" t="n"/>
+      <c r="R71" s="55" t="n"/>
+      <c r="S71" s="55" t="n"/>
+      <c r="T71" s="55" t="n"/>
+      <c r="U71" s="55" t="n"/>
+      <c r="V71" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W71" s="57" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B72" s="45" t="n"/>
+      <c r="C72" s="46" t="n"/>
+      <c r="D72" s="46" t="n"/>
+      <c r="E72" s="47" t="n"/>
+      <c r="F72" s="47" t="n"/>
+      <c r="G72" s="60" t="n"/>
+      <c r="H72" s="49" t="n"/>
+      <c r="I72" s="49" t="n"/>
+      <c r="J72" s="50" t="n"/>
+      <c r="K72" s="50" t="n"/>
+      <c r="L72" s="50" t="n"/>
+      <c r="M72" s="51" t="n"/>
+      <c r="N72" s="51" t="n"/>
+      <c r="O72" s="51" t="n"/>
+      <c r="P72" s="51" t="n"/>
+      <c r="Q72" s="51" t="n"/>
+      <c r="R72" s="51" t="n"/>
+      <c r="S72" s="51" t="n"/>
+      <c r="T72" s="51" t="n"/>
+      <c r="U72" s="51" t="n"/>
+      <c r="V72" s="61" t="n"/>
+      <c r="W72" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W72"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,193 +1982,197 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/16(四)</t>
+          <t>2026/04/17(五)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G4" s="66" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="H4" s="67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" s="67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" s="68" t="n">
+        <v>13</v>
+      </c>
+      <c r="K4" s="68" t="n">
+        <v>58</v>
+      </c>
+      <c r="L4" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="K4" s="68" t="n">
-        <v>71</v>
-      </c>
-      <c r="L4" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="M4" s="69" t="inlineStr">
         <is>
+          <t>均瑶健康、京投发展</t>
+        </is>
+      </c>
+      <c r="N4" s="69" t="inlineStr">
+        <is>
           <t>盛视科技</t>
         </is>
       </c>
-      <c r="N4" s="69" t="inlineStr">
+      <c r="O4" s="69" t="inlineStr">
         <is>
           <t>博云新材</t>
         </is>
       </c>
-      <c r="O4" s="69" t="inlineStr"/>
-      <c r="P4" s="69" t="inlineStr">
+      <c r="P4" s="69" t="inlineStr"/>
+      <c r="Q4" s="69" t="inlineStr">
         <is>
           <t>圣阳股份</t>
         </is>
       </c>
-      <c r="Q4" s="69" t="inlineStr"/>
       <c r="R4" s="69" t="inlineStr"/>
       <c r="S4" s="69" t="inlineStr"/>
       <c r="T4" s="69" t="inlineStr"/>
       <c r="U4" s="69" t="inlineStr"/>
       <c r="V4" s="69" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="W4" s="69" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/15(三)</t>
+          <t>2026/04/16(四)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
       <c r="C5" s="64" t="inlineStr"/>
       <c r="D5" s="64" t="inlineStr"/>
       <c r="E5" s="65" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>57</v>
-      </c>
-      <c r="G5" s="71" t="n">
-        <v>29.6</v>
+        <v>79</v>
+      </c>
+      <c r="G5" s="66" t="n">
+        <v>22.5</v>
       </c>
       <c r="H5" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I5" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" s="68" t="n">
-        <v>11</v>
-      </c>
       <c r="K5" s="68" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="L5" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M5" s="69" t="inlineStr">
         <is>
-          <t>博云新材、天邦食品</t>
-        </is>
-      </c>
-      <c r="N5" s="69" t="inlineStr"/>
-      <c r="O5" s="69" t="inlineStr">
+          <t>盛视科技</t>
+        </is>
+      </c>
+      <c r="N5" s="69" t="inlineStr">
+        <is>
+          <t>博云新材</t>
+        </is>
+      </c>
+      <c r="O5" s="69" t="inlineStr"/>
+      <c r="P5" s="69" t="inlineStr">
         <is>
           <t>圣阳股份</t>
         </is>
       </c>
-      <c r="P5" s="69" t="inlineStr"/>
       <c r="Q5" s="69" t="inlineStr"/>
       <c r="R5" s="69" t="inlineStr"/>
       <c r="S5" s="69" t="inlineStr"/>
       <c r="T5" s="69" t="inlineStr"/>
       <c r="U5" s="69" t="inlineStr"/>
       <c r="V5" s="69" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="W5" s="69" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/04/14(二)</t>
+          <t>2026/04/15(三)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
       <c r="C6" s="64" t="inlineStr"/>
       <c r="D6" s="64" t="inlineStr"/>
       <c r="E6" s="65" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>55</v>
-      </c>
-      <c r="G6" s="66" t="n">
-        <v>24.7</v>
+        <v>57</v>
+      </c>
+      <c r="G6" s="71" t="n">
+        <v>29.6</v>
       </c>
       <c r="H6" s="67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I6" s="67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J6" s="68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" s="68" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L6" s="68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M6" s="69" t="inlineStr">
         <is>
-          <t>美能能源</t>
-        </is>
-      </c>
-      <c r="N6" s="69" t="inlineStr">
-        <is>
-          <t>中恒电气、圣阳股份</t>
-        </is>
-      </c>
-      <c r="O6" s="69" t="inlineStr"/>
-      <c r="P6" s="69" t="inlineStr">
-        <is>
-          <t>华远控股</t>
-        </is>
-      </c>
+          <t>博云新材、天邦食品</t>
+        </is>
+      </c>
+      <c r="N6" s="69" t="inlineStr"/>
+      <c r="O6" s="69" t="inlineStr">
+        <is>
+          <t>圣阳股份</t>
+        </is>
+      </c>
+      <c r="P6" s="69" t="inlineStr"/>
       <c r="Q6" s="69" t="inlineStr"/>
       <c r="R6" s="69" t="inlineStr"/>
       <c r="S6" s="69" t="inlineStr"/>
       <c r="T6" s="69" t="inlineStr"/>
       <c r="U6" s="69" t="inlineStr"/>
       <c r="V6" s="69" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="W6" s="69" t="inlineStr"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="62" t="inlineStr">
         <is>
-          <t>2026/04/13(一)</t>
+          <t>2026/04/14(二)</t>
         </is>
       </c>
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="64" t="inlineStr"/>
       <c r="D7" s="64" t="inlineStr"/>
       <c r="E7" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F7" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G7" s="66" t="n">
-        <v>20.3</v>
+        <v>24.7</v>
       </c>
       <c r="H7" s="67" t="n">
         <v>4</v>
@@ -2177,30 +2181,30 @@
         <v>4</v>
       </c>
       <c r="J7" s="68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K7" s="68" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L7" s="68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M7" s="69" t="inlineStr">
         <is>
+          <t>美能能源</t>
+        </is>
+      </c>
+      <c r="N7" s="69" t="inlineStr">
+        <is>
           <t>中恒电气、圣阳股份</t>
         </is>
       </c>
-      <c r="N7" s="69" t="inlineStr">
-        <is>
-          <t>长源东谷</t>
-        </is>
-      </c>
-      <c r="O7" s="69" t="inlineStr">
+      <c r="O7" s="69" t="inlineStr"/>
+      <c r="P7" s="69" t="inlineStr">
         <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="P7" s="69" t="inlineStr"/>
       <c r="Q7" s="69" t="inlineStr"/>
       <c r="R7" s="69" t="inlineStr"/>
       <c r="S7" s="69" t="inlineStr"/>
@@ -2214,7 +2218,7 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="62" t="inlineStr">
         <is>
-          <t>2026/04/10(五)</t>
+          <t>2026/04/13(一)</t>
         </is>
       </c>
       <c r="B8" s="63" t="inlineStr"/>
@@ -2226,35 +2230,39 @@
       <c r="F8" s="65" t="n">
         <v>59</v>
       </c>
-      <c r="G8" s="71" t="n">
-        <v>31.4</v>
+      <c r="G8" s="66" t="n">
+        <v>20.3</v>
       </c>
       <c r="H8" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I8" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" s="68" t="n">
-        <v>13</v>
-      </c>
       <c r="K8" s="68" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L8" s="68" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M8" s="69" t="inlineStr">
         <is>
-          <t>中嘉博创、长源东谷、来伊份</t>
+          <t>中恒电气、圣阳股份</t>
         </is>
       </c>
       <c r="N8" s="69" t="inlineStr">
         <is>
+          <t>长源东谷</t>
+        </is>
+      </c>
+      <c r="O8" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="O8" s="69" t="inlineStr"/>
       <c r="P8" s="69" t="inlineStr"/>
       <c r="Q8" s="69" t="inlineStr"/>
       <c r="R8" s="69" t="inlineStr"/>
@@ -2262,54 +2270,54 @@
       <c r="T8" s="69" t="inlineStr"/>
       <c r="U8" s="69" t="inlineStr"/>
       <c r="V8" s="69" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="W8" s="69" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="62" t="inlineStr">
         <is>
-          <t>2026/04/09(四)</t>
+          <t>2026/04/10(五)</t>
         </is>
       </c>
       <c r="B9" s="63" t="inlineStr"/>
       <c r="C9" s="64" t="inlineStr"/>
       <c r="D9" s="64" t="inlineStr"/>
       <c r="E9" s="65" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F9" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G9" s="66" t="n">
-        <v>23.2</v>
+        <v>59</v>
+      </c>
+      <c r="G9" s="71" t="n">
+        <v>31.4</v>
       </c>
       <c r="H9" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I9" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J9" s="68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K9" s="68" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L9" s="68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M9" s="69" t="inlineStr">
         <is>
+          <t>中嘉博创、长源东谷、来伊份</t>
+        </is>
+      </c>
+      <c r="N9" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="N9" s="69" t="inlineStr"/>
-      <c r="O9" s="69" t="inlineStr">
-        <is>
-          <t>汇源通信</t>
-        </is>
-      </c>
+      <c r="O9" s="69" t="inlineStr"/>
       <c r="P9" s="69" t="inlineStr"/>
       <c r="Q9" s="69" t="inlineStr"/>
       <c r="R9" s="69" t="inlineStr"/>
@@ -2317,54 +2325,54 @@
       <c r="T9" s="69" t="inlineStr"/>
       <c r="U9" s="69" t="inlineStr"/>
       <c r="V9" s="69" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="W9" s="69" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="62" t="inlineStr">
         <is>
-          <t>2026/04/08(三)</t>
+          <t>2026/04/09(四)</t>
         </is>
       </c>
       <c r="B10" s="63" t="inlineStr"/>
       <c r="C10" s="64" t="inlineStr"/>
       <c r="D10" s="64" t="inlineStr"/>
       <c r="E10" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="F10" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="G10" s="66" t="n">
-        <v>11.5</v>
+        <v>23.2</v>
       </c>
       <c r="H10" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I10" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J10" s="68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K10" s="68" t="n">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="L10" s="68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M10" s="69" t="inlineStr">
         <is>
-          <t>中安科</t>
-        </is>
-      </c>
-      <c r="N10" s="69" t="inlineStr">
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="N10" s="69" t="inlineStr"/>
+      <c r="O10" s="69" t="inlineStr">
         <is>
           <t>汇源通信</t>
         </is>
       </c>
-      <c r="O10" s="69" t="inlineStr"/>
       <c r="P10" s="69" t="inlineStr"/>
       <c r="Q10" s="69" t="inlineStr"/>
       <c r="R10" s="69" t="inlineStr"/>
@@ -2379,20 +2387,20 @@
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="62" t="inlineStr">
         <is>
-          <t>2026/04/07(二)</t>
+          <t>2026/04/08(三)</t>
         </is>
       </c>
       <c r="B11" s="63" t="inlineStr"/>
       <c r="C11" s="64" t="inlineStr"/>
       <c r="D11" s="64" t="inlineStr"/>
       <c r="E11" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F11" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G11" s="66" t="n">
-        <v>21.8</v>
+        <v>11.5</v>
       </c>
       <c r="H11" s="67" t="n">
         <v>4</v>
@@ -2401,91 +2409,95 @@
         <v>4</v>
       </c>
       <c r="J11" s="68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K11" s="68" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="L11" s="68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M11" s="69" t="inlineStr">
         <is>
-          <t>汇源通信、新能泰山</t>
-        </is>
-      </c>
-      <c r="N11" s="69" t="inlineStr"/>
+          <t>中安科</t>
+        </is>
+      </c>
+      <c r="N11" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信</t>
+        </is>
+      </c>
       <c r="O11" s="69" t="inlineStr"/>
       <c r="P11" s="69" t="inlineStr"/>
-      <c r="Q11" s="69" t="inlineStr">
-        <is>
-          <t>津药药业</t>
-        </is>
-      </c>
+      <c r="Q11" s="69" t="inlineStr"/>
       <c r="R11" s="69" t="inlineStr"/>
       <c r="S11" s="69" t="inlineStr"/>
       <c r="T11" s="69" t="inlineStr"/>
       <c r="U11" s="69" t="inlineStr"/>
       <c r="V11" s="69" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W11" s="69" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="62" t="inlineStr">
         <is>
-          <t>2026/04/06(一)</t>
+          <t>2026/04/07(二)</t>
         </is>
       </c>
       <c r="B12" s="63" t="inlineStr"/>
       <c r="C12" s="64" t="inlineStr"/>
       <c r="D12" s="64" t="inlineStr"/>
       <c r="E12" s="65" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F12" s="65" t="n">
-        <v>36</v>
-      </c>
-      <c r="G12" s="71" t="n">
-        <v>25</v>
+        <v>93</v>
+      </c>
+      <c r="G12" s="66" t="n">
+        <v>21.8</v>
       </c>
       <c r="H12" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I12" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J12" s="68" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="L12" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K12" s="68" t="n">
-        <v>32</v>
-      </c>
-      <c r="L12" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="M12" s="69" t="inlineStr"/>
+      <c r="M12" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信、新能泰山</t>
+        </is>
+      </c>
       <c r="N12" s="69" t="inlineStr"/>
       <c r="O12" s="69" t="inlineStr"/>
-      <c r="P12" s="69" t="inlineStr">
+      <c r="P12" s="69" t="inlineStr"/>
+      <c r="Q12" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="Q12" s="69" t="inlineStr"/>
       <c r="R12" s="69" t="inlineStr"/>
       <c r="S12" s="69" t="inlineStr"/>
       <c r="T12" s="69" t="inlineStr"/>
       <c r="U12" s="69" t="inlineStr"/>
       <c r="V12" s="69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W12" s="69" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="62" t="inlineStr">
         <is>
-          <t>2026/04/03(五)</t>
+          <t>2026/04/06(一)</t>
         </is>
       </c>
       <c r="B13" s="63" t="inlineStr"/>
@@ -2529,105 +2541,105 @@
       <c r="T13" s="69" t="inlineStr"/>
       <c r="U13" s="69" t="inlineStr"/>
       <c r="V13" s="69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W13" s="69" t="inlineStr"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B14" s="63" t="inlineStr"/>
       <c r="C14" s="64" t="inlineStr"/>
       <c r="D14" s="64" t="inlineStr"/>
       <c r="E14" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F14" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G14" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H14" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I14" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J14" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K14" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L14" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M14" s="69" t="inlineStr"/>
       <c r="N14" s="69" t="inlineStr"/>
-      <c r="O14" s="69" t="inlineStr">
+      <c r="O14" s="69" t="inlineStr"/>
+      <c r="P14" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P14" s="69" t="inlineStr"/>
       <c r="Q14" s="69" t="inlineStr"/>
       <c r="R14" s="69" t="inlineStr"/>
       <c r="S14" s="69" t="inlineStr"/>
       <c r="T14" s="69" t="inlineStr"/>
       <c r="U14" s="69" t="inlineStr"/>
       <c r="V14" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W14" s="69" t="inlineStr"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B15" s="63" t="inlineStr"/>
       <c r="C15" s="64" t="inlineStr"/>
       <c r="D15" s="64" t="inlineStr"/>
       <c r="E15" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F15" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G15" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G15" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H15" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I15" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K15" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L15" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M15" s="69" t="inlineStr"/>
-      <c r="N15" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M15" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N15" s="69" t="inlineStr"/>
+      <c r="O15" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O15" s="69" t="inlineStr"/>
       <c r="P15" s="69" t="inlineStr"/>
       <c r="Q15" s="69" t="inlineStr"/>
       <c r="R15" s="69" t="inlineStr"/>
@@ -2635,51 +2647,47 @@
       <c r="T15" s="69" t="inlineStr"/>
       <c r="U15" s="69" t="inlineStr"/>
       <c r="V15" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W15" s="69" t="inlineStr"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B16" s="63" t="inlineStr"/>
       <c r="C16" s="64" t="inlineStr"/>
       <c r="D16" s="64" t="inlineStr"/>
       <c r="E16" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F16" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G16" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G16" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H16" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I16" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J16" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K16" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L16" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M16" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M16" s="69" t="inlineStr"/>
+      <c r="N16" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N16" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O16" s="69" t="inlineStr"/>
@@ -2690,254 +2698,250 @@
       <c r="T16" s="69" t="inlineStr"/>
       <c r="U16" s="69" t="inlineStr"/>
       <c r="V16" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W16" s="69" t="inlineStr"/>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr"/>
+      <c r="C17" s="64" t="inlineStr"/>
+      <c r="D17" s="64" t="inlineStr"/>
+      <c r="E17" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F17" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G17" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L17" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M17" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N17" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O17" s="69" t="inlineStr"/>
+      <c r="P17" s="69" t="inlineStr"/>
+      <c r="Q17" s="69" t="inlineStr"/>
+      <c r="R17" s="69" t="inlineStr"/>
+      <c r="S17" s="69" t="inlineStr"/>
+      <c r="T17" s="69" t="inlineStr"/>
+      <c r="U17" s="69" t="inlineStr"/>
+      <c r="V17" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="69" t="inlineStr"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="36" t="inlineStr">
+      <c r="W17" s="69" t="inlineStr"/>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D17" s="38" t="inlineStr">
+      <c r="D18" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E17" s="39" t="n">
+      <c r="E18" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F17" s="39" t="n">
+      <c r="F18" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G17" s="40" t="n">
+      <c r="G18" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H17" s="41" t="n">
+      <c r="H18" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I17" s="41" t="n">
+      <c r="I18" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J17" s="42" t="n">
+      <c r="J18" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K17" s="42" t="n">
+      <c r="K18" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L17" s="42" t="n">
+      <c r="L18" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M17" s="43" t="inlineStr">
+      <c r="M18" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N17" s="43" t="inlineStr"/>
-      <c r="O17" s="43" t="inlineStr">
+      <c r="N18" s="43" t="inlineStr"/>
+      <c r="O18" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P17" s="43" t="inlineStr"/>
-      <c r="Q17" s="43" t="inlineStr"/>
-      <c r="R17" s="43" t="inlineStr"/>
-      <c r="S17" s="43" t="inlineStr"/>
-      <c r="T17" s="43" t="inlineStr"/>
-      <c r="U17" s="43" t="inlineStr"/>
-      <c r="V17" s="43" t="n">
+      <c r="P18" s="43" t="inlineStr"/>
+      <c r="Q18" s="43" t="inlineStr"/>
+      <c r="R18" s="43" t="inlineStr"/>
+      <c r="S18" s="43" t="inlineStr"/>
+      <c r="T18" s="43" t="inlineStr"/>
+      <c r="U18" s="43" t="inlineStr"/>
+      <c r="V18" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W17" s="43" t="inlineStr"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B18" s="45" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
-      <c r="E18" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F18" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G18" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H18" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K18" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L18" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" s="51" t="n"/>
-      <c r="N18" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O18" s="51" t="n"/>
-      <c r="P18" s="51" t="n"/>
-      <c r="Q18" s="51" t="n"/>
-      <c r="R18" s="51" t="n"/>
-      <c r="S18" s="51" t="n"/>
-      <c r="T18" s="51" t="n"/>
-      <c r="U18" s="51" t="n"/>
-      <c r="V18" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W18" s="43" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B19" s="45" t="n"/>
-      <c r="C19" s="53" t="n"/>
-      <c r="D19" s="53" t="n"/>
+      <c r="C19" s="46" t="n"/>
+      <c r="D19" s="46" t="n"/>
       <c r="E19" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F19" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G19" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G19" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H19" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I19" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J19" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K19" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L19" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M19" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N19" s="55" t="n"/>
-      <c r="O19" s="55" t="n"/>
-      <c r="P19" s="55" t="n"/>
-      <c r="Q19" s="55" t="n"/>
-      <c r="R19" s="55" t="n"/>
-      <c r="S19" s="55" t="n"/>
-      <c r="T19" s="55" t="n"/>
-      <c r="U19" s="55" t="n"/>
-      <c r="V19" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W19" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M19" s="51" t="n"/>
+      <c r="N19" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O19" s="51" t="n"/>
+      <c r="P19" s="51" t="n"/>
+      <c r="Q19" s="51" t="n"/>
+      <c r="R19" s="51" t="n"/>
+      <c r="S19" s="51" t="n"/>
+      <c r="T19" s="51" t="n"/>
+      <c r="U19" s="51" t="n"/>
+      <c r="V19" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B20" s="45" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="46" t="n"/>
+      <c r="C20" s="53" t="n"/>
+      <c r="D20" s="53" t="n"/>
       <c r="E20" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F20" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G20" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G20" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H20" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J20" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K20" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L20" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M20" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N20" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O20" s="51" t="n"/>
-      <c r="P20" s="51" t="n"/>
-      <c r="Q20" s="51" t="n"/>
-      <c r="R20" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S20" s="51" t="n"/>
-      <c r="T20" s="51" t="n"/>
-      <c r="U20" s="51" t="n"/>
-      <c r="V20" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W20" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M20" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N20" s="55" t="n"/>
+      <c r="O20" s="55" t="n"/>
+      <c r="P20" s="55" t="n"/>
+      <c r="Q20" s="55" t="n"/>
+      <c r="R20" s="55" t="n"/>
+      <c r="S20" s="55" t="n"/>
+      <c r="T20" s="55" t="n"/>
+      <c r="U20" s="55" t="n"/>
+      <c r="V20" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W20" s="57" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="53" t="n"/>
-      <c r="D21" s="53" t="n"/>
+      <c r="C21" s="46" t="n"/>
+      <c r="D21" s="46" t="n"/>
       <c r="E21" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F21" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G21" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H21" s="49" t="n">
         <v>1</v>
@@ -2946,493 +2950,497 @@
         <v>1</v>
       </c>
       <c r="J21" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K21" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L21" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M21" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M21" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N21" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N21" s="55" t="n"/>
-      <c r="O21" s="55" t="n"/>
-      <c r="P21" s="55" t="n"/>
-      <c r="Q21" s="55" t="inlineStr">
+      <c r="O21" s="51" t="n"/>
+      <c r="P21" s="51" t="n"/>
+      <c r="Q21" s="51" t="n"/>
+      <c r="R21" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R21" s="55" t="n"/>
-      <c r="S21" s="55" t="n"/>
-      <c r="T21" s="55" t="n"/>
-      <c r="U21" s="55" t="n"/>
-      <c r="V21" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W21" s="57" t="n"/>
+      <c r="S21" s="51" t="n"/>
+      <c r="T21" s="51" t="n"/>
+      <c r="U21" s="51" t="n"/>
+      <c r="V21" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W21" s="58" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="46" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
       <c r="E22" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G22" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G22" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H22" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K22" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L22" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M22" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N22" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O22" s="51" t="n"/>
-      <c r="P22" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M22" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N22" s="55" t="n"/>
+      <c r="O22" s="55" t="n"/>
+      <c r="P22" s="55" t="n"/>
+      <c r="Q22" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q22" s="51" t="n"/>
-      <c r="R22" s="51" t="n"/>
-      <c r="S22" s="51" t="n"/>
-      <c r="T22" s="51" t="n"/>
-      <c r="U22" s="51" t="n"/>
-      <c r="V22" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W22" s="58" t="n"/>
+      <c r="R22" s="55" t="n"/>
+      <c r="S22" s="55" t="n"/>
+      <c r="T22" s="55" t="n"/>
+      <c r="U22" s="55" t="n"/>
+      <c r="V22" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W22" s="57" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="53" t="n"/>
-      <c r="D23" s="53" t="n"/>
+      <c r="C23" s="46" t="n"/>
+      <c r="D23" s="46" t="n"/>
       <c r="E23" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F23" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G23" s="59" t="n">
-        <v>45.1</v>
+      <c r="G23" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H23" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L23" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M23" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N23" s="55" t="n"/>
-      <c r="O23" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P23" s="55" t="n"/>
-      <c r="Q23" s="55" t="n"/>
-      <c r="R23" s="55" t="n"/>
-      <c r="S23" s="55" t="n"/>
-      <c r="T23" s="55" t="n"/>
-      <c r="U23" s="55" t="n"/>
-      <c r="V23" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W23" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M23" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N23" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O23" s="51" t="n"/>
+      <c r="P23" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q23" s="51" t="n"/>
+      <c r="R23" s="51" t="n"/>
+      <c r="S23" s="51" t="n"/>
+      <c r="T23" s="51" t="n"/>
+      <c r="U23" s="51" t="n"/>
+      <c r="V23" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W23" s="58" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
       <c r="E24" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F24" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G24" s="54" t="n">
-        <v>26.3</v>
+      <c r="G24" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H24" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L24" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M24" s="51" t="n"/>
-      <c r="N24" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M24" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N24" s="55" t="n"/>
+      <c r="O24" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O24" s="51" t="n"/>
-      <c r="P24" s="51" t="n"/>
-      <c r="Q24" s="51" t="n"/>
-      <c r="R24" s="51" t="n"/>
-      <c r="S24" s="51" t="n"/>
-      <c r="T24" s="51" t="n"/>
-      <c r="U24" s="51" t="n"/>
-      <c r="V24" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W24" s="58" t="n"/>
+      <c r="P24" s="55" t="n"/>
+      <c r="Q24" s="55" t="n"/>
+      <c r="R24" s="55" t="n"/>
+      <c r="S24" s="55" t="n"/>
+      <c r="T24" s="55" t="n"/>
+      <c r="U24" s="55" t="n"/>
+      <c r="V24" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W24" s="57" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="53" t="n"/>
-      <c r="D25" s="53" t="n"/>
+      <c r="C25" s="46" t="n"/>
+      <c r="D25" s="46" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G25" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H25" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L25" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M25" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M25" s="51" t="n"/>
+      <c r="N25" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N25" s="55" t="n"/>
-      <c r="O25" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P25" s="55" t="n"/>
-      <c r="Q25" s="55" t="n"/>
-      <c r="R25" s="55" t="n"/>
-      <c r="S25" s="55" t="n"/>
-      <c r="T25" s="55" t="n"/>
-      <c r="U25" s="55" t="n"/>
-      <c r="V25" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W25" s="57" t="n"/>
+      <c r="O25" s="51" t="n"/>
+      <c r="P25" s="51" t="n"/>
+      <c r="Q25" s="51" t="n"/>
+      <c r="R25" s="51" t="n"/>
+      <c r="S25" s="51" t="n"/>
+      <c r="T25" s="51" t="n"/>
+      <c r="U25" s="51" t="n"/>
+      <c r="V25" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W25" s="58" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="46" t="n"/>
-      <c r="D26" s="46" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G26" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H26" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I26" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L26" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M26" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N26" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O26" s="51" t="n"/>
-      <c r="P26" s="51" t="n"/>
-      <c r="Q26" s="51" t="n"/>
-      <c r="R26" s="51" t="n"/>
-      <c r="S26" s="51" t="n"/>
-      <c r="T26" s="51" t="n"/>
-      <c r="U26" s="51" t="n"/>
-      <c r="V26" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W26" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M26" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N26" s="55" t="n"/>
+      <c r="O26" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P26" s="55" t="n"/>
+      <c r="Q26" s="55" t="n"/>
+      <c r="R26" s="55" t="n"/>
+      <c r="S26" s="55" t="n"/>
+      <c r="T26" s="55" t="n"/>
+      <c r="U26" s="55" t="n"/>
+      <c r="V26" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W26" s="57" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="53" t="n"/>
-      <c r="D27" s="53" t="n"/>
+      <c r="C27" s="46" t="n"/>
+      <c r="D27" s="46" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G27" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H27" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K27" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L27" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I27" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J27" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K27" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L27" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M27" s="55" t="inlineStr">
+      <c r="M27" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N27" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N27" s="55" t="n"/>
-      <c r="O27" s="55" t="n"/>
-      <c r="P27" s="55" t="n"/>
-      <c r="Q27" s="55" t="n"/>
-      <c r="R27" s="55" t="n"/>
-      <c r="S27" s="55" t="n"/>
-      <c r="T27" s="55" t="n"/>
-      <c r="U27" s="55" t="n"/>
-      <c r="V27" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W27" s="57" t="n"/>
+      <c r="O27" s="51" t="n"/>
+      <c r="P27" s="51" t="n"/>
+      <c r="Q27" s="51" t="n"/>
+      <c r="R27" s="51" t="n"/>
+      <c r="S27" s="51" t="n"/>
+      <c r="T27" s="51" t="n"/>
+      <c r="U27" s="51" t="n"/>
+      <c r="V27" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W27" s="58" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="46" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="53" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G28" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G28" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H28" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I28" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L28" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M28" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N28" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O28" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P28" s="51" t="n"/>
-      <c r="Q28" s="51" t="n"/>
-      <c r="R28" s="51" t="n"/>
-      <c r="S28" s="51" t="n"/>
-      <c r="T28" s="51" t="n"/>
-      <c r="U28" s="51" t="n"/>
-      <c r="V28" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W28" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M28" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N28" s="55" t="n"/>
+      <c r="O28" s="55" t="n"/>
+      <c r="P28" s="55" t="n"/>
+      <c r="Q28" s="55" t="n"/>
+      <c r="R28" s="55" t="n"/>
+      <c r="S28" s="55" t="n"/>
+      <c r="T28" s="55" t="n"/>
+      <c r="U28" s="55" t="n"/>
+      <c r="V28" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W28" s="57" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="53" t="n"/>
-      <c r="D29" s="53" t="n"/>
+      <c r="C29" s="46" t="n"/>
+      <c r="D29" s="46" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G29" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G29" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H29" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I29" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J29" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L29" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M29" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N29" s="55" t="inlineStr">
+      <c r="M29" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N29" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O29" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O29" s="55" t="n"/>
-      <c r="P29" s="55" t="n"/>
-      <c r="Q29" s="55" t="n"/>
-      <c r="R29" s="55" t="n"/>
-      <c r="S29" s="55" t="n"/>
-      <c r="T29" s="55" t="n"/>
-      <c r="U29" s="55" t="n"/>
-      <c r="V29" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W29" s="57" t="n"/>
+      <c r="P29" s="51" t="n"/>
+      <c r="Q29" s="51" t="n"/>
+      <c r="R29" s="51" t="n"/>
+      <c r="S29" s="51" t="n"/>
+      <c r="T29" s="51" t="n"/>
+      <c r="U29" s="51" t="n"/>
+      <c r="V29" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W29" s="58" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="46" t="n"/>
-      <c r="D30" s="46" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="53" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G30" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H30" s="49" t="n">
         <v>2</v>
@@ -3441,208 +3449,218 @@
         <v>2</v>
       </c>
       <c r="J30" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K30" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L30" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M30" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M30" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N30" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N30" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O30" s="51" t="n"/>
-      <c r="P30" s="51" t="n"/>
-      <c r="Q30" s="51" t="n"/>
-      <c r="R30" s="51" t="n"/>
-      <c r="S30" s="51" t="n"/>
-      <c r="T30" s="51" t="n"/>
-      <c r="U30" s="51" t="n"/>
-      <c r="V30" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W30" s="58" t="n"/>
+      <c r="O30" s="55" t="n"/>
+      <c r="P30" s="55" t="n"/>
+      <c r="Q30" s="55" t="n"/>
+      <c r="R30" s="55" t="n"/>
+      <c r="S30" s="55" t="n"/>
+      <c r="T30" s="55" t="n"/>
+      <c r="U30" s="55" t="n"/>
+      <c r="V30" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W30" s="57" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="53" t="n"/>
-      <c r="D31" s="53" t="n"/>
+      <c r="C31" s="46" t="n"/>
+      <c r="D31" s="46" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G31" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H31" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I31" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J31" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L31" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M31" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M31" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N31" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N31" s="55" t="n"/>
-      <c r="O31" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P31" s="55" t="n"/>
-      <c r="Q31" s="55" t="n"/>
-      <c r="R31" s="55" t="n"/>
-      <c r="S31" s="55" t="n"/>
-      <c r="T31" s="55" t="n"/>
-      <c r="U31" s="55" t="n"/>
-      <c r="V31" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W31" s="57" t="n"/>
+      <c r="O31" s="51" t="n"/>
+      <c r="P31" s="51" t="n"/>
+      <c r="Q31" s="51" t="n"/>
+      <c r="R31" s="51" t="n"/>
+      <c r="S31" s="51" t="n"/>
+      <c r="T31" s="51" t="n"/>
+      <c r="U31" s="51" t="n"/>
+      <c r="V31" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W31" s="58" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="46" t="n"/>
-      <c r="D32" s="46" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G32" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G32" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H32" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L32" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M32" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N32" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O32" s="51" t="n"/>
-      <c r="P32" s="51" t="n"/>
-      <c r="Q32" s="51" t="n"/>
-      <c r="R32" s="51" t="n"/>
-      <c r="S32" s="51" t="n"/>
-      <c r="T32" s="51" t="n"/>
-      <c r="U32" s="51" t="n"/>
-      <c r="V32" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W32" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M32" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N32" s="55" t="n"/>
+      <c r="O32" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P32" s="55" t="n"/>
+      <c r="Q32" s="55" t="n"/>
+      <c r="R32" s="55" t="n"/>
+      <c r="S32" s="55" t="n"/>
+      <c r="T32" s="55" t="n"/>
+      <c r="U32" s="55" t="n"/>
+      <c r="V32" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W32" s="57" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="53" t="n"/>
-      <c r="D33" s="53" t="n"/>
+      <c r="C33" s="46" t="n"/>
+      <c r="D33" s="46" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G33" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G33" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H33" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J33" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L33" s="50" t="n"/>
-      <c r="M33" s="55" t="n"/>
-      <c r="N33" s="55" t="n"/>
-      <c r="O33" s="55" t="n"/>
-      <c r="P33" s="55" t="n"/>
-      <c r="Q33" s="55" t="n"/>
-      <c r="R33" s="55" t="n"/>
-      <c r="S33" s="55" t="n"/>
-      <c r="T33" s="55" t="n"/>
-      <c r="U33" s="55" t="n"/>
-      <c r="V33" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W33" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L33" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M33" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N33" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O33" s="51" t="n"/>
+      <c r="P33" s="51" t="n"/>
+      <c r="Q33" s="51" t="n"/>
+      <c r="R33" s="51" t="n"/>
+      <c r="S33" s="51" t="n"/>
+      <c r="T33" s="51" t="n"/>
+      <c r="U33" s="51" t="n"/>
+      <c r="V33" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W33" s="58" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="46" t="n"/>
-      <c r="D34" s="46" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G34" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H34" s="49" t="n">
         <v>0</v>
@@ -3651,43 +3669,43 @@
         <v>0</v>
       </c>
       <c r="J34" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L34" s="50" t="n"/>
-      <c r="M34" s="51" t="n"/>
-      <c r="N34" s="51" t="n"/>
-      <c r="O34" s="51" t="n"/>
-      <c r="P34" s="51" t="n"/>
-      <c r="Q34" s="51" t="n"/>
-      <c r="R34" s="51" t="n"/>
-      <c r="S34" s="51" t="n"/>
-      <c r="T34" s="51" t="n"/>
-      <c r="U34" s="51" t="n"/>
-      <c r="V34" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W34" s="58" t="n"/>
+      <c r="M34" s="55" t="n"/>
+      <c r="N34" s="55" t="n"/>
+      <c r="O34" s="55" t="n"/>
+      <c r="P34" s="55" t="n"/>
+      <c r="Q34" s="55" t="n"/>
+      <c r="R34" s="55" t="n"/>
+      <c r="S34" s="55" t="n"/>
+      <c r="T34" s="55" t="n"/>
+      <c r="U34" s="55" t="n"/>
+      <c r="V34" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W34" s="57" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="53" t="n"/>
-      <c r="D35" s="53" t="n"/>
+      <c r="C35" s="46" t="n"/>
+      <c r="D35" s="46" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G35" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H35" s="49" t="n">
         <v>0</v>
@@ -3696,43 +3714,43 @@
         <v>0</v>
       </c>
       <c r="J35" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L35" s="50" t="n"/>
-      <c r="M35" s="55" t="n"/>
-      <c r="N35" s="55" t="n"/>
-      <c r="O35" s="55" t="n"/>
-      <c r="P35" s="55" t="n"/>
-      <c r="Q35" s="55" t="n"/>
-      <c r="R35" s="55" t="n"/>
-      <c r="S35" s="55" t="n"/>
-      <c r="T35" s="55" t="n"/>
-      <c r="U35" s="55" t="n"/>
-      <c r="V35" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W35" s="57" t="n"/>
+      <c r="M35" s="51" t="n"/>
+      <c r="N35" s="51" t="n"/>
+      <c r="O35" s="51" t="n"/>
+      <c r="P35" s="51" t="n"/>
+      <c r="Q35" s="51" t="n"/>
+      <c r="R35" s="51" t="n"/>
+      <c r="S35" s="51" t="n"/>
+      <c r="T35" s="51" t="n"/>
+      <c r="U35" s="51" t="n"/>
+      <c r="V35" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W35" s="58" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
+      <c r="C36" s="53" t="n"/>
+      <c r="D36" s="53" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G36" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G36" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H36" s="49" t="n">
         <v>0</v>
@@ -3741,43 +3759,43 @@
         <v>0</v>
       </c>
       <c r="J36" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="51" t="n"/>
-      <c r="N36" s="51" t="n"/>
-      <c r="O36" s="51" t="n"/>
-      <c r="P36" s="51" t="n"/>
-      <c r="Q36" s="51" t="n"/>
-      <c r="R36" s="51" t="n"/>
-      <c r="S36" s="51" t="n"/>
-      <c r="T36" s="51" t="n"/>
-      <c r="U36" s="51" t="n"/>
-      <c r="V36" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W36" s="58" t="n"/>
+      <c r="M36" s="55" t="n"/>
+      <c r="N36" s="55" t="n"/>
+      <c r="O36" s="55" t="n"/>
+      <c r="P36" s="55" t="n"/>
+      <c r="Q36" s="55" t="n"/>
+      <c r="R36" s="55" t="n"/>
+      <c r="S36" s="55" t="n"/>
+      <c r="T36" s="55" t="n"/>
+      <c r="U36" s="55" t="n"/>
+      <c r="V36" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W36" s="57" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="53" t="n"/>
-      <c r="D37" s="53" t="n"/>
+      <c r="C37" s="46" t="n"/>
+      <c r="D37" s="46" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G37" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H37" s="49" t="n">
         <v>0</v>
@@ -3786,43 +3804,43 @@
         <v>0</v>
       </c>
       <c r="J37" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="55" t="n"/>
-      <c r="N37" s="55" t="n"/>
-      <c r="O37" s="55" t="n"/>
-      <c r="P37" s="55" t="n"/>
-      <c r="Q37" s="55" t="n"/>
-      <c r="R37" s="55" t="n"/>
-      <c r="S37" s="55" t="n"/>
-      <c r="T37" s="55" t="n"/>
-      <c r="U37" s="55" t="n"/>
-      <c r="V37" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W37" s="57" t="n"/>
+      <c r="M37" s="51" t="n"/>
+      <c r="N37" s="51" t="n"/>
+      <c r="O37" s="51" t="n"/>
+      <c r="P37" s="51" t="n"/>
+      <c r="Q37" s="51" t="n"/>
+      <c r="R37" s="51" t="n"/>
+      <c r="S37" s="51" t="n"/>
+      <c r="T37" s="51" t="n"/>
+      <c r="U37" s="51" t="n"/>
+      <c r="V37" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W37" s="58" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="46" t="n"/>
-      <c r="D38" s="46" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G38" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H38" s="49" t="n">
         <v>0</v>
@@ -3831,1371 +3849,1375 @@
         <v>0</v>
       </c>
       <c r="J38" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="51" t="n"/>
-      <c r="N38" s="51" t="n"/>
-      <c r="O38" s="51" t="n"/>
-      <c r="P38" s="51" t="n"/>
-      <c r="Q38" s="51" t="n"/>
-      <c r="R38" s="51" t="n"/>
-      <c r="S38" s="51" t="n"/>
-      <c r="T38" s="51" t="n"/>
-      <c r="U38" s="51" t="n"/>
-      <c r="V38" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W38" s="58" t="n"/>
+      <c r="M38" s="55" t="n"/>
+      <c r="N38" s="55" t="n"/>
+      <c r="O38" s="55" t="n"/>
+      <c r="P38" s="55" t="n"/>
+      <c r="Q38" s="55" t="n"/>
+      <c r="R38" s="55" t="n"/>
+      <c r="S38" s="55" t="n"/>
+      <c r="T38" s="55" t="n"/>
+      <c r="U38" s="55" t="n"/>
+      <c r="V38" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W38" s="57" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="53" t="n"/>
-      <c r="D39" s="53" t="n"/>
+      <c r="C39" s="46" t="n"/>
+      <c r="D39" s="46" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G39" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H39" s="49" t="n"/>
-      <c r="I39" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G39" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H39" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J39" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="55" t="n"/>
-      <c r="N39" s="55" t="n"/>
-      <c r="O39" s="55" t="n"/>
-      <c r="P39" s="55" t="n"/>
-      <c r="Q39" s="55" t="n"/>
-      <c r="R39" s="55" t="n"/>
-      <c r="S39" s="55" t="n"/>
-      <c r="T39" s="55" t="n"/>
-      <c r="U39" s="55" t="n"/>
-      <c r="V39" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W39" s="57" t="n"/>
+      <c r="M39" s="51" t="n"/>
+      <c r="N39" s="51" t="n"/>
+      <c r="O39" s="51" t="n"/>
+      <c r="P39" s="51" t="n"/>
+      <c r="Q39" s="51" t="n"/>
+      <c r="R39" s="51" t="n"/>
+      <c r="S39" s="51" t="n"/>
+      <c r="T39" s="51" t="n"/>
+      <c r="U39" s="51" t="n"/>
+      <c r="V39" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W39" s="58" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="46" t="n"/>
-      <c r="D40" s="46" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G40" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H40" s="49" t="n"/>
       <c r="I40" s="49" t="n"/>
       <c r="J40" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="51" t="n"/>
-      <c r="N40" s="51" t="n"/>
-      <c r="O40" s="51" t="n"/>
-      <c r="P40" s="51" t="n"/>
-      <c r="Q40" s="51" t="n"/>
-      <c r="R40" s="51" t="n"/>
-      <c r="S40" s="51" t="n"/>
-      <c r="T40" s="51" t="n"/>
-      <c r="U40" s="51" t="n"/>
-      <c r="V40" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W40" s="58" t="n"/>
+      <c r="M40" s="55" t="n"/>
+      <c r="N40" s="55" t="n"/>
+      <c r="O40" s="55" t="n"/>
+      <c r="P40" s="55" t="n"/>
+      <c r="Q40" s="55" t="n"/>
+      <c r="R40" s="55" t="n"/>
+      <c r="S40" s="55" t="n"/>
+      <c r="T40" s="55" t="n"/>
+      <c r="U40" s="55" t="n"/>
+      <c r="V40" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W40" s="57" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="53" t="n"/>
-      <c r="D41" s="53" t="n"/>
+      <c r="C41" s="46" t="n"/>
+      <c r="D41" s="46" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G41" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H41" s="49" t="n"/>
       <c r="I41" s="49" t="n"/>
       <c r="J41" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="55" t="n"/>
-      <c r="N41" s="55" t="n"/>
-      <c r="O41" s="55" t="n"/>
-      <c r="P41" s="55" t="n"/>
-      <c r="Q41" s="55" t="n"/>
-      <c r="R41" s="55" t="n"/>
-      <c r="S41" s="55" t="n"/>
-      <c r="T41" s="55" t="n"/>
-      <c r="U41" s="55" t="n"/>
-      <c r="V41" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W41" s="57" t="n"/>
+      <c r="M41" s="51" t="n"/>
+      <c r="N41" s="51" t="n"/>
+      <c r="O41" s="51" t="n"/>
+      <c r="P41" s="51" t="n"/>
+      <c r="Q41" s="51" t="n"/>
+      <c r="R41" s="51" t="n"/>
+      <c r="S41" s="51" t="n"/>
+      <c r="T41" s="51" t="n"/>
+      <c r="U41" s="51" t="n"/>
+      <c r="V41" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W41" s="58" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="46" t="n"/>
-      <c r="D42" s="46" t="n"/>
+      <c r="C42" s="53" t="n"/>
+      <c r="D42" s="53" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G42" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H42" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I42" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H42" s="49" t="n"/>
+      <c r="I42" s="49" t="n"/>
       <c r="J42" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K42" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="51" t="n"/>
-      <c r="N42" s="51" t="n"/>
-      <c r="O42" s="51" t="n"/>
-      <c r="P42" s="51" t="n"/>
-      <c r="Q42" s="51" t="n"/>
-      <c r="R42" s="51" t="n"/>
-      <c r="S42" s="51" t="n"/>
-      <c r="T42" s="51" t="n"/>
-      <c r="U42" s="51" t="n"/>
-      <c r="V42" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W42" s="58" t="n"/>
+      <c r="M42" s="55" t="n"/>
+      <c r="N42" s="55" t="n"/>
+      <c r="O42" s="55" t="n"/>
+      <c r="P42" s="55" t="n"/>
+      <c r="Q42" s="55" t="n"/>
+      <c r="R42" s="55" t="n"/>
+      <c r="S42" s="55" t="n"/>
+      <c r="T42" s="55" t="n"/>
+      <c r="U42" s="55" t="n"/>
+      <c r="V42" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W42" s="57" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="53" t="n"/>
-      <c r="D43" s="53" t="n"/>
+      <c r="C43" s="46" t="n"/>
+      <c r="D43" s="46" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G43" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H43" s="49" t="n"/>
-      <c r="I43" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G43" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H43" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I43" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J43" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K43" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="55" t="n"/>
-      <c r="N43" s="55" t="n"/>
-      <c r="O43" s="55" t="n"/>
-      <c r="P43" s="55" t="n"/>
-      <c r="Q43" s="55" t="n"/>
-      <c r="R43" s="55" t="n"/>
-      <c r="S43" s="55" t="n"/>
-      <c r="T43" s="55" t="n"/>
-      <c r="U43" s="55" t="n"/>
-      <c r="V43" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W43" s="57" t="n"/>
+      <c r="M43" s="51" t="n"/>
+      <c r="N43" s="51" t="n"/>
+      <c r="O43" s="51" t="n"/>
+      <c r="P43" s="51" t="n"/>
+      <c r="Q43" s="51" t="n"/>
+      <c r="R43" s="51" t="n"/>
+      <c r="S43" s="51" t="n"/>
+      <c r="T43" s="51" t="n"/>
+      <c r="U43" s="51" t="n"/>
+      <c r="V43" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W43" s="58" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="46" t="n"/>
-      <c r="D44" s="46" t="n"/>
+      <c r="C44" s="53" t="n"/>
+      <c r="D44" s="53" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G44" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G44" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H44" s="49" t="n"/>
       <c r="I44" s="49" t="n"/>
       <c r="J44" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K44" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="51" t="n"/>
-      <c r="N44" s="51" t="n"/>
-      <c r="O44" s="51" t="n"/>
-      <c r="P44" s="51" t="n"/>
-      <c r="Q44" s="51" t="n"/>
-      <c r="R44" s="51" t="n"/>
-      <c r="S44" s="51" t="n"/>
-      <c r="T44" s="51" t="n"/>
-      <c r="U44" s="51" t="n"/>
-      <c r="V44" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W44" s="58" t="n"/>
+      <c r="M44" s="55" t="n"/>
+      <c r="N44" s="55" t="n"/>
+      <c r="O44" s="55" t="n"/>
+      <c r="P44" s="55" t="n"/>
+      <c r="Q44" s="55" t="n"/>
+      <c r="R44" s="55" t="n"/>
+      <c r="S44" s="55" t="n"/>
+      <c r="T44" s="55" t="n"/>
+      <c r="U44" s="55" t="n"/>
+      <c r="V44" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W44" s="57" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="53" t="n"/>
-      <c r="D45" s="53" t="n"/>
+      <c r="C45" s="46" t="n"/>
+      <c r="D45" s="46" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G45" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G45" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H45" s="49" t="n"/>
       <c r="I45" s="49" t="n"/>
       <c r="J45" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K45" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K45" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="55" t="n"/>
-      <c r="N45" s="55" t="n"/>
-      <c r="O45" s="55" t="n"/>
-      <c r="P45" s="55" t="n"/>
-      <c r="Q45" s="55" t="n"/>
-      <c r="R45" s="55" t="n"/>
-      <c r="S45" s="55" t="n"/>
-      <c r="T45" s="55" t="n"/>
-      <c r="U45" s="55" t="n"/>
-      <c r="V45" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W45" s="57" t="n"/>
+      <c r="M45" s="51" t="n"/>
+      <c r="N45" s="51" t="n"/>
+      <c r="O45" s="51" t="n"/>
+      <c r="P45" s="51" t="n"/>
+      <c r="Q45" s="51" t="n"/>
+      <c r="R45" s="51" t="n"/>
+      <c r="S45" s="51" t="n"/>
+      <c r="T45" s="51" t="n"/>
+      <c r="U45" s="51" t="n"/>
+      <c r="V45" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W45" s="58" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="46" t="n"/>
-      <c r="D46" s="46" t="n"/>
+      <c r="C46" s="53" t="n"/>
+      <c r="D46" s="53" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G46" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H46" s="49" t="n"/>
       <c r="I46" s="49" t="n"/>
       <c r="J46" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K46" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="51" t="n"/>
-      <c r="N46" s="51" t="n"/>
-      <c r="O46" s="51" t="n"/>
-      <c r="P46" s="51" t="n"/>
-      <c r="Q46" s="51" t="n"/>
-      <c r="R46" s="51" t="n"/>
-      <c r="S46" s="51" t="n"/>
-      <c r="T46" s="51" t="n"/>
-      <c r="U46" s="51" t="n"/>
-      <c r="V46" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W46" s="58" t="n"/>
+      <c r="M46" s="55" t="n"/>
+      <c r="N46" s="55" t="n"/>
+      <c r="O46" s="55" t="n"/>
+      <c r="P46" s="55" t="n"/>
+      <c r="Q46" s="55" t="n"/>
+      <c r="R46" s="55" t="n"/>
+      <c r="S46" s="55" t="n"/>
+      <c r="T46" s="55" t="n"/>
+      <c r="U46" s="55" t="n"/>
+      <c r="V46" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W46" s="57" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="53" t="n"/>
-      <c r="D47" s="53" t="n"/>
+      <c r="C47" s="46" t="n"/>
+      <c r="D47" s="46" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G47" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G47" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H47" s="49" t="n"/>
       <c r="I47" s="49" t="n"/>
       <c r="J47" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K47" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="55" t="n"/>
-      <c r="N47" s="55" t="n"/>
-      <c r="O47" s="55" t="n"/>
-      <c r="P47" s="55" t="n"/>
-      <c r="Q47" s="55" t="n"/>
-      <c r="R47" s="55" t="n"/>
-      <c r="S47" s="55" t="n"/>
-      <c r="T47" s="55" t="n"/>
-      <c r="U47" s="55" t="n"/>
-      <c r="V47" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W47" s="57" t="n"/>
+      <c r="M47" s="51" t="n"/>
+      <c r="N47" s="51" t="n"/>
+      <c r="O47" s="51" t="n"/>
+      <c r="P47" s="51" t="n"/>
+      <c r="Q47" s="51" t="n"/>
+      <c r="R47" s="51" t="n"/>
+      <c r="S47" s="51" t="n"/>
+      <c r="T47" s="51" t="n"/>
+      <c r="U47" s="51" t="n"/>
+      <c r="V47" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W47" s="58" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
+      <c r="C48" s="53" t="n"/>
+      <c r="D48" s="53" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G48" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H48" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I48" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G48" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H48" s="49" t="n"/>
+      <c r="I48" s="49" t="n"/>
       <c r="J48" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K48" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="51" t="n"/>
-      <c r="N48" s="51" t="n"/>
-      <c r="O48" s="51" t="n"/>
-      <c r="P48" s="51" t="n"/>
-      <c r="Q48" s="51" t="n"/>
-      <c r="R48" s="51" t="n"/>
-      <c r="S48" s="51" t="n"/>
-      <c r="T48" s="51" t="n"/>
-      <c r="U48" s="51" t="n"/>
-      <c r="V48" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W48" s="58" t="n"/>
+      <c r="M48" s="55" t="n"/>
+      <c r="N48" s="55" t="n"/>
+      <c r="O48" s="55" t="n"/>
+      <c r="P48" s="55" t="n"/>
+      <c r="Q48" s="55" t="n"/>
+      <c r="R48" s="55" t="n"/>
+      <c r="S48" s="55" t="n"/>
+      <c r="T48" s="55" t="n"/>
+      <c r="U48" s="55" t="n"/>
+      <c r="V48" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W48" s="57" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="53" t="n"/>
-      <c r="D49" s="53" t="n"/>
+      <c r="C49" s="46" t="n"/>
+      <c r="D49" s="46" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G49" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H49" s="49" t="n"/>
-      <c r="I49" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H49" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I49" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J49" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K49" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="55" t="n"/>
-      <c r="N49" s="55" t="n"/>
-      <c r="O49" s="55" t="n"/>
-      <c r="P49" s="55" t="n"/>
-      <c r="Q49" s="55" t="n"/>
-      <c r="R49" s="55" t="n"/>
-      <c r="S49" s="55" t="n"/>
-      <c r="T49" s="55" t="n"/>
-      <c r="U49" s="55" t="n"/>
-      <c r="V49" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W49" s="57" t="n"/>
+      <c r="M49" s="51" t="n"/>
+      <c r="N49" s="51" t="n"/>
+      <c r="O49" s="51" t="n"/>
+      <c r="P49" s="51" t="n"/>
+      <c r="Q49" s="51" t="n"/>
+      <c r="R49" s="51" t="n"/>
+      <c r="S49" s="51" t="n"/>
+      <c r="T49" s="51" t="n"/>
+      <c r="U49" s="51" t="n"/>
+      <c r="V49" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W49" s="58" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
+      <c r="C50" s="53" t="n"/>
+      <c r="D50" s="53" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G50" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="49" t="n"/>
       <c r="J50" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="51" t="n"/>
-      <c r="N50" s="51" t="n"/>
-      <c r="O50" s="51" t="n"/>
-      <c r="P50" s="51" t="n"/>
-      <c r="Q50" s="51" t="n"/>
-      <c r="R50" s="51" t="n"/>
-      <c r="S50" s="51" t="n"/>
-      <c r="T50" s="51" t="n"/>
-      <c r="U50" s="51" t="n"/>
-      <c r="V50" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W50" s="58" t="n"/>
+      <c r="M50" s="55" t="n"/>
+      <c r="N50" s="55" t="n"/>
+      <c r="O50" s="55" t="n"/>
+      <c r="P50" s="55" t="n"/>
+      <c r="Q50" s="55" t="n"/>
+      <c r="R50" s="55" t="n"/>
+      <c r="S50" s="55" t="n"/>
+      <c r="T50" s="55" t="n"/>
+      <c r="U50" s="55" t="n"/>
+      <c r="V50" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W50" s="57" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="53" t="n"/>
-      <c r="D51" s="53" t="n"/>
+      <c r="C51" s="46" t="n"/>
+      <c r="D51" s="46" t="n"/>
       <c r="E51" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F51" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G51" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H51" s="49" t="n"/>
+      <c r="I51" s="49" t="n"/>
+      <c r="J51" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F51" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G51" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H51" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I51" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J51" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K51" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="55" t="n"/>
-      <c r="N51" s="55" t="n"/>
-      <c r="O51" s="55" t="n"/>
-      <c r="P51" s="55" t="n"/>
-      <c r="Q51" s="55" t="n"/>
-      <c r="R51" s="55" t="n"/>
-      <c r="S51" s="55" t="n"/>
-      <c r="T51" s="55" t="n"/>
-      <c r="U51" s="55" t="n"/>
-      <c r="V51" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W51" s="57" t="n"/>
+      <c r="M51" s="51" t="n"/>
+      <c r="N51" s="51" t="n"/>
+      <c r="O51" s="51" t="n"/>
+      <c r="P51" s="51" t="n"/>
+      <c r="Q51" s="51" t="n"/>
+      <c r="R51" s="51" t="n"/>
+      <c r="S51" s="51" t="n"/>
+      <c r="T51" s="51" t="n"/>
+      <c r="U51" s="51" t="n"/>
+      <c r="V51" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W51" s="58" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="46" t="n"/>
-      <c r="D52" s="46" t="n"/>
+      <c r="C52" s="53" t="n"/>
+      <c r="D52" s="53" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G52" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H52" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I52" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J52" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="51" t="n"/>
-      <c r="N52" s="51" t="n"/>
-      <c r="O52" s="51" t="n"/>
-      <c r="P52" s="51" t="n"/>
-      <c r="Q52" s="51" t="n"/>
-      <c r="R52" s="51" t="n"/>
-      <c r="S52" s="51" t="n"/>
-      <c r="T52" s="51" t="n"/>
-      <c r="U52" s="51" t="n"/>
-      <c r="V52" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W52" s="58" t="n"/>
+      <c r="M52" s="55" t="n"/>
+      <c r="N52" s="55" t="n"/>
+      <c r="O52" s="55" t="n"/>
+      <c r="P52" s="55" t="n"/>
+      <c r="Q52" s="55" t="n"/>
+      <c r="R52" s="55" t="n"/>
+      <c r="S52" s="55" t="n"/>
+      <c r="T52" s="55" t="n"/>
+      <c r="U52" s="55" t="n"/>
+      <c r="V52" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W52" s="57" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="53" t="n"/>
-      <c r="D53" s="53" t="n"/>
+      <c r="C53" s="46" t="n"/>
+      <c r="D53" s="46" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G53" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H53" s="49" t="n"/>
-      <c r="I53" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H53" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I53" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J53" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="55" t="n"/>
-      <c r="N53" s="55" t="n"/>
-      <c r="O53" s="55" t="n"/>
-      <c r="P53" s="55" t="n"/>
-      <c r="Q53" s="55" t="n"/>
-      <c r="R53" s="55" t="n"/>
-      <c r="S53" s="55" t="n"/>
-      <c r="T53" s="55" t="n"/>
-      <c r="U53" s="55" t="n"/>
-      <c r="V53" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W53" s="57" t="n"/>
+      <c r="M53" s="51" t="n"/>
+      <c r="N53" s="51" t="n"/>
+      <c r="O53" s="51" t="n"/>
+      <c r="P53" s="51" t="n"/>
+      <c r="Q53" s="51" t="n"/>
+      <c r="R53" s="51" t="n"/>
+      <c r="S53" s="51" t="n"/>
+      <c r="T53" s="51" t="n"/>
+      <c r="U53" s="51" t="n"/>
+      <c r="V53" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W53" s="58" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="46" t="n"/>
-      <c r="D54" s="46" t="n"/>
+      <c r="C54" s="53" t="n"/>
+      <c r="D54" s="53" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G54" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G54" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K54" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="51" t="n"/>
-      <c r="N54" s="51" t="n"/>
-      <c r="O54" s="51" t="n"/>
-      <c r="P54" s="51" t="n"/>
-      <c r="Q54" s="51" t="n"/>
-      <c r="R54" s="51" t="n"/>
-      <c r="S54" s="51" t="n"/>
-      <c r="T54" s="51" t="n"/>
-      <c r="U54" s="51" t="n"/>
-      <c r="V54" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W54" s="58" t="n"/>
+      <c r="M54" s="55" t="n"/>
+      <c r="N54" s="55" t="n"/>
+      <c r="O54" s="55" t="n"/>
+      <c r="P54" s="55" t="n"/>
+      <c r="Q54" s="55" t="n"/>
+      <c r="R54" s="55" t="n"/>
+      <c r="S54" s="55" t="n"/>
+      <c r="T54" s="55" t="n"/>
+      <c r="U54" s="55" t="n"/>
+      <c r="V54" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W54" s="57" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="53" t="n"/>
-      <c r="D55" s="53" t="n"/>
+      <c r="C55" s="46" t="n"/>
+      <c r="D55" s="46" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G55" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G55" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="55" t="n"/>
-      <c r="N55" s="55" t="n"/>
-      <c r="O55" s="55" t="n"/>
-      <c r="P55" s="55" t="n"/>
-      <c r="Q55" s="55" t="n"/>
-      <c r="R55" s="55" t="n"/>
-      <c r="S55" s="55" t="n"/>
-      <c r="T55" s="55" t="n"/>
-      <c r="U55" s="55" t="n"/>
-      <c r="V55" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W55" s="57" t="n"/>
+      <c r="M55" s="51" t="n"/>
+      <c r="N55" s="51" t="n"/>
+      <c r="O55" s="51" t="n"/>
+      <c r="P55" s="51" t="n"/>
+      <c r="Q55" s="51" t="n"/>
+      <c r="R55" s="51" t="n"/>
+      <c r="S55" s="51" t="n"/>
+      <c r="T55" s="51" t="n"/>
+      <c r="U55" s="51" t="n"/>
+      <c r="V55" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W55" s="58" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="46" t="n"/>
-      <c r="D56" s="46" t="n"/>
+      <c r="C56" s="53" t="n"/>
+      <c r="D56" s="53" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G56" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="51" t="n"/>
-      <c r="N56" s="51" t="n"/>
-      <c r="O56" s="51" t="n"/>
-      <c r="P56" s="51" t="n"/>
-      <c r="Q56" s="51" t="n"/>
-      <c r="R56" s="51" t="n"/>
-      <c r="S56" s="51" t="n"/>
-      <c r="T56" s="51" t="n"/>
-      <c r="U56" s="51" t="n"/>
-      <c r="V56" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W56" s="58" t="n"/>
+      <c r="M56" s="55" t="n"/>
+      <c r="N56" s="55" t="n"/>
+      <c r="O56" s="55" t="n"/>
+      <c r="P56" s="55" t="n"/>
+      <c r="Q56" s="55" t="n"/>
+      <c r="R56" s="55" t="n"/>
+      <c r="S56" s="55" t="n"/>
+      <c r="T56" s="55" t="n"/>
+      <c r="U56" s="55" t="n"/>
+      <c r="V56" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W56" s="57" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="53" t="n"/>
-      <c r="D57" s="53" t="n"/>
+      <c r="C57" s="46" t="n"/>
+      <c r="D57" s="46" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G57" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G57" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="55" t="n"/>
-      <c r="N57" s="55" t="n"/>
-      <c r="O57" s="55" t="n"/>
-      <c r="P57" s="55" t="n"/>
-      <c r="Q57" s="55" t="n"/>
-      <c r="R57" s="55" t="n"/>
-      <c r="S57" s="55" t="n"/>
-      <c r="T57" s="55" t="n"/>
-      <c r="U57" s="55" t="n"/>
-      <c r="V57" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W57" s="57" t="n"/>
+      <c r="M57" s="51" t="n"/>
+      <c r="N57" s="51" t="n"/>
+      <c r="O57" s="51" t="n"/>
+      <c r="P57" s="51" t="n"/>
+      <c r="Q57" s="51" t="n"/>
+      <c r="R57" s="51" t="n"/>
+      <c r="S57" s="51" t="n"/>
+      <c r="T57" s="51" t="n"/>
+      <c r="U57" s="51" t="n"/>
+      <c r="V57" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W57" s="58" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="46" t="n"/>
-      <c r="D58" s="46" t="n"/>
+      <c r="C58" s="53" t="n"/>
+      <c r="D58" s="53" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G58" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G58" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="51" t="n"/>
-      <c r="N58" s="51" t="n"/>
-      <c r="O58" s="51" t="n"/>
-      <c r="P58" s="51" t="n"/>
-      <c r="Q58" s="51" t="n"/>
-      <c r="R58" s="51" t="n"/>
-      <c r="S58" s="51" t="n"/>
-      <c r="T58" s="51" t="n"/>
-      <c r="U58" s="51" t="n"/>
-      <c r="V58" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W58" s="58" t="n"/>
+      <c r="M58" s="55" t="n"/>
+      <c r="N58" s="55" t="n"/>
+      <c r="O58" s="55" t="n"/>
+      <c r="P58" s="55" t="n"/>
+      <c r="Q58" s="55" t="n"/>
+      <c r="R58" s="55" t="n"/>
+      <c r="S58" s="55" t="n"/>
+      <c r="T58" s="55" t="n"/>
+      <c r="U58" s="55" t="n"/>
+      <c r="V58" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W58" s="57" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="53" t="n"/>
-      <c r="D59" s="53" t="n"/>
+      <c r="C59" s="46" t="n"/>
+      <c r="D59" s="46" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G59" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G59" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="55" t="n"/>
-      <c r="N59" s="55" t="n"/>
-      <c r="O59" s="55" t="n"/>
-      <c r="P59" s="55" t="n"/>
-      <c r="Q59" s="55" t="n"/>
-      <c r="R59" s="55" t="n"/>
-      <c r="S59" s="55" t="n"/>
-      <c r="T59" s="55" t="n"/>
-      <c r="U59" s="55" t="n"/>
-      <c r="V59" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W59" s="57" t="n"/>
+      <c r="M59" s="51" t="n"/>
+      <c r="N59" s="51" t="n"/>
+      <c r="O59" s="51" t="n"/>
+      <c r="P59" s="51" t="n"/>
+      <c r="Q59" s="51" t="n"/>
+      <c r="R59" s="51" t="n"/>
+      <c r="S59" s="51" t="n"/>
+      <c r="T59" s="51" t="n"/>
+      <c r="U59" s="51" t="n"/>
+      <c r="V59" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W59" s="58" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
+      <c r="C60" s="53" t="n"/>
+      <c r="D60" s="53" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G60" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="51" t="n"/>
-      <c r="N60" s="51" t="n"/>
-      <c r="O60" s="51" t="n"/>
-      <c r="P60" s="51" t="n"/>
-      <c r="Q60" s="51" t="n"/>
-      <c r="R60" s="51" t="n"/>
-      <c r="S60" s="51" t="n"/>
-      <c r="T60" s="51" t="n"/>
-      <c r="U60" s="51" t="n"/>
-      <c r="V60" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W60" s="58" t="n"/>
+      <c r="M60" s="55" t="n"/>
+      <c r="N60" s="55" t="n"/>
+      <c r="O60" s="55" t="n"/>
+      <c r="P60" s="55" t="n"/>
+      <c r="Q60" s="55" t="n"/>
+      <c r="R60" s="55" t="n"/>
+      <c r="S60" s="55" t="n"/>
+      <c r="T60" s="55" t="n"/>
+      <c r="U60" s="55" t="n"/>
+      <c r="V60" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W60" s="57" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="53" t="n"/>
-      <c r="D61" s="53" t="n"/>
+      <c r="C61" s="46" t="n"/>
+      <c r="D61" s="46" t="n"/>
       <c r="E61" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F61" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G61" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
       <c r="J61" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K61" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="55" t="n"/>
-      <c r="N61" s="55" t="n"/>
-      <c r="O61" s="55" t="n"/>
-      <c r="P61" s="55" t="n"/>
-      <c r="Q61" s="55" t="n"/>
-      <c r="R61" s="55" t="n"/>
-      <c r="S61" s="55" t="n"/>
-      <c r="T61" s="55" t="n"/>
-      <c r="U61" s="55" t="n"/>
-      <c r="V61" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W61" s="57" t="n"/>
+      <c r="M61" s="51" t="n"/>
+      <c r="N61" s="51" t="n"/>
+      <c r="O61" s="51" t="n"/>
+      <c r="P61" s="51" t="n"/>
+      <c r="Q61" s="51" t="n"/>
+      <c r="R61" s="51" t="n"/>
+      <c r="S61" s="51" t="n"/>
+      <c r="T61" s="51" t="n"/>
+      <c r="U61" s="51" t="n"/>
+      <c r="V61" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W61" s="58" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B62" s="45" t="n"/>
-      <c r="C62" s="46" t="n"/>
-      <c r="D62" s="46" t="n"/>
+      <c r="C62" s="53" t="n"/>
+      <c r="D62" s="53" t="n"/>
       <c r="E62" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F62" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G62" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G62" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="49" t="n"/>
       <c r="J62" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K62" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L62" s="50" t="n"/>
-      <c r="M62" s="51" t="n"/>
-      <c r="N62" s="51" t="n"/>
-      <c r="O62" s="51" t="n"/>
-      <c r="P62" s="51" t="n"/>
-      <c r="Q62" s="51" t="n"/>
-      <c r="R62" s="51" t="n"/>
-      <c r="S62" s="51" t="n"/>
-      <c r="T62" s="51" t="n"/>
-      <c r="U62" s="51" t="n"/>
-      <c r="V62" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W62" s="58" t="n"/>
+      <c r="M62" s="55" t="n"/>
+      <c r="N62" s="55" t="n"/>
+      <c r="O62" s="55" t="n"/>
+      <c r="P62" s="55" t="n"/>
+      <c r="Q62" s="55" t="n"/>
+      <c r="R62" s="55" t="n"/>
+      <c r="S62" s="55" t="n"/>
+      <c r="T62" s="55" t="n"/>
+      <c r="U62" s="55" t="n"/>
+      <c r="V62" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W62" s="57" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B63" s="45" t="n"/>
-      <c r="C63" s="53" t="n"/>
-      <c r="D63" s="53" t="n"/>
+      <c r="C63" s="46" t="n"/>
+      <c r="D63" s="46" t="n"/>
       <c r="E63" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F63" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G63" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G63" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="49" t="n"/>
       <c r="J63" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K63" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L63" s="50" t="n"/>
-      <c r="M63" s="55" t="n"/>
-      <c r="N63" s="55" t="n"/>
-      <c r="O63" s="55" t="n"/>
-      <c r="P63" s="55" t="n"/>
-      <c r="Q63" s="55" t="n"/>
-      <c r="R63" s="55" t="n"/>
-      <c r="S63" s="55" t="n"/>
-      <c r="T63" s="55" t="n"/>
-      <c r="U63" s="55" t="n"/>
-      <c r="V63" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W63" s="57" t="n"/>
+      <c r="M63" s="51" t="n"/>
+      <c r="N63" s="51" t="n"/>
+      <c r="O63" s="51" t="n"/>
+      <c r="P63" s="51" t="n"/>
+      <c r="Q63" s="51" t="n"/>
+      <c r="R63" s="51" t="n"/>
+      <c r="S63" s="51" t="n"/>
+      <c r="T63" s="51" t="n"/>
+      <c r="U63" s="51" t="n"/>
+      <c r="V63" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W63" s="58" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B64" s="45" t="n"/>
-      <c r="C64" s="46" t="n"/>
-      <c r="D64" s="46" t="n"/>
+      <c r="C64" s="53" t="n"/>
+      <c r="D64" s="53" t="n"/>
       <c r="E64" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F64" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G64" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G64" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="49" t="n"/>
       <c r="J64" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K64" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L64" s="50" t="n"/>
-      <c r="M64" s="51" t="n"/>
-      <c r="N64" s="51" t="n"/>
-      <c r="O64" s="51" t="n"/>
-      <c r="P64" s="51" t="n"/>
-      <c r="Q64" s="51" t="n"/>
-      <c r="R64" s="51" t="n"/>
-      <c r="S64" s="51" t="n"/>
-      <c r="T64" s="51" t="n"/>
-      <c r="U64" s="51" t="n"/>
-      <c r="V64" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W64" s="58" t="n"/>
+      <c r="M64" s="55" t="n"/>
+      <c r="N64" s="55" t="n"/>
+      <c r="O64" s="55" t="n"/>
+      <c r="P64" s="55" t="n"/>
+      <c r="Q64" s="55" t="n"/>
+      <c r="R64" s="55" t="n"/>
+      <c r="S64" s="55" t="n"/>
+      <c r="T64" s="55" t="n"/>
+      <c r="U64" s="55" t="n"/>
+      <c r="V64" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W64" s="57" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B65" s="45" t="n"/>
-      <c r="C65" s="53" t="n"/>
-      <c r="D65" s="53" t="n"/>
+      <c r="C65" s="46" t="n"/>
+      <c r="D65" s="46" t="n"/>
       <c r="E65" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F65" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G65" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G65" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H65" s="49" t="n"/>
       <c r="I65" s="49" t="n"/>
       <c r="J65" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K65" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L65" s="50" t="n"/>
-      <c r="M65" s="55" t="n"/>
-      <c r="N65" s="55" t="n"/>
-      <c r="O65" s="55" t="n"/>
-      <c r="P65" s="55" t="n"/>
-      <c r="Q65" s="55" t="n"/>
-      <c r="R65" s="55" t="n"/>
-      <c r="S65" s="55" t="n"/>
-      <c r="T65" s="55" t="n"/>
-      <c r="U65" s="55" t="n"/>
-      <c r="V65" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W65" s="57" t="n"/>
+      <c r="M65" s="51" t="n"/>
+      <c r="N65" s="51" t="n"/>
+      <c r="O65" s="51" t="n"/>
+      <c r="P65" s="51" t="n"/>
+      <c r="Q65" s="51" t="n"/>
+      <c r="R65" s="51" t="n"/>
+      <c r="S65" s="51" t="n"/>
+      <c r="T65" s="51" t="n"/>
+      <c r="U65" s="51" t="n"/>
+      <c r="V65" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W65" s="58" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B66" s="45" t="n"/>
-      <c r="C66" s="46" t="n"/>
-      <c r="D66" s="46" t="n"/>
+      <c r="C66" s="53" t="n"/>
+      <c r="D66" s="53" t="n"/>
       <c r="E66" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F66" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G66" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G66" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H66" s="49" t="n"/>
       <c r="I66" s="49" t="n"/>
       <c r="J66" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K66" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L66" s="50" t="n"/>
-      <c r="M66" s="51" t="n"/>
-      <c r="N66" s="51" t="n"/>
-      <c r="O66" s="51" t="n"/>
-      <c r="P66" s="51" t="n"/>
-      <c r="Q66" s="51" t="n"/>
-      <c r="R66" s="51" t="n"/>
-      <c r="S66" s="51" t="n"/>
-      <c r="T66" s="51" t="n"/>
-      <c r="U66" s="51" t="n"/>
-      <c r="V66" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W66" s="58" t="n"/>
+      <c r="M66" s="55" t="n"/>
+      <c r="N66" s="55" t="n"/>
+      <c r="O66" s="55" t="n"/>
+      <c r="P66" s="55" t="n"/>
+      <c r="Q66" s="55" t="n"/>
+      <c r="R66" s="55" t="n"/>
+      <c r="S66" s="55" t="n"/>
+      <c r="T66" s="55" t="n"/>
+      <c r="U66" s="55" t="n"/>
+      <c r="V66" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W66" s="57" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B67" s="45" t="n"/>
-      <c r="C67" s="53" t="n"/>
-      <c r="D67" s="53" t="n"/>
+      <c r="C67" s="46" t="n"/>
+      <c r="D67" s="46" t="n"/>
       <c r="E67" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F67" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G67" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G67" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H67" s="49" t="n"/>
       <c r="I67" s="49" t="n"/>
       <c r="J67" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K67" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L67" s="50" t="n"/>
-      <c r="M67" s="55" t="n"/>
-      <c r="N67" s="55" t="n"/>
-      <c r="O67" s="55" t="n"/>
-      <c r="P67" s="55" t="n"/>
-      <c r="Q67" s="55" t="n"/>
-      <c r="R67" s="55" t="n"/>
-      <c r="S67" s="55" t="n"/>
-      <c r="T67" s="55" t="n"/>
-      <c r="U67" s="55" t="n"/>
-      <c r="V67" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W67" s="57" t="n"/>
+      <c r="M67" s="51" t="n"/>
+      <c r="N67" s="51" t="n"/>
+      <c r="O67" s="51" t="n"/>
+      <c r="P67" s="51" t="n"/>
+      <c r="Q67" s="51" t="n"/>
+      <c r="R67" s="51" t="n"/>
+      <c r="S67" s="51" t="n"/>
+      <c r="T67" s="51" t="n"/>
+      <c r="U67" s="51" t="n"/>
+      <c r="V67" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W67" s="58" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B68" s="45" t="n"/>
-      <c r="C68" s="46" t="n"/>
-      <c r="D68" s="46" t="n"/>
+      <c r="C68" s="53" t="n"/>
+      <c r="D68" s="53" t="n"/>
       <c r="E68" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F68" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G68" s="48" t="n">
-        <v>24</v>
+      <c r="G68" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H68" s="49" t="n"/>
       <c r="I68" s="49" t="n"/>
       <c r="J68" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K68" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L68" s="50" t="n"/>
-      <c r="M68" s="51" t="n"/>
-      <c r="N68" s="51" t="n"/>
-      <c r="O68" s="51" t="n"/>
-      <c r="P68" s="51" t="n"/>
-      <c r="Q68" s="51" t="n"/>
-      <c r="R68" s="51" t="n"/>
-      <c r="S68" s="51" t="n"/>
-      <c r="T68" s="51" t="n"/>
-      <c r="U68" s="51" t="n"/>
-      <c r="V68" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W68" s="58" t="n"/>
+      <c r="M68" s="55" t="n"/>
+      <c r="N68" s="55" t="n"/>
+      <c r="O68" s="55" t="n"/>
+      <c r="P68" s="55" t="n"/>
+      <c r="Q68" s="55" t="n"/>
+      <c r="R68" s="55" t="n"/>
+      <c r="S68" s="55" t="n"/>
+      <c r="T68" s="55" t="n"/>
+      <c r="U68" s="55" t="n"/>
+      <c r="V68" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W68" s="57" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B69" s="45" t="n"/>
-      <c r="C69" s="53" t="n"/>
-      <c r="D69" s="53" t="n"/>
+      <c r="C69" s="46" t="n"/>
+      <c r="D69" s="46" t="n"/>
       <c r="E69" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F69" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G69" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G69" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H69" s="49" t="n"/>
       <c r="I69" s="49" t="n"/>
       <c r="J69" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K69" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L69" s="50" t="n"/>
-      <c r="M69" s="55" t="n"/>
-      <c r="N69" s="55" t="n"/>
-      <c r="O69" s="55" t="n"/>
-      <c r="P69" s="55" t="n"/>
-      <c r="Q69" s="55" t="n"/>
-      <c r="R69" s="55" t="n"/>
-      <c r="S69" s="55" t="n"/>
-      <c r="T69" s="55" t="n"/>
-      <c r="U69" s="55" t="n"/>
-      <c r="V69" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W69" s="57" t="n"/>
+      <c r="M69" s="51" t="n"/>
+      <c r="N69" s="51" t="n"/>
+      <c r="O69" s="51" t="n"/>
+      <c r="P69" s="51" t="n"/>
+      <c r="Q69" s="51" t="n"/>
+      <c r="R69" s="51" t="n"/>
+      <c r="S69" s="51" t="n"/>
+      <c r="T69" s="51" t="n"/>
+      <c r="U69" s="51" t="n"/>
+      <c r="V69" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W69" s="58" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B70" s="45" t="n"/>
-      <c r="C70" s="46" t="n"/>
-      <c r="D70" s="46" t="n"/>
+      <c r="C70" s="53" t="n"/>
+      <c r="D70" s="53" t="n"/>
       <c r="E70" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F70" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G70" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G70" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H70" s="49" t="n"/>
       <c r="I70" s="49" t="n"/>
       <c r="J70" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K70" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L70" s="50" t="n"/>
-      <c r="M70" s="51" t="n"/>
-      <c r="N70" s="51" t="n"/>
-      <c r="O70" s="51" t="n"/>
-      <c r="P70" s="51" t="n"/>
-      <c r="Q70" s="51" t="n"/>
-      <c r="R70" s="51" t="n"/>
-      <c r="S70" s="51" t="n"/>
-      <c r="T70" s="51" t="n"/>
-      <c r="U70" s="51" t="n"/>
-      <c r="V70" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W70" s="58" t="n"/>
+      <c r="M70" s="55" t="n"/>
+      <c r="N70" s="55" t="n"/>
+      <c r="O70" s="55" t="n"/>
+      <c r="P70" s="55" t="n"/>
+      <c r="Q70" s="55" t="n"/>
+      <c r="R70" s="55" t="n"/>
+      <c r="S70" s="55" t="n"/>
+      <c r="T70" s="55" t="n"/>
+      <c r="U70" s="55" t="n"/>
+      <c r="V70" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W70" s="57" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B71" s="45" t="n"/>
-      <c r="C71" s="53" t="n"/>
-      <c r="D71" s="53" t="n"/>
+      <c r="C71" s="46" t="n"/>
+      <c r="D71" s="46" t="n"/>
       <c r="E71" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F71" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G71" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H71" s="49" t="n"/>
       <c r="I71" s="49" t="n"/>
@@ -5203,51 +5225,92 @@
         <v>59</v>
       </c>
       <c r="K71" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L71" s="50" t="n"/>
-      <c r="M71" s="55" t="n"/>
-      <c r="N71" s="55" t="n"/>
-      <c r="O71" s="55" t="n"/>
-      <c r="P71" s="55" t="n"/>
-      <c r="Q71" s="55" t="n"/>
-      <c r="R71" s="55" t="n"/>
-      <c r="S71" s="55" t="n"/>
-      <c r="T71" s="55" t="n"/>
-      <c r="U71" s="55" t="n"/>
-      <c r="V71" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W71" s="57" t="n"/>
+      <c r="M71" s="51" t="n"/>
+      <c r="N71" s="51" t="n"/>
+      <c r="O71" s="51" t="n"/>
+      <c r="P71" s="51" t="n"/>
+      <c r="Q71" s="51" t="n"/>
+      <c r="R71" s="51" t="n"/>
+      <c r="S71" s="51" t="n"/>
+      <c r="T71" s="51" t="n"/>
+      <c r="U71" s="51" t="n"/>
+      <c r="V71" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W71" s="58" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B72" s="45" t="n"/>
-      <c r="C72" s="46" t="n"/>
-      <c r="D72" s="46" t="n"/>
-      <c r="E72" s="47" t="n"/>
-      <c r="F72" s="47" t="n"/>
-      <c r="G72" s="60" t="n"/>
+      <c r="C72" s="53" t="n"/>
+      <c r="D72" s="53" t="n"/>
+      <c r="E72" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F72" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G72" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H72" s="49" t="n"/>
       <c r="I72" s="49" t="n"/>
-      <c r="J72" s="50" t="n"/>
-      <c r="K72" s="50" t="n"/>
+      <c r="J72" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K72" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L72" s="50" t="n"/>
-      <c r="M72" s="51" t="n"/>
-      <c r="N72" s="51" t="n"/>
-      <c r="O72" s="51" t="n"/>
-      <c r="P72" s="51" t="n"/>
-      <c r="Q72" s="51" t="n"/>
-      <c r="R72" s="51" t="n"/>
-      <c r="S72" s="51" t="n"/>
-      <c r="T72" s="51" t="n"/>
-      <c r="U72" s="51" t="n"/>
-      <c r="V72" s="61" t="n"/>
-      <c r="W72" s="61" t="n"/>
+      <c r="M72" s="55" t="n"/>
+      <c r="N72" s="55" t="n"/>
+      <c r="O72" s="55" t="n"/>
+      <c r="P72" s="55" t="n"/>
+      <c r="Q72" s="55" t="n"/>
+      <c r="R72" s="55" t="n"/>
+      <c r="S72" s="55" t="n"/>
+      <c r="T72" s="55" t="n"/>
+      <c r="U72" s="55" t="n"/>
+      <c r="V72" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W72" s="57" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B73" s="45" t="n"/>
+      <c r="C73" s="46" t="n"/>
+      <c r="D73" s="46" t="n"/>
+      <c r="E73" s="47" t="n"/>
+      <c r="F73" s="47" t="n"/>
+      <c r="G73" s="60" t="n"/>
+      <c r="H73" s="49" t="n"/>
+      <c r="I73" s="49" t="n"/>
+      <c r="J73" s="50" t="n"/>
+      <c r="K73" s="50" t="n"/>
+      <c r="L73" s="50" t="n"/>
+      <c r="M73" s="51" t="n"/>
+      <c r="N73" s="51" t="n"/>
+      <c r="O73" s="51" t="n"/>
+      <c r="P73" s="51" t="n"/>
+      <c r="Q73" s="51" t="n"/>
+      <c r="R73" s="51" t="n"/>
+      <c r="S73" s="51" t="n"/>
+      <c r="T73" s="51" t="n"/>
+      <c r="U73" s="51" t="n"/>
+      <c r="V73" s="61" t="n"/>
+      <c r="W73" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W73"/>
+  <dimension ref="A1:W74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,57 +1982,49 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/17(五)</t>
+          <t>2026/04/20(一)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G4" s="66" t="n">
-        <v>22</v>
+        <v>16.7</v>
       </c>
       <c r="H4" s="67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I4" s="67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J4" s="68" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K4" s="68" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L4" s="68" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M4" s="69" t="inlineStr">
         <is>
-          <t>均瑶健康、京投发展</t>
-        </is>
-      </c>
-      <c r="N4" s="69" t="inlineStr">
-        <is>
-          <t>盛视科技</t>
-        </is>
-      </c>
-      <c r="O4" s="69" t="inlineStr">
+          <t>株冶集团、华升股份、可川科技</t>
+        </is>
+      </c>
+      <c r="N4" s="69" t="inlineStr"/>
+      <c r="O4" s="69" t="inlineStr"/>
+      <c r="P4" s="69" t="inlineStr">
         <is>
           <t>博云新材</t>
         </is>
       </c>
-      <c r="P4" s="69" t="inlineStr"/>
-      <c r="Q4" s="69" t="inlineStr">
-        <is>
-          <t>圣阳股份</t>
-        </is>
-      </c>
+      <c r="Q4" s="69" t="inlineStr"/>
       <c r="R4" s="69" t="inlineStr"/>
       <c r="S4" s="69" t="inlineStr"/>
       <c r="T4" s="69" t="inlineStr"/>
@@ -2045,193 +2037,197 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/16(四)</t>
+          <t>2026/04/17(五)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
       <c r="C5" s="64" t="inlineStr"/>
       <c r="D5" s="64" t="inlineStr"/>
       <c r="E5" s="65" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G5" s="66" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" s="67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" s="68" t="n">
+        <v>13</v>
+      </c>
+      <c r="K5" s="68" t="n">
+        <v>58</v>
+      </c>
+      <c r="L5" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="K5" s="68" t="n">
-        <v>71</v>
-      </c>
-      <c r="L5" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="M5" s="69" t="inlineStr">
         <is>
+          <t>均瑶健康、京投发展</t>
+        </is>
+      </c>
+      <c r="N5" s="69" t="inlineStr">
+        <is>
           <t>盛视科技</t>
         </is>
       </c>
-      <c r="N5" s="69" t="inlineStr">
+      <c r="O5" s="69" t="inlineStr">
         <is>
           <t>博云新材</t>
         </is>
       </c>
-      <c r="O5" s="69" t="inlineStr"/>
-      <c r="P5" s="69" t="inlineStr">
+      <c r="P5" s="69" t="inlineStr"/>
+      <c r="Q5" s="69" t="inlineStr">
         <is>
           <t>圣阳股份</t>
         </is>
       </c>
-      <c r="Q5" s="69" t="inlineStr"/>
       <c r="R5" s="69" t="inlineStr"/>
       <c r="S5" s="69" t="inlineStr"/>
       <c r="T5" s="69" t="inlineStr"/>
       <c r="U5" s="69" t="inlineStr"/>
       <c r="V5" s="69" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="W5" s="69" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/04/15(三)</t>
+          <t>2026/04/16(四)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
       <c r="C6" s="64" t="inlineStr"/>
       <c r="D6" s="64" t="inlineStr"/>
       <c r="E6" s="65" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>57</v>
-      </c>
-      <c r="G6" s="71" t="n">
-        <v>29.6</v>
+        <v>79</v>
+      </c>
+      <c r="G6" s="66" t="n">
+        <v>22.5</v>
       </c>
       <c r="H6" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I6" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" s="68" t="n">
-        <v>11</v>
-      </c>
       <c r="K6" s="68" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="L6" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M6" s="69" t="inlineStr">
         <is>
-          <t>博云新材、天邦食品</t>
-        </is>
-      </c>
-      <c r="N6" s="69" t="inlineStr"/>
-      <c r="O6" s="69" t="inlineStr">
+          <t>盛视科技</t>
+        </is>
+      </c>
+      <c r="N6" s="69" t="inlineStr">
+        <is>
+          <t>博云新材</t>
+        </is>
+      </c>
+      <c r="O6" s="69" t="inlineStr"/>
+      <c r="P6" s="69" t="inlineStr">
         <is>
           <t>圣阳股份</t>
         </is>
       </c>
-      <c r="P6" s="69" t="inlineStr"/>
       <c r="Q6" s="69" t="inlineStr"/>
       <c r="R6" s="69" t="inlineStr"/>
       <c r="S6" s="69" t="inlineStr"/>
       <c r="T6" s="69" t="inlineStr"/>
       <c r="U6" s="69" t="inlineStr"/>
       <c r="V6" s="69" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="W6" s="69" t="inlineStr"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="62" t="inlineStr">
         <is>
-          <t>2026/04/14(二)</t>
+          <t>2026/04/15(三)</t>
         </is>
       </c>
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="64" t="inlineStr"/>
       <c r="D7" s="64" t="inlineStr"/>
       <c r="E7" s="65" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F7" s="65" t="n">
-        <v>55</v>
-      </c>
-      <c r="G7" s="66" t="n">
-        <v>24.7</v>
+        <v>57</v>
+      </c>
+      <c r="G7" s="71" t="n">
+        <v>29.6</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I7" s="67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J7" s="68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K7" s="68" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L7" s="68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M7" s="69" t="inlineStr">
         <is>
-          <t>美能能源</t>
-        </is>
-      </c>
-      <c r="N7" s="69" t="inlineStr">
-        <is>
-          <t>中恒电气、圣阳股份</t>
-        </is>
-      </c>
-      <c r="O7" s="69" t="inlineStr"/>
-      <c r="P7" s="69" t="inlineStr">
-        <is>
-          <t>华远控股</t>
-        </is>
-      </c>
+          <t>博云新材、天邦食品</t>
+        </is>
+      </c>
+      <c r="N7" s="69" t="inlineStr"/>
+      <c r="O7" s="69" t="inlineStr">
+        <is>
+          <t>圣阳股份</t>
+        </is>
+      </c>
+      <c r="P7" s="69" t="inlineStr"/>
       <c r="Q7" s="69" t="inlineStr"/>
       <c r="R7" s="69" t="inlineStr"/>
       <c r="S7" s="69" t="inlineStr"/>
       <c r="T7" s="69" t="inlineStr"/>
       <c r="U7" s="69" t="inlineStr"/>
       <c r="V7" s="69" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="W7" s="69" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="62" t="inlineStr">
         <is>
-          <t>2026/04/13(一)</t>
+          <t>2026/04/14(二)</t>
         </is>
       </c>
       <c r="B8" s="63" t="inlineStr"/>
       <c r="C8" s="64" t="inlineStr"/>
       <c r="D8" s="64" t="inlineStr"/>
       <c r="E8" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F8" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G8" s="66" t="n">
-        <v>20.3</v>
+        <v>24.7</v>
       </c>
       <c r="H8" s="67" t="n">
         <v>4</v>
@@ -2240,30 +2236,30 @@
         <v>4</v>
       </c>
       <c r="J8" s="68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K8" s="68" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L8" s="68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M8" s="69" t="inlineStr">
         <is>
+          <t>美能能源</t>
+        </is>
+      </c>
+      <c r="N8" s="69" t="inlineStr">
+        <is>
           <t>中恒电气、圣阳股份</t>
         </is>
       </c>
-      <c r="N8" s="69" t="inlineStr">
-        <is>
-          <t>长源东谷</t>
-        </is>
-      </c>
-      <c r="O8" s="69" t="inlineStr">
+      <c r="O8" s="69" t="inlineStr"/>
+      <c r="P8" s="69" t="inlineStr">
         <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="P8" s="69" t="inlineStr"/>
       <c r="Q8" s="69" t="inlineStr"/>
       <c r="R8" s="69" t="inlineStr"/>
       <c r="S8" s="69" t="inlineStr"/>
@@ -2277,7 +2273,7 @@
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="62" t="inlineStr">
         <is>
-          <t>2026/04/10(五)</t>
+          <t>2026/04/13(一)</t>
         </is>
       </c>
       <c r="B9" s="63" t="inlineStr"/>
@@ -2289,35 +2285,39 @@
       <c r="F9" s="65" t="n">
         <v>59</v>
       </c>
-      <c r="G9" s="71" t="n">
-        <v>31.4</v>
+      <c r="G9" s="66" t="n">
+        <v>20.3</v>
       </c>
       <c r="H9" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I9" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" s="68" t="n">
-        <v>13</v>
-      </c>
       <c r="K9" s="68" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L9" s="68" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M9" s="69" t="inlineStr">
         <is>
-          <t>中嘉博创、长源东谷、来伊份</t>
+          <t>中恒电气、圣阳股份</t>
         </is>
       </c>
       <c r="N9" s="69" t="inlineStr">
         <is>
+          <t>长源东谷</t>
+        </is>
+      </c>
+      <c r="O9" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="O9" s="69" t="inlineStr"/>
       <c r="P9" s="69" t="inlineStr"/>
       <c r="Q9" s="69" t="inlineStr"/>
       <c r="R9" s="69" t="inlineStr"/>
@@ -2325,54 +2325,54 @@
       <c r="T9" s="69" t="inlineStr"/>
       <c r="U9" s="69" t="inlineStr"/>
       <c r="V9" s="69" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="W9" s="69" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="62" t="inlineStr">
         <is>
-          <t>2026/04/09(四)</t>
+          <t>2026/04/10(五)</t>
         </is>
       </c>
       <c r="B10" s="63" t="inlineStr"/>
       <c r="C10" s="64" t="inlineStr"/>
       <c r="D10" s="64" t="inlineStr"/>
       <c r="E10" s="65" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F10" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G10" s="66" t="n">
-        <v>23.2</v>
+        <v>59</v>
+      </c>
+      <c r="G10" s="71" t="n">
+        <v>31.4</v>
       </c>
       <c r="H10" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I10" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J10" s="68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K10" s="68" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L10" s="68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M10" s="69" t="inlineStr">
         <is>
+          <t>中嘉博创、长源东谷、来伊份</t>
+        </is>
+      </c>
+      <c r="N10" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="N10" s="69" t="inlineStr"/>
-      <c r="O10" s="69" t="inlineStr">
-        <is>
-          <t>汇源通信</t>
-        </is>
-      </c>
+      <c r="O10" s="69" t="inlineStr"/>
       <c r="P10" s="69" t="inlineStr"/>
       <c r="Q10" s="69" t="inlineStr"/>
       <c r="R10" s="69" t="inlineStr"/>
@@ -2380,54 +2380,54 @@
       <c r="T10" s="69" t="inlineStr"/>
       <c r="U10" s="69" t="inlineStr"/>
       <c r="V10" s="69" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="W10" s="69" t="inlineStr"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="62" t="inlineStr">
         <is>
-          <t>2026/04/08(三)</t>
+          <t>2026/04/09(四)</t>
         </is>
       </c>
       <c r="B11" s="63" t="inlineStr"/>
       <c r="C11" s="64" t="inlineStr"/>
       <c r="D11" s="64" t="inlineStr"/>
       <c r="E11" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="F11" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="G11" s="66" t="n">
-        <v>11.5</v>
+        <v>23.2</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J11" s="68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K11" s="68" t="n">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="L11" s="68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M11" s="69" t="inlineStr">
         <is>
-          <t>中安科</t>
-        </is>
-      </c>
-      <c r="N11" s="69" t="inlineStr">
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="N11" s="69" t="inlineStr"/>
+      <c r="O11" s="69" t="inlineStr">
         <is>
           <t>汇源通信</t>
         </is>
       </c>
-      <c r="O11" s="69" t="inlineStr"/>
       <c r="P11" s="69" t="inlineStr"/>
       <c r="Q11" s="69" t="inlineStr"/>
       <c r="R11" s="69" t="inlineStr"/>
@@ -2442,20 +2442,20 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="62" t="inlineStr">
         <is>
-          <t>2026/04/07(二)</t>
+          <t>2026/04/08(三)</t>
         </is>
       </c>
       <c r="B12" s="63" t="inlineStr"/>
       <c r="C12" s="64" t="inlineStr"/>
       <c r="D12" s="64" t="inlineStr"/>
       <c r="E12" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F12" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G12" s="66" t="n">
-        <v>21.8</v>
+        <v>11.5</v>
       </c>
       <c r="H12" s="67" t="n">
         <v>4</v>
@@ -2464,91 +2464,95 @@
         <v>4</v>
       </c>
       <c r="J12" s="68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K12" s="68" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="L12" s="68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M12" s="69" t="inlineStr">
         <is>
-          <t>汇源通信、新能泰山</t>
-        </is>
-      </c>
-      <c r="N12" s="69" t="inlineStr"/>
+          <t>中安科</t>
+        </is>
+      </c>
+      <c r="N12" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信</t>
+        </is>
+      </c>
       <c r="O12" s="69" t="inlineStr"/>
       <c r="P12" s="69" t="inlineStr"/>
-      <c r="Q12" s="69" t="inlineStr">
-        <is>
-          <t>津药药业</t>
-        </is>
-      </c>
+      <c r="Q12" s="69" t="inlineStr"/>
       <c r="R12" s="69" t="inlineStr"/>
       <c r="S12" s="69" t="inlineStr"/>
       <c r="T12" s="69" t="inlineStr"/>
       <c r="U12" s="69" t="inlineStr"/>
       <c r="V12" s="69" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W12" s="69" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="62" t="inlineStr">
         <is>
-          <t>2026/04/06(一)</t>
+          <t>2026/04/07(二)</t>
         </is>
       </c>
       <c r="B13" s="63" t="inlineStr"/>
       <c r="C13" s="64" t="inlineStr"/>
       <c r="D13" s="64" t="inlineStr"/>
       <c r="E13" s="65" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F13" s="65" t="n">
-        <v>36</v>
-      </c>
-      <c r="G13" s="71" t="n">
-        <v>25</v>
+        <v>93</v>
+      </c>
+      <c r="G13" s="66" t="n">
+        <v>21.8</v>
       </c>
       <c r="H13" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I13" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J13" s="68" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="L13" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K13" s="68" t="n">
-        <v>32</v>
-      </c>
-      <c r="L13" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" s="69" t="inlineStr"/>
+      <c r="M13" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信、新能泰山</t>
+        </is>
+      </c>
       <c r="N13" s="69" t="inlineStr"/>
       <c r="O13" s="69" t="inlineStr"/>
-      <c r="P13" s="69" t="inlineStr">
+      <c r="P13" s="69" t="inlineStr"/>
+      <c r="Q13" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="Q13" s="69" t="inlineStr"/>
       <c r="R13" s="69" t="inlineStr"/>
       <c r="S13" s="69" t="inlineStr"/>
       <c r="T13" s="69" t="inlineStr"/>
       <c r="U13" s="69" t="inlineStr"/>
       <c r="V13" s="69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W13" s="69" t="inlineStr"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="62" t="inlineStr">
         <is>
-          <t>2026/04/03(五)</t>
+          <t>2026/04/06(一)</t>
         </is>
       </c>
       <c r="B14" s="63" t="inlineStr"/>
@@ -2592,105 +2596,105 @@
       <c r="T14" s="69" t="inlineStr"/>
       <c r="U14" s="69" t="inlineStr"/>
       <c r="V14" s="69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W14" s="69" t="inlineStr"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B15" s="63" t="inlineStr"/>
       <c r="C15" s="64" t="inlineStr"/>
       <c r="D15" s="64" t="inlineStr"/>
       <c r="E15" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F15" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G15" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H15" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I15" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J15" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K15" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L15" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M15" s="69" t="inlineStr"/>
       <c r="N15" s="69" t="inlineStr"/>
-      <c r="O15" s="69" t="inlineStr">
+      <c r="O15" s="69" t="inlineStr"/>
+      <c r="P15" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P15" s="69" t="inlineStr"/>
       <c r="Q15" s="69" t="inlineStr"/>
       <c r="R15" s="69" t="inlineStr"/>
       <c r="S15" s="69" t="inlineStr"/>
       <c r="T15" s="69" t="inlineStr"/>
       <c r="U15" s="69" t="inlineStr"/>
       <c r="V15" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W15" s="69" t="inlineStr"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B16" s="63" t="inlineStr"/>
       <c r="C16" s="64" t="inlineStr"/>
       <c r="D16" s="64" t="inlineStr"/>
       <c r="E16" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F16" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G16" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G16" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H16" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I16" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K16" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L16" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" s="69" t="inlineStr"/>
-      <c r="N16" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M16" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N16" s="69" t="inlineStr"/>
+      <c r="O16" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O16" s="69" t="inlineStr"/>
       <c r="P16" s="69" t="inlineStr"/>
       <c r="Q16" s="69" t="inlineStr"/>
       <c r="R16" s="69" t="inlineStr"/>
@@ -2698,51 +2702,47 @@
       <c r="T16" s="69" t="inlineStr"/>
       <c r="U16" s="69" t="inlineStr"/>
       <c r="V16" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W16" s="69" t="inlineStr"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B17" s="63" t="inlineStr"/>
       <c r="C17" s="64" t="inlineStr"/>
       <c r="D17" s="64" t="inlineStr"/>
       <c r="E17" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F17" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G17" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G17" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H17" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I17" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J17" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K17" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L17" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M17" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M17" s="69" t="inlineStr"/>
+      <c r="N17" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N17" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O17" s="69" t="inlineStr"/>
@@ -2753,254 +2753,250 @@
       <c r="T17" s="69" t="inlineStr"/>
       <c r="U17" s="69" t="inlineStr"/>
       <c r="V17" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W17" s="69" t="inlineStr"/>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B18" s="63" t="inlineStr"/>
+      <c r="C18" s="64" t="inlineStr"/>
+      <c r="D18" s="64" t="inlineStr"/>
+      <c r="E18" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F18" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G18" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L18" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M18" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N18" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O18" s="69" t="inlineStr"/>
+      <c r="P18" s="69" t="inlineStr"/>
+      <c r="Q18" s="69" t="inlineStr"/>
+      <c r="R18" s="69" t="inlineStr"/>
+      <c r="S18" s="69" t="inlineStr"/>
+      <c r="T18" s="69" t="inlineStr"/>
+      <c r="U18" s="69" t="inlineStr"/>
+      <c r="V18" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W17" s="69" t="inlineStr"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="W18" s="69" t="inlineStr"/>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C18" s="38" t="inlineStr">
+      <c r="C19" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D18" s="38" t="inlineStr">
+      <c r="D19" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E18" s="39" t="n">
+      <c r="E19" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F18" s="39" t="n">
+      <c r="F19" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G18" s="40" t="n">
+      <c r="G19" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H18" s="41" t="n">
+      <c r="H19" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I18" s="41" t="n">
+      <c r="I19" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J18" s="42" t="n">
+      <c r="J19" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K18" s="42" t="n">
+      <c r="K19" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L18" s="42" t="n">
+      <c r="L19" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M18" s="43" t="inlineStr">
+      <c r="M19" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N18" s="43" t="inlineStr"/>
-      <c r="O18" s="43" t="inlineStr">
+      <c r="N19" s="43" t="inlineStr"/>
+      <c r="O19" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P18" s="43" t="inlineStr"/>
-      <c r="Q18" s="43" t="inlineStr"/>
-      <c r="R18" s="43" t="inlineStr"/>
-      <c r="S18" s="43" t="inlineStr"/>
-      <c r="T18" s="43" t="inlineStr"/>
-      <c r="U18" s="43" t="inlineStr"/>
-      <c r="V18" s="43" t="n">
+      <c r="P19" s="43" t="inlineStr"/>
+      <c r="Q19" s="43" t="inlineStr"/>
+      <c r="R19" s="43" t="inlineStr"/>
+      <c r="S19" s="43" t="inlineStr"/>
+      <c r="T19" s="43" t="inlineStr"/>
+      <c r="U19" s="43" t="inlineStr"/>
+      <c r="V19" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W18" s="43" t="inlineStr"/>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B19" s="45" t="n"/>
-      <c r="C19" s="46" t="n"/>
-      <c r="D19" s="46" t="n"/>
-      <c r="E19" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F19" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G19" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H19" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K19" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L19" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M19" s="51" t="n"/>
-      <c r="N19" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O19" s="51" t="n"/>
-      <c r="P19" s="51" t="n"/>
-      <c r="Q19" s="51" t="n"/>
-      <c r="R19" s="51" t="n"/>
-      <c r="S19" s="51" t="n"/>
-      <c r="T19" s="51" t="n"/>
-      <c r="U19" s="51" t="n"/>
-      <c r="V19" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W19" s="43" t="inlineStr"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B20" s="45" t="n"/>
-      <c r="C20" s="53" t="n"/>
-      <c r="D20" s="53" t="n"/>
+      <c r="C20" s="46" t="n"/>
+      <c r="D20" s="46" t="n"/>
       <c r="E20" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F20" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G20" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G20" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H20" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I20" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J20" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K20" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L20" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M20" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N20" s="55" t="n"/>
-      <c r="O20" s="55" t="n"/>
-      <c r="P20" s="55" t="n"/>
-      <c r="Q20" s="55" t="n"/>
-      <c r="R20" s="55" t="n"/>
-      <c r="S20" s="55" t="n"/>
-      <c r="T20" s="55" t="n"/>
-      <c r="U20" s="55" t="n"/>
-      <c r="V20" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W20" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M20" s="51" t="n"/>
+      <c r="N20" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O20" s="51" t="n"/>
+      <c r="P20" s="51" t="n"/>
+      <c r="Q20" s="51" t="n"/>
+      <c r="R20" s="51" t="n"/>
+      <c r="S20" s="51" t="n"/>
+      <c r="T20" s="51" t="n"/>
+      <c r="U20" s="51" t="n"/>
+      <c r="V20" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="46" t="n"/>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="53" t="n"/>
       <c r="E21" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F21" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G21" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G21" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H21" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J21" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K21" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L21" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M21" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N21" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O21" s="51" t="n"/>
-      <c r="P21" s="51" t="n"/>
-      <c r="Q21" s="51" t="n"/>
-      <c r="R21" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S21" s="51" t="n"/>
-      <c r="T21" s="51" t="n"/>
-      <c r="U21" s="51" t="n"/>
-      <c r="V21" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W21" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M21" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N21" s="55" t="n"/>
+      <c r="O21" s="55" t="n"/>
+      <c r="P21" s="55" t="n"/>
+      <c r="Q21" s="55" t="n"/>
+      <c r="R21" s="55" t="n"/>
+      <c r="S21" s="55" t="n"/>
+      <c r="T21" s="55" t="n"/>
+      <c r="U21" s="55" t="n"/>
+      <c r="V21" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W21" s="57" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="53" t="n"/>
+      <c r="C22" s="46" t="n"/>
+      <c r="D22" s="46" t="n"/>
       <c r="E22" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G22" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H22" s="49" t="n">
         <v>1</v>
@@ -3009,493 +3005,497 @@
         <v>1</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K22" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L22" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M22" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M22" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N22" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N22" s="55" t="n"/>
-      <c r="O22" s="55" t="n"/>
-      <c r="P22" s="55" t="n"/>
-      <c r="Q22" s="55" t="inlineStr">
+      <c r="O22" s="51" t="n"/>
+      <c r="P22" s="51" t="n"/>
+      <c r="Q22" s="51" t="n"/>
+      <c r="R22" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R22" s="55" t="n"/>
-      <c r="S22" s="55" t="n"/>
-      <c r="T22" s="55" t="n"/>
-      <c r="U22" s="55" t="n"/>
-      <c r="V22" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W22" s="57" t="n"/>
+      <c r="S22" s="51" t="n"/>
+      <c r="T22" s="51" t="n"/>
+      <c r="U22" s="51" t="n"/>
+      <c r="V22" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W22" s="58" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="46" t="n"/>
-      <c r="D23" s="46" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G23" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G23" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H23" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L23" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N23" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O23" s="51" t="n"/>
-      <c r="P23" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M23" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N23" s="55" t="n"/>
+      <c r="O23" s="55" t="n"/>
+      <c r="P23" s="55" t="n"/>
+      <c r="Q23" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q23" s="51" t="n"/>
-      <c r="R23" s="51" t="n"/>
-      <c r="S23" s="51" t="n"/>
-      <c r="T23" s="51" t="n"/>
-      <c r="U23" s="51" t="n"/>
-      <c r="V23" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W23" s="58" t="n"/>
+      <c r="R23" s="55" t="n"/>
+      <c r="S23" s="55" t="n"/>
+      <c r="T23" s="55" t="n"/>
+      <c r="U23" s="55" t="n"/>
+      <c r="V23" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W23" s="57" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
+      <c r="C24" s="46" t="n"/>
+      <c r="D24" s="46" t="n"/>
       <c r="E24" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F24" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G24" s="59" t="n">
-        <v>45.1</v>
+      <c r="G24" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H24" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L24" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M24" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N24" s="55" t="n"/>
-      <c r="O24" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P24" s="55" t="n"/>
-      <c r="Q24" s="55" t="n"/>
-      <c r="R24" s="55" t="n"/>
-      <c r="S24" s="55" t="n"/>
-      <c r="T24" s="55" t="n"/>
-      <c r="U24" s="55" t="n"/>
-      <c r="V24" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W24" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M24" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N24" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O24" s="51" t="n"/>
+      <c r="P24" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q24" s="51" t="n"/>
+      <c r="R24" s="51" t="n"/>
+      <c r="S24" s="51" t="n"/>
+      <c r="T24" s="51" t="n"/>
+      <c r="U24" s="51" t="n"/>
+      <c r="V24" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W24" s="58" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="46" t="n"/>
-      <c r="D25" s="46" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
       <c r="E25" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F25" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G25" s="54" t="n">
-        <v>26.3</v>
+      <c r="G25" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H25" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L25" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M25" s="51" t="n"/>
-      <c r="N25" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M25" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N25" s="55" t="n"/>
+      <c r="O25" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O25" s="51" t="n"/>
-      <c r="P25" s="51" t="n"/>
-      <c r="Q25" s="51" t="n"/>
-      <c r="R25" s="51" t="n"/>
-      <c r="S25" s="51" t="n"/>
-      <c r="T25" s="51" t="n"/>
-      <c r="U25" s="51" t="n"/>
-      <c r="V25" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W25" s="58" t="n"/>
+      <c r="P25" s="55" t="n"/>
+      <c r="Q25" s="55" t="n"/>
+      <c r="R25" s="55" t="n"/>
+      <c r="S25" s="55" t="n"/>
+      <c r="T25" s="55" t="n"/>
+      <c r="U25" s="55" t="n"/>
+      <c r="V25" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W25" s="57" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="53" t="n"/>
-      <c r="D26" s="53" t="n"/>
+      <c r="C26" s="46" t="n"/>
+      <c r="D26" s="46" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G26" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H26" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I26" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L26" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M26" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M26" s="51" t="n"/>
+      <c r="N26" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N26" s="55" t="n"/>
-      <c r="O26" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P26" s="55" t="n"/>
-      <c r="Q26" s="55" t="n"/>
-      <c r="R26" s="55" t="n"/>
-      <c r="S26" s="55" t="n"/>
-      <c r="T26" s="55" t="n"/>
-      <c r="U26" s="55" t="n"/>
-      <c r="V26" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W26" s="57" t="n"/>
+      <c r="O26" s="51" t="n"/>
+      <c r="P26" s="51" t="n"/>
+      <c r="Q26" s="51" t="n"/>
+      <c r="R26" s="51" t="n"/>
+      <c r="S26" s="51" t="n"/>
+      <c r="T26" s="51" t="n"/>
+      <c r="U26" s="51" t="n"/>
+      <c r="V26" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W26" s="58" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="46" t="n"/>
-      <c r="D27" s="46" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G27" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H27" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I27" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L27" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M27" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N27" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O27" s="51" t="n"/>
-      <c r="P27" s="51" t="n"/>
-      <c r="Q27" s="51" t="n"/>
-      <c r="R27" s="51" t="n"/>
-      <c r="S27" s="51" t="n"/>
-      <c r="T27" s="51" t="n"/>
-      <c r="U27" s="51" t="n"/>
-      <c r="V27" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W27" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M27" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N27" s="55" t="n"/>
+      <c r="O27" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P27" s="55" t="n"/>
+      <c r="Q27" s="55" t="n"/>
+      <c r="R27" s="55" t="n"/>
+      <c r="S27" s="55" t="n"/>
+      <c r="T27" s="55" t="n"/>
+      <c r="U27" s="55" t="n"/>
+      <c r="V27" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W27" s="57" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="53" t="n"/>
-      <c r="D28" s="53" t="n"/>
+      <c r="C28" s="46" t="n"/>
+      <c r="D28" s="46" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G28" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H28" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I28" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K28" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L28" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I28" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J28" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K28" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L28" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M28" s="55" t="inlineStr">
+      <c r="M28" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N28" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N28" s="55" t="n"/>
-      <c r="O28" s="55" t="n"/>
-      <c r="P28" s="55" t="n"/>
-      <c r="Q28" s="55" t="n"/>
-      <c r="R28" s="55" t="n"/>
-      <c r="S28" s="55" t="n"/>
-      <c r="T28" s="55" t="n"/>
-      <c r="U28" s="55" t="n"/>
-      <c r="V28" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W28" s="57" t="n"/>
+      <c r="O28" s="51" t="n"/>
+      <c r="P28" s="51" t="n"/>
+      <c r="Q28" s="51" t="n"/>
+      <c r="R28" s="51" t="n"/>
+      <c r="S28" s="51" t="n"/>
+      <c r="T28" s="51" t="n"/>
+      <c r="U28" s="51" t="n"/>
+      <c r="V28" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W28" s="58" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="46" t="n"/>
-      <c r="D29" s="46" t="n"/>
+      <c r="C29" s="53" t="n"/>
+      <c r="D29" s="53" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G29" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G29" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H29" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I29" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J29" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L29" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M29" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N29" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O29" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P29" s="51" t="n"/>
-      <c r="Q29" s="51" t="n"/>
-      <c r="R29" s="51" t="n"/>
-      <c r="S29" s="51" t="n"/>
-      <c r="T29" s="51" t="n"/>
-      <c r="U29" s="51" t="n"/>
-      <c r="V29" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W29" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M29" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N29" s="55" t="n"/>
+      <c r="O29" s="55" t="n"/>
+      <c r="P29" s="55" t="n"/>
+      <c r="Q29" s="55" t="n"/>
+      <c r="R29" s="55" t="n"/>
+      <c r="S29" s="55" t="n"/>
+      <c r="T29" s="55" t="n"/>
+      <c r="U29" s="55" t="n"/>
+      <c r="V29" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W29" s="57" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="53" t="n"/>
-      <c r="D30" s="53" t="n"/>
+      <c r="C30" s="46" t="n"/>
+      <c r="D30" s="46" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G30" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G30" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H30" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I30" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J30" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L30" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M30" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N30" s="55" t="inlineStr">
+      <c r="M30" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N30" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O30" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O30" s="55" t="n"/>
-      <c r="P30" s="55" t="n"/>
-      <c r="Q30" s="55" t="n"/>
-      <c r="R30" s="55" t="n"/>
-      <c r="S30" s="55" t="n"/>
-      <c r="T30" s="55" t="n"/>
-      <c r="U30" s="55" t="n"/>
-      <c r="V30" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W30" s="57" t="n"/>
+      <c r="P30" s="51" t="n"/>
+      <c r="Q30" s="51" t="n"/>
+      <c r="R30" s="51" t="n"/>
+      <c r="S30" s="51" t="n"/>
+      <c r="T30" s="51" t="n"/>
+      <c r="U30" s="51" t="n"/>
+      <c r="V30" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W30" s="58" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="46" t="n"/>
-      <c r="D31" s="46" t="n"/>
+      <c r="C31" s="53" t="n"/>
+      <c r="D31" s="53" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G31" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H31" s="49" t="n">
         <v>2</v>
@@ -3504,208 +3504,218 @@
         <v>2</v>
       </c>
       <c r="J31" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K31" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L31" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M31" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M31" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N31" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N31" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O31" s="51" t="n"/>
-      <c r="P31" s="51" t="n"/>
-      <c r="Q31" s="51" t="n"/>
-      <c r="R31" s="51" t="n"/>
-      <c r="S31" s="51" t="n"/>
-      <c r="T31" s="51" t="n"/>
-      <c r="U31" s="51" t="n"/>
-      <c r="V31" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W31" s="58" t="n"/>
+      <c r="O31" s="55" t="n"/>
+      <c r="P31" s="55" t="n"/>
+      <c r="Q31" s="55" t="n"/>
+      <c r="R31" s="55" t="n"/>
+      <c r="S31" s="55" t="n"/>
+      <c r="T31" s="55" t="n"/>
+      <c r="U31" s="55" t="n"/>
+      <c r="V31" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W31" s="57" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="53" t="n"/>
-      <c r="D32" s="53" t="n"/>
+      <c r="C32" s="46" t="n"/>
+      <c r="D32" s="46" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G32" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H32" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I32" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J32" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L32" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M32" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M32" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N32" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N32" s="55" t="n"/>
-      <c r="O32" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P32" s="55" t="n"/>
-      <c r="Q32" s="55" t="n"/>
-      <c r="R32" s="55" t="n"/>
-      <c r="S32" s="55" t="n"/>
-      <c r="T32" s="55" t="n"/>
-      <c r="U32" s="55" t="n"/>
-      <c r="V32" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W32" s="57" t="n"/>
+      <c r="O32" s="51" t="n"/>
+      <c r="P32" s="51" t="n"/>
+      <c r="Q32" s="51" t="n"/>
+      <c r="R32" s="51" t="n"/>
+      <c r="S32" s="51" t="n"/>
+      <c r="T32" s="51" t="n"/>
+      <c r="U32" s="51" t="n"/>
+      <c r="V32" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W32" s="58" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="46" t="n"/>
-      <c r="D33" s="46" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G33" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G33" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H33" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L33" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M33" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N33" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O33" s="51" t="n"/>
-      <c r="P33" s="51" t="n"/>
-      <c r="Q33" s="51" t="n"/>
-      <c r="R33" s="51" t="n"/>
-      <c r="S33" s="51" t="n"/>
-      <c r="T33" s="51" t="n"/>
-      <c r="U33" s="51" t="n"/>
-      <c r="V33" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W33" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M33" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N33" s="55" t="n"/>
+      <c r="O33" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P33" s="55" t="n"/>
+      <c r="Q33" s="55" t="n"/>
+      <c r="R33" s="55" t="n"/>
+      <c r="S33" s="55" t="n"/>
+      <c r="T33" s="55" t="n"/>
+      <c r="U33" s="55" t="n"/>
+      <c r="V33" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W33" s="57" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="53" t="n"/>
-      <c r="D34" s="53" t="n"/>
+      <c r="C34" s="46" t="n"/>
+      <c r="D34" s="46" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G34" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G34" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H34" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I34" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J34" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L34" s="50" t="n"/>
-      <c r="M34" s="55" t="n"/>
-      <c r="N34" s="55" t="n"/>
-      <c r="O34" s="55" t="n"/>
-      <c r="P34" s="55" t="n"/>
-      <c r="Q34" s="55" t="n"/>
-      <c r="R34" s="55" t="n"/>
-      <c r="S34" s="55" t="n"/>
-      <c r="T34" s="55" t="n"/>
-      <c r="U34" s="55" t="n"/>
-      <c r="V34" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W34" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L34" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M34" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N34" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O34" s="51" t="n"/>
+      <c r="P34" s="51" t="n"/>
+      <c r="Q34" s="51" t="n"/>
+      <c r="R34" s="51" t="n"/>
+      <c r="S34" s="51" t="n"/>
+      <c r="T34" s="51" t="n"/>
+      <c r="U34" s="51" t="n"/>
+      <c r="V34" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W34" s="58" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="46" t="n"/>
-      <c r="D35" s="46" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G35" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H35" s="49" t="n">
         <v>0</v>
@@ -3714,43 +3724,43 @@
         <v>0</v>
       </c>
       <c r="J35" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L35" s="50" t="n"/>
-      <c r="M35" s="51" t="n"/>
-      <c r="N35" s="51" t="n"/>
-      <c r="O35" s="51" t="n"/>
-      <c r="P35" s="51" t="n"/>
-      <c r="Q35" s="51" t="n"/>
-      <c r="R35" s="51" t="n"/>
-      <c r="S35" s="51" t="n"/>
-      <c r="T35" s="51" t="n"/>
-      <c r="U35" s="51" t="n"/>
-      <c r="V35" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W35" s="58" t="n"/>
+      <c r="M35" s="55" t="n"/>
+      <c r="N35" s="55" t="n"/>
+      <c r="O35" s="55" t="n"/>
+      <c r="P35" s="55" t="n"/>
+      <c r="Q35" s="55" t="n"/>
+      <c r="R35" s="55" t="n"/>
+      <c r="S35" s="55" t="n"/>
+      <c r="T35" s="55" t="n"/>
+      <c r="U35" s="55" t="n"/>
+      <c r="V35" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W35" s="57" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
+      <c r="C36" s="46" t="n"/>
+      <c r="D36" s="46" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G36" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H36" s="49" t="n">
         <v>0</v>
@@ -3759,43 +3769,43 @@
         <v>0</v>
       </c>
       <c r="J36" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="55" t="n"/>
-      <c r="N36" s="55" t="n"/>
-      <c r="O36" s="55" t="n"/>
-      <c r="P36" s="55" t="n"/>
-      <c r="Q36" s="55" t="n"/>
-      <c r="R36" s="55" t="n"/>
-      <c r="S36" s="55" t="n"/>
-      <c r="T36" s="55" t="n"/>
-      <c r="U36" s="55" t="n"/>
-      <c r="V36" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W36" s="57" t="n"/>
+      <c r="M36" s="51" t="n"/>
+      <c r="N36" s="51" t="n"/>
+      <c r="O36" s="51" t="n"/>
+      <c r="P36" s="51" t="n"/>
+      <c r="Q36" s="51" t="n"/>
+      <c r="R36" s="51" t="n"/>
+      <c r="S36" s="51" t="n"/>
+      <c r="T36" s="51" t="n"/>
+      <c r="U36" s="51" t="n"/>
+      <c r="V36" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W36" s="58" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="46" t="n"/>
-      <c r="D37" s="46" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G37" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G37" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H37" s="49" t="n">
         <v>0</v>
@@ -3804,43 +3814,43 @@
         <v>0</v>
       </c>
       <c r="J37" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="51" t="n"/>
-      <c r="N37" s="51" t="n"/>
-      <c r="O37" s="51" t="n"/>
-      <c r="P37" s="51" t="n"/>
-      <c r="Q37" s="51" t="n"/>
-      <c r="R37" s="51" t="n"/>
-      <c r="S37" s="51" t="n"/>
-      <c r="T37" s="51" t="n"/>
-      <c r="U37" s="51" t="n"/>
-      <c r="V37" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W37" s="58" t="n"/>
+      <c r="M37" s="55" t="n"/>
+      <c r="N37" s="55" t="n"/>
+      <c r="O37" s="55" t="n"/>
+      <c r="P37" s="55" t="n"/>
+      <c r="Q37" s="55" t="n"/>
+      <c r="R37" s="55" t="n"/>
+      <c r="S37" s="55" t="n"/>
+      <c r="T37" s="55" t="n"/>
+      <c r="U37" s="55" t="n"/>
+      <c r="V37" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W37" s="57" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="53" t="n"/>
-      <c r="D38" s="53" t="n"/>
+      <c r="C38" s="46" t="n"/>
+      <c r="D38" s="46" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G38" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H38" s="49" t="n">
         <v>0</v>
@@ -3849,43 +3859,43 @@
         <v>0</v>
       </c>
       <c r="J38" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="55" t="n"/>
-      <c r="N38" s="55" t="n"/>
-      <c r="O38" s="55" t="n"/>
-      <c r="P38" s="55" t="n"/>
-      <c r="Q38" s="55" t="n"/>
-      <c r="R38" s="55" t="n"/>
-      <c r="S38" s="55" t="n"/>
-      <c r="T38" s="55" t="n"/>
-      <c r="U38" s="55" t="n"/>
-      <c r="V38" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W38" s="57" t="n"/>
+      <c r="M38" s="51" t="n"/>
+      <c r="N38" s="51" t="n"/>
+      <c r="O38" s="51" t="n"/>
+      <c r="P38" s="51" t="n"/>
+      <c r="Q38" s="51" t="n"/>
+      <c r="R38" s="51" t="n"/>
+      <c r="S38" s="51" t="n"/>
+      <c r="T38" s="51" t="n"/>
+      <c r="U38" s="51" t="n"/>
+      <c r="V38" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W38" s="58" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="46" t="n"/>
-      <c r="D39" s="46" t="n"/>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G39" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H39" s="49" t="n">
         <v>0</v>
@@ -3894,1371 +3904,1375 @@
         <v>0</v>
       </c>
       <c r="J39" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="51" t="n"/>
-      <c r="N39" s="51" t="n"/>
-      <c r="O39" s="51" t="n"/>
-      <c r="P39" s="51" t="n"/>
-      <c r="Q39" s="51" t="n"/>
-      <c r="R39" s="51" t="n"/>
-      <c r="S39" s="51" t="n"/>
-      <c r="T39" s="51" t="n"/>
-      <c r="U39" s="51" t="n"/>
-      <c r="V39" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W39" s="58" t="n"/>
+      <c r="M39" s="55" t="n"/>
+      <c r="N39" s="55" t="n"/>
+      <c r="O39" s="55" t="n"/>
+      <c r="P39" s="55" t="n"/>
+      <c r="Q39" s="55" t="n"/>
+      <c r="R39" s="55" t="n"/>
+      <c r="S39" s="55" t="n"/>
+      <c r="T39" s="55" t="n"/>
+      <c r="U39" s="55" t="n"/>
+      <c r="V39" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W39" s="57" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="53" t="n"/>
-      <c r="D40" s="53" t="n"/>
+      <c r="C40" s="46" t="n"/>
+      <c r="D40" s="46" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G40" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H40" s="49" t="n"/>
-      <c r="I40" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G40" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H40" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J40" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="55" t="n"/>
-      <c r="N40" s="55" t="n"/>
-      <c r="O40" s="55" t="n"/>
-      <c r="P40" s="55" t="n"/>
-      <c r="Q40" s="55" t="n"/>
-      <c r="R40" s="55" t="n"/>
-      <c r="S40" s="55" t="n"/>
-      <c r="T40" s="55" t="n"/>
-      <c r="U40" s="55" t="n"/>
-      <c r="V40" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W40" s="57" t="n"/>
+      <c r="M40" s="51" t="n"/>
+      <c r="N40" s="51" t="n"/>
+      <c r="O40" s="51" t="n"/>
+      <c r="P40" s="51" t="n"/>
+      <c r="Q40" s="51" t="n"/>
+      <c r="R40" s="51" t="n"/>
+      <c r="S40" s="51" t="n"/>
+      <c r="T40" s="51" t="n"/>
+      <c r="U40" s="51" t="n"/>
+      <c r="V40" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W40" s="58" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="46" t="n"/>
-      <c r="D41" s="46" t="n"/>
+      <c r="C41" s="53" t="n"/>
+      <c r="D41" s="53" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G41" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H41" s="49" t="n"/>
       <c r="I41" s="49" t="n"/>
       <c r="J41" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="51" t="n"/>
-      <c r="N41" s="51" t="n"/>
-      <c r="O41" s="51" t="n"/>
-      <c r="P41" s="51" t="n"/>
-      <c r="Q41" s="51" t="n"/>
-      <c r="R41" s="51" t="n"/>
-      <c r="S41" s="51" t="n"/>
-      <c r="T41" s="51" t="n"/>
-      <c r="U41" s="51" t="n"/>
-      <c r="V41" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W41" s="58" t="n"/>
+      <c r="M41" s="55" t="n"/>
+      <c r="N41" s="55" t="n"/>
+      <c r="O41" s="55" t="n"/>
+      <c r="P41" s="55" t="n"/>
+      <c r="Q41" s="55" t="n"/>
+      <c r="R41" s="55" t="n"/>
+      <c r="S41" s="55" t="n"/>
+      <c r="T41" s="55" t="n"/>
+      <c r="U41" s="55" t="n"/>
+      <c r="V41" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W41" s="57" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="53" t="n"/>
-      <c r="D42" s="53" t="n"/>
+      <c r="C42" s="46" t="n"/>
+      <c r="D42" s="46" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G42" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H42" s="49" t="n"/>
       <c r="I42" s="49" t="n"/>
       <c r="J42" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K42" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="55" t="n"/>
-      <c r="N42" s="55" t="n"/>
-      <c r="O42" s="55" t="n"/>
-      <c r="P42" s="55" t="n"/>
-      <c r="Q42" s="55" t="n"/>
-      <c r="R42" s="55" t="n"/>
-      <c r="S42" s="55" t="n"/>
-      <c r="T42" s="55" t="n"/>
-      <c r="U42" s="55" t="n"/>
-      <c r="V42" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W42" s="57" t="n"/>
+      <c r="M42" s="51" t="n"/>
+      <c r="N42" s="51" t="n"/>
+      <c r="O42" s="51" t="n"/>
+      <c r="P42" s="51" t="n"/>
+      <c r="Q42" s="51" t="n"/>
+      <c r="R42" s="51" t="n"/>
+      <c r="S42" s="51" t="n"/>
+      <c r="T42" s="51" t="n"/>
+      <c r="U42" s="51" t="n"/>
+      <c r="V42" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W42" s="58" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="46" t="n"/>
-      <c r="D43" s="46" t="n"/>
+      <c r="C43" s="53" t="n"/>
+      <c r="D43" s="53" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G43" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H43" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I43" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H43" s="49" t="n"/>
+      <c r="I43" s="49" t="n"/>
       <c r="J43" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K43" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="51" t="n"/>
-      <c r="N43" s="51" t="n"/>
-      <c r="O43" s="51" t="n"/>
-      <c r="P43" s="51" t="n"/>
-      <c r="Q43" s="51" t="n"/>
-      <c r="R43" s="51" t="n"/>
-      <c r="S43" s="51" t="n"/>
-      <c r="T43" s="51" t="n"/>
-      <c r="U43" s="51" t="n"/>
-      <c r="V43" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W43" s="58" t="n"/>
+      <c r="M43" s="55" t="n"/>
+      <c r="N43" s="55" t="n"/>
+      <c r="O43" s="55" t="n"/>
+      <c r="P43" s="55" t="n"/>
+      <c r="Q43" s="55" t="n"/>
+      <c r="R43" s="55" t="n"/>
+      <c r="S43" s="55" t="n"/>
+      <c r="T43" s="55" t="n"/>
+      <c r="U43" s="55" t="n"/>
+      <c r="V43" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W43" s="57" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="53" t="n"/>
-      <c r="D44" s="53" t="n"/>
+      <c r="C44" s="46" t="n"/>
+      <c r="D44" s="46" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G44" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H44" s="49" t="n"/>
-      <c r="I44" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G44" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H44" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I44" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J44" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K44" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="55" t="n"/>
-      <c r="N44" s="55" t="n"/>
-      <c r="O44" s="55" t="n"/>
-      <c r="P44" s="55" t="n"/>
-      <c r="Q44" s="55" t="n"/>
-      <c r="R44" s="55" t="n"/>
-      <c r="S44" s="55" t="n"/>
-      <c r="T44" s="55" t="n"/>
-      <c r="U44" s="55" t="n"/>
-      <c r="V44" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W44" s="57" t="n"/>
+      <c r="M44" s="51" t="n"/>
+      <c r="N44" s="51" t="n"/>
+      <c r="O44" s="51" t="n"/>
+      <c r="P44" s="51" t="n"/>
+      <c r="Q44" s="51" t="n"/>
+      <c r="R44" s="51" t="n"/>
+      <c r="S44" s="51" t="n"/>
+      <c r="T44" s="51" t="n"/>
+      <c r="U44" s="51" t="n"/>
+      <c r="V44" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W44" s="58" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="46" t="n"/>
-      <c r="D45" s="46" t="n"/>
+      <c r="C45" s="53" t="n"/>
+      <c r="D45" s="53" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G45" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G45" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H45" s="49" t="n"/>
       <c r="I45" s="49" t="n"/>
       <c r="J45" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K45" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="51" t="n"/>
-      <c r="N45" s="51" t="n"/>
-      <c r="O45" s="51" t="n"/>
-      <c r="P45" s="51" t="n"/>
-      <c r="Q45" s="51" t="n"/>
-      <c r="R45" s="51" t="n"/>
-      <c r="S45" s="51" t="n"/>
-      <c r="T45" s="51" t="n"/>
-      <c r="U45" s="51" t="n"/>
-      <c r="V45" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W45" s="58" t="n"/>
+      <c r="M45" s="55" t="n"/>
+      <c r="N45" s="55" t="n"/>
+      <c r="O45" s="55" t="n"/>
+      <c r="P45" s="55" t="n"/>
+      <c r="Q45" s="55" t="n"/>
+      <c r="R45" s="55" t="n"/>
+      <c r="S45" s="55" t="n"/>
+      <c r="T45" s="55" t="n"/>
+      <c r="U45" s="55" t="n"/>
+      <c r="V45" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W45" s="57" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="53" t="n"/>
-      <c r="D46" s="53" t="n"/>
+      <c r="C46" s="46" t="n"/>
+      <c r="D46" s="46" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G46" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G46" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H46" s="49" t="n"/>
       <c r="I46" s="49" t="n"/>
       <c r="J46" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K46" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K46" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="55" t="n"/>
-      <c r="N46" s="55" t="n"/>
-      <c r="O46" s="55" t="n"/>
-      <c r="P46" s="55" t="n"/>
-      <c r="Q46" s="55" t="n"/>
-      <c r="R46" s="55" t="n"/>
-      <c r="S46" s="55" t="n"/>
-      <c r="T46" s="55" t="n"/>
-      <c r="U46" s="55" t="n"/>
-      <c r="V46" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W46" s="57" t="n"/>
+      <c r="M46" s="51" t="n"/>
+      <c r="N46" s="51" t="n"/>
+      <c r="O46" s="51" t="n"/>
+      <c r="P46" s="51" t="n"/>
+      <c r="Q46" s="51" t="n"/>
+      <c r="R46" s="51" t="n"/>
+      <c r="S46" s="51" t="n"/>
+      <c r="T46" s="51" t="n"/>
+      <c r="U46" s="51" t="n"/>
+      <c r="V46" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W46" s="58" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="46" t="n"/>
-      <c r="D47" s="46" t="n"/>
+      <c r="C47" s="53" t="n"/>
+      <c r="D47" s="53" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G47" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H47" s="49" t="n"/>
       <c r="I47" s="49" t="n"/>
       <c r="J47" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K47" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="51" t="n"/>
-      <c r="N47" s="51" t="n"/>
-      <c r="O47" s="51" t="n"/>
-      <c r="P47" s="51" t="n"/>
-      <c r="Q47" s="51" t="n"/>
-      <c r="R47" s="51" t="n"/>
-      <c r="S47" s="51" t="n"/>
-      <c r="T47" s="51" t="n"/>
-      <c r="U47" s="51" t="n"/>
-      <c r="V47" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W47" s="58" t="n"/>
+      <c r="M47" s="55" t="n"/>
+      <c r="N47" s="55" t="n"/>
+      <c r="O47" s="55" t="n"/>
+      <c r="P47" s="55" t="n"/>
+      <c r="Q47" s="55" t="n"/>
+      <c r="R47" s="55" t="n"/>
+      <c r="S47" s="55" t="n"/>
+      <c r="T47" s="55" t="n"/>
+      <c r="U47" s="55" t="n"/>
+      <c r="V47" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W47" s="57" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
+      <c r="C48" s="46" t="n"/>
+      <c r="D48" s="46" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G48" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G48" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H48" s="49" t="n"/>
       <c r="I48" s="49" t="n"/>
       <c r="J48" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K48" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="55" t="n"/>
-      <c r="N48" s="55" t="n"/>
-      <c r="O48" s="55" t="n"/>
-      <c r="P48" s="55" t="n"/>
-      <c r="Q48" s="55" t="n"/>
-      <c r="R48" s="55" t="n"/>
-      <c r="S48" s="55" t="n"/>
-      <c r="T48" s="55" t="n"/>
-      <c r="U48" s="55" t="n"/>
-      <c r="V48" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W48" s="57" t="n"/>
+      <c r="M48" s="51" t="n"/>
+      <c r="N48" s="51" t="n"/>
+      <c r="O48" s="51" t="n"/>
+      <c r="P48" s="51" t="n"/>
+      <c r="Q48" s="51" t="n"/>
+      <c r="R48" s="51" t="n"/>
+      <c r="S48" s="51" t="n"/>
+      <c r="T48" s="51" t="n"/>
+      <c r="U48" s="51" t="n"/>
+      <c r="V48" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W48" s="58" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="46" t="n"/>
-      <c r="D49" s="46" t="n"/>
+      <c r="C49" s="53" t="n"/>
+      <c r="D49" s="53" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G49" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H49" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I49" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G49" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H49" s="49" t="n"/>
+      <c r="I49" s="49" t="n"/>
       <c r="J49" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K49" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="51" t="n"/>
-      <c r="N49" s="51" t="n"/>
-      <c r="O49" s="51" t="n"/>
-      <c r="P49" s="51" t="n"/>
-      <c r="Q49" s="51" t="n"/>
-      <c r="R49" s="51" t="n"/>
-      <c r="S49" s="51" t="n"/>
-      <c r="T49" s="51" t="n"/>
-      <c r="U49" s="51" t="n"/>
-      <c r="V49" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W49" s="58" t="n"/>
+      <c r="M49" s="55" t="n"/>
+      <c r="N49" s="55" t="n"/>
+      <c r="O49" s="55" t="n"/>
+      <c r="P49" s="55" t="n"/>
+      <c r="Q49" s="55" t="n"/>
+      <c r="R49" s="55" t="n"/>
+      <c r="S49" s="55" t="n"/>
+      <c r="T49" s="55" t="n"/>
+      <c r="U49" s="55" t="n"/>
+      <c r="V49" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W49" s="57" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="53" t="n"/>
-      <c r="D50" s="53" t="n"/>
+      <c r="C50" s="46" t="n"/>
+      <c r="D50" s="46" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G50" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H50" s="49" t="n"/>
-      <c r="I50" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H50" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I50" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J50" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="55" t="n"/>
-      <c r="N50" s="55" t="n"/>
-      <c r="O50" s="55" t="n"/>
-      <c r="P50" s="55" t="n"/>
-      <c r="Q50" s="55" t="n"/>
-      <c r="R50" s="55" t="n"/>
-      <c r="S50" s="55" t="n"/>
-      <c r="T50" s="55" t="n"/>
-      <c r="U50" s="55" t="n"/>
-      <c r="V50" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W50" s="57" t="n"/>
+      <c r="M50" s="51" t="n"/>
+      <c r="N50" s="51" t="n"/>
+      <c r="O50" s="51" t="n"/>
+      <c r="P50" s="51" t="n"/>
+      <c r="Q50" s="51" t="n"/>
+      <c r="R50" s="51" t="n"/>
+      <c r="S50" s="51" t="n"/>
+      <c r="T50" s="51" t="n"/>
+      <c r="U50" s="51" t="n"/>
+      <c r="V50" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W50" s="58" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="46" t="n"/>
-      <c r="D51" s="46" t="n"/>
+      <c r="C51" s="53" t="n"/>
+      <c r="D51" s="53" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G51" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H51" s="49" t="n"/>
       <c r="I51" s="49" t="n"/>
       <c r="J51" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="51" t="n"/>
-      <c r="N51" s="51" t="n"/>
-      <c r="O51" s="51" t="n"/>
-      <c r="P51" s="51" t="n"/>
-      <c r="Q51" s="51" t="n"/>
-      <c r="R51" s="51" t="n"/>
-      <c r="S51" s="51" t="n"/>
-      <c r="T51" s="51" t="n"/>
-      <c r="U51" s="51" t="n"/>
-      <c r="V51" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W51" s="58" t="n"/>
+      <c r="M51" s="55" t="n"/>
+      <c r="N51" s="55" t="n"/>
+      <c r="O51" s="55" t="n"/>
+      <c r="P51" s="55" t="n"/>
+      <c r="Q51" s="55" t="n"/>
+      <c r="R51" s="55" t="n"/>
+      <c r="S51" s="55" t="n"/>
+      <c r="T51" s="55" t="n"/>
+      <c r="U51" s="55" t="n"/>
+      <c r="V51" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W51" s="57" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="53" t="n"/>
-      <c r="D52" s="53" t="n"/>
+      <c r="C52" s="46" t="n"/>
+      <c r="D52" s="46" t="n"/>
       <c r="E52" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F52" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G52" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H52" s="49" t="n"/>
+      <c r="I52" s="49" t="n"/>
+      <c r="J52" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F52" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G52" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H52" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I52" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J52" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K52" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="55" t="n"/>
-      <c r="N52" s="55" t="n"/>
-      <c r="O52" s="55" t="n"/>
-      <c r="P52" s="55" t="n"/>
-      <c r="Q52" s="55" t="n"/>
-      <c r="R52" s="55" t="n"/>
-      <c r="S52" s="55" t="n"/>
-      <c r="T52" s="55" t="n"/>
-      <c r="U52" s="55" t="n"/>
-      <c r="V52" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W52" s="57" t="n"/>
+      <c r="M52" s="51" t="n"/>
+      <c r="N52" s="51" t="n"/>
+      <c r="O52" s="51" t="n"/>
+      <c r="P52" s="51" t="n"/>
+      <c r="Q52" s="51" t="n"/>
+      <c r="R52" s="51" t="n"/>
+      <c r="S52" s="51" t="n"/>
+      <c r="T52" s="51" t="n"/>
+      <c r="U52" s="51" t="n"/>
+      <c r="V52" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W52" s="58" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="46" t="n"/>
-      <c r="D53" s="46" t="n"/>
+      <c r="C53" s="53" t="n"/>
+      <c r="D53" s="53" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G53" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H53" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I53" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J53" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="51" t="n"/>
-      <c r="N53" s="51" t="n"/>
-      <c r="O53" s="51" t="n"/>
-      <c r="P53" s="51" t="n"/>
-      <c r="Q53" s="51" t="n"/>
-      <c r="R53" s="51" t="n"/>
-      <c r="S53" s="51" t="n"/>
-      <c r="T53" s="51" t="n"/>
-      <c r="U53" s="51" t="n"/>
-      <c r="V53" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W53" s="58" t="n"/>
+      <c r="M53" s="55" t="n"/>
+      <c r="N53" s="55" t="n"/>
+      <c r="O53" s="55" t="n"/>
+      <c r="P53" s="55" t="n"/>
+      <c r="Q53" s="55" t="n"/>
+      <c r="R53" s="55" t="n"/>
+      <c r="S53" s="55" t="n"/>
+      <c r="T53" s="55" t="n"/>
+      <c r="U53" s="55" t="n"/>
+      <c r="V53" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W53" s="57" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="53" t="n"/>
-      <c r="D54" s="53" t="n"/>
+      <c r="C54" s="46" t="n"/>
+      <c r="D54" s="46" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G54" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H54" s="49" t="n"/>
-      <c r="I54" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H54" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I54" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J54" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="55" t="n"/>
-      <c r="N54" s="55" t="n"/>
-      <c r="O54" s="55" t="n"/>
-      <c r="P54" s="55" t="n"/>
-      <c r="Q54" s="55" t="n"/>
-      <c r="R54" s="55" t="n"/>
-      <c r="S54" s="55" t="n"/>
-      <c r="T54" s="55" t="n"/>
-      <c r="U54" s="55" t="n"/>
-      <c r="V54" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W54" s="57" t="n"/>
+      <c r="M54" s="51" t="n"/>
+      <c r="N54" s="51" t="n"/>
+      <c r="O54" s="51" t="n"/>
+      <c r="P54" s="51" t="n"/>
+      <c r="Q54" s="51" t="n"/>
+      <c r="R54" s="51" t="n"/>
+      <c r="S54" s="51" t="n"/>
+      <c r="T54" s="51" t="n"/>
+      <c r="U54" s="51" t="n"/>
+      <c r="V54" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W54" s="58" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="46" t="n"/>
-      <c r="D55" s="46" t="n"/>
+      <c r="C55" s="53" t="n"/>
+      <c r="D55" s="53" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G55" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G55" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H55" s="49" t="n"/>
       <c r="I55" s="49" t="n"/>
       <c r="J55" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K55" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="51" t="n"/>
-      <c r="N55" s="51" t="n"/>
-      <c r="O55" s="51" t="n"/>
-      <c r="P55" s="51" t="n"/>
-      <c r="Q55" s="51" t="n"/>
-      <c r="R55" s="51" t="n"/>
-      <c r="S55" s="51" t="n"/>
-      <c r="T55" s="51" t="n"/>
-      <c r="U55" s="51" t="n"/>
-      <c r="V55" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W55" s="58" t="n"/>
+      <c r="M55" s="55" t="n"/>
+      <c r="N55" s="55" t="n"/>
+      <c r="O55" s="55" t="n"/>
+      <c r="P55" s="55" t="n"/>
+      <c r="Q55" s="55" t="n"/>
+      <c r="R55" s="55" t="n"/>
+      <c r="S55" s="55" t="n"/>
+      <c r="T55" s="55" t="n"/>
+      <c r="U55" s="55" t="n"/>
+      <c r="V55" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W55" s="57" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="53" t="n"/>
-      <c r="D56" s="53" t="n"/>
+      <c r="C56" s="46" t="n"/>
+      <c r="D56" s="46" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G56" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G56" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="55" t="n"/>
-      <c r="N56" s="55" t="n"/>
-      <c r="O56" s="55" t="n"/>
-      <c r="P56" s="55" t="n"/>
-      <c r="Q56" s="55" t="n"/>
-      <c r="R56" s="55" t="n"/>
-      <c r="S56" s="55" t="n"/>
-      <c r="T56" s="55" t="n"/>
-      <c r="U56" s="55" t="n"/>
-      <c r="V56" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W56" s="57" t="n"/>
+      <c r="M56" s="51" t="n"/>
+      <c r="N56" s="51" t="n"/>
+      <c r="O56" s="51" t="n"/>
+      <c r="P56" s="51" t="n"/>
+      <c r="Q56" s="51" t="n"/>
+      <c r="R56" s="51" t="n"/>
+      <c r="S56" s="51" t="n"/>
+      <c r="T56" s="51" t="n"/>
+      <c r="U56" s="51" t="n"/>
+      <c r="V56" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W56" s="58" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="46" t="n"/>
-      <c r="D57" s="46" t="n"/>
+      <c r="C57" s="53" t="n"/>
+      <c r="D57" s="53" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G57" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="51" t="n"/>
-      <c r="N57" s="51" t="n"/>
-      <c r="O57" s="51" t="n"/>
-      <c r="P57" s="51" t="n"/>
-      <c r="Q57" s="51" t="n"/>
-      <c r="R57" s="51" t="n"/>
-      <c r="S57" s="51" t="n"/>
-      <c r="T57" s="51" t="n"/>
-      <c r="U57" s="51" t="n"/>
-      <c r="V57" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W57" s="58" t="n"/>
+      <c r="M57" s="55" t="n"/>
+      <c r="N57" s="55" t="n"/>
+      <c r="O57" s="55" t="n"/>
+      <c r="P57" s="55" t="n"/>
+      <c r="Q57" s="55" t="n"/>
+      <c r="R57" s="55" t="n"/>
+      <c r="S57" s="55" t="n"/>
+      <c r="T57" s="55" t="n"/>
+      <c r="U57" s="55" t="n"/>
+      <c r="V57" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W57" s="57" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="53" t="n"/>
-      <c r="D58" s="53" t="n"/>
+      <c r="C58" s="46" t="n"/>
+      <c r="D58" s="46" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G58" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G58" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="55" t="n"/>
-      <c r="N58" s="55" t="n"/>
-      <c r="O58" s="55" t="n"/>
-      <c r="P58" s="55" t="n"/>
-      <c r="Q58" s="55" t="n"/>
-      <c r="R58" s="55" t="n"/>
-      <c r="S58" s="55" t="n"/>
-      <c r="T58" s="55" t="n"/>
-      <c r="U58" s="55" t="n"/>
-      <c r="V58" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W58" s="57" t="n"/>
+      <c r="M58" s="51" t="n"/>
+      <c r="N58" s="51" t="n"/>
+      <c r="O58" s="51" t="n"/>
+      <c r="P58" s="51" t="n"/>
+      <c r="Q58" s="51" t="n"/>
+      <c r="R58" s="51" t="n"/>
+      <c r="S58" s="51" t="n"/>
+      <c r="T58" s="51" t="n"/>
+      <c r="U58" s="51" t="n"/>
+      <c r="V58" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W58" s="58" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="46" t="n"/>
-      <c r="D59" s="46" t="n"/>
+      <c r="C59" s="53" t="n"/>
+      <c r="D59" s="53" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G59" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G59" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="51" t="n"/>
-      <c r="N59" s="51" t="n"/>
-      <c r="O59" s="51" t="n"/>
-      <c r="P59" s="51" t="n"/>
-      <c r="Q59" s="51" t="n"/>
-      <c r="R59" s="51" t="n"/>
-      <c r="S59" s="51" t="n"/>
-      <c r="T59" s="51" t="n"/>
-      <c r="U59" s="51" t="n"/>
-      <c r="V59" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W59" s="58" t="n"/>
+      <c r="M59" s="55" t="n"/>
+      <c r="N59" s="55" t="n"/>
+      <c r="O59" s="55" t="n"/>
+      <c r="P59" s="55" t="n"/>
+      <c r="Q59" s="55" t="n"/>
+      <c r="R59" s="55" t="n"/>
+      <c r="S59" s="55" t="n"/>
+      <c r="T59" s="55" t="n"/>
+      <c r="U59" s="55" t="n"/>
+      <c r="V59" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W59" s="57" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
+      <c r="C60" s="46" t="n"/>
+      <c r="D60" s="46" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G60" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G60" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="55" t="n"/>
-      <c r="N60" s="55" t="n"/>
-      <c r="O60" s="55" t="n"/>
-      <c r="P60" s="55" t="n"/>
-      <c r="Q60" s="55" t="n"/>
-      <c r="R60" s="55" t="n"/>
-      <c r="S60" s="55" t="n"/>
-      <c r="T60" s="55" t="n"/>
-      <c r="U60" s="55" t="n"/>
-      <c r="V60" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W60" s="57" t="n"/>
+      <c r="M60" s="51" t="n"/>
+      <c r="N60" s="51" t="n"/>
+      <c r="O60" s="51" t="n"/>
+      <c r="P60" s="51" t="n"/>
+      <c r="Q60" s="51" t="n"/>
+      <c r="R60" s="51" t="n"/>
+      <c r="S60" s="51" t="n"/>
+      <c r="T60" s="51" t="n"/>
+      <c r="U60" s="51" t="n"/>
+      <c r="V60" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W60" s="58" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="46" t="n"/>
-      <c r="D61" s="46" t="n"/>
+      <c r="C61" s="53" t="n"/>
+      <c r="D61" s="53" t="n"/>
       <c r="E61" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F61" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G61" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
       <c r="J61" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K61" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="51" t="n"/>
-      <c r="N61" s="51" t="n"/>
-      <c r="O61" s="51" t="n"/>
-      <c r="P61" s="51" t="n"/>
-      <c r="Q61" s="51" t="n"/>
-      <c r="R61" s="51" t="n"/>
-      <c r="S61" s="51" t="n"/>
-      <c r="T61" s="51" t="n"/>
-      <c r="U61" s="51" t="n"/>
-      <c r="V61" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W61" s="58" t="n"/>
+      <c r="M61" s="55" t="n"/>
+      <c r="N61" s="55" t="n"/>
+      <c r="O61" s="55" t="n"/>
+      <c r="P61" s="55" t="n"/>
+      <c r="Q61" s="55" t="n"/>
+      <c r="R61" s="55" t="n"/>
+      <c r="S61" s="55" t="n"/>
+      <c r="T61" s="55" t="n"/>
+      <c r="U61" s="55" t="n"/>
+      <c r="V61" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W61" s="57" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B62" s="45" t="n"/>
-      <c r="C62" s="53" t="n"/>
-      <c r="D62" s="53" t="n"/>
+      <c r="C62" s="46" t="n"/>
+      <c r="D62" s="46" t="n"/>
       <c r="E62" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F62" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G62" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="49" t="n"/>
       <c r="J62" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K62" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L62" s="50" t="n"/>
-      <c r="M62" s="55" t="n"/>
-      <c r="N62" s="55" t="n"/>
-      <c r="O62" s="55" t="n"/>
-      <c r="P62" s="55" t="n"/>
-      <c r="Q62" s="55" t="n"/>
-      <c r="R62" s="55" t="n"/>
-      <c r="S62" s="55" t="n"/>
-      <c r="T62" s="55" t="n"/>
-      <c r="U62" s="55" t="n"/>
-      <c r="V62" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W62" s="57" t="n"/>
+      <c r="M62" s="51" t="n"/>
+      <c r="N62" s="51" t="n"/>
+      <c r="O62" s="51" t="n"/>
+      <c r="P62" s="51" t="n"/>
+      <c r="Q62" s="51" t="n"/>
+      <c r="R62" s="51" t="n"/>
+      <c r="S62" s="51" t="n"/>
+      <c r="T62" s="51" t="n"/>
+      <c r="U62" s="51" t="n"/>
+      <c r="V62" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W62" s="58" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B63" s="45" t="n"/>
-      <c r="C63" s="46" t="n"/>
-      <c r="D63" s="46" t="n"/>
+      <c r="C63" s="53" t="n"/>
+      <c r="D63" s="53" t="n"/>
       <c r="E63" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F63" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G63" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G63" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="49" t="n"/>
       <c r="J63" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K63" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L63" s="50" t="n"/>
-      <c r="M63" s="51" t="n"/>
-      <c r="N63" s="51" t="n"/>
-      <c r="O63" s="51" t="n"/>
-      <c r="P63" s="51" t="n"/>
-      <c r="Q63" s="51" t="n"/>
-      <c r="R63" s="51" t="n"/>
-      <c r="S63" s="51" t="n"/>
-      <c r="T63" s="51" t="n"/>
-      <c r="U63" s="51" t="n"/>
-      <c r="V63" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W63" s="58" t="n"/>
+      <c r="M63" s="55" t="n"/>
+      <c r="N63" s="55" t="n"/>
+      <c r="O63" s="55" t="n"/>
+      <c r="P63" s="55" t="n"/>
+      <c r="Q63" s="55" t="n"/>
+      <c r="R63" s="55" t="n"/>
+      <c r="S63" s="55" t="n"/>
+      <c r="T63" s="55" t="n"/>
+      <c r="U63" s="55" t="n"/>
+      <c r="V63" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W63" s="57" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B64" s="45" t="n"/>
-      <c r="C64" s="53" t="n"/>
-      <c r="D64" s="53" t="n"/>
+      <c r="C64" s="46" t="n"/>
+      <c r="D64" s="46" t="n"/>
       <c r="E64" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F64" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G64" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G64" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="49" t="n"/>
       <c r="J64" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K64" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L64" s="50" t="n"/>
-      <c r="M64" s="55" t="n"/>
-      <c r="N64" s="55" t="n"/>
-      <c r="O64" s="55" t="n"/>
-      <c r="P64" s="55" t="n"/>
-      <c r="Q64" s="55" t="n"/>
-      <c r="R64" s="55" t="n"/>
-      <c r="S64" s="55" t="n"/>
-      <c r="T64" s="55" t="n"/>
-      <c r="U64" s="55" t="n"/>
-      <c r="V64" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W64" s="57" t="n"/>
+      <c r="M64" s="51" t="n"/>
+      <c r="N64" s="51" t="n"/>
+      <c r="O64" s="51" t="n"/>
+      <c r="P64" s="51" t="n"/>
+      <c r="Q64" s="51" t="n"/>
+      <c r="R64" s="51" t="n"/>
+      <c r="S64" s="51" t="n"/>
+      <c r="T64" s="51" t="n"/>
+      <c r="U64" s="51" t="n"/>
+      <c r="V64" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W64" s="58" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B65" s="45" t="n"/>
-      <c r="C65" s="46" t="n"/>
-      <c r="D65" s="46" t="n"/>
+      <c r="C65" s="53" t="n"/>
+      <c r="D65" s="53" t="n"/>
       <c r="E65" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F65" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G65" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G65" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H65" s="49" t="n"/>
       <c r="I65" s="49" t="n"/>
       <c r="J65" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K65" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L65" s="50" t="n"/>
-      <c r="M65" s="51" t="n"/>
-      <c r="N65" s="51" t="n"/>
-      <c r="O65" s="51" t="n"/>
-      <c r="P65" s="51" t="n"/>
-      <c r="Q65" s="51" t="n"/>
-      <c r="R65" s="51" t="n"/>
-      <c r="S65" s="51" t="n"/>
-      <c r="T65" s="51" t="n"/>
-      <c r="U65" s="51" t="n"/>
-      <c r="V65" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W65" s="58" t="n"/>
+      <c r="M65" s="55" t="n"/>
+      <c r="N65" s="55" t="n"/>
+      <c r="O65" s="55" t="n"/>
+      <c r="P65" s="55" t="n"/>
+      <c r="Q65" s="55" t="n"/>
+      <c r="R65" s="55" t="n"/>
+      <c r="S65" s="55" t="n"/>
+      <c r="T65" s="55" t="n"/>
+      <c r="U65" s="55" t="n"/>
+      <c r="V65" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W65" s="57" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B66" s="45" t="n"/>
-      <c r="C66" s="53" t="n"/>
-      <c r="D66" s="53" t="n"/>
+      <c r="C66" s="46" t="n"/>
+      <c r="D66" s="46" t="n"/>
       <c r="E66" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F66" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G66" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G66" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H66" s="49" t="n"/>
       <c r="I66" s="49" t="n"/>
       <c r="J66" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K66" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L66" s="50" t="n"/>
-      <c r="M66" s="55" t="n"/>
-      <c r="N66" s="55" t="n"/>
-      <c r="O66" s="55" t="n"/>
-      <c r="P66" s="55" t="n"/>
-      <c r="Q66" s="55" t="n"/>
-      <c r="R66" s="55" t="n"/>
-      <c r="S66" s="55" t="n"/>
-      <c r="T66" s="55" t="n"/>
-      <c r="U66" s="55" t="n"/>
-      <c r="V66" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W66" s="57" t="n"/>
+      <c r="M66" s="51" t="n"/>
+      <c r="N66" s="51" t="n"/>
+      <c r="O66" s="51" t="n"/>
+      <c r="P66" s="51" t="n"/>
+      <c r="Q66" s="51" t="n"/>
+      <c r="R66" s="51" t="n"/>
+      <c r="S66" s="51" t="n"/>
+      <c r="T66" s="51" t="n"/>
+      <c r="U66" s="51" t="n"/>
+      <c r="V66" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W66" s="58" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B67" s="45" t="n"/>
-      <c r="C67" s="46" t="n"/>
-      <c r="D67" s="46" t="n"/>
+      <c r="C67" s="53" t="n"/>
+      <c r="D67" s="53" t="n"/>
       <c r="E67" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F67" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G67" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G67" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H67" s="49" t="n"/>
       <c r="I67" s="49" t="n"/>
       <c r="J67" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K67" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L67" s="50" t="n"/>
-      <c r="M67" s="51" t="n"/>
-      <c r="N67" s="51" t="n"/>
-      <c r="O67" s="51" t="n"/>
-      <c r="P67" s="51" t="n"/>
-      <c r="Q67" s="51" t="n"/>
-      <c r="R67" s="51" t="n"/>
-      <c r="S67" s="51" t="n"/>
-      <c r="T67" s="51" t="n"/>
-      <c r="U67" s="51" t="n"/>
-      <c r="V67" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W67" s="58" t="n"/>
+      <c r="M67" s="55" t="n"/>
+      <c r="N67" s="55" t="n"/>
+      <c r="O67" s="55" t="n"/>
+      <c r="P67" s="55" t="n"/>
+      <c r="Q67" s="55" t="n"/>
+      <c r="R67" s="55" t="n"/>
+      <c r="S67" s="55" t="n"/>
+      <c r="T67" s="55" t="n"/>
+      <c r="U67" s="55" t="n"/>
+      <c r="V67" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W67" s="57" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B68" s="45" t="n"/>
-      <c r="C68" s="53" t="n"/>
-      <c r="D68" s="53" t="n"/>
+      <c r="C68" s="46" t="n"/>
+      <c r="D68" s="46" t="n"/>
       <c r="E68" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F68" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G68" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G68" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H68" s="49" t="n"/>
       <c r="I68" s="49" t="n"/>
       <c r="J68" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K68" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L68" s="50" t="n"/>
-      <c r="M68" s="55" t="n"/>
-      <c r="N68" s="55" t="n"/>
-      <c r="O68" s="55" t="n"/>
-      <c r="P68" s="55" t="n"/>
-      <c r="Q68" s="55" t="n"/>
-      <c r="R68" s="55" t="n"/>
-      <c r="S68" s="55" t="n"/>
-      <c r="T68" s="55" t="n"/>
-      <c r="U68" s="55" t="n"/>
-      <c r="V68" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W68" s="57" t="n"/>
+      <c r="M68" s="51" t="n"/>
+      <c r="N68" s="51" t="n"/>
+      <c r="O68" s="51" t="n"/>
+      <c r="P68" s="51" t="n"/>
+      <c r="Q68" s="51" t="n"/>
+      <c r="R68" s="51" t="n"/>
+      <c r="S68" s="51" t="n"/>
+      <c r="T68" s="51" t="n"/>
+      <c r="U68" s="51" t="n"/>
+      <c r="V68" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W68" s="58" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B69" s="45" t="n"/>
-      <c r="C69" s="46" t="n"/>
-      <c r="D69" s="46" t="n"/>
+      <c r="C69" s="53" t="n"/>
+      <c r="D69" s="53" t="n"/>
       <c r="E69" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F69" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G69" s="48" t="n">
-        <v>24</v>
+      <c r="G69" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H69" s="49" t="n"/>
       <c r="I69" s="49" t="n"/>
       <c r="J69" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K69" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L69" s="50" t="n"/>
-      <c r="M69" s="51" t="n"/>
-      <c r="N69" s="51" t="n"/>
-      <c r="O69" s="51" t="n"/>
-      <c r="P69" s="51" t="n"/>
-      <c r="Q69" s="51" t="n"/>
-      <c r="R69" s="51" t="n"/>
-      <c r="S69" s="51" t="n"/>
-      <c r="T69" s="51" t="n"/>
-      <c r="U69" s="51" t="n"/>
-      <c r="V69" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W69" s="58" t="n"/>
+      <c r="M69" s="55" t="n"/>
+      <c r="N69" s="55" t="n"/>
+      <c r="O69" s="55" t="n"/>
+      <c r="P69" s="55" t="n"/>
+      <c r="Q69" s="55" t="n"/>
+      <c r="R69" s="55" t="n"/>
+      <c r="S69" s="55" t="n"/>
+      <c r="T69" s="55" t="n"/>
+      <c r="U69" s="55" t="n"/>
+      <c r="V69" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W69" s="57" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B70" s="45" t="n"/>
-      <c r="C70" s="53" t="n"/>
-      <c r="D70" s="53" t="n"/>
+      <c r="C70" s="46" t="n"/>
+      <c r="D70" s="46" t="n"/>
       <c r="E70" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F70" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G70" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G70" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H70" s="49" t="n"/>
       <c r="I70" s="49" t="n"/>
       <c r="J70" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K70" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L70" s="50" t="n"/>
-      <c r="M70" s="55" t="n"/>
-      <c r="N70" s="55" t="n"/>
-      <c r="O70" s="55" t="n"/>
-      <c r="P70" s="55" t="n"/>
-      <c r="Q70" s="55" t="n"/>
-      <c r="R70" s="55" t="n"/>
-      <c r="S70" s="55" t="n"/>
-      <c r="T70" s="55" t="n"/>
-      <c r="U70" s="55" t="n"/>
-      <c r="V70" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W70" s="57" t="n"/>
+      <c r="M70" s="51" t="n"/>
+      <c r="N70" s="51" t="n"/>
+      <c r="O70" s="51" t="n"/>
+      <c r="P70" s="51" t="n"/>
+      <c r="Q70" s="51" t="n"/>
+      <c r="R70" s="51" t="n"/>
+      <c r="S70" s="51" t="n"/>
+      <c r="T70" s="51" t="n"/>
+      <c r="U70" s="51" t="n"/>
+      <c r="V70" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W70" s="58" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B71" s="45" t="n"/>
-      <c r="C71" s="46" t="n"/>
-      <c r="D71" s="46" t="n"/>
+      <c r="C71" s="53" t="n"/>
+      <c r="D71" s="53" t="n"/>
       <c r="E71" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F71" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G71" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G71" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H71" s="49" t="n"/>
       <c r="I71" s="49" t="n"/>
       <c r="J71" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K71" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L71" s="50" t="n"/>
-      <c r="M71" s="51" t="n"/>
-      <c r="N71" s="51" t="n"/>
-      <c r="O71" s="51" t="n"/>
-      <c r="P71" s="51" t="n"/>
-      <c r="Q71" s="51" t="n"/>
-      <c r="R71" s="51" t="n"/>
-      <c r="S71" s="51" t="n"/>
-      <c r="T71" s="51" t="n"/>
-      <c r="U71" s="51" t="n"/>
-      <c r="V71" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W71" s="58" t="n"/>
+      <c r="M71" s="55" t="n"/>
+      <c r="N71" s="55" t="n"/>
+      <c r="O71" s="55" t="n"/>
+      <c r="P71" s="55" t="n"/>
+      <c r="Q71" s="55" t="n"/>
+      <c r="R71" s="55" t="n"/>
+      <c r="S71" s="55" t="n"/>
+      <c r="T71" s="55" t="n"/>
+      <c r="U71" s="55" t="n"/>
+      <c r="V71" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W71" s="57" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B72" s="45" t="n"/>
-      <c r="C72" s="53" t="n"/>
-      <c r="D72" s="53" t="n"/>
+      <c r="C72" s="46" t="n"/>
+      <c r="D72" s="46" t="n"/>
       <c r="E72" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F72" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G72" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H72" s="49" t="n"/>
       <c r="I72" s="49" t="n"/>
@@ -5266,51 +5280,92 @@
         <v>59</v>
       </c>
       <c r="K72" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L72" s="50" t="n"/>
-      <c r="M72" s="55" t="n"/>
-      <c r="N72" s="55" t="n"/>
-      <c r="O72" s="55" t="n"/>
-      <c r="P72" s="55" t="n"/>
-      <c r="Q72" s="55" t="n"/>
-      <c r="R72" s="55" t="n"/>
-      <c r="S72" s="55" t="n"/>
-      <c r="T72" s="55" t="n"/>
-      <c r="U72" s="55" t="n"/>
-      <c r="V72" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W72" s="57" t="n"/>
+      <c r="M72" s="51" t="n"/>
+      <c r="N72" s="51" t="n"/>
+      <c r="O72" s="51" t="n"/>
+      <c r="P72" s="51" t="n"/>
+      <c r="Q72" s="51" t="n"/>
+      <c r="R72" s="51" t="n"/>
+      <c r="S72" s="51" t="n"/>
+      <c r="T72" s="51" t="n"/>
+      <c r="U72" s="51" t="n"/>
+      <c r="V72" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W72" s="58" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B73" s="45" t="n"/>
-      <c r="C73" s="46" t="n"/>
-      <c r="D73" s="46" t="n"/>
-      <c r="E73" s="47" t="n"/>
-      <c r="F73" s="47" t="n"/>
-      <c r="G73" s="60" t="n"/>
+      <c r="C73" s="53" t="n"/>
+      <c r="D73" s="53" t="n"/>
+      <c r="E73" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F73" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G73" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H73" s="49" t="n"/>
       <c r="I73" s="49" t="n"/>
-      <c r="J73" s="50" t="n"/>
-      <c r="K73" s="50" t="n"/>
+      <c r="J73" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K73" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L73" s="50" t="n"/>
-      <c r="M73" s="51" t="n"/>
-      <c r="N73" s="51" t="n"/>
-      <c r="O73" s="51" t="n"/>
-      <c r="P73" s="51" t="n"/>
-      <c r="Q73" s="51" t="n"/>
-      <c r="R73" s="51" t="n"/>
-      <c r="S73" s="51" t="n"/>
-      <c r="T73" s="51" t="n"/>
-      <c r="U73" s="51" t="n"/>
-      <c r="V73" s="61" t="n"/>
-      <c r="W73" s="61" t="n"/>
+      <c r="M73" s="55" t="n"/>
+      <c r="N73" s="55" t="n"/>
+      <c r="O73" s="55" t="n"/>
+      <c r="P73" s="55" t="n"/>
+      <c r="Q73" s="55" t="n"/>
+      <c r="R73" s="55" t="n"/>
+      <c r="S73" s="55" t="n"/>
+      <c r="T73" s="55" t="n"/>
+      <c r="U73" s="55" t="n"/>
+      <c r="V73" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W73" s="57" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B74" s="45" t="n"/>
+      <c r="C74" s="46" t="n"/>
+      <c r="D74" s="46" t="n"/>
+      <c r="E74" s="47" t="n"/>
+      <c r="F74" s="47" t="n"/>
+      <c r="G74" s="60" t="n"/>
+      <c r="H74" s="49" t="n"/>
+      <c r="I74" s="49" t="n"/>
+      <c r="J74" s="50" t="n"/>
+      <c r="K74" s="50" t="n"/>
+      <c r="L74" s="50" t="n"/>
+      <c r="M74" s="51" t="n"/>
+      <c r="N74" s="51" t="n"/>
+      <c r="O74" s="51" t="n"/>
+      <c r="P74" s="51" t="n"/>
+      <c r="Q74" s="51" t="n"/>
+      <c r="R74" s="51" t="n"/>
+      <c r="S74" s="51" t="n"/>
+      <c r="T74" s="51" t="n"/>
+      <c r="U74" s="51" t="n"/>
+      <c r="V74" s="61" t="n"/>
+      <c r="W74" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W74"/>
+  <dimension ref="A1:W75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,48 +1982,48 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/20(一)</t>
+          <t>2026/04/21(二)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="G4" s="66" t="n">
-        <v>16.7</v>
+        <v>15.9</v>
       </c>
       <c r="H4" s="67" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I4" s="67" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J4" s="68" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K4" s="68" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="L4" s="68" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M4" s="69" t="inlineStr">
         <is>
-          <t>株冶集团、华升股份、可川科技</t>
-        </is>
-      </c>
-      <c r="N4" s="69" t="inlineStr"/>
+          <t>金 螳 螂、金富科技、圣龙股份</t>
+        </is>
+      </c>
+      <c r="N4" s="69" t="inlineStr">
+        <is>
+          <t>株冶集团</t>
+        </is>
+      </c>
       <c r="O4" s="69" t="inlineStr"/>
-      <c r="P4" s="69" t="inlineStr">
-        <is>
-          <t>博云新材</t>
-        </is>
-      </c>
+      <c r="P4" s="69" t="inlineStr"/>
       <c r="Q4" s="69" t="inlineStr"/>
       <c r="R4" s="69" t="inlineStr"/>
       <c r="S4" s="69" t="inlineStr"/>
@@ -2037,57 +2037,49 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/17(五)</t>
+          <t>2026/04/20(一)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
       <c r="C5" s="64" t="inlineStr"/>
       <c r="D5" s="64" t="inlineStr"/>
       <c r="E5" s="65" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G5" s="66" t="n">
-        <v>22</v>
+        <v>16.7</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I5" s="67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J5" s="68" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K5" s="68" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L5" s="68" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M5" s="69" t="inlineStr">
         <is>
-          <t>均瑶健康、京投发展</t>
-        </is>
-      </c>
-      <c r="N5" s="69" t="inlineStr">
-        <is>
-          <t>盛视科技</t>
-        </is>
-      </c>
-      <c r="O5" s="69" t="inlineStr">
+          <t>株冶集团、华升股份、可川科技</t>
+        </is>
+      </c>
+      <c r="N5" s="69" t="inlineStr"/>
+      <c r="O5" s="69" t="inlineStr"/>
+      <c r="P5" s="69" t="inlineStr">
         <is>
           <t>博云新材</t>
         </is>
       </c>
-      <c r="P5" s="69" t="inlineStr"/>
-      <c r="Q5" s="69" t="inlineStr">
-        <is>
-          <t>圣阳股份</t>
-        </is>
-      </c>
+      <c r="Q5" s="69" t="inlineStr"/>
       <c r="R5" s="69" t="inlineStr"/>
       <c r="S5" s="69" t="inlineStr"/>
       <c r="T5" s="69" t="inlineStr"/>
@@ -2100,193 +2092,197 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/04/16(四)</t>
+          <t>2026/04/17(五)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
       <c r="C6" s="64" t="inlineStr"/>
       <c r="D6" s="64" t="inlineStr"/>
       <c r="E6" s="65" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G6" s="66" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="H6" s="67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" s="67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" s="68" t="n">
+        <v>13</v>
+      </c>
+      <c r="K6" s="68" t="n">
+        <v>58</v>
+      </c>
+      <c r="L6" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="K6" s="68" t="n">
-        <v>71</v>
-      </c>
-      <c r="L6" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="M6" s="69" t="inlineStr">
         <is>
+          <t>均瑶健康、京投发展</t>
+        </is>
+      </c>
+      <c r="N6" s="69" t="inlineStr">
+        <is>
           <t>盛视科技</t>
         </is>
       </c>
-      <c r="N6" s="69" t="inlineStr">
+      <c r="O6" s="69" t="inlineStr">
         <is>
           <t>博云新材</t>
         </is>
       </c>
-      <c r="O6" s="69" t="inlineStr"/>
-      <c r="P6" s="69" t="inlineStr">
+      <c r="P6" s="69" t="inlineStr"/>
+      <c r="Q6" s="69" t="inlineStr">
         <is>
           <t>圣阳股份</t>
         </is>
       </c>
-      <c r="Q6" s="69" t="inlineStr"/>
       <c r="R6" s="69" t="inlineStr"/>
       <c r="S6" s="69" t="inlineStr"/>
       <c r="T6" s="69" t="inlineStr"/>
       <c r="U6" s="69" t="inlineStr"/>
       <c r="V6" s="69" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="W6" s="69" t="inlineStr"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="62" t="inlineStr">
         <is>
-          <t>2026/04/15(三)</t>
+          <t>2026/04/16(四)</t>
         </is>
       </c>
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="64" t="inlineStr"/>
       <c r="D7" s="64" t="inlineStr"/>
       <c r="E7" s="65" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="F7" s="65" t="n">
-        <v>57</v>
-      </c>
-      <c r="G7" s="71" t="n">
-        <v>29.6</v>
+        <v>79</v>
+      </c>
+      <c r="G7" s="66" t="n">
+        <v>22.5</v>
       </c>
       <c r="H7" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I7" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" s="68" t="n">
-        <v>11</v>
-      </c>
       <c r="K7" s="68" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="L7" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M7" s="69" t="inlineStr">
         <is>
-          <t>博云新材、天邦食品</t>
-        </is>
-      </c>
-      <c r="N7" s="69" t="inlineStr"/>
-      <c r="O7" s="69" t="inlineStr">
+          <t>盛视科技</t>
+        </is>
+      </c>
+      <c r="N7" s="69" t="inlineStr">
+        <is>
+          <t>博云新材</t>
+        </is>
+      </c>
+      <c r="O7" s="69" t="inlineStr"/>
+      <c r="P7" s="69" t="inlineStr">
         <is>
           <t>圣阳股份</t>
         </is>
       </c>
-      <c r="P7" s="69" t="inlineStr"/>
       <c r="Q7" s="69" t="inlineStr"/>
       <c r="R7" s="69" t="inlineStr"/>
       <c r="S7" s="69" t="inlineStr"/>
       <c r="T7" s="69" t="inlineStr"/>
       <c r="U7" s="69" t="inlineStr"/>
       <c r="V7" s="69" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="W7" s="69" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="62" t="inlineStr">
         <is>
-          <t>2026/04/14(二)</t>
+          <t>2026/04/15(三)</t>
         </is>
       </c>
       <c r="B8" s="63" t="inlineStr"/>
       <c r="C8" s="64" t="inlineStr"/>
       <c r="D8" s="64" t="inlineStr"/>
       <c r="E8" s="65" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F8" s="65" t="n">
-        <v>55</v>
-      </c>
-      <c r="G8" s="66" t="n">
-        <v>24.7</v>
+        <v>57</v>
+      </c>
+      <c r="G8" s="71" t="n">
+        <v>29.6</v>
       </c>
       <c r="H8" s="67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I8" s="67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J8" s="68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K8" s="68" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L8" s="68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M8" s="69" t="inlineStr">
         <is>
-          <t>美能能源</t>
-        </is>
-      </c>
-      <c r="N8" s="69" t="inlineStr">
-        <is>
-          <t>中恒电气、圣阳股份</t>
-        </is>
-      </c>
-      <c r="O8" s="69" t="inlineStr"/>
-      <c r="P8" s="69" t="inlineStr">
-        <is>
-          <t>华远控股</t>
-        </is>
-      </c>
+          <t>博云新材、天邦食品</t>
+        </is>
+      </c>
+      <c r="N8" s="69" t="inlineStr"/>
+      <c r="O8" s="69" t="inlineStr">
+        <is>
+          <t>圣阳股份</t>
+        </is>
+      </c>
+      <c r="P8" s="69" t="inlineStr"/>
       <c r="Q8" s="69" t="inlineStr"/>
       <c r="R8" s="69" t="inlineStr"/>
       <c r="S8" s="69" t="inlineStr"/>
       <c r="T8" s="69" t="inlineStr"/>
       <c r="U8" s="69" t="inlineStr"/>
       <c r="V8" s="69" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="W8" s="69" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="62" t="inlineStr">
         <is>
-          <t>2026/04/13(一)</t>
+          <t>2026/04/14(二)</t>
         </is>
       </c>
       <c r="B9" s="63" t="inlineStr"/>
       <c r="C9" s="64" t="inlineStr"/>
       <c r="D9" s="64" t="inlineStr"/>
       <c r="E9" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F9" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G9" s="66" t="n">
-        <v>20.3</v>
+        <v>24.7</v>
       </c>
       <c r="H9" s="67" t="n">
         <v>4</v>
@@ -2295,30 +2291,30 @@
         <v>4</v>
       </c>
       <c r="J9" s="68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K9" s="68" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L9" s="68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M9" s="69" t="inlineStr">
         <is>
+          <t>美能能源</t>
+        </is>
+      </c>
+      <c r="N9" s="69" t="inlineStr">
+        <is>
           <t>中恒电气、圣阳股份</t>
         </is>
       </c>
-      <c r="N9" s="69" t="inlineStr">
-        <is>
-          <t>长源东谷</t>
-        </is>
-      </c>
-      <c r="O9" s="69" t="inlineStr">
+      <c r="O9" s="69" t="inlineStr"/>
+      <c r="P9" s="69" t="inlineStr">
         <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="P9" s="69" t="inlineStr"/>
       <c r="Q9" s="69" t="inlineStr"/>
       <c r="R9" s="69" t="inlineStr"/>
       <c r="S9" s="69" t="inlineStr"/>
@@ -2332,7 +2328,7 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="62" t="inlineStr">
         <is>
-          <t>2026/04/10(五)</t>
+          <t>2026/04/13(一)</t>
         </is>
       </c>
       <c r="B10" s="63" t="inlineStr"/>
@@ -2344,35 +2340,39 @@
       <c r="F10" s="65" t="n">
         <v>59</v>
       </c>
-      <c r="G10" s="71" t="n">
-        <v>31.4</v>
+      <c r="G10" s="66" t="n">
+        <v>20.3</v>
       </c>
       <c r="H10" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I10" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J10" s="68" t="n">
-        <v>13</v>
-      </c>
       <c r="K10" s="68" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L10" s="68" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M10" s="69" t="inlineStr">
         <is>
-          <t>中嘉博创、长源东谷、来伊份</t>
+          <t>中恒电气、圣阳股份</t>
         </is>
       </c>
       <c r="N10" s="69" t="inlineStr">
         <is>
+          <t>长源东谷</t>
+        </is>
+      </c>
+      <c r="O10" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="O10" s="69" t="inlineStr"/>
       <c r="P10" s="69" t="inlineStr"/>
       <c r="Q10" s="69" t="inlineStr"/>
       <c r="R10" s="69" t="inlineStr"/>
@@ -2380,54 +2380,54 @@
       <c r="T10" s="69" t="inlineStr"/>
       <c r="U10" s="69" t="inlineStr"/>
       <c r="V10" s="69" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="W10" s="69" t="inlineStr"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="62" t="inlineStr">
         <is>
-          <t>2026/04/09(四)</t>
+          <t>2026/04/10(五)</t>
         </is>
       </c>
       <c r="B11" s="63" t="inlineStr"/>
       <c r="C11" s="64" t="inlineStr"/>
       <c r="D11" s="64" t="inlineStr"/>
       <c r="E11" s="65" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F11" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G11" s="66" t="n">
-        <v>23.2</v>
+        <v>59</v>
+      </c>
+      <c r="G11" s="71" t="n">
+        <v>31.4</v>
       </c>
       <c r="H11" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I11" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J11" s="68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K11" s="68" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L11" s="68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M11" s="69" t="inlineStr">
         <is>
+          <t>中嘉博创、长源东谷、来伊份</t>
+        </is>
+      </c>
+      <c r="N11" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="N11" s="69" t="inlineStr"/>
-      <c r="O11" s="69" t="inlineStr">
-        <is>
-          <t>汇源通信</t>
-        </is>
-      </c>
+      <c r="O11" s="69" t="inlineStr"/>
       <c r="P11" s="69" t="inlineStr"/>
       <c r="Q11" s="69" t="inlineStr"/>
       <c r="R11" s="69" t="inlineStr"/>
@@ -2435,54 +2435,54 @@
       <c r="T11" s="69" t="inlineStr"/>
       <c r="U11" s="69" t="inlineStr"/>
       <c r="V11" s="69" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="W11" s="69" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="62" t="inlineStr">
         <is>
-          <t>2026/04/08(三)</t>
+          <t>2026/04/09(四)</t>
         </is>
       </c>
       <c r="B12" s="63" t="inlineStr"/>
       <c r="C12" s="64" t="inlineStr"/>
       <c r="D12" s="64" t="inlineStr"/>
       <c r="E12" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="F12" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="G12" s="66" t="n">
-        <v>11.5</v>
+        <v>23.2</v>
       </c>
       <c r="H12" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I12" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J12" s="68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K12" s="68" t="n">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="L12" s="68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M12" s="69" t="inlineStr">
         <is>
-          <t>中安科</t>
-        </is>
-      </c>
-      <c r="N12" s="69" t="inlineStr">
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="N12" s="69" t="inlineStr"/>
+      <c r="O12" s="69" t="inlineStr">
         <is>
           <t>汇源通信</t>
         </is>
       </c>
-      <c r="O12" s="69" t="inlineStr"/>
       <c r="P12" s="69" t="inlineStr"/>
       <c r="Q12" s="69" t="inlineStr"/>
       <c r="R12" s="69" t="inlineStr"/>
@@ -2497,20 +2497,20 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="62" t="inlineStr">
         <is>
-          <t>2026/04/07(二)</t>
+          <t>2026/04/08(三)</t>
         </is>
       </c>
       <c r="B13" s="63" t="inlineStr"/>
       <c r="C13" s="64" t="inlineStr"/>
       <c r="D13" s="64" t="inlineStr"/>
       <c r="E13" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F13" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G13" s="66" t="n">
-        <v>21.8</v>
+        <v>11.5</v>
       </c>
       <c r="H13" s="67" t="n">
         <v>4</v>
@@ -2519,91 +2519,95 @@
         <v>4</v>
       </c>
       <c r="J13" s="68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K13" s="68" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="L13" s="68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M13" s="69" t="inlineStr">
         <is>
-          <t>汇源通信、新能泰山</t>
-        </is>
-      </c>
-      <c r="N13" s="69" t="inlineStr"/>
+          <t>中安科</t>
+        </is>
+      </c>
+      <c r="N13" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信</t>
+        </is>
+      </c>
       <c r="O13" s="69" t="inlineStr"/>
       <c r="P13" s="69" t="inlineStr"/>
-      <c r="Q13" s="69" t="inlineStr">
-        <is>
-          <t>津药药业</t>
-        </is>
-      </c>
+      <c r="Q13" s="69" t="inlineStr"/>
       <c r="R13" s="69" t="inlineStr"/>
       <c r="S13" s="69" t="inlineStr"/>
       <c r="T13" s="69" t="inlineStr"/>
       <c r="U13" s="69" t="inlineStr"/>
       <c r="V13" s="69" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W13" s="69" t="inlineStr"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="62" t="inlineStr">
         <is>
-          <t>2026/04/06(一)</t>
+          <t>2026/04/07(二)</t>
         </is>
       </c>
       <c r="B14" s="63" t="inlineStr"/>
       <c r="C14" s="64" t="inlineStr"/>
       <c r="D14" s="64" t="inlineStr"/>
       <c r="E14" s="65" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F14" s="65" t="n">
-        <v>36</v>
-      </c>
-      <c r="G14" s="71" t="n">
-        <v>25</v>
+        <v>93</v>
+      </c>
+      <c r="G14" s="66" t="n">
+        <v>21.8</v>
       </c>
       <c r="H14" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I14" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J14" s="68" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="L14" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K14" s="68" t="n">
-        <v>32</v>
-      </c>
-      <c r="L14" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" s="69" t="inlineStr"/>
+      <c r="M14" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信、新能泰山</t>
+        </is>
+      </c>
       <c r="N14" s="69" t="inlineStr"/>
       <c r="O14" s="69" t="inlineStr"/>
-      <c r="P14" s="69" t="inlineStr">
+      <c r="P14" s="69" t="inlineStr"/>
+      <c r="Q14" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="Q14" s="69" t="inlineStr"/>
       <c r="R14" s="69" t="inlineStr"/>
       <c r="S14" s="69" t="inlineStr"/>
       <c r="T14" s="69" t="inlineStr"/>
       <c r="U14" s="69" t="inlineStr"/>
       <c r="V14" s="69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W14" s="69" t="inlineStr"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="62" t="inlineStr">
         <is>
-          <t>2026/04/03(五)</t>
+          <t>2026/04/06(一)</t>
         </is>
       </c>
       <c r="B15" s="63" t="inlineStr"/>
@@ -2647,105 +2651,105 @@
       <c r="T15" s="69" t="inlineStr"/>
       <c r="U15" s="69" t="inlineStr"/>
       <c r="V15" s="69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W15" s="69" t="inlineStr"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B16" s="63" t="inlineStr"/>
       <c r="C16" s="64" t="inlineStr"/>
       <c r="D16" s="64" t="inlineStr"/>
       <c r="E16" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F16" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G16" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H16" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I16" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J16" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K16" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L16" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M16" s="69" t="inlineStr"/>
       <c r="N16" s="69" t="inlineStr"/>
-      <c r="O16" s="69" t="inlineStr">
+      <c r="O16" s="69" t="inlineStr"/>
+      <c r="P16" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P16" s="69" t="inlineStr"/>
       <c r="Q16" s="69" t="inlineStr"/>
       <c r="R16" s="69" t="inlineStr"/>
       <c r="S16" s="69" t="inlineStr"/>
       <c r="T16" s="69" t="inlineStr"/>
       <c r="U16" s="69" t="inlineStr"/>
       <c r="V16" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W16" s="69" t="inlineStr"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B17" s="63" t="inlineStr"/>
       <c r="C17" s="64" t="inlineStr"/>
       <c r="D17" s="64" t="inlineStr"/>
       <c r="E17" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F17" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G17" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G17" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H17" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I17" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J17" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K17" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L17" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M17" s="69" t="inlineStr"/>
-      <c r="N17" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M17" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N17" s="69" t="inlineStr"/>
+      <c r="O17" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O17" s="69" t="inlineStr"/>
       <c r="P17" s="69" t="inlineStr"/>
       <c r="Q17" s="69" t="inlineStr"/>
       <c r="R17" s="69" t="inlineStr"/>
@@ -2753,51 +2757,47 @@
       <c r="T17" s="69" t="inlineStr"/>
       <c r="U17" s="69" t="inlineStr"/>
       <c r="V17" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W17" s="69" t="inlineStr"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B18" s="63" t="inlineStr"/>
       <c r="C18" s="64" t="inlineStr"/>
       <c r="D18" s="64" t="inlineStr"/>
       <c r="E18" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F18" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G18" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G18" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H18" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I18" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J18" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K18" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L18" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M18" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M18" s="69" t="inlineStr"/>
+      <c r="N18" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N18" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O18" s="69" t="inlineStr"/>
@@ -2808,254 +2808,250 @@
       <c r="T18" s="69" t="inlineStr"/>
       <c r="U18" s="69" t="inlineStr"/>
       <c r="V18" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W18" s="69" t="inlineStr"/>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B19" s="63" t="inlineStr"/>
+      <c r="C19" s="64" t="inlineStr"/>
+      <c r="D19" s="64" t="inlineStr"/>
+      <c r="E19" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F19" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G19" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H19" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K19" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L19" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M19" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N19" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O19" s="69" t="inlineStr"/>
+      <c r="P19" s="69" t="inlineStr"/>
+      <c r="Q19" s="69" t="inlineStr"/>
+      <c r="R19" s="69" t="inlineStr"/>
+      <c r="S19" s="69" t="inlineStr"/>
+      <c r="T19" s="69" t="inlineStr"/>
+      <c r="U19" s="69" t="inlineStr"/>
+      <c r="V19" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W18" s="69" t="inlineStr"/>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="W19" s="69" t="inlineStr"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C19" s="38" t="inlineStr">
+      <c r="C20" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D19" s="38" t="inlineStr">
+      <c r="D20" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E19" s="39" t="n">
+      <c r="E20" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F19" s="39" t="n">
+      <c r="F20" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G19" s="40" t="n">
+      <c r="G20" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H19" s="41" t="n">
+      <c r="H20" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I19" s="41" t="n">
+      <c r="I20" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J19" s="42" t="n">
+      <c r="J20" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K19" s="42" t="n">
+      <c r="K20" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L19" s="42" t="n">
+      <c r="L20" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M19" s="43" t="inlineStr">
+      <c r="M20" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N19" s="43" t="inlineStr"/>
-      <c r="O19" s="43" t="inlineStr">
+      <c r="N20" s="43" t="inlineStr"/>
+      <c r="O20" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P19" s="43" t="inlineStr"/>
-      <c r="Q19" s="43" t="inlineStr"/>
-      <c r="R19" s="43" t="inlineStr"/>
-      <c r="S19" s="43" t="inlineStr"/>
-      <c r="T19" s="43" t="inlineStr"/>
-      <c r="U19" s="43" t="inlineStr"/>
-      <c r="V19" s="43" t="n">
+      <c r="P20" s="43" t="inlineStr"/>
+      <c r="Q20" s="43" t="inlineStr"/>
+      <c r="R20" s="43" t="inlineStr"/>
+      <c r="S20" s="43" t="inlineStr"/>
+      <c r="T20" s="43" t="inlineStr"/>
+      <c r="U20" s="43" t="inlineStr"/>
+      <c r="V20" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W19" s="43" t="inlineStr"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B20" s="45" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="46" t="n"/>
-      <c r="E20" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F20" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G20" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H20" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K20" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L20" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M20" s="51" t="n"/>
-      <c r="N20" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O20" s="51" t="n"/>
-      <c r="P20" s="51" t="n"/>
-      <c r="Q20" s="51" t="n"/>
-      <c r="R20" s="51" t="n"/>
-      <c r="S20" s="51" t="n"/>
-      <c r="T20" s="51" t="n"/>
-      <c r="U20" s="51" t="n"/>
-      <c r="V20" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W20" s="43" t="inlineStr"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B21" s="45" t="n"/>
-      <c r="C21" s="53" t="n"/>
-      <c r="D21" s="53" t="n"/>
+      <c r="C21" s="46" t="n"/>
+      <c r="D21" s="46" t="n"/>
       <c r="E21" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F21" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G21" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G21" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H21" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I21" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J21" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K21" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L21" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M21" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N21" s="55" t="n"/>
-      <c r="O21" s="55" t="n"/>
-      <c r="P21" s="55" t="n"/>
-      <c r="Q21" s="55" t="n"/>
-      <c r="R21" s="55" t="n"/>
-      <c r="S21" s="55" t="n"/>
-      <c r="T21" s="55" t="n"/>
-      <c r="U21" s="55" t="n"/>
-      <c r="V21" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W21" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M21" s="51" t="n"/>
+      <c r="N21" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O21" s="51" t="n"/>
+      <c r="P21" s="51" t="n"/>
+      <c r="Q21" s="51" t="n"/>
+      <c r="R21" s="51" t="n"/>
+      <c r="S21" s="51" t="n"/>
+      <c r="T21" s="51" t="n"/>
+      <c r="U21" s="51" t="n"/>
+      <c r="V21" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="46" t="n"/>
+      <c r="C22" s="53" t="n"/>
+      <c r="D22" s="53" t="n"/>
       <c r="E22" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G22" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G22" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H22" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K22" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L22" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M22" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N22" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O22" s="51" t="n"/>
-      <c r="P22" s="51" t="n"/>
-      <c r="Q22" s="51" t="n"/>
-      <c r="R22" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S22" s="51" t="n"/>
-      <c r="T22" s="51" t="n"/>
-      <c r="U22" s="51" t="n"/>
-      <c r="V22" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W22" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M22" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N22" s="55" t="n"/>
+      <c r="O22" s="55" t="n"/>
+      <c r="P22" s="55" t="n"/>
+      <c r="Q22" s="55" t="n"/>
+      <c r="R22" s="55" t="n"/>
+      <c r="S22" s="55" t="n"/>
+      <c r="T22" s="55" t="n"/>
+      <c r="U22" s="55" t="n"/>
+      <c r="V22" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W22" s="57" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="53" t="n"/>
-      <c r="D23" s="53" t="n"/>
+      <c r="C23" s="46" t="n"/>
+      <c r="D23" s="46" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G23" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H23" s="49" t="n">
         <v>1</v>
@@ -3064,493 +3060,497 @@
         <v>1</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L23" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M23" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M23" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N23" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N23" s="55" t="n"/>
-      <c r="O23" s="55" t="n"/>
-      <c r="P23" s="55" t="n"/>
-      <c r="Q23" s="55" t="inlineStr">
+      <c r="O23" s="51" t="n"/>
+      <c r="P23" s="51" t="n"/>
+      <c r="Q23" s="51" t="n"/>
+      <c r="R23" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R23" s="55" t="n"/>
-      <c r="S23" s="55" t="n"/>
-      <c r="T23" s="55" t="n"/>
-      <c r="U23" s="55" t="n"/>
-      <c r="V23" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W23" s="57" t="n"/>
+      <c r="S23" s="51" t="n"/>
+      <c r="T23" s="51" t="n"/>
+      <c r="U23" s="51" t="n"/>
+      <c r="V23" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W23" s="58" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G24" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G24" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H24" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L24" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N24" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O24" s="51" t="n"/>
-      <c r="P24" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M24" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N24" s="55" t="n"/>
+      <c r="O24" s="55" t="n"/>
+      <c r="P24" s="55" t="n"/>
+      <c r="Q24" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q24" s="51" t="n"/>
-      <c r="R24" s="51" t="n"/>
-      <c r="S24" s="51" t="n"/>
-      <c r="T24" s="51" t="n"/>
-      <c r="U24" s="51" t="n"/>
-      <c r="V24" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W24" s="58" t="n"/>
+      <c r="R24" s="55" t="n"/>
+      <c r="S24" s="55" t="n"/>
+      <c r="T24" s="55" t="n"/>
+      <c r="U24" s="55" t="n"/>
+      <c r="V24" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W24" s="57" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="53" t="n"/>
-      <c r="D25" s="53" t="n"/>
+      <c r="C25" s="46" t="n"/>
+      <c r="D25" s="46" t="n"/>
       <c r="E25" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F25" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G25" s="59" t="n">
-        <v>45.1</v>
+      <c r="G25" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H25" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L25" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M25" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N25" s="55" t="n"/>
-      <c r="O25" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P25" s="55" t="n"/>
-      <c r="Q25" s="55" t="n"/>
-      <c r="R25" s="55" t="n"/>
-      <c r="S25" s="55" t="n"/>
-      <c r="T25" s="55" t="n"/>
-      <c r="U25" s="55" t="n"/>
-      <c r="V25" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W25" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M25" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N25" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O25" s="51" t="n"/>
+      <c r="P25" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q25" s="51" t="n"/>
+      <c r="R25" s="51" t="n"/>
+      <c r="S25" s="51" t="n"/>
+      <c r="T25" s="51" t="n"/>
+      <c r="U25" s="51" t="n"/>
+      <c r="V25" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W25" s="58" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="46" t="n"/>
-      <c r="D26" s="46" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
       <c r="E26" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F26" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G26" s="54" t="n">
-        <v>26.3</v>
+      <c r="G26" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H26" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I26" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L26" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M26" s="51" t="n"/>
-      <c r="N26" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M26" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N26" s="55" t="n"/>
+      <c r="O26" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O26" s="51" t="n"/>
-      <c r="P26" s="51" t="n"/>
-      <c r="Q26" s="51" t="n"/>
-      <c r="R26" s="51" t="n"/>
-      <c r="S26" s="51" t="n"/>
-      <c r="T26" s="51" t="n"/>
-      <c r="U26" s="51" t="n"/>
-      <c r="V26" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W26" s="58" t="n"/>
+      <c r="P26" s="55" t="n"/>
+      <c r="Q26" s="55" t="n"/>
+      <c r="R26" s="55" t="n"/>
+      <c r="S26" s="55" t="n"/>
+      <c r="T26" s="55" t="n"/>
+      <c r="U26" s="55" t="n"/>
+      <c r="V26" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W26" s="57" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="53" t="n"/>
-      <c r="D27" s="53" t="n"/>
+      <c r="C27" s="46" t="n"/>
+      <c r="D27" s="46" t="n"/>
       <c r="E27" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F27" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G27" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H27" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L27" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M27" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M27" s="51" t="n"/>
+      <c r="N27" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N27" s="55" t="n"/>
-      <c r="O27" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P27" s="55" t="n"/>
-      <c r="Q27" s="55" t="n"/>
-      <c r="R27" s="55" t="n"/>
-      <c r="S27" s="55" t="n"/>
-      <c r="T27" s="55" t="n"/>
-      <c r="U27" s="55" t="n"/>
-      <c r="V27" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W27" s="57" t="n"/>
+      <c r="O27" s="51" t="n"/>
+      <c r="P27" s="51" t="n"/>
+      <c r="Q27" s="51" t="n"/>
+      <c r="R27" s="51" t="n"/>
+      <c r="S27" s="51" t="n"/>
+      <c r="T27" s="51" t="n"/>
+      <c r="U27" s="51" t="n"/>
+      <c r="V27" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W27" s="58" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="46" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="53" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G28" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H28" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I28" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L28" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M28" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N28" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O28" s="51" t="n"/>
-      <c r="P28" s="51" t="n"/>
-      <c r="Q28" s="51" t="n"/>
-      <c r="R28" s="51" t="n"/>
-      <c r="S28" s="51" t="n"/>
-      <c r="T28" s="51" t="n"/>
-      <c r="U28" s="51" t="n"/>
-      <c r="V28" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W28" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M28" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N28" s="55" t="n"/>
+      <c r="O28" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P28" s="55" t="n"/>
+      <c r="Q28" s="55" t="n"/>
+      <c r="R28" s="55" t="n"/>
+      <c r="S28" s="55" t="n"/>
+      <c r="T28" s="55" t="n"/>
+      <c r="U28" s="55" t="n"/>
+      <c r="V28" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W28" s="57" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="53" t="n"/>
-      <c r="D29" s="53" t="n"/>
+      <c r="C29" s="46" t="n"/>
+      <c r="D29" s="46" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G29" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H29" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K29" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L29" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I29" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J29" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K29" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L29" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M29" s="55" t="inlineStr">
+      <c r="M29" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N29" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N29" s="55" t="n"/>
-      <c r="O29" s="55" t="n"/>
-      <c r="P29" s="55" t="n"/>
-      <c r="Q29" s="55" t="n"/>
-      <c r="R29" s="55" t="n"/>
-      <c r="S29" s="55" t="n"/>
-      <c r="T29" s="55" t="n"/>
-      <c r="U29" s="55" t="n"/>
-      <c r="V29" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W29" s="57" t="n"/>
+      <c r="O29" s="51" t="n"/>
+      <c r="P29" s="51" t="n"/>
+      <c r="Q29" s="51" t="n"/>
+      <c r="R29" s="51" t="n"/>
+      <c r="S29" s="51" t="n"/>
+      <c r="T29" s="51" t="n"/>
+      <c r="U29" s="51" t="n"/>
+      <c r="V29" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W29" s="58" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="46" t="n"/>
-      <c r="D30" s="46" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="53" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G30" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G30" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H30" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I30" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J30" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L30" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N30" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O30" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P30" s="51" t="n"/>
-      <c r="Q30" s="51" t="n"/>
-      <c r="R30" s="51" t="n"/>
-      <c r="S30" s="51" t="n"/>
-      <c r="T30" s="51" t="n"/>
-      <c r="U30" s="51" t="n"/>
-      <c r="V30" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W30" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M30" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N30" s="55" t="n"/>
+      <c r="O30" s="55" t="n"/>
+      <c r="P30" s="55" t="n"/>
+      <c r="Q30" s="55" t="n"/>
+      <c r="R30" s="55" t="n"/>
+      <c r="S30" s="55" t="n"/>
+      <c r="T30" s="55" t="n"/>
+      <c r="U30" s="55" t="n"/>
+      <c r="V30" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W30" s="57" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="53" t="n"/>
-      <c r="D31" s="53" t="n"/>
+      <c r="C31" s="46" t="n"/>
+      <c r="D31" s="46" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G31" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G31" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H31" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I31" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J31" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L31" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M31" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N31" s="55" t="inlineStr">
+      <c r="M31" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N31" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O31" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O31" s="55" t="n"/>
-      <c r="P31" s="55" t="n"/>
-      <c r="Q31" s="55" t="n"/>
-      <c r="R31" s="55" t="n"/>
-      <c r="S31" s="55" t="n"/>
-      <c r="T31" s="55" t="n"/>
-      <c r="U31" s="55" t="n"/>
-      <c r="V31" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W31" s="57" t="n"/>
+      <c r="P31" s="51" t="n"/>
+      <c r="Q31" s="51" t="n"/>
+      <c r="R31" s="51" t="n"/>
+      <c r="S31" s="51" t="n"/>
+      <c r="T31" s="51" t="n"/>
+      <c r="U31" s="51" t="n"/>
+      <c r="V31" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W31" s="58" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="46" t="n"/>
-      <c r="D32" s="46" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G32" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H32" s="49" t="n">
         <v>2</v>
@@ -3559,208 +3559,218 @@
         <v>2</v>
       </c>
       <c r="J32" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K32" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L32" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M32" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M32" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N32" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N32" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O32" s="51" t="n"/>
-      <c r="P32" s="51" t="n"/>
-      <c r="Q32" s="51" t="n"/>
-      <c r="R32" s="51" t="n"/>
-      <c r="S32" s="51" t="n"/>
-      <c r="T32" s="51" t="n"/>
-      <c r="U32" s="51" t="n"/>
-      <c r="V32" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W32" s="58" t="n"/>
+      <c r="O32" s="55" t="n"/>
+      <c r="P32" s="55" t="n"/>
+      <c r="Q32" s="55" t="n"/>
+      <c r="R32" s="55" t="n"/>
+      <c r="S32" s="55" t="n"/>
+      <c r="T32" s="55" t="n"/>
+      <c r="U32" s="55" t="n"/>
+      <c r="V32" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W32" s="57" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="53" t="n"/>
-      <c r="D33" s="53" t="n"/>
+      <c r="C33" s="46" t="n"/>
+      <c r="D33" s="46" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G33" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H33" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I33" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J33" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L33" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M33" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M33" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N33" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N33" s="55" t="n"/>
-      <c r="O33" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P33" s="55" t="n"/>
-      <c r="Q33" s="55" t="n"/>
-      <c r="R33" s="55" t="n"/>
-      <c r="S33" s="55" t="n"/>
-      <c r="T33" s="55" t="n"/>
-      <c r="U33" s="55" t="n"/>
-      <c r="V33" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W33" s="57" t="n"/>
+      <c r="O33" s="51" t="n"/>
+      <c r="P33" s="51" t="n"/>
+      <c r="Q33" s="51" t="n"/>
+      <c r="R33" s="51" t="n"/>
+      <c r="S33" s="51" t="n"/>
+      <c r="T33" s="51" t="n"/>
+      <c r="U33" s="51" t="n"/>
+      <c r="V33" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W33" s="58" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="46" t="n"/>
-      <c r="D34" s="46" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G34" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G34" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H34" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J34" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L34" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M34" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N34" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O34" s="51" t="n"/>
-      <c r="P34" s="51" t="n"/>
-      <c r="Q34" s="51" t="n"/>
-      <c r="R34" s="51" t="n"/>
-      <c r="S34" s="51" t="n"/>
-      <c r="T34" s="51" t="n"/>
-      <c r="U34" s="51" t="n"/>
-      <c r="V34" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W34" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M34" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N34" s="55" t="n"/>
+      <c r="O34" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P34" s="55" t="n"/>
+      <c r="Q34" s="55" t="n"/>
+      <c r="R34" s="55" t="n"/>
+      <c r="S34" s="55" t="n"/>
+      <c r="T34" s="55" t="n"/>
+      <c r="U34" s="55" t="n"/>
+      <c r="V34" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W34" s="57" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="53" t="n"/>
-      <c r="D35" s="53" t="n"/>
+      <c r="C35" s="46" t="n"/>
+      <c r="D35" s="46" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G35" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G35" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H35" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I35" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J35" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L35" s="50" t="n"/>
-      <c r="M35" s="55" t="n"/>
-      <c r="N35" s="55" t="n"/>
-      <c r="O35" s="55" t="n"/>
-      <c r="P35" s="55" t="n"/>
-      <c r="Q35" s="55" t="n"/>
-      <c r="R35" s="55" t="n"/>
-      <c r="S35" s="55" t="n"/>
-      <c r="T35" s="55" t="n"/>
-      <c r="U35" s="55" t="n"/>
-      <c r="V35" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W35" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L35" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M35" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N35" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O35" s="51" t="n"/>
+      <c r="P35" s="51" t="n"/>
+      <c r="Q35" s="51" t="n"/>
+      <c r="R35" s="51" t="n"/>
+      <c r="S35" s="51" t="n"/>
+      <c r="T35" s="51" t="n"/>
+      <c r="U35" s="51" t="n"/>
+      <c r="V35" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W35" s="58" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
+      <c r="C36" s="53" t="n"/>
+      <c r="D36" s="53" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G36" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H36" s="49" t="n">
         <v>0</v>
@@ -3769,43 +3779,43 @@
         <v>0</v>
       </c>
       <c r="J36" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L36" s="50" t="n"/>
-      <c r="M36" s="51" t="n"/>
-      <c r="N36" s="51" t="n"/>
-      <c r="O36" s="51" t="n"/>
-      <c r="P36" s="51" t="n"/>
-      <c r="Q36" s="51" t="n"/>
-      <c r="R36" s="51" t="n"/>
-      <c r="S36" s="51" t="n"/>
-      <c r="T36" s="51" t="n"/>
-      <c r="U36" s="51" t="n"/>
-      <c r="V36" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W36" s="58" t="n"/>
+      <c r="M36" s="55" t="n"/>
+      <c r="N36" s="55" t="n"/>
+      <c r="O36" s="55" t="n"/>
+      <c r="P36" s="55" t="n"/>
+      <c r="Q36" s="55" t="n"/>
+      <c r="R36" s="55" t="n"/>
+      <c r="S36" s="55" t="n"/>
+      <c r="T36" s="55" t="n"/>
+      <c r="U36" s="55" t="n"/>
+      <c r="V36" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W36" s="57" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="53" t="n"/>
-      <c r="D37" s="53" t="n"/>
+      <c r="C37" s="46" t="n"/>
+      <c r="D37" s="46" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G37" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H37" s="49" t="n">
         <v>0</v>
@@ -3814,43 +3824,43 @@
         <v>0</v>
       </c>
       <c r="J37" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="55" t="n"/>
-      <c r="N37" s="55" t="n"/>
-      <c r="O37" s="55" t="n"/>
-      <c r="P37" s="55" t="n"/>
-      <c r="Q37" s="55" t="n"/>
-      <c r="R37" s="55" t="n"/>
-      <c r="S37" s="55" t="n"/>
-      <c r="T37" s="55" t="n"/>
-      <c r="U37" s="55" t="n"/>
-      <c r="V37" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W37" s="57" t="n"/>
+      <c r="M37" s="51" t="n"/>
+      <c r="N37" s="51" t="n"/>
+      <c r="O37" s="51" t="n"/>
+      <c r="P37" s="51" t="n"/>
+      <c r="Q37" s="51" t="n"/>
+      <c r="R37" s="51" t="n"/>
+      <c r="S37" s="51" t="n"/>
+      <c r="T37" s="51" t="n"/>
+      <c r="U37" s="51" t="n"/>
+      <c r="V37" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W37" s="58" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="46" t="n"/>
-      <c r="D38" s="46" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G38" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G38" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H38" s="49" t="n">
         <v>0</v>
@@ -3859,43 +3869,43 @@
         <v>0</v>
       </c>
       <c r="J38" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="51" t="n"/>
-      <c r="N38" s="51" t="n"/>
-      <c r="O38" s="51" t="n"/>
-      <c r="P38" s="51" t="n"/>
-      <c r="Q38" s="51" t="n"/>
-      <c r="R38" s="51" t="n"/>
-      <c r="S38" s="51" t="n"/>
-      <c r="T38" s="51" t="n"/>
-      <c r="U38" s="51" t="n"/>
-      <c r="V38" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W38" s="58" t="n"/>
+      <c r="M38" s="55" t="n"/>
+      <c r="N38" s="55" t="n"/>
+      <c r="O38" s="55" t="n"/>
+      <c r="P38" s="55" t="n"/>
+      <c r="Q38" s="55" t="n"/>
+      <c r="R38" s="55" t="n"/>
+      <c r="S38" s="55" t="n"/>
+      <c r="T38" s="55" t="n"/>
+      <c r="U38" s="55" t="n"/>
+      <c r="V38" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W38" s="57" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="53" t="n"/>
-      <c r="D39" s="53" t="n"/>
+      <c r="C39" s="46" t="n"/>
+      <c r="D39" s="46" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G39" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H39" s="49" t="n">
         <v>0</v>
@@ -3904,43 +3914,43 @@
         <v>0</v>
       </c>
       <c r="J39" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="55" t="n"/>
-      <c r="N39" s="55" t="n"/>
-      <c r="O39" s="55" t="n"/>
-      <c r="P39" s="55" t="n"/>
-      <c r="Q39" s="55" t="n"/>
-      <c r="R39" s="55" t="n"/>
-      <c r="S39" s="55" t="n"/>
-      <c r="T39" s="55" t="n"/>
-      <c r="U39" s="55" t="n"/>
-      <c r="V39" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W39" s="57" t="n"/>
+      <c r="M39" s="51" t="n"/>
+      <c r="N39" s="51" t="n"/>
+      <c r="O39" s="51" t="n"/>
+      <c r="P39" s="51" t="n"/>
+      <c r="Q39" s="51" t="n"/>
+      <c r="R39" s="51" t="n"/>
+      <c r="S39" s="51" t="n"/>
+      <c r="T39" s="51" t="n"/>
+      <c r="U39" s="51" t="n"/>
+      <c r="V39" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W39" s="58" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="46" t="n"/>
-      <c r="D40" s="46" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G40" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H40" s="49" t="n">
         <v>0</v>
@@ -3949,1371 +3959,1375 @@
         <v>0</v>
       </c>
       <c r="J40" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="51" t="n"/>
-      <c r="N40" s="51" t="n"/>
-      <c r="O40" s="51" t="n"/>
-      <c r="P40" s="51" t="n"/>
-      <c r="Q40" s="51" t="n"/>
-      <c r="R40" s="51" t="n"/>
-      <c r="S40" s="51" t="n"/>
-      <c r="T40" s="51" t="n"/>
-      <c r="U40" s="51" t="n"/>
-      <c r="V40" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W40" s="58" t="n"/>
+      <c r="M40" s="55" t="n"/>
+      <c r="N40" s="55" t="n"/>
+      <c r="O40" s="55" t="n"/>
+      <c r="P40" s="55" t="n"/>
+      <c r="Q40" s="55" t="n"/>
+      <c r="R40" s="55" t="n"/>
+      <c r="S40" s="55" t="n"/>
+      <c r="T40" s="55" t="n"/>
+      <c r="U40" s="55" t="n"/>
+      <c r="V40" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W40" s="57" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="53" t="n"/>
-      <c r="D41" s="53" t="n"/>
+      <c r="C41" s="46" t="n"/>
+      <c r="D41" s="46" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G41" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H41" s="49" t="n"/>
-      <c r="I41" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G41" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H41" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J41" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="55" t="n"/>
-      <c r="N41" s="55" t="n"/>
-      <c r="O41" s="55" t="n"/>
-      <c r="P41" s="55" t="n"/>
-      <c r="Q41" s="55" t="n"/>
-      <c r="R41" s="55" t="n"/>
-      <c r="S41" s="55" t="n"/>
-      <c r="T41" s="55" t="n"/>
-      <c r="U41" s="55" t="n"/>
-      <c r="V41" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W41" s="57" t="n"/>
+      <c r="M41" s="51" t="n"/>
+      <c r="N41" s="51" t="n"/>
+      <c r="O41" s="51" t="n"/>
+      <c r="P41" s="51" t="n"/>
+      <c r="Q41" s="51" t="n"/>
+      <c r="R41" s="51" t="n"/>
+      <c r="S41" s="51" t="n"/>
+      <c r="T41" s="51" t="n"/>
+      <c r="U41" s="51" t="n"/>
+      <c r="V41" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W41" s="58" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="46" t="n"/>
-      <c r="D42" s="46" t="n"/>
+      <c r="C42" s="53" t="n"/>
+      <c r="D42" s="53" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G42" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H42" s="49" t="n"/>
       <c r="I42" s="49" t="n"/>
       <c r="J42" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K42" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="51" t="n"/>
-      <c r="N42" s="51" t="n"/>
-      <c r="O42" s="51" t="n"/>
-      <c r="P42" s="51" t="n"/>
-      <c r="Q42" s="51" t="n"/>
-      <c r="R42" s="51" t="n"/>
-      <c r="S42" s="51" t="n"/>
-      <c r="T42" s="51" t="n"/>
-      <c r="U42" s="51" t="n"/>
-      <c r="V42" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W42" s="58" t="n"/>
+      <c r="M42" s="55" t="n"/>
+      <c r="N42" s="55" t="n"/>
+      <c r="O42" s="55" t="n"/>
+      <c r="P42" s="55" t="n"/>
+      <c r="Q42" s="55" t="n"/>
+      <c r="R42" s="55" t="n"/>
+      <c r="S42" s="55" t="n"/>
+      <c r="T42" s="55" t="n"/>
+      <c r="U42" s="55" t="n"/>
+      <c r="V42" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W42" s="57" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="53" t="n"/>
-      <c r="D43" s="53" t="n"/>
+      <c r="C43" s="46" t="n"/>
+      <c r="D43" s="46" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G43" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H43" s="49" t="n"/>
       <c r="I43" s="49" t="n"/>
       <c r="J43" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K43" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="55" t="n"/>
-      <c r="N43" s="55" t="n"/>
-      <c r="O43" s="55" t="n"/>
-      <c r="P43" s="55" t="n"/>
-      <c r="Q43" s="55" t="n"/>
-      <c r="R43" s="55" t="n"/>
-      <c r="S43" s="55" t="n"/>
-      <c r="T43" s="55" t="n"/>
-      <c r="U43" s="55" t="n"/>
-      <c r="V43" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W43" s="57" t="n"/>
+      <c r="M43" s="51" t="n"/>
+      <c r="N43" s="51" t="n"/>
+      <c r="O43" s="51" t="n"/>
+      <c r="P43" s="51" t="n"/>
+      <c r="Q43" s="51" t="n"/>
+      <c r="R43" s="51" t="n"/>
+      <c r="S43" s="51" t="n"/>
+      <c r="T43" s="51" t="n"/>
+      <c r="U43" s="51" t="n"/>
+      <c r="V43" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W43" s="58" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="46" t="n"/>
-      <c r="D44" s="46" t="n"/>
+      <c r="C44" s="53" t="n"/>
+      <c r="D44" s="53" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G44" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H44" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I44" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H44" s="49" t="n"/>
+      <c r="I44" s="49" t="n"/>
       <c r="J44" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K44" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="51" t="n"/>
-      <c r="N44" s="51" t="n"/>
-      <c r="O44" s="51" t="n"/>
-      <c r="P44" s="51" t="n"/>
-      <c r="Q44" s="51" t="n"/>
-      <c r="R44" s="51" t="n"/>
-      <c r="S44" s="51" t="n"/>
-      <c r="T44" s="51" t="n"/>
-      <c r="U44" s="51" t="n"/>
-      <c r="V44" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W44" s="58" t="n"/>
+      <c r="M44" s="55" t="n"/>
+      <c r="N44" s="55" t="n"/>
+      <c r="O44" s="55" t="n"/>
+      <c r="P44" s="55" t="n"/>
+      <c r="Q44" s="55" t="n"/>
+      <c r="R44" s="55" t="n"/>
+      <c r="S44" s="55" t="n"/>
+      <c r="T44" s="55" t="n"/>
+      <c r="U44" s="55" t="n"/>
+      <c r="V44" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W44" s="57" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="53" t="n"/>
-      <c r="D45" s="53" t="n"/>
+      <c r="C45" s="46" t="n"/>
+      <c r="D45" s="46" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G45" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H45" s="49" t="n"/>
-      <c r="I45" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G45" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H45" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I45" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J45" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K45" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="55" t="n"/>
-      <c r="N45" s="55" t="n"/>
-      <c r="O45" s="55" t="n"/>
-      <c r="P45" s="55" t="n"/>
-      <c r="Q45" s="55" t="n"/>
-      <c r="R45" s="55" t="n"/>
-      <c r="S45" s="55" t="n"/>
-      <c r="T45" s="55" t="n"/>
-      <c r="U45" s="55" t="n"/>
-      <c r="V45" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W45" s="57" t="n"/>
+      <c r="M45" s="51" t="n"/>
+      <c r="N45" s="51" t="n"/>
+      <c r="O45" s="51" t="n"/>
+      <c r="P45" s="51" t="n"/>
+      <c r="Q45" s="51" t="n"/>
+      <c r="R45" s="51" t="n"/>
+      <c r="S45" s="51" t="n"/>
+      <c r="T45" s="51" t="n"/>
+      <c r="U45" s="51" t="n"/>
+      <c r="V45" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W45" s="58" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="46" t="n"/>
-      <c r="D46" s="46" t="n"/>
+      <c r="C46" s="53" t="n"/>
+      <c r="D46" s="53" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G46" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G46" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H46" s="49" t="n"/>
       <c r="I46" s="49" t="n"/>
       <c r="J46" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K46" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="51" t="n"/>
-      <c r="N46" s="51" t="n"/>
-      <c r="O46" s="51" t="n"/>
-      <c r="P46" s="51" t="n"/>
-      <c r="Q46" s="51" t="n"/>
-      <c r="R46" s="51" t="n"/>
-      <c r="S46" s="51" t="n"/>
-      <c r="T46" s="51" t="n"/>
-      <c r="U46" s="51" t="n"/>
-      <c r="V46" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W46" s="58" t="n"/>
+      <c r="M46" s="55" t="n"/>
+      <c r="N46" s="55" t="n"/>
+      <c r="O46" s="55" t="n"/>
+      <c r="P46" s="55" t="n"/>
+      <c r="Q46" s="55" t="n"/>
+      <c r="R46" s="55" t="n"/>
+      <c r="S46" s="55" t="n"/>
+      <c r="T46" s="55" t="n"/>
+      <c r="U46" s="55" t="n"/>
+      <c r="V46" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W46" s="57" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="53" t="n"/>
-      <c r="D47" s="53" t="n"/>
+      <c r="C47" s="46" t="n"/>
+      <c r="D47" s="46" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G47" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G47" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H47" s="49" t="n"/>
       <c r="I47" s="49" t="n"/>
       <c r="J47" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K47" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K47" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="55" t="n"/>
-      <c r="N47" s="55" t="n"/>
-      <c r="O47" s="55" t="n"/>
-      <c r="P47" s="55" t="n"/>
-      <c r="Q47" s="55" t="n"/>
-      <c r="R47" s="55" t="n"/>
-      <c r="S47" s="55" t="n"/>
-      <c r="T47" s="55" t="n"/>
-      <c r="U47" s="55" t="n"/>
-      <c r="V47" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W47" s="57" t="n"/>
+      <c r="M47" s="51" t="n"/>
+      <c r="N47" s="51" t="n"/>
+      <c r="O47" s="51" t="n"/>
+      <c r="P47" s="51" t="n"/>
+      <c r="Q47" s="51" t="n"/>
+      <c r="R47" s="51" t="n"/>
+      <c r="S47" s="51" t="n"/>
+      <c r="T47" s="51" t="n"/>
+      <c r="U47" s="51" t="n"/>
+      <c r="V47" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W47" s="58" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
+      <c r="C48" s="53" t="n"/>
+      <c r="D48" s="53" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G48" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H48" s="49" t="n"/>
       <c r="I48" s="49" t="n"/>
       <c r="J48" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K48" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="51" t="n"/>
-      <c r="N48" s="51" t="n"/>
-      <c r="O48" s="51" t="n"/>
-      <c r="P48" s="51" t="n"/>
-      <c r="Q48" s="51" t="n"/>
-      <c r="R48" s="51" t="n"/>
-      <c r="S48" s="51" t="n"/>
-      <c r="T48" s="51" t="n"/>
-      <c r="U48" s="51" t="n"/>
-      <c r="V48" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W48" s="58" t="n"/>
+      <c r="M48" s="55" t="n"/>
+      <c r="N48" s="55" t="n"/>
+      <c r="O48" s="55" t="n"/>
+      <c r="P48" s="55" t="n"/>
+      <c r="Q48" s="55" t="n"/>
+      <c r="R48" s="55" t="n"/>
+      <c r="S48" s="55" t="n"/>
+      <c r="T48" s="55" t="n"/>
+      <c r="U48" s="55" t="n"/>
+      <c r="V48" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W48" s="57" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="53" t="n"/>
-      <c r="D49" s="53" t="n"/>
+      <c r="C49" s="46" t="n"/>
+      <c r="D49" s="46" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G49" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G49" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H49" s="49" t="n"/>
       <c r="I49" s="49" t="n"/>
       <c r="J49" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K49" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="55" t="n"/>
-      <c r="N49" s="55" t="n"/>
-      <c r="O49" s="55" t="n"/>
-      <c r="P49" s="55" t="n"/>
-      <c r="Q49" s="55" t="n"/>
-      <c r="R49" s="55" t="n"/>
-      <c r="S49" s="55" t="n"/>
-      <c r="T49" s="55" t="n"/>
-      <c r="U49" s="55" t="n"/>
-      <c r="V49" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W49" s="57" t="n"/>
+      <c r="M49" s="51" t="n"/>
+      <c r="N49" s="51" t="n"/>
+      <c r="O49" s="51" t="n"/>
+      <c r="P49" s="51" t="n"/>
+      <c r="Q49" s="51" t="n"/>
+      <c r="R49" s="51" t="n"/>
+      <c r="S49" s="51" t="n"/>
+      <c r="T49" s="51" t="n"/>
+      <c r="U49" s="51" t="n"/>
+      <c r="V49" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W49" s="58" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
+      <c r="C50" s="53" t="n"/>
+      <c r="D50" s="53" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G50" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H50" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I50" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G50" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H50" s="49" t="n"/>
+      <c r="I50" s="49" t="n"/>
       <c r="J50" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="51" t="n"/>
-      <c r="N50" s="51" t="n"/>
-      <c r="O50" s="51" t="n"/>
-      <c r="P50" s="51" t="n"/>
-      <c r="Q50" s="51" t="n"/>
-      <c r="R50" s="51" t="n"/>
-      <c r="S50" s="51" t="n"/>
-      <c r="T50" s="51" t="n"/>
-      <c r="U50" s="51" t="n"/>
-      <c r="V50" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W50" s="58" t="n"/>
+      <c r="M50" s="55" t="n"/>
+      <c r="N50" s="55" t="n"/>
+      <c r="O50" s="55" t="n"/>
+      <c r="P50" s="55" t="n"/>
+      <c r="Q50" s="55" t="n"/>
+      <c r="R50" s="55" t="n"/>
+      <c r="S50" s="55" t="n"/>
+      <c r="T50" s="55" t="n"/>
+      <c r="U50" s="55" t="n"/>
+      <c r="V50" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W50" s="57" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="53" t="n"/>
-      <c r="D51" s="53" t="n"/>
+      <c r="C51" s="46" t="n"/>
+      <c r="D51" s="46" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G51" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H51" s="49" t="n"/>
-      <c r="I51" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H51" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I51" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J51" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="55" t="n"/>
-      <c r="N51" s="55" t="n"/>
-      <c r="O51" s="55" t="n"/>
-      <c r="P51" s="55" t="n"/>
-      <c r="Q51" s="55" t="n"/>
-      <c r="R51" s="55" t="n"/>
-      <c r="S51" s="55" t="n"/>
-      <c r="T51" s="55" t="n"/>
-      <c r="U51" s="55" t="n"/>
-      <c r="V51" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W51" s="57" t="n"/>
+      <c r="M51" s="51" t="n"/>
+      <c r="N51" s="51" t="n"/>
+      <c r="O51" s="51" t="n"/>
+      <c r="P51" s="51" t="n"/>
+      <c r="Q51" s="51" t="n"/>
+      <c r="R51" s="51" t="n"/>
+      <c r="S51" s="51" t="n"/>
+      <c r="T51" s="51" t="n"/>
+      <c r="U51" s="51" t="n"/>
+      <c r="V51" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W51" s="58" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="46" t="n"/>
-      <c r="D52" s="46" t="n"/>
+      <c r="C52" s="53" t="n"/>
+      <c r="D52" s="53" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G52" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H52" s="49" t="n"/>
       <c r="I52" s="49" t="n"/>
       <c r="J52" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="51" t="n"/>
-      <c r="N52" s="51" t="n"/>
-      <c r="O52" s="51" t="n"/>
-      <c r="P52" s="51" t="n"/>
-      <c r="Q52" s="51" t="n"/>
-      <c r="R52" s="51" t="n"/>
-      <c r="S52" s="51" t="n"/>
-      <c r="T52" s="51" t="n"/>
-      <c r="U52" s="51" t="n"/>
-      <c r="V52" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W52" s="58" t="n"/>
+      <c r="M52" s="55" t="n"/>
+      <c r="N52" s="55" t="n"/>
+      <c r="O52" s="55" t="n"/>
+      <c r="P52" s="55" t="n"/>
+      <c r="Q52" s="55" t="n"/>
+      <c r="R52" s="55" t="n"/>
+      <c r="S52" s="55" t="n"/>
+      <c r="T52" s="55" t="n"/>
+      <c r="U52" s="55" t="n"/>
+      <c r="V52" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W52" s="57" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="53" t="n"/>
-      <c r="D53" s="53" t="n"/>
+      <c r="C53" s="46" t="n"/>
+      <c r="D53" s="46" t="n"/>
       <c r="E53" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F53" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G53" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H53" s="49" t="n"/>
+      <c r="I53" s="49" t="n"/>
+      <c r="J53" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F53" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G53" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H53" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I53" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J53" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K53" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="55" t="n"/>
-      <c r="N53" s="55" t="n"/>
-      <c r="O53" s="55" t="n"/>
-      <c r="P53" s="55" t="n"/>
-      <c r="Q53" s="55" t="n"/>
-      <c r="R53" s="55" t="n"/>
-      <c r="S53" s="55" t="n"/>
-      <c r="T53" s="55" t="n"/>
-      <c r="U53" s="55" t="n"/>
-      <c r="V53" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W53" s="57" t="n"/>
+      <c r="M53" s="51" t="n"/>
+      <c r="N53" s="51" t="n"/>
+      <c r="O53" s="51" t="n"/>
+      <c r="P53" s="51" t="n"/>
+      <c r="Q53" s="51" t="n"/>
+      <c r="R53" s="51" t="n"/>
+      <c r="S53" s="51" t="n"/>
+      <c r="T53" s="51" t="n"/>
+      <c r="U53" s="51" t="n"/>
+      <c r="V53" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W53" s="58" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="46" t="n"/>
-      <c r="D54" s="46" t="n"/>
+      <c r="C54" s="53" t="n"/>
+      <c r="D54" s="53" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G54" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H54" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I54" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J54" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="51" t="n"/>
-      <c r="N54" s="51" t="n"/>
-      <c r="O54" s="51" t="n"/>
-      <c r="P54" s="51" t="n"/>
-      <c r="Q54" s="51" t="n"/>
-      <c r="R54" s="51" t="n"/>
-      <c r="S54" s="51" t="n"/>
-      <c r="T54" s="51" t="n"/>
-      <c r="U54" s="51" t="n"/>
-      <c r="V54" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W54" s="58" t="n"/>
+      <c r="M54" s="55" t="n"/>
+      <c r="N54" s="55" t="n"/>
+      <c r="O54" s="55" t="n"/>
+      <c r="P54" s="55" t="n"/>
+      <c r="Q54" s="55" t="n"/>
+      <c r="R54" s="55" t="n"/>
+      <c r="S54" s="55" t="n"/>
+      <c r="T54" s="55" t="n"/>
+      <c r="U54" s="55" t="n"/>
+      <c r="V54" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W54" s="57" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="53" t="n"/>
-      <c r="D55" s="53" t="n"/>
+      <c r="C55" s="46" t="n"/>
+      <c r="D55" s="46" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G55" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H55" s="49" t="n"/>
-      <c r="I55" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H55" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I55" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J55" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="55" t="n"/>
-      <c r="N55" s="55" t="n"/>
-      <c r="O55" s="55" t="n"/>
-      <c r="P55" s="55" t="n"/>
-      <c r="Q55" s="55" t="n"/>
-      <c r="R55" s="55" t="n"/>
-      <c r="S55" s="55" t="n"/>
-      <c r="T55" s="55" t="n"/>
-      <c r="U55" s="55" t="n"/>
-      <c r="V55" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W55" s="57" t="n"/>
+      <c r="M55" s="51" t="n"/>
+      <c r="N55" s="51" t="n"/>
+      <c r="O55" s="51" t="n"/>
+      <c r="P55" s="51" t="n"/>
+      <c r="Q55" s="51" t="n"/>
+      <c r="R55" s="51" t="n"/>
+      <c r="S55" s="51" t="n"/>
+      <c r="T55" s="51" t="n"/>
+      <c r="U55" s="51" t="n"/>
+      <c r="V55" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W55" s="58" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="46" t="n"/>
-      <c r="D56" s="46" t="n"/>
+      <c r="C56" s="53" t="n"/>
+      <c r="D56" s="53" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G56" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G56" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H56" s="49" t="n"/>
       <c r="I56" s="49" t="n"/>
       <c r="J56" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K56" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="51" t="n"/>
-      <c r="N56" s="51" t="n"/>
-      <c r="O56" s="51" t="n"/>
-      <c r="P56" s="51" t="n"/>
-      <c r="Q56" s="51" t="n"/>
-      <c r="R56" s="51" t="n"/>
-      <c r="S56" s="51" t="n"/>
-      <c r="T56" s="51" t="n"/>
-      <c r="U56" s="51" t="n"/>
-      <c r="V56" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W56" s="58" t="n"/>
+      <c r="M56" s="55" t="n"/>
+      <c r="N56" s="55" t="n"/>
+      <c r="O56" s="55" t="n"/>
+      <c r="P56" s="55" t="n"/>
+      <c r="Q56" s="55" t="n"/>
+      <c r="R56" s="55" t="n"/>
+      <c r="S56" s="55" t="n"/>
+      <c r="T56" s="55" t="n"/>
+      <c r="U56" s="55" t="n"/>
+      <c r="V56" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W56" s="57" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="53" t="n"/>
-      <c r="D57" s="53" t="n"/>
+      <c r="C57" s="46" t="n"/>
+      <c r="D57" s="46" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G57" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G57" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="55" t="n"/>
-      <c r="N57" s="55" t="n"/>
-      <c r="O57" s="55" t="n"/>
-      <c r="P57" s="55" t="n"/>
-      <c r="Q57" s="55" t="n"/>
-      <c r="R57" s="55" t="n"/>
-      <c r="S57" s="55" t="n"/>
-      <c r="T57" s="55" t="n"/>
-      <c r="U57" s="55" t="n"/>
-      <c r="V57" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W57" s="57" t="n"/>
+      <c r="M57" s="51" t="n"/>
+      <c r="N57" s="51" t="n"/>
+      <c r="O57" s="51" t="n"/>
+      <c r="P57" s="51" t="n"/>
+      <c r="Q57" s="51" t="n"/>
+      <c r="R57" s="51" t="n"/>
+      <c r="S57" s="51" t="n"/>
+      <c r="T57" s="51" t="n"/>
+      <c r="U57" s="51" t="n"/>
+      <c r="V57" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W57" s="58" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="46" t="n"/>
-      <c r="D58" s="46" t="n"/>
+      <c r="C58" s="53" t="n"/>
+      <c r="D58" s="53" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G58" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="51" t="n"/>
-      <c r="N58" s="51" t="n"/>
-      <c r="O58" s="51" t="n"/>
-      <c r="P58" s="51" t="n"/>
-      <c r="Q58" s="51" t="n"/>
-      <c r="R58" s="51" t="n"/>
-      <c r="S58" s="51" t="n"/>
-      <c r="T58" s="51" t="n"/>
-      <c r="U58" s="51" t="n"/>
-      <c r="V58" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W58" s="58" t="n"/>
+      <c r="M58" s="55" t="n"/>
+      <c r="N58" s="55" t="n"/>
+      <c r="O58" s="55" t="n"/>
+      <c r="P58" s="55" t="n"/>
+      <c r="Q58" s="55" t="n"/>
+      <c r="R58" s="55" t="n"/>
+      <c r="S58" s="55" t="n"/>
+      <c r="T58" s="55" t="n"/>
+      <c r="U58" s="55" t="n"/>
+      <c r="V58" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W58" s="57" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="53" t="n"/>
-      <c r="D59" s="53" t="n"/>
+      <c r="C59" s="46" t="n"/>
+      <c r="D59" s="46" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G59" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G59" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="55" t="n"/>
-      <c r="N59" s="55" t="n"/>
-      <c r="O59" s="55" t="n"/>
-      <c r="P59" s="55" t="n"/>
-      <c r="Q59" s="55" t="n"/>
-      <c r="R59" s="55" t="n"/>
-      <c r="S59" s="55" t="n"/>
-      <c r="T59" s="55" t="n"/>
-      <c r="U59" s="55" t="n"/>
-      <c r="V59" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W59" s="57" t="n"/>
+      <c r="M59" s="51" t="n"/>
+      <c r="N59" s="51" t="n"/>
+      <c r="O59" s="51" t="n"/>
+      <c r="P59" s="51" t="n"/>
+      <c r="Q59" s="51" t="n"/>
+      <c r="R59" s="51" t="n"/>
+      <c r="S59" s="51" t="n"/>
+      <c r="T59" s="51" t="n"/>
+      <c r="U59" s="51" t="n"/>
+      <c r="V59" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W59" s="58" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
+      <c r="C60" s="53" t="n"/>
+      <c r="D60" s="53" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G60" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G60" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="51" t="n"/>
-      <c r="N60" s="51" t="n"/>
-      <c r="O60" s="51" t="n"/>
-      <c r="P60" s="51" t="n"/>
-      <c r="Q60" s="51" t="n"/>
-      <c r="R60" s="51" t="n"/>
-      <c r="S60" s="51" t="n"/>
-      <c r="T60" s="51" t="n"/>
-      <c r="U60" s="51" t="n"/>
-      <c r="V60" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W60" s="58" t="n"/>
+      <c r="M60" s="55" t="n"/>
+      <c r="N60" s="55" t="n"/>
+      <c r="O60" s="55" t="n"/>
+      <c r="P60" s="55" t="n"/>
+      <c r="Q60" s="55" t="n"/>
+      <c r="R60" s="55" t="n"/>
+      <c r="S60" s="55" t="n"/>
+      <c r="T60" s="55" t="n"/>
+      <c r="U60" s="55" t="n"/>
+      <c r="V60" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W60" s="57" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="53" t="n"/>
-      <c r="D61" s="53" t="n"/>
+      <c r="C61" s="46" t="n"/>
+      <c r="D61" s="46" t="n"/>
       <c r="E61" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F61" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G61" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G61" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
       <c r="J61" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K61" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="55" t="n"/>
-      <c r="N61" s="55" t="n"/>
-      <c r="O61" s="55" t="n"/>
-      <c r="P61" s="55" t="n"/>
-      <c r="Q61" s="55" t="n"/>
-      <c r="R61" s="55" t="n"/>
-      <c r="S61" s="55" t="n"/>
-      <c r="T61" s="55" t="n"/>
-      <c r="U61" s="55" t="n"/>
-      <c r="V61" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W61" s="57" t="n"/>
+      <c r="M61" s="51" t="n"/>
+      <c r="N61" s="51" t="n"/>
+      <c r="O61" s="51" t="n"/>
+      <c r="P61" s="51" t="n"/>
+      <c r="Q61" s="51" t="n"/>
+      <c r="R61" s="51" t="n"/>
+      <c r="S61" s="51" t="n"/>
+      <c r="T61" s="51" t="n"/>
+      <c r="U61" s="51" t="n"/>
+      <c r="V61" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W61" s="58" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B62" s="45" t="n"/>
-      <c r="C62" s="46" t="n"/>
-      <c r="D62" s="46" t="n"/>
+      <c r="C62" s="53" t="n"/>
+      <c r="D62" s="53" t="n"/>
       <c r="E62" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F62" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G62" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="49" t="n"/>
       <c r="J62" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K62" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L62" s="50" t="n"/>
-      <c r="M62" s="51" t="n"/>
-      <c r="N62" s="51" t="n"/>
-      <c r="O62" s="51" t="n"/>
-      <c r="P62" s="51" t="n"/>
-      <c r="Q62" s="51" t="n"/>
-      <c r="R62" s="51" t="n"/>
-      <c r="S62" s="51" t="n"/>
-      <c r="T62" s="51" t="n"/>
-      <c r="U62" s="51" t="n"/>
-      <c r="V62" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W62" s="58" t="n"/>
+      <c r="M62" s="55" t="n"/>
+      <c r="N62" s="55" t="n"/>
+      <c r="O62" s="55" t="n"/>
+      <c r="P62" s="55" t="n"/>
+      <c r="Q62" s="55" t="n"/>
+      <c r="R62" s="55" t="n"/>
+      <c r="S62" s="55" t="n"/>
+      <c r="T62" s="55" t="n"/>
+      <c r="U62" s="55" t="n"/>
+      <c r="V62" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W62" s="57" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B63" s="45" t="n"/>
-      <c r="C63" s="53" t="n"/>
-      <c r="D63" s="53" t="n"/>
+      <c r="C63" s="46" t="n"/>
+      <c r="D63" s="46" t="n"/>
       <c r="E63" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F63" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G63" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="49" t="n"/>
       <c r="J63" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K63" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L63" s="50" t="n"/>
-      <c r="M63" s="55" t="n"/>
-      <c r="N63" s="55" t="n"/>
-      <c r="O63" s="55" t="n"/>
-      <c r="P63" s="55" t="n"/>
-      <c r="Q63" s="55" t="n"/>
-      <c r="R63" s="55" t="n"/>
-      <c r="S63" s="55" t="n"/>
-      <c r="T63" s="55" t="n"/>
-      <c r="U63" s="55" t="n"/>
-      <c r="V63" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W63" s="57" t="n"/>
+      <c r="M63" s="51" t="n"/>
+      <c r="N63" s="51" t="n"/>
+      <c r="O63" s="51" t="n"/>
+      <c r="P63" s="51" t="n"/>
+      <c r="Q63" s="51" t="n"/>
+      <c r="R63" s="51" t="n"/>
+      <c r="S63" s="51" t="n"/>
+      <c r="T63" s="51" t="n"/>
+      <c r="U63" s="51" t="n"/>
+      <c r="V63" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W63" s="58" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B64" s="45" t="n"/>
-      <c r="C64" s="46" t="n"/>
-      <c r="D64" s="46" t="n"/>
+      <c r="C64" s="53" t="n"/>
+      <c r="D64" s="53" t="n"/>
       <c r="E64" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F64" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G64" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G64" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="49" t="n"/>
       <c r="J64" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K64" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L64" s="50" t="n"/>
-      <c r="M64" s="51" t="n"/>
-      <c r="N64" s="51" t="n"/>
-      <c r="O64" s="51" t="n"/>
-      <c r="P64" s="51" t="n"/>
-      <c r="Q64" s="51" t="n"/>
-      <c r="R64" s="51" t="n"/>
-      <c r="S64" s="51" t="n"/>
-      <c r="T64" s="51" t="n"/>
-      <c r="U64" s="51" t="n"/>
-      <c r="V64" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W64" s="58" t="n"/>
+      <c r="M64" s="55" t="n"/>
+      <c r="N64" s="55" t="n"/>
+      <c r="O64" s="55" t="n"/>
+      <c r="P64" s="55" t="n"/>
+      <c r="Q64" s="55" t="n"/>
+      <c r="R64" s="55" t="n"/>
+      <c r="S64" s="55" t="n"/>
+      <c r="T64" s="55" t="n"/>
+      <c r="U64" s="55" t="n"/>
+      <c r="V64" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W64" s="57" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B65" s="45" t="n"/>
-      <c r="C65" s="53" t="n"/>
-      <c r="D65" s="53" t="n"/>
+      <c r="C65" s="46" t="n"/>
+      <c r="D65" s="46" t="n"/>
       <c r="E65" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F65" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G65" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G65" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H65" s="49" t="n"/>
       <c r="I65" s="49" t="n"/>
       <c r="J65" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K65" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L65" s="50" t="n"/>
-      <c r="M65" s="55" t="n"/>
-      <c r="N65" s="55" t="n"/>
-      <c r="O65" s="55" t="n"/>
-      <c r="P65" s="55" t="n"/>
-      <c r="Q65" s="55" t="n"/>
-      <c r="R65" s="55" t="n"/>
-      <c r="S65" s="55" t="n"/>
-      <c r="T65" s="55" t="n"/>
-      <c r="U65" s="55" t="n"/>
-      <c r="V65" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W65" s="57" t="n"/>
+      <c r="M65" s="51" t="n"/>
+      <c r="N65" s="51" t="n"/>
+      <c r="O65" s="51" t="n"/>
+      <c r="P65" s="51" t="n"/>
+      <c r="Q65" s="51" t="n"/>
+      <c r="R65" s="51" t="n"/>
+      <c r="S65" s="51" t="n"/>
+      <c r="T65" s="51" t="n"/>
+      <c r="U65" s="51" t="n"/>
+      <c r="V65" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W65" s="58" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B66" s="45" t="n"/>
-      <c r="C66" s="46" t="n"/>
-      <c r="D66" s="46" t="n"/>
+      <c r="C66" s="53" t="n"/>
+      <c r="D66" s="53" t="n"/>
       <c r="E66" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F66" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G66" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G66" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H66" s="49" t="n"/>
       <c r="I66" s="49" t="n"/>
       <c r="J66" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K66" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L66" s="50" t="n"/>
-      <c r="M66" s="51" t="n"/>
-      <c r="N66" s="51" t="n"/>
-      <c r="O66" s="51" t="n"/>
-      <c r="P66" s="51" t="n"/>
-      <c r="Q66" s="51" t="n"/>
-      <c r="R66" s="51" t="n"/>
-      <c r="S66" s="51" t="n"/>
-      <c r="T66" s="51" t="n"/>
-      <c r="U66" s="51" t="n"/>
-      <c r="V66" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W66" s="58" t="n"/>
+      <c r="M66" s="55" t="n"/>
+      <c r="N66" s="55" t="n"/>
+      <c r="O66" s="55" t="n"/>
+      <c r="P66" s="55" t="n"/>
+      <c r="Q66" s="55" t="n"/>
+      <c r="R66" s="55" t="n"/>
+      <c r="S66" s="55" t="n"/>
+      <c r="T66" s="55" t="n"/>
+      <c r="U66" s="55" t="n"/>
+      <c r="V66" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W66" s="57" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B67" s="45" t="n"/>
-      <c r="C67" s="53" t="n"/>
-      <c r="D67" s="53" t="n"/>
+      <c r="C67" s="46" t="n"/>
+      <c r="D67" s="46" t="n"/>
       <c r="E67" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F67" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G67" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G67" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H67" s="49" t="n"/>
       <c r="I67" s="49" t="n"/>
       <c r="J67" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K67" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L67" s="50" t="n"/>
-      <c r="M67" s="55" t="n"/>
-      <c r="N67" s="55" t="n"/>
-      <c r="O67" s="55" t="n"/>
-      <c r="P67" s="55" t="n"/>
-      <c r="Q67" s="55" t="n"/>
-      <c r="R67" s="55" t="n"/>
-      <c r="S67" s="55" t="n"/>
-      <c r="T67" s="55" t="n"/>
-      <c r="U67" s="55" t="n"/>
-      <c r="V67" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W67" s="57" t="n"/>
+      <c r="M67" s="51" t="n"/>
+      <c r="N67" s="51" t="n"/>
+      <c r="O67" s="51" t="n"/>
+      <c r="P67" s="51" t="n"/>
+      <c r="Q67" s="51" t="n"/>
+      <c r="R67" s="51" t="n"/>
+      <c r="S67" s="51" t="n"/>
+      <c r="T67" s="51" t="n"/>
+      <c r="U67" s="51" t="n"/>
+      <c r="V67" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W67" s="58" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B68" s="45" t="n"/>
-      <c r="C68" s="46" t="n"/>
-      <c r="D68" s="46" t="n"/>
+      <c r="C68" s="53" t="n"/>
+      <c r="D68" s="53" t="n"/>
       <c r="E68" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F68" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G68" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G68" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H68" s="49" t="n"/>
       <c r="I68" s="49" t="n"/>
       <c r="J68" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K68" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L68" s="50" t="n"/>
-      <c r="M68" s="51" t="n"/>
-      <c r="N68" s="51" t="n"/>
-      <c r="O68" s="51" t="n"/>
-      <c r="P68" s="51" t="n"/>
-      <c r="Q68" s="51" t="n"/>
-      <c r="R68" s="51" t="n"/>
-      <c r="S68" s="51" t="n"/>
-      <c r="T68" s="51" t="n"/>
-      <c r="U68" s="51" t="n"/>
-      <c r="V68" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W68" s="58" t="n"/>
+      <c r="M68" s="55" t="n"/>
+      <c r="N68" s="55" t="n"/>
+      <c r="O68" s="55" t="n"/>
+      <c r="P68" s="55" t="n"/>
+      <c r="Q68" s="55" t="n"/>
+      <c r="R68" s="55" t="n"/>
+      <c r="S68" s="55" t="n"/>
+      <c r="T68" s="55" t="n"/>
+      <c r="U68" s="55" t="n"/>
+      <c r="V68" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W68" s="57" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B69" s="45" t="n"/>
-      <c r="C69" s="53" t="n"/>
-      <c r="D69" s="53" t="n"/>
+      <c r="C69" s="46" t="n"/>
+      <c r="D69" s="46" t="n"/>
       <c r="E69" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F69" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G69" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G69" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H69" s="49" t="n"/>
       <c r="I69" s="49" t="n"/>
       <c r="J69" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K69" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L69" s="50" t="n"/>
-      <c r="M69" s="55" t="n"/>
-      <c r="N69" s="55" t="n"/>
-      <c r="O69" s="55" t="n"/>
-      <c r="P69" s="55" t="n"/>
-      <c r="Q69" s="55" t="n"/>
-      <c r="R69" s="55" t="n"/>
-      <c r="S69" s="55" t="n"/>
-      <c r="T69" s="55" t="n"/>
-      <c r="U69" s="55" t="n"/>
-      <c r="V69" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W69" s="57" t="n"/>
+      <c r="M69" s="51" t="n"/>
+      <c r="N69" s="51" t="n"/>
+      <c r="O69" s="51" t="n"/>
+      <c r="P69" s="51" t="n"/>
+      <c r="Q69" s="51" t="n"/>
+      <c r="R69" s="51" t="n"/>
+      <c r="S69" s="51" t="n"/>
+      <c r="T69" s="51" t="n"/>
+      <c r="U69" s="51" t="n"/>
+      <c r="V69" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W69" s="58" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B70" s="45" t="n"/>
-      <c r="C70" s="46" t="n"/>
-      <c r="D70" s="46" t="n"/>
+      <c r="C70" s="53" t="n"/>
+      <c r="D70" s="53" t="n"/>
       <c r="E70" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F70" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G70" s="48" t="n">
-        <v>24</v>
+      <c r="G70" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H70" s="49" t="n"/>
       <c r="I70" s="49" t="n"/>
       <c r="J70" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K70" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L70" s="50" t="n"/>
-      <c r="M70" s="51" t="n"/>
-      <c r="N70" s="51" t="n"/>
-      <c r="O70" s="51" t="n"/>
-      <c r="P70" s="51" t="n"/>
-      <c r="Q70" s="51" t="n"/>
-      <c r="R70" s="51" t="n"/>
-      <c r="S70" s="51" t="n"/>
-      <c r="T70" s="51" t="n"/>
-      <c r="U70" s="51" t="n"/>
-      <c r="V70" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W70" s="58" t="n"/>
+      <c r="M70" s="55" t="n"/>
+      <c r="N70" s="55" t="n"/>
+      <c r="O70" s="55" t="n"/>
+      <c r="P70" s="55" t="n"/>
+      <c r="Q70" s="55" t="n"/>
+      <c r="R70" s="55" t="n"/>
+      <c r="S70" s="55" t="n"/>
+      <c r="T70" s="55" t="n"/>
+      <c r="U70" s="55" t="n"/>
+      <c r="V70" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W70" s="57" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B71" s="45" t="n"/>
-      <c r="C71" s="53" t="n"/>
-      <c r="D71" s="53" t="n"/>
+      <c r="C71" s="46" t="n"/>
+      <c r="D71" s="46" t="n"/>
       <c r="E71" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F71" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G71" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G71" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H71" s="49" t="n"/>
       <c r="I71" s="49" t="n"/>
       <c r="J71" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K71" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L71" s="50" t="n"/>
-      <c r="M71" s="55" t="n"/>
-      <c r="N71" s="55" t="n"/>
-      <c r="O71" s="55" t="n"/>
-      <c r="P71" s="55" t="n"/>
-      <c r="Q71" s="55" t="n"/>
-      <c r="R71" s="55" t="n"/>
-      <c r="S71" s="55" t="n"/>
-      <c r="T71" s="55" t="n"/>
-      <c r="U71" s="55" t="n"/>
-      <c r="V71" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W71" s="57" t="n"/>
+      <c r="M71" s="51" t="n"/>
+      <c r="N71" s="51" t="n"/>
+      <c r="O71" s="51" t="n"/>
+      <c r="P71" s="51" t="n"/>
+      <c r="Q71" s="51" t="n"/>
+      <c r="R71" s="51" t="n"/>
+      <c r="S71" s="51" t="n"/>
+      <c r="T71" s="51" t="n"/>
+      <c r="U71" s="51" t="n"/>
+      <c r="V71" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W71" s="58" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B72" s="45" t="n"/>
-      <c r="C72" s="46" t="n"/>
-      <c r="D72" s="46" t="n"/>
+      <c r="C72" s="53" t="n"/>
+      <c r="D72" s="53" t="n"/>
       <c r="E72" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F72" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G72" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G72" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H72" s="49" t="n"/>
       <c r="I72" s="49" t="n"/>
       <c r="J72" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K72" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L72" s="50" t="n"/>
-      <c r="M72" s="51" t="n"/>
-      <c r="N72" s="51" t="n"/>
-      <c r="O72" s="51" t="n"/>
-      <c r="P72" s="51" t="n"/>
-      <c r="Q72" s="51" t="n"/>
-      <c r="R72" s="51" t="n"/>
-      <c r="S72" s="51" t="n"/>
-      <c r="T72" s="51" t="n"/>
-      <c r="U72" s="51" t="n"/>
-      <c r="V72" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W72" s="58" t="n"/>
+      <c r="M72" s="55" t="n"/>
+      <c r="N72" s="55" t="n"/>
+      <c r="O72" s="55" t="n"/>
+      <c r="P72" s="55" t="n"/>
+      <c r="Q72" s="55" t="n"/>
+      <c r="R72" s="55" t="n"/>
+      <c r="S72" s="55" t="n"/>
+      <c r="T72" s="55" t="n"/>
+      <c r="U72" s="55" t="n"/>
+      <c r="V72" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W72" s="57" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B73" s="45" t="n"/>
-      <c r="C73" s="53" t="n"/>
-      <c r="D73" s="53" t="n"/>
+      <c r="C73" s="46" t="n"/>
+      <c r="D73" s="46" t="n"/>
       <c r="E73" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F73" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G73" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H73" s="49" t="n"/>
       <c r="I73" s="49" t="n"/>
@@ -5321,51 +5335,92 @@
         <v>59</v>
       </c>
       <c r="K73" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L73" s="50" t="n"/>
-      <c r="M73" s="55" t="n"/>
-      <c r="N73" s="55" t="n"/>
-      <c r="O73" s="55" t="n"/>
-      <c r="P73" s="55" t="n"/>
-      <c r="Q73" s="55" t="n"/>
-      <c r="R73" s="55" t="n"/>
-      <c r="S73" s="55" t="n"/>
-      <c r="T73" s="55" t="n"/>
-      <c r="U73" s="55" t="n"/>
-      <c r="V73" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W73" s="57" t="n"/>
+      <c r="M73" s="51" t="n"/>
+      <c r="N73" s="51" t="n"/>
+      <c r="O73" s="51" t="n"/>
+      <c r="P73" s="51" t="n"/>
+      <c r="Q73" s="51" t="n"/>
+      <c r="R73" s="51" t="n"/>
+      <c r="S73" s="51" t="n"/>
+      <c r="T73" s="51" t="n"/>
+      <c r="U73" s="51" t="n"/>
+      <c r="V73" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W73" s="58" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B74" s="45" t="n"/>
-      <c r="C74" s="46" t="n"/>
-      <c r="D74" s="46" t="n"/>
-      <c r="E74" s="47" t="n"/>
-      <c r="F74" s="47" t="n"/>
-      <c r="G74" s="60" t="n"/>
+      <c r="C74" s="53" t="n"/>
+      <c r="D74" s="53" t="n"/>
+      <c r="E74" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F74" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G74" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H74" s="49" t="n"/>
       <c r="I74" s="49" t="n"/>
-      <c r="J74" s="50" t="n"/>
-      <c r="K74" s="50" t="n"/>
+      <c r="J74" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K74" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L74" s="50" t="n"/>
-      <c r="M74" s="51" t="n"/>
-      <c r="N74" s="51" t="n"/>
-      <c r="O74" s="51" t="n"/>
-      <c r="P74" s="51" t="n"/>
-      <c r="Q74" s="51" t="n"/>
-      <c r="R74" s="51" t="n"/>
-      <c r="S74" s="51" t="n"/>
-      <c r="T74" s="51" t="n"/>
-      <c r="U74" s="51" t="n"/>
-      <c r="V74" s="61" t="n"/>
-      <c r="W74" s="61" t="n"/>
+      <c r="M74" s="55" t="n"/>
+      <c r="N74" s="55" t="n"/>
+      <c r="O74" s="55" t="n"/>
+      <c r="P74" s="55" t="n"/>
+      <c r="Q74" s="55" t="n"/>
+      <c r="R74" s="55" t="n"/>
+      <c r="S74" s="55" t="n"/>
+      <c r="T74" s="55" t="n"/>
+      <c r="U74" s="55" t="n"/>
+      <c r="V74" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W74" s="57" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B75" s="45" t="n"/>
+      <c r="C75" s="46" t="n"/>
+      <c r="D75" s="46" t="n"/>
+      <c r="E75" s="47" t="n"/>
+      <c r="F75" s="47" t="n"/>
+      <c r="G75" s="60" t="n"/>
+      <c r="H75" s="49" t="n"/>
+      <c r="I75" s="49" t="n"/>
+      <c r="J75" s="50" t="n"/>
+      <c r="K75" s="50" t="n"/>
+      <c r="L75" s="50" t="n"/>
+      <c r="M75" s="51" t="n"/>
+      <c r="N75" s="51" t="n"/>
+      <c r="O75" s="51" t="n"/>
+      <c r="P75" s="51" t="n"/>
+      <c r="Q75" s="51" t="n"/>
+      <c r="R75" s="51" t="n"/>
+      <c r="S75" s="51" t="n"/>
+      <c r="T75" s="51" t="n"/>
+      <c r="U75" s="51" t="n"/>
+      <c r="V75" s="61" t="n"/>
+      <c r="W75" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W75"/>
+  <dimension ref="A1:W76"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,44 +1982,40 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/21(二)</t>
+          <t>2026/04/22(三)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G4" s="66" t="n">
-        <v>15.9</v>
+        <v>55</v>
+      </c>
+      <c r="G4" s="71" t="n">
+        <v>27.6</v>
       </c>
       <c r="H4" s="67" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I4" s="67" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J4" s="68" t="n">
         <v>8</v>
       </c>
       <c r="K4" s="68" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L4" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" s="69" t="inlineStr">
-        <is>
-          <t>金 螳 螂、金富科技、圣龙股份</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M4" s="69" t="inlineStr"/>
       <c r="N4" s="69" t="inlineStr">
         <is>
-          <t>株冶集团</t>
+          <t>金 螳 螂、金富科技</t>
         </is>
       </c>
       <c r="O4" s="69" t="inlineStr"/>
@@ -2030,55 +2026,55 @@
       <c r="T4" s="69" t="inlineStr"/>
       <c r="U4" s="69" t="inlineStr"/>
       <c r="V4" s="69" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="W4" s="69" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/20(一)</t>
+          <t>2026/04/21(二)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
       <c r="C5" s="64" t="inlineStr"/>
       <c r="D5" s="64" t="inlineStr"/>
       <c r="E5" s="65" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="G5" s="66" t="n">
-        <v>16.7</v>
+        <v>15.9</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I5" s="67" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J5" s="68" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K5" s="68" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="L5" s="68" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M5" s="69" t="inlineStr">
         <is>
-          <t>株冶集团、华升股份、可川科技</t>
-        </is>
-      </c>
-      <c r="N5" s="69" t="inlineStr"/>
+          <t>金 螳 螂、金富科技、圣龙股份</t>
+        </is>
+      </c>
+      <c r="N5" s="69" t="inlineStr">
+        <is>
+          <t>株冶集团</t>
+        </is>
+      </c>
       <c r="O5" s="69" t="inlineStr"/>
-      <c r="P5" s="69" t="inlineStr">
-        <is>
-          <t>博云新材</t>
-        </is>
-      </c>
+      <c r="P5" s="69" t="inlineStr"/>
       <c r="Q5" s="69" t="inlineStr"/>
       <c r="R5" s="69" t="inlineStr"/>
       <c r="S5" s="69" t="inlineStr"/>
@@ -2092,57 +2088,49 @@
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/04/17(五)</t>
+          <t>2026/04/20(一)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
       <c r="C6" s="64" t="inlineStr"/>
       <c r="D6" s="64" t="inlineStr"/>
       <c r="E6" s="65" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G6" s="66" t="n">
-        <v>22</v>
+        <v>16.7</v>
       </c>
       <c r="H6" s="67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I6" s="67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J6" s="68" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K6" s="68" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L6" s="68" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M6" s="69" t="inlineStr">
         <is>
-          <t>均瑶健康、京投发展</t>
-        </is>
-      </c>
-      <c r="N6" s="69" t="inlineStr">
-        <is>
-          <t>盛视科技</t>
-        </is>
-      </c>
-      <c r="O6" s="69" t="inlineStr">
+          <t>株冶集团、华升股份、可川科技</t>
+        </is>
+      </c>
+      <c r="N6" s="69" t="inlineStr"/>
+      <c r="O6" s="69" t="inlineStr"/>
+      <c r="P6" s="69" t="inlineStr">
         <is>
           <t>博云新材</t>
         </is>
       </c>
-      <c r="P6" s="69" t="inlineStr"/>
-      <c r="Q6" s="69" t="inlineStr">
-        <is>
-          <t>圣阳股份</t>
-        </is>
-      </c>
+      <c r="Q6" s="69" t="inlineStr"/>
       <c r="R6" s="69" t="inlineStr"/>
       <c r="S6" s="69" t="inlineStr"/>
       <c r="T6" s="69" t="inlineStr"/>
@@ -2155,193 +2143,197 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="62" t="inlineStr">
         <is>
-          <t>2026/04/16(四)</t>
+          <t>2026/04/17(五)</t>
         </is>
       </c>
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="64" t="inlineStr"/>
       <c r="D7" s="64" t="inlineStr"/>
       <c r="E7" s="65" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F7" s="65" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G7" s="66" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" s="67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" s="68" t="n">
+        <v>13</v>
+      </c>
+      <c r="K7" s="68" t="n">
+        <v>58</v>
+      </c>
+      <c r="L7" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="K7" s="68" t="n">
-        <v>71</v>
-      </c>
-      <c r="L7" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="M7" s="69" t="inlineStr">
         <is>
+          <t>均瑶健康、京投发展</t>
+        </is>
+      </c>
+      <c r="N7" s="69" t="inlineStr">
+        <is>
           <t>盛视科技</t>
         </is>
       </c>
-      <c r="N7" s="69" t="inlineStr">
+      <c r="O7" s="69" t="inlineStr">
         <is>
           <t>博云新材</t>
         </is>
       </c>
-      <c r="O7" s="69" t="inlineStr"/>
-      <c r="P7" s="69" t="inlineStr">
+      <c r="P7" s="69" t="inlineStr"/>
+      <c r="Q7" s="69" t="inlineStr">
         <is>
           <t>圣阳股份</t>
         </is>
       </c>
-      <c r="Q7" s="69" t="inlineStr"/>
       <c r="R7" s="69" t="inlineStr"/>
       <c r="S7" s="69" t="inlineStr"/>
       <c r="T7" s="69" t="inlineStr"/>
       <c r="U7" s="69" t="inlineStr"/>
       <c r="V7" s="69" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="W7" s="69" t="inlineStr"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="62" t="inlineStr">
         <is>
-          <t>2026/04/15(三)</t>
+          <t>2026/04/16(四)</t>
         </is>
       </c>
       <c r="B8" s="63" t="inlineStr"/>
       <c r="C8" s="64" t="inlineStr"/>
       <c r="D8" s="64" t="inlineStr"/>
       <c r="E8" s="65" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="F8" s="65" t="n">
-        <v>57</v>
-      </c>
-      <c r="G8" s="71" t="n">
-        <v>29.6</v>
+        <v>79</v>
+      </c>
+      <c r="G8" s="66" t="n">
+        <v>22.5</v>
       </c>
       <c r="H8" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I8" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" s="68" t="n">
-        <v>11</v>
-      </c>
       <c r="K8" s="68" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="L8" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M8" s="69" t="inlineStr">
         <is>
-          <t>博云新材、天邦食品</t>
-        </is>
-      </c>
-      <c r="N8" s="69" t="inlineStr"/>
-      <c r="O8" s="69" t="inlineStr">
+          <t>盛视科技</t>
+        </is>
+      </c>
+      <c r="N8" s="69" t="inlineStr">
+        <is>
+          <t>博云新材</t>
+        </is>
+      </c>
+      <c r="O8" s="69" t="inlineStr"/>
+      <c r="P8" s="69" t="inlineStr">
         <is>
           <t>圣阳股份</t>
         </is>
       </c>
-      <c r="P8" s="69" t="inlineStr"/>
       <c r="Q8" s="69" t="inlineStr"/>
       <c r="R8" s="69" t="inlineStr"/>
       <c r="S8" s="69" t="inlineStr"/>
       <c r="T8" s="69" t="inlineStr"/>
       <c r="U8" s="69" t="inlineStr"/>
       <c r="V8" s="69" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="W8" s="69" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="62" t="inlineStr">
         <is>
-          <t>2026/04/14(二)</t>
+          <t>2026/04/15(三)</t>
         </is>
       </c>
       <c r="B9" s="63" t="inlineStr"/>
       <c r="C9" s="64" t="inlineStr"/>
       <c r="D9" s="64" t="inlineStr"/>
       <c r="E9" s="65" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F9" s="65" t="n">
-        <v>55</v>
-      </c>
-      <c r="G9" s="66" t="n">
-        <v>24.7</v>
+        <v>57</v>
+      </c>
+      <c r="G9" s="71" t="n">
+        <v>29.6</v>
       </c>
       <c r="H9" s="67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I9" s="67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J9" s="68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K9" s="68" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L9" s="68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M9" s="69" t="inlineStr">
         <is>
-          <t>美能能源</t>
-        </is>
-      </c>
-      <c r="N9" s="69" t="inlineStr">
-        <is>
-          <t>中恒电气、圣阳股份</t>
-        </is>
-      </c>
-      <c r="O9" s="69" t="inlineStr"/>
-      <c r="P9" s="69" t="inlineStr">
-        <is>
-          <t>华远控股</t>
-        </is>
-      </c>
+          <t>博云新材、天邦食品</t>
+        </is>
+      </c>
+      <c r="N9" s="69" t="inlineStr"/>
+      <c r="O9" s="69" t="inlineStr">
+        <is>
+          <t>圣阳股份</t>
+        </is>
+      </c>
+      <c r="P9" s="69" t="inlineStr"/>
       <c r="Q9" s="69" t="inlineStr"/>
       <c r="R9" s="69" t="inlineStr"/>
       <c r="S9" s="69" t="inlineStr"/>
       <c r="T9" s="69" t="inlineStr"/>
       <c r="U9" s="69" t="inlineStr"/>
       <c r="V9" s="69" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="W9" s="69" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="62" t="inlineStr">
         <is>
-          <t>2026/04/13(一)</t>
+          <t>2026/04/14(二)</t>
         </is>
       </c>
       <c r="B10" s="63" t="inlineStr"/>
       <c r="C10" s="64" t="inlineStr"/>
       <c r="D10" s="64" t="inlineStr"/>
       <c r="E10" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F10" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G10" s="66" t="n">
-        <v>20.3</v>
+        <v>24.7</v>
       </c>
       <c r="H10" s="67" t="n">
         <v>4</v>
@@ -2350,30 +2342,30 @@
         <v>4</v>
       </c>
       <c r="J10" s="68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K10" s="68" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L10" s="68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M10" s="69" t="inlineStr">
         <is>
+          <t>美能能源</t>
+        </is>
+      </c>
+      <c r="N10" s="69" t="inlineStr">
+        <is>
           <t>中恒电气、圣阳股份</t>
         </is>
       </c>
-      <c r="N10" s="69" t="inlineStr">
-        <is>
-          <t>长源东谷</t>
-        </is>
-      </c>
-      <c r="O10" s="69" t="inlineStr">
+      <c r="O10" s="69" t="inlineStr"/>
+      <c r="P10" s="69" t="inlineStr">
         <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="P10" s="69" t="inlineStr"/>
       <c r="Q10" s="69" t="inlineStr"/>
       <c r="R10" s="69" t="inlineStr"/>
       <c r="S10" s="69" t="inlineStr"/>
@@ -2387,7 +2379,7 @@
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="62" t="inlineStr">
         <is>
-          <t>2026/04/10(五)</t>
+          <t>2026/04/13(一)</t>
         </is>
       </c>
       <c r="B11" s="63" t="inlineStr"/>
@@ -2399,35 +2391,39 @@
       <c r="F11" s="65" t="n">
         <v>59</v>
       </c>
-      <c r="G11" s="71" t="n">
-        <v>31.4</v>
+      <c r="G11" s="66" t="n">
+        <v>20.3</v>
       </c>
       <c r="H11" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I11" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" s="68" t="n">
-        <v>13</v>
-      </c>
       <c r="K11" s="68" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L11" s="68" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M11" s="69" t="inlineStr">
         <is>
-          <t>中嘉博创、长源东谷、来伊份</t>
+          <t>中恒电气、圣阳股份</t>
         </is>
       </c>
       <c r="N11" s="69" t="inlineStr">
         <is>
+          <t>长源东谷</t>
+        </is>
+      </c>
+      <c r="O11" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="O11" s="69" t="inlineStr"/>
       <c r="P11" s="69" t="inlineStr"/>
       <c r="Q11" s="69" t="inlineStr"/>
       <c r="R11" s="69" t="inlineStr"/>
@@ -2435,54 +2431,54 @@
       <c r="T11" s="69" t="inlineStr"/>
       <c r="U11" s="69" t="inlineStr"/>
       <c r="V11" s="69" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="W11" s="69" t="inlineStr"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="62" t="inlineStr">
         <is>
-          <t>2026/04/09(四)</t>
+          <t>2026/04/10(五)</t>
         </is>
       </c>
       <c r="B12" s="63" t="inlineStr"/>
       <c r="C12" s="64" t="inlineStr"/>
       <c r="D12" s="64" t="inlineStr"/>
       <c r="E12" s="65" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F12" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G12" s="66" t="n">
-        <v>23.2</v>
+        <v>59</v>
+      </c>
+      <c r="G12" s="71" t="n">
+        <v>31.4</v>
       </c>
       <c r="H12" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I12" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J12" s="68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K12" s="68" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L12" s="68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M12" s="69" t="inlineStr">
         <is>
+          <t>中嘉博创、长源东谷、来伊份</t>
+        </is>
+      </c>
+      <c r="N12" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="N12" s="69" t="inlineStr"/>
-      <c r="O12" s="69" t="inlineStr">
-        <is>
-          <t>汇源通信</t>
-        </is>
-      </c>
+      <c r="O12" s="69" t="inlineStr"/>
       <c r="P12" s="69" t="inlineStr"/>
       <c r="Q12" s="69" t="inlineStr"/>
       <c r="R12" s="69" t="inlineStr"/>
@@ -2490,54 +2486,54 @@
       <c r="T12" s="69" t="inlineStr"/>
       <c r="U12" s="69" t="inlineStr"/>
       <c r="V12" s="69" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="W12" s="69" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="62" t="inlineStr">
         <is>
-          <t>2026/04/08(三)</t>
+          <t>2026/04/09(四)</t>
         </is>
       </c>
       <c r="B13" s="63" t="inlineStr"/>
       <c r="C13" s="64" t="inlineStr"/>
       <c r="D13" s="64" t="inlineStr"/>
       <c r="E13" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="F13" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="G13" s="66" t="n">
-        <v>11.5</v>
+        <v>23.2</v>
       </c>
       <c r="H13" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I13" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J13" s="68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K13" s="68" t="n">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="L13" s="68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M13" s="69" t="inlineStr">
         <is>
-          <t>中安科</t>
-        </is>
-      </c>
-      <c r="N13" s="69" t="inlineStr">
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="N13" s="69" t="inlineStr"/>
+      <c r="O13" s="69" t="inlineStr">
         <is>
           <t>汇源通信</t>
         </is>
       </c>
-      <c r="O13" s="69" t="inlineStr"/>
       <c r="P13" s="69" t="inlineStr"/>
       <c r="Q13" s="69" t="inlineStr"/>
       <c r="R13" s="69" t="inlineStr"/>
@@ -2552,20 +2548,20 @@
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="62" t="inlineStr">
         <is>
-          <t>2026/04/07(二)</t>
+          <t>2026/04/08(三)</t>
         </is>
       </c>
       <c r="B14" s="63" t="inlineStr"/>
       <c r="C14" s="64" t="inlineStr"/>
       <c r="D14" s="64" t="inlineStr"/>
       <c r="E14" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F14" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G14" s="66" t="n">
-        <v>21.8</v>
+        <v>11.5</v>
       </c>
       <c r="H14" s="67" t="n">
         <v>4</v>
@@ -2574,91 +2570,95 @@
         <v>4</v>
       </c>
       <c r="J14" s="68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K14" s="68" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="L14" s="68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M14" s="69" t="inlineStr">
         <is>
-          <t>汇源通信、新能泰山</t>
-        </is>
-      </c>
-      <c r="N14" s="69" t="inlineStr"/>
+          <t>中安科</t>
+        </is>
+      </c>
+      <c r="N14" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信</t>
+        </is>
+      </c>
       <c r="O14" s="69" t="inlineStr"/>
       <c r="P14" s="69" t="inlineStr"/>
-      <c r="Q14" s="69" t="inlineStr">
-        <is>
-          <t>津药药业</t>
-        </is>
-      </c>
+      <c r="Q14" s="69" t="inlineStr"/>
       <c r="R14" s="69" t="inlineStr"/>
       <c r="S14" s="69" t="inlineStr"/>
       <c r="T14" s="69" t="inlineStr"/>
       <c r="U14" s="69" t="inlineStr"/>
       <c r="V14" s="69" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W14" s="69" t="inlineStr"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="62" t="inlineStr">
         <is>
-          <t>2026/04/06(一)</t>
+          <t>2026/04/07(二)</t>
         </is>
       </c>
       <c r="B15" s="63" t="inlineStr"/>
       <c r="C15" s="64" t="inlineStr"/>
       <c r="D15" s="64" t="inlineStr"/>
       <c r="E15" s="65" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F15" s="65" t="n">
-        <v>36</v>
-      </c>
-      <c r="G15" s="71" t="n">
-        <v>25</v>
+        <v>93</v>
+      </c>
+      <c r="G15" s="66" t="n">
+        <v>21.8</v>
       </c>
       <c r="H15" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I15" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J15" s="68" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="L15" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K15" s="68" t="n">
-        <v>32</v>
-      </c>
-      <c r="L15" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="M15" s="69" t="inlineStr"/>
+      <c r="M15" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信、新能泰山</t>
+        </is>
+      </c>
       <c r="N15" s="69" t="inlineStr"/>
       <c r="O15" s="69" t="inlineStr"/>
-      <c r="P15" s="69" t="inlineStr">
+      <c r="P15" s="69" t="inlineStr"/>
+      <c r="Q15" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="Q15" s="69" t="inlineStr"/>
       <c r="R15" s="69" t="inlineStr"/>
       <c r="S15" s="69" t="inlineStr"/>
       <c r="T15" s="69" t="inlineStr"/>
       <c r="U15" s="69" t="inlineStr"/>
       <c r="V15" s="69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W15" s="69" t="inlineStr"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="62" t="inlineStr">
         <is>
-          <t>2026/04/03(五)</t>
+          <t>2026/04/06(一)</t>
         </is>
       </c>
       <c r="B16" s="63" t="inlineStr"/>
@@ -2702,105 +2702,105 @@
       <c r="T16" s="69" t="inlineStr"/>
       <c r="U16" s="69" t="inlineStr"/>
       <c r="V16" s="69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W16" s="69" t="inlineStr"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B17" s="63" t="inlineStr"/>
       <c r="C17" s="64" t="inlineStr"/>
       <c r="D17" s="64" t="inlineStr"/>
       <c r="E17" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F17" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G17" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H17" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I17" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J17" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K17" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L17" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M17" s="69" t="inlineStr"/>
       <c r="N17" s="69" t="inlineStr"/>
-      <c r="O17" s="69" t="inlineStr">
+      <c r="O17" s="69" t="inlineStr"/>
+      <c r="P17" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P17" s="69" t="inlineStr"/>
       <c r="Q17" s="69" t="inlineStr"/>
       <c r="R17" s="69" t="inlineStr"/>
       <c r="S17" s="69" t="inlineStr"/>
       <c r="T17" s="69" t="inlineStr"/>
       <c r="U17" s="69" t="inlineStr"/>
       <c r="V17" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W17" s="69" t="inlineStr"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B18" s="63" t="inlineStr"/>
       <c r="C18" s="64" t="inlineStr"/>
       <c r="D18" s="64" t="inlineStr"/>
       <c r="E18" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F18" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G18" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G18" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H18" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I18" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J18" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K18" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L18" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M18" s="69" t="inlineStr"/>
-      <c r="N18" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M18" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N18" s="69" t="inlineStr"/>
+      <c r="O18" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O18" s="69" t="inlineStr"/>
       <c r="P18" s="69" t="inlineStr"/>
       <c r="Q18" s="69" t="inlineStr"/>
       <c r="R18" s="69" t="inlineStr"/>
@@ -2808,51 +2808,47 @@
       <c r="T18" s="69" t="inlineStr"/>
       <c r="U18" s="69" t="inlineStr"/>
       <c r="V18" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W18" s="69" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B19" s="63" t="inlineStr"/>
       <c r="C19" s="64" t="inlineStr"/>
       <c r="D19" s="64" t="inlineStr"/>
       <c r="E19" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F19" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G19" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G19" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H19" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I19" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J19" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K19" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L19" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M19" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M19" s="69" t="inlineStr"/>
+      <c r="N19" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N19" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O19" s="69" t="inlineStr"/>
@@ -2863,254 +2859,250 @@
       <c r="T19" s="69" t="inlineStr"/>
       <c r="U19" s="69" t="inlineStr"/>
       <c r="V19" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W19" s="69" t="inlineStr"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B20" s="63" t="inlineStr"/>
+      <c r="C20" s="64" t="inlineStr"/>
+      <c r="D20" s="64" t="inlineStr"/>
+      <c r="E20" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F20" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G20" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H20" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K20" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L20" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N20" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O20" s="69" t="inlineStr"/>
+      <c r="P20" s="69" t="inlineStr"/>
+      <c r="Q20" s="69" t="inlineStr"/>
+      <c r="R20" s="69" t="inlineStr"/>
+      <c r="S20" s="69" t="inlineStr"/>
+      <c r="T20" s="69" t="inlineStr"/>
+      <c r="U20" s="69" t="inlineStr"/>
+      <c r="V20" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W19" s="69" t="inlineStr"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="36" t="inlineStr">
+      <c r="W20" s="69" t="inlineStr"/>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C20" s="38" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D20" s="38" t="inlineStr">
+      <c r="D21" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E20" s="39" t="n">
+      <c r="E21" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F20" s="39" t="n">
+      <c r="F21" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G20" s="40" t="n">
+      <c r="G21" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H20" s="41" t="n">
+      <c r="H21" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I20" s="41" t="n">
+      <c r="I21" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J20" s="42" t="n">
+      <c r="J21" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K20" s="42" t="n">
+      <c r="K21" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L20" s="42" t="n">
+      <c r="L21" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M20" s="43" t="inlineStr">
+      <c r="M21" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N20" s="43" t="inlineStr"/>
-      <c r="O20" s="43" t="inlineStr">
+      <c r="N21" s="43" t="inlineStr"/>
+      <c r="O21" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P20" s="43" t="inlineStr"/>
-      <c r="Q20" s="43" t="inlineStr"/>
-      <c r="R20" s="43" t="inlineStr"/>
-      <c r="S20" s="43" t="inlineStr"/>
-      <c r="T20" s="43" t="inlineStr"/>
-      <c r="U20" s="43" t="inlineStr"/>
-      <c r="V20" s="43" t="n">
+      <c r="P21" s="43" t="inlineStr"/>
+      <c r="Q21" s="43" t="inlineStr"/>
+      <c r="R21" s="43" t="inlineStr"/>
+      <c r="S21" s="43" t="inlineStr"/>
+      <c r="T21" s="43" t="inlineStr"/>
+      <c r="U21" s="43" t="inlineStr"/>
+      <c r="V21" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W20" s="43" t="inlineStr"/>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B21" s="45" t="n"/>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="46" t="n"/>
-      <c r="E21" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F21" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G21" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H21" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K21" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L21" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M21" s="51" t="n"/>
-      <c r="N21" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O21" s="51" t="n"/>
-      <c r="P21" s="51" t="n"/>
-      <c r="Q21" s="51" t="n"/>
-      <c r="R21" s="51" t="n"/>
-      <c r="S21" s="51" t="n"/>
-      <c r="T21" s="51" t="n"/>
-      <c r="U21" s="51" t="n"/>
-      <c r="V21" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W21" s="43" t="inlineStr"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B22" s="45" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="53" t="n"/>
+      <c r="C22" s="46" t="n"/>
+      <c r="D22" s="46" t="n"/>
       <c r="E22" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F22" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G22" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G22" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H22" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I22" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J22" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K22" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L22" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M22" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N22" s="55" t="n"/>
-      <c r="O22" s="55" t="n"/>
-      <c r="P22" s="55" t="n"/>
-      <c r="Q22" s="55" t="n"/>
-      <c r="R22" s="55" t="n"/>
-      <c r="S22" s="55" t="n"/>
-      <c r="T22" s="55" t="n"/>
-      <c r="U22" s="55" t="n"/>
-      <c r="V22" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W22" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M22" s="51" t="n"/>
+      <c r="N22" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O22" s="51" t="n"/>
+      <c r="P22" s="51" t="n"/>
+      <c r="Q22" s="51" t="n"/>
+      <c r="R22" s="51" t="n"/>
+      <c r="S22" s="51" t="n"/>
+      <c r="T22" s="51" t="n"/>
+      <c r="U22" s="51" t="n"/>
+      <c r="V22" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="46" t="n"/>
-      <c r="D23" s="46" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G23" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G23" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H23" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L23" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M23" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N23" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O23" s="51" t="n"/>
-      <c r="P23" s="51" t="n"/>
-      <c r="Q23" s="51" t="n"/>
-      <c r="R23" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S23" s="51" t="n"/>
-      <c r="T23" s="51" t="n"/>
-      <c r="U23" s="51" t="n"/>
-      <c r="V23" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W23" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M23" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N23" s="55" t="n"/>
+      <c r="O23" s="55" t="n"/>
+      <c r="P23" s="55" t="n"/>
+      <c r="Q23" s="55" t="n"/>
+      <c r="R23" s="55" t="n"/>
+      <c r="S23" s="55" t="n"/>
+      <c r="T23" s="55" t="n"/>
+      <c r="U23" s="55" t="n"/>
+      <c r="V23" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W23" s="57" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="53" t="n"/>
-      <c r="D24" s="53" t="n"/>
+      <c r="C24" s="46" t="n"/>
+      <c r="D24" s="46" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G24" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H24" s="49" t="n">
         <v>1</v>
@@ -3119,493 +3111,497 @@
         <v>1</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L24" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M24" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M24" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N24" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N24" s="55" t="n"/>
-      <c r="O24" s="55" t="n"/>
-      <c r="P24" s="55" t="n"/>
-      <c r="Q24" s="55" t="inlineStr">
+      <c r="O24" s="51" t="n"/>
+      <c r="P24" s="51" t="n"/>
+      <c r="Q24" s="51" t="n"/>
+      <c r="R24" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R24" s="55" t="n"/>
-      <c r="S24" s="55" t="n"/>
-      <c r="T24" s="55" t="n"/>
-      <c r="U24" s="55" t="n"/>
-      <c r="V24" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W24" s="57" t="n"/>
+      <c r="S24" s="51" t="n"/>
+      <c r="T24" s="51" t="n"/>
+      <c r="U24" s="51" t="n"/>
+      <c r="V24" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W24" s="58" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="46" t="n"/>
-      <c r="D25" s="46" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G25" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G25" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H25" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L25" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N25" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O25" s="51" t="n"/>
-      <c r="P25" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M25" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N25" s="55" t="n"/>
+      <c r="O25" s="55" t="n"/>
+      <c r="P25" s="55" t="n"/>
+      <c r="Q25" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q25" s="51" t="n"/>
-      <c r="R25" s="51" t="n"/>
-      <c r="S25" s="51" t="n"/>
-      <c r="T25" s="51" t="n"/>
-      <c r="U25" s="51" t="n"/>
-      <c r="V25" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W25" s="58" t="n"/>
+      <c r="R25" s="55" t="n"/>
+      <c r="S25" s="55" t="n"/>
+      <c r="T25" s="55" t="n"/>
+      <c r="U25" s="55" t="n"/>
+      <c r="V25" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W25" s="57" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="53" t="n"/>
-      <c r="D26" s="53" t="n"/>
+      <c r="C26" s="46" t="n"/>
+      <c r="D26" s="46" t="n"/>
       <c r="E26" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F26" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G26" s="59" t="n">
-        <v>45.1</v>
+      <c r="G26" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H26" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I26" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L26" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M26" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N26" s="55" t="n"/>
-      <c r="O26" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P26" s="55" t="n"/>
-      <c r="Q26" s="55" t="n"/>
-      <c r="R26" s="55" t="n"/>
-      <c r="S26" s="55" t="n"/>
-      <c r="T26" s="55" t="n"/>
-      <c r="U26" s="55" t="n"/>
-      <c r="V26" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W26" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M26" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N26" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O26" s="51" t="n"/>
+      <c r="P26" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q26" s="51" t="n"/>
+      <c r="R26" s="51" t="n"/>
+      <c r="S26" s="51" t="n"/>
+      <c r="T26" s="51" t="n"/>
+      <c r="U26" s="51" t="n"/>
+      <c r="V26" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W26" s="58" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="46" t="n"/>
-      <c r="D27" s="46" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
       <c r="E27" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F27" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G27" s="54" t="n">
-        <v>26.3</v>
+      <c r="G27" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H27" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I27" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L27" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M27" s="51" t="n"/>
-      <c r="N27" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M27" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N27" s="55" t="n"/>
+      <c r="O27" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O27" s="51" t="n"/>
-      <c r="P27" s="51" t="n"/>
-      <c r="Q27" s="51" t="n"/>
-      <c r="R27" s="51" t="n"/>
-      <c r="S27" s="51" t="n"/>
-      <c r="T27" s="51" t="n"/>
-      <c r="U27" s="51" t="n"/>
-      <c r="V27" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W27" s="58" t="n"/>
+      <c r="P27" s="55" t="n"/>
+      <c r="Q27" s="55" t="n"/>
+      <c r="R27" s="55" t="n"/>
+      <c r="S27" s="55" t="n"/>
+      <c r="T27" s="55" t="n"/>
+      <c r="U27" s="55" t="n"/>
+      <c r="V27" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W27" s="57" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="53" t="n"/>
-      <c r="D28" s="53" t="n"/>
+      <c r="C28" s="46" t="n"/>
+      <c r="D28" s="46" t="n"/>
       <c r="E28" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F28" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G28" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H28" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I28" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L28" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M28" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M28" s="51" t="n"/>
+      <c r="N28" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N28" s="55" t="n"/>
-      <c r="O28" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P28" s="55" t="n"/>
-      <c r="Q28" s="55" t="n"/>
-      <c r="R28" s="55" t="n"/>
-      <c r="S28" s="55" t="n"/>
-      <c r="T28" s="55" t="n"/>
-      <c r="U28" s="55" t="n"/>
-      <c r="V28" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W28" s="57" t="n"/>
+      <c r="O28" s="51" t="n"/>
+      <c r="P28" s="51" t="n"/>
+      <c r="Q28" s="51" t="n"/>
+      <c r="R28" s="51" t="n"/>
+      <c r="S28" s="51" t="n"/>
+      <c r="T28" s="51" t="n"/>
+      <c r="U28" s="51" t="n"/>
+      <c r="V28" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W28" s="58" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="46" t="n"/>
-      <c r="D29" s="46" t="n"/>
+      <c r="C29" s="53" t="n"/>
+      <c r="D29" s="53" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G29" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H29" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I29" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J29" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L29" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M29" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N29" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O29" s="51" t="n"/>
-      <c r="P29" s="51" t="n"/>
-      <c r="Q29" s="51" t="n"/>
-      <c r="R29" s="51" t="n"/>
-      <c r="S29" s="51" t="n"/>
-      <c r="T29" s="51" t="n"/>
-      <c r="U29" s="51" t="n"/>
-      <c r="V29" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W29" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M29" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N29" s="55" t="n"/>
+      <c r="O29" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P29" s="55" t="n"/>
+      <c r="Q29" s="55" t="n"/>
+      <c r="R29" s="55" t="n"/>
+      <c r="S29" s="55" t="n"/>
+      <c r="T29" s="55" t="n"/>
+      <c r="U29" s="55" t="n"/>
+      <c r="V29" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W29" s="57" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="53" t="n"/>
-      <c r="D30" s="53" t="n"/>
+      <c r="C30" s="46" t="n"/>
+      <c r="D30" s="46" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G30" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H30" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J30" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K30" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L30" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I30" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K30" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L30" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M30" s="55" t="inlineStr">
+      <c r="M30" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N30" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N30" s="55" t="n"/>
-      <c r="O30" s="55" t="n"/>
-      <c r="P30" s="55" t="n"/>
-      <c r="Q30" s="55" t="n"/>
-      <c r="R30" s="55" t="n"/>
-      <c r="S30" s="55" t="n"/>
-      <c r="T30" s="55" t="n"/>
-      <c r="U30" s="55" t="n"/>
-      <c r="V30" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W30" s="57" t="n"/>
+      <c r="O30" s="51" t="n"/>
+      <c r="P30" s="51" t="n"/>
+      <c r="Q30" s="51" t="n"/>
+      <c r="R30" s="51" t="n"/>
+      <c r="S30" s="51" t="n"/>
+      <c r="T30" s="51" t="n"/>
+      <c r="U30" s="51" t="n"/>
+      <c r="V30" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W30" s="58" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="46" t="n"/>
-      <c r="D31" s="46" t="n"/>
+      <c r="C31" s="53" t="n"/>
+      <c r="D31" s="53" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G31" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G31" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H31" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I31" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J31" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K31" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L31" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M31" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N31" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O31" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P31" s="51" t="n"/>
-      <c r="Q31" s="51" t="n"/>
-      <c r="R31" s="51" t="n"/>
-      <c r="S31" s="51" t="n"/>
-      <c r="T31" s="51" t="n"/>
-      <c r="U31" s="51" t="n"/>
-      <c r="V31" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W31" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M31" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N31" s="55" t="n"/>
+      <c r="O31" s="55" t="n"/>
+      <c r="P31" s="55" t="n"/>
+      <c r="Q31" s="55" t="n"/>
+      <c r="R31" s="55" t="n"/>
+      <c r="S31" s="55" t="n"/>
+      <c r="T31" s="55" t="n"/>
+      <c r="U31" s="55" t="n"/>
+      <c r="V31" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W31" s="57" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="53" t="n"/>
-      <c r="D32" s="53" t="n"/>
+      <c r="C32" s="46" t="n"/>
+      <c r="D32" s="46" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G32" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G32" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H32" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I32" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J32" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L32" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M32" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N32" s="55" t="inlineStr">
+      <c r="M32" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N32" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O32" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O32" s="55" t="n"/>
-      <c r="P32" s="55" t="n"/>
-      <c r="Q32" s="55" t="n"/>
-      <c r="R32" s="55" t="n"/>
-      <c r="S32" s="55" t="n"/>
-      <c r="T32" s="55" t="n"/>
-      <c r="U32" s="55" t="n"/>
-      <c r="V32" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W32" s="57" t="n"/>
+      <c r="P32" s="51" t="n"/>
+      <c r="Q32" s="51" t="n"/>
+      <c r="R32" s="51" t="n"/>
+      <c r="S32" s="51" t="n"/>
+      <c r="T32" s="51" t="n"/>
+      <c r="U32" s="51" t="n"/>
+      <c r="V32" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W32" s="58" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="46" t="n"/>
-      <c r="D33" s="46" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G33" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H33" s="49" t="n">
         <v>2</v>
@@ -3614,208 +3610,218 @@
         <v>2</v>
       </c>
       <c r="J33" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K33" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L33" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M33" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M33" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N33" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N33" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O33" s="51" t="n"/>
-      <c r="P33" s="51" t="n"/>
-      <c r="Q33" s="51" t="n"/>
-      <c r="R33" s="51" t="n"/>
-      <c r="S33" s="51" t="n"/>
-      <c r="T33" s="51" t="n"/>
-      <c r="U33" s="51" t="n"/>
-      <c r="V33" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W33" s="58" t="n"/>
+      <c r="O33" s="55" t="n"/>
+      <c r="P33" s="55" t="n"/>
+      <c r="Q33" s="55" t="n"/>
+      <c r="R33" s="55" t="n"/>
+      <c r="S33" s="55" t="n"/>
+      <c r="T33" s="55" t="n"/>
+      <c r="U33" s="55" t="n"/>
+      <c r="V33" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W33" s="57" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="53" t="n"/>
-      <c r="D34" s="53" t="n"/>
+      <c r="C34" s="46" t="n"/>
+      <c r="D34" s="46" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G34" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H34" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I34" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J34" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K34" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L34" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M34" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N34" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N34" s="55" t="n"/>
-      <c r="O34" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P34" s="55" t="n"/>
-      <c r="Q34" s="55" t="n"/>
-      <c r="R34" s="55" t="n"/>
-      <c r="S34" s="55" t="n"/>
-      <c r="T34" s="55" t="n"/>
-      <c r="U34" s="55" t="n"/>
-      <c r="V34" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W34" s="57" t="n"/>
+      <c r="O34" s="51" t="n"/>
+      <c r="P34" s="51" t="n"/>
+      <c r="Q34" s="51" t="n"/>
+      <c r="R34" s="51" t="n"/>
+      <c r="S34" s="51" t="n"/>
+      <c r="T34" s="51" t="n"/>
+      <c r="U34" s="51" t="n"/>
+      <c r="V34" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W34" s="58" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="46" t="n"/>
-      <c r="D35" s="46" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G35" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G35" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H35" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L35" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M35" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N35" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O35" s="51" t="n"/>
-      <c r="P35" s="51" t="n"/>
-      <c r="Q35" s="51" t="n"/>
-      <c r="R35" s="51" t="n"/>
-      <c r="S35" s="51" t="n"/>
-      <c r="T35" s="51" t="n"/>
-      <c r="U35" s="51" t="n"/>
-      <c r="V35" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W35" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M35" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N35" s="55" t="n"/>
+      <c r="O35" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P35" s="55" t="n"/>
+      <c r="Q35" s="55" t="n"/>
+      <c r="R35" s="55" t="n"/>
+      <c r="S35" s="55" t="n"/>
+      <c r="T35" s="55" t="n"/>
+      <c r="U35" s="55" t="n"/>
+      <c r="V35" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W35" s="57" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
+      <c r="C36" s="46" t="n"/>
+      <c r="D36" s="46" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G36" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G36" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H36" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I36" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J36" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L36" s="50" t="n"/>
-      <c r="M36" s="55" t="n"/>
-      <c r="N36" s="55" t="n"/>
-      <c r="O36" s="55" t="n"/>
-      <c r="P36" s="55" t="n"/>
-      <c r="Q36" s="55" t="n"/>
-      <c r="R36" s="55" t="n"/>
-      <c r="S36" s="55" t="n"/>
-      <c r="T36" s="55" t="n"/>
-      <c r="U36" s="55" t="n"/>
-      <c r="V36" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W36" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L36" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M36" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N36" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O36" s="51" t="n"/>
+      <c r="P36" s="51" t="n"/>
+      <c r="Q36" s="51" t="n"/>
+      <c r="R36" s="51" t="n"/>
+      <c r="S36" s="51" t="n"/>
+      <c r="T36" s="51" t="n"/>
+      <c r="U36" s="51" t="n"/>
+      <c r="V36" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W36" s="58" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="46" t="n"/>
-      <c r="D37" s="46" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G37" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H37" s="49" t="n">
         <v>0</v>
@@ -3824,43 +3830,43 @@
         <v>0</v>
       </c>
       <c r="J37" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L37" s="50" t="n"/>
-      <c r="M37" s="51" t="n"/>
-      <c r="N37" s="51" t="n"/>
-      <c r="O37" s="51" t="n"/>
-      <c r="P37" s="51" t="n"/>
-      <c r="Q37" s="51" t="n"/>
-      <c r="R37" s="51" t="n"/>
-      <c r="S37" s="51" t="n"/>
-      <c r="T37" s="51" t="n"/>
-      <c r="U37" s="51" t="n"/>
-      <c r="V37" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W37" s="58" t="n"/>
+      <c r="M37" s="55" t="n"/>
+      <c r="N37" s="55" t="n"/>
+      <c r="O37" s="55" t="n"/>
+      <c r="P37" s="55" t="n"/>
+      <c r="Q37" s="55" t="n"/>
+      <c r="R37" s="55" t="n"/>
+      <c r="S37" s="55" t="n"/>
+      <c r="T37" s="55" t="n"/>
+      <c r="U37" s="55" t="n"/>
+      <c r="V37" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W37" s="57" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="53" t="n"/>
-      <c r="D38" s="53" t="n"/>
+      <c r="C38" s="46" t="n"/>
+      <c r="D38" s="46" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G38" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H38" s="49" t="n">
         <v>0</v>
@@ -3869,43 +3875,43 @@
         <v>0</v>
       </c>
       <c r="J38" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="55" t="n"/>
-      <c r="N38" s="55" t="n"/>
-      <c r="O38" s="55" t="n"/>
-      <c r="P38" s="55" t="n"/>
-      <c r="Q38" s="55" t="n"/>
-      <c r="R38" s="55" t="n"/>
-      <c r="S38" s="55" t="n"/>
-      <c r="T38" s="55" t="n"/>
-      <c r="U38" s="55" t="n"/>
-      <c r="V38" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W38" s="57" t="n"/>
+      <c r="M38" s="51" t="n"/>
+      <c r="N38" s="51" t="n"/>
+      <c r="O38" s="51" t="n"/>
+      <c r="P38" s="51" t="n"/>
+      <c r="Q38" s="51" t="n"/>
+      <c r="R38" s="51" t="n"/>
+      <c r="S38" s="51" t="n"/>
+      <c r="T38" s="51" t="n"/>
+      <c r="U38" s="51" t="n"/>
+      <c r="V38" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W38" s="58" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="46" t="n"/>
-      <c r="D39" s="46" t="n"/>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G39" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G39" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H39" s="49" t="n">
         <v>0</v>
@@ -3914,43 +3920,43 @@
         <v>0</v>
       </c>
       <c r="J39" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="51" t="n"/>
-      <c r="N39" s="51" t="n"/>
-      <c r="O39" s="51" t="n"/>
-      <c r="P39" s="51" t="n"/>
-      <c r="Q39" s="51" t="n"/>
-      <c r="R39" s="51" t="n"/>
-      <c r="S39" s="51" t="n"/>
-      <c r="T39" s="51" t="n"/>
-      <c r="U39" s="51" t="n"/>
-      <c r="V39" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W39" s="58" t="n"/>
+      <c r="M39" s="55" t="n"/>
+      <c r="N39" s="55" t="n"/>
+      <c r="O39" s="55" t="n"/>
+      <c r="P39" s="55" t="n"/>
+      <c r="Q39" s="55" t="n"/>
+      <c r="R39" s="55" t="n"/>
+      <c r="S39" s="55" t="n"/>
+      <c r="T39" s="55" t="n"/>
+      <c r="U39" s="55" t="n"/>
+      <c r="V39" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W39" s="57" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="53" t="n"/>
-      <c r="D40" s="53" t="n"/>
+      <c r="C40" s="46" t="n"/>
+      <c r="D40" s="46" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G40" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H40" s="49" t="n">
         <v>0</v>
@@ -3959,43 +3965,43 @@
         <v>0</v>
       </c>
       <c r="J40" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="55" t="n"/>
-      <c r="N40" s="55" t="n"/>
-      <c r="O40" s="55" t="n"/>
-      <c r="P40" s="55" t="n"/>
-      <c r="Q40" s="55" t="n"/>
-      <c r="R40" s="55" t="n"/>
-      <c r="S40" s="55" t="n"/>
-      <c r="T40" s="55" t="n"/>
-      <c r="U40" s="55" t="n"/>
-      <c r="V40" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W40" s="57" t="n"/>
+      <c r="M40" s="51" t="n"/>
+      <c r="N40" s="51" t="n"/>
+      <c r="O40" s="51" t="n"/>
+      <c r="P40" s="51" t="n"/>
+      <c r="Q40" s="51" t="n"/>
+      <c r="R40" s="51" t="n"/>
+      <c r="S40" s="51" t="n"/>
+      <c r="T40" s="51" t="n"/>
+      <c r="U40" s="51" t="n"/>
+      <c r="V40" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W40" s="58" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="46" t="n"/>
-      <c r="D41" s="46" t="n"/>
+      <c r="C41" s="53" t="n"/>
+      <c r="D41" s="53" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G41" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H41" s="49" t="n">
         <v>0</v>
@@ -4004,1371 +4010,1375 @@
         <v>0</v>
       </c>
       <c r="J41" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="51" t="n"/>
-      <c r="N41" s="51" t="n"/>
-      <c r="O41" s="51" t="n"/>
-      <c r="P41" s="51" t="n"/>
-      <c r="Q41" s="51" t="n"/>
-      <c r="R41" s="51" t="n"/>
-      <c r="S41" s="51" t="n"/>
-      <c r="T41" s="51" t="n"/>
-      <c r="U41" s="51" t="n"/>
-      <c r="V41" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W41" s="58" t="n"/>
+      <c r="M41" s="55" t="n"/>
+      <c r="N41" s="55" t="n"/>
+      <c r="O41" s="55" t="n"/>
+      <c r="P41" s="55" t="n"/>
+      <c r="Q41" s="55" t="n"/>
+      <c r="R41" s="55" t="n"/>
+      <c r="S41" s="55" t="n"/>
+      <c r="T41" s="55" t="n"/>
+      <c r="U41" s="55" t="n"/>
+      <c r="V41" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W41" s="57" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="53" t="n"/>
-      <c r="D42" s="53" t="n"/>
+      <c r="C42" s="46" t="n"/>
+      <c r="D42" s="46" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G42" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H42" s="49" t="n"/>
-      <c r="I42" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G42" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H42" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J42" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K42" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="55" t="n"/>
-      <c r="N42" s="55" t="n"/>
-      <c r="O42" s="55" t="n"/>
-      <c r="P42" s="55" t="n"/>
-      <c r="Q42" s="55" t="n"/>
-      <c r="R42" s="55" t="n"/>
-      <c r="S42" s="55" t="n"/>
-      <c r="T42" s="55" t="n"/>
-      <c r="U42" s="55" t="n"/>
-      <c r="V42" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W42" s="57" t="n"/>
+      <c r="M42" s="51" t="n"/>
+      <c r="N42" s="51" t="n"/>
+      <c r="O42" s="51" t="n"/>
+      <c r="P42" s="51" t="n"/>
+      <c r="Q42" s="51" t="n"/>
+      <c r="R42" s="51" t="n"/>
+      <c r="S42" s="51" t="n"/>
+      <c r="T42" s="51" t="n"/>
+      <c r="U42" s="51" t="n"/>
+      <c r="V42" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W42" s="58" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="46" t="n"/>
-      <c r="D43" s="46" t="n"/>
+      <c r="C43" s="53" t="n"/>
+      <c r="D43" s="53" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G43" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H43" s="49" t="n"/>
       <c r="I43" s="49" t="n"/>
       <c r="J43" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K43" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="51" t="n"/>
-      <c r="N43" s="51" t="n"/>
-      <c r="O43" s="51" t="n"/>
-      <c r="P43" s="51" t="n"/>
-      <c r="Q43" s="51" t="n"/>
-      <c r="R43" s="51" t="n"/>
-      <c r="S43" s="51" t="n"/>
-      <c r="T43" s="51" t="n"/>
-      <c r="U43" s="51" t="n"/>
-      <c r="V43" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W43" s="58" t="n"/>
+      <c r="M43" s="55" t="n"/>
+      <c r="N43" s="55" t="n"/>
+      <c r="O43" s="55" t="n"/>
+      <c r="P43" s="55" t="n"/>
+      <c r="Q43" s="55" t="n"/>
+      <c r="R43" s="55" t="n"/>
+      <c r="S43" s="55" t="n"/>
+      <c r="T43" s="55" t="n"/>
+      <c r="U43" s="55" t="n"/>
+      <c r="V43" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W43" s="57" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="53" t="n"/>
-      <c r="D44" s="53" t="n"/>
+      <c r="C44" s="46" t="n"/>
+      <c r="D44" s="46" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G44" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H44" s="49" t="n"/>
       <c r="I44" s="49" t="n"/>
       <c r="J44" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K44" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="55" t="n"/>
-      <c r="N44" s="55" t="n"/>
-      <c r="O44" s="55" t="n"/>
-      <c r="P44" s="55" t="n"/>
-      <c r="Q44" s="55" t="n"/>
-      <c r="R44" s="55" t="n"/>
-      <c r="S44" s="55" t="n"/>
-      <c r="T44" s="55" t="n"/>
-      <c r="U44" s="55" t="n"/>
-      <c r="V44" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W44" s="57" t="n"/>
+      <c r="M44" s="51" t="n"/>
+      <c r="N44" s="51" t="n"/>
+      <c r="O44" s="51" t="n"/>
+      <c r="P44" s="51" t="n"/>
+      <c r="Q44" s="51" t="n"/>
+      <c r="R44" s="51" t="n"/>
+      <c r="S44" s="51" t="n"/>
+      <c r="T44" s="51" t="n"/>
+      <c r="U44" s="51" t="n"/>
+      <c r="V44" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W44" s="58" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="46" t="n"/>
-      <c r="D45" s="46" t="n"/>
+      <c r="C45" s="53" t="n"/>
+      <c r="D45" s="53" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G45" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H45" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I45" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H45" s="49" t="n"/>
+      <c r="I45" s="49" t="n"/>
       <c r="J45" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K45" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="51" t="n"/>
-      <c r="N45" s="51" t="n"/>
-      <c r="O45" s="51" t="n"/>
-      <c r="P45" s="51" t="n"/>
-      <c r="Q45" s="51" t="n"/>
-      <c r="R45" s="51" t="n"/>
-      <c r="S45" s="51" t="n"/>
-      <c r="T45" s="51" t="n"/>
-      <c r="U45" s="51" t="n"/>
-      <c r="V45" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W45" s="58" t="n"/>
+      <c r="M45" s="55" t="n"/>
+      <c r="N45" s="55" t="n"/>
+      <c r="O45" s="55" t="n"/>
+      <c r="P45" s="55" t="n"/>
+      <c r="Q45" s="55" t="n"/>
+      <c r="R45" s="55" t="n"/>
+      <c r="S45" s="55" t="n"/>
+      <c r="T45" s="55" t="n"/>
+      <c r="U45" s="55" t="n"/>
+      <c r="V45" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W45" s="57" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="53" t="n"/>
-      <c r="D46" s="53" t="n"/>
+      <c r="C46" s="46" t="n"/>
+      <c r="D46" s="46" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G46" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H46" s="49" t="n"/>
-      <c r="I46" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G46" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H46" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I46" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J46" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K46" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="55" t="n"/>
-      <c r="N46" s="55" t="n"/>
-      <c r="O46" s="55" t="n"/>
-      <c r="P46" s="55" t="n"/>
-      <c r="Q46" s="55" t="n"/>
-      <c r="R46" s="55" t="n"/>
-      <c r="S46" s="55" t="n"/>
-      <c r="T46" s="55" t="n"/>
-      <c r="U46" s="55" t="n"/>
-      <c r="V46" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W46" s="57" t="n"/>
+      <c r="M46" s="51" t="n"/>
+      <c r="N46" s="51" t="n"/>
+      <c r="O46" s="51" t="n"/>
+      <c r="P46" s="51" t="n"/>
+      <c r="Q46" s="51" t="n"/>
+      <c r="R46" s="51" t="n"/>
+      <c r="S46" s="51" t="n"/>
+      <c r="T46" s="51" t="n"/>
+      <c r="U46" s="51" t="n"/>
+      <c r="V46" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W46" s="58" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="46" t="n"/>
-      <c r="D47" s="46" t="n"/>
+      <c r="C47" s="53" t="n"/>
+      <c r="D47" s="53" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G47" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G47" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H47" s="49" t="n"/>
       <c r="I47" s="49" t="n"/>
       <c r="J47" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K47" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="51" t="n"/>
-      <c r="N47" s="51" t="n"/>
-      <c r="O47" s="51" t="n"/>
-      <c r="P47" s="51" t="n"/>
-      <c r="Q47" s="51" t="n"/>
-      <c r="R47" s="51" t="n"/>
-      <c r="S47" s="51" t="n"/>
-      <c r="T47" s="51" t="n"/>
-      <c r="U47" s="51" t="n"/>
-      <c r="V47" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W47" s="58" t="n"/>
+      <c r="M47" s="55" t="n"/>
+      <c r="N47" s="55" t="n"/>
+      <c r="O47" s="55" t="n"/>
+      <c r="P47" s="55" t="n"/>
+      <c r="Q47" s="55" t="n"/>
+      <c r="R47" s="55" t="n"/>
+      <c r="S47" s="55" t="n"/>
+      <c r="T47" s="55" t="n"/>
+      <c r="U47" s="55" t="n"/>
+      <c r="V47" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W47" s="57" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="53" t="n"/>
-      <c r="D48" s="53" t="n"/>
+      <c r="C48" s="46" t="n"/>
+      <c r="D48" s="46" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G48" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G48" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H48" s="49" t="n"/>
       <c r="I48" s="49" t="n"/>
       <c r="J48" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K48" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K48" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="55" t="n"/>
-      <c r="N48" s="55" t="n"/>
-      <c r="O48" s="55" t="n"/>
-      <c r="P48" s="55" t="n"/>
-      <c r="Q48" s="55" t="n"/>
-      <c r="R48" s="55" t="n"/>
-      <c r="S48" s="55" t="n"/>
-      <c r="T48" s="55" t="n"/>
-      <c r="U48" s="55" t="n"/>
-      <c r="V48" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W48" s="57" t="n"/>
+      <c r="M48" s="51" t="n"/>
+      <c r="N48" s="51" t="n"/>
+      <c r="O48" s="51" t="n"/>
+      <c r="P48" s="51" t="n"/>
+      <c r="Q48" s="51" t="n"/>
+      <c r="R48" s="51" t="n"/>
+      <c r="S48" s="51" t="n"/>
+      <c r="T48" s="51" t="n"/>
+      <c r="U48" s="51" t="n"/>
+      <c r="V48" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W48" s="58" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="46" t="n"/>
-      <c r="D49" s="46" t="n"/>
+      <c r="C49" s="53" t="n"/>
+      <c r="D49" s="53" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G49" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H49" s="49" t="n"/>
       <c r="I49" s="49" t="n"/>
       <c r="J49" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K49" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="51" t="n"/>
-      <c r="N49" s="51" t="n"/>
-      <c r="O49" s="51" t="n"/>
-      <c r="P49" s="51" t="n"/>
-      <c r="Q49" s="51" t="n"/>
-      <c r="R49" s="51" t="n"/>
-      <c r="S49" s="51" t="n"/>
-      <c r="T49" s="51" t="n"/>
-      <c r="U49" s="51" t="n"/>
-      <c r="V49" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W49" s="58" t="n"/>
+      <c r="M49" s="55" t="n"/>
+      <c r="N49" s="55" t="n"/>
+      <c r="O49" s="55" t="n"/>
+      <c r="P49" s="55" t="n"/>
+      <c r="Q49" s="55" t="n"/>
+      <c r="R49" s="55" t="n"/>
+      <c r="S49" s="55" t="n"/>
+      <c r="T49" s="55" t="n"/>
+      <c r="U49" s="55" t="n"/>
+      <c r="V49" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W49" s="57" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="53" t="n"/>
-      <c r="D50" s="53" t="n"/>
+      <c r="C50" s="46" t="n"/>
+      <c r="D50" s="46" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G50" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G50" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="49" t="n"/>
       <c r="J50" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="55" t="n"/>
-      <c r="N50" s="55" t="n"/>
-      <c r="O50" s="55" t="n"/>
-      <c r="P50" s="55" t="n"/>
-      <c r="Q50" s="55" t="n"/>
-      <c r="R50" s="55" t="n"/>
-      <c r="S50" s="55" t="n"/>
-      <c r="T50" s="55" t="n"/>
-      <c r="U50" s="55" t="n"/>
-      <c r="V50" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W50" s="57" t="n"/>
+      <c r="M50" s="51" t="n"/>
+      <c r="N50" s="51" t="n"/>
+      <c r="O50" s="51" t="n"/>
+      <c r="P50" s="51" t="n"/>
+      <c r="Q50" s="51" t="n"/>
+      <c r="R50" s="51" t="n"/>
+      <c r="S50" s="51" t="n"/>
+      <c r="T50" s="51" t="n"/>
+      <c r="U50" s="51" t="n"/>
+      <c r="V50" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W50" s="58" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="46" t="n"/>
-      <c r="D51" s="46" t="n"/>
+      <c r="C51" s="53" t="n"/>
+      <c r="D51" s="53" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G51" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H51" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I51" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G51" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H51" s="49" t="n"/>
+      <c r="I51" s="49" t="n"/>
       <c r="J51" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="51" t="n"/>
-      <c r="N51" s="51" t="n"/>
-      <c r="O51" s="51" t="n"/>
-      <c r="P51" s="51" t="n"/>
-      <c r="Q51" s="51" t="n"/>
-      <c r="R51" s="51" t="n"/>
-      <c r="S51" s="51" t="n"/>
-      <c r="T51" s="51" t="n"/>
-      <c r="U51" s="51" t="n"/>
-      <c r="V51" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W51" s="58" t="n"/>
+      <c r="M51" s="55" t="n"/>
+      <c r="N51" s="55" t="n"/>
+      <c r="O51" s="55" t="n"/>
+      <c r="P51" s="55" t="n"/>
+      <c r="Q51" s="55" t="n"/>
+      <c r="R51" s="55" t="n"/>
+      <c r="S51" s="55" t="n"/>
+      <c r="T51" s="55" t="n"/>
+      <c r="U51" s="55" t="n"/>
+      <c r="V51" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W51" s="57" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="53" t="n"/>
-      <c r="D52" s="53" t="n"/>
+      <c r="C52" s="46" t="n"/>
+      <c r="D52" s="46" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G52" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H52" s="49" t="n"/>
-      <c r="I52" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H52" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I52" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J52" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="55" t="n"/>
-      <c r="N52" s="55" t="n"/>
-      <c r="O52" s="55" t="n"/>
-      <c r="P52" s="55" t="n"/>
-      <c r="Q52" s="55" t="n"/>
-      <c r="R52" s="55" t="n"/>
-      <c r="S52" s="55" t="n"/>
-      <c r="T52" s="55" t="n"/>
-      <c r="U52" s="55" t="n"/>
-      <c r="V52" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W52" s="57" t="n"/>
+      <c r="M52" s="51" t="n"/>
+      <c r="N52" s="51" t="n"/>
+      <c r="O52" s="51" t="n"/>
+      <c r="P52" s="51" t="n"/>
+      <c r="Q52" s="51" t="n"/>
+      <c r="R52" s="51" t="n"/>
+      <c r="S52" s="51" t="n"/>
+      <c r="T52" s="51" t="n"/>
+      <c r="U52" s="51" t="n"/>
+      <c r="V52" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W52" s="58" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="46" t="n"/>
-      <c r="D53" s="46" t="n"/>
+      <c r="C53" s="53" t="n"/>
+      <c r="D53" s="53" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G53" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H53" s="49" t="n"/>
       <c r="I53" s="49" t="n"/>
       <c r="J53" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="51" t="n"/>
-      <c r="N53" s="51" t="n"/>
-      <c r="O53" s="51" t="n"/>
-      <c r="P53" s="51" t="n"/>
-      <c r="Q53" s="51" t="n"/>
-      <c r="R53" s="51" t="n"/>
-      <c r="S53" s="51" t="n"/>
-      <c r="T53" s="51" t="n"/>
-      <c r="U53" s="51" t="n"/>
-      <c r="V53" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W53" s="58" t="n"/>
+      <c r="M53" s="55" t="n"/>
+      <c r="N53" s="55" t="n"/>
+      <c r="O53" s="55" t="n"/>
+      <c r="P53" s="55" t="n"/>
+      <c r="Q53" s="55" t="n"/>
+      <c r="R53" s="55" t="n"/>
+      <c r="S53" s="55" t="n"/>
+      <c r="T53" s="55" t="n"/>
+      <c r="U53" s="55" t="n"/>
+      <c r="V53" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W53" s="57" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="53" t="n"/>
-      <c r="D54" s="53" t="n"/>
+      <c r="C54" s="46" t="n"/>
+      <c r="D54" s="46" t="n"/>
       <c r="E54" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F54" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G54" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H54" s="49" t="n"/>
+      <c r="I54" s="49" t="n"/>
+      <c r="J54" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F54" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G54" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H54" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I54" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J54" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K54" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="55" t="n"/>
-      <c r="N54" s="55" t="n"/>
-      <c r="O54" s="55" t="n"/>
-      <c r="P54" s="55" t="n"/>
-      <c r="Q54" s="55" t="n"/>
-      <c r="R54" s="55" t="n"/>
-      <c r="S54" s="55" t="n"/>
-      <c r="T54" s="55" t="n"/>
-      <c r="U54" s="55" t="n"/>
-      <c r="V54" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W54" s="57" t="n"/>
+      <c r="M54" s="51" t="n"/>
+      <c r="N54" s="51" t="n"/>
+      <c r="O54" s="51" t="n"/>
+      <c r="P54" s="51" t="n"/>
+      <c r="Q54" s="51" t="n"/>
+      <c r="R54" s="51" t="n"/>
+      <c r="S54" s="51" t="n"/>
+      <c r="T54" s="51" t="n"/>
+      <c r="U54" s="51" t="n"/>
+      <c r="V54" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W54" s="58" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="46" t="n"/>
-      <c r="D55" s="46" t="n"/>
+      <c r="C55" s="53" t="n"/>
+      <c r="D55" s="53" t="n"/>
       <c r="E55" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F55" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G55" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H55" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I55" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J55" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K55" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="51" t="n"/>
-      <c r="N55" s="51" t="n"/>
-      <c r="O55" s="51" t="n"/>
-      <c r="P55" s="51" t="n"/>
-      <c r="Q55" s="51" t="n"/>
-      <c r="R55" s="51" t="n"/>
-      <c r="S55" s="51" t="n"/>
-      <c r="T55" s="51" t="n"/>
-      <c r="U55" s="51" t="n"/>
-      <c r="V55" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W55" s="58" t="n"/>
+      <c r="M55" s="55" t="n"/>
+      <c r="N55" s="55" t="n"/>
+      <c r="O55" s="55" t="n"/>
+      <c r="P55" s="55" t="n"/>
+      <c r="Q55" s="55" t="n"/>
+      <c r="R55" s="55" t="n"/>
+      <c r="S55" s="55" t="n"/>
+      <c r="T55" s="55" t="n"/>
+      <c r="U55" s="55" t="n"/>
+      <c r="V55" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W55" s="57" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="53" t="n"/>
-      <c r="D56" s="53" t="n"/>
+      <c r="C56" s="46" t="n"/>
+      <c r="D56" s="46" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G56" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H56" s="49" t="n"/>
-      <c r="I56" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H56" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I56" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J56" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="55" t="n"/>
-      <c r="N56" s="55" t="n"/>
-      <c r="O56" s="55" t="n"/>
-      <c r="P56" s="55" t="n"/>
-      <c r="Q56" s="55" t="n"/>
-      <c r="R56" s="55" t="n"/>
-      <c r="S56" s="55" t="n"/>
-      <c r="T56" s="55" t="n"/>
-      <c r="U56" s="55" t="n"/>
-      <c r="V56" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W56" s="57" t="n"/>
+      <c r="M56" s="51" t="n"/>
+      <c r="N56" s="51" t="n"/>
+      <c r="O56" s="51" t="n"/>
+      <c r="P56" s="51" t="n"/>
+      <c r="Q56" s="51" t="n"/>
+      <c r="R56" s="51" t="n"/>
+      <c r="S56" s="51" t="n"/>
+      <c r="T56" s="51" t="n"/>
+      <c r="U56" s="51" t="n"/>
+      <c r="V56" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W56" s="58" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="46" t="n"/>
-      <c r="D57" s="46" t="n"/>
+      <c r="C57" s="53" t="n"/>
+      <c r="D57" s="53" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G57" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G57" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H57" s="49" t="n"/>
       <c r="I57" s="49" t="n"/>
       <c r="J57" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K57" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="51" t="n"/>
-      <c r="N57" s="51" t="n"/>
-      <c r="O57" s="51" t="n"/>
-      <c r="P57" s="51" t="n"/>
-      <c r="Q57" s="51" t="n"/>
-      <c r="R57" s="51" t="n"/>
-      <c r="S57" s="51" t="n"/>
-      <c r="T57" s="51" t="n"/>
-      <c r="U57" s="51" t="n"/>
-      <c r="V57" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W57" s="58" t="n"/>
+      <c r="M57" s="55" t="n"/>
+      <c r="N57" s="55" t="n"/>
+      <c r="O57" s="55" t="n"/>
+      <c r="P57" s="55" t="n"/>
+      <c r="Q57" s="55" t="n"/>
+      <c r="R57" s="55" t="n"/>
+      <c r="S57" s="55" t="n"/>
+      <c r="T57" s="55" t="n"/>
+      <c r="U57" s="55" t="n"/>
+      <c r="V57" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W57" s="57" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="53" t="n"/>
-      <c r="D58" s="53" t="n"/>
+      <c r="C58" s="46" t="n"/>
+      <c r="D58" s="46" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G58" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G58" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K58" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="55" t="n"/>
-      <c r="N58" s="55" t="n"/>
-      <c r="O58" s="55" t="n"/>
-      <c r="P58" s="55" t="n"/>
-      <c r="Q58" s="55" t="n"/>
-      <c r="R58" s="55" t="n"/>
-      <c r="S58" s="55" t="n"/>
-      <c r="T58" s="55" t="n"/>
-      <c r="U58" s="55" t="n"/>
-      <c r="V58" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W58" s="57" t="n"/>
+      <c r="M58" s="51" t="n"/>
+      <c r="N58" s="51" t="n"/>
+      <c r="O58" s="51" t="n"/>
+      <c r="P58" s="51" t="n"/>
+      <c r="Q58" s="51" t="n"/>
+      <c r="R58" s="51" t="n"/>
+      <c r="S58" s="51" t="n"/>
+      <c r="T58" s="51" t="n"/>
+      <c r="U58" s="51" t="n"/>
+      <c r="V58" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W58" s="58" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="46" t="n"/>
-      <c r="D59" s="46" t="n"/>
+      <c r="C59" s="53" t="n"/>
+      <c r="D59" s="53" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G59" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="51" t="n"/>
-      <c r="N59" s="51" t="n"/>
-      <c r="O59" s="51" t="n"/>
-      <c r="P59" s="51" t="n"/>
-      <c r="Q59" s="51" t="n"/>
-      <c r="R59" s="51" t="n"/>
-      <c r="S59" s="51" t="n"/>
-      <c r="T59" s="51" t="n"/>
-      <c r="U59" s="51" t="n"/>
-      <c r="V59" s="52" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="W59" s="58" t="n"/>
+      <c r="M59" s="55" t="n"/>
+      <c r="N59" s="55" t="n"/>
+      <c r="O59" s="55" t="n"/>
+      <c r="P59" s="55" t="n"/>
+      <c r="Q59" s="55" t="n"/>
+      <c r="R59" s="55" t="n"/>
+      <c r="S59" s="55" t="n"/>
+      <c r="T59" s="55" t="n"/>
+      <c r="U59" s="55" t="n"/>
+      <c r="V59" s="56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="W59" s="57" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/23（五）</t>
+          <t>2026/01/26（一）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
+      <c r="C60" s="46" t="n"/>
+      <c r="D60" s="46" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>102</v>
-      </c>
-      <c r="G60" s="48" t="n">
-        <v>15</v>
+        <v>70</v>
+      </c>
+      <c r="G60" s="54" t="n">
+        <v>35.8</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="55" t="n"/>
-      <c r="N60" s="55" t="n"/>
-      <c r="O60" s="55" t="n"/>
-      <c r="P60" s="55" t="n"/>
-      <c r="Q60" s="55" t="n"/>
-      <c r="R60" s="55" t="n"/>
-      <c r="S60" s="55" t="n"/>
-      <c r="T60" s="55" t="n"/>
-      <c r="U60" s="55" t="n"/>
-      <c r="V60" s="56" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="W60" s="57" t="n"/>
+      <c r="M60" s="51" t="n"/>
+      <c r="N60" s="51" t="n"/>
+      <c r="O60" s="51" t="n"/>
+      <c r="P60" s="51" t="n"/>
+      <c r="Q60" s="51" t="n"/>
+      <c r="R60" s="51" t="n"/>
+      <c r="S60" s="51" t="n"/>
+      <c r="T60" s="51" t="n"/>
+      <c r="U60" s="51" t="n"/>
+      <c r="V60" s="52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W60" s="58" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>2026/01/22（四）</t>
+          <t>2026/01/23（五）</t>
         </is>
       </c>
       <c r="B61" s="45" t="n"/>
-      <c r="C61" s="46" t="n"/>
-      <c r="D61" s="46" t="n"/>
+      <c r="C61" s="53" t="n"/>
+      <c r="D61" s="53" t="n"/>
       <c r="E61" s="47" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="F61" s="47" t="n">
-        <v>72</v>
-      </c>
-      <c r="G61" s="54" t="n">
-        <v>26.5</v>
+        <v>102</v>
+      </c>
+      <c r="G61" s="48" t="n">
+        <v>15</v>
       </c>
       <c r="H61" s="49" t="n"/>
       <c r="I61" s="49" t="n"/>
       <c r="J61" s="50" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="K61" s="50" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L61" s="50" t="n"/>
-      <c r="M61" s="51" t="n"/>
-      <c r="N61" s="51" t="n"/>
-      <c r="O61" s="51" t="n"/>
-      <c r="P61" s="51" t="n"/>
-      <c r="Q61" s="51" t="n"/>
-      <c r="R61" s="51" t="n"/>
-      <c r="S61" s="51" t="n"/>
-      <c r="T61" s="51" t="n"/>
-      <c r="U61" s="51" t="n"/>
-      <c r="V61" s="52" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="W61" s="58" t="n"/>
+      <c r="M61" s="55" t="n"/>
+      <c r="N61" s="55" t="n"/>
+      <c r="O61" s="55" t="n"/>
+      <c r="P61" s="55" t="n"/>
+      <c r="Q61" s="55" t="n"/>
+      <c r="R61" s="55" t="n"/>
+      <c r="S61" s="55" t="n"/>
+      <c r="T61" s="55" t="n"/>
+      <c r="U61" s="55" t="n"/>
+      <c r="V61" s="56" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="W61" s="57" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>2026/01/21（三）</t>
+          <t>2026/01/22（四）</t>
         </is>
       </c>
       <c r="B62" s="45" t="n"/>
-      <c r="C62" s="53" t="n"/>
-      <c r="D62" s="53" t="n"/>
+      <c r="C62" s="46" t="n"/>
+      <c r="D62" s="46" t="n"/>
       <c r="E62" s="47" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F62" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G62" s="48" t="n">
-        <v>24.3</v>
+        <v>72</v>
+      </c>
+      <c r="G62" s="54" t="n">
+        <v>26.5</v>
       </c>
       <c r="H62" s="49" t="n"/>
       <c r="I62" s="49" t="n"/>
       <c r="J62" s="50" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K62" s="50" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L62" s="50" t="n"/>
-      <c r="M62" s="55" t="n"/>
-      <c r="N62" s="55" t="n"/>
-      <c r="O62" s="55" t="n"/>
-      <c r="P62" s="55" t="n"/>
-      <c r="Q62" s="55" t="n"/>
-      <c r="R62" s="55" t="n"/>
-      <c r="S62" s="55" t="n"/>
-      <c r="T62" s="55" t="n"/>
-      <c r="U62" s="55" t="n"/>
-      <c r="V62" s="56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="W62" s="57" t="n"/>
+      <c r="M62" s="51" t="n"/>
+      <c r="N62" s="51" t="n"/>
+      <c r="O62" s="51" t="n"/>
+      <c r="P62" s="51" t="n"/>
+      <c r="Q62" s="51" t="n"/>
+      <c r="R62" s="51" t="n"/>
+      <c r="S62" s="51" t="n"/>
+      <c r="T62" s="51" t="n"/>
+      <c r="U62" s="51" t="n"/>
+      <c r="V62" s="52" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="W62" s="58" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>2026/01/20（二）</t>
+          <t>2026/01/21（三）</t>
         </is>
       </c>
       <c r="B63" s="45" t="n"/>
-      <c r="C63" s="46" t="n"/>
-      <c r="D63" s="46" t="n"/>
+      <c r="C63" s="53" t="n"/>
+      <c r="D63" s="53" t="n"/>
       <c r="E63" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F63" s="47" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="G63" s="48" t="n">
-        <v>22.1</v>
+        <v>24.3</v>
       </c>
       <c r="H63" s="49" t="n"/>
       <c r="I63" s="49" t="n"/>
       <c r="J63" s="50" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K63" s="50" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L63" s="50" t="n"/>
-      <c r="M63" s="51" t="n"/>
-      <c r="N63" s="51" t="n"/>
-      <c r="O63" s="51" t="n"/>
-      <c r="P63" s="51" t="n"/>
-      <c r="Q63" s="51" t="n"/>
-      <c r="R63" s="51" t="n"/>
-      <c r="S63" s="51" t="n"/>
-      <c r="T63" s="51" t="n"/>
-      <c r="U63" s="51" t="n"/>
-      <c r="V63" s="52" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="W63" s="58" t="n"/>
+      <c r="M63" s="55" t="n"/>
+      <c r="N63" s="55" t="n"/>
+      <c r="O63" s="55" t="n"/>
+      <c r="P63" s="55" t="n"/>
+      <c r="Q63" s="55" t="n"/>
+      <c r="R63" s="55" t="n"/>
+      <c r="S63" s="55" t="n"/>
+      <c r="T63" s="55" t="n"/>
+      <c r="U63" s="55" t="n"/>
+      <c r="V63" s="56" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="W63" s="57" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="44" t="inlineStr">
         <is>
-          <t>2026/01/19（一）</t>
+          <t>2026/01/20（二）</t>
         </is>
       </c>
       <c r="B64" s="45" t="n"/>
-      <c r="C64" s="53" t="n"/>
-      <c r="D64" s="53" t="n"/>
+      <c r="C64" s="46" t="n"/>
+      <c r="D64" s="46" t="n"/>
       <c r="E64" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F64" s="47" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="G64" s="48" t="n">
-        <v>18.7</v>
+        <v>22.1</v>
       </c>
       <c r="H64" s="49" t="n"/>
       <c r="I64" s="49" t="n"/>
       <c r="J64" s="50" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K64" s="50" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L64" s="50" t="n"/>
-      <c r="M64" s="55" t="n"/>
-      <c r="N64" s="55" t="n"/>
-      <c r="O64" s="55" t="n"/>
-      <c r="P64" s="55" t="n"/>
-      <c r="Q64" s="55" t="n"/>
-      <c r="R64" s="55" t="n"/>
-      <c r="S64" s="55" t="n"/>
-      <c r="T64" s="55" t="n"/>
-      <c r="U64" s="55" t="n"/>
-      <c r="V64" s="56" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="W64" s="57" t="n"/>
+      <c r="M64" s="51" t="n"/>
+      <c r="N64" s="51" t="n"/>
+      <c r="O64" s="51" t="n"/>
+      <c r="P64" s="51" t="n"/>
+      <c r="Q64" s="51" t="n"/>
+      <c r="R64" s="51" t="n"/>
+      <c r="S64" s="51" t="n"/>
+      <c r="T64" s="51" t="n"/>
+      <c r="U64" s="51" t="n"/>
+      <c r="V64" s="52" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="W64" s="58" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>2026/01/16（五）</t>
+          <t>2026/01/19（一）</t>
         </is>
       </c>
       <c r="B65" s="45" t="n"/>
-      <c r="C65" s="46" t="n"/>
-      <c r="D65" s="46" t="n"/>
+      <c r="C65" s="53" t="n"/>
+      <c r="D65" s="53" t="n"/>
       <c r="E65" s="47" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F65" s="47" t="n">
-        <v>58</v>
-      </c>
-      <c r="G65" s="59" t="n">
-        <v>40.2</v>
+        <v>87</v>
+      </c>
+      <c r="G65" s="48" t="n">
+        <v>18.7</v>
       </c>
       <c r="H65" s="49" t="n"/>
       <c r="I65" s="49" t="n"/>
       <c r="J65" s="50" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K65" s="50" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L65" s="50" t="n"/>
-      <c r="M65" s="51" t="n"/>
-      <c r="N65" s="51" t="n"/>
-      <c r="O65" s="51" t="n"/>
-      <c r="P65" s="51" t="n"/>
-      <c r="Q65" s="51" t="n"/>
-      <c r="R65" s="51" t="n"/>
-      <c r="S65" s="51" t="n"/>
-      <c r="T65" s="51" t="n"/>
-      <c r="U65" s="51" t="n"/>
-      <c r="V65" s="52" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="W65" s="58" t="n"/>
+      <c r="M65" s="55" t="n"/>
+      <c r="N65" s="55" t="n"/>
+      <c r="O65" s="55" t="n"/>
+      <c r="P65" s="55" t="n"/>
+      <c r="Q65" s="55" t="n"/>
+      <c r="R65" s="55" t="n"/>
+      <c r="S65" s="55" t="n"/>
+      <c r="T65" s="55" t="n"/>
+      <c r="U65" s="55" t="n"/>
+      <c r="V65" s="56" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="W65" s="57" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="44" t="inlineStr">
         <is>
-          <t>2026/01/15（四）</t>
+          <t>2026/01/16（五）</t>
         </is>
       </c>
       <c r="B66" s="45" t="n"/>
-      <c r="C66" s="53" t="n"/>
-      <c r="D66" s="53" t="n"/>
+      <c r="C66" s="46" t="n"/>
+      <c r="D66" s="46" t="n"/>
       <c r="E66" s="47" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F66" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G66" s="48" t="n">
-        <v>24.7</v>
+        <v>58</v>
+      </c>
+      <c r="G66" s="59" t="n">
+        <v>40.2</v>
       </c>
       <c r="H66" s="49" t="n"/>
       <c r="I66" s="49" t="n"/>
       <c r="J66" s="50" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K66" s="50" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L66" s="50" t="n"/>
-      <c r="M66" s="55" t="n"/>
-      <c r="N66" s="55" t="n"/>
-      <c r="O66" s="55" t="n"/>
-      <c r="P66" s="55" t="n"/>
-      <c r="Q66" s="55" t="n"/>
-      <c r="R66" s="55" t="n"/>
-      <c r="S66" s="55" t="n"/>
-      <c r="T66" s="55" t="n"/>
-      <c r="U66" s="55" t="n"/>
-      <c r="V66" s="56" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="W66" s="57" t="n"/>
+      <c r="M66" s="51" t="n"/>
+      <c r="N66" s="51" t="n"/>
+      <c r="O66" s="51" t="n"/>
+      <c r="P66" s="51" t="n"/>
+      <c r="Q66" s="51" t="n"/>
+      <c r="R66" s="51" t="n"/>
+      <c r="S66" s="51" t="n"/>
+      <c r="T66" s="51" t="n"/>
+      <c r="U66" s="51" t="n"/>
+      <c r="V66" s="52" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W66" s="58" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="44" t="inlineStr">
         <is>
-          <t>2026/01/14（三）</t>
+          <t>2026/01/15（四）</t>
         </is>
       </c>
       <c r="B67" s="45" t="n"/>
-      <c r="C67" s="46" t="n"/>
-      <c r="D67" s="46" t="n"/>
+      <c r="C67" s="53" t="n"/>
+      <c r="D67" s="53" t="n"/>
       <c r="E67" s="47" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="F67" s="47" t="n">
-        <v>99</v>
-      </c>
-      <c r="G67" s="54" t="n">
-        <v>37.3</v>
+        <v>55</v>
+      </c>
+      <c r="G67" s="48" t="n">
+        <v>24.7</v>
       </c>
       <c r="H67" s="49" t="n"/>
       <c r="I67" s="49" t="n"/>
       <c r="J67" s="50" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="K67" s="50" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L67" s="50" t="n"/>
-      <c r="M67" s="51" t="n"/>
-      <c r="N67" s="51" t="n"/>
-      <c r="O67" s="51" t="n"/>
-      <c r="P67" s="51" t="n"/>
-      <c r="Q67" s="51" t="n"/>
-      <c r="R67" s="51" t="n"/>
-      <c r="S67" s="51" t="n"/>
-      <c r="T67" s="51" t="n"/>
-      <c r="U67" s="51" t="n"/>
-      <c r="V67" s="52" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W67" s="58" t="n"/>
+      <c r="M67" s="55" t="n"/>
+      <c r="N67" s="55" t="n"/>
+      <c r="O67" s="55" t="n"/>
+      <c r="P67" s="55" t="n"/>
+      <c r="Q67" s="55" t="n"/>
+      <c r="R67" s="55" t="n"/>
+      <c r="S67" s="55" t="n"/>
+      <c r="T67" s="55" t="n"/>
+      <c r="U67" s="55" t="n"/>
+      <c r="V67" s="56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="W67" s="57" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="44" t="inlineStr">
         <is>
-          <t>2026/01/13（二）</t>
+          <t>2026/01/14（三）</t>
         </is>
       </c>
       <c r="B68" s="45" t="n"/>
-      <c r="C68" s="53" t="n"/>
-      <c r="D68" s="53" t="n"/>
+      <c r="C68" s="46" t="n"/>
+      <c r="D68" s="46" t="n"/>
       <c r="E68" s="47" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F68" s="47" t="n">
-        <v>65</v>
-      </c>
-      <c r="G68" s="59" t="n">
-        <v>47.6</v>
+        <v>99</v>
+      </c>
+      <c r="G68" s="54" t="n">
+        <v>37.3</v>
       </c>
       <c r="H68" s="49" t="n"/>
       <c r="I68" s="49" t="n"/>
       <c r="J68" s="50" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="K68" s="50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L68" s="50" t="n"/>
-      <c r="M68" s="55" t="n"/>
-      <c r="N68" s="55" t="n"/>
-      <c r="O68" s="55" t="n"/>
-      <c r="P68" s="55" t="n"/>
-      <c r="Q68" s="55" t="n"/>
-      <c r="R68" s="55" t="n"/>
-      <c r="S68" s="55" t="n"/>
-      <c r="T68" s="55" t="n"/>
-      <c r="U68" s="55" t="n"/>
-      <c r="V68" s="56" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="W68" s="57" t="n"/>
+      <c r="M68" s="51" t="n"/>
+      <c r="N68" s="51" t="n"/>
+      <c r="O68" s="51" t="n"/>
+      <c r="P68" s="51" t="n"/>
+      <c r="Q68" s="51" t="n"/>
+      <c r="R68" s="51" t="n"/>
+      <c r="S68" s="51" t="n"/>
+      <c r="T68" s="51" t="n"/>
+      <c r="U68" s="51" t="n"/>
+      <c r="V68" s="52" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="W68" s="58" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="44" t="inlineStr">
         <is>
-          <t>2026/01/12（一）</t>
+          <t>2026/01/13（二）</t>
         </is>
       </c>
       <c r="B69" s="45" t="n"/>
-      <c r="C69" s="46" t="n"/>
-      <c r="D69" s="46" t="n"/>
+      <c r="C69" s="53" t="n"/>
+      <c r="D69" s="53" t="n"/>
       <c r="E69" s="47" t="n">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="F69" s="47" t="n">
-        <v>178</v>
-      </c>
-      <c r="G69" s="48" t="n">
-        <v>20.9</v>
+        <v>65</v>
+      </c>
+      <c r="G69" s="59" t="n">
+        <v>47.6</v>
       </c>
       <c r="H69" s="49" t="n"/>
       <c r="I69" s="49" t="n"/>
       <c r="J69" s="50" t="n">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K69" s="50" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="L69" s="50" t="n"/>
-      <c r="M69" s="51" t="n"/>
-      <c r="N69" s="51" t="n"/>
-      <c r="O69" s="51" t="n"/>
-      <c r="P69" s="51" t="n"/>
-      <c r="Q69" s="51" t="n"/>
-      <c r="R69" s="51" t="n"/>
-      <c r="S69" s="51" t="n"/>
-      <c r="T69" s="51" t="n"/>
-      <c r="U69" s="51" t="n"/>
-      <c r="V69" s="52" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="W69" s="58" t="n"/>
+      <c r="M69" s="55" t="n"/>
+      <c r="N69" s="55" t="n"/>
+      <c r="O69" s="55" t="n"/>
+      <c r="P69" s="55" t="n"/>
+      <c r="Q69" s="55" t="n"/>
+      <c r="R69" s="55" t="n"/>
+      <c r="S69" s="55" t="n"/>
+      <c r="T69" s="55" t="n"/>
+      <c r="U69" s="55" t="n"/>
+      <c r="V69" s="56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W69" s="57" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="44" t="inlineStr">
         <is>
-          <t>2026/01/09（五）</t>
+          <t>2026/01/12（一）</t>
         </is>
       </c>
       <c r="B70" s="45" t="n"/>
-      <c r="C70" s="53" t="n"/>
-      <c r="D70" s="53" t="n"/>
+      <c r="C70" s="46" t="n"/>
+      <c r="D70" s="46" t="n"/>
       <c r="E70" s="47" t="n">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="F70" s="47" t="n">
-        <v>92</v>
-      </c>
-      <c r="G70" s="54" t="n">
-        <v>33.3</v>
+        <v>178</v>
+      </c>
+      <c r="G70" s="48" t="n">
+        <v>20.9</v>
       </c>
       <c r="H70" s="49" t="n"/>
       <c r="I70" s="49" t="n"/>
       <c r="J70" s="50" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="K70" s="50" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L70" s="50" t="n"/>
-      <c r="M70" s="55" t="n"/>
-      <c r="N70" s="55" t="n"/>
-      <c r="O70" s="55" t="n"/>
-      <c r="P70" s="55" t="n"/>
-      <c r="Q70" s="55" t="n"/>
-      <c r="R70" s="55" t="n"/>
-      <c r="S70" s="55" t="n"/>
-      <c r="T70" s="55" t="n"/>
-      <c r="U70" s="55" t="n"/>
-      <c r="V70" s="56" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="W70" s="57" t="n"/>
+      <c r="M70" s="51" t="n"/>
+      <c r="N70" s="51" t="n"/>
+      <c r="O70" s="51" t="n"/>
+      <c r="P70" s="51" t="n"/>
+      <c r="Q70" s="51" t="n"/>
+      <c r="R70" s="51" t="n"/>
+      <c r="S70" s="51" t="n"/>
+      <c r="T70" s="51" t="n"/>
+      <c r="U70" s="51" t="n"/>
+      <c r="V70" s="52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W70" s="58" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="44" t="inlineStr">
         <is>
-          <t>2026/01/08（四）</t>
+          <t>2026/01/09（五）</t>
         </is>
       </c>
       <c r="B71" s="45" t="n"/>
-      <c r="C71" s="46" t="n"/>
-      <c r="D71" s="46" t="n"/>
+      <c r="C71" s="53" t="n"/>
+      <c r="D71" s="53" t="n"/>
       <c r="E71" s="47" t="n">
         <v>92</v>
       </c>
       <c r="F71" s="47" t="n">
         <v>92</v>
       </c>
-      <c r="G71" s="48" t="n">
-        <v>24</v>
+      <c r="G71" s="54" t="n">
+        <v>33.3</v>
       </c>
       <c r="H71" s="49" t="n"/>
       <c r="I71" s="49" t="n"/>
       <c r="J71" s="50" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K71" s="50" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L71" s="50" t="n"/>
-      <c r="M71" s="51" t="n"/>
-      <c r="N71" s="51" t="n"/>
-      <c r="O71" s="51" t="n"/>
-      <c r="P71" s="51" t="n"/>
-      <c r="Q71" s="51" t="n"/>
-      <c r="R71" s="51" t="n"/>
-      <c r="S71" s="51" t="n"/>
-      <c r="T71" s="51" t="n"/>
-      <c r="U71" s="51" t="n"/>
-      <c r="V71" s="52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W71" s="58" t="n"/>
+      <c r="M71" s="55" t="n"/>
+      <c r="N71" s="55" t="n"/>
+      <c r="O71" s="55" t="n"/>
+      <c r="P71" s="55" t="n"/>
+      <c r="Q71" s="55" t="n"/>
+      <c r="R71" s="55" t="n"/>
+      <c r="S71" s="55" t="n"/>
+      <c r="T71" s="55" t="n"/>
+      <c r="U71" s="55" t="n"/>
+      <c r="V71" s="56" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="W71" s="57" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="44" t="inlineStr">
         <is>
-          <t>2026/01/07（三）</t>
+          <t>2026/01/08（四）</t>
         </is>
       </c>
       <c r="B72" s="45" t="n"/>
-      <c r="C72" s="53" t="n"/>
-      <c r="D72" s="53" t="n"/>
+      <c r="C72" s="46" t="n"/>
+      <c r="D72" s="46" t="n"/>
       <c r="E72" s="47" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F72" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G72" s="54" t="n">
-        <v>35.5</v>
+        <v>92</v>
+      </c>
+      <c r="G72" s="48" t="n">
+        <v>24</v>
       </c>
       <c r="H72" s="49" t="n"/>
       <c r="I72" s="49" t="n"/>
       <c r="J72" s="50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K72" s="50" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L72" s="50" t="n"/>
-      <c r="M72" s="55" t="n"/>
-      <c r="N72" s="55" t="n"/>
-      <c r="O72" s="55" t="n"/>
-      <c r="P72" s="55" t="n"/>
-      <c r="Q72" s="55" t="n"/>
-      <c r="R72" s="55" t="n"/>
-      <c r="S72" s="55" t="n"/>
-      <c r="T72" s="55" t="n"/>
-      <c r="U72" s="55" t="n"/>
-      <c r="V72" s="56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="W72" s="57" t="n"/>
+      <c r="M72" s="51" t="n"/>
+      <c r="N72" s="51" t="n"/>
+      <c r="O72" s="51" t="n"/>
+      <c r="P72" s="51" t="n"/>
+      <c r="Q72" s="51" t="n"/>
+      <c r="R72" s="51" t="n"/>
+      <c r="S72" s="51" t="n"/>
+      <c r="T72" s="51" t="n"/>
+      <c r="U72" s="51" t="n"/>
+      <c r="V72" s="52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W72" s="58" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="44" t="inlineStr">
         <is>
-          <t>2026/01/06（二）</t>
+          <t>2026/01/07（三）</t>
         </is>
       </c>
       <c r="B73" s="45" t="n"/>
-      <c r="C73" s="46" t="n"/>
-      <c r="D73" s="46" t="n"/>
+      <c r="C73" s="53" t="n"/>
+      <c r="D73" s="53" t="n"/>
       <c r="E73" s="47" t="n">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="F73" s="47" t="n">
-        <v>117</v>
-      </c>
-      <c r="G73" s="48" t="n">
-        <v>17.6</v>
+        <v>80</v>
+      </c>
+      <c r="G73" s="54" t="n">
+        <v>35.5</v>
       </c>
       <c r="H73" s="49" t="n"/>
       <c r="I73" s="49" t="n"/>
       <c r="J73" s="50" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K73" s="50" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L73" s="50" t="n"/>
-      <c r="M73" s="51" t="n"/>
-      <c r="N73" s="51" t="n"/>
-      <c r="O73" s="51" t="n"/>
-      <c r="P73" s="51" t="n"/>
-      <c r="Q73" s="51" t="n"/>
-      <c r="R73" s="51" t="n"/>
-      <c r="S73" s="51" t="n"/>
-      <c r="T73" s="51" t="n"/>
-      <c r="U73" s="51" t="n"/>
-      <c r="V73" s="52" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W73" s="58" t="n"/>
+      <c r="M73" s="55" t="n"/>
+      <c r="N73" s="55" t="n"/>
+      <c r="O73" s="55" t="n"/>
+      <c r="P73" s="55" t="n"/>
+      <c r="Q73" s="55" t="n"/>
+      <c r="R73" s="55" t="n"/>
+      <c r="S73" s="55" t="n"/>
+      <c r="T73" s="55" t="n"/>
+      <c r="U73" s="55" t="n"/>
+      <c r="V73" s="56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="W73" s="57" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="44" t="inlineStr">
         <is>
-          <t>2026/01/05（一）</t>
+          <t>2026/01/06（二）</t>
         </is>
       </c>
       <c r="B74" s="45" t="n"/>
-      <c r="C74" s="53" t="n"/>
-      <c r="D74" s="53" t="n"/>
+      <c r="C74" s="46" t="n"/>
+      <c r="D74" s="46" t="n"/>
       <c r="E74" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F74" s="47" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G74" s="48" t="n">
-        <v>19.5</v>
+        <v>17.6</v>
       </c>
       <c r="H74" s="49" t="n"/>
       <c r="I74" s="49" t="n"/>
@@ -5376,51 +5386,92 @@
         <v>59</v>
       </c>
       <c r="K74" s="50" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="L74" s="50" t="n"/>
-      <c r="M74" s="55" t="n"/>
-      <c r="N74" s="55" t="n"/>
-      <c r="O74" s="55" t="n"/>
-      <c r="P74" s="55" t="n"/>
-      <c r="Q74" s="55" t="n"/>
-      <c r="R74" s="55" t="n"/>
-      <c r="S74" s="55" t="n"/>
-      <c r="T74" s="55" t="n"/>
-      <c r="U74" s="55" t="n"/>
-      <c r="V74" s="56" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="W74" s="57" t="n"/>
+      <c r="M74" s="51" t="n"/>
+      <c r="N74" s="51" t="n"/>
+      <c r="O74" s="51" t="n"/>
+      <c r="P74" s="51" t="n"/>
+      <c r="Q74" s="51" t="n"/>
+      <c r="R74" s="51" t="n"/>
+      <c r="S74" s="51" t="n"/>
+      <c r="T74" s="51" t="n"/>
+      <c r="U74" s="51" t="n"/>
+      <c r="V74" s="52" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="W74" s="58" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="44" t="inlineStr">
         <is>
-          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+          <t>2026/01/05（一）</t>
         </is>
       </c>
       <c r="B75" s="45" t="n"/>
-      <c r="C75" s="46" t="n"/>
-      <c r="D75" s="46" t="n"/>
-      <c r="E75" s="47" t="n"/>
-      <c r="F75" s="47" t="n"/>
-      <c r="G75" s="60" t="n"/>
+      <c r="C75" s="53" t="n"/>
+      <c r="D75" s="53" t="n"/>
+      <c r="E75" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="F75" s="47" t="n">
+        <v>107</v>
+      </c>
+      <c r="G75" s="48" t="n">
+        <v>19.5</v>
+      </c>
       <c r="H75" s="49" t="n"/>
       <c r="I75" s="49" t="n"/>
-      <c r="J75" s="50" t="n"/>
-      <c r="K75" s="50" t="n"/>
+      <c r="J75" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="K75" s="50" t="n">
+        <v>48</v>
+      </c>
       <c r="L75" s="50" t="n"/>
-      <c r="M75" s="51" t="n"/>
-      <c r="N75" s="51" t="n"/>
-      <c r="O75" s="51" t="n"/>
-      <c r="P75" s="51" t="n"/>
-      <c r="Q75" s="51" t="n"/>
-      <c r="R75" s="51" t="n"/>
-      <c r="S75" s="51" t="n"/>
-      <c r="T75" s="51" t="n"/>
-      <c r="U75" s="51" t="n"/>
-      <c r="V75" s="61" t="n"/>
-      <c r="W75" s="61" t="n"/>
+      <c r="M75" s="55" t="n"/>
+      <c r="N75" s="55" t="n"/>
+      <c r="O75" s="55" t="n"/>
+      <c r="P75" s="55" t="n"/>
+      <c r="Q75" s="55" t="n"/>
+      <c r="R75" s="55" t="n"/>
+      <c r="S75" s="55" t="n"/>
+      <c r="T75" s="55" t="n"/>
+      <c r="U75" s="55" t="n"/>
+      <c r="V75" s="56" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="W75" s="57" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="44" t="inlineStr">
+        <is>
+          <t>━━━━━━━━━  2026年新数据（自动抓取）  ━━━━━━━━━</t>
+        </is>
+      </c>
+      <c r="B76" s="45" t="n"/>
+      <c r="C76" s="46" t="n"/>
+      <c r="D76" s="46" t="n"/>
+      <c r="E76" s="47" t="n"/>
+      <c r="F76" s="47" t="n"/>
+      <c r="G76" s="60" t="n"/>
+      <c r="H76" s="49" t="n"/>
+      <c r="I76" s="49" t="n"/>
+      <c r="J76" s="50" t="n"/>
+      <c r="K76" s="50" t="n"/>
+      <c r="L76" s="50" t="n"/>
+      <c r="M76" s="51" t="n"/>
+      <c r="N76" s="51" t="n"/>
+      <c r="O76" s="51" t="n"/>
+      <c r="P76" s="51" t="n"/>
+      <c r="Q76" s="51" t="n"/>
+      <c r="R76" s="51" t="n"/>
+      <c r="S76" s="51" t="n"/>
+      <c r="T76" s="51" t="n"/>
+      <c r="U76" s="51" t="n"/>
+      <c r="V76" s="61" t="n"/>
+      <c r="W76" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/情绪周期.xlsx
+++ b/情绪周期.xlsx
@@ -1720,7 +1720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W76"/>
+  <dimension ref="A1:W77"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1982,43 +1982,47 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
-          <t>2026/04/22(三)</t>
+          <t>2026/04/23(四)</t>
         </is>
       </c>
       <c r="B4" s="63" t="inlineStr"/>
       <c r="C4" s="64" t="inlineStr"/>
       <c r="D4" s="64" t="inlineStr"/>
       <c r="E4" s="65" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G4" s="71" t="n">
-        <v>27.6</v>
+        <v>28.6</v>
       </c>
       <c r="H4" s="67" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I4" s="67" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J4" s="68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" s="68" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L4" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M4" s="69" t="inlineStr"/>
-      <c r="N4" s="69" t="inlineStr">
-        <is>
-          <t>金 螳 螂、金富科技</t>
-        </is>
-      </c>
-      <c r="O4" s="69" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="M4" s="69" t="inlineStr">
+        <is>
+          <t>安诺其、苏州高新、华电辽能</t>
+        </is>
+      </c>
+      <c r="N4" s="69" t="inlineStr"/>
+      <c r="O4" s="69" t="inlineStr">
+        <is>
+          <t>金 螳 螂</t>
+        </is>
+      </c>
       <c r="P4" s="69" t="inlineStr"/>
       <c r="Q4" s="69" t="inlineStr"/>
       <c r="R4" s="69" t="inlineStr"/>
@@ -2026,51 +2030,47 @@
       <c r="T4" s="69" t="inlineStr"/>
       <c r="U4" s="69" t="inlineStr"/>
       <c r="V4" s="69" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="W4" s="69" t="inlineStr"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="62" t="inlineStr">
         <is>
-          <t>2026/04/21(二)</t>
+          <t>2026/04/22(三)</t>
         </is>
       </c>
       <c r="B5" s="63" t="inlineStr"/>
       <c r="C5" s="64" t="inlineStr"/>
       <c r="D5" s="64" t="inlineStr"/>
       <c r="E5" s="65" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G5" s="66" t="n">
-        <v>15.9</v>
+        <v>55</v>
+      </c>
+      <c r="G5" s="71" t="n">
+        <v>27.6</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I5" s="67" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J5" s="68" t="n">
         <v>8</v>
       </c>
       <c r="K5" s="68" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L5" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M5" s="69" t="inlineStr">
-        <is>
-          <t>金 螳 螂、金富科技、圣龙股份</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="M5" s="69" t="inlineStr"/>
       <c r="N5" s="69" t="inlineStr">
         <is>
-          <t>株冶集团</t>
+          <t>金 螳 螂、金富科技</t>
         </is>
       </c>
       <c r="O5" s="69" t="inlineStr"/>
@@ -2081,55 +2081,55 @@
       <c r="T5" s="69" t="inlineStr"/>
       <c r="U5" s="69" t="inlineStr"/>
       <c r="V5" s="69" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="W5" s="69" t="inlineStr"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="62" t="inlineStr">
         <is>
-          <t>2026/04/20(一)</t>
+          <t>2026/04/21(二)</t>
         </is>
       </c>
       <c r="B6" s="63" t="inlineStr"/>
       <c r="C6" s="64" t="inlineStr"/>
       <c r="D6" s="64" t="inlineStr"/>
       <c r="E6" s="65" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="G6" s="66" t="n">
-        <v>16.7</v>
+        <v>15.9</v>
       </c>
       <c r="H6" s="67" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I6" s="67" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J6" s="68" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K6" s="68" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="L6" s="68" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M6" s="69" t="inlineStr">
         <is>
-          <t>株冶集团、华升股份、可川科技</t>
-        </is>
-      </c>
-      <c r="N6" s="69" t="inlineStr"/>
+          <t>金 螳 螂、金富科技、圣龙股份</t>
+        </is>
+      </c>
+      <c r="N6" s="69" t="inlineStr">
+        <is>
+          <t>株冶集团</t>
+        </is>
+      </c>
       <c r="O6" s="69" t="inlineStr"/>
-      <c r="P6" s="69" t="inlineStr">
-        <is>
-          <t>博云新材</t>
-        </is>
-      </c>
+      <c r="P6" s="69" t="inlineStr"/>
       <c r="Q6" s="69" t="inlineStr"/>
       <c r="R6" s="69" t="inlineStr"/>
       <c r="S6" s="69" t="inlineStr"/>
@@ -2143,57 +2143,49 @@
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="62" t="inlineStr">
         <is>
-          <t>2026/04/17(五)</t>
+          <t>2026/04/20(一)</t>
         </is>
       </c>
       <c r="B7" s="63" t="inlineStr"/>
       <c r="C7" s="64" t="inlineStr"/>
       <c r="D7" s="64" t="inlineStr"/>
       <c r="E7" s="65" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F7" s="65" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G7" s="66" t="n">
-        <v>22</v>
+        <v>16.7</v>
       </c>
       <c r="H7" s="67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I7" s="67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J7" s="68" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K7" s="68" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L7" s="68" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M7" s="69" t="inlineStr">
         <is>
-          <t>均瑶健康、京投发展</t>
-        </is>
-      </c>
-      <c r="N7" s="69" t="inlineStr">
-        <is>
-          <t>盛视科技</t>
-        </is>
-      </c>
-      <c r="O7" s="69" t="inlineStr">
+          <t>株冶集团、华升股份、可川科技</t>
+        </is>
+      </c>
+      <c r="N7" s="69" t="inlineStr"/>
+      <c r="O7" s="69" t="inlineStr"/>
+      <c r="P7" s="69" t="inlineStr">
         <is>
           <t>博云新材</t>
         </is>
       </c>
-      <c r="P7" s="69" t="inlineStr"/>
-      <c r="Q7" s="69" t="inlineStr">
-        <is>
-          <t>圣阳股份</t>
-        </is>
-      </c>
+      <c r="Q7" s="69" t="inlineStr"/>
       <c r="R7" s="69" t="inlineStr"/>
       <c r="S7" s="69" t="inlineStr"/>
       <c r="T7" s="69" t="inlineStr"/>
@@ -2206,193 +2198,197 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="62" t="inlineStr">
         <is>
-          <t>2026/04/16(四)</t>
+          <t>2026/04/17(五)</t>
         </is>
       </c>
       <c r="B8" s="63" t="inlineStr"/>
       <c r="C8" s="64" t="inlineStr"/>
       <c r="D8" s="64" t="inlineStr"/>
       <c r="E8" s="65" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F8" s="65" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G8" s="66" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="H8" s="67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" s="67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" s="68" t="n">
+        <v>13</v>
+      </c>
+      <c r="K8" s="68" t="n">
+        <v>58</v>
+      </c>
+      <c r="L8" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="K8" s="68" t="n">
-        <v>71</v>
-      </c>
-      <c r="L8" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="M8" s="69" t="inlineStr">
         <is>
+          <t>均瑶健康、京投发展</t>
+        </is>
+      </c>
+      <c r="N8" s="69" t="inlineStr">
+        <is>
           <t>盛视科技</t>
         </is>
       </c>
-      <c r="N8" s="69" t="inlineStr">
+      <c r="O8" s="69" t="inlineStr">
         <is>
           <t>博云新材</t>
         </is>
       </c>
-      <c r="O8" s="69" t="inlineStr"/>
-      <c r="P8" s="69" t="inlineStr">
+      <c r="P8" s="69" t="inlineStr"/>
+      <c r="Q8" s="69" t="inlineStr">
         <is>
           <t>圣阳股份</t>
         </is>
       </c>
-      <c r="Q8" s="69" t="inlineStr"/>
       <c r="R8" s="69" t="inlineStr"/>
       <c r="S8" s="69" t="inlineStr"/>
       <c r="T8" s="69" t="inlineStr"/>
       <c r="U8" s="69" t="inlineStr"/>
       <c r="V8" s="69" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="W8" s="69" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="62" t="inlineStr">
         <is>
-          <t>2026/04/15(三)</t>
+          <t>2026/04/16(四)</t>
         </is>
       </c>
       <c r="B9" s="63" t="inlineStr"/>
       <c r="C9" s="64" t="inlineStr"/>
       <c r="D9" s="64" t="inlineStr"/>
       <c r="E9" s="65" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="F9" s="65" t="n">
-        <v>57</v>
-      </c>
-      <c r="G9" s="71" t="n">
-        <v>29.6</v>
+        <v>79</v>
+      </c>
+      <c r="G9" s="66" t="n">
+        <v>22.5</v>
       </c>
       <c r="H9" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I9" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" s="68" t="n">
-        <v>11</v>
-      </c>
       <c r="K9" s="68" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="L9" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M9" s="69" t="inlineStr">
         <is>
-          <t>博云新材、天邦食品</t>
-        </is>
-      </c>
-      <c r="N9" s="69" t="inlineStr"/>
-      <c r="O9" s="69" t="inlineStr">
+          <t>盛视科技</t>
+        </is>
+      </c>
+      <c r="N9" s="69" t="inlineStr">
+        <is>
+          <t>博云新材</t>
+        </is>
+      </c>
+      <c r="O9" s="69" t="inlineStr"/>
+      <c r="P9" s="69" t="inlineStr">
         <is>
           <t>圣阳股份</t>
         </is>
       </c>
-      <c r="P9" s="69" t="inlineStr"/>
       <c r="Q9" s="69" t="inlineStr"/>
       <c r="R9" s="69" t="inlineStr"/>
       <c r="S9" s="69" t="inlineStr"/>
       <c r="T9" s="69" t="inlineStr"/>
       <c r="U9" s="69" t="inlineStr"/>
       <c r="V9" s="69" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="W9" s="69" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="62" t="inlineStr">
         <is>
-          <t>2026/04/14(二)</t>
+          <t>2026/04/15(三)</t>
         </is>
       </c>
       <c r="B10" s="63" t="inlineStr"/>
       <c r="C10" s="64" t="inlineStr"/>
       <c r="D10" s="64" t="inlineStr"/>
       <c r="E10" s="65" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F10" s="65" t="n">
-        <v>55</v>
-      </c>
-      <c r="G10" s="66" t="n">
-        <v>24.7</v>
+        <v>57</v>
+      </c>
+      <c r="G10" s="71" t="n">
+        <v>29.6</v>
       </c>
       <c r="H10" s="67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I10" s="67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J10" s="68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K10" s="68" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L10" s="68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M10" s="69" t="inlineStr">
         <is>
-          <t>美能能源</t>
-        </is>
-      </c>
-      <c r="N10" s="69" t="inlineStr">
-        <is>
-          <t>中恒电气、圣阳股份</t>
-        </is>
-      </c>
-      <c r="O10" s="69" t="inlineStr"/>
-      <c r="P10" s="69" t="inlineStr">
-        <is>
-          <t>华远控股</t>
-        </is>
-      </c>
+          <t>博云新材、天邦食品</t>
+        </is>
+      </c>
+      <c r="N10" s="69" t="inlineStr"/>
+      <c r="O10" s="69" t="inlineStr">
+        <is>
+          <t>圣阳股份</t>
+        </is>
+      </c>
+      <c r="P10" s="69" t="inlineStr"/>
       <c r="Q10" s="69" t="inlineStr"/>
       <c r="R10" s="69" t="inlineStr"/>
       <c r="S10" s="69" t="inlineStr"/>
       <c r="T10" s="69" t="inlineStr"/>
       <c r="U10" s="69" t="inlineStr"/>
       <c r="V10" s="69" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="W10" s="69" t="inlineStr"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="62" t="inlineStr">
         <is>
-          <t>2026/04/13(一)</t>
+          <t>2026/04/14(二)</t>
         </is>
       </c>
       <c r="B11" s="63" t="inlineStr"/>
       <c r="C11" s="64" t="inlineStr"/>
       <c r="D11" s="64" t="inlineStr"/>
       <c r="E11" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F11" s="65" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G11" s="66" t="n">
-        <v>20.3</v>
+        <v>24.7</v>
       </c>
       <c r="H11" s="67" t="n">
         <v>4</v>
@@ -2401,30 +2397,30 @@
         <v>4</v>
       </c>
       <c r="J11" s="68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K11" s="68" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L11" s="68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M11" s="69" t="inlineStr">
         <is>
+          <t>美能能源</t>
+        </is>
+      </c>
+      <c r="N11" s="69" t="inlineStr">
+        <is>
           <t>中恒电气、圣阳股份</t>
         </is>
       </c>
-      <c r="N11" s="69" t="inlineStr">
-        <is>
-          <t>长源东谷</t>
-        </is>
-      </c>
-      <c r="O11" s="69" t="inlineStr">
+      <c r="O11" s="69" t="inlineStr"/>
+      <c r="P11" s="69" t="inlineStr">
         <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="P11" s="69" t="inlineStr"/>
       <c r="Q11" s="69" t="inlineStr"/>
       <c r="R11" s="69" t="inlineStr"/>
       <c r="S11" s="69" t="inlineStr"/>
@@ -2438,7 +2434,7 @@
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="62" t="inlineStr">
         <is>
-          <t>2026/04/10(五)</t>
+          <t>2026/04/13(一)</t>
         </is>
       </c>
       <c r="B12" s="63" t="inlineStr"/>
@@ -2450,35 +2446,39 @@
       <c r="F12" s="65" t="n">
         <v>59</v>
       </c>
-      <c r="G12" s="71" t="n">
-        <v>31.4</v>
+      <c r="G12" s="66" t="n">
+        <v>20.3</v>
       </c>
       <c r="H12" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="68" t="n">
         <v>8</v>
       </c>
-      <c r="I12" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="J12" s="68" t="n">
-        <v>13</v>
-      </c>
       <c r="K12" s="68" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L12" s="68" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M12" s="69" t="inlineStr">
         <is>
-          <t>中嘉博创、长源东谷、来伊份</t>
+          <t>中恒电气、圣阳股份</t>
         </is>
       </c>
       <c r="N12" s="69" t="inlineStr">
         <is>
+          <t>长源东谷</t>
+        </is>
+      </c>
+      <c r="O12" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="O12" s="69" t="inlineStr"/>
       <c r="P12" s="69" t="inlineStr"/>
       <c r="Q12" s="69" t="inlineStr"/>
       <c r="R12" s="69" t="inlineStr"/>
@@ -2486,54 +2486,54 @@
       <c r="T12" s="69" t="inlineStr"/>
       <c r="U12" s="69" t="inlineStr"/>
       <c r="V12" s="69" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="W12" s="69" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="62" t="inlineStr">
         <is>
-          <t>2026/04/09(四)</t>
+          <t>2026/04/10(五)</t>
         </is>
       </c>
       <c r="B13" s="63" t="inlineStr"/>
       <c r="C13" s="64" t="inlineStr"/>
       <c r="D13" s="64" t="inlineStr"/>
       <c r="E13" s="65" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F13" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G13" s="66" t="n">
-        <v>23.2</v>
+        <v>59</v>
+      </c>
+      <c r="G13" s="71" t="n">
+        <v>31.4</v>
       </c>
       <c r="H13" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I13" s="67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J13" s="68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K13" s="68" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L13" s="68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M13" s="69" t="inlineStr">
         <is>
+          <t>中嘉博创、长源东谷、来伊份</t>
+        </is>
+      </c>
+      <c r="N13" s="69" t="inlineStr">
+        <is>
           <t>华远控股</t>
         </is>
       </c>
-      <c r="N13" s="69" t="inlineStr"/>
-      <c r="O13" s="69" t="inlineStr">
-        <is>
-          <t>汇源通信</t>
-        </is>
-      </c>
+      <c r="O13" s="69" t="inlineStr"/>
       <c r="P13" s="69" t="inlineStr"/>
       <c r="Q13" s="69" t="inlineStr"/>
       <c r="R13" s="69" t="inlineStr"/>
@@ -2541,54 +2541,54 @@
       <c r="T13" s="69" t="inlineStr"/>
       <c r="U13" s="69" t="inlineStr"/>
       <c r="V13" s="69" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="W13" s="69" t="inlineStr"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="62" t="inlineStr">
         <is>
-          <t>2026/04/08(三)</t>
+          <t>2026/04/09(四)</t>
         </is>
       </c>
       <c r="B14" s="63" t="inlineStr"/>
       <c r="C14" s="64" t="inlineStr"/>
       <c r="D14" s="64" t="inlineStr"/>
       <c r="E14" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="F14" s="65" t="n">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="G14" s="66" t="n">
-        <v>11.5</v>
+        <v>23.2</v>
       </c>
       <c r="H14" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I14" s="67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J14" s="68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K14" s="68" t="n">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="L14" s="68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M14" s="69" t="inlineStr">
         <is>
-          <t>中安科</t>
-        </is>
-      </c>
-      <c r="N14" s="69" t="inlineStr">
+          <t>华远控股</t>
+        </is>
+      </c>
+      <c r="N14" s="69" t="inlineStr"/>
+      <c r="O14" s="69" t="inlineStr">
         <is>
           <t>汇源通信</t>
         </is>
       </c>
-      <c r="O14" s="69" t="inlineStr"/>
       <c r="P14" s="69" t="inlineStr"/>
       <c r="Q14" s="69" t="inlineStr"/>
       <c r="R14" s="69" t="inlineStr"/>
@@ -2603,20 +2603,20 @@
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="62" t="inlineStr">
         <is>
-          <t>2026/04/07(二)</t>
+          <t>2026/04/08(三)</t>
         </is>
       </c>
       <c r="B15" s="63" t="inlineStr"/>
       <c r="C15" s="64" t="inlineStr"/>
       <c r="D15" s="64" t="inlineStr"/>
       <c r="E15" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="F15" s="65" t="n">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="G15" s="66" t="n">
-        <v>21.8</v>
+        <v>11.5</v>
       </c>
       <c r="H15" s="67" t="n">
         <v>4</v>
@@ -2625,91 +2625,95 @@
         <v>4</v>
       </c>
       <c r="J15" s="68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K15" s="68" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="L15" s="68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M15" s="69" t="inlineStr">
         <is>
-          <t>汇源通信、新能泰山</t>
-        </is>
-      </c>
-      <c r="N15" s="69" t="inlineStr"/>
+          <t>中安科</t>
+        </is>
+      </c>
+      <c r="N15" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信</t>
+        </is>
+      </c>
       <c r="O15" s="69" t="inlineStr"/>
       <c r="P15" s="69" t="inlineStr"/>
-      <c r="Q15" s="69" t="inlineStr">
-        <is>
-          <t>津药药业</t>
-        </is>
-      </c>
+      <c r="Q15" s="69" t="inlineStr"/>
       <c r="R15" s="69" t="inlineStr"/>
       <c r="S15" s="69" t="inlineStr"/>
       <c r="T15" s="69" t="inlineStr"/>
       <c r="U15" s="69" t="inlineStr"/>
       <c r="V15" s="69" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W15" s="69" t="inlineStr"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="62" t="inlineStr">
         <is>
-          <t>2026/04/06(一)</t>
+          <t>2026/04/07(二)</t>
         </is>
       </c>
       <c r="B16" s="63" t="inlineStr"/>
       <c r="C16" s="64" t="inlineStr"/>
       <c r="D16" s="64" t="inlineStr"/>
       <c r="E16" s="65" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="F16" s="65" t="n">
-        <v>36</v>
-      </c>
-      <c r="G16" s="71" t="n">
-        <v>25</v>
+        <v>93</v>
+      </c>
+      <c r="G16" s="66" t="n">
+        <v>21.8</v>
       </c>
       <c r="H16" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I16" s="67" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J16" s="68" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="L16" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="K16" s="68" t="n">
-        <v>32</v>
-      </c>
-      <c r="L16" s="68" t="n">
-        <v>3</v>
-      </c>
-      <c r="M16" s="69" t="inlineStr"/>
+      <c r="M16" s="69" t="inlineStr">
+        <is>
+          <t>汇源通信、新能泰山</t>
+        </is>
+      </c>
       <c r="N16" s="69" t="inlineStr"/>
       <c r="O16" s="69" t="inlineStr"/>
-      <c r="P16" s="69" t="inlineStr">
+      <c r="P16" s="69" t="inlineStr"/>
+      <c r="Q16" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="Q16" s="69" t="inlineStr"/>
       <c r="R16" s="69" t="inlineStr"/>
       <c r="S16" s="69" t="inlineStr"/>
       <c r="T16" s="69" t="inlineStr"/>
       <c r="U16" s="69" t="inlineStr"/>
       <c r="V16" s="69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W16" s="69" t="inlineStr"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="62" t="inlineStr">
         <is>
-          <t>2026/04/03(五)</t>
+          <t>2026/04/06(一)</t>
         </is>
       </c>
       <c r="B17" s="63" t="inlineStr"/>
@@ -2753,105 +2757,105 @@
       <c r="T17" s="69" t="inlineStr"/>
       <c r="U17" s="69" t="inlineStr"/>
       <c r="V17" s="69" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W17" s="69" t="inlineStr"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="62" t="inlineStr">
         <is>
-          <t>2026/04/02(四)</t>
+          <t>2026/04/03(五)</t>
         </is>
       </c>
       <c r="B18" s="63" t="inlineStr"/>
       <c r="C18" s="64" t="inlineStr"/>
       <c r="D18" s="64" t="inlineStr"/>
       <c r="E18" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F18" s="65" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G18" s="71" t="n">
-        <v>39.1</v>
+        <v>25</v>
       </c>
       <c r="H18" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I18" s="67" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J18" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K18" s="68" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="L18" s="68" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" s="69" t="inlineStr">
-        <is>
-          <t>新中港、通达股份、星辉环材</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="M18" s="69" t="inlineStr"/>
       <c r="N18" s="69" t="inlineStr"/>
-      <c r="O18" s="69" t="inlineStr">
+      <c r="O18" s="69" t="inlineStr"/>
+      <c r="P18" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="P18" s="69" t="inlineStr"/>
       <c r="Q18" s="69" t="inlineStr"/>
       <c r="R18" s="69" t="inlineStr"/>
       <c r="S18" s="69" t="inlineStr"/>
       <c r="T18" s="69" t="inlineStr"/>
       <c r="U18" s="69" t="inlineStr"/>
       <c r="V18" s="69" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W18" s="69" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="62" t="inlineStr">
         <is>
-          <t>2026/04/01(三)</t>
+          <t>2026/04/02(四)</t>
         </is>
       </c>
       <c r="B19" s="63" t="inlineStr"/>
       <c r="C19" s="64" t="inlineStr"/>
       <c r="D19" s="64" t="inlineStr"/>
       <c r="E19" s="65" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="F19" s="65" t="n">
-        <v>56</v>
-      </c>
-      <c r="G19" s="70" t="n">
-        <v>40.4</v>
+        <v>28</v>
+      </c>
+      <c r="G19" s="71" t="n">
+        <v>39.1</v>
       </c>
       <c r="H19" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="I19" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J19" s="68" t="n">
-        <v>5</v>
-      </c>
       <c r="K19" s="68" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L19" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="M19" s="69" t="inlineStr"/>
-      <c r="N19" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="M19" s="69" t="inlineStr">
+        <is>
+          <t>新中港、通达股份、星辉环材</t>
+        </is>
+      </c>
+      <c r="N19" s="69" t="inlineStr"/>
+      <c r="O19" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
         </is>
       </c>
-      <c r="O19" s="69" t="inlineStr"/>
       <c r="P19" s="69" t="inlineStr"/>
       <c r="Q19" s="69" t="inlineStr"/>
       <c r="R19" s="69" t="inlineStr"/>
@@ -2859,51 +2863,47 @@
       <c r="T19" s="69" t="inlineStr"/>
       <c r="U19" s="69" t="inlineStr"/>
       <c r="V19" s="69" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="W19" s="69" t="inlineStr"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="62" t="inlineStr">
         <is>
-          <t>2026/03/31(二)</t>
+          <t>2026/04/01(三)</t>
         </is>
       </c>
       <c r="B20" s="63" t="inlineStr"/>
       <c r="C20" s="64" t="inlineStr"/>
       <c r="D20" s="64" t="inlineStr"/>
       <c r="E20" s="65" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F20" s="65" t="n">
-        <v>53</v>
-      </c>
-      <c r="G20" s="66" t="n">
-        <v>24.3</v>
+        <v>56</v>
+      </c>
+      <c r="G20" s="70" t="n">
+        <v>40.4</v>
       </c>
       <c r="H20" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I20" s="67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J20" s="68" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K20" s="68" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L20" s="68" t="n">
-        <v>6</v>
-      </c>
-      <c r="M20" s="69" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M20" s="69" t="inlineStr"/>
+      <c r="N20" s="69" t="inlineStr">
         <is>
           <t>津药药业</t>
-        </is>
-      </c>
-      <c r="N20" s="69" t="inlineStr">
-        <is>
-          <t>神剑股份</t>
         </is>
       </c>
       <c r="O20" s="69" t="inlineStr"/>
@@ -2914,254 +2914,250 @@
       <c r="T20" s="69" t="inlineStr"/>
       <c r="U20" s="69" t="inlineStr"/>
       <c r="V20" s="69" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="W20" s="69" t="inlineStr"/>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="62" t="inlineStr">
+        <is>
+          <t>2026/03/31(二)</t>
+        </is>
+      </c>
+      <c r="B21" s="63" t="inlineStr"/>
+      <c r="C21" s="64" t="inlineStr"/>
+      <c r="D21" s="64" t="inlineStr"/>
+      <c r="E21" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="F21" s="65" t="n">
+        <v>53</v>
+      </c>
+      <c r="G21" s="66" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H21" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" s="68" t="n">
+        <v>45</v>
+      </c>
+      <c r="L21" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="M21" s="69" t="inlineStr">
+        <is>
+          <t>津药药业</t>
+        </is>
+      </c>
+      <c r="N21" s="69" t="inlineStr">
+        <is>
+          <t>神剑股份</t>
+        </is>
+      </c>
+      <c r="O21" s="69" t="inlineStr"/>
+      <c r="P21" s="69" t="inlineStr"/>
+      <c r="Q21" s="69" t="inlineStr"/>
+      <c r="R21" s="69" t="inlineStr"/>
+      <c r="S21" s="69" t="inlineStr"/>
+      <c r="T21" s="69" t="inlineStr"/>
+      <c r="U21" s="69" t="inlineStr"/>
+      <c r="V21" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="W20" s="69" t="inlineStr"/>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="36" t="inlineStr">
+      <c r="W21" s="69" t="inlineStr"/>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>2026/03/30(一)</t>
         </is>
       </c>
-      <c r="B21" s="37" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>人气活跃</t>
         </is>
       </c>
-      <c r="C21" s="38" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>五板新高度，成交量提升，情绪较好</t>
         </is>
       </c>
-      <c r="D21" s="38" t="inlineStr">
+      <c r="D22" s="38" t="inlineStr">
         <is>
           <t>主升分歧阶段</t>
         </is>
       </c>
-      <c r="E21" s="39" t="n">
+      <c r="E22" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="F21" s="39" t="n">
+      <c r="F22" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="G21" s="40" t="n">
+      <c r="G22" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="H21" s="41" t="n">
+      <c r="H22" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="I21" s="41" t="n">
+      <c r="I22" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="J21" s="42" t="n">
+      <c r="J22" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="K21" s="42" t="n">
+      <c r="K22" s="42" t="n">
         <v>50</v>
       </c>
-      <c r="L21" s="42" t="n">
+      <c r="L22" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="M21" s="43" t="inlineStr">
+      <c r="M22" s="43" t="inlineStr">
         <is>
           <t>神剑股份</t>
         </is>
       </c>
-      <c r="N21" s="43" t="inlineStr"/>
-      <c r="O21" s="43" t="inlineStr">
+      <c r="N22" s="43" t="inlineStr"/>
+      <c r="O22" s="43" t="inlineStr">
         <is>
           <t>美诺华</t>
         </is>
       </c>
-      <c r="P21" s="43" t="inlineStr"/>
-      <c r="Q21" s="43" t="inlineStr"/>
-      <c r="R21" s="43" t="inlineStr"/>
-      <c r="S21" s="43" t="inlineStr"/>
-      <c r="T21" s="43" t="inlineStr"/>
-      <c r="U21" s="43" t="inlineStr"/>
-      <c r="V21" s="43" t="n">
+      <c r="P22" s="43" t="inlineStr"/>
+      <c r="Q22" s="43" t="inlineStr"/>
+      <c r="R22" s="43" t="inlineStr"/>
+      <c r="S22" s="43" t="inlineStr"/>
+      <c r="T22" s="43" t="inlineStr"/>
+      <c r="U22" s="43" t="inlineStr"/>
+      <c r="V22" s="43" t="n">
         <v>1.92</v>
       </c>
-      <c r="W21" s="43" t="inlineStr"/>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="44" t="inlineStr">
-        <is>
-          <t>2026/03/27（五）</t>
-        </is>
-      </c>
-      <c r="B22" s="45" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="46" t="n"/>
-      <c r="E22" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="F22" s="47" t="n">
-        <v>78</v>
-      </c>
-      <c r="G22" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="H22" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="50" t="n">
-        <v>10</v>
-      </c>
-      <c r="K22" s="50" t="n">
-        <v>68</v>
-      </c>
-      <c r="L22" s="50" t="n">
-        <v>7</v>
-      </c>
-      <c r="M22" s="51" t="n"/>
-      <c r="N22" s="51" t="inlineStr">
-        <is>
-          <t>新能泰山/美诺华/融捷股份</t>
-        </is>
-      </c>
-      <c r="O22" s="51" t="n"/>
-      <c r="P22" s="51" t="n"/>
-      <c r="Q22" s="51" t="n"/>
-      <c r="R22" s="51" t="n"/>
-      <c r="S22" s="51" t="n"/>
-      <c r="T22" s="51" t="n"/>
-      <c r="U22" s="51" t="n"/>
-      <c r="V22" s="52" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="W22" s="43" t="inlineStr"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2026/03/26（四）</t>
+          <t>2026/03/27（五）</t>
         </is>
       </c>
       <c r="B23" s="45" t="n"/>
-      <c r="C23" s="53" t="n"/>
-      <c r="D23" s="53" t="n"/>
+      <c r="C23" s="46" t="n"/>
+      <c r="D23" s="46" t="n"/>
       <c r="E23" s="47" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F23" s="47" t="n">
-        <v>39</v>
-      </c>
-      <c r="G23" s="54" t="n">
-        <v>31.6</v>
+        <v>78</v>
+      </c>
+      <c r="G23" s="48" t="n">
+        <v>17</v>
       </c>
       <c r="H23" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I23" s="49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J23" s="50" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K23" s="50" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="L23" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M23" s="55" t="inlineStr">
-        <is>
-          <t>新能泰山、湖南发展、美诺华</t>
-        </is>
-      </c>
-      <c r="N23" s="55" t="n"/>
-      <c r="O23" s="55" t="n"/>
-      <c r="P23" s="55" t="n"/>
-      <c r="Q23" s="55" t="n"/>
-      <c r="R23" s="55" t="n"/>
-      <c r="S23" s="55" t="n"/>
-      <c r="T23" s="55" t="n"/>
-      <c r="U23" s="55" t="n"/>
-      <c r="V23" s="56" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W23" s="57" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="M23" s="51" t="n"/>
+      <c r="N23" s="51" t="inlineStr">
+        <is>
+          <t>新能泰山/美诺华/融捷股份</t>
+        </is>
+      </c>
+      <c r="O23" s="51" t="n"/>
+      <c r="P23" s="51" t="n"/>
+      <c r="Q23" s="51" t="n"/>
+      <c r="R23" s="51" t="n"/>
+      <c r="S23" s="51" t="n"/>
+      <c r="T23" s="51" t="n"/>
+      <c r="U23" s="51" t="n"/>
+      <c r="V23" s="52" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2026/03/25（三）</t>
+          <t>2026/03/26（四）</t>
         </is>
       </c>
       <c r="B24" s="45" t="n"/>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
       <c r="E24" s="47" t="n">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="F24" s="47" t="n">
-        <v>84</v>
-      </c>
-      <c r="G24" s="48" t="n">
-        <v>14.3</v>
+        <v>39</v>
+      </c>
+      <c r="G24" s="54" t="n">
+        <v>31.6</v>
       </c>
       <c r="H24" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I24" s="49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J24" s="50" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="K24" s="50" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="L24" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="M24" s="51" t="inlineStr">
-        <is>
-          <t>辽宁能源、浙江新能</t>
-        </is>
-      </c>
-      <c r="N24" s="51" t="inlineStr">
-        <is>
-          <t>中利集团</t>
-        </is>
-      </c>
-      <c r="O24" s="51" t="n"/>
-      <c r="P24" s="51" t="n"/>
-      <c r="Q24" s="51" t="n"/>
-      <c r="R24" s="51" t="inlineStr">
-        <is>
-          <t>华电辽能</t>
-        </is>
-      </c>
-      <c r="S24" s="51" t="n"/>
-      <c r="T24" s="51" t="n"/>
-      <c r="U24" s="51" t="n"/>
-      <c r="V24" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W24" s="58" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="M24" s="55" t="inlineStr">
+        <is>
+          <t>新能泰山、湖南发展、美诺华</t>
+        </is>
+      </c>
+      <c r="N24" s="55" t="n"/>
+      <c r="O24" s="55" t="n"/>
+      <c r="P24" s="55" t="n"/>
+      <c r="Q24" s="55" t="n"/>
+      <c r="R24" s="55" t="n"/>
+      <c r="S24" s="55" t="n"/>
+      <c r="T24" s="55" t="n"/>
+      <c r="U24" s="55" t="n"/>
+      <c r="V24" s="56" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W24" s="57" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2026/03/24（二）</t>
+          <t>2026/03/25（三）</t>
         </is>
       </c>
       <c r="B25" s="45" t="n"/>
-      <c r="C25" s="53" t="n"/>
-      <c r="D25" s="53" t="n"/>
+      <c r="C25" s="46" t="n"/>
+      <c r="D25" s="46" t="n"/>
       <c r="E25" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F25" s="47" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G25" s="48" t="n">
-        <v>21</v>
+        <v>14.3</v>
       </c>
       <c r="H25" s="49" t="n">
         <v>1</v>
@@ -3170,493 +3166,497 @@
         <v>1</v>
       </c>
       <c r="J25" s="50" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K25" s="50" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L25" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M25" s="55" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="M25" s="51" t="inlineStr">
+        <is>
+          <t>辽宁能源、浙江新能</t>
+        </is>
+      </c>
+      <c r="N25" s="51" t="inlineStr">
         <is>
           <t>中利集团</t>
         </is>
       </c>
-      <c r="N25" s="55" t="n"/>
-      <c r="O25" s="55" t="n"/>
-      <c r="P25" s="55" t="n"/>
-      <c r="Q25" s="55" t="inlineStr">
+      <c r="O25" s="51" t="n"/>
+      <c r="P25" s="51" t="n"/>
+      <c r="Q25" s="51" t="n"/>
+      <c r="R25" s="51" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="R25" s="55" t="n"/>
-      <c r="S25" s="55" t="n"/>
-      <c r="T25" s="55" t="n"/>
-      <c r="U25" s="55" t="n"/>
-      <c r="V25" s="56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W25" s="57" t="n"/>
+      <c r="S25" s="51" t="n"/>
+      <c r="T25" s="51" t="n"/>
+      <c r="U25" s="51" t="n"/>
+      <c r="V25" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W25" s="58" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2026/03/23（一）</t>
+          <t>2026/03/24（二）</t>
         </is>
       </c>
       <c r="B26" s="45" t="n"/>
-      <c r="C26" s="46" t="n"/>
-      <c r="D26" s="46" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
       <c r="E26" s="47" t="n">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F26" s="47" t="n">
-        <v>28</v>
-      </c>
-      <c r="G26" s="54" t="n">
-        <v>34.9</v>
+        <v>83</v>
+      </c>
+      <c r="G26" s="48" t="n">
+        <v>21</v>
       </c>
       <c r="H26" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="I26" s="49" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="J26" s="50" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K26" s="50" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L26" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" s="51" t="inlineStr">
-        <is>
-          <t>东方新能</t>
-        </is>
-      </c>
-      <c r="N26" s="51" t="inlineStr">
-        <is>
-          <t>大胜达</t>
-        </is>
-      </c>
-      <c r="O26" s="51" t="n"/>
-      <c r="P26" s="51" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="M26" s="55" t="inlineStr">
+        <is>
+          <t>中利集团</t>
+        </is>
+      </c>
+      <c r="N26" s="55" t="n"/>
+      <c r="O26" s="55" t="n"/>
+      <c r="P26" s="55" t="n"/>
+      <c r="Q26" s="55" t="inlineStr">
         <is>
           <t>华电辽能</t>
         </is>
       </c>
-      <c r="Q26" s="51" t="n"/>
-      <c r="R26" s="51" t="n"/>
-      <c r="S26" s="51" t="n"/>
-      <c r="T26" s="51" t="n"/>
-      <c r="U26" s="51" t="n"/>
-      <c r="V26" s="52" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="W26" s="58" t="n"/>
+      <c r="R26" s="55" t="n"/>
+      <c r="S26" s="55" t="n"/>
+      <c r="T26" s="55" t="n"/>
+      <c r="U26" s="55" t="n"/>
+      <c r="V26" s="56" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W26" s="57" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2026/03/20（五）</t>
+          <t>2026/03/23（一）</t>
         </is>
       </c>
       <c r="B27" s="45" t="n"/>
-      <c r="C27" s="53" t="n"/>
-      <c r="D27" s="53" t="n"/>
+      <c r="C27" s="46" t="n"/>
+      <c r="D27" s="46" t="n"/>
       <c r="E27" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F27" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G27" s="59" t="n">
-        <v>45.1</v>
+      <c r="G27" s="54" t="n">
+        <v>34.9</v>
       </c>
       <c r="H27" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="I27" s="49" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="J27" s="50" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K27" s="50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L27" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="M27" s="55" t="inlineStr">
-        <is>
-          <t>大胜达、韶能股份</t>
-        </is>
-      </c>
-      <c r="N27" s="55" t="n"/>
-      <c r="O27" s="55" t="inlineStr">
-        <is>
-          <t>深华发Ａ、华电辽能</t>
-        </is>
-      </c>
-      <c r="P27" s="55" t="n"/>
-      <c r="Q27" s="55" t="n"/>
-      <c r="R27" s="55" t="n"/>
-      <c r="S27" s="55" t="n"/>
-      <c r="T27" s="55" t="n"/>
-      <c r="U27" s="55" t="n"/>
-      <c r="V27" s="56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="W27" s="57" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="M27" s="51" t="inlineStr">
+        <is>
+          <t>东方新能</t>
+        </is>
+      </c>
+      <c r="N27" s="51" t="inlineStr">
+        <is>
+          <t>大胜达</t>
+        </is>
+      </c>
+      <c r="O27" s="51" t="n"/>
+      <c r="P27" s="51" t="inlineStr">
+        <is>
+          <t>华电辽能</t>
+        </is>
+      </c>
+      <c r="Q27" s="51" t="n"/>
+      <c r="R27" s="51" t="n"/>
+      <c r="S27" s="51" t="n"/>
+      <c r="T27" s="51" t="n"/>
+      <c r="U27" s="51" t="n"/>
+      <c r="V27" s="52" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W27" s="58" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2026/03/19（四）</t>
+          <t>2026/03/20（五）</t>
         </is>
       </c>
       <c r="B28" s="45" t="n"/>
-      <c r="C28" s="46" t="n"/>
-      <c r="D28" s="46" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="53" t="n"/>
       <c r="E28" s="47" t="n">
         <v>28</v>
       </c>
       <c r="F28" s="47" t="n">
         <v>28</v>
       </c>
-      <c r="G28" s="54" t="n">
-        <v>26.3</v>
+      <c r="G28" s="59" t="n">
+        <v>45.1</v>
       </c>
       <c r="H28" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I28" s="49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J28" s="50" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K28" s="50" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L28" s="50" t="n">
-        <v>6</v>
-      </c>
-      <c r="M28" s="51" t="n"/>
-      <c r="N28" s="51" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="M28" s="55" t="inlineStr">
+        <is>
+          <t>大胜达、韶能股份</t>
+        </is>
+      </c>
+      <c r="N28" s="55" t="n"/>
+      <c r="O28" s="55" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="O28" s="51" t="n"/>
-      <c r="P28" s="51" t="n"/>
-      <c r="Q28" s="51" t="n"/>
-      <c r="R28" s="51" t="n"/>
-      <c r="S28" s="51" t="n"/>
-      <c r="T28" s="51" t="n"/>
-      <c r="U28" s="51" t="n"/>
-      <c r="V28" s="52" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W28" s="58" t="n"/>
+      <c r="P28" s="55" t="n"/>
+      <c r="Q28" s="55" t="n"/>
+      <c r="R28" s="55" t="n"/>
+      <c r="S28" s="55" t="n"/>
+      <c r="T28" s="55" t="n"/>
+      <c r="U28" s="55" t="n"/>
+      <c r="V28" s="56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W28" s="57" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2026/03/18（三）</t>
+          <t>2026/03/19（四）</t>
         </is>
       </c>
       <c r="B29" s="45" t="n"/>
-      <c r="C29" s="53" t="n"/>
-      <c r="D29" s="53" t="n"/>
+      <c r="C29" s="46" t="n"/>
+      <c r="D29" s="46" t="n"/>
       <c r="E29" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="G29" s="54" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="H29" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="50" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K29" s="50" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L29" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M29" s="55" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="M29" s="51" t="n"/>
+      <c r="N29" s="51" t="inlineStr">
         <is>
           <t>深华发Ａ、华电辽能</t>
         </is>
       </c>
-      <c r="N29" s="55" t="n"/>
-      <c r="O29" s="55" t="inlineStr">
-        <is>
-          <t>三房巷</t>
-        </is>
-      </c>
-      <c r="P29" s="55" t="n"/>
-      <c r="Q29" s="55" t="n"/>
-      <c r="R29" s="55" t="n"/>
-      <c r="S29" s="55" t="n"/>
-      <c r="T29" s="55" t="n"/>
-      <c r="U29" s="55" t="n"/>
-      <c r="V29" s="56" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="W29" s="57" t="n"/>
+      <c r="O29" s="51" t="n"/>
+      <c r="P29" s="51" t="n"/>
+      <c r="Q29" s="51" t="n"/>
+      <c r="R29" s="51" t="n"/>
+      <c r="S29" s="51" t="n"/>
+      <c r="T29" s="51" t="n"/>
+      <c r="U29" s="51" t="n"/>
+      <c r="V29" s="52" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W29" s="58" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2026/03/17（二）</t>
+          <t>2026/03/18（三）</t>
         </is>
       </c>
       <c r="B30" s="45" t="n"/>
-      <c r="C30" s="46" t="n"/>
-      <c r="D30" s="46" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="53" t="n"/>
       <c r="E30" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F30" s="47" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G30" s="54" t="n">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="H30" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I30" s="49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J30" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K30" s="50" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L30" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" s="51" t="inlineStr">
-        <is>
-          <t>京投发展、赤天化、亚翔集成</t>
-        </is>
-      </c>
-      <c r="N30" s="51" t="inlineStr">
-        <is>
-          <t>三房巷、法尔胜</t>
-        </is>
-      </c>
-      <c r="O30" s="51" t="n"/>
-      <c r="P30" s="51" t="n"/>
-      <c r="Q30" s="51" t="n"/>
-      <c r="R30" s="51" t="n"/>
-      <c r="S30" s="51" t="n"/>
-      <c r="T30" s="51" t="n"/>
-      <c r="U30" s="51" t="n"/>
-      <c r="V30" s="52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="W30" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M30" s="55" t="inlineStr">
+        <is>
+          <t>深华发Ａ、华电辽能</t>
+        </is>
+      </c>
+      <c r="N30" s="55" t="n"/>
+      <c r="O30" s="55" t="inlineStr">
+        <is>
+          <t>三房巷</t>
+        </is>
+      </c>
+      <c r="P30" s="55" t="n"/>
+      <c r="Q30" s="55" t="n"/>
+      <c r="R30" s="55" t="n"/>
+      <c r="S30" s="55" t="n"/>
+      <c r="T30" s="55" t="n"/>
+      <c r="U30" s="55" t="n"/>
+      <c r="V30" s="56" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W30" s="57" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>2026/03/16（一）</t>
+          <t>2026/03/17（二）</t>
         </is>
       </c>
       <c r="B31" s="45" t="n"/>
-      <c r="C31" s="53" t="n"/>
-      <c r="D31" s="53" t="n"/>
+      <c r="C31" s="46" t="n"/>
+      <c r="D31" s="46" t="n"/>
       <c r="E31" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F31" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G31" s="54" t="n">
-        <v>35.3</v>
+        <v>30.4</v>
       </c>
       <c r="H31" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K31" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="L31" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="I31" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="J31" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K31" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="L31" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M31" s="55" t="inlineStr">
+      <c r="M31" s="51" t="inlineStr">
+        <is>
+          <t>京投发展、赤天化、亚翔集成</t>
+        </is>
+      </c>
+      <c r="N31" s="51" t="inlineStr">
         <is>
           <t>三房巷、法尔胜</t>
         </is>
       </c>
-      <c r="N31" s="55" t="n"/>
-      <c r="O31" s="55" t="n"/>
-      <c r="P31" s="55" t="n"/>
-      <c r="Q31" s="55" t="n"/>
-      <c r="R31" s="55" t="n"/>
-      <c r="S31" s="55" t="n"/>
-      <c r="T31" s="55" t="n"/>
-      <c r="U31" s="55" t="n"/>
-      <c r="V31" s="56" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="W31" s="57" t="n"/>
+      <c r="O31" s="51" t="n"/>
+      <c r="P31" s="51" t="n"/>
+      <c r="Q31" s="51" t="n"/>
+      <c r="R31" s="51" t="n"/>
+      <c r="S31" s="51" t="n"/>
+      <c r="T31" s="51" t="n"/>
+      <c r="U31" s="51" t="n"/>
+      <c r="V31" s="52" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="W31" s="58" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>2026/03/13（五）</t>
+          <t>2026/03/16（一）</t>
         </is>
       </c>
       <c r="B32" s="45" t="n"/>
-      <c r="C32" s="46" t="n"/>
-      <c r="D32" s="46" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
       <c r="E32" s="47" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F32" s="47" t="n">
-        <v>59</v>
-      </c>
-      <c r="G32" s="48" t="n">
-        <v>23.4</v>
+        <v>44</v>
+      </c>
+      <c r="G32" s="54" t="n">
+        <v>35.3</v>
       </c>
       <c r="H32" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I32" s="49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J32" s="50" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K32" s="50" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="L32" s="50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M32" s="51" t="inlineStr">
-        <is>
-          <t>金牛化工</t>
-        </is>
-      </c>
-      <c r="N32" s="51" t="inlineStr">
-        <is>
-          <t>华电能源</t>
-        </is>
-      </c>
-      <c r="O32" s="51" t="inlineStr">
-        <is>
-          <t>中南文化</t>
-        </is>
-      </c>
-      <c r="P32" s="51" t="n"/>
-      <c r="Q32" s="51" t="n"/>
-      <c r="R32" s="51" t="n"/>
-      <c r="S32" s="51" t="n"/>
-      <c r="T32" s="51" t="n"/>
-      <c r="U32" s="51" t="n"/>
-      <c r="V32" s="52" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W32" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M32" s="55" t="inlineStr">
+        <is>
+          <t>三房巷、法尔胜</t>
+        </is>
+      </c>
+      <c r="N32" s="55" t="n"/>
+      <c r="O32" s="55" t="n"/>
+      <c r="P32" s="55" t="n"/>
+      <c r="Q32" s="55" t="n"/>
+      <c r="R32" s="55" t="n"/>
+      <c r="S32" s="55" t="n"/>
+      <c r="T32" s="55" t="n"/>
+      <c r="U32" s="55" t="n"/>
+      <c r="V32" s="56" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="W32" s="57" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>2026/03/12（四）</t>
+          <t>2026/03/13（五）</t>
         </is>
       </c>
       <c r="B33" s="45" t="n"/>
-      <c r="C33" s="53" t="n"/>
-      <c r="D33" s="53" t="n"/>
+      <c r="C33" s="46" t="n"/>
+      <c r="D33" s="46" t="n"/>
       <c r="E33" s="47" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F33" s="47" t="n">
-        <v>52</v>
-      </c>
-      <c r="G33" s="54" t="n">
-        <v>28.8</v>
+        <v>59</v>
+      </c>
+      <c r="G33" s="48" t="n">
+        <v>23.4</v>
       </c>
       <c r="H33" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I33" s="49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J33" s="50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K33" s="50" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L33" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="M33" s="55" t="inlineStr">
-        <is>
-          <t>绿发电力、华电能源</t>
-        </is>
-      </c>
-      <c r="N33" s="55" t="inlineStr">
+      <c r="M33" s="51" t="inlineStr">
+        <is>
+          <t>金牛化工</t>
+        </is>
+      </c>
+      <c r="N33" s="51" t="inlineStr">
+        <is>
+          <t>华电能源</t>
+        </is>
+      </c>
+      <c r="O33" s="51" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="O33" s="55" t="n"/>
-      <c r="P33" s="55" t="n"/>
-      <c r="Q33" s="55" t="n"/>
-      <c r="R33" s="55" t="n"/>
-      <c r="S33" s="55" t="n"/>
-      <c r="T33" s="55" t="n"/>
-      <c r="U33" s="55" t="n"/>
-      <c r="V33" s="56" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W33" s="57" t="n"/>
+      <c r="P33" s="51" t="n"/>
+      <c r="Q33" s="51" t="n"/>
+      <c r="R33" s="51" t="n"/>
+      <c r="S33" s="51" t="n"/>
+      <c r="T33" s="51" t="n"/>
+      <c r="U33" s="51" t="n"/>
+      <c r="V33" s="52" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W33" s="58" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>2026/03/11（三）</t>
+          <t>2026/03/12（四）</t>
         </is>
       </c>
       <c r="B34" s="45" t="n"/>
-      <c r="C34" s="46" t="n"/>
-      <c r="D34" s="46" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
       <c r="E34" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F34" s="47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G34" s="54" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="H34" s="49" t="n">
         <v>2</v>
@@ -3665,208 +3665,218 @@
         <v>2</v>
       </c>
       <c r="J34" s="50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K34" s="50" t="n">
         <v>24</v>
       </c>
       <c r="L34" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M34" s="51" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="M34" s="55" t="inlineStr">
+        <is>
+          <t>绿发电力、华电能源</t>
+        </is>
+      </c>
+      <c r="N34" s="55" t="inlineStr">
         <is>
           <t>中南文化</t>
         </is>
       </c>
-      <c r="N34" s="51" t="inlineStr">
-        <is>
-          <t>宁波建工</t>
-        </is>
-      </c>
-      <c r="O34" s="51" t="n"/>
-      <c r="P34" s="51" t="n"/>
-      <c r="Q34" s="51" t="n"/>
-      <c r="R34" s="51" t="n"/>
-      <c r="S34" s="51" t="n"/>
-      <c r="T34" s="51" t="n"/>
-      <c r="U34" s="51" t="n"/>
-      <c r="V34" s="52" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="W34" s="58" t="n"/>
+      <c r="O34" s="55" t="n"/>
+      <c r="P34" s="55" t="n"/>
+      <c r="Q34" s="55" t="n"/>
+      <c r="R34" s="55" t="n"/>
+      <c r="S34" s="55" t="n"/>
+      <c r="T34" s="55" t="n"/>
+      <c r="U34" s="55" t="n"/>
+      <c r="V34" s="56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W34" s="57" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>2026/03/10（二）</t>
+          <t>2026/03/11（三）</t>
         </is>
       </c>
       <c r="B35" s="45" t="n"/>
-      <c r="C35" s="53" t="n"/>
-      <c r="D35" s="53" t="n"/>
+      <c r="C35" s="46" t="n"/>
+      <c r="D35" s="46" t="n"/>
       <c r="E35" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F35" s="47" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G35" s="54" t="n">
-        <v>28.6</v>
+        <v>25.4</v>
       </c>
       <c r="H35" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I35" s="49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J35" s="50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K35" s="50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L35" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="M35" s="55" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="M35" s="51" t="inlineStr">
+        <is>
+          <t>中南文化</t>
+        </is>
+      </c>
+      <c r="N35" s="51" t="inlineStr">
         <is>
           <t>宁波建工</t>
         </is>
       </c>
-      <c r="N35" s="55" t="n"/>
-      <c r="O35" s="55" t="inlineStr">
-        <is>
-          <t>王力安防</t>
-        </is>
-      </c>
-      <c r="P35" s="55" t="n"/>
-      <c r="Q35" s="55" t="n"/>
-      <c r="R35" s="55" t="n"/>
-      <c r="S35" s="55" t="n"/>
-      <c r="T35" s="55" t="n"/>
-      <c r="U35" s="55" t="n"/>
-      <c r="V35" s="56" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W35" s="57" t="n"/>
+      <c r="O35" s="51" t="n"/>
+      <c r="P35" s="51" t="n"/>
+      <c r="Q35" s="51" t="n"/>
+      <c r="R35" s="51" t="n"/>
+      <c r="S35" s="51" t="n"/>
+      <c r="T35" s="51" t="n"/>
+      <c r="U35" s="51" t="n"/>
+      <c r="V35" s="52" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="W35" s="58" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>2026/03/09（一）</t>
+          <t>2026/03/10（二）</t>
         </is>
       </c>
       <c r="B36" s="45" t="n"/>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
+      <c r="C36" s="53" t="n"/>
+      <c r="D36" s="53" t="n"/>
       <c r="E36" s="47" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F36" s="47" t="n">
-        <v>42</v>
-      </c>
-      <c r="G36" s="59" t="n">
-        <v>44</v>
+        <v>55</v>
+      </c>
+      <c r="G36" s="54" t="n">
+        <v>28.6</v>
       </c>
       <c r="H36" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I36" s="49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J36" s="50" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K36" s="50" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L36" s="50" t="n">
-        <v>8</v>
-      </c>
-      <c r="M36" s="51" t="inlineStr">
-        <is>
-          <t>美利云</t>
-        </is>
-      </c>
-      <c r="N36" s="51" t="inlineStr">
-        <is>
-          <t>王力安防、顺钠股份</t>
-        </is>
-      </c>
-      <c r="O36" s="51" t="n"/>
-      <c r="P36" s="51" t="n"/>
-      <c r="Q36" s="51" t="n"/>
-      <c r="R36" s="51" t="n"/>
-      <c r="S36" s="51" t="n"/>
-      <c r="T36" s="51" t="n"/>
-      <c r="U36" s="51" t="n"/>
-      <c r="V36" s="52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W36" s="58" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="M36" s="55" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+      <c r="N36" s="55" t="n"/>
+      <c r="O36" s="55" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+      <c r="P36" s="55" t="n"/>
+      <c r="Q36" s="55" t="n"/>
+      <c r="R36" s="55" t="n"/>
+      <c r="S36" s="55" t="n"/>
+      <c r="T36" s="55" t="n"/>
+      <c r="U36" s="55" t="n"/>
+      <c r="V36" s="56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W36" s="57" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>2026/03/06（五）</t>
+          <t>2026/03/09（一）</t>
         </is>
       </c>
       <c r="B37" s="45" t="n"/>
-      <c r="C37" s="53" t="n"/>
-      <c r="D37" s="53" t="n"/>
+      <c r="C37" s="46" t="n"/>
+      <c r="D37" s="46" t="n"/>
       <c r="E37" s="47" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F37" s="47" t="n">
-        <v>74</v>
-      </c>
-      <c r="G37" s="54" t="n">
-        <v>25.3</v>
+        <v>42</v>
+      </c>
+      <c r="G37" s="59" t="n">
+        <v>44</v>
       </c>
       <c r="H37" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I37" s="49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J37" s="50" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="K37" s="50" t="n">
-        <v>40</v>
-      </c>
-      <c r="L37" s="50" t="n"/>
-      <c r="M37" s="55" t="n"/>
-      <c r="N37" s="55" t="n"/>
-      <c r="O37" s="55" t="n"/>
-      <c r="P37" s="55" t="n"/>
-      <c r="Q37" s="55" t="n"/>
-      <c r="R37" s="55" t="n"/>
-      <c r="S37" s="55" t="n"/>
-      <c r="T37" s="55" t="n"/>
-      <c r="U37" s="55" t="n"/>
-      <c r="V37" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W37" s="57" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="L37" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M37" s="51" t="inlineStr">
+        <is>
+          <t>美利云</t>
+        </is>
+      </c>
+      <c r="N37" s="51" t="inlineStr">
+        <is>
+          <t>王力安防、顺钠股份</t>
+        </is>
+      </c>
+      <c r="O37" s="51" t="n"/>
+      <c r="P37" s="51" t="n"/>
+      <c r="Q37" s="51" t="n"/>
+      <c r="R37" s="51" t="n"/>
+      <c r="S37" s="51" t="n"/>
+      <c r="T37" s="51" t="n"/>
+      <c r="U37" s="51" t="n"/>
+      <c r="V37" s="52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="W37" s="58" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>2026/03/05（四）</t>
+          <t>2026/03/06（五）</t>
         </is>
       </c>
       <c r="B38" s="45" t="n"/>
-      <c r="C38" s="46" t="n"/>
-      <c r="D38" s="46" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
       <c r="E38" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F38" s="47" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G38" s="54" t="n">
-        <v>29.9</v>
+        <v>25.3</v>
       </c>
       <c r="H38" s="49" t="n">
         <v>0</v>
@@ -3875,43 +3885,43 @@
         <v>0</v>
       </c>
       <c r="J38" s="50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K38" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L38" s="50" t="n"/>
-      <c r="M38" s="51" t="n"/>
-      <c r="N38" s="51" t="n"/>
-      <c r="O38" s="51" t="n"/>
-      <c r="P38" s="51" t="n"/>
-      <c r="Q38" s="51" t="n"/>
-      <c r="R38" s="51" t="n"/>
-      <c r="S38" s="51" t="n"/>
-      <c r="T38" s="51" t="n"/>
-      <c r="U38" s="51" t="n"/>
-      <c r="V38" s="52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="W38" s="58" t="n"/>
+      <c r="M38" s="55" t="n"/>
+      <c r="N38" s="55" t="n"/>
+      <c r="O38" s="55" t="n"/>
+      <c r="P38" s="55" t="n"/>
+      <c r="Q38" s="55" t="n"/>
+      <c r="R38" s="55" t="n"/>
+      <c r="S38" s="55" t="n"/>
+      <c r="T38" s="55" t="n"/>
+      <c r="U38" s="55" t="n"/>
+      <c r="V38" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W38" s="57" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>2026/03/04（三）</t>
+          <t>2026/03/05（四）</t>
         </is>
       </c>
       <c r="B39" s="45" t="n"/>
-      <c r="C39" s="53" t="n"/>
-      <c r="D39" s="53" t="n"/>
+      <c r="C39" s="46" t="n"/>
+      <c r="D39" s="46" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F39" s="47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="G39" s="54" t="n">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="H39" s="49" t="n">
         <v>0</v>
@@ -3920,43 +3930,43 @@
         <v>0</v>
       </c>
       <c r="J39" s="50" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K39" s="50" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="L39" s="50" t="n"/>
-      <c r="M39" s="55" t="n"/>
-      <c r="N39" s="55" t="n"/>
-      <c r="O39" s="55" t="n"/>
-      <c r="P39" s="55" t="n"/>
-      <c r="Q39" s="55" t="n"/>
-      <c r="R39" s="55" t="n"/>
-      <c r="S39" s="55" t="n"/>
-      <c r="T39" s="55" t="n"/>
-      <c r="U39" s="55" t="n"/>
-      <c r="V39" s="56" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="W39" s="57" t="n"/>
+      <c r="M39" s="51" t="n"/>
+      <c r="N39" s="51" t="n"/>
+      <c r="O39" s="51" t="n"/>
+      <c r="P39" s="51" t="n"/>
+      <c r="Q39" s="51" t="n"/>
+      <c r="R39" s="51" t="n"/>
+      <c r="S39" s="51" t="n"/>
+      <c r="T39" s="51" t="n"/>
+      <c r="U39" s="51" t="n"/>
+      <c r="V39" s="52" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W39" s="58" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>2026/03/03（二）</t>
+          <t>2026/03/04（三）</t>
         </is>
       </c>
       <c r="B40" s="45" t="n"/>
-      <c r="C40" s="46" t="n"/>
-      <c r="D40" s="46" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="F40" s="47" t="n">
-        <v>76</v>
-      </c>
-      <c r="G40" s="48" t="n">
-        <v>24</v>
+        <v>44</v>
+      </c>
+      <c r="G40" s="54" t="n">
+        <v>30.2</v>
       </c>
       <c r="H40" s="49" t="n">
         <v>0</v>
@@ -3965,43 +3975,43 @@
         <v>0</v>
       </c>
       <c r="J40" s="50" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K40" s="50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L40" s="50" t="n"/>
-      <c r="M40" s="51" t="n"/>
-      <c r="N40" s="51" t="n"/>
-      <c r="O40" s="51" t="n"/>
-      <c r="P40" s="51" t="n"/>
-      <c r="Q40" s="51" t="n"/>
-      <c r="R40" s="51" t="n"/>
-      <c r="S40" s="51" t="n"/>
-      <c r="T40" s="51" t="n"/>
-      <c r="U40" s="51" t="n"/>
-      <c r="V40" s="52" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="W40" s="58" t="n"/>
+      <c r="M40" s="55" t="n"/>
+      <c r="N40" s="55" t="n"/>
+      <c r="O40" s="55" t="n"/>
+      <c r="P40" s="55" t="n"/>
+      <c r="Q40" s="55" t="n"/>
+      <c r="R40" s="55" t="n"/>
+      <c r="S40" s="55" t="n"/>
+      <c r="T40" s="55" t="n"/>
+      <c r="U40" s="55" t="n"/>
+      <c r="V40" s="56" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="W40" s="57" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>2026/03/02（一）</t>
+          <t>2026/03/03（二）</t>
         </is>
       </c>
       <c r="B41" s="45" t="n"/>
-      <c r="C41" s="53" t="n"/>
-      <c r="D41" s="53" t="n"/>
+      <c r="C41" s="46" t="n"/>
+      <c r="D41" s="46" t="n"/>
       <c r="E41" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F41" s="47" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G41" s="48" t="n">
-        <v>20.9</v>
+        <v>24</v>
       </c>
       <c r="H41" s="49" t="n">
         <v>0</v>
@@ -4010,43 +4020,43 @@
         <v>0</v>
       </c>
       <c r="J41" s="50" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="K41" s="50" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L41" s="50" t="n"/>
-      <c r="M41" s="55" t="n"/>
-      <c r="N41" s="55" t="n"/>
-      <c r="O41" s="55" t="n"/>
-      <c r="P41" s="55" t="n"/>
-      <c r="Q41" s="55" t="n"/>
-      <c r="R41" s="55" t="n"/>
-      <c r="S41" s="55" t="n"/>
-      <c r="T41" s="55" t="n"/>
-      <c r="U41" s="55" t="n"/>
-      <c r="V41" s="56" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="W41" s="57" t="n"/>
+      <c r="M41" s="51" t="n"/>
+      <c r="N41" s="51" t="n"/>
+      <c r="O41" s="51" t="n"/>
+      <c r="P41" s="51" t="n"/>
+      <c r="Q41" s="51" t="n"/>
+      <c r="R41" s="51" t="n"/>
+      <c r="S41" s="51" t="n"/>
+      <c r="T41" s="51" t="n"/>
+      <c r="U41" s="51" t="n"/>
+      <c r="V41" s="52" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="W41" s="58" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="44" t="inlineStr">
         <is>
-          <t>2026/02/27（五）</t>
+          <t>2026/03/02（一）</t>
         </is>
       </c>
       <c r="B42" s="45" t="n"/>
-      <c r="C42" s="46" t="n"/>
-      <c r="D42" s="46" t="n"/>
+      <c r="C42" s="53" t="n"/>
+      <c r="D42" s="53" t="n"/>
       <c r="E42" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F42" s="47" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G42" s="48" t="n">
-        <v>16.7</v>
+        <v>20.9</v>
       </c>
       <c r="H42" s="49" t="n">
         <v>0</v>
@@ -4055,1371 +4065,1375 @@
         <v>0</v>
       </c>
       <c r="J42" s="50" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K42" s="50" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L42" s="50" t="n"/>
-      <c r="M42" s="51" t="n"/>
-      <c r="N42" s="51" t="n"/>
-      <c r="O42" s="51" t="n"/>
-      <c r="P42" s="51" t="n"/>
-      <c r="Q42" s="51" t="n"/>
-      <c r="R42" s="51" t="n"/>
-      <c r="S42" s="51" t="n"/>
-      <c r="T42" s="51" t="n"/>
-      <c r="U42" s="51" t="n"/>
-      <c r="V42" s="52" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="W42" s="58" t="n"/>
+      <c r="M42" s="55" t="n"/>
+      <c r="N42" s="55" t="n"/>
+      <c r="O42" s="55" t="n"/>
+      <c r="P42" s="55" t="n"/>
+      <c r="Q42" s="55" t="n"/>
+      <c r="R42" s="55" t="n"/>
+      <c r="S42" s="55" t="n"/>
+      <c r="T42" s="55" t="n"/>
+      <c r="U42" s="55" t="n"/>
+      <c r="V42" s="56" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="W42" s="57" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>2026/02/26（四）</t>
+          <t>2026/02/27（五）</t>
         </is>
       </c>
       <c r="B43" s="45" t="n"/>
-      <c r="C43" s="53" t="n"/>
-      <c r="D43" s="53" t="n"/>
+      <c r="C43" s="46" t="n"/>
+      <c r="D43" s="46" t="n"/>
       <c r="E43" s="47" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="F43" s="47" t="n">
-        <v>61</v>
-      </c>
-      <c r="G43" s="54" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="H43" s="49" t="n"/>
-      <c r="I43" s="49" t="n"/>
+        <v>75</v>
+      </c>
+      <c r="G43" s="48" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H43" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="49" t="n">
+        <v>0</v>
+      </c>
       <c r="J43" s="50" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K43" s="50" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L43" s="50" t="n"/>
-      <c r="M43" s="55" t="n"/>
-      <c r="N43" s="55" t="n"/>
-      <c r="O43" s="55" t="n"/>
-      <c r="P43" s="55" t="n"/>
-      <c r="Q43" s="55" t="n"/>
-      <c r="R43" s="55" t="n"/>
-      <c r="S43" s="55" t="n"/>
-      <c r="T43" s="55" t="n"/>
-      <c r="U43" s="55" t="n"/>
-      <c r="V43" s="56" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W43" s="57" t="n"/>
+      <c r="M43" s="51" t="n"/>
+      <c r="N43" s="51" t="n"/>
+      <c r="O43" s="51" t="n"/>
+      <c r="P43" s="51" t="n"/>
+      <c r="Q43" s="51" t="n"/>
+      <c r="R43" s="51" t="n"/>
+      <c r="S43" s="51" t="n"/>
+      <c r="T43" s="51" t="n"/>
+      <c r="U43" s="51" t="n"/>
+      <c r="V43" s="52" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="W43" s="58" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
         <is>
-          <t>2026/02/25（三）</t>
+          <t>2026/02/26（四）</t>
         </is>
       </c>
       <c r="B44" s="45" t="n"/>
-      <c r="C44" s="46" t="n"/>
-      <c r="D44" s="46" t="n"/>
+      <c r="C44" s="53" t="n"/>
+      <c r="D44" s="53" t="n"/>
       <c r="E44" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F44" s="47" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G44" s="54" t="n">
-        <v>31.8</v>
+        <v>27.4</v>
       </c>
       <c r="H44" s="49" t="n"/>
       <c r="I44" s="49" t="n"/>
       <c r="J44" s="50" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K44" s="50" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L44" s="50" t="n"/>
-      <c r="M44" s="51" t="n"/>
-      <c r="N44" s="51" t="n"/>
-      <c r="O44" s="51" t="n"/>
-      <c r="P44" s="51" t="n"/>
-      <c r="Q44" s="51" t="n"/>
-      <c r="R44" s="51" t="n"/>
-      <c r="S44" s="51" t="n"/>
-      <c r="T44" s="51" t="n"/>
-      <c r="U44" s="51" t="n"/>
-      <c r="V44" s="52" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="W44" s="58" t="n"/>
+      <c r="M44" s="55" t="n"/>
+      <c r="N44" s="55" t="n"/>
+      <c r="O44" s="55" t="n"/>
+      <c r="P44" s="55" t="n"/>
+      <c r="Q44" s="55" t="n"/>
+      <c r="R44" s="55" t="n"/>
+      <c r="S44" s="55" t="n"/>
+      <c r="T44" s="55" t="n"/>
+      <c r="U44" s="55" t="n"/>
+      <c r="V44" s="56" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W44" s="57" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>2026/02/24（二）</t>
+          <t>2026/02/25（三）</t>
         </is>
       </c>
       <c r="B45" s="45" t="n"/>
-      <c r="C45" s="53" t="n"/>
-      <c r="D45" s="53" t="n"/>
+      <c r="C45" s="46" t="n"/>
+      <c r="D45" s="46" t="n"/>
       <c r="E45" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F45" s="47" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G45" s="54" t="n">
-        <v>30.8</v>
+        <v>31.8</v>
       </c>
       <c r="H45" s="49" t="n"/>
       <c r="I45" s="49" t="n"/>
       <c r="J45" s="50" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K45" s="50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L45" s="50" t="n"/>
-      <c r="M45" s="55" t="n"/>
-      <c r="N45" s="55" t="n"/>
-      <c r="O45" s="55" t="n"/>
-      <c r="P45" s="55" t="n"/>
-      <c r="Q45" s="55" t="n"/>
-      <c r="R45" s="55" t="n"/>
-      <c r="S45" s="55" t="n"/>
-      <c r="T45" s="55" t="n"/>
-      <c r="U45" s="55" t="n"/>
-      <c r="V45" s="56" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W45" s="57" t="n"/>
+      <c r="M45" s="51" t="n"/>
+      <c r="N45" s="51" t="n"/>
+      <c r="O45" s="51" t="n"/>
+      <c r="P45" s="51" t="n"/>
+      <c r="Q45" s="51" t="n"/>
+      <c r="R45" s="51" t="n"/>
+      <c r="S45" s="51" t="n"/>
+      <c r="T45" s="51" t="n"/>
+      <c r="U45" s="51" t="n"/>
+      <c r="V45" s="52" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="W45" s="58" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
         <is>
-          <t>2026/02/13（五）</t>
+          <t>2026/02/24（二）</t>
         </is>
       </c>
       <c r="B46" s="45" t="n"/>
-      <c r="C46" s="46" t="n"/>
-      <c r="D46" s="46" t="n"/>
+      <c r="C46" s="53" t="n"/>
+      <c r="D46" s="53" t="n"/>
       <c r="E46" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="F46" s="47" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="G46" s="54" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="H46" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="I46" s="49" t="n">
-        <v>32</v>
-      </c>
+        <v>30.8</v>
+      </c>
+      <c r="H46" s="49" t="n"/>
+      <c r="I46" s="49" t="n"/>
       <c r="J46" s="50" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K46" s="50" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="L46" s="50" t="n"/>
-      <c r="M46" s="51" t="n"/>
-      <c r="N46" s="51" t="n"/>
-      <c r="O46" s="51" t="n"/>
-      <c r="P46" s="51" t="n"/>
-      <c r="Q46" s="51" t="n"/>
-      <c r="R46" s="51" t="n"/>
-      <c r="S46" s="51" t="n"/>
-      <c r="T46" s="51" t="n"/>
-      <c r="U46" s="51" t="n"/>
-      <c r="V46" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W46" s="58" t="n"/>
+      <c r="M46" s="55" t="n"/>
+      <c r="N46" s="55" t="n"/>
+      <c r="O46" s="55" t="n"/>
+      <c r="P46" s="55" t="n"/>
+      <c r="Q46" s="55" t="n"/>
+      <c r="R46" s="55" t="n"/>
+      <c r="S46" s="55" t="n"/>
+      <c r="T46" s="55" t="n"/>
+      <c r="U46" s="55" t="n"/>
+      <c r="V46" s="56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W46" s="57" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>2026/02/12（四）</t>
+          <t>2026/02/13（五）</t>
         </is>
       </c>
       <c r="B47" s="45" t="n"/>
-      <c r="C47" s="53" t="n"/>
-      <c r="D47" s="53" t="n"/>
+      <c r="C47" s="46" t="n"/>
+      <c r="D47" s="46" t="n"/>
       <c r="E47" s="47" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G47" s="48" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H47" s="49" t="n"/>
-      <c r="I47" s="49" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="G47" s="54" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H47" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="I47" s="49" t="n">
+        <v>32</v>
+      </c>
       <c r="J47" s="50" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K47" s="50" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="L47" s="50" t="n"/>
-      <c r="M47" s="55" t="n"/>
-      <c r="N47" s="55" t="n"/>
-      <c r="O47" s="55" t="n"/>
-      <c r="P47" s="55" t="n"/>
-      <c r="Q47" s="55" t="n"/>
-      <c r="R47" s="55" t="n"/>
-      <c r="S47" s="55" t="n"/>
-      <c r="T47" s="55" t="n"/>
-      <c r="U47" s="55" t="n"/>
-      <c r="V47" s="56" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="W47" s="57" t="n"/>
+      <c r="M47" s="51" t="n"/>
+      <c r="N47" s="51" t="n"/>
+      <c r="O47" s="51" t="n"/>
+      <c r="P47" s="51" t="n"/>
+      <c r="Q47" s="51" t="n"/>
+      <c r="R47" s="51" t="n"/>
+      <c r="S47" s="51" t="n"/>
+      <c r="T47" s="51" t="n"/>
+      <c r="U47" s="51" t="n"/>
+      <c r="V47" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W47" s="58" t="n"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
         <is>
-          <t>2026/02/11（三）</t>
+          <t>2026/02/12（四）</t>
         </is>
       </c>
       <c r="B48" s="45" t="n"/>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
+      <c r="C48" s="53" t="n"/>
+      <c r="D48" s="53" t="n"/>
       <c r="E48" s="47" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F48" s="47" t="n">
-        <v>51</v>
-      </c>
-      <c r="G48" s="54" t="n">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="G48" s="48" t="n">
+        <v>24.1</v>
       </c>
       <c r="H48" s="49" t="n"/>
       <c r="I48" s="49" t="n"/>
       <c r="J48" s="50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K48" s="50" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="L48" s="50" t="n"/>
-      <c r="M48" s="51" t="n"/>
-      <c r="N48" s="51" t="n"/>
-      <c r="O48" s="51" t="n"/>
-      <c r="P48" s="51" t="n"/>
-      <c r="Q48" s="51" t="n"/>
-      <c r="R48" s="51" t="n"/>
-      <c r="S48" s="51" t="n"/>
-      <c r="T48" s="51" t="n"/>
-      <c r="U48" s="51" t="n"/>
-      <c r="V48" s="52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W48" s="58" t="n"/>
+      <c r="M48" s="55" t="n"/>
+      <c r="N48" s="55" t="n"/>
+      <c r="O48" s="55" t="n"/>
+      <c r="P48" s="55" t="n"/>
+      <c r="Q48" s="55" t="n"/>
+      <c r="R48" s="55" t="n"/>
+      <c r="S48" s="55" t="n"/>
+      <c r="T48" s="55" t="n"/>
+      <c r="U48" s="55" t="n"/>
+      <c r="V48" s="56" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W48" s="57" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="44" t="inlineStr">
         <is>
-          <t>2026/02/10（二）</t>
+          <t>2026/02/11（三）</t>
         </is>
       </c>
       <c r="B49" s="45" t="n"/>
-      <c r="C49" s="53" t="n"/>
-      <c r="D49" s="53" t="n"/>
+      <c r="C49" s="46" t="n"/>
+      <c r="D49" s="46" t="n"/>
       <c r="E49" s="47" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F49" s="47" t="n">
-        <v>60</v>
-      </c>
-      <c r="G49" s="48" t="n">
-        <v>11.8</v>
+        <v>51</v>
+      </c>
+      <c r="G49" s="54" t="n">
+        <v>25</v>
       </c>
       <c r="H49" s="49" t="n"/>
       <c r="I49" s="49" t="n"/>
       <c r="J49" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="K49" s="50" t="n">
         <v>29</v>
       </c>
-      <c r="K49" s="50" t="n">
-        <v>31</v>
-      </c>
       <c r="L49" s="50" t="n"/>
-      <c r="M49" s="55" t="n"/>
-      <c r="N49" s="55" t="n"/>
-      <c r="O49" s="55" t="n"/>
-      <c r="P49" s="55" t="n"/>
-      <c r="Q49" s="55" t="n"/>
-      <c r="R49" s="55" t="n"/>
-      <c r="S49" s="55" t="n"/>
-      <c r="T49" s="55" t="n"/>
-      <c r="U49" s="55" t="n"/>
-      <c r="V49" s="56" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="W49" s="57" t="n"/>
+      <c r="M49" s="51" t="n"/>
+      <c r="N49" s="51" t="n"/>
+      <c r="O49" s="51" t="n"/>
+      <c r="P49" s="51" t="n"/>
+      <c r="Q49" s="51" t="n"/>
+      <c r="R49" s="51" t="n"/>
+      <c r="S49" s="51" t="n"/>
+      <c r="T49" s="51" t="n"/>
+      <c r="U49" s="51" t="n"/>
+      <c r="V49" s="52" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W49" s="58" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="44" t="inlineStr">
         <is>
-          <t>2026/02/09（一）</t>
+          <t>2026/02/10（二）</t>
         </is>
       </c>
       <c r="B50" s="45" t="n"/>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
+      <c r="C50" s="53" t="n"/>
+      <c r="D50" s="53" t="n"/>
       <c r="E50" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F50" s="47" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G50" s="48" t="n">
-        <v>23.1</v>
+        <v>11.8</v>
       </c>
       <c r="H50" s="49" t="n"/>
       <c r="I50" s="49" t="n"/>
       <c r="J50" s="50" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K50" s="50" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L50" s="50" t="n"/>
-      <c r="M50" s="51" t="n"/>
-      <c r="N50" s="51" t="n"/>
-      <c r="O50" s="51" t="n"/>
-      <c r="P50" s="51" t="n"/>
-      <c r="Q50" s="51" t="n"/>
-      <c r="R50" s="51" t="n"/>
-      <c r="S50" s="51" t="n"/>
-      <c r="T50" s="51" t="n"/>
-      <c r="U50" s="51" t="n"/>
-      <c r="V50" s="52" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="W50" s="58" t="n"/>
+      <c r="M50" s="55" t="n"/>
+      <c r="N50" s="55" t="n"/>
+      <c r="O50" s="55" t="n"/>
+      <c r="P50" s="55" t="n"/>
+      <c r="Q50" s="55" t="n"/>
+      <c r="R50" s="55" t="n"/>
+      <c r="S50" s="55" t="n"/>
+      <c r="T50" s="55" t="n"/>
+      <c r="U50" s="55" t="n"/>
+      <c r="V50" s="56" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="W50" s="57" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="44" t="inlineStr">
         <is>
-          <t>2026/02/06（五）</t>
+          <t>2026/02/09（一）</t>
         </is>
       </c>
       <c r="B51" s="45" t="n"/>
-      <c r="C51" s="53" t="n"/>
-      <c r="D51" s="53" t="n"/>
+      <c r="C51" s="46" t="n"/>
+      <c r="D51" s="46" t="n"/>
       <c r="E51" s="47" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G51" s="54" t="n">
-        <v>32.1</v>
+        <v>83</v>
+      </c>
+      <c r="G51" s="48" t="n">
+        <v>23.1</v>
       </c>
       <c r="H51" s="49" t="n"/>
       <c r="I51" s="49" t="n"/>
       <c r="J51" s="50" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K51" s="50" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L51" s="50" t="n"/>
-      <c r="M51" s="55" t="n"/>
-      <c r="N51" s="55" t="n"/>
-      <c r="O51" s="55" t="n"/>
-      <c r="P51" s="55" t="n"/>
-      <c r="Q51" s="55" t="n"/>
-      <c r="R51" s="55" t="n"/>
-      <c r="S51" s="55" t="n"/>
-      <c r="T51" s="55" t="n"/>
-      <c r="U51" s="55" t="n"/>
-      <c r="V51" s="56" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W51" s="57" t="n"/>
+      <c r="M51" s="51" t="n"/>
+      <c r="N51" s="51" t="n"/>
+      <c r="O51" s="51" t="n"/>
+      <c r="P51" s="51" t="n"/>
+      <c r="Q51" s="51" t="n"/>
+      <c r="R51" s="51" t="n"/>
+      <c r="S51" s="51" t="n"/>
+      <c r="T51" s="51" t="n"/>
+      <c r="U51" s="51" t="n"/>
+      <c r="V51" s="52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W51" s="58" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="44" t="inlineStr">
         <is>
-          <t>2026/02/05（四）</t>
+          <t>2026/02/06（五）</t>
         </is>
       </c>
       <c r="B52" s="45" t="n"/>
-      <c r="C52" s="46" t="n"/>
-      <c r="D52" s="46" t="n"/>
+      <c r="C52" s="53" t="n"/>
+      <c r="D52" s="53" t="n"/>
       <c r="E52" s="47" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F52" s="47" t="n">
-        <v>44</v>
-      </c>
-      <c r="G52" s="48" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H52" s="49" t="n">
-        <v>44</v>
-      </c>
-      <c r="I52" s="49" t="n">
-        <v>44</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G52" s="54" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="H52" s="49" t="n"/>
+      <c r="I52" s="49" t="n"/>
       <c r="J52" s="50" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K52" s="50" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L52" s="50" t="n"/>
-      <c r="M52" s="51" t="n"/>
-      <c r="N52" s="51" t="n"/>
-      <c r="O52" s="51" t="n"/>
-      <c r="P52" s="51" t="n"/>
-      <c r="Q52" s="51" t="n"/>
-      <c r="R52" s="51" t="n"/>
-      <c r="S52" s="51" t="n"/>
-      <c r="T52" s="51" t="n"/>
-      <c r="U52" s="51" t="n"/>
-      <c r="V52" s="52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="W52" s="58" t="n"/>
+      <c r="M52" s="55" t="n"/>
+      <c r="N52" s="55" t="n"/>
+      <c r="O52" s="55" t="n"/>
+      <c r="P52" s="55" t="n"/>
+      <c r="Q52" s="55" t="n"/>
+      <c r="R52" s="55" t="n"/>
+      <c r="S52" s="55" t="n"/>
+      <c r="T52" s="55" t="n"/>
+      <c r="U52" s="55" t="n"/>
+      <c r="V52" s="56" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W52" s="57" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="44" t="inlineStr">
         <is>
-          <t>2026/02/04（三）</t>
+          <t>2026/02/05（四）</t>
         </is>
       </c>
       <c r="B53" s="45" t="n"/>
-      <c r="C53" s="53" t="n"/>
-      <c r="D53" s="53" t="n"/>
+      <c r="C53" s="46" t="n"/>
+      <c r="D53" s="46" t="n"/>
       <c r="E53" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="F53" s="47" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G53" s="48" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H53" s="49" t="n"/>
-      <c r="I53" s="49" t="n"/>
+        <v>18.5</v>
+      </c>
+      <c r="H53" s="49" t="n">
+        <v>44</v>
+      </c>
+      <c r="I53" s="49" t="n">
+        <v>44</v>
+      </c>
       <c r="J53" s="50" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K53" s="50" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L53" s="50" t="n"/>
-      <c r="M53" s="55" t="n"/>
-      <c r="N53" s="55" t="n"/>
-      <c r="O53" s="55" t="n"/>
-      <c r="P53" s="55" t="n"/>
-      <c r="Q53" s="55" t="n"/>
-      <c r="R53" s="55" t="n"/>
-      <c r="S53" s="55" t="n"/>
-      <c r="T53" s="55" t="n"/>
-      <c r="U53" s="55" t="n"/>
-      <c r="V53" s="56" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W53" s="57" t="n"/>
+      <c r="M53" s="51" t="n"/>
+      <c r="N53" s="51" t="n"/>
+      <c r="O53" s="51" t="n"/>
+      <c r="P53" s="51" t="n"/>
+      <c r="Q53" s="51" t="n"/>
+      <c r="R53" s="51" t="n"/>
+      <c r="S53" s="51" t="n"/>
+      <c r="T53" s="51" t="n"/>
+      <c r="U53" s="51" t="n"/>
+      <c r="V53" s="52" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W53" s="58" t="n"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="44" t="inlineStr">
         <is>
-          <t>2026/02/03（二）</t>
+          <t>2026/02/04（三）</t>
         </is>
       </c>
       <c r="B54" s="45" t="n"/>
-      <c r="C54" s="46" t="n"/>
-      <c r="D54" s="46" t="n"/>
+      <c r="C54" s="53" t="n"/>
+      <c r="D54" s="53" t="n"/>
       <c r="E54" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G54" s="48" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="H54" s="49" t="n"/>
       <c r="I54" s="49" t="n"/>
       <c r="J54" s="50" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K54" s="50" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L54" s="50" t="n"/>
-      <c r="M54" s="51" t="n"/>
-      <c r="N54" s="51" t="n"/>
-      <c r="O54" s="51" t="n"/>
-      <c r="P54" s="51" t="n"/>
-      <c r="Q54" s="51" t="n"/>
-      <c r="R54" s="51" t="n"/>
-      <c r="S54" s="51" t="n"/>
-      <c r="T54" s="51" t="n"/>
-      <c r="U54" s="51" t="n"/>
-      <c r="V54" s="52" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W54" s="58" t="n"/>
+      <c r="M54" s="55" t="n"/>
+      <c r="N54" s="55" t="n"/>
+      <c r="O54" s="55" t="n"/>
+      <c r="P54" s="55" t="n"/>
+      <c r="Q54" s="55" t="n"/>
+      <c r="R54" s="55" t="n"/>
+      <c r="S54" s="55" t="n"/>
+      <c r="T54" s="55" t="n"/>
+      <c r="U54" s="55" t="n"/>
+      <c r="V54" s="56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="W54" s="57" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>2026/02/02（一）</t>
+          <t>2026/02/03（二）</t>
         </is>
       </c>
       <c r="B55" s="45" t="n"/>
-      <c r="C55" s="53" t="n"/>
-      <c r="D55" s="53" t="n"/>
+      <c r="C55" s="46" t="n"/>
+      <c r="D55" s="46" t="n"/>
       <c r="E55" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="F55" s="47" t="n">
+        <v>69</v>
+      </c>
+      <c r="G55" s="48" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H55" s="49" t="n"/>
+      <c r="I55" s="49" t="n"/>
+      <c r="J55" s="50" t="n">
         <v>36</v>
       </c>
-      <c r="F55" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="G55" s="54" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H55" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="I55" s="49" t="n">
-        <v>36</v>
-      </c>
-      <c r="J55" s="50" t="n">
-        <v>14</v>
-      </c>
       <c r="K55" s="50" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L55" s="50" t="n"/>
-      <c r="M55" s="55" t="n"/>
-      <c r="N55" s="55" t="n"/>
-      <c r="O55" s="55" t="n"/>
-      <c r="P55" s="55" t="n"/>
-      <c r="Q55" s="55" t="n"/>
-      <c r="R55" s="55" t="n"/>
-      <c r="S55" s="55" t="n"/>
-      <c r="T55" s="55" t="n"/>
-      <c r="U55" s="55" t="n"/>
-      <c r="V55" s="56" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="W55" s="57" t="n"/>
+      <c r="M55" s="51" t="n"/>
+      <c r="N55" s="51" t="n"/>
+      <c r="O55" s="51" t="n"/>
+      <c r="P55" s="51" t="n"/>
+      <c r="Q55" s="51" t="n"/>
+      <c r="R55" s="51" t="n"/>
+      <c r="S55" s="51" t="n"/>
+      <c r="T55" s="51" t="n"/>
+      <c r="U55" s="51" t="n"/>
+      <c r="V55" s="52" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="W55" s="58" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="44" t="inlineStr">
         <is>
-          <t>2026/01/30（五）</t>
+          <t>2026/02/02（一）</t>
         </is>
       </c>
       <c r="B56" s="45" t="n"/>
-      <c r="C56" s="46" t="n"/>
-      <c r="D56" s="46" t="n"/>
+      <c r="C56" s="53" t="n"/>
+      <c r="D56" s="53" t="n"/>
       <c r="E56" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F56" s="47" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G56" s="54" t="n">
-        <v>30.4</v>
+        <v>33.3</v>
       </c>
       <c r="H56" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I56" s="49" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="J56" s="50" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K56" s="50" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L56" s="50" t="n"/>
-      <c r="M56" s="51" t="n"/>
-      <c r="N56" s="51" t="n"/>
-      <c r="O56" s="51" t="n"/>
-      <c r="P56" s="51" t="n"/>
-      <c r="Q56" s="51" t="n"/>
-      <c r="R56" s="51" t="n"/>
-      <c r="S56" s="51" t="n"/>
-      <c r="T56" s="51" t="n"/>
-      <c r="U56" s="51" t="n"/>
-      <c r="V56" s="52" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="W56" s="58" t="n"/>
+      <c r="M56" s="55" t="n"/>
+      <c r="N56" s="55" t="n"/>
+      <c r="O56" s="55" t="n"/>
+      <c r="P56" s="55" t="n"/>
+      <c r="Q56" s="55" t="n"/>
+      <c r="R56" s="55" t="n"/>
+      <c r="S56" s="55" t="n"/>
+      <c r="T56" s="55" t="n"/>
+      <c r="U56" s="55" t="n"/>
+      <c r="V56" s="56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="W56" s="57" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>2026/01/29（四）</t>
+          <t>2026/01/30（五）</t>
         </is>
       </c>
       <c r="B57" s="45" t="n"/>
-      <c r="C57" s="53" t="n"/>
-      <c r="D57" s="53" t="n"/>
+      <c r="C57" s="46" t="n"/>
+      <c r="D57" s="46" t="n"/>
       <c r="E57" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F57" s="47" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G57" s="54" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="H57" s="49" t="n"/>
-      <c r="I57" s="49" t="n"/>
+        <v>30.4</v>
+      </c>
+      <c r="H57" s="49" t="n">
+        <v>48</v>
+      </c>
+      <c r="I57" s="49" t="n">
+        <v>48</v>
+      </c>
       <c r="J57" s="50" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K57" s="50" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="L57" s="50" t="n"/>
-      <c r="M57" s="55" t="n"/>
-      <c r="N57" s="55" t="n"/>
-      <c r="O57" s="55" t="n"/>
-      <c r="P57" s="55" t="n"/>
-      <c r="Q57" s="55" t="n"/>
-      <c r="R57" s="55" t="n"/>
-      <c r="S57" s="55" t="n"/>
-      <c r="T57" s="55" t="n"/>
-      <c r="U57" s="55" t="n"/>
-      <c r="V57" s="56" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W57" s="57" t="n"/>
+      <c r="M57" s="51" t="n"/>
+      <c r="N57" s="51" t="n"/>
+      <c r="O57" s="51" t="n"/>
+      <c r="P57" s="51" t="n"/>
+      <c r="Q57" s="51" t="n"/>
+      <c r="R57" s="51" t="n"/>
+      <c r="S57" s="51" t="n"/>
+      <c r="T57" s="51" t="n"/>
+      <c r="U57" s="51" t="n"/>
+      <c r="V57" s="52" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="W57" s="58" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="44" t="inlineStr">
         <is>
-          <t>2026/01/28（三）</t>
+          <t>2026/01/29（四）</t>
         </is>
       </c>
       <c r="B58" s="45" t="n"/>
-      <c r="C58" s="46" t="n"/>
-      <c r="D58" s="46" t="n"/>
+      <c r="C58" s="53" t="n"/>
+      <c r="D58" s="53" t="n"/>
       <c r="E58" s="47" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F58" s="47" t="n">
-        <v>80</v>
-      </c>
-      <c r="G58" s="48" t="n">
-        <v>24.5</v>
+        <v>82</v>
+      </c>
+      <c r="G58" s="54" t="n">
+        <v>29.3</v>
       </c>
       <c r="H58" s="49" t="n"/>
       <c r="I58" s="49" t="n"/>
       <c r="J58" s="50" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K58" s="50" t="n">
         <v>31</v>
       </c>
       <c r="L58" s="50" t="n"/>
-      <c r="M58" s="51" t="n"/>
-      <c r="N58" s="51" t="n"/>
-      <c r="O58" s="51" t="n"/>
-      <c r="P58" s="51" t="n"/>
-      <c r="Q58" s="51" t="n"/>
-      <c r="R58" s="51" t="n"/>
-      <c r="S58" s="51" t="n"/>
-      <c r="T58" s="51" t="n"/>
-      <c r="U58" s="51" t="n"/>
-      <c r="V58" s="52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="W58" s="58" t="n"/>
+      <c r="M58" s="55" t="n"/>
+      <c r="N58" s="55" t="n"/>
+      <c r="O58" s="55" t="n"/>
+      <c r="P58" s="55" t="n"/>
+      <c r="Q58" s="55" t="n"/>
+      <c r="R58" s="55" t="n"/>
+      <c r="S58" s="55" t="n"/>
+      <c r="T58" s="55" t="n"/>
+      <c r="U58" s="55" t="n"/>
+      <c r="V58" s="56" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="W58" s="57" t="n"/>
     </row>
     <row r="59" ht="105" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>2026/01/27（二）</t>
+          <t>2026/01/28（三）</t>
         </is>
       </c>
       <c r="B59" s="45" t="n"/>
-      <c r="C59" s="53" t="n"/>
-      <c r="D59" s="53" t="n"/>
+      <c r="C59" s="46" t="n"/>
+      <c r="D59" s="46" t="n"/>
       <c r="E59" s="47" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="F59" s="47" t="n">
-        <v>53</v>
-      </c>
-      <c r="G59" s="54" t="n">
-        <v>25.4</v>
+        <v>80</v>
+      </c>
+      <c r="G59" s="48" t="n">
+        <v>24.5</v>
       </c>
       <c r="H59" s="49" t="n"/>
       <c r="I59" s="49" t="n"/>
       <c r="J59" s="50" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K59" s="50" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L59" s="50" t="n"/>
-      <c r="M59" s="55" t="n"/>
-      <c r="N59" s="55" t="n"/>
-      <c r="O59" s="55" t="n"/>
-      <c r="P59" s="55" t="n"/>
-      <c r="Q59" s="55" t="n"/>
-      <c r="R59" s="55" t="n"/>
-      <c r="S59" s="55" t="n"/>
-      <c r="T59" s="55" t="n"/>
-      <c r="U59" s="55" t="n"/>
-      <c r="V59" s="56" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="W59" s="57" t="n"/>
+      <c r="M59" s="51" t="n"/>
+      <c r="N59" s="51" t="n"/>
+      <c r="O59" s="51" t="n"/>
+      <c r="P59" s="51" t="n"/>
+      <c r="Q59" s="51" t="n"/>
+      <c r="R59" s="51" t="n"/>
+      <c r="S59" s="51" t="n"/>
+      <c r="T59" s="51" t="n"/>
+      <c r="U59" s="51" t="n"/>
+      <c r="V59" s="52" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="W59" s="58" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>2026/01/26（一）</t>
+          <t>2026/01/27（二）</t>
         </is>
       </c>
       <c r="B60" s="45" t="n"/>
-      <c r="C60" s="46" t="n"/>
-      <c r="D60" s="46" t="n"/>
+      <c r="C60" s="53" t="n"/>
+      <c r="D60" s="53" t="n"/>
       <c r="E60" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F60" s="47" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G60" s="54" t="n">
-        <v>35.8</v>
+        <v>25.4</v>
       </c>
       <c r="H60" s="49" t="n"/>
       <c r="I60" s="49" t="n"/>
       <c r="J60" s="50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K60" s="50" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L60" s="50" t="n"/>
-      <c r="M60" s="51" t="n"/>
-      <c r="N60" s="51" t="n"/>
